--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.08261955736578876</v>
+        <v>0.08268320268530761</v>
       </c>
       <c r="AZ2" s="12" t="n">
         <v>0.6749418153607452</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.043720531307671</v>
+        <v>3.038208683697854</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.811440556933591</v>
+        <v>2.806184372457599</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.279452054794521</v>
+        <v>3.273972602739726</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003285452753345824</v>
+        <v>0.003291413145402782</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.009073790975560776</v>
+        <v>-0.009236975335859465</v>
       </c>
       <c r="AZ3" s="12" t="n">
         <v>0.09815289219179468</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.756172097656257</v>
+        <v>1.750699546841039</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.772253152316152</v>
+        <v>1.767021480675977</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.775342465753425</v>
+        <v>1.76986301369863</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005694202756862923</v>
+        <v>0.005712002392440208</v>
       </c>
     </row>
     <row r="4">
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01751214380992983</v>
+        <v>0.01748300266381058</v>
       </c>
       <c r="AZ4" s="12" t="n">
         <v>0.1917137476459512</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.408572088428278</v>
+        <v>4.403122072273234</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.332697270738221</v>
+        <v>4.327464990319924</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.775342465753424</v>
+        <v>4.76986301369863</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002268308150443594</v>
+        <v>0.002271115775547241</v>
       </c>
     </row>
     <row r="5">
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.04162162013972666</v>
+        <v>0.04216221893268751</v>
       </c>
       <c r="AZ5" s="12" t="n">
         <v>1.659212880143112</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.3041095890410959</v>
+        <v>0.2986301369863014</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.2919578310983038</v>
+        <v>0.2865486116855572</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.2767123287671233</v>
+        <v>0.2712328767123288</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.03288288288288289</v>
+        <v>0.03348623853211009</v>
       </c>
     </row>
     <row r="6">
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1186177960633496</v>
+        <v>-0.1187210331918223</v>
       </c>
       <c r="AZ6" s="12" t="n">
         <v>0.02684444444444445</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.559365619974716</v>
+        <v>6.554061623195342</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.442135308243836</v>
+        <v>7.436988592764092</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>6.950684931506849</v>
+        <v>6.945205479452055</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001524537673208487</v>
+        <v>0.00152577143379446</v>
       </c>
     </row>
     <row r="7">
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.0595615314157825</v>
+        <v>-0.05974016890131063</v>
       </c>
       <c r="AZ7" s="12" t="n">
         <v>0.2213333333333334</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.965650627309429</v>
+        <v>1.960172486638279</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.090142729134226</v>
+        <v>2.084713631069219</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>1.947945205479452</v>
+        <v>1.942465753424657</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005087374053693327</v>
+        <v>0.005101591858964477</v>
       </c>
     </row>
     <row r="8">
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.0434371132147585</v>
+        <v>0.04369020246746916</v>
       </c>
       <c r="AZ8" s="12" t="n">
         <v>3.042809945328032</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.8876712328767125</v>
+        <v>0.8821917808219178</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.8507184780325266</v>
+        <v>0.8452621081775603</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.8602739726027397</v>
+        <v>0.8547945205479452</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01126543209876543</v>
+        <v>0.01133540372670807</v>
       </c>
     </row>
     <row r="9">
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1529121388831565</v>
+        <v>0.1532527088191327</v>
       </c>
       <c r="AZ9" s="12" t="n">
         <v>2.277267559886317</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.667453777739622</v>
+        <v>1.661960930217891</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.446297355629294</v>
+        <v>1.441107328435974</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.695890410958904</v>
+        <v>1.69041095890411</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005997167737720363</v>
+        <v>0.006016988617589798</v>
       </c>
     </row>
     <row r="10">
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.01132538237075419</v>
+        <v>-0.0113631438252168</v>
       </c>
       <c r="AZ10" s="3" t="n">
         <v>0.4327044025157232</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.128029271922316</v>
+        <v>4.122568733752124</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.175316325831207</v>
+        <v>4.169952503797093</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.284931506849315</v>
+        <v>4.279452054794521</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.00242246344230579</v>
+        <v>0.002425672110237584</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03403832509411971</v>
+        <v>0.03399955114350078</v>
       </c>
       <c r="AZ11" s="12" t="n">
         <v>0.4991128765880217</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.653691327472403</v>
+        <v>2.648220398574267</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.566337497433531</v>
+        <v>2.561142696479508</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.775342465753424</v>
+        <v>2.76986301369863</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003768335788143392</v>
+        <v>0.003776120750895107</v>
       </c>
     </row>
     <row r="12">
@@ -2111,7 +2111,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>-0.04931506849315068</v>
+        <v>-0.0547945205479452</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1290224140552754</v>
+        <v>-0.1292048653120022</v>
       </c>
       <c r="AZ13" s="12" t="n">
         <v>0.02040816326530615</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.250794660773738</v>
+        <v>4.245477083860979</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.880486856803579</v>
+        <v>4.875402852798569</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.526027397260274</v>
+        <v>4.52054794520548</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002352501308115359</v>
+        <v>0.002355447880761063</v>
       </c>
     </row>
     <row r="14">
@@ -2317,22 +2317,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1933893213127987</v>
+        <v>-0.1937136919991779</v>
       </c>
       <c r="AZ14" s="12" t="n">
         <v>0.01632310000000015</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.17251637048556</v>
+        <v>3.167146799321049</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.933144519793597</v>
+        <v>3.928067198826622</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.279452054794521</v>
+        <v>3.273972602739726</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003152071993396674</v>
+        <v>0.003157416006780529</v>
       </c>
     </row>
     <row r="15">
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1675131090723769</v>
+        <v>-0.1680461872410457</v>
       </c>
       <c r="AZ15" s="12" t="n">
         <v>0.1611175710594315</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.922825890114093</v>
+        <v>1.917472566146698</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.309737139490001</v>
+        <v>2.304782473185511</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.041095890410959</v>
+        <v>2.035616438356164</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005200678881750775</v>
+        <v>0.00521519847352796</v>
       </c>
     </row>
     <row r="16">
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.0395294956312813</v>
+        <v>-0.03971512311395421</v>
       </c>
       <c r="AZ16" s="12" t="n">
         <v>0.1401269653679655</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.777110111187416</v>
+        <v>1.771634981755567</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.850249542390106</v>
+        <v>1.844905636232155</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.775342465753425</v>
+        <v>1.76986301369863</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005627113332509417</v>
+        <v>0.005644503581708854</v>
       </c>
     </row>
     <row r="17">
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05567670138982807</v>
+        <v>0.05568640271019477</v>
       </c>
       <c r="AZ17" s="12" t="n">
         <v>0.8535888077858882</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.024231438560451</v>
+        <v>3.018746628596366</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.864732578240067</v>
+        <v>2.859510760815461</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.279452054794521</v>
+        <v>3.273972602739726</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003306625237901782</v>
+        <v>0.003312633099204395</v>
       </c>
     </row>
     <row r="18">
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1329167406430863</v>
+        <v>0.1331597716575706</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>1.745549738219896</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.748813039242917</v>
+        <v>1.743323168838557</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.543637741861087</v>
+        <v>1.53846192959043</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.775342465753425</v>
+        <v>1.76986301369863</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005718164135103387</v>
+        <v>0.005736171112016044</v>
       </c>
     </row>
     <row r="19">
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.02030846460575468</v>
+        <v>0.02026932480156678</v>
       </c>
       <c r="AZ19" s="12" t="n">
         <v>0.4834737524303305</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.215958170738824</v>
+        <v>3.210498789940575</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.151946967313913</v>
+        <v>3.146716961783584</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.441095890410959</v>
+        <v>3.435616438356164</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003109493180286805</v>
+        <v>0.003114780803323429</v>
       </c>
     </row>
     <row r="20">
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5617697488607545</v>
+        <v>-0.5631485611897022</v>
       </c>
       <c r="AZ20" s="12" t="n">
         <v>0.008979988341781375</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.453957985243766</v>
+        <v>1.448515209014694</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.317794655809322</v>
+        <v>3.315807343932569</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.438356164383562</v>
+        <v>1.432876712328767</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006877777832296463</v>
+        <v>0.006903620989110757</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3124,22 +3124,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03829610498097111</v>
+        <v>0.03830562373296448</v>
       </c>
       <c r="AZ21" s="12" t="n">
         <v>0.4119619957894736</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.8027397260273972</v>
+        <v>0.7972602739726028</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.7731317898395748</v>
+        <v>0.767847400369706</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.7753424657534247</v>
+        <v>0.7698630136986301</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01245733788395905</v>
+        <v>0.01254295532646048</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.08254439228176888</v>
+        <v>0.08258350038318134</v>
       </c>
       <c r="AZ22" s="12" t="n">
         <v>0.1118753092528451</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.859451438626711</v>
+        <v>1.853961480687864</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.717667609646373</v>
+        <v>1.712534395759452</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.041095890410959</v>
+        <v>2.035616438356164</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005377930174603244</v>
+        <v>0.005393855322328359</v>
       </c>
     </row>
     <row r="23">
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02238235181110175</v>
+        <v>0.02240400785721699</v>
       </c>
       <c r="AZ23" s="12" t="n">
         <v>0.538010018438382</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.342436172466027</v>
+        <v>4.336953443792852</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.24737004191593</v>
+        <v>4.241917490994935</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.367123287671233</v>
+        <v>4.361643835616438</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002302854803809609</v>
+        <v>0.002305766047434111</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1743645407492142</v>
+        <v>0.1745581673007211</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.4951934058064515</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.927681811421254</v>
+        <v>2.922075572571685</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.492992345931587</v>
+        <v>2.487808312879875</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.279452054794521</v>
+        <v>3.273972602739726</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003415671730783293</v>
+        <v>0.00342222497387332</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.2489760718656629</v>
+        <v>0.2493095995674254</v>
       </c>
       <c r="AZ25" s="12" t="n">
         <v>1.017301038062284</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.907566957686703</v>
+        <v>2.901870034904349</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.327960497548615</v>
+        <v>2.322778945994752</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.279452054794521</v>
+        <v>3.273972602739726</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003439301706728751</v>
+        <v>0.003446053710096503</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3699,22 +3699,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>67.43676874073606</v>
+        <v>68.59019802827143</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.3966249999999998</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.304109589041096</v>
+        <v>0.2986301369863013</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.004443657914259164</v>
+        <v>0.004291267239460664</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.2767123287671233</v>
+        <v>0.2712328767123288</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.03288288288288287</v>
+        <v>0.0334862385321101</v>
       </c>
     </row>
     <row r="27">
@@ -3808,22 +3808,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05368303438279184</v>
+        <v>0.05417010269804687</v>
       </c>
       <c r="AZ27" s="12" t="n">
         <v>0.542103365079365</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.2986301369863014</v>
+        <v>0.2931506849315069</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.2834155312761847</v>
+        <v>0.2780866998420994</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.2767123287671233</v>
+        <v>0.2712328767123288</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.03348623853211009</v>
+        <v>0.03411214953271028</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3938,7 +3938,7 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-2.616921254488378</v>
+        <v>-2.664974578356107</v>
       </c>
       <c r="AZ28" s="12" t="n">
         <v>0.05728412458498044</v>
@@ -3946,7 +3946,7 @@
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.2767123287671233</v>
+        <v>0.2712328767123288</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1571468415599019</v>
+        <v>-0.1574865595387808</v>
       </c>
       <c r="AZ29" s="12" t="n">
         <v>0.2083831884057969</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.702370351785959</v>
+        <v>2.696952678367188</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.206217268957434</v>
+        <v>3.201079708462323</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.775342465753424</v>
+        <v>2.76986301369863</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003700455044361754</v>
+        <v>0.003707888566311176</v>
       </c>
     </row>
     <row r="30">
@@ -4189,22 +4189,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05530285603132896</v>
+        <v>0.05530148308972638</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.6507586360555744</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.648992167425987</v>
+        <v>2.643513020362766</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.510172461190938</v>
+        <v>2.504983706289365</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.775342465753424</v>
+        <v>2.76986301369863</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003775020599519912</v>
+        <v>0.003782844995644361</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1166994052024226</v>
+        <v>0.1168187008761466</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.50754899939577</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.183858183154455</v>
+        <v>2.178348445335936</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.955636559830163</v>
+        <v>1.950494241927555</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.347945205479452</v>
+        <v>2.342465753424658</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004579051916986472</v>
+        <v>0.004590633799386416</v>
       </c>
     </row>
     <row r="32">
@@ -4412,22 +4412,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.272028260600055</v>
+        <v>-0.2728528560788701</v>
       </c>
       <c r="AZ32" s="12" t="n">
         <v>0.1146548012056838</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.646736277196668</v>
+        <v>1.6412868371938</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.262088193909898</v>
+        <v>2.257159160858675</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.649315068493151</v>
+        <v>1.643835616438356</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.006072617782504654</v>
+        <v>0.006092780234012942</v>
       </c>
     </row>
     <row r="33">
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.1098096917643928</v>
+        <v>-0.1100844536724899</v>
       </c>
       <c r="AZ33" s="12" t="n">
         <v>0.005948460987831083</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.684113632300835</v>
+        <v>2.678689892263281</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>3.015213272340445</v>
+        <v>3.010049552811677</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.775342465753424</v>
+        <v>2.76986301369863</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003725624682822371</v>
+        <v>0.003733168228574152</v>
       </c>
     </row>
     <row r="34">
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.02979840968069481</v>
+        <v>0.02975117298677777</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.29111266620014</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.678085569582806</v>
+        <v>1.672607982568473</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.629528220094186</v>
+        <v>1.624283639043691</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.695890410958904</v>
+        <v>1.69041095890411</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.00595917167828702</v>
+        <v>0.005978687238263626</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.08268320268530761</v>
+        <v>0.08271512196505244</v>
       </c>
       <c r="AZ2" s="12" t="n">
         <v>0.6749418153607452</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.038208683697854</v>
+        <v>3.035452709918621</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.806184372457599</v>
+        <v>2.80355621560867</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.273972602739726</v>
+        <v>3.271232876712329</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003291413145402782</v>
+        <v>0.003294401512935477</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9823</v>
+        <v>9737</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.009236975335859465</v>
+        <v>-0.009318928716467676</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.09815289219179468</v>
+        <v>0.1078520961281708</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.750699546841039</v>
+        <v>1.747963286746559</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.767021480675977</v>
+        <v>1.764405657293812</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.76986301369863</v>
+        <v>1.767123287671233</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005712002392440208</v>
+        <v>0.005720943955643803</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>113</v>
+        <v>113.2</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01748300266381058</v>
+        <v>0.01706306207265681</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.1917137476459512</v>
+        <v>0.1938229755178908</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.403122072273234</v>
+        <v>4.400806383572784</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.327464990319924</v>
+        <v>4.326974941558146</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.76986301369863</v>
+        <v>4.767123287671233</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002271115775547241</v>
+        <v>0.00227231082860808</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6149</v>
+        <v>6148</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.04216221893268751</v>
+        <v>0.04244003775595155</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.659212880143112</v>
+        <v>1.659645413142485</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.2986301369863014</v>
+        <v>0.2958904109589041</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.2865486116855572</v>
+        <v>0.2838440584034588</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.2712328767123288</v>
+        <v>0.2684931506849315</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.03348623853211009</v>
+        <v>0.0337962962962963</v>
       </c>
     </row>
     <row r="6">
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>22500</v>
+        <v>22120</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1187210331918223</v>
+        <v>-0.1187727106458985</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02684444444444445</v>
+        <v>0.04448462929475583</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.554061623195342</v>
+        <v>6.551409702638343</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.436988592764092</v>
+        <v>7.434415367958272</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>6.945205479452055</v>
+        <v>6.942465753424657</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.00152577143379446</v>
+        <v>0.001526389045089466</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22500</v>
+        <v>22120</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05974016890131063</v>
+        <v>-0.05982984961643226</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2213333333333334</v>
+        <v>0.2423146473779385</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.960172486638279</v>
+        <v>1.957433418961262</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.084713631069219</v>
+        <v>2.081999112780462</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>1.942465753424657</v>
+        <v>1.93972602739726</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005101591858964477</v>
+        <v>0.005108730597491604</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2012</v>
+        <v>1956</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04369020246746916</v>
+        <v>0.04381792993224948</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.042809945328032</v>
+        <v>3.158555015337424</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.8821917808219178</v>
+        <v>0.8794520547945205</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.8452621081775603</v>
+        <v>0.842533960737389</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.8547945205479452</v>
+        <v>0.852054794520548</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01133540372670807</v>
+        <v>0.01137071651090343</v>
       </c>
     </row>
     <row r="9">
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>246.3</v>
+        <v>250</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1532527088191327</v>
+        <v>0.1534238980651479</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.277267559886317</v>
+        <v>2.228764</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.661960930217891</v>
+        <v>1.659214471031818</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.441107328435974</v>
+        <v>1.438512305679747</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.69041095890411</v>
+        <v>1.687671232876712</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006016988617589798</v>
+        <v>0.006026948399130878</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12720</v>
+        <v>12650</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.0113631438252168</v>
+        <v>-0.0113820607997417</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4327044025157232</v>
+        <v>0.4406324110671938</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.122568733752124</v>
+        <v>4.119838482280837</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.169952503797093</v>
+        <v>4.167270609729758</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.279452054794521</v>
+        <v>4.276712328767124</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002425672110237584</v>
+        <v>0.002427279623463241</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03399955114350078</v>
+        <v>0.03398011624199031</v>
       </c>
       <c r="AZ11" s="12" t="n">
         <v>0.4991128765880217</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.648220398574267</v>
+        <v>2.645484944597639</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.561142696479508</v>
+        <v>2.558545278619744</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.76986301369863</v>
+        <v>2.767123287671233</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003776120750895107</v>
+        <v>0.003780025291930336</v>
       </c>
     </row>
     <row r="12">
@@ -2111,7 +2111,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>-0.0547945205479452</v>
+        <v>-0.05753424657534247</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>225</v>
+        <v>222.3</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>220.5</v>
+        <v>219.7</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1292048653120022</v>
+        <v>-0.1268420572622477</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.02040816326530615</v>
+        <v>0.01183431952662728</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.245477083860979</v>
+        <v>4.240636629461016</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.875402852798569</v>
+        <v>4.856666156142</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.52054794520548</v>
+        <v>4.517808219178082</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002355447880761063</v>
+        <v>0.002358136495479689</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>250</v>
+        <v>249.9</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2317,22 +2317,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1937136919991779</v>
+        <v>-0.1938762443979485</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.01632310000000015</v>
+        <v>0.01672979191676682</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.167146799321049</v>
+        <v>3.164462117537143</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.928067198826622</v>
+        <v>3.925528922260543</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.273972602739726</v>
+        <v>3.271232876712329</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003157416006780529</v>
+        <v>0.003160094710750673</v>
       </c>
     </row>
     <row r="15">
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>77.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1680461872410457</v>
+        <v>-0.1683137203804096</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1611175710594315</v>
+        <v>0.09731990231990229</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.917472566146698</v>
+        <v>1.914796123587026</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.304782473185511</v>
+        <v>2.302305773834391</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.035616438356164</v>
+        <v>2.032876712328767</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.00521519847352796</v>
+        <v>0.005222488116002031</v>
       </c>
     </row>
     <row r="16">
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18480</v>
+        <v>18390</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.03971512311395421</v>
+        <v>-0.03980835140533329</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1401269653679655</v>
+        <v>0.1457067058183796</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.771634981755567</v>
+        <v>1.768897426707509</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.844905636232155</v>
+        <v>1.842233713755438</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.76986301369863</v>
+        <v>1.767123287671233</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005644503581708854</v>
+        <v>0.00565323904541669</v>
       </c>
     </row>
     <row r="17">
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05568640271019477</v>
+        <v>0.05569127613617968</v>
       </c>
       <c r="AZ17" s="12" t="n">
         <v>0.8535888077858882</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.018746628596366</v>
+        <v>3.016004211021325</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.859510760815461</v>
+        <v>2.856899814555514</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.273972602739726</v>
+        <v>3.271232876712329</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003312633099204395</v>
+        <v>0.003315645237979839</v>
       </c>
     </row>
     <row r="18">
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1331597716575706</v>
+        <v>0.1332819046315776</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>1.745549738219896</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.743323168838557</v>
+        <v>1.740578207252948</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.53846192959043</v>
+        <v>1.535873995816423</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.76986301369863</v>
+        <v>1.767123287671233</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005736171112016044</v>
+        <v>0.005745217283733784</v>
       </c>
     </row>
     <row r="19">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>154.3</v>
+        <v>152</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.02026932480156678</v>
+        <v>0.02024971190493471</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4834737524303305</v>
+        <v>0.5059210526315789</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.210498789940575</v>
+        <v>3.207769121268711</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.146716961783584</v>
+        <v>3.144101962331753</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.435616438356164</v>
+        <v>3.432876712328767</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003114780803323429</v>
+        <v>0.003117431343077734</v>
       </c>
     </row>
     <row r="20">
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27620</v>
+        <v>27690</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5631485611897022</v>
+        <v>-0.5638402332481854</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.008979988341781375</v>
+        <v>0.006429298591549282</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.448515209014694</v>
+        <v>1.445793882197358</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.315807343932569</v>
+        <v>3.314826337524273</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.432876712328767</v>
+        <v>1.43013698630137</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006903620989110757</v>
+        <v>0.006916615240342363</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>475</v>
+        <v>470.3</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3124,22 +3124,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03830562373296448</v>
+        <v>0.03831046980256778</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.4119619957894736</v>
+        <v>0.4260726089729958</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.7972602739726028</v>
+        <v>0.7945205479452054</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.767847400369706</v>
+        <v>0.7652051780776915</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.7698630136986301</v>
+        <v>0.7671232876712328</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01254295532646048</v>
+        <v>0.01258620689655172</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>97.7</v>
+        <v>98</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.08258350038318134</v>
+        <v>0.08092618985831926</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1118753092528451</v>
+        <v>0.1152894606630379</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.853961480687864</v>
+        <v>1.851666823597571</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.712534395759452</v>
+        <v>1.713037246178923</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.035616438356164</v>
+        <v>2.032876712328767</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005393855322328359</v>
+        <v>0.005400539596303385</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10630</v>
+        <v>10670</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02240400785721699</v>
+        <v>0.02241485666917468</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.538010018438382</v>
+        <v>0.5322442826616682</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.336953443792852</v>
+        <v>4.334212076252138</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.241917490994935</v>
+        <v>4.239191212823475</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.361643835616438</v>
+        <v>4.358904109589041</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002305766047434111</v>
+        <v>0.002307224432969408</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1745581673007211</v>
+        <v>0.1746552923326495</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.4951934058064515</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.922075572571685</v>
+        <v>2.919272241797438</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.487808312879875</v>
+        <v>2.48521609773732</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.273972602739726</v>
+        <v>3.271232876712329</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.00342222497387332</v>
+        <v>0.003425511282169029</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>28.9</v>
+        <v>28</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.2493095995674254</v>
+        <v>0.2494769108931565</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>1.017301038062284</v>
+        <v>1.082142857142857</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.901870034904349</v>
+        <v>2.899021196941307</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.322778945994752</v>
+        <v>2.320187889561734</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.273972602739726</v>
+        <v>3.271232876712329</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003446053710096503</v>
+        <v>0.003449440111217806</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3699,22 +3699,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>68.59019802827143</v>
+        <v>69.18300653594773</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.3966249999999998</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.2986301369863013</v>
+        <v>0.2958904109589042</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.004291267239460664</v>
+        <v>0.004215983691256503</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.2712328767123288</v>
+        <v>0.2684931506849315</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.0334862385321101</v>
+        <v>0.03379629629629629</v>
       </c>
     </row>
     <row r="27">
@@ -3808,22 +3808,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05417010269804687</v>
+        <v>0.05442058756680161</v>
       </c>
       <c r="AZ27" s="12" t="n">
         <v>0.542103365079365</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.2931506849315069</v>
+        <v>0.2904109589041096</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.2780866998420994</v>
+        <v>0.275422314708656</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.2712328767123288</v>
+        <v>0.2684931506849315</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.03411214953271028</v>
+        <v>0.03443396226415094</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12650</v>
+        <v>12760</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3938,15 +3938,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-2.664974578356107</v>
+        <v>-2.689668646097396</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.05728412458498044</v>
+        <v>0.04816960626959266</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.2712328767123288</v>
+        <v>0.2684931506849315</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>17250</v>
+        <v>16920</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1574865595387808</v>
+        <v>-0.1576568795749231</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.2083831884057969</v>
+        <v>0.2319509456264774</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.696952678367188</v>
+        <v>2.694243920063763</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.201079708462323</v>
+        <v>3.198511217975105</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.76986301369863</v>
+        <v>2.767123287671233</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003707888566311176</v>
+        <v>0.003711616429949422</v>
       </c>
     </row>
     <row r="30">
@@ -4189,22 +4189,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05530148308972638</v>
+        <v>0.05530080782280266</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.6507586360555744</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.643513020362766</v>
+        <v>2.640773444342202</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.504983706289365</v>
+        <v>2.50238929484987</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.76986301369863</v>
+        <v>2.767123287671233</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003782844995644361</v>
+        <v>0.003786769372974716</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4286,7 +4286,7 @@
         <v>0.9284102</v>
       </c>
       <c r="AJ31" t="n">
-        <v>33.1</v>
+        <v>33</v>
       </c>
       <c r="AK31" s="10" t="n">
         <v>47133</v>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1168187008761466</v>
+        <v>0.1168786061321426</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>1.50754899939577</v>
+        <v>1.515147632727273</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.178348445335936</v>
+        <v>2.175593510519608</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.950494241927555</v>
+        <v>1.947922986951909</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.342465753424658</v>
+        <v>2.33972602739726</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004590633799386416</v>
+        <v>0.004596446878356266</v>
       </c>
     </row>
     <row r="32">
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>69670</v>
+        <v>69000</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4412,22 +4412,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2728528560788701</v>
+        <v>-0.2732668611937489</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1146548012056838</v>
+        <v>0.1254782608695653</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.6412868371938</v>
+        <v>1.638562180032464</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.257159160858675</v>
+        <v>2.254695833361893</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.643835616438356</v>
+        <v>1.641095890410959</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.006092780234012942</v>
+        <v>0.006102911517097187</v>
       </c>
     </row>
     <row r="33">
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.1100844536724899</v>
+        <v>-0.1102222180299785</v>
       </c>
       <c r="AZ33" s="12" t="n">
         <v>0.005948460987831083</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.678689892263281</v>
+        <v>2.675978096395653</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>3.010049552811677</v>
+        <v>3.007467876384681</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.76986301369863</v>
+        <v>2.767123287671233</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003733168228574152</v>
+        <v>0.003736951364986609</v>
       </c>
     </row>
     <row r="34">
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.02975117298677777</v>
+        <v>0.02972745228127878</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.29111266620014</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.672607982568473</v>
+        <v>1.669869193105457</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.624283639043691</v>
+        <v>1.621661333206176</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.69041095890411</v>
+        <v>1.687671232876712</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005978687238263626</v>
+        <v>0.005988493015673275</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>902.3</v>
+        <v>912</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.08271512196505244</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.6749418153607452</v>
+        <v>0.6571271929824563</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.035452709918621</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9737</v>
+        <v>9662</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.009318928716467676</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1078520961281708</v>
+        <v>0.1164516518319187</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.747963286746559</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>113.2</v>
+        <v>113</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>106.2</v>
+        <v>104.1</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01706306207265681</v>
+        <v>0.01746840950546664</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.1938229755178908</v>
+        <v>0.2157540826128725</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.400806383572784</v>
+        <v>4.400397086499002</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.326974941558146</v>
+        <v>4.324848855639443</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.767123287671233</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.00227231082860808</v>
+        <v>0.002272522184573142</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6148</v>
+        <v>6146</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.04244003775595155</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.659645413142485</v>
+        <v>1.660510901399284</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2958904109589041</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>288.8</v>
+        <v>289.9</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>22120</v>
+        <v>22510</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1187727106458985</v>
+        <v>-0.1192836324469424</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.04448462929475583</v>
+        <v>0.03029764549089298</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.551409702638343</v>
+        <v>6.552277014224546</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.434415367958272</v>
+        <v>7.439713005935265</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.942465753424657</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001526389045089466</v>
+        <v>0.00152618700007504</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22120</v>
+        <v>22510</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.05982984961643226</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2423146473779385</v>
+        <v>0.2207907596623724</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.957433418961262</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1956</v>
+        <v>1930</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04381792993224948</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.158555015337424</v>
+        <v>3.214577</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8794520547945205</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1534238980651479</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.228764</v>
+        <v>2.434855319148936</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.659214471031818</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>113.9</v>
+        <v>111.2</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12650</v>
+        <v>12600</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.0113820607997417</v>
+        <v>-0.00567795396056388</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4406324110671938</v>
+        <v>0.412063492063492</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.119838482280837</v>
+        <v>4.116965173683212</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.167270609729758</v>
+        <v>4.140474597824545</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.276712328767124</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002427279623463241</v>
+        <v>0.002428973668255147</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105.5</v>
+        <v>104.6</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1102</v>
+        <v>1093</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03398011624199031</v>
+        <v>0.03729879054376263</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4991128765880217</v>
+        <v>0.4985629533394325</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.645484944597639</v>
+        <v>2.644754851111895</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.558545278619744</v>
+        <v>2.549655774422996</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.767123287671233</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003780025291930336</v>
+        <v>0.003781068780645529</v>
       </c>
     </row>
     <row r="12">
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222.3</v>
+        <v>218.3</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>219.7</v>
+        <v>217.6</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1268420572622477</v>
+        <v>-0.123136060888477</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.01183431952662728</v>
+        <v>0.003216911764706065</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.240636629461016</v>
+        <v>4.237322529285271</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.856666156142</v>
+        <v>4.832360347237807</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.517808219178082</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002358136495479689</v>
+        <v>0.002359980844244761</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>249.9</v>
+        <v>249.1</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1938762443979485</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.01672979191676682</v>
+        <v>0.01999508229626668</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.164462117537143</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>81.90000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2429,7 +2429,7 @@
         <v>-0.1683137203804096</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.09731990231990229</v>
+        <v>0.1040601965601966</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.914796123587026</v>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>112.3</v>
+        <v>111.8</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18390</v>
+        <v>18340</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.03980835140533329</v>
+        <v>-0.03739426124689962</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1457067058183796</v>
+        <v>0.1437152191930209</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.768897426707509</v>
+        <v>1.768841213621174</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.842233713755438</v>
+        <v>1.837555234100745</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.767123287671233</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.00565323904541669</v>
+        <v>0.005653418703156508</v>
       </c>
     </row>
     <row r="17">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>152</v>
+        <v>153.2</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.02024971190493471</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5059210526315789</v>
+        <v>0.4941253263707572</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.207769121268711</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27690</v>
+        <v>27980</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5638402332481854</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.006429298591549282</v>
+        <v>-0.004001884274481671</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.445793882197358</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>470.3</v>
+        <v>469.8</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03831046980256778</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.4260726089729958</v>
+        <v>0.4275903533418475</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7945205479452054</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>202.1</v>
+        <v>204.9</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3262,7 +3262,7 @@
         <v>0.08092618985831926</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1152894606630379</v>
+        <v>0.1000488042947778</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.851666823597571</v>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>92.8</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10670</v>
+        <v>10650</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02241485666917468</v>
+        <v>0.02343099622158679</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5322442826616682</v>
+        <v>0.5285048326760564</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.334212076252138</v>
+        <v>4.334058152263212</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.239191212823475</v>
+        <v>4.234831823800683</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.358904109589041</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002307224432969408</v>
+        <v>0.002307306373999176</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>31</v>
+        <v>33.5</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3480,7 +3480,7 @@
         <v>0.1746552923326495</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.4951934058064515</v>
+        <v>0.3836118083582087</v>
       </c>
       <c r="BA24" s="8" t="n">
         <v>2.919272241797438</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>28</v>
+        <v>28.7</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3589,7 +3589,7 @@
         <v>0.2494769108931565</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>1.082142857142857</v>
+        <v>1.031358885017422</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>2.899021196941307</v>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1197</v>
+        <v>1186</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.05442058756680161</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.542103365079365</v>
+        <v>0.556406178752108</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2904109589041096</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12760</v>
+        <v>12800</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-2.689668646097396</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.04816960626959266</v>
+        <v>0.04489407625000008</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>16920</v>
+        <v>16900</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.1576568795749231</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.2319509456264774</v>
+        <v>0.2334088757396449</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.694243920063763</v>
@@ -4286,7 +4286,7 @@
         <v>0.9284102</v>
       </c>
       <c r="AJ31" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="AK31" s="10" t="n">
         <v>47133</v>
@@ -4306,7 +4306,7 @@
         <v>0.1168786061321426</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>1.515147632727273</v>
+        <v>0.9761874257142857</v>
       </c>
       <c r="BA31" s="8" t="n">
         <v>2.175593510519608</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>69000</v>
+        <v>69510</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2732668611937489</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1254782608695653</v>
+        <v>0.1172205438066465</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.638562180032464</v>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102.5</v>
+        <v>102</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.02972745228127878</v>
+        <v>0.03270958506956264</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.29111266620014</v>
+        <v>0.2848145556333099</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.669869193105457</v>
+        <v>1.669751463947399</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.621661333206176</v>
+        <v>1.616864497132488</v>
       </c>
       <c r="BC34" s="8" t="n">
         <v>1.687671232876712</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005988493015673275</v>
+        <v>0.005988915246320169</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>88.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>912</v>
+        <v>885.1</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.08271512196505244</v>
+        <v>0.09099510789962488</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.6571271929824563</v>
+        <v>0.6671562535306743</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.035452709918621</v>
+        <v>3.031220075669391</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.80355621560867</v>
+        <v>2.778399328943896</v>
       </c>
       <c r="BC2" s="8" t="n">
         <v>3.271232876712329</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003294401512935477</v>
+        <v>0.003299001639724782</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9662</v>
+        <v>9661</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.009318928716467676</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1164516518319187</v>
+        <v>0.1165672145740606</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.747963286746559</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>113</v>
+        <v>112.7</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01746840950546664</v>
+        <v>0.01807814153258816</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2157540826128725</v>
+        <v>0.2125264169068206</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.400397086499002</v>
+        <v>4.399780918338722</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.324848855639443</v>
+        <v>4.321653455515121</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.767123287671233</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002272522184573142</v>
+        <v>0.002272840440377159</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6146</v>
+        <v>6133</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.04244003775595155</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.660510901399284</v>
+        <v>1.666150334257296</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2958904109589041</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>22510</v>
+        <v>22310</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.1192836324469424</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.03029764549089298</v>
+        <v>0.03953384132675941</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.552277014224546</v>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>114.5</v>
+        <v>114.3</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22510</v>
+        <v>22310</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05982984961643226</v>
+        <v>-0.05898997058033848</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2207907596623724</v>
+        <v>0.2295831465710443</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.957433418961262</v>
+        <v>1.957427253403653</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.081999112780462</v>
+        <v>2.08013431547678</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>1.93972602739726</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005108730597491604</v>
+        <v>0.005108746689110209</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1930</v>
+        <v>1912</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04381792993224948</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.214577</v>
+        <v>3.254253980125523</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8794520547945205</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1534238980651479</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.434855319148936</v>
+        <v>2.294657142857143</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.659214471031818</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>111.2</v>
+        <v>111</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12600</v>
+        <v>12560</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.00567795396056388</v>
+        <v>-0.005248515458094492</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.412063492063492</v>
+        <v>0.4140127388535031</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.116965173683212</v>
+        <v>4.116747519001145</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.140474597824545</v>
+        <v>4.13846833402511</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.276712328767124</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002428973668255147</v>
+        <v>0.002429102089415073</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>104.6</v>
+        <v>105</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03729879054376263</v>
+        <v>0.03581892352065712</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4985629533394325</v>
+        <v>0.4988084776663628</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.644754851111895</v>
+        <v>2.645080565395712</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.549655774422996</v>
+        <v>2.553612900221321</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.767123287671233</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003781068780645529</v>
+        <v>0.003780603181175303</v>
       </c>
     </row>
     <row r="12">
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>218.3</v>
+        <v>220.1</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>217.6</v>
+        <v>216.5</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.123136060888477</v>
+        <v>-0.1248143012173981</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.003216911764706065</v>
+        <v>0.01662817551963047</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.237322529285271</v>
+        <v>4.23882620301621</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.832360347237807</v>
+        <v>4.843344914013664</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.517808219178082</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002359980844244761</v>
+        <v>0.00235914366880254</v>
       </c>
     </row>
     <row r="14">
@@ -2246,7 +2246,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>224.9</v>
+        <v>224.2</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>249.1</v>
+        <v>252.5</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2317,22 +2317,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1938762443979485</v>
+        <v>-0.1930915449093849</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.01999508229626668</v>
+        <v>0.003128514851485242</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.164462117537143</v>
+        <v>3.164196272268881</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.925528922260543</v>
+        <v>3.92138197624109</v>
       </c>
       <c r="BC14" s="8" t="n">
         <v>3.271232876712329</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003160094710750673</v>
+        <v>0.00316036021141935</v>
       </c>
     </row>
     <row r="15">
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>81.40000000000001</v>
+        <v>78</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2429,7 +2429,7 @@
         <v>-0.1683137203804096</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1040601965601966</v>
+        <v>0.1521858974358976</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.914796123587026</v>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>111.8</v>
+        <v>113.4</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18340</v>
+        <v>18620</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.03739426124689962</v>
+        <v>-0.0450606036981257</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1437152191930209</v>
+        <v>0.1426383759398497</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.768841213621174</v>
+        <v>1.769019749919071</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.837555234100745</v>
+        <v>1.852494259604146</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.767123287671233</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005653418703156508</v>
+        <v>0.005652848138330552</v>
       </c>
     </row>
     <row r="17">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>98.3</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>82.2</v>
+        <v>82</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05569127613617968</v>
+        <v>0.05880444016037616</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8535888077858882</v>
+        <v>0.8410975609756102</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.016004211021325</v>
+        <v>3.014282142162941</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.856899814555514</v>
+        <v>2.846873348685967</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.271232876712329</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003315645237979839</v>
+        <v>0.003317539476521717</v>
       </c>
     </row>
     <row r="18">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>153.2</v>
+        <v>153.6</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.02024971190493471</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4941253263707572</v>
+        <v>0.490234375</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.207769121268711</v>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>347.1</v>
+        <v>357.1</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5638402332481854</v>
+        <v>-0.5722883226016878</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.004001884274481671</v>
+        <v>0.02469296204431748</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.445793882197358</v>
+        <v>1.446018665631005</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.314826337524273</v>
+        <v>3.380825780644706</v>
       </c>
       <c r="BC20" s="8" t="n">
         <v>1.43013698630137</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006916615240342363</v>
+        <v>0.006915540053306475</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>469.8</v>
+        <v>462.5</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03831046980256778</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.4275903533418475</v>
+        <v>0.4501231308108107</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7945205479452054</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>98</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>204.9</v>
+        <v>205.7</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.08092618985831926</v>
+        <v>0.08148431513294861</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1000488042947778</v>
+        <v>0.09465240641711237</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.851666823597571</v>
+        <v>1.851516973084544</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.713037246178923</v>
+        <v>1.712014633200607</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>2.032876712328767</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005400539596303385</v>
+        <v>0.005400976683103503</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10650</v>
+        <v>10470</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.02343099622158679</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5285048326760564</v>
+        <v>0.5547828527220631</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.334058152263212</v>
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>33.5</v>
+        <v>34.9</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3480,7 +3480,7 @@
         <v>0.1746552923326495</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.3836118083582087</v>
+        <v>0.3281087558739255</v>
       </c>
       <c r="BA24" s="8" t="n">
         <v>2.919272241797438</v>
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>58.3</v>
+        <v>56.8</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>28.7</v>
+        <v>28.4</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.2494769108931565</v>
+        <v>0.2601213400640637</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>1.031358885017422</v>
+        <v>1</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.899021196941307</v>
+        <v>2.892052642536901</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.320187889561734</v>
+        <v>2.295058857101707</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.271232876712329</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003449440111217806</v>
+        <v>0.003457751720324159</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1186</v>
+        <v>1194</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.05442058756680161</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.556406178752108</v>
+        <v>0.5459779966499161</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2904109589041096</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12800</v>
+        <v>12610</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-2.689668646097396</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.04489407625000008</v>
+        <v>0.06063792038065041</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>16900</v>
+        <v>16780</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.1576568795749231</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.2334088757396449</v>
+        <v>0.2422294398092966</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.694243920063763</v>
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>590.2</v>
+        <v>576.1</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4192,7 +4192,7 @@
         <v>0.05530080782280266</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.6507586360555744</v>
+        <v>0.6911608175663948</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.640773444342202</v>
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>89.40000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -4286,7 +4286,7 @@
         <v>0.9284102</v>
       </c>
       <c r="AJ31" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="AK31" s="10" t="n">
         <v>47133</v>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1168786061321426</v>
+        <v>0.1060649393988121</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>0.9761874257142857</v>
+        <v>1.175812622564103</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.175593510519608</v>
+        <v>2.178332845014415</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.947922986951909</v>
+        <v>1.96944389738854</v>
       </c>
       <c r="BC31" s="8" t="n">
         <v>2.33972602739726</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004596446878356266</v>
+        <v>0.00459066667561257</v>
       </c>
     </row>
     <row r="32">
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>69510</v>
+        <v>70310</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2732668611937489</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1172205438066465</v>
+        <v>0.1045086047503911</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.638562180032464</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>86.8</v>
+        <v>85.7</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>885.1</v>
+        <v>877.7</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.09099510789962488</v>
+        <v>0.09548281986288594</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.6671562535306743</v>
+        <v>0.6599065740002279</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.031220075669391</v>
+        <v>3.026171408193248</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.778399328943896</v>
+        <v>2.762408824058065</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.271232876712329</v>
+        <v>3.268493150684932</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003299001639724782</v>
+        <v>0.003304505479407203</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9661</v>
+        <v>9530</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.009318928716467676</v>
+        <v>-0.009401124371027371</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1165672145740606</v>
+        <v>0.1319156201469045</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.747963286746559</v>
+        <v>1.745227036923449</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.764405657293812</v>
+        <v>1.761789842346966</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.767123287671233</v>
+        <v>1.764383561643836</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005720943955643803</v>
+        <v>0.005729913523244728</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112.7</v>
+        <v>113</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>104.1</v>
+        <v>104</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01807814153258816</v>
+        <v>0.01745380125246476</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2125264169068206</v>
+        <v>0.216923076923077</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.399780918338722</v>
+        <v>4.397672115630404</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.321653455515121</v>
+        <v>4.322232724686821</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.767123287671233</v>
+        <v>4.764383561643836</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002272840440377159</v>
+        <v>0.002273930328834101</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6133</v>
+        <v>6110</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.04244003775595155</v>
+        <v>0.04272305692946612</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.666150334257296</v>
+        <v>1.676186579378069</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.2958904109589041</v>
+        <v>0.2931506849315069</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.2838440584034588</v>
+        <v>0.281139544180365</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.2684931506849315</v>
+        <v>0.2657534246575343</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.0337962962962963</v>
+        <v>0.03411214953271027</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>289.9</v>
+        <v>290.4</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>22310</v>
+        <v>21530</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1192836324469424</v>
+        <v>-0.1195670551433581</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.03953384132675941</v>
+        <v>0.079052484904784</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.552277014224546</v>
+        <v>6.550017785073059</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.439713005935265</v>
+        <v>7.439541901898704</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>6.942465753424657</v>
+        <v>6.93972602739726</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.00152618700007504</v>
+        <v>0.001526713411800066</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>114.3</v>
+        <v>113</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22310</v>
+        <v>21530</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05898997058033848</v>
+        <v>-0.05355778292191601</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2295831465710443</v>
+        <v>0.259637714816535</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.957427253403653</v>
+        <v>1.954647651499283</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.08013431547678</v>
+        <v>2.06525830761628</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>1.93972602739726</v>
+        <v>1.936986301369863</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005108746689110209</v>
+        <v>0.005116011569824183</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1912</v>
+        <v>1901</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04381792993224948</v>
+        <v>0.04394645581296335</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.254253980125523</v>
+        <v>3.278870915307733</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.8794520547945205</v>
+        <v>0.8767123287671232</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.842533960737389</v>
+        <v>0.8398058385900566</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.852054794520548</v>
+        <v>0.8493150684931506</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01137071651090343</v>
+        <v>0.01140625</v>
       </c>
     </row>
     <row r="9">
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>84.7</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>245</v>
+        <v>225.2</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1534238980651479</v>
+        <v>0.1601200774570336</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.294657142857143</v>
+        <v>2.55047513321492</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.659214471031818</v>
+        <v>1.656211447771387</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.438512305679747</v>
+        <v>1.427620709230184</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.687671232876712</v>
+        <v>1.684931506849315</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006026948399130878</v>
+        <v>0.006037876391602105</v>
       </c>
     </row>
     <row r="10">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>111</v>
+        <v>112.1</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12560</v>
+        <v>12620</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.005248515458094492</v>
+        <v>-0.007615166295976782</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4140127388535031</v>
+        <v>0.4212361331220285</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.116747519001145</v>
+        <v>4.115204969059841</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.13846833402511</v>
+        <v>4.146783414353542</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.276712328767124</v>
+        <v>4.273972602739726</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002429102089415073</v>
+        <v>0.002430012617885373</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1097</v>
+        <v>1103</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03581892352065712</v>
+        <v>0.03580106622131049</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4988084776663628</v>
+        <v>0.4906553943789664</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.645080565395712</v>
+        <v>2.642344768231213</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.553612900221321</v>
+        <v>2.551015686700063</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.767123287671233</v>
+        <v>2.764383561643835</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003780603181175303</v>
+        <v>0.003784517493791699</v>
       </c>
     </row>
     <row r="12">
@@ -2111,7 +2111,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>-0.05753424657534247</v>
+        <v>-0.06027397260273973</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220.1</v>
+        <v>215</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>216.5</v>
+        <v>212.6</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1248143012173981</v>
+        <v>-0.1201005680914091</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.01662817551963047</v>
+        <v>0.01128880526810905</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.23882620301621</v>
+        <v>4.231850848575469</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.843344914013664</v>
+        <v>4.809471054431933</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.517808219178082</v>
+        <v>4.515068493150685</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.00235914366880254</v>
+        <v>0.00236303224234999</v>
       </c>
     </row>
     <row r="14">
@@ -2246,7 +2246,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>224.2</v>
+        <v>223.6</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>252.5</v>
+        <v>250.5</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2317,22 +2317,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1930915449093849</v>
+        <v>-0.1925782764789204</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.003128514851485242</v>
+        <v>0.00843153692614762</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.164196272268881</v>
+        <v>3.161282485119293</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.92138197624109</v>
+        <v>3.915280445184555</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.271232876712329</v>
+        <v>3.268493150684932</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.00316036021141935</v>
+        <v>0.003163273148499617</v>
       </c>
     </row>
     <row r="15">
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>78</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1683137203804096</v>
+        <v>-0.1685819194923656</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1521858974358976</v>
+        <v>0.1507106274007683</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.914796123587026</v>
+        <v>1.912119827974829</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.302305773834391</v>
+        <v>2.299829499506863</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.032876712328767</v>
+        <v>2.03013698630137</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005222488116002031</v>
+        <v>0.005229797763559219</v>
       </c>
     </row>
     <row r="16">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>113.4</v>
+        <v>114.4</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18620</v>
+        <v>18470</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.0450606036981257</v>
+        <v>-0.04987394000893693</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1426383759398497</v>
+        <v>0.1620760671358963</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.769019749919071</v>
+        <v>1.766392151793501</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.852494259604146</v>
+        <v>1.859113465228094</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.767123287671233</v>
+        <v>1.764383561643836</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005652848138330552</v>
+        <v>0.005661257037315599</v>
       </c>
     </row>
     <row r="17">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>97.40000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>82</v>
+        <v>81.7</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05880444016037616</v>
+        <v>0.05535236099677505</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8410975609756102</v>
+        <v>0.8668298653610771</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.014282142162941</v>
+        <v>3.01345163317686</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.846873348685967</v>
+        <v>2.855398580177212</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.271232876712329</v>
+        <v>3.268493150684932</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003317539476521717</v>
+        <v>0.003318453792290583</v>
       </c>
     </row>
     <row r="18">
@@ -2781,7 +2781,7 @@
         <v>4.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>133.7</v>
+        <v>132</v>
       </c>
       <c r="AK18" s="10" t="n">
         <v>46924</v>
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1332819046315776</v>
+        <v>0.1334044519359965</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.745549738219896</v>
+        <v>1.780909090909091</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.740578207252948</v>
+        <v>1.737833227964026</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.535873995816423</v>
+        <v>1.53328604364981</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.767123287671233</v>
+        <v>1.764383561643836</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005745217283733784</v>
+        <v>0.005754292091488889</v>
       </c>
     </row>
     <row r="19">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>153.6</v>
+        <v>151.6</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.02024971190493471</v>
+        <v>0.02023007024722531</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.490234375</v>
+        <v>0.5098944591029024</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.207769121268711</v>
+        <v>3.205039467130717</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.144101962331753</v>
+        <v>3.141486965145089</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.432876712328767</v>
+        <v>3.43013698630137</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003117431343077734</v>
+        <v>0.003120086383507911</v>
       </c>
     </row>
     <row r="20">
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>357.1</v>
+        <v>356.6</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27980</v>
+        <v>28310</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5722883226016878</v>
+        <v>-0.5725706699687361</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.02469296204431748</v>
+        <v>0.01133044818085471</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.446018665631005</v>
+        <v>1.443286453957018</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.380825780644706</v>
+        <v>3.376666860581256</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.43013698630137</v>
+        <v>1.427397260273973</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006915540053306475</v>
+        <v>0.006928631508030359</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>462.5</v>
+        <v>437.1</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3124,22 +3124,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03831046980256778</v>
+        <v>0.03831537445801731</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.4501231308108107</v>
+        <v>0.5343901807366733</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.7945205479452054</v>
+        <v>0.7917808219178082</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.7652051780776915</v>
+        <v>0.7625629374226536</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.7671232876712328</v>
+        <v>0.7643835616438356</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01258620689655172</v>
+        <v>0.01262975778546713</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>97.90000000000001</v>
+        <v>98.3</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>205.7</v>
+        <v>205.8</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.08148431513294861</v>
+        <v>0.07927234106935732</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.09465240641711237</v>
+        <v>0.09859086491739544</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.851516973084544</v>
+        <v>1.849370938222767</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.712014633200607</v>
+        <v>1.713535006734617</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.032876712328767</v>
+        <v>2.03013698630137</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005400976683103503</v>
+        <v>0.005407244048946684</v>
       </c>
     </row>
     <row r="23">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>92.40000000000001</v>
+        <v>92</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10470</v>
+        <v>10320</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02343099622158679</v>
+        <v>0.02446472773812439</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5547828527220631</v>
+        <v>0.5705529496124031</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.334058152263212</v>
+        <v>4.331161484131022</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.234831823800683</v>
+        <v>4.227731191579064</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.358904109589041</v>
+        <v>4.356164383561643</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002307306373999176</v>
+        <v>0.002308849493753369</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>34.9</v>
+        <v>31.7</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1746552923326495</v>
+        <v>0.1747526260293723</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.3281087558739255</v>
+        <v>0.4621765167192429</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.919272241797438</v>
+        <v>2.916468769541173</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.48521609773732</v>
+        <v>2.482623749817651</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.271232876712329</v>
+        <v>3.268493150684932</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003425511282169029</v>
+        <v>0.003428804074446931</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>56.8</v>
+        <v>56</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>28.4</v>
+        <v>28.9</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.2601213400640637</v>
+        <v>0.2661385614353796</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>1</v>
+        <v>0.9377162629757787</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.892052642536901</v>
+        <v>2.885350454584842</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.295058857101707</v>
+        <v>2.278858367060407</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.271232876712329</v>
+        <v>3.268493150684932</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003457751720324159</v>
+        <v>0.003465783500964304</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3685,7 +3685,7 @@
         <v>0.55865</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AK26" s="10" t="n">
         <v>46377</v>
@@ -3699,22 +3699,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>69.18300653594773</v>
+        <v>69.78694526345566</v>
       </c>
       <c r="AZ26" s="12" t="n">
-        <v>0.3966249999999998</v>
+        <v>0.3144705882352941</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.2958904109589042</v>
+        <v>0.2931506849315069</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.004215983691256503</v>
+        <v>0.004141310009076607</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.2684931506849315</v>
+        <v>0.2657534246575343</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.03379629629629629</v>
+        <v>0.03411214953271028</v>
       </c>
     </row>
     <row r="27">
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1194</v>
+        <v>1247</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3808,22 +3808,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05442058756680161</v>
+        <v>0.05467588275729529</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5459779966499161</v>
+        <v>0.4802708323977545</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.2904109589041096</v>
+        <v>0.2876712328767123</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.275422314708656</v>
+        <v>0.2727579511201471</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.2684931506849315</v>
+        <v>0.2657534246575343</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.03443396226415094</v>
+        <v>0.03476190476190476</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12610</v>
+        <v>12440</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3938,15 +3938,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-2.689668646097396</v>
+        <v>-2.714824284210281</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.06063792038065041</v>
+        <v>0.07513216848874604</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.2684931506849315</v>
+        <v>0.2657534246575343</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>181.1</v>
+        <v>191.7</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>16780</v>
+        <v>15500</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1576568795749231</v>
+        <v>-0.1753319532384043</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.2422294398092966</v>
+        <v>0.4235270967741935</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.694243920063763</v>
+        <v>2.694698060957128</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.198511217975105</v>
+        <v>3.267615462414227</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.767123287671233</v>
+        <v>2.764383561643835</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003711616429949422</v>
+        <v>0.003710990906509246</v>
       </c>
     </row>
     <row r="30">
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>576.1</v>
+        <v>576</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4189,22 +4189,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05530080782280266</v>
+        <v>0.05530014005259564</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.6911608175663948</v>
+        <v>0.6914544218750001</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.640773444342202</v>
+        <v>2.638033866656232</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.50238929484987</v>
+        <v>2.499794860753789</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.767123287671233</v>
+        <v>2.764383561643835</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003786769372974716</v>
+        <v>0.00379070190356397</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4286,7 +4286,7 @@
         <v>0.9284102</v>
       </c>
       <c r="AJ31" t="n">
-        <v>39</v>
+        <v>35.3</v>
       </c>
       <c r="AK31" s="10" t="n">
         <v>47133</v>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1060649393988121</v>
+        <v>0.1061127896500487</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>1.175812622564103</v>
+        <v>1.403872302549575</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.178332845014415</v>
+        <v>2.175581024397577</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.96944389738854</v>
+        <v>1.966870869548381</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.33972602739726</v>
+        <v>2.336986301369863</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.00459066667561257</v>
+        <v>0.004596473258342113</v>
       </c>
     </row>
     <row r="32">
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>70310</v>
+        <v>69360</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4412,22 +4412,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2732668611937489</v>
+        <v>-0.2736820107510893</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1045086047503911</v>
+        <v>0.1196366782006921</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.638562180032464</v>
+        <v>1.635837564995078</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.254695833361893</v>
+        <v>2.252233304432824</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.641095890410959</v>
+        <v>1.638356164383562</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.006102911517097187</v>
+        <v>0.00611307639217228</v>
       </c>
     </row>
     <row r="33">
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.1102222180299785</v>
+        <v>-0.1103602389470308</v>
       </c>
       <c r="AZ33" s="12" t="n">
         <v>0.005948460987831083</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.675978096395653</v>
+        <v>2.673266350138008</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>3.007467876384681</v>
+        <v>3.004886322722306</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.767123287671233</v>
+        <v>2.764383561643835</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003736951364986609</v>
+        <v>0.003740742107303954</v>
       </c>
     </row>
     <row r="34">
@@ -4616,7 +4616,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1429</v>
+        <v>1447</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03270958506956264</v>
+        <v>0.03269027706650856</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2848145556333099</v>
+        <v>0.2688320663441603</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.669751463947399</v>
+        <v>1.667012500071601</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.616864497132488</v>
+        <v>1.614242466586369</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.687671232876712</v>
+        <v>1.684931506849315</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005988915246320169</v>
+        <v>0.005998755258026249</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21530</v>
+        <v>21510</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.1195670551433581</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.079052484904784</v>
+        <v>0.08005578800557878</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.550017785073059</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21530</v>
+        <v>21510</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.05355778292191601</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.259637714816535</v>
+        <v>0.2608089260808926</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.954647651499283</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>225.2</v>
+        <v>226.2</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1601200774570336</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.55047513321492</v>
+        <v>2.534778956675509</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.656211447771387</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18470</v>
+        <v>18500</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,16 +2535,16 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.04987394000893693</v>
+        <v>-0.04987394000893687</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1620760671358963</v>
+        <v>0.1601916194594597</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.766392151793501</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.859113465228094</v>
+        <v>1.859113465228093</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.764383561643836</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>28310</v>
+        <v>28350</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5725706699687361</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.01133044818085471</v>
+        <v>0.009903526913580318</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.443286453957018</v>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15500</v>
+        <v>15510</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,16 +4059,16 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1753319532384043</v>
+        <v>-0.1753319532384042</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.4235270967741935</v>
+        <v>0.4226092843326885</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.694698060957128</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.267615462414227</v>
+        <v>3.267615462414226</v>
       </c>
       <c r="BC29" s="8" t="n">
         <v>2.764383561643835</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>104</v>
+        <v>103.6</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.01745380125246476</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.216923076923077</v>
+        <v>0.2216216216216218</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.397672115630404</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6110</v>
+        <v>6114</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.04272305692946612</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.676186579378069</v>
+        <v>1.674435721295387</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2931506849315069</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21510</v>
+        <v>21450</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.1195670551433581</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.08005578800557878</v>
+        <v>0.08307692307692305</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.550017785073059</v>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>113</v>
+        <v>108.8</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21510</v>
+        <v>21450</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05355778292191601</v>
+        <v>-0.03504331165985219</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2608089260808926</v>
+        <v>0.2173426573426573</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.954647651499283</v>
+        <v>1.954511766998383</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.06525830761628</v>
+        <v>2.025491704047774</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>1.936986301369863</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005116011569824183</v>
+        <v>0.005116367252859969</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1901</v>
+        <v>1898</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04394645581296335</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.278870915307733</v>
+        <v>3.285634146469969</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8767123287671232</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>226.2</v>
+        <v>223.9</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1601200774570336</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.534778956675509</v>
+        <v>2.571089772219741</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.656211447771387</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12620</v>
+        <v>12580</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.007615166295976782</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4212361331220285</v>
+        <v>0.4257551669316375</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.115204969059841</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1103</v>
+        <v>1114</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03580106622131049</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4906553943789664</v>
+        <v>0.4759361759425493</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.642344768231213</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>212.6</v>
+        <v>212</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2211,7 +2211,7 @@
         <v>-0.1201005680914091</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.01128880526810905</v>
+        <v>0.01415094339622636</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.231850848575469</v>
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>250.5</v>
+        <v>251.1</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1925782764789204</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.00843153692614762</v>
+        <v>0.006021903624054081</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.161282485119293</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18500</v>
+        <v>18700</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2538,7 +2538,7 @@
         <v>-0.04987394000893687</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1601916194594597</v>
+        <v>0.1477831529411766</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.766392151793501</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>28350</v>
+        <v>28650</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5725706699687361</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.009903526913580318</v>
+        <v>-0.0006713791273996739</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.443286453957018</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>437.1</v>
+        <v>436</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03831537445801731</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5343901807366733</v>
+        <v>0.538261348623853</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7917808219178082</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10320</v>
+        <v>10330</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.02446472773812439</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5705529496124031</v>
+        <v>0.569032569215876</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.331161484131022</v>
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>56</v>
+        <v>55.3</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>28.9</v>
+        <v>28</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.2661385614353796</v>
+        <v>0.2713424652676688</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.9377162629757787</v>
+        <v>0.9749999999999999</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.885350454584842</v>
+        <v>2.881910195435249</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.278858367060407</v>
+        <v>2.266824458528955</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.268493150684932</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003465783500964304</v>
+        <v>0.003469920754588163</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1247</v>
+        <v>1202</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.05467588275729529</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.4802708323977545</v>
+        <v>0.5356886256239599</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2876712328767123</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12440</v>
+        <v>12450</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-2.714824284210281</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.07513216848874604</v>
+        <v>0.07426860851405626</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15510</v>
+        <v>15400</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.1753319532384042</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.4226092843326885</v>
+        <v>0.4327707792207791</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.694698060957128</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>69360</v>
+        <v>69610</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2736820107510893</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1196366782006921</v>
+        <v>0.115615572475219</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.635837564995078</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21450</v>
+        <v>21490</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.1195670551433581</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.08307692307692305</v>
+        <v>0.08106095858538853</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.550017785073059</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21450</v>
+        <v>21490</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.03504331165985219</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2173426573426573</v>
+        <v>0.2150767798976267</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.954511766998383</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1898</v>
+        <v>1909</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04394645581296335</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.285634146469969</v>
+        <v>3.260939554740702</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8767123287671232</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>223.9</v>
+        <v>224</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1601200774570336</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.571089772219741</v>
+        <v>2.569495535714286</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.656211447771387</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12580</v>
+        <v>12500</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.007615166295976782</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4257551669316375</v>
+        <v>0.4348799999999999</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.115204969059841</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1114</v>
+        <v>1108</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03580106622131049</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4759361759425493</v>
+        <v>0.4839286101083033</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.642344768231213</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>212</v>
+        <v>211.4</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2211,7 +2211,7 @@
         <v>-0.1201005680914091</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.01415094339622636</v>
+        <v>0.01702932828760639</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.231850848575469</v>
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>251.1</v>
+        <v>250</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1925782764789204</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.006021903624054081</v>
+        <v>0.01044840000000002</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.161282485119293</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18700</v>
+        <v>18610</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2538,7 +2538,7 @@
         <v>-0.04987394000893687</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1477831529411766</v>
+        <v>0.1533339580870501</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.766392151793501</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>28650</v>
+        <v>28540</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5725706699687361</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.0006713791273996739</v>
+        <v>0.0031802728801682</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.443286453957018</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>436</v>
+        <v>435.3</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03831537445801731</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.538261348623853</v>
+        <v>0.5407350057431655</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7917808219178082</v>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1202</v>
+        <v>1167</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.05467588275729529</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5356886256239599</v>
+        <v>0.5817461251071121</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2876712328767123</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12450</v>
+        <v>12480</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-2.714824284210281</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.07426860851405626</v>
+        <v>0.07168623205128211</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15400</v>
+        <v>15210</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.1753319532384042</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.4327707792207791</v>
+        <v>0.4506686390532544</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.694698060957128</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>69610</v>
+        <v>69540</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2736820107510893</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.115615572475219</v>
+        <v>0.1167385677308024</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.635837564995078</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>877.7</v>
+        <v>873</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.09548281986288594</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.6599065740002279</v>
+        <v>0.6688430698739978</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.026171408193248</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9530</v>
+        <v>9505</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.009401124371027371</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1319156201469045</v>
+        <v>0.1348927785376117</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.745227036923449</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>113</v>
+        <v>112.8</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>103.6</v>
+        <v>104</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01745380125246476</v>
+        <v>0.01786026150298581</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2216216216216218</v>
+        <v>0.2147692307692308</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.397672115630404</v>
+        <v>4.397261440490358</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.322232724686821</v>
+        <v>4.320103266431979</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.764383561643836</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002273930328834101</v>
+        <v>0.00227414269888962</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6114</v>
+        <v>6135</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.04272305692946612</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.674435721295387</v>
+        <v>1.665281173594132</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2931506849315069</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21490</v>
+        <v>21280</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.1195670551433581</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.08106095858538853</v>
+        <v>0.09172932330827077</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.550017785073059</v>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>108.8</v>
+        <v>113.8</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21490</v>
+        <v>21280</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.03504331165985219</v>
+        <v>-0.0569666347880046</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2150767798976267</v>
+        <v>0.2834586466165414</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.954511766998383</v>
+        <v>1.954672674369083</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.025491704047774</v>
+        <v>2.072750282732223</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>1.936986301369863</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005116367252859969</v>
+        <v>0.005115946076868209</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1909</v>
+        <v>1902</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04394645581296335</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.260939554740702</v>
+        <v>3.276621246056783</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8767123287671232</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>224</v>
+        <v>215.6</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1601200774570336</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.569495535714286</v>
+        <v>2.708566790352505</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.656211447771387</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12500</v>
+        <v>12540</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.007615166295976782</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4348799999999999</v>
+        <v>0.4303030303030304</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.115204969059841</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03580106622131049</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4839286101083033</v>
+        <v>0.485269105691057</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.642344768231213</v>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>211.4</v>
+        <v>212.7</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1201005680914091</v>
+        <v>-0.1220011832422442</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.01702932828760639</v>
+        <v>0.02021626704278323</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.231850848575469</v>
+        <v>4.233563249765481</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.809471054431933</v>
+        <v>4.82183252296289</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.515068493150685</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.00236303224234999</v>
+        <v>0.002362076437751096</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>250</v>
+        <v>249.5</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1925782764789204</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.01044840000000002</v>
+        <v>0.01247334669338684</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.161282485119293</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18610</v>
+        <v>18490</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2538,7 +2538,7 @@
         <v>-0.04987394000893687</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1533339580870501</v>
+        <v>0.1608190892374257</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.766392151793501</v>
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>81.7</v>
+        <v>81</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2668,7 +2668,7 @@
         <v>0.05535236099677505</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8668298653610771</v>
+        <v>0.8829629629629632</v>
       </c>
       <c r="BA17" s="8" t="n">
         <v>3.01345163317686</v>
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>151.6</v>
+        <v>152.2</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.02023007024722531</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5098944591029024</v>
+        <v>0.5039421813403417</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.205039467130717</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>28540</v>
+        <v>28300</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5725706699687361</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.0031802728801682</v>
+        <v>0.01168780876325082</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.443286453957018</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>435.3</v>
+        <v>433.4</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03831537445801731</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5407350057431655</v>
+        <v>0.5474894970004613</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7917808219178082</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10330</v>
+        <v>10320</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.02446472773812439</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.569032569215876</v>
+        <v>0.5705529496124031</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.331161484131022</v>
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>31.7</v>
+        <v>31</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3480,7 +3480,7 @@
         <v>0.1747526260293723</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.4621765167192429</v>
+        <v>0.4951934058064515</v>
       </c>
       <c r="BA24" s="8" t="n">
         <v>2.916468769541173</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>28</v>
+        <v>28.7</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3589,7 +3589,7 @@
         <v>0.2713424652676688</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.9749999999999999</v>
+        <v>0.9268292682926829</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>2.881910195435249</v>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1167</v>
+        <v>1212</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.05467588275729529</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5817461251071121</v>
+        <v>0.5230179273927391</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2876712328767123</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12480</v>
+        <v>12490</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-2.714824284210281</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.07168623205128211</v>
+        <v>0.07082819663730988</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15210</v>
+        <v>15300</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.1753319532384042</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.4506686390532544</v>
+        <v>0.4421352941176468</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.694698060957128</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>69540</v>
+        <v>69480</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2736820107510893</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1167385677308024</v>
+        <v>0.1177029360967186</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.635837564995078</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>873</v>
+        <v>835</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.09548281986288594</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.6688430698739978</v>
+        <v>0.7447904191616768</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.026171408193248</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>290.4</v>
+        <v>272.9</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21280</v>
+        <v>21210</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1195670551433581</v>
+        <v>-0.1111681206112823</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.09172932330827077</v>
+        <v>0.02932578972182931</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.550017785073059</v>
+        <v>6.535588648451204</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.439541901898704</v>
+        <v>7.353008819784872</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.93972602739726</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001526713411800066</v>
+        <v>0.001530084057901929</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21280</v>
+        <v>21210</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.0569666347880046</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2834586466165414</v>
+        <v>0.2876944837340878</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.954672674369083</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1902</v>
+        <v>1895</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04394645581296335</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.276621246056783</v>
+        <v>3.292418791556728</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8767123287671232</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>215.6</v>
+        <v>216</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1601200774570336</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.708566790352505</v>
+        <v>2.701699074074074</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.656211447771387</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12540</v>
+        <v>12490</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.007615166295976782</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4303030303030304</v>
+        <v>0.4360288230584468</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.115204969059841</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03580106622131049</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.485269105691057</v>
+        <v>0.479921602160216</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.642344768231213</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>212.7</v>
+        <v>212.9</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2211,7 +2211,7 @@
         <v>-0.1220011832422442</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.02021626704278323</v>
+        <v>0.0192578675434476</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.233563249765481</v>
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>249.5</v>
+        <v>249.8</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1925782764789204</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.01247334669338684</v>
+        <v>0.01125740592473967</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.161282485119293</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18490</v>
+        <v>18430</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2538,7 +2538,7 @@
         <v>-0.04987394000893687</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1608190892374257</v>
+        <v>0.1645982072707544</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.766392151793501</v>
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>152.2</v>
+        <v>152</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.02023007024722531</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5039421813403417</v>
+        <v>0.5059210526315789</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.205039467130717</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>28300</v>
+        <v>28230</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5725706699687361</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.01168780876325082</v>
+        <v>0.01419642182075798</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.443286453957018</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>433.4</v>
+        <v>435</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03831537445801731</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5474894970004613</v>
+        <v>0.5417975816091951</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7917808219178082</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>205.8</v>
+        <v>205.3</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3262,7 +3262,7 @@
         <v>0.07927234106935732</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.09859086491739544</v>
+        <v>0.1012664393570384</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.849370938222767</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10320</v>
+        <v>10330</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.02446472773812439</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5705529496124031</v>
+        <v>0.569032569215876</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.331161484131022</v>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1212</v>
+        <v>1187</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.05467588275729529</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5230179273927391</v>
+        <v>0.5550949688289806</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2876712328767123</v>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15300</v>
+        <v>15340</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.1753319532384042</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.4421352941176468</v>
+        <v>0.4383748370273792</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.694698060957128</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>69480</v>
+        <v>69220</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2736820107510893</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1177029360967186</v>
+        <v>0.1219011846287201</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.635837564995078</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>835</v>
+        <v>857.2</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.09548281986288594</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7447904191616768</v>
+        <v>0.699603359776015</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.026171408193248</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9505</v>
+        <v>9447</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.009401124371027371</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1348927785376117</v>
+        <v>0.1418604699904731</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.745227036923449</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112.8</v>
+        <v>112.7</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01786026150298581</v>
+        <v>0.01806383492017977</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2147692307692308</v>
+        <v>0.2136923076923078</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.397261440490358</v>
+        <v>4.397055656752143</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.320103266431979</v>
+        <v>4.319037280306583</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.764383561643836</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.00227414269888962</v>
+        <v>0.002274249129561038</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6135</v>
+        <v>6112</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.04272305692946612</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.665281173594132</v>
+        <v>1.675310863874345</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2931506849315069</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>272.9</v>
+        <v>283</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21210</v>
+        <v>21260</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1111681206112823</v>
+        <v>-0.116090881513921</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02932578972182931</v>
+        <v>0.06491063029162758</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.535588648451204</v>
+        <v>6.544093630118055</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.353008819784872</v>
+        <v>7.403581989658046</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.93972602739726</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001530084057901929</v>
+        <v>0.001528095495757692</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21210</v>
+        <v>21260</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.0569666347880046</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2876944837340878</v>
+        <v>0.2846660395108185</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.954672674369083</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1895</v>
+        <v>1912</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04394645581296335</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.292418791556728</v>
+        <v>3.254253980125523</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8767123287671232</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>216</v>
+        <v>218.2</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1601200774570336</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.701699074074074</v>
+        <v>2.664376718606783</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.656211447771387</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12490</v>
+        <v>12470</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.007615166295976782</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4360288230584468</v>
+        <v>0.4383319967923016</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.115204969059841</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1111</v>
+        <v>1118</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03580106622131049</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.479921602160216</v>
+        <v>0.4706555456171735</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.642344768231213</v>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>217</v>
+        <v>220.9</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>212.9</v>
+        <v>212.6</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1220011832422442</v>
+        <v>-0.1256444034839646</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.0192578675434476</v>
+        <v>0.0390404515522107</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.233563249765481</v>
+        <v>4.236828458508882</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.82183252296289</v>
+        <v>4.845658305832299</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.515068493150685</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002362076437751096</v>
+        <v>0.002360256049526117</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>249.8</v>
+        <v>249.3</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1925782764789204</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.01125740592473967</v>
+        <v>0.01328559967910148</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.161282485119293</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>78.09999999999999</v>
+        <v>78</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2429,7 +2429,7 @@
         <v>-0.1685819194923656</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1507106274007683</v>
+        <v>0.1521858974358976</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.912119827974829</v>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>114.4</v>
+        <v>115</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18430</v>
+        <v>18660</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.04987394000893687</v>
+        <v>-0.05267061896577149</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1645982072707544</v>
+        <v>0.1562763129689175</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.766392151793501</v>
+        <v>1.766457312965185</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.859113465228093</v>
+        <v>1.864670671394873</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.764383561643836</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005661257037315599</v>
+        <v>0.005661048204563713</v>
       </c>
     </row>
     <row r="17">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>98.40000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05535236099677505</v>
+        <v>0.05707610791625337</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8829629629629632</v>
+        <v>0.8733950617283952</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.01345163317686</v>
+        <v>3.012499120351924</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.855398580177212</v>
+        <v>2.84984127234724</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.268493150684932</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003318453792290583</v>
+        <v>0.003319503043981565</v>
       </c>
     </row>
     <row r="18">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>152</v>
+        <v>151.9</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.02023007024722531</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5059210526315789</v>
+        <v>0.5069124423963134</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.205039467130717</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>28230</v>
+        <v>28320</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5725706699687361</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.01419642182075798</v>
+        <v>0.01097333997175132</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.443286453957018</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03831537445801731</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5417975816091951</v>
+        <v>0.5347412997711669</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7917808219178082</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>98.3</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>205.3</v>
+        <v>204.7</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.07927234106935732</v>
+        <v>0.08038573539771057</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1012664393570384</v>
+        <v>0.1022471910112359</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.849370938222767</v>
+        <v>1.849072171284863</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.713535006734617</v>
+        <v>1.71149258149376</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>2.03013698630137</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005407244048946684</v>
+        <v>0.005408117733474574</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10330</v>
+        <v>10380</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.02446472773812439</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.569032569215876</v>
+        <v>0.5614746088631983</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.331161484131022</v>
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3480,7 +3480,7 @@
         <v>0.1747526260293723</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.4951934058064515</v>
+        <v>0.4903857099678455</v>
       </c>
       <c r="BA24" s="8" t="n">
         <v>2.916468769541173</v>
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>55.3</v>
+        <v>56.4</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>28.7</v>
+        <v>28</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.2713424652676688</v>
+        <v>0.2632044841469038</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.9268292682926829</v>
+        <v>1.014285714285714</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.881910195435249</v>
+        <v>2.887284684151492</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.266824458528955</v>
+        <v>2.285682738136731</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.268493150684932</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003469920754588163</v>
+        <v>0.003463461727515371</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3685,7 +3685,7 @@
         <v>0.55865</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AK26" s="10" t="n">
         <v>46377</v>
@@ -3702,7 +3702,7 @@
         <v>69.78694526345566</v>
       </c>
       <c r="AZ26" s="12" t="n">
-        <v>0.3144705882352941</v>
+        <v>0.3966249999999998</v>
       </c>
       <c r="BA26" s="8" t="n">
         <v>0.2931506849315069</v>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1187</v>
+        <v>1195</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.05467588275729529</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5550949688289806</v>
+        <v>0.5446842912133891</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2876712328767123</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12490</v>
+        <v>12500</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-2.714824284210281</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.07082819663730988</v>
+        <v>0.06997153408000023</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>191.7</v>
+        <v>185.8</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15340</v>
+        <v>15200</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1753319532384042</v>
+        <v>-0.1657594109688251</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.4383748370273792</v>
+        <v>0.4069460526315791</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.694698060957128</v>
+        <v>2.692973198709029</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.267615462414226</v>
+        <v>3.228053434605056</v>
       </c>
       <c r="BC29" s="8" t="n">
         <v>2.764383561643835</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003710990906509246</v>
+        <v>0.00371336781398116</v>
       </c>
     </row>
     <row r="30">
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>576</v>
+        <v>574.7</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4192,7 +4192,7 @@
         <v>0.05530014005259564</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.6914544218750001</v>
+        <v>0.695280575952671</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.638033866656232</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>69220</v>
+        <v>69340</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2736820107510893</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1219011846287201</v>
+        <v>0.1199596192673782</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.635837564995078</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>139.7</v>
+        <v>138.1</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4524,7 +4524,7 @@
         <v>-0.1103602389470308</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.005948460987831083</v>
+        <v>0.01760318609703115</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.673266350138008</v>
@@ -4616,7 +4616,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1447</v>
+        <v>1436</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4633,7 +4633,7 @@
         <v>0.03269027706650856</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2688320663441603</v>
+        <v>0.2785515320334262</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.667012500071601</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.09548281986288594</v>
+        <v>0.09552525023735095</v>
       </c>
       <c r="AZ2" s="12" t="n">
         <v>0.699603359776015</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.026171408193248</v>
+        <v>3.023409801817647</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.762408824058065</v>
+        <v>2.759781028472516</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.268493150684932</v>
+        <v>3.265753424657534</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003304505479407203</v>
+        <v>0.003307523840793296</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9447</v>
+        <v>9491</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.009401124371027371</v>
+        <v>-0.009483563413216977</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1418604699904731</v>
+        <v>0.1365668380571066</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.745227036923449</v>
+        <v>1.742490797419036</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.761789842346966</v>
+        <v>1.759174035943794</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.764383561643836</v>
+        <v>1.761643835616438</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005729913523244728</v>
+        <v>0.005738911226855213</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112.7</v>
+        <v>115</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>104</v>
+        <v>104.4</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01806383492017977</v>
+        <v>0.01342216533359804</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2136923076923078</v>
+        <v>0.2337164750957854</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.397055656752143</v>
+        <v>4.398991518985079</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.319037280306583</v>
+        <v>4.340729529570749</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.764383561643836</v>
+        <v>4.761643835616439</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002274249129561038</v>
+        <v>0.002273248301762393</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6112</v>
+        <v>6268</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.04272305692946612</v>
+        <v>0.04301142363220972</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.675310863874345</v>
+        <v>1.608726866624122</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.2931506849315069</v>
+        <v>0.2904109589041096</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.281139544180365</v>
+        <v>0.2784350701479137</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.2657534246575343</v>
+        <v>0.263013698630137</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.03411214953271027</v>
+        <v>0.03443396226415094</v>
       </c>
     </row>
     <row r="6">
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21260</v>
+        <v>21520</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.116090881513921</v>
+        <v>-0.1161417935944513</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.06491063029162758</v>
+        <v>0.05204460966542745</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.544093630118055</v>
+        <v>6.541441155251487</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.403581989658046</v>
+        <v>7.401007432916246</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>6.93972602739726</v>
+        <v>6.936986301369863</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001528095495757692</v>
+        <v>0.001528715119904728</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21260</v>
+        <v>21520</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.0569666347880046</v>
+        <v>-0.05705298815382451</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2846660395108185</v>
+        <v>0.2691449814126394</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.954672674369083</v>
+        <v>1.951933582239825</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.072750282732223</v>
+        <v>2.070035280580801</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>1.936986301369863</v>
+        <v>1.934246575342466</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005115946076868209</v>
+        <v>0.005123125136524929</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1912</v>
+        <v>1992</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04394645581296335</v>
+        <v>0.04407578761822219</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.254253980125523</v>
+        <v>3.083400406626506</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.8767123287671232</v>
+        <v>0.873972602739726</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.8398058385900566</v>
+        <v>0.8370777419649383</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.8493150684931506</v>
+        <v>0.8465753424657534</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01140625</v>
+        <v>0.01144200626959248</v>
       </c>
     </row>
     <row r="9">
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>218.2</v>
+        <v>218.6</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1601200774570336</v>
+        <v>0.1603033782532479</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.664376718606783</v>
+        <v>2.657671546203111</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.656211447771387</v>
+        <v>1.653464516309146</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.427620709230184</v>
+        <v>1.42502775334354</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.684931506849315</v>
+        <v>1.682191780821918</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006037876391602105</v>
+        <v>0.006047907228346177</v>
       </c>
     </row>
     <row r="10">
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.007615166295976782</v>
+        <v>-0.00763186813043826</v>
       </c>
       <c r="AZ10" s="3" t="n">
         <v>0.4383319967923016</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.115204969059841</v>
+        <v>4.112473671506868</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.146783414353542</v>
+        <v>4.144100903118701</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.273972602739726</v>
+        <v>4.271232876712329</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002430012617885373</v>
+        <v>0.002431626509680695</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1118</v>
+        <v>1103</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03580106622131049</v>
+        <v>0.03578318009617597</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4706555456171735</v>
+        <v>0.4906553943789664</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.642344768231213</v>
+        <v>2.639608977373526</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.551015686700063</v>
+        <v>2.548418460636163</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.764383561643835</v>
+        <v>2.761643835616439</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003784517493791699</v>
+        <v>0.003788439911259219</v>
       </c>
     </row>
     <row r="12">
@@ -2111,7 +2111,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>-0.06027397260273973</v>
+        <v>-0.06301369863013699</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>212.6</v>
+        <v>213.5</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1256444034839646</v>
+        <v>-0.12573428941719</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.0390404515522107</v>
+        <v>0.0346604215456674</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.236828458508882</v>
+        <v>4.234169005942633</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.845658305832299</v>
+        <v>4.843114575682051</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.515068493150685</v>
+        <v>4.512328767123288</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002360256049526117</v>
+        <v>0.002361738510192922</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>249.3</v>
+        <v>251.8</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2317,22 +2317,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1925782764789204</v>
+        <v>-0.1927404440593757</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.01328559967910148</v>
+        <v>0.003225178713264443</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.161282485119293</v>
+        <v>3.15859776862559</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.915280445184555</v>
+        <v>3.912741255747874</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.268493150684932</v>
+        <v>3.265753424657534</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003163273148499617</v>
+        <v>0.003165961838930612</v>
       </c>
     </row>
     <row r="15">
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>78</v>
+        <v>80.8</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1685819194923656</v>
+        <v>-0.1688507870436689</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1521858974358976</v>
+        <v>0.1122586633663367</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.912119827974829</v>
+        <v>1.909443679811424</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.299829499506863</v>
+        <v>2.297353652083344</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.03013698630137</v>
+        <v>2.027397260273973</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005229797763559219</v>
+        <v>0.005237127497254907</v>
       </c>
     </row>
     <row r="16">
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18660</v>
+        <v>18580</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.05267061896577149</v>
+        <v>-0.05278207986740318</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1562763129689175</v>
+        <v>0.161254897739505</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.766457312965185</v>
+        <v>1.763720184099131</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.864670671394873</v>
+        <v>1.862000440038376</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.764383561643836</v>
+        <v>1.761643835616438</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005661048204563713</v>
+        <v>0.005669833622223799</v>
       </c>
     </row>
     <row r="17">
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>81</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05707610791625337</v>
+        <v>0.05708209017671587</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8733950617283952</v>
+        <v>0.8757107540173052</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.012499120351924</v>
+        <v>3.009756085754649</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.84984127234724</v>
+        <v>2.847230232849275</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.268493150684932</v>
+        <v>3.265753424657534</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003319503043981565</v>
+        <v>0.003322528376080235</v>
       </c>
     </row>
     <row r="18">
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1334044519359965</v>
+        <v>0.133527415601761</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>1.780909090909091</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.737833227964026</v>
+        <v>1.735088230885322</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.53328604364981</v>
+        <v>1.530698073115601</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.764383561643836</v>
+        <v>1.761643835616438</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005754292091488889</v>
+        <v>0.005763395671756438</v>
       </c>
     </row>
     <row r="19">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>151.9</v>
+        <v>151.3</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.02023007024722531</v>
+        <v>0.02021039975459032</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5069124423963134</v>
+        <v>0.5128883013879708</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.205039467130717</v>
+        <v>3.202309827563509</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.141486965145089</v>
+        <v>3.138871970265955</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.43013698630137</v>
+        <v>3.427397260273973</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003120086383507911</v>
+        <v>0.003122745936050961</v>
       </c>
     </row>
     <row r="20">
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>28320</v>
+        <v>28470</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5725706699687361</v>
+        <v>-0.5732674013963318</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.01097333997175132</v>
+        <v>0.005646820793818064</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.443286453957018</v>
+        <v>1.440565271131374</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.376666860581256</v>
+        <v>3.375803198174022</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.427397260273973</v>
+        <v>1.424657534246575</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006928631508030359</v>
+        <v>0.006941719476651216</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>437</v>
+        <v>434.5</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3124,22 +3124,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03831537445801731</v>
+        <v>0.03832033830218638</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5347412997711669</v>
+        <v>0.5435718020713463</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.7917808219178082</v>
+        <v>0.789041095890411</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.7625629374226536</v>
+        <v>0.7599206784108792</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.7643835616438356</v>
+        <v>0.7616438356164383</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01262975778546713</v>
+        <v>0.01267361111111111</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>98.09999999999999</v>
+        <v>99.3</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>204.7</v>
+        <v>207.5</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.08038573539771057</v>
+        <v>0.07376480879790132</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1022471910112359</v>
+        <v>0.1006746987951808</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.849072171284863</v>
+        <v>1.848107099812733</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.71149258149376</v>
+        <v>1.721147019040158</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.03013698630137</v>
+        <v>2.027397260273973</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005408117733474574</v>
+        <v>0.00541094182312989</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10380</v>
+        <v>10370</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02446472773812439</v>
+        <v>0.02447688857241121</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5614746088631983</v>
+        <v>0.5629803702989391</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.331161484131022</v>
+        <v>4.328419909711544</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.227731191579064</v>
+        <v>4.225004934706837</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.356164383561643</v>
+        <v>4.353424657534247</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002308849493753369</v>
+        <v>0.002310311894084792</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1747526260293723</v>
+        <v>0.1748501690145606</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.4903857099678455</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.916468769541173</v>
+        <v>2.913665155363805</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.482623749817651</v>
+        <v>2.480031268844882</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.268493150684932</v>
+        <v>3.265753424657534</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003428804074446931</v>
+        <v>0.003432103370420196</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.2632044841469038</v>
+        <v>0.2633847522494948</v>
       </c>
       <c r="AZ25" s="12" t="n">
         <v>1.014285714285714</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.887284684151492</v>
+        <v>2.884426234126239</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.285682738136731</v>
+        <v>2.283094068525389</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.268493150684932</v>
+        <v>3.265753424657534</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003463461727515371</v>
+        <v>0.003466893998427814</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3685,7 +3685,7 @@
         <v>0.55865</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AK26" s="10" t="n">
         <v>46377</v>
@@ -3699,22 +3699,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>69.78694526345566</v>
+        <v>70.4023291294851</v>
       </c>
       <c r="AZ26" s="12" t="n">
-        <v>0.3966249999999998</v>
+        <v>0.3144705882352941</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.2931506849315069</v>
+        <v>0.2904109589041096</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.004141310009076607</v>
+        <v>0.004067247699685841</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.2657534246575343</v>
+        <v>0.263013698630137</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.03411214953271028</v>
+        <v>0.03443396226415095</v>
       </c>
     </row>
     <row r="27">
@@ -3808,22 +3808,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05467588275729529</v>
+        <v>0.05493612701997067</v>
       </c>
       <c r="AZ27" s="12" t="n">
         <v>0.5446842912133891</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.2876712328767123</v>
+        <v>0.2849315068493151</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.2727579511201471</v>
+        <v>0.2700936099839542</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.2657534246575343</v>
+        <v>0.263013698630137</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.03476190476190476</v>
+        <v>0.03509615384615385</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12500</v>
+        <v>12450</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3938,15 +3938,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-2.714824284210281</v>
+        <v>-2.740454556007244</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.06997153408000023</v>
+        <v>0.07426860851405626</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.2657534246575343</v>
+        <v>0.263013698630137</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15200</v>
+        <v>15380</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1657594109688251</v>
+        <v>-0.1659360997514702</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.4069460526315791</v>
+        <v>0.390479843953186</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.692973198709029</v>
+        <v>2.690265414763648</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.228053434605056</v>
+        <v>3.225490773503106</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.764383561643835</v>
+        <v>2.761643835616439</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.00371336781398116</v>
+        <v>0.00371710536258689</v>
       </c>
     </row>
     <row r="30">
@@ -4189,22 +4189,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05530014005259564</v>
+        <v>0.05529947979981375</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.695280575952671</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.638033866656232</v>
+        <v>2.635294287300261</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.499794860753789</v>
+        <v>2.49720040400301</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.764383561643835</v>
+        <v>2.761643835616439</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.00379070190356397</v>
+        <v>0.003794642612853893</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1061127896500487</v>
+        <v>0.1061607797875998</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.403872302549575</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.175581024397577</v>
+        <v>2.172829168181852</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.966870869548381</v>
+        <v>1.964297783726403</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.336986301369863</v>
+        <v>2.334246575342466</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004596473258342113</v>
+        <v>0.004602294624186979</v>
       </c>
     </row>
     <row r="32">
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>69340</v>
+        <v>69920</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4412,22 +4412,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2736820107510893</v>
+        <v>-0.2740983094259248</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1199596192673782</v>
+        <v>0.1106693363844393</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.635837564995078</v>
+        <v>1.633112992255719</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.252233304432824</v>
+        <v>2.249771578523507</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.638356164383562</v>
+        <v>1.635616438356164</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.00611307639217228</v>
+        <v>0.006123275025929228</v>
       </c>
     </row>
     <row r="33">
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.1103602389470308</v>
+        <v>-0.1104985171449335</v>
       </c>
       <c r="AZ33" s="12" t="n">
         <v>0.01760318609703115</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.673266350138008</v>
+        <v>2.67055465362284</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>3.004886322722306</v>
+        <v>3.002304892231388</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.764383561643835</v>
+        <v>2.761643835616439</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003740742107303954</v>
+        <v>0.003744540478298816</v>
       </c>
     </row>
     <row r="34">
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03269027706650856</v>
+        <v>0.0326709147027008</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.2785515320334262</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.667012500071601</v>
+        <v>1.664273538342823</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.614242466586369</v>
+        <v>1.611620424907538</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.684931506849315</v>
+        <v>1.682191780821918</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005998755258026249</v>
+        <v>0.006008627650210289</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>857.2</v>
+        <v>831</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.09552525023735095</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.699603359776015</v>
+        <v>0.7531889290012035</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.023409801817647</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9491</v>
+        <v>9472</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.009483563413216977</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1365668380571066</v>
+        <v>0.1388466913006756</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.742490797419036</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>115</v>
+        <v>112.7</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>104.4</v>
+        <v>105</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01342216533359804</v>
+        <v>0.01804951356465313</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2337164750957854</v>
+        <v>0.2021333333333335</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.398991518985079</v>
+        <v>4.394330409743461</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.340729529570749</v>
+        <v>4.316421108396699</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.761643835616439</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002273248301762393</v>
+        <v>0.002275659558468157</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6268</v>
+        <v>6266</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.04301142363220972</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.608726866624122</v>
+        <v>1.60955952760932</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2904109589041096</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>283</v>
+        <v>277.5</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21520</v>
+        <v>21730</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1161417935944513</v>
+        <v>-0.1134866475519959</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.05204460966542745</v>
+        <v>0.02162908421537035</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.541441155251487</v>
+        <v>6.5368715355944</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.401007432916246</v>
+        <v>7.373686496140848</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.936986301369863</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001528715119904728</v>
+        <v>0.00152978377279533</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21520</v>
+        <v>21730</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.05705298815382451</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2691449814126394</v>
+        <v>0.2568798895536126</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.951933582239825</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1992</v>
+        <v>1946</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04407578761822219</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.083400406626506</v>
+        <v>3.17992477389517</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.873972602739726</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>218.6</v>
+        <v>219</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1603033782532479</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.657671546203111</v>
+        <v>2.650990867579909</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.653464516309146</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>112.1</v>
+        <v>113.9</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12470</v>
+        <v>12590</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.00763186813043826</v>
+        <v>-0.01141996748075672</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4383319967923016</v>
+        <v>0.4474980142970613</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.112473671506868</v>
+        <v>4.114378014677867</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.144100903118701</v>
+        <v>4.161906855627067</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.271232876712329</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002431626509680695</v>
+        <v>0.002430501029396285</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03578318009617597</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4906553943789664</v>
+        <v>0.4933632152588556</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.639608977373526</v>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220.9</v>
+        <v>218.2</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>213.5</v>
+        <v>216.5</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.12573428941719</v>
+        <v>-0.1232196767285558</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.0346604215456674</v>
+        <v>0.007852193995381063</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.234169005942633</v>
+        <v>4.231918109267528</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.843114575682051</v>
+        <v>4.826657256035797</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.512328767123288</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002361738510192922</v>
+        <v>0.002362994685105291</v>
       </c>
     </row>
     <row r="14">
@@ -2246,7 +2246,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>223.6</v>
+        <v>221.1</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>251.8</v>
+        <v>249.2</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2317,22 +2317,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1927404440593757</v>
+        <v>-0.1898976373357276</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.003225178713264443</v>
+        <v>0.00235844703049759</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.15859776862559</v>
+        <v>3.157631469843213</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.912741255747874</v>
+        <v>3.897817875087247</v>
       </c>
       <c r="BC14" s="8" t="n">
         <v>3.265753424657534</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003165961838930612</v>
+        <v>0.003166930686973593</v>
       </c>
     </row>
     <row r="15">
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>164.9</v>
+        <v>169.8</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>80.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1688507870436689</v>
+        <v>-0.1810062121609265</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1122586633663367</v>
+        <v>0.1481513647642683</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.909443679811424</v>
+        <v>1.912306839094734</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.297353652083344</v>
+        <v>2.334946696165282</v>
       </c>
       <c r="BC15" s="8" t="n">
         <v>2.027397260273973</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005237127497254907</v>
+        <v>0.005229286323492884</v>
       </c>
     </row>
     <row r="16">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>115</v>
+        <v>113.8</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18580</v>
+        <v>18450</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.05278207986740318</v>
+        <v>-0.04715791266341552</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.161254897739505</v>
+        <v>0.1572343588075882</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.763720184099131</v>
+        <v>1.763589152050619</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.862000440038376</v>
+        <v>1.850872432577219</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.761643835616438</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005669833622223799</v>
+        <v>0.00567025488242115</v>
       </c>
     </row>
     <row r="17">
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>80.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2668,7 +2668,7 @@
         <v>0.05708209017671587</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8757107540173052</v>
+        <v>0.8550733496332519</v>
       </c>
       <c r="BA17" s="8" t="n">
         <v>3.009756085754649</v>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>87.40000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.133527415601761</v>
+        <v>0.1254840132165949</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.780909090909091</v>
+        <v>1.815909090909091</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.735088230885322</v>
+        <v>1.735433148740968</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.530698073115601</v>
+        <v>1.541943846702148</v>
       </c>
       <c r="BC18" s="8" t="n">
         <v>1.761643835616438</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005763395671756438</v>
+        <v>0.005762250195148606</v>
       </c>
     </row>
     <row r="19">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>151.3</v>
+        <v>150.4</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.02021039975459032</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5128883013879708</v>
+        <v>0.521941489361702</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.202309827563509</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>28470</v>
+        <v>28480</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5732674013963318</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.005646820793818064</v>
+        <v>0.005293714466292121</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.440565271131374</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>434.5</v>
+        <v>422.8</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03832033830218638</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5435718020713463</v>
+        <v>0.5862865373699147</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.789041095890411</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>99.3</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>207.5</v>
+        <v>211.8</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.07376480879790132</v>
+        <v>0.07049151444823369</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1006746987951808</v>
+        <v>0.08484419263456067</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.848107099812733</v>
+        <v>1.848982683456676</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.721147019040158</v>
+        <v>1.727227781352103</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>2.027397260273973</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.00541094182312989</v>
+        <v>0.005408379477792073</v>
       </c>
     </row>
     <row r="23">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>92</v>
+        <v>91.8</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10370</v>
+        <v>10450</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02447688857241121</v>
+        <v>0.02499038756249621</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5629803702989391</v>
+        <v>0.547643198660287</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.328419909711544</v>
+        <v>4.328341815096703</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.225004934706837</v>
+        <v>4.222812104013799</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.353424657534247</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002310311894084792</v>
+        <v>0.002310353578158101</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>31.1</v>
+        <v>30.8</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3480,7 +3480,7 @@
         <v>0.1748501690145606</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.4903857099678455</v>
+        <v>0.5049024538961038</v>
       </c>
       <c r="BA24" s="8" t="n">
         <v>2.913665155363805</v>
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>56.4</v>
+        <v>56</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.2633847522494948</v>
+        <v>0.2663214874333596</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>1.014285714285714</v>
+        <v>1</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.884426234126239</v>
+        <v>2.882490007602664</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.283094068525389</v>
+        <v>2.27627031224514</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.265753424657534</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003466893998427814</v>
+        <v>0.003469222780868161</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1195</v>
+        <v>1200</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.05493612701997067</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5446842912133891</v>
+        <v>0.5382481066666667</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2849315068493151</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12450</v>
+        <v>12550</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-2.740454556007244</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.07426860851405626</v>
+        <v>0.0657086992828686</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185.8</v>
+        <v>148.6</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15380</v>
+        <v>15620</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1659360997514702</v>
+        <v>-0.0940081312439488</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.390479843953186</v>
+        <v>0.09499743918053749</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.690265414763648</v>
+        <v>2.676942915378869</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.225490773503106</v>
+        <v>2.954709647730478</v>
       </c>
       <c r="BC29" s="8" t="n">
         <v>2.761643835616439</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.00371710536258689</v>
+        <v>0.003735604499651684</v>
       </c>
     </row>
     <row r="30">
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>574.7</v>
+        <v>603.4</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4192,7 +4192,7 @@
         <v>0.05529947979981375</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.695280575952671</v>
+        <v>0.6146465810407691</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.635294287300261</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>69920</v>
+        <v>68410</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2740983094259248</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1106693363844393</v>
+        <v>0.1351849144861863</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.633112992255719</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>138.1</v>
+        <v>136.4</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4524,7 +4524,7 @@
         <v>-0.1104985171449335</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.01760318609703115</v>
+        <v>0.03028592375366568</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.67055465362284</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>857.2</v>
+        <v>849.9</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.09548281986288594</v>
+        <v>0.09552525023735095</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.699603359776015</v>
+        <v>0.7142016707847985</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.026171408193248</v>
+        <v>3.023409801817647</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.762408824058065</v>
+        <v>2.759781028472516</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.268493150684932</v>
+        <v>3.265753424657534</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003304505479407203</v>
+        <v>0.003307523840793296</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9447</v>
+        <v>9547</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.009401124371027371</v>
+        <v>-0.009483563413216977</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1418604699904731</v>
+        <v>0.1299000586571697</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.745227036923449</v>
+        <v>1.742490797419036</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.761789842346966</v>
+        <v>1.759174035943794</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.764383561643836</v>
+        <v>1.761643835616438</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005729913523244728</v>
+        <v>0.005738911226855213</v>
       </c>
     </row>
     <row r="4">
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01806383492017977</v>
+        <v>0.01804951356465313</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2136923076923078</v>
+        <v>0.2254757281553399</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.397055656752143</v>
+        <v>4.394330409743461</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.319037280306583</v>
+        <v>4.316421108396699</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.764383561643836</v>
+        <v>4.761643835616439</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002274249129561038</v>
+        <v>0.002275659558468157</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6112</v>
+        <v>6215</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.04272305692946612</v>
+        <v>0.04301142363220972</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.675310863874345</v>
+        <v>1.630973451327433</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.2931506849315069</v>
+        <v>0.2904109589041096</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.281139544180365</v>
+        <v>0.2784350701479137</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.2657534246575343</v>
+        <v>0.263013698630137</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.03411214953271027</v>
+        <v>0.03443396226415094</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>283</v>
+        <v>273.9</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21260</v>
+        <v>21550</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.116090881513921</v>
+        <v>-0.1117146465532335</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.06491063029162758</v>
+        <v>0.01679814385150813</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.544093630118055</v>
+        <v>6.533799859299339</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.403581989658046</v>
+        <v>7.355519072724302</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>6.93972602739726</v>
+        <v>6.936986301369863</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001528095495757692</v>
+        <v>0.001530502956218858</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21260</v>
+        <v>21550</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.0569666347880046</v>
+        <v>-0.05705298815382451</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2846660395108185</v>
+        <v>0.2673781902552204</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.954672674369083</v>
+        <v>1.951933582239825</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.072750282732223</v>
+        <v>2.070035280580801</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>1.936986301369863</v>
+        <v>1.934246575342466</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005115946076868209</v>
+        <v>0.005123125136524929</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1912</v>
+        <v>1923</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04394645581296335</v>
+        <v>0.04407578761822219</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.254253980125523</v>
+        <v>3.229918673946957</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.8767123287671232</v>
+        <v>0.873972602739726</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.8398058385900566</v>
+        <v>0.8370777419649383</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.8493150684931506</v>
+        <v>0.8465753424657534</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01140625</v>
+        <v>0.01144200626959248</v>
       </c>
     </row>
     <row r="9">
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>218.2</v>
+        <v>216.5</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1601200774570336</v>
+        <v>0.1603033782532479</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.664376718606783</v>
+        <v>2.693150115473441</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.656211447771387</v>
+        <v>1.653464516309146</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.427620709230184</v>
+        <v>1.42502775334354</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.684931506849315</v>
+        <v>1.682191780821918</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006037876391602105</v>
+        <v>0.006047907228346177</v>
       </c>
     </row>
     <row r="10">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>112.1</v>
+        <v>113.9</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12470</v>
+        <v>12560</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.007615166295976782</v>
+        <v>-0.01141996748075672</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4383319967923016</v>
+        <v>0.4509554140127388</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.115204969059841</v>
+        <v>4.114378014677867</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.146783414353542</v>
+        <v>4.161906855627067</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.273972602739726</v>
+        <v>4.271232876712329</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002430012617885373</v>
+        <v>0.002430501029396285</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1118</v>
+        <v>1110</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03580106622131049</v>
+        <v>0.03578318009617597</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4706555456171735</v>
+        <v>0.4812548648648649</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.642344768231213</v>
+        <v>2.639608977373526</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.551015686700063</v>
+        <v>2.548418460636163</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.764383561643835</v>
+        <v>2.761643835616439</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003784517493791699</v>
+        <v>0.003788439911259219</v>
       </c>
     </row>
     <row r="12">
@@ -2111,7 +2111,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>-0.06027397260273973</v>
+        <v>-0.06301369863013699</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220.9</v>
+        <v>215.5</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>212.6</v>
+        <v>216.9</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1256444034839646</v>
+        <v>-0.1206653740161422</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.0390404515522107</v>
+        <v>-0.006454587367450415</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.236828458508882</v>
+        <v>4.229620640851365</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.845658305832299</v>
+        <v>4.810023983894625</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.515068493150685</v>
+        <v>4.512328767123288</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002360256049526117</v>
+        <v>0.002364278229450653</v>
       </c>
     </row>
     <row r="14">
@@ -2246,7 +2246,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>223.6</v>
+        <v>221.1</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>249.3</v>
+        <v>251.3</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2317,22 +2317,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1925782764789204</v>
+        <v>-0.1898976373357276</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.01328559967910148</v>
+        <v>-0.006017807401512254</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.161282485119293</v>
+        <v>3.157631469843213</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.915280445184555</v>
+        <v>3.897817875087247</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.268493150684932</v>
+        <v>3.265753424657534</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003163273148499617</v>
+        <v>0.003166930686973593</v>
       </c>
     </row>
     <row r="15">
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>164.9</v>
+        <v>169.8</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>78</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1685819194923656</v>
+        <v>-0.1810062121609265</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1521858974358976</v>
+        <v>0.1773664122137406</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.912119827974829</v>
+        <v>1.912306839094734</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.299829499506863</v>
+        <v>2.334946696165282</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.03013698630137</v>
+        <v>2.027397260273973</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005229797763559219</v>
+        <v>0.005229286323492884</v>
       </c>
     </row>
     <row r="16">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>115</v>
+        <v>112.2</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18660</v>
+        <v>18520</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.05267061896577149</v>
+        <v>-0.03951283024574755</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1562763129689175</v>
+        <v>0.1366514298056156</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.766457312965185</v>
+        <v>1.763411092973031</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.864670671394873</v>
+        <v>1.835954865929352</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.764383561643836</v>
+        <v>1.761643835616438</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005661048204563713</v>
+        <v>0.005670827432042777</v>
       </c>
     </row>
     <row r="17">
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>81</v>
+        <v>81.8</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05707610791625337</v>
+        <v>0.05708209017671587</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8733950617283952</v>
+        <v>0.8550733496332519</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.012499120351924</v>
+        <v>3.009756085754649</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.84984127234724</v>
+        <v>2.847230232849275</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.268493150684932</v>
+        <v>3.265753424657534</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003319503043981565</v>
+        <v>0.003322528376080235</v>
       </c>
     </row>
     <row r="18">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>87.40000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1334044519359965</v>
+        <v>0.1254840132165949</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.780909090909091</v>
+        <v>1.815909090909091</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.737833227964026</v>
+        <v>1.735433148740968</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.53328604364981</v>
+        <v>1.541943846702148</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.764383561643836</v>
+        <v>1.761643835616438</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005754292091488889</v>
+        <v>0.005762250195148606</v>
       </c>
     </row>
     <row r="19">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>151.9</v>
+        <v>151.2</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.02023007024722531</v>
+        <v>0.02021039975459032</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5069124423963134</v>
+        <v>0.5138888888888891</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.205039467130717</v>
+        <v>3.202309827563509</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.141486965145089</v>
+        <v>3.138871970265955</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.43013698630137</v>
+        <v>3.427397260273973</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003120086383507911</v>
+        <v>0.003122745936050961</v>
       </c>
     </row>
     <row r="20">
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>28320</v>
+        <v>28580</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5725706699687361</v>
+        <v>-0.5732674013963318</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.01097333997175132</v>
+        <v>0.001776241707487802</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.443286453957018</v>
+        <v>1.440565271131374</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.376666860581256</v>
+        <v>3.375803198174022</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.427397260273973</v>
+        <v>1.424657534246575</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006928631508030359</v>
+        <v>0.006941719476651216</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>437</v>
+        <v>424.8</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3124,22 +3124,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03831537445801731</v>
+        <v>0.03832033830218638</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5347412997711669</v>
+        <v>0.5788181450094159</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.7917808219178082</v>
+        <v>0.789041095890411</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.7625629374226536</v>
+        <v>0.7599206784108792</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.7643835616438356</v>
+        <v>0.7616438356164383</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01262975778546713</v>
+        <v>0.01267361111111111</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>98.09999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>204.7</v>
+        <v>214.2</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.08038573539771057</v>
+        <v>0.07049151444823369</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1022471910112359</v>
+        <v>0.07268907563025206</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.849072171284863</v>
+        <v>1.848982683456676</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.71149258149376</v>
+        <v>1.727227781352103</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.03013698630137</v>
+        <v>2.027397260273973</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005408117733474574</v>
+        <v>0.005408379477792073</v>
       </c>
     </row>
     <row r="23">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>92</v>
+        <v>91.8</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02446472773812439</v>
+        <v>0.02499038756249621</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5614746088631983</v>
+        <v>0.5580800988439305</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.331161484131022</v>
+        <v>4.328341815096703</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.227731191579064</v>
+        <v>4.222812104013799</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.356164383561643</v>
+        <v>4.353424657534247</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002308849493753369</v>
+        <v>0.002310353578158101</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>31.1</v>
+        <v>30.8</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1747526260293723</v>
+        <v>0.1748501690145606</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.4903857099678455</v>
+        <v>0.5049024538961038</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.916468769541173</v>
+        <v>2.913665155363805</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.482623749817651</v>
+        <v>2.480031268844882</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.268493150684932</v>
+        <v>3.265753424657534</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003428804074446931</v>
+        <v>0.003432103370420196</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>56.4</v>
+        <v>56</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.2632044841469038</v>
+        <v>0.2663214874333596</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>1.014285714285714</v>
+        <v>1.074074074074074</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.887284684151492</v>
+        <v>2.882490007602664</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.285682738136731</v>
+        <v>2.27627031224514</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.268493150684932</v>
+        <v>3.265753424657534</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003463461727515371</v>
+        <v>0.003469222780868161</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3685,7 +3685,7 @@
         <v>0.55865</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AK26" s="10" t="n">
         <v>46377</v>
@@ -3699,22 +3699,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>69.78694526345566</v>
+        <v>70.4023291294851</v>
       </c>
       <c r="AZ26" s="12" t="n">
-        <v>0.3966249999999998</v>
+        <v>0.3144705882352941</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.2931506849315069</v>
+        <v>0.2904109589041096</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.004141310009076607</v>
+        <v>0.004067247699685841</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.2657534246575343</v>
+        <v>0.263013698630137</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.03411214953271028</v>
+        <v>0.03443396226415095</v>
       </c>
     </row>
     <row r="27">
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1195</v>
+        <v>1183</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3808,22 +3808,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05467588275729529</v>
+        <v>0.05493612701997067</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5446842912133891</v>
+        <v>0.5603531090448013</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.2876712328767123</v>
+        <v>0.2849315068493151</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.2727579511201471</v>
+        <v>0.2700936099839542</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.2657534246575343</v>
+        <v>0.263013698630137</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.03476190476190476</v>
+        <v>0.03509615384615385</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12500</v>
+        <v>12780</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3938,15 +3938,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-2.714824284210281</v>
+        <v>-2.740454556007244</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.06997153408000023</v>
+        <v>0.0465292782472615</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.2657534246575343</v>
+        <v>0.263013698630137</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185.8</v>
+        <v>148.6</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15200</v>
+        <v>15470</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1657594109688251</v>
+        <v>-0.0940081312439488</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.4069460526315791</v>
+        <v>0.1056147382029733</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.692973198709029</v>
+        <v>2.676942915378869</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.228053434605056</v>
+        <v>2.954709647730478</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.764383561643835</v>
+        <v>2.761643835616439</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.00371336781398116</v>
+        <v>0.003735604499651684</v>
       </c>
     </row>
     <row r="30">
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>574.7</v>
+        <v>586.5</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4189,22 +4189,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05530014005259564</v>
+        <v>0.05529947979981375</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.695280575952671</v>
+        <v>0.6611726291560105</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.638033866656232</v>
+        <v>2.635294287300261</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.499794860753789</v>
+        <v>2.49720040400301</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.764383561643835</v>
+        <v>2.761643835616439</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.00379070190356397</v>
+        <v>0.003794642612853893</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1061127896500487</v>
+        <v>0.1061607797875998</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.403872302549575</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.175581024397577</v>
+        <v>2.172829168181852</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.966870869548381</v>
+        <v>1.964297783726403</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.336986301369863</v>
+        <v>2.334246575342466</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004596473258342113</v>
+        <v>0.004602294624186979</v>
       </c>
     </row>
     <row r="32">
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>69340</v>
+        <v>68250</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4412,22 +4412,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2736820107510893</v>
+        <v>-0.2740983094259248</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1199596192673782</v>
+        <v>0.137846153846154</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.635837564995078</v>
+        <v>1.633112992255719</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.252233304432824</v>
+        <v>2.249771578523507</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.638356164383562</v>
+        <v>1.635616438356164</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.00611307639217228</v>
+        <v>0.006123275025929228</v>
       </c>
     </row>
     <row r="33">
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>138.1</v>
+        <v>136.9</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.1103602389470308</v>
+        <v>-0.1104985171449335</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.01760318609703115</v>
+        <v>0.02652300949598252</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.673266350138008</v>
+        <v>2.67055465362284</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>3.004886322722306</v>
+        <v>3.002304892231388</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.764383561643835</v>
+        <v>2.761643835616439</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003740742107303954</v>
+        <v>0.003744540478298816</v>
       </c>
     </row>
     <row r="34">
@@ -4616,7 +4616,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1436</v>
+        <v>1512</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03269027706650856</v>
+        <v>0.0326709147027008</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2785515320334262</v>
+        <v>0.2142857142857142</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.667012500071601</v>
+        <v>1.664273538342823</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.614242466586369</v>
+        <v>1.611620424907538</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.684931506849315</v>
+        <v>1.682191780821918</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005998755258026249</v>
+        <v>0.006008627650210289</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>85.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>849.9</v>
+        <v>847.4</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.09552525023735095</v>
+        <v>0.1042430224068389</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7142016707847985</v>
+        <v>0.6771300448430491</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.023409801817647</v>
+        <v>3.018894513639611</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.759781028472516</v>
+        <v>2.733904088485472</v>
       </c>
       <c r="BC2" s="8" t="n">
         <v>3.265753424657534</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003307523840793296</v>
+        <v>0.003312470824939124</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9547</v>
+        <v>9667</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.009483563413216977</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1299000586571697</v>
+        <v>0.115874196751836</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.742490797419036</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>103</v>
+        <v>103.9</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.01804951356465313</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2254757281553399</v>
+        <v>0.2148604427333975</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.394330409743461</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>273.9</v>
+        <v>281.7</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21550</v>
+        <v>21730</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1117146465532335</v>
+        <v>-0.1155197785466244</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.01679814385150813</v>
+        <v>0.03709157846295441</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.533799859299339</v>
+        <v>6.540374177758506</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.355519072724302</v>
+        <v>7.394596305400001</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.936986301369863</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001530502956218858</v>
+        <v>0.001528964510013273</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>113.8</v>
+        <v>111.6</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21550</v>
+        <v>21730</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05705298815382451</v>
+        <v>-0.04757760603993627</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2673781902552204</v>
+        <v>0.2325816843074091</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.951933582239825</v>
+        <v>1.951864030692043</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.070035280580801</v>
+        <v>2.049368056725772</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>1.934246575342466</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005123125136524929</v>
+        <v>0.005123307690881751</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1923</v>
+        <v>1933</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04407578761822219</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.229918673946957</v>
+        <v>3.208036011381273</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.873972602739726</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>216.5</v>
+        <v>215</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1603033782532479</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.693150115473441</v>
+        <v>2.718916279069767</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.653464516309146</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1110</v>
+        <v>1119</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03578318009617597</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4812548648648649</v>
+        <v>0.4693412868632707</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.639608977373526</v>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>215.5</v>
+        <v>218.3</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>216.9</v>
+        <v>215.4</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1206653740161422</v>
+        <v>-0.1233135113904298</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.006454587367450415</v>
+        <v>0.01346332404828221</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.229620640851365</v>
+        <v>4.232002296883318</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.810023983894625</v>
+        <v>4.827269898496208</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.512328767123288</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002364278229450653</v>
+        <v>0.00236294767783197</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>251.3</v>
+        <v>248.7</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1898976373357276</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.006017807401512254</v>
+        <v>0.004373642943305223</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.157631469843213</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>78.59999999999999</v>
+        <v>78</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2429,7 +2429,7 @@
         <v>-0.1810062121609265</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1773664122137406</v>
+        <v>0.186423076923077</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.912306839094734</v>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>112.2</v>
+        <v>114</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18520</v>
+        <v>18790</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.03951283024574755</v>
+        <v>-0.04810171211750659</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1366514298056156</v>
+        <v>0.1382915167642365</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.763411092973031</v>
+        <v>1.763611138270861</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.835954865929352</v>
+        <v>1.852730654862328</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.761643835616438</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005670827432042777</v>
+        <v>0.00567018419366785</v>
       </c>
     </row>
     <row r="17">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>97.90000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05708209017671587</v>
+        <v>0.0546702637208034</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8550733496332519</v>
+        <v>0.8683374083129582</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.009756085754649</v>
+        <v>3.011088366035719</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.847230232849275</v>
+        <v>2.855004516210411</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.265753424657534</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003322528376080235</v>
+        <v>0.003321058296660223</v>
       </c>
     </row>
     <row r="18">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>151.2</v>
+        <v>150.5</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.02021039975459032</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5138888888888891</v>
+        <v>0.5209302325581395</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.202309827563509</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>28580</v>
+        <v>28790</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5732674013963318</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.001776241707487802</v>
+        <v>-0.005530913928447401</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.440565271131374</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>424.8</v>
+        <v>425</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03832033830218638</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5788181450094159</v>
+        <v>0.5780751717647057</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.789041095890411</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>99.90000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>214.2</v>
+        <v>216.4</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.07049151444823369</v>
+        <v>0.07267037255261427</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.07268907563025206</v>
+        <v>0.057532347504621</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.848982683456676</v>
+        <v>1.848399985549451</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.727227781352103</v>
+        <v>1.72317613392346</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>2.027397260273973</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005408379477792073</v>
+        <v>0.005410084439611929</v>
       </c>
     </row>
     <row r="23">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>91.8</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02499038756249621</v>
+        <v>0.02602154346821414</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5580800988439305</v>
+        <v>0.5512910788053951</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.328341815096703</v>
+        <v>4.328184727320187</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.222812104013799</v>
+        <v>4.218415056558968</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.353424657534247</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002310353578158101</v>
+        <v>0.002310437430472507</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12780</v>
+        <v>12800</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-2.740454556007244</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.0465292782472615</v>
+        <v>0.04489407625000008</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>586.5</v>
+        <v>585</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4192,7 +4192,7 @@
         <v>0.05529947979981375</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.6611726291560105</v>
+        <v>0.6654320461538463</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.635294287300261</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>68250</v>
+        <v>68150</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2740983094259248</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.137846153846154</v>
+        <v>0.1395157740278796</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.633112992255719</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>136.9</v>
+        <v>139.9</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4524,7 +4524,7 @@
         <v>-0.1104985171449335</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.02652300949598252</v>
+        <v>0.004510364546104428</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.67055465362284</v>
@@ -4616,7 +4616,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4633,7 +4633,7 @@
         <v>0.0326709147027008</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2142857142857142</v>
+        <v>0.2158940397350992</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.664273538342823</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>85.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>831</v>
+        <v>847.4</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.09552525023735095</v>
+        <v>0.1042430224068389</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7531889290012035</v>
+        <v>0.6771300448430491</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.023409801817647</v>
+        <v>3.018894513639611</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.759781028472516</v>
+        <v>2.733904088485472</v>
       </c>
       <c r="BC2" s="8" t="n">
         <v>3.265753424657534</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003307523840793296</v>
+        <v>0.003312470824939124</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9472</v>
+        <v>9667</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.009483563413216977</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1388466913006756</v>
+        <v>0.115874196751836</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.742490797419036</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>105</v>
+        <v>103.9</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.01804951356465313</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2021333333333335</v>
+        <v>0.2148604427333975</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.394330409743461</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6266</v>
+        <v>6215</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.04301142363220972</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.60955952760932</v>
+        <v>1.630973451327433</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2904109589041096</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>277.5</v>
+        <v>278</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21730</v>
+        <v>21880</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1134866475519959</v>
+        <v>-0.1137305974624531</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02162908421537035</v>
+        <v>0.01645338208409508</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.5368715355944</v>
+        <v>6.537293030549217</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.373686496140848</v>
+        <v>7.37619172210141</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.936986301369863</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.00152978377279533</v>
+        <v>0.001529685139287671</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>113.8</v>
+        <v>111.6</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21730</v>
+        <v>21880</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05705298815382451</v>
+        <v>-0.04757760603993627</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2568798895536126</v>
+        <v>0.2241316270566727</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.951933582239825</v>
+        <v>1.951864030692043</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.070035280580801</v>
+        <v>2.049368056725772</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>1.934246575342466</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005123125136524929</v>
+        <v>0.005123307690881751</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04407578761822219</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.17992477389517</v>
+        <v>3.177777919876734</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.873972602739726</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1603033782532479</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.650990867579909</v>
+        <v>2.718916279069767</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.653464516309146</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12590</v>
+        <v>12580</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.01141996748075672</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4474980142970613</v>
+        <v>0.4486486486486487</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.114378014677867</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1101</v>
+        <v>1119</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03578318009617597</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4933632152588556</v>
+        <v>0.4693412868632707</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.639608977373526</v>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>218.2</v>
+        <v>218.3</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>216.5</v>
+        <v>215.4</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1232196767285558</v>
+        <v>-0.1233135113904298</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.007852193995381063</v>
+        <v>0.01346332404828221</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.231918109267528</v>
+        <v>4.232002296883318</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.826657256035797</v>
+        <v>4.827269898496208</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.512328767123288</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002362994685105291</v>
+        <v>0.00236294767783197</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>249.2</v>
+        <v>248.7</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1898976373357276</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.00235844703049759</v>
+        <v>0.004373642943305223</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.157631469843213</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>80.59999999999999</v>
+        <v>78</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2429,7 +2429,7 @@
         <v>-0.1810062121609265</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1481513647642683</v>
+        <v>0.186423076923077</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.912306839094734</v>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>113.8</v>
+        <v>114</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18450</v>
+        <v>18790</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.04715791266341552</v>
+        <v>-0.04810171211750659</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1572343588075882</v>
+        <v>0.1382915167642365</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.763589152050619</v>
+        <v>1.763611138270861</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.850872432577219</v>
+        <v>1.852730654862328</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.761643835616438</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.00567025488242115</v>
+        <v>0.00567018419366785</v>
       </c>
     </row>
     <row r="17">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>97.90000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05708209017671587</v>
+        <v>0.0546702637208034</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8550733496332519</v>
+        <v>0.8683374083129582</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.009756085754649</v>
+        <v>3.011088366035719</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.847230232849275</v>
+        <v>2.855004516210411</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.265753424657534</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003322528376080235</v>
+        <v>0.003321058296660223</v>
       </c>
     </row>
     <row r="18">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>150.4</v>
+        <v>150.5</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.02021039975459032</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.521941489361702</v>
+        <v>0.5209302325581395</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.202309827563509</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>28480</v>
+        <v>28790</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5732674013963318</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.005293714466292121</v>
+        <v>-0.005530913928447401</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.440565271131374</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>422.8</v>
+        <v>425</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03832033830218638</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5862865373699147</v>
+        <v>0.5780751717647057</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.789041095890411</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>99.90000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>211.8</v>
+        <v>216.4</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.07049151444823369</v>
+        <v>0.07267037255261427</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.08484419263456067</v>
+        <v>0.057532347504621</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.848982683456676</v>
+        <v>1.848399985549451</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.727227781352103</v>
+        <v>1.72317613392346</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>2.027397260273973</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005408379477792073</v>
+        <v>0.005410084439611929</v>
       </c>
     </row>
     <row r="23">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>91.8</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10450</v>
+        <v>10400</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02499038756249621</v>
+        <v>0.02602154346821414</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.547643198660287</v>
+        <v>0.5483078267307695</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.328341815096703</v>
+        <v>4.328184727320187</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.222812104013799</v>
+        <v>4.218415056558968</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.353424657534247</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002310353578158101</v>
+        <v>0.002310437430472507</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3589,7 +3589,7 @@
         <v>0.2663214874333596</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>1</v>
+        <v>1.074074074074074</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>2.882490007602664</v>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1200</v>
+        <v>1183</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.05493612701997067</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5382481066666667</v>
+        <v>0.5603531090448013</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2849315068493151</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12550</v>
+        <v>12790</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-2.740454556007244</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.0657086992828686</v>
+        <v>0.04571103799843645</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15620</v>
+        <v>15490</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.0940081312439488</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.09499743918053749</v>
+        <v>0.1041872175597158</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.676942915378869</v>
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>603.4</v>
+        <v>585</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4192,7 +4192,7 @@
         <v>0.05529947979981375</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.6146465810407691</v>
+        <v>0.6654320461538463</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.635294287300261</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>68410</v>
+        <v>68140</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2740983094259248</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1351849144861863</v>
+        <v>0.1396830055767537</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.633112992255719</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>136.4</v>
+        <v>139.9</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4524,7 +4524,7 @@
         <v>-0.1104985171449335</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.03028592375366568</v>
+        <v>0.004510364546104428</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.67055465362284</v>
@@ -4616,7 +4616,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1436</v>
+        <v>1510</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4633,7 +4633,7 @@
         <v>0.0326709147027008</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2785515320334262</v>
+        <v>0.2158940397350992</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.664273538342823</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>83.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>847.4</v>
+        <v>890.8</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1042430224068389</v>
+        <v>0.1067880732451126</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.6771300448430491</v>
+        <v>0.583969465648855</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.018894513639611</v>
+        <v>3.017568934814811</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.733904088485472</v>
+        <v>2.72641981582551</v>
       </c>
       <c r="BC2" s="8" t="n">
         <v>3.265753424657534</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003312470824939124</v>
+        <v>0.003313925950332499</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9667</v>
+        <v>9528</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.009483563413216977</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.115874196751836</v>
+        <v>0.1321532178841309</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.742490797419036</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>103.9</v>
+        <v>104</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.01804951356465313</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2148604427333975</v>
+        <v>0.2136923076923078</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.394330409743461</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6215</v>
+        <v>6236</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.04301142363220972</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.630973451327433</v>
+        <v>1.62211353431687</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2904109589041096</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>278</v>
+        <v>279.3</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21880</v>
+        <v>21940</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1137305974624531</v>
+        <v>-0.1143624353844166</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.01645338208409508</v>
+        <v>0.01841385597082956</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.537293030549217</v>
+        <v>6.538383165012474</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.37619172210141</v>
+        <v>7.382685001454857</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.936986301369863</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001529685139287671</v>
+        <v>0.001529430097261808</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>111.6</v>
+        <v>112</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21880</v>
+        <v>21940</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.04757760603993627</v>
+        <v>-0.04932133783060601</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2241316270566727</v>
+        <v>0.2251595259799453</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.951864030692043</v>
+        <v>1.951876829364671</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.049368056725772</v>
+        <v>2.053140463793097</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>1.934246575342466</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005123307690881751</v>
+        <v>0.005123274096785587</v>
       </c>
     </row>
     <row r="8">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>96.5</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1947</v>
+        <v>1984</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,16 +1617,16 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04407578761822219</v>
+        <v>0.04530803675898716</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.177777919876734</v>
+        <v>3.095617165322581</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.873972602739726</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.8370777419649383</v>
+        <v>0.8360909626692506</v>
       </c>
       <c r="BC8" s="8" t="n">
         <v>0.8465753424657534</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>215</v>
+        <v>215.1</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1603033782532479</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.718916279069767</v>
+        <v>2.717187354718736</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.653464516309146</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12580</v>
+        <v>12650</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.01141996748075672</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4486486486486487</v>
+        <v>0.4406324110671938</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.114378014677867</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1119</v>
+        <v>1115</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03578318009617597</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4693412868632707</v>
+        <v>0.4746124663677129</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.639608977373526</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>215.4</v>
+        <v>216.2</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2211,7 +2211,7 @@
         <v>-0.1233135113904298</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.01346332404828221</v>
+        <v>0.009713228492137072</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.232002296883318</v>
@@ -2246,7 +2246,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221.1</v>
+        <v>223.6</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>248.7</v>
+        <v>247.3</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2317,22 +2317,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1898976373357276</v>
+        <v>-0.1927404440593757</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.004373642943305223</v>
+        <v>0.02148038819247877</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.157631469843213</v>
+        <v>3.15859776862559</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.897817875087247</v>
+        <v>3.912741255747874</v>
       </c>
       <c r="BC14" s="8" t="n">
         <v>3.265753424657534</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003166930686973593</v>
+        <v>0.003165961838930612</v>
       </c>
     </row>
     <row r="15">
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>78</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2429,7 +2429,7 @@
         <v>-0.1810062121609265</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.186423076923077</v>
+        <v>0.1879460847240051</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.912306839094734</v>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>114</v>
+        <v>114.8</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18790</v>
+        <v>18780</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.04810171211750659</v>
+        <v>-0.05185111850746386</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1382915167642365</v>
+        <v>0.1468898998935038</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.763611138270861</v>
+        <v>1.763698492101443</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.852730654862328</v>
+        <v>1.860149314657318</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.761643835616438</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.00567018419366785</v>
+        <v>0.005669903356375284</v>
       </c>
     </row>
     <row r="17">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>150.5</v>
+        <v>150.7</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.02021039975459032</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5209302325581395</v>
+        <v>0.5189117451891176</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.202309827563509</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>28790</v>
+        <v>28950</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5732674013963318</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.005530913928447401</v>
+        <v>-0.01102711613126084</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.440565271131374</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>425</v>
+        <v>423.6</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03832033830218638</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5780751717647057</v>
+        <v>0.5832907176581679</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.789041095890411</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>99.5</v>
+        <v>99.8</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>216.4</v>
+        <v>219.9</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.07267037255261427</v>
+        <v>0.0710349824690458</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.057532347504621</v>
+        <v>0.04383810823101397</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.848399985549451</v>
+        <v>1.848837391444845</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.72317613392346</v>
+        <v>1.726215690156768</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>2.027397260273973</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005410084439611929</v>
+        <v>0.005408804498585521</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10400</v>
+        <v>10270</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.02602154346821414</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5483078267307695</v>
+        <v>0.567906659980526</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.328184727320187</v>
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>30.8</v>
+        <v>33.6</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3480,7 +3480,7 @@
         <v>0.1748501690145606</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.5049024538961038</v>
+        <v>0.3794939160714283</v>
       </c>
       <c r="BA24" s="8" t="n">
         <v>2.913665155363805</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12790</v>
+        <v>12800</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-2.740454556007244</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.04571103799843645</v>
+        <v>0.04489407625000008</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15490</v>
+        <v>15350</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.0940081312439488</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1041872175597158</v>
+        <v>0.1142579804560258</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.676942915378869</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>68140</v>
+        <v>67500</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2740983094259248</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1396830055767537</v>
+        <v>0.1504888888888889</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.633112992255719</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>139.9</v>
+        <v>139.2</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4524,7 +4524,7 @@
         <v>-0.1104985171449335</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.004510364546104428</v>
+        <v>0.009561781609195519</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.67055465362284</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1067880732451126</v>
+        <v>0.1154536428983783</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.583969465648855</v>
+        <v>0.5458015267175573</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.017568934814811</v>
+        <v>3.013030541702891</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.72641981582551</v>
+        <v>2.701170560413319</v>
       </c>
       <c r="BC2" s="8" t="n">
         <v>3.265753424657534</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003313925950332499</v>
+        <v>0.00331891756873737</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9528</v>
+        <v>9534</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.009483563413216977</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1321532178841309</v>
+        <v>0.1314407237256134</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.742490797419036</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1984</v>
+        <v>1979</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04530803675898716</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.095617165322581</v>
+        <v>3.105964859019707</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.873972602739726</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>215.1</v>
+        <v>215</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1603033782532479</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.717187354718736</v>
+        <v>2.718916279069767</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.653464516309146</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12650</v>
+        <v>12690</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.01141996748075672</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4406324110671938</v>
+        <v>0.4360914105594957</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.114378014677867</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1115</v>
+        <v>1118</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03578318009617597</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4746124663677129</v>
+        <v>0.4706555456171735</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.639608977373526</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>216.2</v>
+        <v>218.7</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2211,7 +2211,7 @@
         <v>-0.1233135113904298</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.009713228492137072</v>
+        <v>-0.001828989483310339</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.232002296883318</v>
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>247.3</v>
+        <v>247.4</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1927404440593757</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.02148038819247877</v>
+        <v>0.02106750202101848</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.15859776862559</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18780</v>
+        <v>18750</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2538,7 +2538,7 @@
         <v>-0.05185111850746386</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1468898998935038</v>
+        <v>0.1487249237333332</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.763698492101443</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>28950</v>
+        <v>28880</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5732674013963318</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.01102711613126084</v>
+        <v>-0.008630021191135762</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.440565271131374</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>423.6</v>
+        <v>424</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03832033830218638</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5832907176581679</v>
+        <v>0.5817970471698111</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.789041095890411</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10270</v>
+        <v>10290</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.02602154346821414</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.567906659980526</v>
+        <v>0.5648592223517981</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.328184727320187</v>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15350</v>
+        <v>15300</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.0940081312439488</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1142579804560258</v>
+        <v>0.1178993464052285</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.676942915378869</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67500</v>
+        <v>67450</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2740983094259248</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1504888888888889</v>
+        <v>0.1513417346182357</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.633112992255719</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9534</v>
+        <v>9510</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.009483563413216977</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1314407237256134</v>
+        <v>0.1342960946372238</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.742490797419036</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112.7</v>
+        <v>112.9</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01804951356465313</v>
+        <v>0.01764239427536547</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2136923076923078</v>
+        <v>0.215846153846154</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.394330409743461</v>
+        <v>4.394741873778959</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.316421108396699</v>
+        <v>4.318552271899336</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.761643835616439</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002275659558468157</v>
+        <v>0.002275446496565492</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6236</v>
+        <v>6243</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.04301142363220972</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.62211353431687</v>
+        <v>1.619173474291206</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2904109589041096</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>279.3</v>
+        <v>276.6</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21940</v>
+        <v>22000</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1143624353844166</v>
+        <v>-0.1130462188439565</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.01841385597082956</v>
+        <v>0.005818181818181722</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.538383165012474</v>
+        <v>6.536109720646892</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.382685001454857</v>
+        <v>7.369166082282005</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.936986301369863</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001529430097261808</v>
+        <v>0.00152996207643379</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>112</v>
+        <v>112.9</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21940</v>
+        <v>22000</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.04932133783060601</v>
+        <v>-0.05321048748690295</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2251595259799453</v>
+        <v>0.2316363636363636</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.951876829364671</v>
+        <v>1.9519053762009</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.053140463793097</v>
+        <v>2.061604348594745</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>1.934246575342466</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005123274096785587</v>
+        <v>0.005123199168324209</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04530803675898716</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.105964859019707</v>
+        <v>3.10389113939394</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.873972602739726</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12690</v>
+        <v>12670</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.01141996748075672</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4360914105594957</v>
+        <v>0.4383583267561169</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.114378014677867</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03578318009617597</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4706555456171735</v>
+        <v>0.4732911290322581</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.639608977373526</v>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>218.3</v>
+        <v>221</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>218.7</v>
+        <v>217</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1233135113904298</v>
+        <v>-0.1258266754874906</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.001828989483310339</v>
+        <v>0.01843317972350222</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.232002296883318</v>
+        <v>4.234251497819993</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.827269898496208</v>
+        <v>4.843720780637251</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.512328767123288</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.00236294767783197</v>
+        <v>0.002361692498697469</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>247.4</v>
+        <v>247.8</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1927404440593757</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.02106750202101848</v>
+        <v>0.01941928974979823</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.15859776862559</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>77.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2429,7 +2429,7 @@
         <v>-0.1810062121609265</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1879460847240051</v>
+        <v>0.186423076923077</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.912306839094734</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18750</v>
+        <v>18740</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2538,7 +2538,7 @@
         <v>-0.05185111850746386</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1487249237333332</v>
+        <v>0.1493379039487726</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.763698492101443</v>
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>150.7</v>
+        <v>150</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.02021039975459032</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5189117451891176</v>
+        <v>0.526</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.202309827563509</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03832033830218638</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5817970471698111</v>
+        <v>0.5780751717647057</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.789041095890411</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>99.8</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>219.9</v>
+        <v>219.3</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.0710349824690458</v>
+        <v>0.07212440940967904</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.04383810823101397</v>
+        <v>0.04459644322845402</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.848837391444845</v>
+        <v>1.848546043181656</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.726215690156768</v>
+        <v>1.724189867292996</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>2.027397260273973</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005408804498585521</v>
+        <v>0.005409656977106359</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10290</v>
+        <v>10270</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.02602154346821414</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5648592223517981</v>
+        <v>0.567906659980526</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.328184727320187</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>27</v>
+        <v>27.6</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3589,7 +3589,7 @@
         <v>0.2663214874333596</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>1.074074074074074</v>
+        <v>1.028985507246376</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>2.882490007602664</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12800</v>
+        <v>12740</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-2.740454556007244</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.04489407625000008</v>
+        <v>0.04981508445839888</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15300</v>
+        <v>15220</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.0940081312439488</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1178993464052285</v>
+        <v>0.1237752956636002</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.676942915378869</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67450</v>
+        <v>67590</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2740983094259248</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1513417346182357</v>
+        <v>0.1489569462938305</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.633112992255719</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>81</v>
+        <v>80.7</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>890.8</v>
+        <v>840.9</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1154536428983783</v>
+        <v>0.1167783179054878</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.5458015267175573</v>
+        <v>0.6314662861220124</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.013030541702891</v>
+        <v>3.012333380101091</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.701170560413319</v>
+        <v>2.69734228521799</v>
       </c>
       <c r="BC2" s="8" t="n">
         <v>3.265753424657534</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.00331891756873737</v>
+        <v>0.003319685684877418</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9510</v>
+        <v>9441</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.009483563413216977</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1342960946372238</v>
+        <v>0.1425861518906895</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.742490797419036</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>104</v>
+        <v>103.8</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.01764239427536547</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.215846153846154</v>
+        <v>0.2181888246628134</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.394741873778959</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6243</v>
+        <v>6242</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.04301142363220972</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.619173474291206</v>
+        <v>1.619593079141301</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2904109589041096</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>276.6</v>
+        <v>280.7</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>22000</v>
+        <v>21930</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1130462188439565</v>
+        <v>-0.115038980934722</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.005818181818181722</v>
+        <v>0.023985408116735</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.536109720646892</v>
+        <v>6.539547956826016</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.369166082282005</v>
+        <v>7.389645211416521</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.936986301369863</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.00152996207643379</v>
+        <v>0.001529157682766428</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22000</v>
+        <v>21930</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.05321048748690295</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2316363636363636</v>
+        <v>0.2355677154582763</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.9519053762009</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1980</v>
+        <v>1960</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04530803675898716</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.10389113939394</v>
+        <v>3.145767579591837</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.873972602739726</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>215</v>
+        <v>215.8</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1603033782532479</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.718916279069767</v>
+        <v>2.705129749768304</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.653464516309146</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1116</v>
+        <v>1110</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03578318009617597</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4732911290322581</v>
+        <v>0.4812548648648649</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.639608977373526</v>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>217</v>
+        <v>217.5</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1258266754874906</v>
+        <v>-0.1249004263418048</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.01843317972350222</v>
+        <v>0.01149425287356332</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.234251497819993</v>
+        <v>4.233423787972602</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.843720780637251</v>
+        <v>4.837648097890781</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.512328767123288</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002361692498697469</v>
+        <v>0.002362154251698252</v>
       </c>
     </row>
     <row r="14">
@@ -2246,7 +2246,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>223.6</v>
+        <v>222.7</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>247.8</v>
+        <v>247.1</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2317,22 +2317,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1927404440593757</v>
+        <v>-0.1917219148654573</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.01941928974979823</v>
+        <v>0.01819233104006468</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.15859776862559</v>
+        <v>3.158252042702036</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.912741255747874</v>
+        <v>3.907382992050719</v>
       </c>
       <c r="BC14" s="8" t="n">
         <v>3.265753424657534</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003165961838930612</v>
+        <v>0.003166308408826207</v>
       </c>
     </row>
     <row r="15">
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>169.8</v>
+        <v>165.3</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1810062121609265</v>
+        <v>-0.1698634992879429</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.186423076923077</v>
+        <v>0.1549807692307694</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.912306839094734</v>
+        <v>1.90968305549486</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.334946696165282</v>
+        <v>2.300444630319004</v>
       </c>
       <c r="BC15" s="8" t="n">
         <v>2.027397260273973</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005229286323492884</v>
+        <v>0.005236471031790499</v>
       </c>
     </row>
     <row r="16">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>114.8</v>
+        <v>114</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18740</v>
+        <v>18800</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.05185111850746386</v>
+        <v>-0.04810171211750659</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1493379039487726</v>
+        <v>0.1376860425531916</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.763698492101443</v>
+        <v>1.763611138270861</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.860149314657318</v>
+        <v>1.852730654862328</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.761643835616438</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005669903356375284</v>
+        <v>0.00567018419366785</v>
       </c>
     </row>
     <row r="17">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>98.59999999999999</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>81.8</v>
+        <v>81.3</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.0546702637208034</v>
+        <v>0.05639063068338313</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8683374083129582</v>
+        <v>0.8702952029520297</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.011088366035719</v>
+        <v>3.010138375054706</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.855004516210411</v>
+        <v>2.849455767235872</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.265753424657534</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003321058296660223</v>
+        <v>0.003322106413070881</v>
       </c>
     </row>
     <row r="18">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>150</v>
+        <v>150.6</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.02021039975459032</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.526</v>
+        <v>0.5199203187250998</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.202309827563509</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>28880</v>
+        <v>28940</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5732674013963318</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.008630021191135762</v>
+        <v>-0.01068538396682794</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.440565271131374</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>425</v>
+        <v>427.4</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03832033830218638</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5780751717647057</v>
+        <v>0.5692137295273747</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.789041095890411</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>99.59999999999999</v>
+        <v>99.8</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>219.3</v>
+        <v>218.9</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.07212440940967904</v>
+        <v>0.0710349824690458</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.04459644322845402</v>
+        <v>0.04860666971219718</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.848546043181656</v>
+        <v>1.848837391444845</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.724189867292996</v>
+        <v>1.726215690156768</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>2.027397260273973</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005409656977106359</v>
+        <v>0.005408804498585521</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10270</v>
+        <v>10290</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.02602154346821414</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.567906659980526</v>
+        <v>0.5648592223517981</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.328184727320187</v>
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>33.6</v>
+        <v>31.1</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3480,7 +3480,7 @@
         <v>0.1748501690145606</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.3794939160714283</v>
+        <v>0.4903857099678455</v>
       </c>
       <c r="BA24" s="8" t="n">
         <v>2.913665155363805</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>27.6</v>
+        <v>27.1</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3589,7 +3589,7 @@
         <v>0.2663214874333596</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>1.028985507246376</v>
+        <v>1.066420664206642</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>2.882490007602664</v>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1183</v>
+        <v>1178</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.05493612701997067</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5603531090448013</v>
+        <v>0.5669759999999999</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2849315068493151</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12740</v>
+        <v>12720</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-2.740454556007244</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.04981508445839888</v>
+        <v>0.05146573710691826</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>148.6</v>
+        <v>185.8</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15220</v>
+        <v>15200</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.0940081312439488</v>
+        <v>-0.1659360997514702</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1237752956636002</v>
+        <v>0.4069460526315791</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.676942915378869</v>
+        <v>2.690265414763648</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>2.954709647730478</v>
+        <v>3.225490773503106</v>
       </c>
       <c r="BC29" s="8" t="n">
         <v>2.761643835616439</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003735604499651684</v>
+        <v>0.00371710536258689</v>
       </c>
     </row>
     <row r="30">
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>585</v>
+        <v>584.1</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4192,7 +4192,7 @@
         <v>0.05529947979981375</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.6654320461538463</v>
+        <v>0.6679981972265023</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.635294287300261</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67590</v>
+        <v>67790</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2740983094259248</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1489569462938305</v>
+        <v>0.145567192801298</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.633112992255719</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>139.2</v>
+        <v>137.9</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4524,7 +4524,7 @@
         <v>-0.1104985171449335</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.009561781609195519</v>
+        <v>0.01907904278462658</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.67055465362284</v>
@@ -4616,7 +4616,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1510</v>
+        <v>1485</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4633,7 +4633,7 @@
         <v>0.0326709147027008</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2158940397350992</v>
+        <v>0.2363636363636363</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.664273538342823</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1167783179054878</v>
+        <v>0.1168384124043399</v>
       </c>
       <c r="AZ2" s="12" t="n">
         <v>0.6314662861220124</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.012333380101091</v>
+        <v>3.009562005713872</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.69734228521799</v>
+        <v>2.694715701293672</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.265753424657534</v>
+        <v>3.263013698630137</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003319685684877418</v>
+        <v>0.00332274263863455</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.009483563413216977</v>
+        <v>-0.009566246963531927</v>
       </c>
       <c r="AZ3" s="12" t="n">
         <v>0.1425861518906895</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.742490797419036</v>
+        <v>1.739754568280932</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.759174035943794</v>
+        <v>1.756558238193316</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.761643835616438</v>
+        <v>1.758904109589041</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005738911226855213</v>
+        <v>0.005747937198912543</v>
       </c>
     </row>
     <row r="4">
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01764239427536547</v>
+        <v>0.01762785642334557</v>
       </c>
       <c r="AZ4" s="12" t="n">
         <v>0.2181888246628134</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.394741873778959</v>
+        <v>4.39201683584805</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.318552271899336</v>
+        <v>4.315936133356905</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.761643835616439</v>
+        <v>4.758904109589041</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002275446496565492</v>
+        <v>0.002276858303087336</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6242</v>
+        <v>6379</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.04301142363220972</v>
+        <v>0.04330529064998117</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.619593079141301</v>
+        <v>1.563332810785389</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.2904109589041096</v>
+        <v>0.2876712328767124</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.2784350701479137</v>
+        <v>0.2757306374795556</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.263013698630137</v>
+        <v>0.2602739726027397</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.03443396226415094</v>
+        <v>0.03476190476190476</v>
       </c>
     </row>
     <row r="6">
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21930</v>
+        <v>22000</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.115038980934722</v>
+        <v>-0.1150895906384884</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.023985408116735</v>
+        <v>0.02072727272727271</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.539547956826016</v>
+        <v>6.536895261315942</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.389645211416521</v>
+        <v>7.387070139713353</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>6.936986301369863</v>
+        <v>6.934246575342466</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001529157682766428</v>
+        <v>0.00152977822043104</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21930</v>
+        <v>22000</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05321048748690295</v>
+        <v>-0.05329208796837026</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2355677154582763</v>
+        <v>0.2316363636363636</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.9519053762009</v>
+        <v>1.949166249148641</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.061604348594745</v>
+        <v>2.058888728378472</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>1.934246575342466</v>
+        <v>1.931506849315068</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005123199168324209</v>
+        <v>0.00513039870476303</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1960</v>
+        <v>1958</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04530803675898716</v>
+        <v>0.04544203953860144</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.145767579591837</v>
+        <v>3.150002275791624</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.873972602739726</v>
+        <v>0.8712328767123287</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.8360909626692506</v>
+        <v>0.8333631552609471</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.8465753424657534</v>
+        <v>0.8438356164383561</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01144200626959248</v>
+        <v>0.01147798742138365</v>
       </c>
     </row>
     <row r="9">
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>215.8</v>
+        <v>204.2</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1603033782532479</v>
+        <v>0.1604873323299112</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.705129749768304</v>
+        <v>2.915607247796278</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.653464516309146</v>
+        <v>1.650717559276519</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.42502775334354</v>
+        <v>1.422434793805437</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.682191780821918</v>
+        <v>1.679452054794521</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006047907228346177</v>
+        <v>0.006057971543225618</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12670</v>
+        <v>12810</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.01141996748075672</v>
+        <v>-0.01143895728257028</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4383583267561169</v>
+        <v>0.4226385636221701</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.114378014677867</v>
+        <v>4.111647798591146</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.161906855627067</v>
+        <v>4.159224995644927</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.271232876712329</v>
+        <v>4.268493150684932</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002430501029396285</v>
+        <v>0.00243211493052165</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03578318009617597</v>
+        <v>0.03576526505383156</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4812548648648649</v>
+        <v>0.4772622641509434</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.639608977373526</v>
+        <v>2.636873192842595</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.548418460636163</v>
+        <v>2.545821222056089</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.761643835616439</v>
+        <v>2.758904109589041</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003788439911259219</v>
+        <v>0.003792370458747706</v>
       </c>
     </row>
     <row r="12">
@@ -2111,7 +2111,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>-0.06301369863013699</v>
+        <v>-0.06575342465753424</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1249004263418048</v>
+        <v>-0.1249900346814356</v>
       </c>
       <c r="AZ13" s="12" t="n">
         <v>0.01149425287356332</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.233423787972602</v>
+        <v>4.230764201188809</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.837648097890781</v>
+        <v>4.83510402038509</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.512328767123288</v>
+        <v>4.50958904109589</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002362154251698252</v>
+        <v>0.002363639173554055</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>247.1</v>
+        <v>251.8</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2317,22 +2317,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1917219148654573</v>
+        <v>-0.1918837154269528</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.01819233104006468</v>
+        <v>-0.0008128474980143574</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.158252042702036</v>
+        <v>3.155567273669307</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.907382992050719</v>
+        <v>3.904843070123863</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.265753424657534</v>
+        <v>3.263013698630137</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003166308408826207</v>
+        <v>0.003169002316458923</v>
       </c>
     </row>
     <row r="15">
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>165.3</v>
+        <v>166.9</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>78</v>
+        <v>80.8</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1698634992879429</v>
+        <v>-0.1741518710138694</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1549807692307694</v>
+        <v>0.1257487623762379</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.90968305549486</v>
+        <v>1.907955296363158</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.300444630319004</v>
+        <v>2.310298018965665</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.027397260273973</v>
+        <v>2.024657534246575</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005236471031790499</v>
+        <v>0.005241212946163603</v>
       </c>
     </row>
     <row r="16">
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18800</v>
+        <v>18910</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.04810171211750659</v>
+        <v>-0.0482070444492743</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1376860425531916</v>
+        <v>0.1310680909571655</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.763611138270861</v>
+        <v>1.760873866067473</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.852730654862328</v>
+        <v>1.85005978012161</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.761643835616438</v>
+        <v>1.758904109589041</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.00567018419366785</v>
+        <v>0.005678998474963353</v>
       </c>
     </row>
     <row r="17">
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>81.3</v>
+        <v>83</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05639063068338313</v>
+        <v>0.05639608920738953</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8702952029520297</v>
+        <v>0.8319879518072291</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.010138375054706</v>
+        <v>3.007395632197277</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.849455767235872</v>
+        <v>2.846844723226603</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.265753424657534</v>
+        <v>3.263013698630137</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003322106413070881</v>
+        <v>0.003325136171955451</v>
       </c>
     </row>
     <row r="18">
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1254840132165949</v>
+        <v>0.1255950562429721</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>1.815909090909091</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.735433148740968</v>
+        <v>1.732688659250039</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.541943846702148</v>
+        <v>1.539353473205038</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.761643835616438</v>
+        <v>1.758904109589041</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005762250195148606</v>
+        <v>0.00577137730232984</v>
       </c>
     </row>
     <row r="19">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>150.6</v>
+        <v>153.1</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.02021039975459032</v>
+        <v>0.02019070035293249</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5199203187250998</v>
+        <v>0.4951012410189419</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.202309827563509</v>
+        <v>3.199580202604133</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.138871970265955</v>
+        <v>3.136256977736855</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.427397260273973</v>
+        <v>3.424657534246575</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003122745936050961</v>
+        <v>0.003125410012182541</v>
       </c>
     </row>
     <row r="20">
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>28940</v>
+        <v>29170</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5732674013963318</v>
+        <v>-0.5739656366865296</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.01068538396682794</v>
+        <v>-0.01848594487487143</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.440565271131374</v>
+        <v>1.43784412902835</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.375803198174022</v>
+        <v>3.374948719736026</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.424657534246575</v>
+        <v>1.421917808219178</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006941719476651216</v>
+        <v>0.00695485678740274</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>427.4</v>
+        <v>424.8</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3124,22 +3124,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03832033830218638</v>
+        <v>0.0383253619463534</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5692137295273747</v>
+        <v>0.5788181450094159</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.789041095890411</v>
+        <v>0.7863013698630137</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.7599206784108792</v>
+        <v>0.7572784010486676</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.7616438356164383</v>
+        <v>0.7589041095890411</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01267361111111111</v>
+        <v>0.01271777003484321</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>99.8</v>
+        <v>103.9</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>218.9</v>
+        <v>219.9</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.0710349824690458</v>
+        <v>0.04938638771371716</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.04860666971219718</v>
+        <v>0.08672123692587541</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.848837391444845</v>
+        <v>1.851859737697134</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.726215690156768</v>
+        <v>1.764707222600585</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.027397260273973</v>
+        <v>2.024657534246575</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005408804498585521</v>
+        <v>0.005399977004973078</v>
       </c>
     </row>
     <row r="23">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>91.40000000000001</v>
+        <v>91</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10290</v>
+        <v>10280</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02602154346821414</v>
+        <v>0.02707209549673521</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5648592223517981</v>
+        <v>0.5595263978599223</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.328184727320187</v>
+        <v>4.32528459274995</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.218415056558968</v>
+        <v>4.211276512831421</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.353424657534247</v>
+        <v>4.35068493150685</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002310437430472507</v>
+        <v>0.002311986595462878</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>31.1</v>
+        <v>29</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1748501690145606</v>
+        <v>0.1749479219144304</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.4903857099678455</v>
+        <v>0.598310192413793</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.913665155363805</v>
+        <v>2.910861398824401</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.480031268844882</v>
+        <v>2.477438654541826</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.265753424657534</v>
+        <v>3.263013698630137</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003432103370420196</v>
+        <v>0.00343540918988402</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>27.1</v>
+        <v>28.7</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.2663214874333596</v>
+        <v>0.2816427706600622</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>1.066420664206642</v>
+        <v>0.8815331010452963</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.882490007602664</v>
+        <v>2.869585024381855</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.27627031224514</v>
+        <v>2.238989748215084</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.265753424657534</v>
+        <v>3.263013698630137</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003469222780868161</v>
+        <v>0.003484824431070526</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3699,22 +3699,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>70.4023291294851</v>
+        <v>71.02948504983389</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.3144705882352941</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.2904109589041096</v>
+        <v>0.2876712328767123</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.004067247699685841</v>
+        <v>0.003993798271328551</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.263013698630137</v>
+        <v>0.2602739726027397</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.03443396226415095</v>
+        <v>0.03476190476190476</v>
       </c>
     </row>
     <row r="27">
@@ -3808,22 +3808,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05493612701997067</v>
+        <v>0.05520146449364043</v>
       </c>
       <c r="AZ27" s="12" t="n">
         <v>0.5669759999999999</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.2849315068493151</v>
+        <v>0.2821917808219178</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.2700936099839542</v>
+        <v>0.2674292922416793</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.263013698630137</v>
+        <v>0.2602739726027397</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.03509615384615385</v>
+        <v>0.0354368932038835</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12720</v>
+        <v>12640</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3938,15 +3938,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-2.740454556007244</v>
+        <v>-2.766573022450769</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.05146573710691826</v>
+        <v>0.05812058354430394</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.263013698630137</v>
+        <v>0.2602739726027397</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15200</v>
+        <v>15490</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1659360997514702</v>
+        <v>-0.1661131074680614</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.4069460526315791</v>
+        <v>0.3806055519690124</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.690265414763648</v>
+        <v>2.687557684532717</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.225490773503106</v>
+        <v>3.22292832349536</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.761643835616439</v>
+        <v>2.758904109589041</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.00371710536258689</v>
+        <v>0.003720850368180541</v>
       </c>
     </row>
     <row r="30">
@@ -4189,22 +4189,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05529947979981375</v>
+        <v>0.05529882708525183</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.6679981972265023</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.635294287300261</v>
+        <v>2.632554706269672</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.49720040400301</v>
+        <v>2.494605924599405</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.761643835616439</v>
+        <v>2.758904109589041</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003794642612853893</v>
+        <v>0.003798591526392244</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1061607797875998</v>
+        <v>0.1062089103476732</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.403872302549575</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.172829168181852</v>
+        <v>2.170077276229604</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.964297783726403</v>
+        <v>1.961724639830974</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.334246575342466</v>
+        <v>2.331506849315069</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004602294624186979</v>
+        <v>0.004608130829964949</v>
       </c>
     </row>
     <row r="32">
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67790</v>
+        <v>68350</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4412,22 +4412,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2740983094259248</v>
+        <v>-0.2745157619182195</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.145567192801298</v>
+        <v>0.1361814191660571</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.633112992255719</v>
+        <v>1.630388461989407</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.249771578523507</v>
+        <v>2.247310660118877</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.635616438356164</v>
+        <v>1.632876712328767</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.006123275025929228</v>
+        <v>0.006133507586160146</v>
       </c>
     </row>
     <row r="33">
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>137.9</v>
+        <v>136</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.1104985171449335</v>
+        <v>-0.1106370533476557</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.01907904278462658</v>
+        <v>0.03331617647058827</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.67055465362284</v>
+        <v>2.667843006983109</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>3.002304892231388</v>
+        <v>2.999723585320426</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.761643835616439</v>
+        <v>2.758904109589041</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003744540478298816</v>
+        <v>0.003748346500834153</v>
       </c>
     </row>
     <row r="34">
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.0326709147027008</v>
+        <v>0.03265149770848563</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.2363636363636363</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.664273538342823</v>
+        <v>1.661534578771719</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.611620424907538</v>
+        <v>1.608998372111755</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.682191780821918</v>
+        <v>1.679452054794521</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.006008627650210289</v>
+        <v>0.006018532582928516</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9441</v>
+        <v>9667</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.009566246963531927</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1425861518906895</v>
+        <v>0.115874196751836</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.739754568280932</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>103.8</v>
+        <v>104.3</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.01762785642334557</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2181888246628134</v>
+        <v>0.2123489932885909</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.39201683584805</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6379</v>
+        <v>6310</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.04330529064998117</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.563332810785389</v>
+        <v>1.591362916006339</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2876712328767124</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>280.7</v>
+        <v>284.5</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>22000</v>
+        <v>22500</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1150895906384884</v>
+        <v>-0.1169064719173714</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02072727272727271</v>
+        <v>0.01155555555555554</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.536895261315942</v>
+        <v>6.540010165060608</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.387070139713353</v>
+        <v>7.405795600450464</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.934246575342466</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.00152977822043104</v>
+        <v>0.001529049611180127</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22000</v>
+        <v>22500</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.05329208796837026</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2316363636363636</v>
+        <v>0.2042666666666666</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.949166249148641</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1958</v>
+        <v>1950</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04544203953860144</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.150002275791624</v>
+        <v>3.167027926153846</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8712328767123287</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>204.2</v>
+        <v>207.5</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1604873323299112</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.915607247796278</v>
+        <v>2.853334939759036</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.650717559276519</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12810</v>
+        <v>12720</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.01143895728257028</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4226385636221701</v>
+        <v>0.4327044025157232</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.111647798591146</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03576526505383156</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4772622641509434</v>
+        <v>0.478590737410072</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.636873192842595</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>217.5</v>
+        <v>220</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2211,7 +2211,7 @@
         <v>-0.1249900346814356</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.01149425287356332</v>
+        <v>0</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.230764201188809</v>
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>251.8</v>
+        <v>254.5</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1918837154269528</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.0008128474980143574</v>
+        <v>-0.01141326129666009</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.155567273669307</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>80.8</v>
+        <v>80.3</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2429,7 +2429,7 @@
         <v>-0.1741518710138694</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1257487623762379</v>
+        <v>0.1327584059775841</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.907955296363158</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18910</v>
+        <v>18810</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2538,7 +2538,7 @@
         <v>-0.0482070444492743</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1310680909571655</v>
+        <v>0.1370812121212122</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.760873866067473</v>
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>153.1</v>
+        <v>152.1</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.02019070035293249</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4951012410189419</v>
+        <v>0.5049309664694281</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.199580202604133</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>29170</v>
+        <v>29390</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5739656366865296</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.01848594487487143</v>
+        <v>-0.02583310690711127</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.43784412902835</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>424.8</v>
+        <v>431.7</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.0383253619463534</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5788181450094159</v>
+        <v>0.5535833866110724</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7863013698630137</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103.9</v>
+        <v>101.4</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>219.9</v>
+        <v>219.1</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.04938638771371716</v>
+        <v>0.06243105910591953</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.08672123692587541</v>
+        <v>0.0644454586946599</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.851859737697134</v>
+        <v>1.848394008568063</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.764707222600585</v>
+        <v>1.7397778356777</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>2.024657534246575</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005399977004973078</v>
+        <v>0.005410101933703476</v>
       </c>
     </row>
     <row r="23">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10280</v>
+        <v>10260</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02707209549673521</v>
+        <v>0.0244890650131334</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5595263978599223</v>
+        <v>0.5797374697855751</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.32528459274995</v>
+        <v>4.325678332870479</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.211276512831421</v>
+        <v>4.222278675873447</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.35068493150685</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002311986595462878</v>
+        <v>0.002311776149421655</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>29</v>
+        <v>30.7</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3480,7 +3480,7 @@
         <v>0.1749479219144304</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.598310192413793</v>
+        <v>0.5098044162866449</v>
       </c>
       <c r="BA24" s="8" t="n">
         <v>2.910861398824401</v>
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>54</v>
+        <v>53.8</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>28.7</v>
+        <v>27.3</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.2816427706600622</v>
+        <v>0.2831985294939926</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.8815331010452963</v>
+        <v>0.9706959706959706</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.869585024381855</v>
+        <v>2.868546887997529</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.238989748215084</v>
+        <v>2.235466159027389</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.263013698630137</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003484824431070526</v>
+        <v>0.0034860856002883</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>99.2</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3808,16 +3808,16 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05520146449364043</v>
+        <v>0.04810123808940307</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5669759999999999</v>
+        <v>0.5728055238095238</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2821917808219178</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.2674292922416793</v>
+        <v>0.2692409574253807</v>
       </c>
       <c r="BC27" s="8" t="n">
         <v>0.2602739726027397</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12640</v>
+        <v>12840</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-2.766573022450769</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.05812058354430394</v>
+        <v>0.04163895451713406</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15490</v>
+        <v>15870</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.1661131074680614</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.3806055519690124</v>
+        <v>0.3475475740390674</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.687557684532717</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>68350</v>
+        <v>67450</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2745157619182195</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1361814191660571</v>
+        <v>0.1513417346182357</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.630388461989407</v>
@@ -4450,7 +4450,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>157.9</v>
+        <v>149.6</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.1106370533476557</v>
+        <v>-0.09257993774314148</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.03331617647058827</v>
+        <v>-0.02099999999999991</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.667843006983109</v>
+        <v>2.664162737376534</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.999723585320426</v>
+        <v>2.935975132344389</v>
       </c>
       <c r="BC33" s="8" t="n">
         <v>2.758904109589041</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003748346500834153</v>
+        <v>0.003753524459938676</v>
       </c>
     </row>
     <row r="34">
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102</v>
+        <v>102.9</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -4616,7 +4616,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1485</v>
+        <v>1477</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03265149770848563</v>
+        <v>0.02727611864167912</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2363636363636363</v>
+        <v>0.2540284360189573</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.661534578771719</v>
+        <v>1.661746810883719</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.608998372111755</v>
+        <v>1.617624298597511</v>
       </c>
       <c r="BC34" s="8" t="n">
         <v>1.679452054794521</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.006018532582928516</v>
+        <v>0.006017763918368518</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>80.7</v>
+        <v>70</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>840.9</v>
+        <v>840</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1168384124043399</v>
+        <v>0.1689705570791011</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.6314662861220124</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.009562005713872</v>
+        <v>2.981417946177591</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.694715701293672</v>
+        <v>2.550464533193411</v>
       </c>
       <c r="BC2" s="8" t="n">
         <v>3.263013698630137</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.00332274263863455</v>
+        <v>0.003354108743063272</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>110.5</v>
+        <v>113.9</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9667</v>
+        <v>9857</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.009566246963531927</v>
+        <v>-0.0265088746722648</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.115874196751836</v>
+        <v>0.1280377749822461</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.739754568280932</v>
+        <v>1.740471653374817</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.756558238193316</v>
+        <v>1.78786596825818</v>
       </c>
       <c r="BC3" s="8" t="n">
         <v>1.758904109589041</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005747937198912543</v>
+        <v>0.005745569013209585</v>
       </c>
     </row>
     <row r="4">
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>104.3</v>
+        <v>104.9</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,10 +1163,10 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01762785642334557</v>
+        <v>0.01762785642334554</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2123489932885909</v>
+        <v>0.2054146806482366</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.39201683584805</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6310</v>
+        <v>6288</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.04330529064998117</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.591362916006339</v>
+        <v>1.600429389312977</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2876712328767124</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>284.5</v>
+        <v>290.9</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>22500</v>
+        <v>22780</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1169064719173714</v>
+        <v>-0.119902283121301</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.01155555555555554</v>
+        <v>0.02159789288849878</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.540010165060608</v>
+        <v>6.545106081680873</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.405795600450464</v>
+        <v>7.436794751488901</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.934246575342466</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001529049611180127</v>
+        <v>0.001527859117209581</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>112.9</v>
+        <v>115.8</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22500</v>
+        <v>22780</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05329208796837026</v>
+        <v>-0.06552685813335095</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2042666666666666</v>
+        <v>0.2200175592625109</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.949166249148641</v>
+        <v>1.949256064677667</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.058888728378472</v>
+        <v>2.085941240412696</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>1.931506849315068</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.00513039870476303</v>
+        <v>0.005130162312283799</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1950</v>
+        <v>1969</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04544203953860144</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.167027926153846</v>
+        <v>3.126817905535805</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8712328767123287</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>207.5</v>
+        <v>206.4</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1604873323299112</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.853334939759036</v>
+        <v>2.873871124031008</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.650717559276519</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12720</v>
+        <v>12850</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.01143895728257028</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4327044025157232</v>
+        <v>0.4182101167315175</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.111647798591146</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1112</v>
+        <v>1121</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03576526505383156</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.478590737410072</v>
+        <v>0.4667198037466547</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.636873192842595</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>220</v>
+        <v>218.2</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2211,7 +2211,7 @@
         <v>-0.1249900346814356</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0</v>
+        <v>0.008249312557286892</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.230764201188809</v>
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>254.5</v>
+        <v>255</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1918837154269528</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.01141326129666009</v>
+        <v>-0.01335166666666665</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.155567273669307</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>80.3</v>
+        <v>77.8</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2429,7 +2429,7 @@
         <v>-0.1741518710138694</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1327584059775841</v>
+        <v>0.1691580976863756</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.907955296363158</v>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>114</v>
+        <v>114.1</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18810</v>
+        <v>18910</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.0482070444492743</v>
+        <v>-0.04867862341678582</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1370812121212122</v>
+        <v>0.1320602559492332</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.760873866067473</v>
+        <v>1.760884852131167</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.85005978012161</v>
+        <v>1.850988420396478</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.758904109589041</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005678998474963353</v>
+        <v>0.005678963044004373</v>
       </c>
     </row>
     <row r="17">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>98.09999999999999</v>
+        <v>98</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>83</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05639608920738953</v>
+        <v>0.05674185150895975</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8319879518072291</v>
+        <v>0.82791817087846</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.007395632197277</v>
+        <v>3.007204501715036</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.846844723226603</v>
+        <v>2.845732377705057</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.263013698630137</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003325136171955451</v>
+        <v>0.003325347509388506</v>
       </c>
     </row>
     <row r="18">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>88.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1255950562429721</v>
+        <v>0.1212671156459339</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.815909090909091</v>
+        <v>1.835</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.732688659250039</v>
+        <v>1.732874352290148</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.539353473205038</v>
+        <v>1.545460781030649</v>
       </c>
       <c r="BC18" s="8" t="n">
         <v>1.758904109589041</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.00577137730232984</v>
+        <v>0.005770758847451408</v>
       </c>
     </row>
     <row r="19">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>152.1</v>
+        <v>151.3</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.02019070035293249</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5049309664694281</v>
+        <v>0.5128883013879708</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.199580202604133</v>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>356.6</v>
+        <v>367.5</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>29390</v>
+        <v>29600</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5739656366865296</v>
+        <v>-0.5827563193068285</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.02583310690711127</v>
+        <v>-0.003178846283783843</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.43784412902835</v>
+        <v>1.438078157773562</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.374948719736026</v>
+        <v>3.446614590745788</v>
       </c>
       <c r="BC20" s="8" t="n">
         <v>1.421917808219178</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.00695485678740274</v>
+        <v>0.006953724973809518</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>431.7</v>
+        <v>446.2</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.0383253619463534</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5535833866110724</v>
+        <v>0.5030971492604213</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7863013698630137</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101.4</v>
+        <v>100.8</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>219.1</v>
+        <v>218</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.06243105910591953</v>
+        <v>0.06563487225613968</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.0644454586946599</v>
+        <v>0.06348623853211</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.848394008568063</v>
+        <v>1.847539889750176</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.7397778356777</v>
+        <v>1.733745711454247</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>2.024657534246575</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005410101933703476</v>
+        <v>0.005412603027127169</v>
       </c>
     </row>
     <row r="23">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>92</v>
+        <v>91.7</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10260</v>
+        <v>10310</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.0244890650131334</v>
+        <v>0.02526031837143243</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5797374697855751</v>
+        <v>0.5669499436469447</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.325678332870479</v>
+        <v>4.325561001774156</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.222278675873447</v>
+        <v>4.218988021154534</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.35068493150685</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002311776149421655</v>
+        <v>0.002311838856485537</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53.8</v>
+        <v>54</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>27.3</v>
+        <v>28.2</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.2831985294939926</v>
+        <v>0.2816427706600622</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.9706959706959706</v>
+        <v>0.9148936170212767</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.868546887997529</v>
+        <v>2.869585024381855</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.235466159027389</v>
+        <v>2.238989748215084</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.263013698630137</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.0034860856002883</v>
+        <v>0.003484824431070526</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3685,7 +3685,7 @@
         <v>0.55865</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AK26" s="10" t="n">
         <v>46377</v>
@@ -3702,7 +3702,7 @@
         <v>71.02948504983389</v>
       </c>
       <c r="AZ26" s="12" t="n">
-        <v>0.3144705882352941</v>
+        <v>0.2414444444444444</v>
       </c>
       <c r="BA26" s="8" t="n">
         <v>0.2876712328767123</v>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.04810123808940307</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5728055238095238</v>
+        <v>0.5781734607508533</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2821917808219178</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12840</v>
+        <v>12920</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-2.766573022450769</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.04163895451713406</v>
+        <v>0.03518917770897856</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185.8</v>
+        <v>191.7</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15870</v>
+        <v>15960</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1661131074680614</v>
+        <v>-0.1756993748914391</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.3475475740390674</v>
+        <v>0.3824981203007518</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.687557684532717</v>
+        <v>2.68928458298455</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.22292832349536</v>
+        <v>3.262504602165465</v>
       </c>
       <c r="BC29" s="8" t="n">
         <v>2.758904109589041</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003720850368180541</v>
+        <v>0.003718461059596031</v>
       </c>
     </row>
     <row r="30">
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67450</v>
+        <v>67530</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2745157619182195</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1513417346182357</v>
+        <v>0.1499777876499333</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.630388461989407</v>
@@ -4450,7 +4450,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>149.6</v>
+        <v>155</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.09257993774314148</v>
+        <v>-0.1044809869050111</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.02099999999999991</v>
+        <v>0.02947761194029841</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.664162737376534</v>
+        <v>2.666592920033851</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.935975132344389</v>
+        <v>2.977706649485734</v>
       </c>
       <c r="BC33" s="8" t="n">
         <v>2.758904109589041</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003753524459938676</v>
+        <v>0.003750103709070471</v>
       </c>
     </row>
     <row r="34">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1689705570791011</v>
+        <v>0.1482967954688154</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4976190476190476</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.981417946177591</v>
+        <v>2.992742506914415</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.550464533193411</v>
+        <v>2.606244760695833</v>
       </c>
       <c r="BC2" s="8" t="n">
         <v>3.263013698630137</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003354108743063272</v>
+        <v>0.003341416769700721</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>104.9</v>
+        <v>105.6</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,10 +1163,10 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01762785642334554</v>
+        <v>0.01762785642334557</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2054146806482366</v>
+        <v>0.1974242424242427</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.39201683584805</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6288</v>
+        <v>6320</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.04330529064998117</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.600429389312977</v>
+        <v>1.587262658227848</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2876712328767124</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>22780</v>
+        <v>22800</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.119902283121301</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02159789288849878</v>
+        <v>0.02070175438596489</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.545106081680873</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22780</v>
+        <v>22800</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.06552685813335095</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2200175592625109</v>
+        <v>0.2189473684210526</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.949256064677667</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04544203953860144</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.126817905535805</v>
+        <v>3.122630368340944</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8712328767123287</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12850</v>
+        <v>12840</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.01143895728257028</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4182101167315175</v>
+        <v>0.4193146417445484</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.111647798591146</v>
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>255</v>
+        <v>255.3</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1918837154269528</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.01335166666666665</v>
+        <v>-0.01451106541323932</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.155567273669307</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18910</v>
+        <v>18900</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2538,7 +2538,7 @@
         <v>-0.04867862341678582</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1320602559492332</v>
+        <v>0.1326592296296296</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.760884852131167</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>29600</v>
+        <v>29540</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5827563193068285</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.003178846283783843</v>
+        <v>-0.001154158767772584</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.438078157773562</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>446.2</v>
+        <v>444.3</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.0383253619463534</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5030971492604213</v>
+        <v>0.5095249786180507</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7863013698630137</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10310</v>
+        <v>10250</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.02526031837143243</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5669499436469447</v>
+        <v>0.5761223335609758</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.325561001774156</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12920</v>
+        <v>12910</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-2.766573022450769</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.03518917770897856</v>
+        <v>0.03599102835011636</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15960</v>
+        <v>15970</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.1756993748914391</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.3824981203007518</v>
+        <v>0.381632435817157</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.68928458298455</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67530</v>
+        <v>67550</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2745157619182195</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1499777876499333</v>
+        <v>0.149637305699482</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.630388461989407</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>74</v>
+        <v>75.7</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>840</v>
+        <v>827.5</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1482967954688154</v>
+        <v>0.1399612834439084</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.4976190476190476</v>
+        <v>0.555166163141994</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.992742506914415</v>
+        <v>2.997247950087674</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.606244760695833</v>
+        <v>2.629254162942064</v>
       </c>
       <c r="BC2" s="8" t="n">
         <v>3.263013698630137</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003341416769700721</v>
+        <v>0.003336393974248105</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>113.9</v>
+        <v>112.8</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9857</v>
+        <v>9875</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.0265088746722648</v>
+        <v>-0.02111544708156895</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1280377749822461</v>
+        <v>0.1151073312405062</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.740471653374817</v>
+        <v>1.740243263585492</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.78786596825818</v>
+        <v>1.777781923718336</v>
       </c>
       <c r="BC3" s="8" t="n">
         <v>1.758904109589041</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005745569013209585</v>
+        <v>0.005746323062556557</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112.9</v>
+        <v>112</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>105.6</v>
+        <v>105</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01762785642334557</v>
+        <v>0.01946806236815078</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.1974242424242427</v>
+        <v>0.1946666666666668</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.39201683584805</v>
+        <v>4.390154925350555</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.315936133356905</v>
+        <v>4.306319233927292</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.758904109589041</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002276858303087336</v>
+        <v>0.002277823942443557</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6320</v>
+        <v>6314</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.04330529064998117</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.587262658227848</v>
+        <v>1.5897212543554</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2876712328767124</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>290.9</v>
+        <v>293.8</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>22800</v>
+        <v>22900</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.119902283121301</v>
+        <v>-0.1212341130033419</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02070175438596489</v>
+        <v>0.02637554585152846</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.545106081680873</v>
+        <v>6.547355539462034</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.436794751488901</v>
+        <v>7.450625515105973</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.934246575342466</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001527859117209581</v>
+        <v>0.001527334194657413</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22800</v>
+        <v>22900</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.06552685813335095</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2189473684210526</v>
+        <v>0.2136244541484715</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.949256064677667</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1971</v>
+        <v>2031</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04544203953860144</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.122630368340944</v>
+        <v>3.000839220088626</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8712328767123287</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>206.4</v>
+        <v>205.8</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1604873323299112</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.873871124031008</v>
+        <v>2.885165208940719</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.650717559276519</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>113.9</v>
+        <v>112.5</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12840</v>
+        <v>12820</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.01143895728257028</v>
+        <v>-0.008497475162268866</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4193146417445484</v>
+        <v>0.4040561622464898</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.111647798591146</v>
+        <v>4.110170381565014</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.159224995644927</v>
+        <v>4.145395779236853</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.268493150684932</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.00243211493052165</v>
+        <v>0.002432989163868272</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105</v>
+        <v>104.7</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1121</v>
+        <v>1131</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03576526505383156</v>
+        <v>0.03687734792133907</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4667198037466547</v>
+        <v>0.4495978832891248</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.636873192842595</v>
+        <v>2.636628455876081</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.545821222056089</v>
+        <v>2.542854717736687</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.758904109589041</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003792370458747706</v>
+        <v>0.003792722473928269</v>
       </c>
     </row>
     <row r="12">
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>218.2</v>
+        <v>221.9</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2211,7 +2211,7 @@
         <v>-0.1249900346814356</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.008249312557286892</v>
+        <v>-0.008562415502478604</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.230764201188809</v>
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>255.3</v>
+        <v>258.7</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1918837154269528</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.01451106541323932</v>
+        <v>-0.02746298801700808</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.155567273669307</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>77.8</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2429,7 +2429,7 @@
         <v>-0.1741518710138694</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1691580976863756</v>
+        <v>0.1797730220492868</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.907955296363158</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18900</v>
+        <v>18640</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2538,7 +2538,7 @@
         <v>-0.04867862341678582</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1326592296296296</v>
+        <v>0.1484581244635195</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.760884852131167</v>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>98</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>83.09999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05674185150895975</v>
+        <v>0.05639608920738953</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.82791817087846</v>
+        <v>0.8253901560624251</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.007204501715036</v>
+        <v>3.007395632197277</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.845732377705057</v>
+        <v>2.846844723226603</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.263013698630137</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003325347509388506</v>
+        <v>0.003325136171955451</v>
       </c>
     </row>
     <row r="18">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>89.09999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1212671156459339</v>
+        <v>0.1255950562429721</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.835</v>
+        <v>1.815909090909091</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.732874352290148</v>
+        <v>1.732688659250039</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.545460781030649</v>
+        <v>1.539353473205038</v>
       </c>
       <c r="BC18" s="8" t="n">
         <v>1.758904109589041</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005770758847451408</v>
+        <v>0.00577137730232984</v>
       </c>
     </row>
     <row r="19">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>151.3</v>
+        <v>151</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.02019070035293249</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5128883013879708</v>
+        <v>0.5158940397350993</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.199580202604133</v>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>367.5</v>
+        <v>368.5</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>29540</v>
+        <v>29090</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5827563193068285</v>
+        <v>-0.5835407094672453</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.001154158767772584</v>
+        <v>0.01705721313166042</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.438078157773562</v>
+        <v>1.438099045478295</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.446614590745788</v>
+        <v>3.453156354462906</v>
       </c>
       <c r="BC20" s="8" t="n">
         <v>1.421917808219178</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006953724973809518</v>
+        <v>0.006953623974261185</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>444.3</v>
+        <v>440</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.0383253619463534</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5095249786180507</v>
+        <v>0.5242771545454543</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7863013698630137</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>218</v>
+        <v>218.6</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3262,7 +3262,7 @@
         <v>0.06563487225613968</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.06348623853211</v>
+        <v>0.06056724611161934</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.847539889750176</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10250</v>
+        <v>10260</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.02526031837143243</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5761223335609758</v>
+        <v>0.5745861519493178</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.325561001774156</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>71.7</v>
+        <v>71</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>30.7</v>
+        <v>32.2</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1749479219144304</v>
+        <v>0.1787094749277197</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.5098044162866449</v>
+        <v>0.4254184906832295</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.910861398824401</v>
+        <v>2.908393790472131</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.477438654541826</v>
+        <v>2.467439052910369</v>
       </c>
       <c r="BC24" s="8" t="n">
         <v>3.263013698630137</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.00343540918988402</v>
+        <v>0.003438323941125133</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>28.2</v>
+        <v>27.8</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3589,7 +3589,7 @@
         <v>0.2816427706600622</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.9148936170212767</v>
+        <v>0.9424460431654675</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>2.869585024381855</v>
@@ -3685,7 +3685,7 @@
         <v>0.55865</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AK26" s="10" t="n">
         <v>46377</v>
@@ -3702,7 +3702,7 @@
         <v>71.02948504983389</v>
       </c>
       <c r="AZ26" s="12" t="n">
-        <v>0.2414444444444444</v>
+        <v>0.3144705882352941</v>
       </c>
       <c r="BA26" s="8" t="n">
         <v>0.2876712328767123</v>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1172</v>
+        <v>1180</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.04810123808940307</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5781734607508533</v>
+        <v>0.5674739796610171</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2821917808219178</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12910</v>
+        <v>12860</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-2.766573022450769</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.03599102835011636</v>
+        <v>0.04001898724727848</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>191.7</v>
+        <v>187.3</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15970</v>
+        <v>15940</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1756993748914391</v>
+        <v>-0.1685898756295238</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.381632435817157</v>
+        <v>0.352461104140527</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.68928458298455</v>
+        <v>2.688004969251736</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.262504602165465</v>
+        <v>3.233067400143856</v>
       </c>
       <c r="BC29" s="8" t="n">
         <v>2.758904109589041</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003718461059596031</v>
+        <v>0.003720231217721192</v>
       </c>
     </row>
     <row r="30">
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67550</v>
+        <v>66800</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2745157619182195</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.149637305699482</v>
+        <v>0.1625449101796408</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.630388461989407</v>
@@ -4450,7 +4450,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>155</v>
+        <v>155.5</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>134</v>
+        <v>136.1</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.1044809869050111</v>
+        <v>-0.1055537487562172</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.02947761194029841</v>
+        <v>0.01686260102865544</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.666592920033851</v>
+        <v>2.66681110484042</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.977706649485734</v>
+        <v>2.9815219205537</v>
       </c>
       <c r="BC33" s="8" t="n">
         <v>2.758904109589041</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003750103709070471</v>
+        <v>0.003749796894819212</v>
       </c>
     </row>
     <row r="34">
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102.9</v>
+        <v>102.2</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -4616,7 +4616,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1477</v>
+        <v>1485</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.02727611864167912</v>
+        <v>0.03145044298557292</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2540284360189573</v>
+        <v>0.2387878787878788</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.661746810883719</v>
+        <v>1.66158199096457</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.617624298597511</v>
+        <v>1.610917909109678</v>
       </c>
       <c r="BC34" s="8" t="n">
         <v>1.679452054794521</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.006017763918368518</v>
+        <v>0.006018360847901866</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1399612834439084</v>
+        <v>0.1400409741031489</v>
       </c>
       <c r="AZ2" s="12" t="n">
         <v>0.555166163141994</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.997247950087674</v>
+        <v>2.99446531605948</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.629254162942064</v>
+        <v>2.626629554622083</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.263013698630137</v>
+        <v>3.26027397260274</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003336393974248105</v>
+        <v>0.003339494348580182</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.02111544708156895</v>
+        <v>-0.02121413340935381</v>
       </c>
       <c r="AZ3" s="12" t="n">
         <v>0.1151073312405062</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.740243263585492</v>
+        <v>1.73750771554476</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.777781923718336</v>
+        <v>1.775166330912531</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.758904109589041</v>
+        <v>1.756164383561644</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005746323062556557</v>
+        <v>0.00575537012614917</v>
       </c>
     </row>
     <row r="4">
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01946806236815078</v>
+        <v>0.01945442233537062</v>
       </c>
       <c r="AZ4" s="12" t="n">
         <v>0.1946666666666668</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.390154925350555</v>
+        <v>4.387429020155971</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.306319233927292</v>
+        <v>4.30370296506756</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.758904109589041</v>
+        <v>4.756164383561644</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002277823942443557</v>
+        <v>0.002279239152145761</v>
       </c>
     </row>
     <row r="5">
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.04330529064998117</v>
+        <v>0.04360481664495425</v>
       </c>
       <c r="AZ5" s="12" t="n">
         <v>1.5897212543554</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.2876712328767124</v>
+        <v>0.2849315068493151</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.2757306374795556</v>
+        <v>0.273026247392505</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.2602739726027397</v>
+        <v>0.2575342465753425</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.03476190476190476</v>
+        <v>0.03509615384615385</v>
       </c>
     </row>
     <row r="6">
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1212341130033419</v>
+        <v>-0.1212866589803199</v>
       </c>
       <c r="AZ6" s="12" t="n">
         <v>0.02637554585152846</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.547355539462034</v>
+        <v>6.544704362001168</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.450625515105973</v>
+        <v>7.448053940328863</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>6.934246575342466</v>
+        <v>6.931506849315069</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001527334194657413</v>
+        <v>0.00152795289853892</v>
       </c>
     </row>
     <row r="7">
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.06552685813335095</v>
+        <v>-0.06562450832607496</v>
       </c>
       <c r="AZ7" s="12" t="n">
         <v>0.2136244541484715</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.949256064677667</v>
+        <v>1.94651705556634</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.085941240412696</v>
+        <v>2.083227859582631</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>1.931506849315068</v>
+        <v>1.928767123287671</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005130162312283799</v>
+        <v>0.005137381134885817</v>
       </c>
     </row>
     <row r="8">
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04544203953860144</v>
+        <v>0.04557688788239497</v>
       </c>
       <c r="AZ8" s="12" t="n">
         <v>3.000839220088626</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.8712328767123287</v>
+        <v>0.8684931506849315</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.8333631552609471</v>
+        <v>0.8306353753131337</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.8438356164383561</v>
+        <v>0.8410958904109589</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01147798742138365</v>
+        <v>0.01151419558359621</v>
       </c>
     </row>
     <row r="9">
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1604873323299112</v>
+        <v>0.1606719431067762</v>
       </c>
       <c r="AZ9" s="12" t="n">
         <v>2.885165208940719</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.650717559276519</v>
+        <v>1.647970576540252</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.422434793805437</v>
+        <v>1.41984183069776</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.679452054794521</v>
+        <v>1.676712328767123</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006057971543225618</v>
+        <v>0.006068069504610933</v>
       </c>
     </row>
     <row r="10">
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.008497475162268866</v>
+        <v>-0.008514728812566584</v>
       </c>
       <c r="AZ10" s="3" t="n">
         <v>0.4040561622464898</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.110170381565014</v>
+        <v>4.107439347052186</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.145395779236853</v>
+        <v>4.142713428443561</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.268493150684932</v>
+        <v>4.265753424657534</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002432989163868272</v>
+        <v>0.00243460685723254</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03687734792133907</v>
+        <v>0.03686038202138076</v>
       </c>
       <c r="AZ11" s="12" t="n">
         <v>0.4495978832891248</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.636628455876081</v>
+        <v>2.633892464572339</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.542854717736687</v>
+        <v>2.540257599039045</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.758904109589041</v>
+        <v>2.756164383561644</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003792722473928269</v>
+        <v>0.003796662215525828</v>
       </c>
     </row>
     <row r="12">
@@ -2111,7 +2111,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>-0.06575342465753424</v>
+        <v>-0.0684931506849315</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1249900346814356</v>
+        <v>-0.1250797473096705</v>
       </c>
       <c r="AZ13" s="12" t="n">
         <v>-0.008562415502478604</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.230764201188809</v>
+        <v>4.228104693957276</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.83510402038509</v>
+        <v>4.832560088712197</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.50958904109589</v>
+        <v>4.506849315068493</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002363639173554055</v>
+        <v>0.002365125919017995</v>
       </c>
     </row>
     <row r="14">
@@ -2317,22 +2317,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1918837154269528</v>
+        <v>-0.192045761287203</v>
       </c>
       <c r="AZ14" s="12" t="n">
         <v>-0.02746298801700808</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.155567273669307</v>
+        <v>3.152882574329551</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.904843070123863</v>
+        <v>3.902303401926089</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.263013698630137</v>
+        <v>3.26027397260274</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003169002316458923</v>
+        <v>0.003171700741860475</v>
       </c>
     </row>
     <row r="15">
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1741518710138694</v>
+        <v>-0.1744269324469626</v>
       </c>
       <c r="AZ15" s="12" t="n">
         <v>0.1797730220492868</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.907955296363158</v>
+        <v>1.905280386232012</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.310298018965665</v>
+        <v>2.307827690987038</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.024657534246575</v>
+        <v>2.021917808219178</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005241212946163603</v>
+        <v>0.005248571324337491</v>
       </c>
     </row>
     <row r="16">
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.04867862341678582</v>
+        <v>-0.04878492361306582</v>
       </c>
       <c r="AZ16" s="12" t="n">
         <v>0.1484581244635195</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.760884852131167</v>
+        <v>1.758147602543335</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.850988420396478</v>
+        <v>1.848317637291272</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.758904109589041</v>
+        <v>1.756164383561644</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005678963044004373</v>
+        <v>0.005687804587927661</v>
       </c>
     </row>
     <row r="17">
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05639608920738953</v>
+        <v>0.05640156410336023</v>
       </c>
       <c r="AZ17" s="12" t="n">
         <v>0.8253901560624251</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.007395632197277</v>
+        <v>3.004652880274715</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.846844723226603</v>
+        <v>2.844233653539664</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.263013698630137</v>
+        <v>3.26027397260274</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003325136171955451</v>
+        <v>0.00332817147220204</v>
       </c>
     </row>
     <row r="18">
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1255950562429721</v>
+        <v>0.1257064775185884</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>1.815909090909091</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.732688659250039</v>
+        <v>1.729944153581238</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.539353473205038</v>
+        <v>1.536763080012278</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.758904109589041</v>
+        <v>1.756164383561644</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.00577137730232984</v>
+        <v>0.005780533423173538</v>
       </c>
     </row>
     <row r="19">
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.02019070035293249</v>
+        <v>0.0201709719679054</v>
       </c>
       <c r="AZ19" s="12" t="n">
         <v>0.5158940397350993</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.199580202604133</v>
+        <v>3.196850592289757</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.136256977736855</v>
+        <v>3.133641987600418</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.424657534246575</v>
+        <v>3.421917808219178</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003125410012182541</v>
+        <v>0.003128078623417136</v>
       </c>
     </row>
     <row r="20">
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5835407094672453</v>
+        <v>-0.5842424441630839</v>
       </c>
       <c r="AZ20" s="12" t="n">
         <v>0.01705721313166042</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.438099045478295</v>
+        <v>1.435378006852319</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.453156354462906</v>
+        <v>3.452439977820526</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.421917808219178</v>
+        <v>1.419178082191781</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006953623974261185</v>
+        <v>0.006966805923081743</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3124,22 +3124,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.0383253619463534</v>
+        <v>0.03833044601034927</v>
       </c>
       <c r="AZ21" s="12" t="n">
         <v>0.5242771545454543</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.7863013698630137</v>
+        <v>0.7835616438356164</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.7572784010486676</v>
+        <v>0.7546361053423319</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.7589041095890411</v>
+        <v>0.7561643835616438</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01271777003484321</v>
+        <v>0.01276223776223776</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.06563487225613968</v>
+        <v>0.06563246570607856</v>
       </c>
       <c r="AZ22" s="12" t="n">
         <v>0.06056724611161934</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.847539889750176</v>
+        <v>1.844800805725357</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.733745711454247</v>
+        <v>1.731179243401718</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.024657534246575</v>
+        <v>2.021917808219178</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005412603027127169</v>
+        <v>0.005420639436499001</v>
       </c>
     </row>
     <row r="23">
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02526031837143243</v>
+        <v>0.02527299747918941</v>
       </c>
       <c r="AZ23" s="12" t="n">
         <v>0.5745861519493178</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.325561001774156</v>
+        <v>4.32281934520798</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.218988021154534</v>
+        <v>4.216261772070831</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.35068493150685</v>
+        <v>4.347945205479452</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002311838856485537</v>
+        <v>0.002313305091290804</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1787094749277197</v>
+        <v>0.1788106330380194</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.4254184906832295</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.908393790472131</v>
+        <v>2.905587604482425</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.467439052910369</v>
+        <v>2.464846789678316</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.263013698630137</v>
+        <v>3.26027397260274</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003438323941125133</v>
+        <v>0.003441644638273197</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.2816427706600622</v>
+        <v>0.281840340069726</v>
       </c>
       <c r="AZ25" s="12" t="n">
         <v>0.9424460431654675</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.869585024381855</v>
+        <v>2.86671352323734</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.238989748215084</v>
+        <v>2.236404514372987</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.263013698630137</v>
+        <v>3.26027397260274</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003484824431070526</v>
+        <v>0.003488315075413304</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3699,22 +3699,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>71.02948504983389</v>
+        <v>71.66875251419121</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.3144705882352941</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.2876712328767123</v>
+        <v>0.2849315068493151</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.003993798271328551</v>
+        <v>0.00392096323373202</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.2602739726027397</v>
+        <v>0.2575342465753425</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.03476190476190476</v>
+        <v>0.03509615384615385</v>
       </c>
     </row>
     <row r="27">
@@ -3808,22 +3808,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.04810123808940307</v>
+        <v>0.04830327518023549</v>
       </c>
       <c r="AZ27" s="12" t="n">
         <v>0.5674739796610171</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.2821917808219178</v>
+        <v>0.2794520547945206</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.2692409574253807</v>
+        <v>0.2665755811422741</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.2602739726027397</v>
+        <v>0.2575342465753425</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.0354368932038835</v>
+        <v>0.03578431372549019</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3938,7 +3938,7 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-2.766573022450769</v>
+        <v>-2.793193766078819</v>
       </c>
       <c r="AZ28" s="12" t="n">
         <v>0.04001898724727848</v>
@@ -3946,7 +3946,7 @@
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.2602739726027397</v>
+        <v>0.2575342465753425</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1685898756295238</v>
+        <v>-0.1687689889981818</v>
       </c>
       <c r="AZ29" s="12" t="n">
         <v>0.352461104140527</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.688004969251736</v>
+        <v>2.685297559679325</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.233067400143856</v>
+        <v>3.230506951903712</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.758904109589041</v>
+        <v>2.756164383561644</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003720231217721192</v>
+        <v>0.003723982083085864</v>
       </c>
     </row>
     <row r="30">
@@ -4189,22 +4189,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05529882708525183</v>
+        <v>0.05529818192979388</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.6679981972265023</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.632554706269672</v>
+        <v>2.629815123559825</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.494605924599405</v>
+        <v>2.492011422544817</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.758904109589041</v>
+        <v>2.756164383561644</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003798591526392244</v>
+        <v>0.003802548669833335</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1062089103476732</v>
+        <v>0.1062571818692628</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.403872302549575</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.170077276229604</v>
+        <v>2.167325348402473</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.961724639830974</v>
+        <v>1.959151437769927</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.331506849315069</v>
+        <v>2.328767123287671</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004608130829964949</v>
+        <v>0.00461398193278686</v>
       </c>
     </row>
     <row r="32">
@@ -4412,22 +4412,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2745157619182195</v>
+        <v>-0.2749343729530297</v>
       </c>
       <c r="AZ32" s="12" t="n">
         <v>0.1625449101796408</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.630388461989407</v>
+        <v>1.627663974372104</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.247310660118877</v>
+        <v>2.244850553737066</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.632876712328767</v>
+        <v>1.63013698630137</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.006133507586160146</v>
+        <v>0.006143774241767346</v>
       </c>
     </row>
     <row r="33">
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.1055537487562172</v>
+        <v>-0.105688636389984</v>
       </c>
       <c r="AZ33" s="12" t="n">
         <v>0.01686260102865544</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.66681110484042</v>
+        <v>2.664098802831206</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.9815219205537</v>
+        <v>2.978938780423397</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.758904109589041</v>
+        <v>2.756164383561644</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003749796894819212</v>
+        <v>0.003753614539135239</v>
       </c>
     </row>
     <row r="34">
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03145044298557292</v>
+        <v>0.03142915513151236</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.2387878787878788</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.66158199096457</v>
+        <v>1.658843105327449</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.610917909109678</v>
+        <v>1.608295729352287</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.679452054794521</v>
+        <v>1.676712328767123</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.006018360847901866</v>
+        <v>0.006028297653879715</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1400409741031489</v>
+        <v>0.1401208259735178</v>
       </c>
       <c r="AZ2" s="12" t="n">
         <v>0.555166163141994</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.99446531605948</v>
+        <v>2.991682592015035</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.626629554622083</v>
+        <v>2.62400486322186</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.26027397260274</v>
+        <v>3.257534246575343</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003339494348580182</v>
+        <v>0.003342600590948568</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.02121413340935381</v>
+        <v>-0.02131311353087684</v>
       </c>
       <c r="AZ3" s="12" t="n">
         <v>0.1151073312405062</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.73750771554476</v>
+        <v>1.734772179978741</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.775166330912531</v>
+        <v>1.7725507554693</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.756164383561644</v>
+        <v>1.753424657534246</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.00575537012614917</v>
+        <v>0.005764445680770916</v>
       </c>
     </row>
     <row r="4">
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01945442233537062</v>
+        <v>0.01944076837437696</v>
       </c>
       <c r="AZ4" s="12" t="n">
         <v>0.1946666666666668</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.387429020155971</v>
+        <v>4.384703128776279</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.30370296506756</v>
+        <v>4.301086698512385</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.756164383561644</v>
+        <v>4.753424657534246</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002279239152145761</v>
+        <v>0.002280656114292255</v>
       </c>
     </row>
     <row r="5">
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.04360481664495425</v>
+        <v>0.04391016644094273</v>
       </c>
       <c r="AZ5" s="12" t="n">
         <v>1.5897212543554</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.2849315068493151</v>
+        <v>0.2821917808219178</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.273026247392505</v>
+        <v>0.2703219011497981</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.2575342465753425</v>
+        <v>0.2547945205479452</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.03509615384615385</v>
+        <v>0.0354368932038835</v>
       </c>
     </row>
     <row r="6">
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1212866589803199</v>
+        <v>-0.1213392449247728</v>
       </c>
       <c r="AZ6" s="12" t="n">
         <v>0.02637554585152846</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.544704362001168</v>
+        <v>6.542053236592693</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.448053940328863</v>
+        <v>7.44548245589117</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>6.931506849315069</v>
+        <v>6.928767123287671</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.00152795289853892</v>
+        <v>0.001528572091719681</v>
       </c>
     </row>
     <row r="7">
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.06562450832607496</v>
+        <v>-0.0657224233571122</v>
       </c>
       <c r="AZ7" s="12" t="n">
         <v>0.2136244541484715</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.94651705556634</v>
+        <v>1.943778048400407</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.083227859582631</v>
+        <v>2.080514503393015</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>1.928767123287671</v>
+        <v>1.926027397260274</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005137381134885817</v>
+        <v>0.005144620296658508</v>
       </c>
     </row>
     <row r="8">
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04557688788239497</v>
+        <v>0.04571258981787338</v>
       </c>
       <c r="AZ8" s="12" t="n">
         <v>3.000839220088626</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.8684931506849315</v>
+        <v>0.8657534246575341</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.8306353753131337</v>
+        <v>0.8279076230767367</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.8410958904109589</v>
+        <v>0.8383561643835616</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01151419558359621</v>
+        <v>0.01155063291139241</v>
       </c>
     </row>
     <row r="9">
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1606719431067762</v>
+        <v>0.1608572140275503</v>
       </c>
       <c r="AZ9" s="12" t="n">
         <v>2.885165208940719</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.647970576540252</v>
+        <v>1.645223567966159</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.41984183069776</v>
+        <v>1.417248864102862</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.676712328767123</v>
+        <v>1.673972602739726</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006068069504610933</v>
+        <v>0.006078201282006977</v>
       </c>
     </row>
     <row r="10">
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.008514728812566584</v>
+        <v>-0.008532004598993531</v>
       </c>
       <c r="AZ10" s="3" t="n">
         <v>0.4040561622464898</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.107439347052186</v>
+        <v>4.104708323388309</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.142713428443561</v>
+        <v>4.140031087668271</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.265753424657534</v>
+        <v>4.263013698630137</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.00243460685723254</v>
+        <v>0.002436226696796159</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03686038202138076</v>
+        <v>0.0368433890718616</v>
       </c>
       <c r="AZ11" s="12" t="n">
         <v>0.4495978832891248</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.633892464572339</v>
+        <v>2.631156479191243</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.540257599039045</v>
+        <v>2.537660467263569</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.756164383561644</v>
+        <v>2.753424657534246</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003796662215525828</v>
+        <v>0.003800610141998765</v>
       </c>
     </row>
     <row r="12">
@@ -2111,7 +2111,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>-0.0684931506849315</v>
+        <v>-0.07123287671232877</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1250797473096705</v>
+        <v>-0.1251695644073662</v>
       </c>
       <c r="AZ13" s="12" t="n">
         <v>-0.008562415502478604</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.228104693957276</v>
+        <v>4.225445266392144</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.832560088712197</v>
+        <v>4.830016303136176</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.506849315068493</v>
+        <v>4.504109589041096</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002365125919017995</v>
+        <v>0.00236661449138552</v>
       </c>
     </row>
     <row r="14">
@@ -2317,22 +2317,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.192045761287203</v>
+        <v>-0.1922080529967915</v>
       </c>
       <c r="AZ14" s="12" t="n">
         <v>-0.02746298801700808</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.152882574329551</v>
+        <v>3.15019794480821</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.902303401926089</v>
+        <v>3.899763988109797</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.26027397260274</v>
+        <v>3.257534246575343</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003171700741860475</v>
+        <v>0.003174403696275923</v>
       </c>
     </row>
     <row r="15">
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1744269324469626</v>
+        <v>-0.1747026793857149</v>
       </c>
       <c r="AZ15" s="12" t="n">
         <v>0.1797730220492868</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.905280386232012</v>
+        <v>1.902605626374028</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.307827690987038</v>
+        <v>2.3053578133004</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.021917808219178</v>
+        <v>2.019178082191781</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005248571324337491</v>
+        <v>0.005255949977956246</v>
       </c>
     </row>
     <row r="16">
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.04878492361306582</v>
+        <v>-0.04889154160435109</v>
       </c>
       <c r="AZ16" s="12" t="n">
         <v>0.1484581244635195</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.758147602543335</v>
+        <v>1.755410360371673</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.848317637291272</v>
+        <v>1.845646881673977</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.756164383561644</v>
+        <v>1.753424657534246</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005687804587927661</v>
+        <v>0.005696673681407862</v>
       </c>
     </row>
     <row r="17">
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05640156410336023</v>
+        <v>0.0564070554146265</v>
       </c>
       <c r="AZ17" s="12" t="n">
         <v>0.8253901560624251</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.004652880274715</v>
+        <v>3.00191011926292</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.844233653539664</v>
+        <v>2.841622558157479</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.26027397260274</v>
+        <v>3.257534246575343</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.00332817147220204</v>
+        <v>0.003331212329053799</v>
       </c>
     </row>
     <row r="18">
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1257064775185884</v>
+        <v>0.125818278900018</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>1.815909090909091</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.729944153581238</v>
+        <v>1.727199631655412</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.536763080012278</v>
+        <v>1.534172667140362</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.756164383561644</v>
+        <v>1.753424657534246</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005780533423173538</v>
+        <v>0.005789718696509696</v>
       </c>
     </row>
     <row r="19">
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.0201709719679054</v>
+        <v>0.02015121452491104</v>
       </c>
       <c r="AZ19" s="12" t="n">
         <v>0.5158940397350993</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.196850592289757</v>
+        <v>3.194120996657674</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.133641987600418</v>
+        <v>3.131026999899412</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.421917808219178</v>
+        <v>3.419178082191781</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003128078623417136</v>
+        <v>0.00313075178130822</v>
       </c>
     </row>
     <row r="20">
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5842424441630839</v>
+        <v>-0.5849456643072832</v>
       </c>
       <c r="AZ20" s="12" t="n">
         <v>0.01705721313166042</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.435378006852319</v>
+        <v>1.432657008492887</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.452439977820526</v>
+        <v>3.451733629289314</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.419178082191781</v>
+        <v>1.416438356164384</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006966805923081743</v>
+        <v>0.006980037748546463</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3124,22 +3124,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03833044601034927</v>
+        <v>0.03833559112270663</v>
       </c>
       <c r="AZ21" s="12" t="n">
         <v>0.5242771545454543</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.7835616438356164</v>
+        <v>0.7808219178082191</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.7546361053423319</v>
+        <v>0.7519937912981974</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.7561643835616438</v>
+        <v>0.7534246575342466</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01276223776223776</v>
+        <v>0.01280701754385965</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.06563246570607856</v>
+        <v>0.06563007039814722</v>
       </c>
       <c r="AZ22" s="12" t="n">
         <v>0.06056724611161934</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.844800805725357</v>
+        <v>1.842061718700799</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.731179243401718</v>
+        <v>1.728612742705878</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.021917808219178</v>
+        <v>2.019178082191781</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005420639436499001</v>
+        <v>0.005428699754453923</v>
       </c>
     </row>
     <row r="23">
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02527299747918941</v>
+        <v>0.02528569288409933</v>
       </c>
       <c r="AZ23" s="12" t="n">
         <v>0.5745861519493178</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.32281934520798</v>
+        <v>4.320077686106528</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.216261772070831</v>
+        <v>4.21353552096711</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.347945205479452</v>
+        <v>4.345205479452055</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002313305091290804</v>
+        <v>0.002314773188491549</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1788106330380194</v>
+        <v>0.1789120095459956</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.4254184906832295</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.905587604482425</v>
+        <v>2.902781269789748</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.464846789678316</v>
+        <v>2.462254389034193</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.26027397260274</v>
+        <v>3.257534246575343</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003441644638273197</v>
+        <v>0.003444971932289033</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.281840340069726</v>
+        <v>0.282038352472558</v>
       </c>
       <c r="AZ25" s="12" t="n">
         <v>0.9424460431654675</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.86671352323734</v>
+        <v>2.863841709036468</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.236404514372987</v>
+        <v>2.233819061273183</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.26027397260274</v>
+        <v>3.257534246575343</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003488315075413304</v>
+        <v>0.003491813101417702</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3699,22 +3699,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>71.66875251419121</v>
+        <v>72.3204841965202</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.3144705882352941</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.2849315068493151</v>
+        <v>0.2821917808219178</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.00392096323373202</v>
+        <v>0.003848744098109907</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.2575342465753425</v>
+        <v>0.2547945205479452</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.03509615384615385</v>
+        <v>0.0354368932038835</v>
       </c>
     </row>
     <row r="27">
@@ -3808,22 +3808,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.04830327518023549</v>
+        <v>0.0485093534618949</v>
       </c>
       <c r="AZ27" s="12" t="n">
         <v>0.5674739796610171</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.2794520547945206</v>
+        <v>0.2767123287671233</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.2665755811422741</v>
+        <v>0.263910214871707</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.2575342465753425</v>
+        <v>0.2547945205479452</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.03578431372549019</v>
+        <v>0.03613861386138614</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3938,7 +3938,7 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-2.793193766078819</v>
+        <v>-2.820331416324033</v>
       </c>
       <c r="AZ28" s="12" t="n">
         <v>0.04001898724727848</v>
@@ -3946,7 +3946,7 @@
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.2575342465753425</v>
+        <v>0.2547945205479452</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1687689889981818</v>
+        <v>-0.1689484257232958</v>
       </c>
       <c r="AZ29" s="12" t="n">
         <v>0.352461104140527</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.685297559679325</v>
+        <v>2.682590204388005</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.230506951903712</v>
+        <v>3.22794672126428</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.756164383561644</v>
+        <v>2.753424657534246</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003723982083085864</v>
+        <v>0.003727740444158283</v>
       </c>
     </row>
     <row r="30">
@@ -4189,22 +4189,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05529818192979388</v>
+        <v>0.05529754435441166</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.6679981972265023</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.629815123559825</v>
+        <v>2.627075539166064</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.492011422544817</v>
+        <v>2.489416897841075</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.756164383561644</v>
+        <v>2.753424657534246</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003802548669833335</v>
+        <v>0.00380651406893857</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1062571818692628</v>
+        <v>0.1063055948941665</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.403872302549575</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.167325348402473</v>
+        <v>2.164573384561379</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.959151437769927</v>
+        <v>1.956578177450554</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.328767123287671</v>
+        <v>2.326027397260274</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.00461398193278686</v>
+        <v>0.004619847990058495</v>
       </c>
     </row>
     <row r="32">
@@ -4412,22 +4412,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2749343729530297</v>
+        <v>-0.275354147280667</v>
       </c>
       <c r="AZ32" s="12" t="n">
         <v>0.1625449101796408</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.627663974372104</v>
+        <v>1.624939529580728</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.244850553737066</v>
+        <v>2.242391263929711</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.63013698630137</v>
+        <v>1.627397260273973</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.006143774241767346</v>
+        <v>0.006154075162772507</v>
       </c>
     </row>
     <row r="33">
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.105688636389984</v>
+        <v>-0.1058237768386565</v>
       </c>
       <c r="AZ33" s="12" t="n">
         <v>0.01686260102865544</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.664098802831206</v>
+        <v>2.661386549925596</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.978938780423397</v>
+        <v>2.97635575738786</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.756164383561644</v>
+        <v>2.753424657534246</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003753614539135239</v>
+        <v>0.003757439895485895</v>
       </c>
     </row>
     <row r="34">
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03142915513151236</v>
+        <v>0.03140780612540221</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.2387878787878788</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.658843105327449</v>
+        <v>1.656104222105935</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.608295729352287</v>
+        <v>1.605673538895614</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.676712328767123</v>
+        <v>1.673972602739726</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.006028297653879715</v>
+        <v>0.006038267318275295</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1401208259735178</v>
+        <v>0.1402008395204669</v>
       </c>
       <c r="AZ2" s="12" t="n">
         <v>0.555166163141994</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.991682592015035</v>
+        <v>2.98889977768435</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.62400486322186</v>
+        <v>2.621380088565264</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.257534246575343</v>
+        <v>3.254794520547945</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003342600590948568</v>
+        <v>0.003345712718325906</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.02131311353087684</v>
+        <v>-0.02141238879583553</v>
       </c>
       <c r="AZ3" s="12" t="n">
         <v>0.1151073312405062</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.734772179978741</v>
+        <v>1.732036656944906</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.7725507554693</v>
+        <v>1.769935197538024</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.753424657534246</v>
+        <v>1.750684931506849</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005764445680770916</v>
+        <v>0.005773549861028194</v>
       </c>
     </row>
     <row r="4">
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01944076837437696</v>
+        <v>0.01942710045875439</v>
       </c>
       <c r="AZ4" s="12" t="n">
         <v>0.1946666666666668</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.384703128776279</v>
+        <v>4.381977251237329</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.301086698512385</v>
+        <v>4.298470434291366</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.753424657534246</v>
+        <v>4.750684931506849</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002280656114292255</v>
+        <v>0.002282074832126598</v>
       </c>
     </row>
     <row r="5">
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.04391016644094273</v>
+        <v>0.04422151132543733</v>
       </c>
       <c r="AZ5" s="12" t="n">
         <v>1.5897212543554</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.2821917808219178</v>
+        <v>0.2794520547945206</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.2703219011497981</v>
+        <v>0.2676176000624716</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.2547945205479452</v>
+        <v>0.252054794520548</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.0354368932038835</v>
+        <v>0.03578431372549019</v>
       </c>
     </row>
     <row r="6">
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1213392449247728</v>
+        <v>-0.1213918708817559</v>
       </c>
       <c r="AZ6" s="12" t="n">
         <v>0.02637554585152846</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.542053236592693</v>
+        <v>6.539402163278995</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.44548245589117</v>
+        <v>7.442911061888108</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>6.928767123287671</v>
+        <v>6.926027397260274</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001528572091719681</v>
+        <v>0.001529191774770094</v>
       </c>
     </row>
     <row r="7">
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.0657224233571122</v>
+        <v>-0.06582060430528981</v>
       </c>
       <c r="AZ7" s="12" t="n">
         <v>0.2136244541484715</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.943778048400407</v>
+        <v>1.9410390431878</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.080514503393015</v>
+        <v>2.077801171951915</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>1.926027397260274</v>
+        <v>1.923287671232877</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005144620296658508</v>
+        <v>0.005151879883661091</v>
       </c>
     </row>
     <row r="8">
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04571258981787338</v>
+        <v>0.04584915347447836</v>
       </c>
       <c r="AZ8" s="12" t="n">
         <v>3.000839220088626</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.8657534246575341</v>
+        <v>0.863013698630137</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.8279076230767367</v>
+        <v>0.8251798988057383</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.8383561643835616</v>
+        <v>0.8356164383561644</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01155063291139241</v>
+        <v>0.01158730158730159</v>
       </c>
     </row>
     <row r="9">
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1608572140275503</v>
+        <v>0.1610431485601067</v>
       </c>
       <c r="AZ9" s="12" t="n">
         <v>2.885165208940719</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.645223567966159</v>
+        <v>1.642476533419118</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.417248864102862</v>
+        <v>1.414655894103567</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.673972602739726</v>
+        <v>1.671232876712329</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006078201282006977</v>
+        <v>0.006088367046062543</v>
       </c>
     </row>
     <row r="10">
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.008532004598993531</v>
+        <v>-0.008549302565250039</v>
       </c>
       <c r="AZ10" s="3" t="n">
         <v>0.4040561622464898</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.104708323388309</v>
+        <v>4.101977310594242</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.140031087668271</v>
+        <v>4.137348756935242</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.263013698630137</v>
+        <v>4.260273972602739</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002436226696796159</v>
+        <v>0.002437848686820583</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.0368433890718616</v>
+        <v>0.03682636898651232</v>
       </c>
       <c r="AZ11" s="12" t="n">
         <v>0.4495978832891248</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.631156479191243</v>
+        <v>2.628420499751627</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.537660467263569</v>
+        <v>2.535063322435446</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.753424657534246</v>
+        <v>2.750684931506849</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003800610141998765</v>
+        <v>0.003804566278852623</v>
       </c>
     </row>
     <row r="12">
@@ -2111,7 +2111,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>-0.07123287671232877</v>
+        <v>-0.07397260273972603</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1251695644073662</v>
+        <v>-0.1252594861557903</v>
       </c>
       <c r="AZ13" s="12" t="n">
         <v>-0.008562415502478604</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.225445266392144</v>
+        <v>4.222785918607767</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.830016303136176</v>
+        <v>4.827472663921727</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.504109589041096</v>
+        <v>4.501369863013698</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.00236661449138552</v>
+        <v>0.002368104893959899</v>
       </c>
     </row>
     <row r="14">
@@ -2317,22 +2317,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1922080529967915</v>
+        <v>-0.1923705911079219</v>
       </c>
       <c r="AZ14" s="12" t="n">
         <v>-0.02746298801700808</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.15019794480821</v>
+        <v>3.147513385231009</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.899763988109797</v>
+        <v>3.897224829329618</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.257534246575343</v>
+        <v>3.254794520547945</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003174403696275923</v>
+        <v>0.003177111190987376</v>
       </c>
     </row>
     <row r="15">
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1747026793857149</v>
+        <v>-0.1749791143689337</v>
       </c>
       <c r="AZ15" s="12" t="n">
         <v>0.1797730220492868</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.902605626374028</v>
+        <v>1.89993101729986</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.3053578133004</v>
+        <v>2.302888387906186</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.019178082191781</v>
+        <v>2.016438356164384</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005255949977956246</v>
+        <v>0.005263348989486881</v>
       </c>
     </row>
     <row r="16">
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.04889154160435109</v>
+        <v>-0.04899847882579004</v>
       </c>
       <c r="AZ16" s="12" t="n">
         <v>0.1484581244635195</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.755410360371673</v>
+        <v>1.752673125649728</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.845646881673977</v>
+        <v>1.842976153692885</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.753424657534246</v>
+        <v>1.750684931506849</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005696673681407862</v>
+        <v>0.005705570453299974</v>
       </c>
     </row>
     <row r="17">
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.0564070554146265</v>
+        <v>0.05641256318467983</v>
       </c>
       <c r="AZ17" s="12" t="n">
         <v>0.8253901560624251</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.00191011926292</v>
+        <v>2.999167349137707</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.841622558157479</v>
+        <v>2.839011437062395</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.257534246575343</v>
+        <v>3.254794520547945</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003331212329053799</v>
+        <v>0.003334258757809933</v>
       </c>
     </row>
     <row r="18">
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.125818278900018</v>
+        <v>0.1259304622560446</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>1.815909090909091</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.727199631655412</v>
+        <v>1.724455093392893</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.534172667140362</v>
+        <v>1.531582234605835</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.753424657534246</v>
+        <v>1.750684931506849</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005789718696509696</v>
+        <v>0.005798933262057197</v>
       </c>
     </row>
     <row r="19">
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.02015121452491104</v>
+        <v>0.02013142794909992</v>
       </c>
       <c r="AZ19" s="12" t="n">
         <v>0.5158940397350993</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.194120996657674</v>
+        <v>3.191391415745299</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.131026999899412</v>
+        <v>3.128412014676736</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.419178082191781</v>
+        <v>3.416438356164384</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.00313075178130822</v>
+        <v>0.003133429497448422</v>
       </c>
     </row>
     <row r="20">
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5849456643072832</v>
+        <v>-0.585650373573996</v>
       </c>
       <c r="AZ20" s="12" t="n">
         <v>0.01705721313166042</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.432657008492887</v>
+        <v>1.429936050502389</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.451733629289314</v>
+        <v>3.45103738317899</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.416438356164384</v>
+        <v>1.413698630136986</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006980037748546463</v>
+        <v>0.00699331973376476</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3124,22 +3124,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03833559112270663</v>
+        <v>0.03834079792081418</v>
       </c>
       <c r="AZ21" s="12" t="n">
         <v>0.5242771545454543</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.7808219178082191</v>
+        <v>0.7780821917808219</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.7519937912981974</v>
+        <v>0.7493514589226031</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.7534246575342466</v>
+        <v>0.7506849315068493</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01280701754385965</v>
+        <v>0.01285211267605634</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.06563007039814722</v>
+        <v>0.06562768637590169</v>
       </c>
       <c r="AZ22" s="12" t="n">
         <v>0.06056724611161934</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.842061718700799</v>
+        <v>1.839322628664895</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.728612742705878</v>
+        <v>1.72604620936629</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.019178082191781</v>
+        <v>2.016438356164384</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005428699754453923</v>
+        <v>0.005436784087878416</v>
       </c>
     </row>
     <row r="23">
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02528569288409933</v>
+        <v>0.02529840461751157</v>
       </c>
       <c r="AZ23" s="12" t="n">
         <v>0.5745861519493178</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.320077686106528</v>
+        <v>4.317336024464821</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.21353552096711</v>
+        <v>4.210809267839841</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.345205479452055</v>
+        <v>4.342465753424658</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002314773188491549</v>
+        <v>0.002316243151641087</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1789120095459956</v>
+        <v>0.179013605109158</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.4254184906832295</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.902781269789748</v>
+        <v>2.899974785928891</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.462254389034193</v>
+        <v>2.459661850687804</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.257534246575343</v>
+        <v>3.254794520547945</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003444971932289033</v>
+        <v>0.003448305843389221</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.282038352472558</v>
+        <v>0.2822368092974915</v>
       </c>
       <c r="AZ25" s="12" t="n">
         <v>0.9424460431654675</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.863841709036468</v>
+        <v>2.860969580712264</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.233819061273183</v>
+        <v>2.231233388378333</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.257534246575343</v>
+        <v>3.254794520547945</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003491813101417702</v>
+        <v>0.00349531853376449</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3699,22 +3699,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>72.3204841965202</v>
+        <v>72.98504660134512</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.3144705882352941</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.2821917808219178</v>
+        <v>0.2794520547945206</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.003848744098109907</v>
+        <v>0.00377714237716571</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.2547945205479452</v>
+        <v>0.252054794520548</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.0354368932038835</v>
+        <v>0.03578431372549019</v>
       </c>
     </row>
     <row r="27">
@@ -3808,22 +3808,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.0485093534618949</v>
+        <v>0.04871959416099816</v>
       </c>
       <c r="AZ27" s="12" t="n">
         <v>0.5674739796610171</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.2767123287671233</v>
+        <v>0.273972602739726</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.263910214871707</v>
+        <v>0.2612448592217931</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.2547945205479452</v>
+        <v>0.252054794520548</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.03613861386138614</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3938,7 +3938,7 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-2.820331416324033</v>
+        <v>-2.848001176322295</v>
       </c>
       <c r="AZ28" s="12" t="n">
         <v>0.04001898724727848</v>
@@ -3946,7 +3946,7 @@
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.2547945205479452</v>
+        <v>0.252054794520548</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1689484257232958</v>
+        <v>-0.1691281866764841</v>
       </c>
       <c r="AZ29" s="12" t="n">
         <v>0.352461104140527</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.682590204388005</v>
+        <v>2.679882903512479</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.22794672126428</v>
+        <v>3.22538670892307</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.753424657534246</v>
+        <v>2.750684931506849</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003727740444158283</v>
+        <v>0.003731506323240155</v>
       </c>
     </row>
     <row r="30">
@@ -4189,22 +4189,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05529754435441166</v>
+        <v>0.05529691438016596</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.6679981972265023</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.627075539166064</v>
+        <v>2.624335953083712</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.489416897841075</v>
+        <v>2.486822350489984</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.753424657534246</v>
+        <v>2.750684931506849</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.00380651406893857</v>
+        <v>0.003810487749577013</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1063055948941665</v>
+        <v>0.1063541499670041</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.403872302549575</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.164573384561379</v>
+        <v>2.161821384566506</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.956578177450554</v>
+        <v>1.954004858779605</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.326027397260274</v>
+        <v>2.323287671232876</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004619847990058495</v>
+        <v>0.00462572905948251</v>
       </c>
     </row>
     <row r="32">
@@ -4412,22 +4412,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.275354147280667</v>
+        <v>-0.275775089676862</v>
       </c>
       <c r="AZ32" s="12" t="n">
         <v>0.1625449101796408</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.624939529580728</v>
+        <v>1.622215127793154</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.242391263929711</v>
+        <v>2.239932795282264</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.627397260273973</v>
+        <v>1.624657534246575</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.006154075162772507</v>
+        <v>0.006164410520325937</v>
       </c>
     </row>
     <row r="33">
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.1058237768386565</v>
+        <v>-0.1059591708182548</v>
       </c>
       <c r="AZ33" s="12" t="n">
         <v>0.01686260102865544</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.661386549925596</v>
+        <v>2.658674346255964</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.97635575738786</v>
+        <v>2.973772851838621</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.753424657534246</v>
+        <v>2.750684931506849</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003757439895485895</v>
+        <v>0.003761272987074307</v>
       </c>
     </row>
     <row r="34">
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03140780612540221</v>
+        <v>0.03138639566287028</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.2387878787878788</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.656104222105935</v>
+        <v>1.65336534131206</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.605673538895614</v>
+        <v>1.603051337757315</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.673972602739726</v>
+        <v>1.671232876712329</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.006038267318275295</v>
+        <v>0.006048270004295788</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1402008395204669</v>
+        <v>0.1402810152112663</v>
       </c>
       <c r="AZ2" s="12" t="n">
         <v>0.555166163141994</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.98889977768435</v>
+        <v>2.986116872796339</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.621380088565264</v>
+        <v>2.618755230475431</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.254794520547945</v>
+        <v>3.252054794520548</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003345712718325906</v>
+        <v>0.003348830747751522</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.02141238879583553</v>
+        <v>-0.02151196056218583</v>
       </c>
       <c r="AZ3" s="12" t="n">
         <v>0.1151073312405062</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.732036656944906</v>
+        <v>1.729301146501076</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.769935197538024</v>
+        <v>1.767319657269023</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.750684931506849</v>
+        <v>1.747945205479452</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005773549861028194</v>
+        <v>0.005782682802375496</v>
       </c>
     </row>
     <row r="4">
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01942710045875439</v>
+        <v>0.019413418562023</v>
       </c>
       <c r="AZ4" s="12" t="n">
         <v>0.1946666666666668</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.381977251237329</v>
+        <v>4.379251387565035</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.298470434291366</v>
+        <v>4.295854172434158</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.750684931506849</v>
+        <v>4.747945205479452</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002282074832126598</v>
+        <v>0.002283495308900326</v>
       </c>
     </row>
     <row r="5">
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.04422151132543733</v>
+        <v>0.04453902936959349</v>
       </c>
       <c r="AZ5" s="12" t="n">
         <v>1.5897212543554</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.2794520547945206</v>
+        <v>0.2767123287671233</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.2676176000624716</v>
+        <v>0.2649133454918639</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.252054794520548</v>
+        <v>0.2493150684931507</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.03578431372549019</v>
+        <v>0.03613861386138614</v>
       </c>
     </row>
     <row r="6">
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1213918708817559</v>
+        <v>-0.1214445368963917</v>
       </c>
       <c r="AZ6" s="12" t="n">
         <v>0.02637554585152846</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.539402163278995</v>
+        <v>6.536751142102498</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.442911061888108</v>
+        <v>7.440339758415021</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>6.926027397260274</v>
+        <v>6.923287671232877</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001529191774770094</v>
+        <v>0.001529811948261438</v>
       </c>
     </row>
     <row r="7">
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.06582060430528981</v>
+        <v>-0.06591905225529734</v>
       </c>
       <c r="AZ7" s="12" t="n">
         <v>0.2136244541484715</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.9410390431878</v>
+        <v>1.938300039936491</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.077801171951915</v>
+        <v>2.075087865368019</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>1.923287671232877</v>
+        <v>1.920547945205479</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005151879883661091</v>
+        <v>0.005159159982438865</v>
       </c>
     </row>
     <row r="8">
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04584915347447836</v>
+        <v>0.04598658708521187</v>
       </c>
       <c r="AZ8" s="12" t="n">
         <v>3.000839220088626</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.863013698630137</v>
+        <v>0.8602739726027396</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.8251798988057383</v>
+        <v>0.8224522027572204</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.8356164383561644</v>
+        <v>0.8328767123287671</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01158730158730159</v>
+        <v>0.01162420382165605</v>
       </c>
     </row>
     <row r="9">
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1610431485601067</v>
+        <v>0.1612297501966961</v>
       </c>
       <c r="AZ9" s="12" t="n">
         <v>2.885165208940719</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.642476533419118</v>
+        <v>1.639729472763062</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.414655894103567</v>
+        <v>1.412062920783174</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.671232876712329</v>
+        <v>1.668493150684931</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006088367046062543</v>
+        <v>0.006098566968580055</v>
       </c>
     </row>
     <row r="10">
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.008549302565250039</v>
+        <v>-0.008566622755151484</v>
       </c>
       <c r="AZ10" s="3" t="n">
         <v>0.4040561622464898</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.101977310594242</v>
+        <v>4.099246308690886</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.137348756935242</v>
+        <v>4.134666436268787</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.260273972602739</v>
+        <v>4.257534246575342</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002437848686820583</v>
+        <v>0.002439472831578532</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03682636898651232</v>
+        <v>0.03680932167870726</v>
       </c>
       <c r="AZ11" s="12" t="n">
         <v>0.4495978832891248</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.628420499751627</v>
+        <v>2.625684526272408</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.535063322435446</v>
+        <v>2.532466164579943</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.750684931506849</v>
+        <v>2.747945205479452</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003804566278852623</v>
+        <v>0.00380853065169891</v>
       </c>
     </row>
     <row r="12">
@@ -2111,7 +2111,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>-0.07397260273972603</v>
+        <v>-0.07671232876712329</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1252594861557903</v>
+        <v>-0.1253495127366223</v>
       </c>
       <c r="AZ13" s="12" t="n">
         <v>-0.008562415502478604</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.222785918607767</v>
+        <v>4.220126650718697</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.827472663921727</v>
+        <v>4.824929171334148</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.501369863013698</v>
+        <v>4.498630136986302</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002368104893959899</v>
+        <v>0.002369597130052241</v>
       </c>
     </row>
     <row r="14">
@@ -2317,22 +2317,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1923705911079219</v>
+        <v>-0.1925333761744243</v>
       </c>
       <c r="AZ14" s="12" t="n">
         <v>-0.02746298801700808</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.147513385231009</v>
+        <v>3.144828895723947</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.897224829329618</v>
+        <v>3.894685926242414</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.254794520547945</v>
+        <v>3.252054794520548</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003177111190987376</v>
+        <v>0.003179823237314149</v>
       </c>
     </row>
     <row r="15">
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1749791143689337</v>
+        <v>-0.1752562399477074</v>
       </c>
       <c r="AZ15" s="12" t="n">
         <v>0.1797730220492868</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.89993101729986</v>
+        <v>1.897256559522379</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.302888387906186</v>
+        <v>2.300419416816302</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.016438356164384</v>
+        <v>2.013698630136986</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005263348989486881</v>
+        <v>0.005270768441837635</v>
       </c>
     </row>
     <row r="16">
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.04899847882579004</v>
+        <v>-0.04910573672117587</v>
       </c>
       <c r="AZ16" s="12" t="n">
         <v>0.1484581244635195</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.752673125649728</v>
+        <v>1.749935898411249</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.842976153692885</v>
+        <v>1.840305453497228</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.750684931506849</v>
+        <v>1.747945205479452</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005705570453299974</v>
+        <v>0.005714495033263168</v>
       </c>
     </row>
     <row r="17">
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05641256318467983</v>
+        <v>0.05641808745717243</v>
       </c>
       <c r="AZ17" s="12" t="n">
         <v>0.8253901560624251</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.999167349137707</v>
+        <v>2.996424569874795</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.839011437062395</v>
+        <v>2.836400290236673</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.254794520547945</v>
+        <v>3.252054794520548</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003334258757809933</v>
+        <v>0.003337310773825969</v>
       </c>
     </row>
     <row r="18">
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1259304622560446</v>
+        <v>0.1260430294677624</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>1.815909090909091</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.724455093392893</v>
+        <v>1.721710538713489</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.531582234605835</v>
+        <v>1.528991782425291</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.750684931506849</v>
+        <v>1.747945205479452</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005798933262057197</v>
+        <v>0.005808177260430947</v>
       </c>
     </row>
     <row r="19">
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.02013142794909992</v>
+        <v>0.02011161216537004</v>
       </c>
       <c r="AZ19" s="12" t="n">
         <v>0.5158940397350993</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.191391415745299</v>
+        <v>3.188661849590173</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.128412014676736</v>
+        <v>3.125797031975419</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.416438356164384</v>
+        <v>3.413698630136986</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003133429497448422</v>
+        <v>0.003136111783469691</v>
       </c>
     </row>
     <row r="20">
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.585650373573996</v>
+        <v>-0.5863565756405765</v>
       </c>
       <c r="AZ20" s="12" t="n">
         <v>0.01705721313166042</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.429936050502389</v>
+        <v>1.427215132983324</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.45103738317899</v>
+        <v>3.450351314525399</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.413698630136986</v>
+        <v>1.410958904109589</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.00699331973376476</v>
+        <v>0.007006652163992182</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3124,22 +3124,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03834079792081418</v>
+        <v>0.03834606705107262</v>
       </c>
       <c r="AZ21" s="12" t="n">
         <v>0.5242771545454543</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.7780821917808219</v>
+        <v>0.7753424657534246</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.7493514589226031</v>
+        <v>0.7467091082219008</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.7506849315068493</v>
+        <v>0.7479452054794521</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01285211267605634</v>
+        <v>0.01289752650176679</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.06562768637590169</v>
+        <v>0.06562531368316273</v>
       </c>
       <c r="AZ22" s="12" t="n">
         <v>0.06056724611161934</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.839322628664895</v>
+        <v>1.836583535605961</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.72604620936629</v>
+        <v>1.723479643382442</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.016438356164384</v>
+        <v>2.013698630136986</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005436784087878416</v>
+        <v>0.005444892544297262</v>
       </c>
     </row>
     <row r="23">
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02529840461751157</v>
+        <v>0.02531113271085653</v>
       </c>
       <c r="AZ23" s="12" t="n">
         <v>0.5745861519493178</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.317336024464821</v>
+        <v>4.314594360277863</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.210809267839841</v>
+        <v>4.20808301268548</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.342465753424658</v>
+        <v>4.33972602739726</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002316243151641087</v>
+        <v>0.00231771498430179</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.179013605109158</v>
+        <v>0.1791154203877198</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.4254184906832295</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.899974785928891</v>
+        <v>2.897168152432663</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.459661850687804</v>
+        <v>2.457069174347672</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.254794520547945</v>
+        <v>3.252054794520548</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003448305843389221</v>
+        <v>0.00345164639187522</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.2822368092974915</v>
+        <v>0.2824357119798018</v>
       </c>
       <c r="AZ25" s="12" t="n">
         <v>0.9424460431654675</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.860969580712264</v>
+        <v>2.858097137192812</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.231233388378333</v>
+        <v>2.228647495148534</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.254794520547945</v>
+        <v>3.252054794520548</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.00349531853376449</v>
+        <v>0.003498831397249807</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3699,22 +3699,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>72.98504660134512</v>
+        <v>73.66282074843215</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.3144705882352941</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.2794520547945206</v>
+        <v>0.2767123287671233</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.00377714237716571</v>
+        <v>0.003706159585096227</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.252054794520548</v>
+        <v>0.2493150684931507</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.03578431372549019</v>
+        <v>0.03613861386138614</v>
       </c>
     </row>
     <row r="27">
@@ -3808,22 +3808,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.04871959416099816</v>
+        <v>0.04893412340220841</v>
       </c>
       <c r="AZ27" s="12" t="n">
         <v>0.5674739796610171</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.273972602739726</v>
+        <v>0.2712328767123288</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.2612448592217931</v>
+        <v>0.2585795148246177</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.252054794520548</v>
+        <v>0.2493150684931507</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.0365</v>
+        <v>0.03686868686868687</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3938,7 +3938,7 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-2.848001176322295</v>
+        <v>-2.876218851313876</v>
       </c>
       <c r="AZ28" s="12" t="n">
         <v>0.04001898724727848</v>
@@ -3946,7 +3946,7 @@
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.252054794520548</v>
+        <v>0.2493150684931507</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1691281866764841</v>
+        <v>-0.1693082727324618</v>
       </c>
       <c r="AZ29" s="12" t="n">
         <v>0.352461104140527</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.679882903512479</v>
+        <v>2.677175657187885</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.22538670892307</v>
+        <v>3.222826915580508</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.750684931506849</v>
+        <v>2.747945205479452</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003731506323240155</v>
+        <v>0.003735279742721117</v>
       </c>
     </row>
     <row r="30">
@@ -4189,22 +4189,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05529691438016596</v>
+        <v>0.05529629202820728</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.6679981972265023</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.624335953083712</v>
+        <v>2.621596365308072</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.486822350489984</v>
+        <v>2.484227780493327</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.750684931506849</v>
+        <v>2.747945205479452</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003810487749577013</v>
+        <v>0.003814469737725956</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1063541499670041</v>
+        <v>0.1064028476352361</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.403872302549575</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.161821384566506</v>
+        <v>2.159069348277303</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.954004858779605</v>
+        <v>1.951431481663282</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.323287671232876</v>
+        <v>2.32054794520548</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.00462572905948251</v>
+        <v>0.004631625199060367</v>
       </c>
     </row>
     <row r="32">
@@ -4412,22 +4412,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.275775089676862</v>
+        <v>-0.2761972049429299</v>
       </c>
       <c r="AZ32" s="12" t="n">
         <v>0.1625449101796408</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.622215127793154</v>
+        <v>1.61949076918822</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.239932795282264</v>
+        <v>2.237475152414309</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.624657534246575</v>
+        <v>1.621917808219178</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.006164410520325937</v>
+        <v>0.006174780486715934</v>
       </c>
     </row>
     <row r="33">
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.1059591708182548</v>
+        <v>-0.106094819047482</v>
       </c>
       <c r="AZ33" s="12" t="n">
         <v>0.01686260102865544</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.658674346255964</v>
+        <v>2.655962191955153</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.973772851838621</v>
+        <v>2.97119006416882</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.750684931506849</v>
+        <v>2.747945205479452</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003761272987074307</v>
+        <v>0.003765113837196089</v>
       </c>
     </row>
     <row r="34">
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03138639566287028</v>
+        <v>0.03136492343753731</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.2387878787878788</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.65336534131206</v>
+        <v>1.650626462957929</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.603051337757315</v>
+        <v>1.600429125955142</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.671232876712329</v>
+        <v>1.668493150684931</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.006048270004295788</v>
+        <v>0.006058305876230748</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>75.7</v>
+        <v>76</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1402810152112663</v>
+        <v>0.1389103902456063</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.555166163141994</v>
+        <v>0.5613293051359516</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.986116872796339</v>
+        <v>2.984114854562726</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.618755230475431</v>
+        <v>2.620148942463507</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.252054794520548</v>
+        <v>3.249315068493151</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003348830747751522</v>
+        <v>0.003351077450893002</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9875</v>
+        <v>9900</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.02151196056218583</v>
+        <v>-0.02161183019620526</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1151073312405062</v>
+        <v>0.1122914036363636</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.729301146501076</v>
+        <v>1.726565648705428</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.767319657269023</v>
+        <v>1.76470413481356</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.747945205479452</v>
+        <v>1.745205479452055</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005782682802375496</v>
+        <v>0.005791844641122079</v>
       </c>
     </row>
     <row r="4">
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>105</v>
+        <v>105.1</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.019413418562023</v>
+        <v>0.01939972265763748</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.1946666666666668</v>
+        <v>0.1935299714557566</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.379251387565035</v>
+        <v>4.376525537785374</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.295854172434158</v>
+        <v>4.293237912970492</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.747945205479452</v>
+        <v>4.745205479452054</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002283495308900326</v>
+        <v>0.002284917547872973</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6314</v>
+        <v>6402</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.04453902936959349</v>
+        <v>0.04486290576741293</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.5897212543554</v>
+        <v>1.554123711340206</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.2767123287671233</v>
+        <v>0.273972602739726</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.2649133454918639</v>
+        <v>0.2622091388520519</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.2493150684931507</v>
+        <v>0.2465753424657534</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.03613861386138614</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="6">
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>22900</v>
+        <v>23170</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1214445368963917</v>
+        <v>-0.121497243013869</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02637554585152846</v>
+        <v>0.01441519205869657</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.536751142102498</v>
+        <v>6.534100173105672</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.440339758415021</v>
+        <v>7.437768545567383</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>6.923287671232877</v>
+        <v>6.920547945205479</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001529811948261438</v>
+        <v>0.001530432612765864</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22900</v>
+        <v>23170</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.06591905225529734</v>
+        <v>-0.06601776829772903</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2136244541484715</v>
+        <v>0.1994820889080708</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.938300039936491</v>
+        <v>1.935561038654494</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.075087865368019</v>
+        <v>2.072374583750647</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>1.920547945205479</v>
+        <v>1.917808219178082</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005159159982438865</v>
+        <v>0.005166460680026656</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2031</v>
+        <v>2070</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04598658708521187</v>
+        <v>0.04612489898828995</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.000839220088626</v>
+        <v>2.925461089855073</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.8602739726027396</v>
+        <v>0.8575342465753426</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.8224522027572204</v>
+        <v>0.8197245351914157</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.8328767123287671</v>
+        <v>0.8301369863013699</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01162420382165605</v>
+        <v>0.01166134185303514</v>
       </c>
     </row>
     <row r="9">
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1612297501966961</v>
+        <v>0.1614170224541626</v>
       </c>
       <c r="AZ9" s="12" t="n">
         <v>2.885165208940719</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.639729472763062</v>
+        <v>1.636982385860969</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.412062920783174</v>
+        <v>1.40946994422546</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.668493150684931</v>
+        <v>1.665753424657534</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006098566968580055</v>
+        <v>0.006108801222525381</v>
       </c>
     </row>
     <row r="10">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>112.5</v>
+        <v>113.9</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12820</v>
+        <v>12770</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.008566622755151484</v>
+        <v>-0.01153427282241466</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4040561622464898</v>
+        <v>0.4270947533281129</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.099246308690886</v>
+        <v>4.097996896209573</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.134666436268787</v>
+        <v>4.145815867496777</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.257534246575342</v>
+        <v>4.254794520547946</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002439472831578532</v>
+        <v>0.00244021658709636</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1131</v>
+        <v>1180</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03680932167870726</v>
+        <v>0.03679224706146256</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4495978832891248</v>
+        <v>0.3894027169491525</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.625684526272408</v>
+        <v>2.622948558772582</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.532466164579943</v>
+        <v>2.529868993722413</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.747945205479452</v>
+        <v>2.745205479452055</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.00380853065169891</v>
+        <v>0.003812503286255655</v>
       </c>
     </row>
     <row r="12">
@@ -2111,7 +2111,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>-0.07671232876712329</v>
+        <v>-0.07945205479452055</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220</v>
+        <v>222.7</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>221.9</v>
+        <v>223.6</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1253495127366223</v>
+        <v>-0.1279352643100924</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.008562415502478604</v>
+        <v>-0.00402504472271914</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.220126650718697</v>
+        <v>4.21969195351043</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.824929171334148</v>
+        <v>4.838737057945759</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.498630136986302</v>
+        <v>4.495890410958904</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002369597130052241</v>
+        <v>0.002369841237268716</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>258.7</v>
+        <v>261</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2317,22 +2317,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1925333761744243</v>
+        <v>-0.1926964087517613</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.02746298801700808</v>
+        <v>-0.03603323754789267</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.144828895723947</v>
+        <v>3.142144476413295</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.894685926242414</v>
+        <v>3.892147279507287</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.252054794520548</v>
+        <v>3.249315068493151</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003179823237314149</v>
+        <v>0.00318253984661292</v>
       </c>
     </row>
     <row r="15">
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>77.09999999999999</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1752562399477074</v>
+        <v>-0.1755340586854788</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1797730220492868</v>
+        <v>0.1646670934699106</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.897256559522379</v>
+        <v>1.894582253556685</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.300419416816302</v>
+        <v>2.29795090205422</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.013698630136986</v>
+        <v>2.010958904109589</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005270768441837635</v>
+        <v>0.005278208418360867</v>
       </c>
     </row>
     <row r="16">
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18640</v>
+        <v>18800</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.04910573672117587</v>
+        <v>-0.04921331674301122</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1484581244635195</v>
+        <v>0.1386840127659574</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.749935898411249</v>
+        <v>1.747198678690189</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.840305453497228</v>
+        <v>1.837634781237189</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.747945205479452</v>
+        <v>1.745205479452055</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005714495033263168</v>
+        <v>0.005723447551767058</v>
       </c>
     </row>
     <row r="17">
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05641808745717243</v>
+        <v>0.0564236282759181</v>
       </c>
       <c r="AZ17" s="12" t="n">
         <v>0.8253901560624251</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.996424569874795</v>
+        <v>2.99368178144982</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.836400290236673</v>
+        <v>2.833789117662489</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.252054794520548</v>
+        <v>3.249315068493151</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003337310773825969</v>
+        <v>0.003340368392514006</v>
       </c>
     </row>
     <row r="18">
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1260430294677624</v>
+        <v>0.1261559824286756</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>1.815909090909091</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.721710538713489</v>
+        <v>1.718965967536477</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.528991782425291</v>
+        <v>1.526401310615376</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.747945205479452</v>
+        <v>1.745205479452055</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005808177260430947</v>
+        <v>0.005817450833149085</v>
       </c>
     </row>
     <row r="19">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>151</v>
+        <v>153.1</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.02011161216537004</v>
+        <v>0.02009176709836447</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5158940397350993</v>
+        <v>0.4951012410189419</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.188661849590173</v>
+        <v>3.185932298229962</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.125797031975419</v>
+        <v>3.123182051838628</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.413698630136986</v>
+        <v>3.410958904109589</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003136111783469691</v>
+        <v>0.003138798651043462</v>
       </c>
     </row>
     <row r="20">
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>29090</v>
+        <v>29780</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5863565756405765</v>
+        <v>-0.5870642741874619</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.01705721313166042</v>
+        <v>-0.006507913700470214</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.427215132983324</v>
+        <v>1.424494256038299</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.450351314525399</v>
+        <v>3.449675499099299</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.410958904109589</v>
+        <v>1.408219178082192</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.007006652163992182</v>
+        <v>0.007020035326650796</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3124,22 +3124,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03834606705107262</v>
+        <v>0.0383513991690538</v>
       </c>
       <c r="AZ21" s="12" t="n">
         <v>0.5242771545454543</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.7753424657534246</v>
+        <v>0.7726027397260274</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.7467091082219008</v>
+        <v>0.7440667392024577</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.7479452054794521</v>
+        <v>0.7452054794520548</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01289752650176679</v>
+        <v>0.01294326241134752</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100.8</v>
+        <v>103.9</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>218.6</v>
+        <v>218.9</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.06562531368316273</v>
+        <v>0.04926877563033986</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.06056724611161934</v>
+        <v>0.09168570123344</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.836583535605961</v>
+        <v>1.83819226731524</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.723479643382442</v>
+        <v>1.751879318252809</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.013698630136986</v>
+        <v>2.010958904109589</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005444892544297262</v>
+        <v>0.005440127334778444</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10260</v>
+        <v>10250</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02531113271085653</v>
+        <v>0.02532387719564478</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5745861519493178</v>
+        <v>0.5761223335609758</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.314594360277863</v>
+        <v>4.311852693540646</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.20808301268548</v>
+        <v>4.205356755500477</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.33972602739726</v>
+        <v>4.336986301369863</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.00231771498430179</v>
+        <v>0.002319188690045108</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1791154203877198</v>
+        <v>0.1792174560446127</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.4254184906832295</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.897168152432663</v>
+        <v>2.894361368831888</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.457069174347672</v>
+        <v>2.454476359721041</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.252054794520548</v>
+        <v>3.249315068493151</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.00345164639187522</v>
+        <v>0.003454993598133816</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>27.8</v>
+        <v>28.6</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.2824357119798018</v>
+        <v>0.2826350619611426</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.9424460431654675</v>
+        <v>0.8881118881118881</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.858097137192812</v>
+        <v>2.855224377401221</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.228647495148534</v>
+        <v>2.226061381041305</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.252054794520548</v>
+        <v>3.249315068493151</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003498831397249807</v>
+        <v>0.003502351716785859</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3685,7 +3685,7 @@
         <v>0.55865</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AK26" s="10" t="n">
         <v>46377</v>
@@ -3699,22 +3699,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>73.66282074843215</v>
+        <v>74.35420289855074</v>
       </c>
       <c r="AZ26" s="12" t="n">
-        <v>0.3144705882352941</v>
+        <v>0.3966249999999998</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.2767123287671233</v>
+        <v>0.2739726027397261</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.003706159585096227</v>
+        <v>0.003635797237595028</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.2493150684931507</v>
+        <v>0.2465753424657534</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.03613861386138614</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="27">
@@ -3808,22 +3808,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.04893412340220841</v>
+        <v>0.04915307245813855</v>
       </c>
       <c r="AZ27" s="12" t="n">
         <v>0.5674739796610171</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.2712328767123288</v>
+        <v>0.2684931506849315</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.2585795148246177</v>
+        <v>0.2559141823374343</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.2493150684931507</v>
+        <v>0.2465753424657534</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.03686868686868687</v>
+        <v>0.03724489795918368</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12860</v>
+        <v>12920</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3938,15 +3938,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-2.876218851313876</v>
+        <v>-2.905000878748662</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.04001898724727848</v>
+        <v>0.03518917770897856</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.2493150684931507</v>
+        <v>0.2465753424657534</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15940</v>
+        <v>16280</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1693082727324618</v>
+        <v>-0.1694886847690532</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.352461104140527</v>
+        <v>0.324215601965602</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.677175657187885</v>
+        <v>2.674468465549795</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.222826915580508</v>
+        <v>3.220267341939929</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.747945205479452</v>
+        <v>2.745205479452055</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003735279742721117</v>
+        <v>0.003739060725079173</v>
       </c>
     </row>
     <row r="30">
@@ -4189,22 +4189,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05529629202820728</v>
+        <v>0.0552956773197756</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.6679981972265023</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.621596365308072</v>
+        <v>2.618856775834427</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.484227780493327</v>
+        <v>2.481633187852869</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.747945205479452</v>
+        <v>2.745205479452055</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003814469737725956</v>
+        <v>0.003818460059471474</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1064028476352361</v>
+        <v>0.1064516884491822</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.403872302549575</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.159069348277303</v>
+        <v>2.156317275552483</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.951431481663282</v>
+        <v>1.948858046007238</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.32054794520548</v>
+        <v>2.317808219178082</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004631625199060367</v>
+        <v>0.004637536467094269</v>
       </c>
     </row>
     <row r="32">
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>66800</v>
+        <v>67400</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4412,22 +4412,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2761972049429299</v>
+        <v>-0.2766204979059366</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1625449101796408</v>
+        <v>0.1521958456973294</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.61949076918822</v>
+        <v>1.616766453945738</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.237475152414309</v>
+        <v>2.23501833997987</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.621917808219178</v>
+        <v>1.619178082191781</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.006174780486715934</v>
+        <v>0.006185185235378231</v>
       </c>
     </row>
     <row r="33">
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.106094819047482</v>
+        <v>-0.1062307222477365</v>
       </c>
       <c r="AZ33" s="12" t="n">
         <v>0.01686260102865544</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.655962191955153</v>
+        <v>2.653250087156481</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.97119006416882</v>
+        <v>2.96860739477321</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.747945205479452</v>
+        <v>2.745205479452055</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003765113837196089</v>
+        <v>0.003768962469239799</v>
       </c>
     </row>
     <row r="34">
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03136492343753731</v>
+        <v>0.0313433891409984</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.2387878787878788</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.650626462957929</v>
+        <v>1.647887587055733</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.600429125955142</v>
+        <v>1.597806903506941</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.668493150684931</v>
+        <v>1.665753424657534</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.006058305876230748</v>
+        <v>0.006068375099461073</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>76</v>
+        <v>76.7</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>827.5</v>
+        <v>825</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1389103902456063</v>
+        <v>0.135554642388285</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.5613293051359516</v>
+        <v>0.5804848484848486</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.984114854562726</v>
+        <v>2.985917002676144</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.620148942463507</v>
+        <v>2.62947892705207</v>
       </c>
       <c r="BC2" s="8" t="n">
         <v>3.249315068493151</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003351077450893002</v>
+        <v>0.003349054910447091</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9900</v>
+        <v>9828</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.02161183019620526</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1122914036363636</v>
+        <v>0.1204400586080585</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.726565648705428</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>105.1</v>
+        <v>106.3</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.01939972265763748</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.1935299714557566</v>
+        <v>0.1800564440263406</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.376525537785374</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6402</v>
+        <v>6385</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.04486290576741293</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.554123711340206</v>
+        <v>1.560924040720438</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.273972602739726</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>293.8</v>
+        <v>298.4</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>23170</v>
+        <v>22520</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.121497243013869</v>
+        <v>-0.1235813309072376</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.01441519205869657</v>
+        <v>0.06003552397868561</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.534100173105672</v>
+        <v>6.537597469343716</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.437768545567383</v>
+        <v>7.459445696325941</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.920547945205479</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001530432612765864</v>
+        <v>0.001529613905856437</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>115.8</v>
+        <v>115.9</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>23170</v>
+        <v>22520</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.06601776829772903</v>
+        <v>-0.06643403996972004</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1994820889080708</v>
+        <v>0.2351687388987567</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.935561038654494</v>
+        <v>1.935564094815588</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.072374583750647</v>
+        <v>2.073301917255861</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>1.917808219178082</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005166460680026656</v>
+        <v>0.005166452522437784</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2070</v>
+        <v>1991</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04612489898828995</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.925461089855073</v>
+        <v>3.081217707684581</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8575342465753426</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>205.8</v>
+        <v>201.8</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1614170224541626</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.885165208940719</v>
+        <v>2.962175421209118</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.636982385860969</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12770</v>
+        <v>12300</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.01153427282241466</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4270947533281129</v>
+        <v>0.4816260162601627</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.097996896209573</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>104.7</v>
+        <v>104.9</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1180</v>
+        <v>1164</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03679224706146256</v>
+        <v>0.03604708811274462</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.3894027169491525</v>
+        <v>0.4111915824742267</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.622948558772582</v>
+        <v>2.623112554584949</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.529868993722413</v>
+        <v>2.531846848161304</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.745205479452055</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003812503286255655</v>
+        <v>0.003812264930271848</v>
       </c>
     </row>
     <row r="12">
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222.7</v>
+        <v>222.6</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>223.6</v>
+        <v>220</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1279352643100924</v>
+        <v>-0.1278435181343278</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.00402504472271914</v>
+        <v>0.01181818181818173</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.21969195351043</v>
+        <v>4.219610362757316</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.838737057945759</v>
+        <v>4.838134498216355</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.495890410958904</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002369841237268716</v>
+        <v>0.002369887060725074</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>261</v>
+        <v>255.1</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1926964087517613</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.03603323754789267</v>
+        <v>-0.01373843590748725</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.142144476413295</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>78.09999999999999</v>
+        <v>78</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2429,7 +2429,7 @@
         <v>-0.1755340586854788</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1646670934699106</v>
+        <v>0.1661602564102564</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.894582253556685</v>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>114.1</v>
+        <v>114.6</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18800</v>
+        <v>19100</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.04921331674301122</v>
+        <v>-0.05157786530999873</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1386840127659574</v>
+        <v>0.1257104</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.747198678690189</v>
+        <v>1.747253769144812</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.837634781237189</v>
+        <v>1.842274347293587</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.745205479452055</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005723447551767058</v>
+        <v>0.005723267092961813</v>
       </c>
     </row>
     <row r="17">
@@ -2781,7 +2781,7 @@
         <v>4.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="AK18" s="10" t="n">
         <v>46924</v>
@@ -2798,7 +2798,7 @@
         <v>0.1261559824286756</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.815909090909091</v>
+        <v>1.95</v>
       </c>
       <c r="BA18" s="8" t="n">
         <v>1.718965967536477</v>
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>153.1</v>
+        <v>150.3</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.02009176709836447</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4951012410189419</v>
+        <v>0.5229540918163671</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.185932298229962</v>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>368.5</v>
+        <v>374</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>29780</v>
+        <v>30220</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5870642741874619</v>
+        <v>-0.5913184659949068</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.006507913700470214</v>
+        <v>-0.006360710787557955</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.424494256038299</v>
+        <v>1.424607578766043</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.449675499099299</v>
+        <v>3.485862365262358</v>
       </c>
       <c r="BC20" s="8" t="n">
         <v>1.408219178082192</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.007020035326650796</v>
+        <v>0.007019476906518869</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>440</v>
+        <v>439.4</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.0383513991690538</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5242771545454543</v>
+        <v>0.5263585525716885</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7726027397260274</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103.9</v>
+        <v>101.9</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>218.9</v>
+        <v>217.7</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.04926877563033986</v>
+        <v>0.05973299787363038</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.09168570123344</v>
+        <v>0.07657326596233349</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.83819226731524</v>
+        <v>1.835413776148634</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.751879318252809</v>
+        <v>1.731958691322643</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>2.010958904109589</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005440127334778444</v>
+        <v>0.005448362723409235</v>
       </c>
     </row>
     <row r="23">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>91.7</v>
+        <v>92</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10250</v>
+        <v>10490</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02532387719564478</v>
+        <v>0.02455018236491463</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5761223335609758</v>
+        <v>0.5451007092469018</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.311852693540646</v>
+        <v>4.31197041217477</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.205356755500477</v>
+        <v>4.208647352169397</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.336986301369863</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002319188690045108</v>
+        <v>0.00231912537520322</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>32.2</v>
+        <v>34.5</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1792174560446127</v>
+        <v>0.1036238724672493</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.4254184906832295</v>
+        <v>0.6301969217391303</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.894361368831888</v>
+        <v>2.942551325755068</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.454476359721041</v>
+        <v>2.666262844764976</v>
       </c>
       <c r="BC24" s="8" t="n">
         <v>3.249315068493151</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003454993598133816</v>
+        <v>0.003398411410014733</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>28.6</v>
+        <v>27.6</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.2826350619611426</v>
+        <v>0.3069466706150087</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.8881118881118881</v>
+        <v>0.8478260869565217</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.855224377401221</v>
+        <v>2.838868085632898</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.226061381041305</v>
+        <v>2.172137662125888</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.249315068493151</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003502351716785859</v>
+        <v>0.0035225307053218</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3685,7 +3685,7 @@
         <v>0.55865</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AK26" s="10" t="n">
         <v>46377</v>
@@ -3702,7 +3702,7 @@
         <v>74.35420289855074</v>
       </c>
       <c r="AZ26" s="12" t="n">
-        <v>0.3966249999999998</v>
+        <v>0.3144705882352941</v>
       </c>
       <c r="BA26" s="8" t="n">
         <v>0.2739726027397261</v>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.04915307245813855</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5674739796610171</v>
+        <v>0.5688034741306192</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2684931506849315</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12920</v>
+        <v>12600</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-2.905000878748662</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.03518917770897856</v>
+        <v>0.06147969650793672</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>187.3</v>
+        <v>145.5</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>16280</v>
+        <v>16140</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1694886847690532</v>
+        <v>-0.08759966831361073</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.324215601965602</v>
+        <v>0.03761152416356883</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.674468465549795</v>
+        <v>2.659287142407959</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.220267341939929</v>
+        <v>2.91460562875158</v>
       </c>
       <c r="BC29" s="8" t="n">
         <v>2.745205479452055</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003739060725079173</v>
+        <v>0.003760406253438692</v>
       </c>
     </row>
     <row r="30">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>91.40000000000001</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1064516884491822</v>
+        <v>0.08563674521434453</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>1.403872302549575</v>
+        <v>1.509074591501417</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.156317275552483</v>
+        <v>2.161556312121849</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.948858046007238</v>
+        <v>1.991049328101987</v>
       </c>
       <c r="BC31" s="8" t="n">
         <v>2.317808219178082</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004637536467094269</v>
+        <v>0.004626296314336451</v>
       </c>
     </row>
     <row r="32">
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67400</v>
+        <v>67580</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2766204979059366</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1521958456973294</v>
+        <v>0.1491269606392425</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.616766453945738</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>76.7</v>
+        <v>75.8</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>825</v>
+        <v>830</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.135554642388285</v>
+        <v>0.1398768387482748</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.5804848484848486</v>
+        <v>0.5525301204819275</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.985917002676144</v>
+        <v>2.983594784178803</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.62947892705207</v>
+        <v>2.617471188777867</v>
       </c>
       <c r="BC2" s="8" t="n">
         <v>3.249315068493151</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003349054910447091</v>
+        <v>0.003351661577177738</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9828</v>
+        <v>9710</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.02161183019620526</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1204400586080585</v>
+        <v>0.1340561169927907</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.726565648705428</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>113.9</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>106.3</v>
+        <v>105.4</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01939972265763748</v>
+        <v>0.0155269648094829</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.1800564440263406</v>
+        <v>0.2103225806451614</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.376525537785374</v>
+        <v>4.380437254602742</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.293237912970492</v>
+        <v>4.31346227761124</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.745205479452054</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002284917547872973</v>
+        <v>0.002282877123623334</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6385</v>
+        <v>6508</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.04486290576741293</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.560924040720438</v>
+        <v>1.512523048555623</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.273972602739726</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>298.4</v>
+        <v>292</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>22520</v>
+        <v>22470</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1235813309072376</v>
+        <v>-0.1206711649074771</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.06003552397868561</v>
+        <v>0.03960836671117041</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.537597469343716</v>
+        <v>6.532707290457708</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.459445696325941</v>
+        <v>7.429197166916898</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.920547945205479</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001529613905856437</v>
+        <v>0.001530758926640866</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22520</v>
+        <v>22470</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.06643403996972004</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2351687388987567</v>
+        <v>0.2379172229639519</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.935564094815588</v>
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>96.40000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1991</v>
+        <v>1958</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,16 +1617,16 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04612489898828995</v>
+        <v>0.04111740637811597</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.081217707684581</v>
+        <v>3.16722220224719</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8575342465753426</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.8197245351914157</v>
+        <v>0.8236671880826292</v>
       </c>
       <c r="BC8" s="8" t="n">
         <v>0.8301369863013699</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>201.8</v>
+        <v>204</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1614170224541626</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.962175421209118</v>
+        <v>2.919446078431373</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.636982385860969</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>113.9</v>
+        <v>113.1</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12300</v>
+        <v>12580</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.01153427282241466</v>
+        <v>-0.009854005148489752</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4816260162601627</v>
+        <v>0.4384737678855326</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.097996896209573</v>
+        <v>4.097154182735435</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.145815867496777</v>
+        <v>4.137929359952493</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.254794520547946</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.00244021658709636</v>
+        <v>0.002440718497277438</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1164</v>
+        <v>1152</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03604708811274462</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4111915824742267</v>
+        <v>0.4258914947916665</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.623112554584949</v>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222.6</v>
+        <v>225</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>220</v>
+        <v>221.2</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1278435181343278</v>
+        <v>-0.1300311470205705</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.01181818181818173</v>
+        <v>0.01717902350813749</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.219610362757316</v>
+        <v>4.221551936860918</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.838134498216355</v>
+        <v>4.852532274463781</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.495890410958904</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002369887060725074</v>
+        <v>0.002368797103426341</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>255.1</v>
+        <v>251.3</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1926964087517613</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.01373843590748725</v>
+        <v>0.001175189017111</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.142144476413295</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2429,7 +2429,7 @@
         <v>-0.1755340586854788</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1661602564102564</v>
+        <v>0.1813051948051949</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.894582253556685</v>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>114.6</v>
+        <v>115.9</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>19100</v>
+        <v>18890</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.05157786530999873</v>
+        <v>-0.05765051618462918</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1257104</v>
+        <v>0.1511367157226047</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.747253769144812</v>
+        <v>1.747395281313276</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.842274347293587</v>
+        <v>1.854296427519064</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.745205479452055</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005723267092961813</v>
+        <v>0.005722803596267229</v>
       </c>
     </row>
     <row r="17">
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>83.3</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2668,7 +2668,7 @@
         <v>0.0564236282759181</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8253901560624251</v>
+        <v>0.8679975429975431</v>
       </c>
       <c r="BA17" s="8" t="n">
         <v>2.99368178144982</v>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>88.5</v>
+        <v>89.5</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1261559824286756</v>
+        <v>0.1189128403700675</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.95</v>
+        <v>1.983333333333333</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.718965967536477</v>
+        <v>1.719276764345186</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.526401310615376</v>
+        <v>1.5365600449956</v>
       </c>
       <c r="BC18" s="8" t="n">
         <v>1.745205479452055</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005817450833149085</v>
+        <v>0.005816399201910148</v>
       </c>
     </row>
     <row r="19">
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>109</v>
+        <v>107.2</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>150.3</v>
+        <v>150.1</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.02009176709836447</v>
+        <v>0.0253098522667662</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5229540918163671</v>
+        <v>0.4998001332445037</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.185932298229962</v>
+        <v>3.183249414625294</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.123182051838628</v>
+        <v>3.104670658911285</v>
       </c>
       <c r="BC19" s="8" t="n">
         <v>3.410958904109589</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003138798651043462</v>
+        <v>0.003141444070972089</v>
       </c>
     </row>
     <row r="20">
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>374</v>
+        <v>375.5</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>30220</v>
+        <v>29740</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5913184659949068</v>
+        <v>-0.5924602932398729</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.006360710787557955</v>
+        <v>0.01372601176866173</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.424607578766043</v>
+        <v>1.424637999065055</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.485862365262358</v>
+        <v>3.49570354847308</v>
       </c>
       <c r="BC20" s="8" t="n">
         <v>1.408219178082192</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.007019476906518869</v>
+        <v>0.007019327019609675</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>439.4</v>
+        <v>443.3</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.0383513991690538</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5263585525716885</v>
+        <v>0.5129301782088878</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7726027397260274</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101.9</v>
+        <v>102.1</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>217.7</v>
+        <v>214.7</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.05973299787363038</v>
+        <v>0.05867251522529567</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.07657326596233349</v>
+        <v>0.09375873311597571</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.835413776148634</v>
+        <v>1.835695921359884</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.731958691322643</v>
+        <v>1.733960119829153</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>2.010958904109589</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005448362723409235</v>
+        <v>0.005447525313774188</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10490</v>
+        <v>10550</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.02455018236491463</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5451007092469018</v>
+        <v>0.536313406635071</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.31197041217477</v>
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3480,7 +3480,7 @@
         <v>0.1036238724672493</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.6301969217391303</v>
+        <v>0.6069083942857141</v>
       </c>
       <c r="BA24" s="8" t="n">
         <v>2.942551325755068</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>27.6</v>
+        <v>26.6</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3589,7 +3589,7 @@
         <v>0.3069466706150087</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.8478260869565217</v>
+        <v>0.9172932330827066</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>2.838868085632898</v>
@@ -3685,7 +3685,7 @@
         <v>0.55865</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AK26" s="10" t="n">
         <v>46377</v>
@@ -3702,7 +3702,7 @@
         <v>74.35420289855074</v>
       </c>
       <c r="AZ26" s="12" t="n">
-        <v>0.3144705882352941</v>
+        <v>0.3966249999999998</v>
       </c>
       <c r="BA26" s="8" t="n">
         <v>0.2739726027397261</v>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1179</v>
+        <v>1175</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.04915307245813855</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5688034741306192</v>
+        <v>0.5741440817021277</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2684931506849315</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12600</v>
+        <v>12510</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-2.905000878748662</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.06147969650793672</v>
+        <v>0.06911624108713044</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>16140</v>
+        <v>15970</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.08759966831361073</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.03761152416356883</v>
+        <v>0.0486568566061365</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.659287142407959</v>
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>584.1</v>
+        <v>572.1</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4192,7 +4192,7 @@
         <v>0.0552956773197756</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.6679981972265023</v>
+        <v>0.7029850498164658</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.618856775834427</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67580</v>
+        <v>67690</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2766204979059366</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1491269606392425</v>
+        <v>0.1472595656670115</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.616766453945738</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>136.1</v>
+        <v>138.5</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4521,10 +4521,10 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.1062307222477365</v>
+        <v>-0.1062307222477364</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.01686260102865544</v>
+        <v>-0.0007581227436822546</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.653250087156481</v>
@@ -4616,7 +4616,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1485</v>
+        <v>1500</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4633,7 +4633,7 @@
         <v>0.0313433891409984</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2387878787878788</v>
+        <v>0.2264000000000002</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.647887587055733</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>22470</v>
+        <v>22480</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.1206711649074771</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.03960836671117041</v>
+        <v>0.03914590747330959</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.532707290457708</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22470</v>
+        <v>22480</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.06643403996972004</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2379172229639519</v>
+        <v>0.2373665480427045</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.935564094815588</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1958</v>
+        <v>1960</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04111740637811597</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.16722220224719</v>
+        <v>3.162969934693877</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8575342465753426</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12580</v>
+        <v>12570</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.009854005148489752</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4384737678855326</v>
+        <v>0.439618138424821</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.097154182735435</v>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>115.9</v>
+        <v>116</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18890</v>
+        <v>18910</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.05765051618462918</v>
+        <v>-0.05811320872310085</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1511367157226047</v>
+        <v>0.1509113907985193</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.747395281313276</v>
+        <v>1.747406065207872</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.854296427519064</v>
+        <v>1.855218781483224</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.745205479452055</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005722803596267229</v>
+        <v>0.005722768278711677</v>
       </c>
     </row>
     <row r="17">
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>29740</v>
+        <v>29770</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5924602932398729</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.01372601176866173</v>
+        <v>0.01270445381256291</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.424637999065055</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67690</v>
+        <v>67740</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2766204979059366</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1472595656670115</v>
+        <v>0.1464127546501328</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.616766453945738</v>
@@ -4521,7 +4521,7 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.1062307222477364</v>
+        <v>-0.1062307222477365</v>
       </c>
       <c r="AZ33" s="12" t="n">
         <v>-0.0007581227436822546</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.1398768387482748</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.5525301204819275</v>
+        <v>0.5432335329341316</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>2.983594784178803</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9710</v>
+        <v>9627</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.02161183019620526</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1340561169927907</v>
+        <v>0.1438334783421626</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.726565648705428</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>113.9</v>
+        <v>112.7</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>105.4</v>
+        <v>105.1</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.0155269648094829</v>
+        <v>0.01796327426295387</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2103225806451614</v>
+        <v>0.2009895337773551</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.380437254602742</v>
+        <v>4.377979235350322</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.31346227761124</v>
+        <v>4.300724147951363</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.745205479452054</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002282877123623334</v>
+        <v>0.002284158846450036</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6508</v>
+        <v>6511</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.04486290576741293</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.512523048555623</v>
+        <v>1.511365381661803</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.273972602739726</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>22480</v>
+        <v>22290</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.1206711649074771</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.03914590747330959</v>
+        <v>0.0480035890533872</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.532707290457708</v>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>115.9</v>
+        <v>114.1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22480</v>
+        <v>22290</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.06643403996972004</v>
+        <v>-0.05885662880229889</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2373665480427045</v>
+        <v>0.2285329744279947</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.935564094815588</v>
+        <v>1.935508466328635</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.073301917255861</v>
+        <v>2.05655007043773</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>1.917808219178082</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005166452522437784</v>
+        <v>0.005166601011551492</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1960</v>
+        <v>1981</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04111740637811597</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.162969934693877</v>
+        <v>3.118839511357899</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8575342465753426</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>204</v>
+        <v>203.3</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1614170224541626</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.919446078431373</v>
+        <v>2.932941465814068</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.636982385860969</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>113.1</v>
+        <v>112.8</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12570</v>
+        <v>12700</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.009854005148489752</v>
+        <v>-0.009220047147972083</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.439618138424821</v>
+        <v>0.4211023622047243</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.097154182735435</v>
+        <v>4.096835488516294</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.137929359952493</v>
+        <v>4.134960014807801</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.254794520547946</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002440718497277438</v>
+        <v>0.002440908361595352</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1152</v>
+        <v>1166</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03604708811274462</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4258914947916665</v>
+        <v>0.408771013722127</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.623112554584949</v>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>225</v>
+        <v>223.2</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>221.2</v>
+        <v>221.4</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1300311470205705</v>
+        <v>-0.1283932143700623</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.01717902350813749</v>
+        <v>0.008130081300812941</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.221551936860918</v>
+        <v>4.220098998442158</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.852532274463781</v>
+        <v>4.841746379237008</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.495890410958904</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002368797103426341</v>
+        <v>0.00236961265688115</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>251.3</v>
+        <v>249.8</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1926964087517613</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.001175189017111</v>
+        <v>0.007187049639711729</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.142144476413295</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>166.9</v>
+        <v>163.7</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>77</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1755340586854788</v>
+        <v>-0.1673996684033524</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1813051948051949</v>
+        <v>0.1571530479896239</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.894582253556685</v>
+        <v>1.892662057969872</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.29795090205422</v>
+        <v>2.273193975722279</v>
       </c>
       <c r="BC15" s="8" t="n">
         <v>2.010958904109589</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005278208418360867</v>
+        <v>0.005283563411593041</v>
       </c>
     </row>
     <row r="16">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>116</v>
+        <v>115.7</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18910</v>
+        <v>19050</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.05811320872310085</v>
+        <v>-0.05672324612111733</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1509113907985193</v>
+        <v>0.1394986288713911</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.747406065207872</v>
+        <v>1.747373670307221</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.855218781483224</v>
+        <v>1.852450686526284</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.745205479452055</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005722768278711677</v>
+        <v>0.005722874374226901</v>
       </c>
     </row>
     <row r="17">
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>81.40000000000001</v>
+        <v>82.7</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2668,7 +2668,7 @@
         <v>0.0564236282759181</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8679975429975431</v>
+        <v>0.8386336154776299</v>
       </c>
       <c r="BA17" s="8" t="n">
         <v>2.99368178144982</v>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>89.5</v>
+        <v>89.2</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2781,7 +2781,7 @@
         <v>4.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>126</v>
+        <v>118.8</v>
       </c>
       <c r="AK18" s="10" t="n">
         <v>46924</v>
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1189128403700675</v>
+        <v>0.1210723279362329</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.983333333333333</v>
+        <v>2.153535353535354</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.719276764345186</v>
+        <v>1.719184081352278</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.5365600449956</v>
+        <v>1.533517542545271</v>
       </c>
       <c r="BC18" s="8" t="n">
         <v>1.745205479452055</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005816399201910148</v>
+        <v>0.00581671277001017</v>
       </c>
     </row>
     <row r="19">
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>107.2</v>
+        <v>108.3</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>150.1</v>
+        <v>150.3</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.0253098522667662</v>
+        <v>0.02210728152438137</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4998001332445037</v>
+        <v>0.5131736526946107</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.183249414625294</v>
+        <v>3.184897814361213</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.104670658911285</v>
+        <v>3.116011275852788</v>
       </c>
       <c r="BC19" s="8" t="n">
         <v>3.410958904109589</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003141444070972089</v>
+        <v>0.003139818161483361</v>
       </c>
     </row>
     <row r="20">
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>375.5</v>
+        <v>374.1</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>29770</v>
+        <v>29820</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5924602932398729</v>
+        <v>-0.5913948299285876</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.01270445381256291</v>
+        <v>0.007237026760563481</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.424637999065055</v>
+        <v>1.424609613178021</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.49570354847308</v>
+        <v>3.486518814554011</v>
       </c>
       <c r="BC20" s="8" t="n">
         <v>1.408219178082192</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.007019327019609675</v>
+        <v>0.007019466882363645</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>443.3</v>
+        <v>443.2</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.0383513991690538</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5129301782088878</v>
+        <v>0.5132715433212995</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7726027397260274</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102.1</v>
+        <v>101.8</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>214.7</v>
+        <v>215.2</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.05867251522529567</v>
+        <v>0.06026443131042223</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.09375873311597571</v>
+        <v>0.08801115241635693</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.835695921359884</v>
+        <v>1.835272338874242</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.733960119829153</v>
+        <v>1.730957188298732</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>2.010958904109589</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005447525313774188</v>
+        <v>0.005448782607454329</v>
       </c>
     </row>
     <row r="23">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>92</v>
+        <v>91.7</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10550</v>
+        <v>10440</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02455018236491463</v>
+        <v>0.02532387719564478</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.536313406635071</v>
+        <v>0.5474381148467433</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.31197041217477</v>
+        <v>4.311852693540646</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.208647352169397</v>
+        <v>4.205356755500477</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.336986301369863</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.00231912537520322</v>
+        <v>0.002319188690045108</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>87</v>
+        <v>72.8</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>35</v>
+        <v>33.5</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1036238724672493</v>
+        <v>0.1696039484163598</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.6069083942857141</v>
+        <v>0.4048387677611938</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.942551325755068</v>
+        <v>2.900656029911825</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.666262844764976</v>
+        <v>2.480032692980649</v>
       </c>
       <c r="BC24" s="8" t="n">
         <v>3.249315068493151</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003398411410014733</v>
+        <v>0.003447495979143719</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>51</v>
+        <v>49.7</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>26.6</v>
+        <v>26.8</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.3069466706150087</v>
+        <v>0.3180965010123845</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.9172932330827066</v>
+        <v>0.8544776119402986</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.838868085632898</v>
+        <v>2.831280409606686</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.172137662125888</v>
+        <v>2.148006923189673</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.249315068493151</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.0035225307053218</v>
+        <v>0.003531970894182528</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.04915307245813855</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5741440817021277</v>
+        <v>0.5795211750640479</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2684931506849315</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12510</v>
+        <v>12530</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-2.905000878748662</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.06911624108713044</v>
+        <v>0.06740975067837196</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>145.5</v>
+        <v>166.2</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15970</v>
+        <v>15810</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.08759966831361073</v>
+        <v>-0.131731449635735</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.0486568566061365</v>
+        <v>0.2099696394686907</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.659287142407959</v>
+        <v>2.667570805340278</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>2.91460562875158</v>
+        <v>3.072287720453714</v>
       </c>
       <c r="BC29" s="8" t="n">
         <v>2.745205479452055</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003760406253438692</v>
+        <v>0.003748728985930099</v>
       </c>
     </row>
     <row r="30">
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>99.90000000000001</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="F30" t="n">
         <v>0.1</v>
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>572.1</v>
+        <v>575</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4189,22 +4189,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.0552956773197756</v>
+        <v>0.05649332216360742</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.7029850498164658</v>
+        <v>0.6893078052173913</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.618856775834427</v>
+        <v>2.618590648752103</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.481633187852869</v>
+        <v>2.478568102436705</v>
       </c>
       <c r="BC30" s="8" t="n">
         <v>2.745205479452055</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003818460059471474</v>
+        <v>0.003818848129151278</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>95.40000000000001</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.08563674521434453</v>
+        <v>0.08312426209928228</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>1.509074591501417</v>
+        <v>1.522224877620397</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.161556312121849</v>
+        <v>2.162185562702315</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.991049328101987</v>
+        <v>1.996248850073421</v>
       </c>
       <c r="BC31" s="8" t="n">
         <v>2.317808219178082</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004626296314336451</v>
+        <v>0.004624949945323809</v>
       </c>
     </row>
     <row r="32">
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67740</v>
+        <v>67780</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2766204979059366</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1464127546501328</v>
+        <v>0.1457362053703157</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.616766453945738</v>
@@ -4450,7 +4450,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>155.5</v>
+        <v>153.7</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>138.5</v>
+        <v>136.6</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.1062307222477365</v>
+        <v>-0.1023310648360507</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.0007581227436822546</v>
+        <v>0.001412884333821252</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.653250087156481</v>
+        <v>2.652456590335032</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.96860739477321</v>
+        <v>2.954827204586945</v>
       </c>
       <c r="BC33" s="8" t="n">
         <v>2.745205479452055</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003768962469239799</v>
+        <v>0.003770089974870013</v>
       </c>
     </row>
     <row r="34">
@@ -4616,7 +4616,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4633,7 +4633,7 @@
         <v>0.0313433891409984</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2264000000000002</v>
+        <v>0.2280373831775702</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.647887587055733</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>75.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>835</v>
+        <v>845</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1398768387482748</v>
+        <v>0.1290362008837699</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.5432335329341316</v>
+        <v>0.5712426035502955</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.983594784178803</v>
+        <v>2.986661597642756</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.617471188777867</v>
+        <v>2.645319605611319</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.249315068493151</v>
+        <v>3.246575342465754</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003351661577177738</v>
+        <v>0.003348219968372906</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9627</v>
+        <v>9614</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.02161183019620526</v>
+        <v>-0.02171199907255639</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1438334783421626</v>
+        <v>0.1453801639276056</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.726565648705428</v>
+        <v>1.723830163616499</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.76470413481356</v>
+        <v>1.762088630323852</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.745205479452055</v>
+        <v>1.742465753424657</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005791844641122079</v>
+        <v>0.005801035514438709</v>
       </c>
     </row>
     <row r="4">
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>105.1</v>
+        <v>107</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01796327426295387</v>
+        <v>0.01794884892263297</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2009895337773551</v>
+        <v>0.1796635514018694</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.377979235350322</v>
+        <v>4.375254091149866</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.300724147951363</v>
+        <v>4.298108000004623</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.745205479452054</v>
+        <v>4.742465753424658</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002284158846450036</v>
+        <v>0.002285581543761699</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6511</v>
+        <v>6413</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.04486290576741293</v>
+        <v>0.04519333319548185</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.511365381661803</v>
+        <v>1.549742710120068</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.273972602739726</v>
+        <v>0.2712328767123288</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.2622091388520519</v>
+        <v>0.2595049816124308</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.2465753424657534</v>
+        <v>0.2438356164383562</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.0365</v>
+        <v>0.03686868686868687</v>
       </c>
     </row>
     <row r="6">
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>22290</v>
+        <v>22240</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1206711649074771</v>
+        <v>-0.1207236562143214</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.0480035890533872</v>
+        <v>0.05035971223021574</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.532707290457708</v>
+        <v>6.53005618451483</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.429197166916898</v>
+        <v>7.426625577574409</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>6.920547945205479</v>
+        <v>6.917808219178082</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001530758926640866</v>
+        <v>0.001531380392057527</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22290</v>
+        <v>22240</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05885662880229889</v>
+        <v>-0.05894631552153758</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2285329744279947</v>
+        <v>0.2312949640287769</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.935508466328635</v>
+        <v>1.932769398687092</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.05655007043773</v>
+        <v>2.053835429971506</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>1.917808219178082</v>
+        <v>1.915068493150685</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005166601011551492</v>
+        <v>0.005173922976425891</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1981</v>
+        <v>1977</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04111740637811597</v>
+        <v>0.0412406265738751</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.118839511357899</v>
+        <v>3.127173025796661</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.8575342465753426</v>
+        <v>0.8547945205479451</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.8236671880826292</v>
+        <v>0.8209385023331091</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.8301369863013699</v>
+        <v>0.8273972602739726</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01166134185303514</v>
+        <v>0.01169871794871795</v>
       </c>
     </row>
     <row r="9">
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1614170224541626</v>
+        <v>0.1616049688741593</v>
       </c>
       <c r="AZ9" s="12" t="n">
         <v>2.932941465814068</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.636982385860969</v>
+        <v>1.634235272574854</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.40946994422546</v>
+        <v>1.406876964514687</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.665753424657534</v>
+        <v>1.663013698630137</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006108801222525381</v>
+        <v>0.006119069982037708</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12700</v>
+        <v>12750</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.009220047147972083</v>
+        <v>-0.009237794379734793</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4211023622047243</v>
+        <v>0.4155294117647059</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.096835488516294</v>
+        <v>4.094104689655294</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.134960014807801</v>
+        <v>4.132277822499482</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.254794520547946</v>
+        <v>4.252054794520548</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002440908361595352</v>
+        <v>0.002442536465974435</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03604708811274462</v>
+        <v>0.03602932658469628</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.408771013722127</v>
+        <v>0.4099802592274677</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.623112554584949</v>
+        <v>2.62037673679665</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.531846848161304</v>
+        <v>2.52924957774584</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.745205479452055</v>
+        <v>2.742465753424657</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003812264930271848</v>
+        <v>0.003816245145049169</v>
       </c>
     </row>
     <row r="12">
@@ -2111,7 +2111,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>-0.07945205479452055</v>
+        <v>-0.0821917808219178</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>221.4</v>
+        <v>221.8</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1283932143700623</v>
+        <v>-0.1284848073698582</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.008130081300812941</v>
+        <v>0.006311992786293796</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.220098998442158</v>
+        <v>4.217440641181118</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.841746379237008</v>
+        <v>4.839204958037877</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.495890410958904</v>
+        <v>4.493150684931507</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.00236961265688115</v>
+        <v>0.002371106282410994</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>249.8</v>
+        <v>248.2</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2317,22 +2317,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1926964087517613</v>
+        <v>-0.1928596893970326</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.007187049639711729</v>
+        <v>0.01367979452054802</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.142144476413295</v>
+        <v>3.139460127425606</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.892147279507287</v>
+        <v>3.889608889785592</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.249315068493151</v>
+        <v>3.246575342465754</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.00318253984661292</v>
+        <v>0.003185261030277877</v>
       </c>
     </row>
     <row r="15">
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1673996684033524</v>
+        <v>-0.1676702829191477</v>
       </c>
       <c r="AZ15" s="12" t="n">
         <v>0.1571530479896239</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.892662057969872</v>
+        <v>1.889986369995816</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.273193975722279</v>
+        <v>2.270718359815842</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.010958904109589</v>
+        <v>2.008219178082192</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005283563411593041</v>
+        <v>0.005291043448118695</v>
       </c>
     </row>
     <row r="16">
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>19050</v>
+        <v>18910</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.05672324612111733</v>
+        <v>-0.05684158768249657</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1394986288713911</v>
+        <v>0.1479348958223163</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.747373670307221</v>
+        <v>1.744636702301436</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.852450686526284</v>
+        <v>1.849781202729838</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.745205479452055</v>
+        <v>1.742465753424657</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005722874374226901</v>
+        <v>0.005731852360327231</v>
       </c>
     </row>
     <row r="17">
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>82.7</v>
+        <v>82</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.0564236282759181</v>
+        <v>0.05642918568489265</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8386336154776299</v>
+        <v>0.8543292682926831</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.99368178144982</v>
+        <v>2.990938983838319</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.833789117662489</v>
+        <v>2.831177919321934</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.249315068493151</v>
+        <v>3.246575342465754</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003340368392514006</v>
+        <v>0.003343431629342984</v>
       </c>
     </row>
     <row r="18">
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1210723279362329</v>
+        <v>0.1211778189263902</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>2.153535353535354</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.719184081352278</v>
+        <v>1.716439828223285</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.533517542545271</v>
+        <v>1.530925602744177</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.745205479452055</v>
+        <v>1.742465753424657</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.00581671277001017</v>
+        <v>0.005826012561332349</v>
       </c>
     </row>
     <row r="19">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>150.3</v>
+        <v>159.2</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.02210728152438137</v>
+        <v>0.02208886227830516</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5131736526946107</v>
+        <v>0.4285804020100503</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.184897814361213</v>
+        <v>3.18216755243813</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.116011275852788</v>
+        <v>3.113396173151582</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.410958904109589</v>
+        <v>3.408219178082192</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003139818161483361</v>
+        <v>0.003142512088132553</v>
       </c>
     </row>
     <row r="20">
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>29820</v>
+        <v>29730</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5913948299285876</v>
+        <v>-0.5921047315921046</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.007237026760563481</v>
+        <v>0.01028618022199801</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.424609613178021</v>
+        <v>1.421888800045325</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.486518814554011</v>
+        <v>3.485916386319627</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.408219178082192</v>
+        <v>1.405479452054795</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.007019466882363645</v>
+        <v>0.007032898774982427</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>443.2</v>
+        <v>449.6</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3124,22 +3124,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.0383513991690538</v>
+        <v>0.03835679493966514</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5132715433212995</v>
+        <v>0.4917303113879001</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.7726027397260274</v>
+        <v>0.7698630136986301</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.7440667392024577</v>
+        <v>0.7414243518706534</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.7452054794520548</v>
+        <v>0.7424657534246575</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01294326241134752</v>
+        <v>0.01298932384341637</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101.8</v>
+        <v>103.9</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>215.2</v>
+        <v>222.8</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.06026443131042223</v>
+        <v>0.04924509585505125</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.08801115241635693</v>
+        <v>0.07257630161579876</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.835272338874242</v>
+        <v>1.835458814738462</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.730957188298732</v>
+        <v>1.749313694187638</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.010958904109589</v>
+        <v>2.008219178082192</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005448782607454329</v>
+        <v>0.005448229031183639</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10440</v>
+        <v>10310</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02532387719564478</v>
+        <v>0.02533663810346833</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5474381148467433</v>
+        <v>0.5669499436469447</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.311852693540646</v>
+        <v>4.309111024248148</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.205356755500477</v>
+        <v>4.20263049628127</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.336986301369863</v>
+        <v>4.334246575342465</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002319188690045108</v>
+        <v>0.002320664272451601</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>33.5</v>
+        <v>37.5</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1696039484163598</v>
+        <v>0.1696979992903886</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.4048387677611938</v>
+        <v>0.2549892991999998</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.900656029911825</v>
+        <v>2.897854951018001</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.480032692980649</v>
+        <v>2.47743858053619</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.249315068493151</v>
+        <v>3.246575342465754</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003447495979143719</v>
+        <v>0.003450828343387943</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.3180965010123845</v>
+        <v>0.3183294574077659</v>
       </c>
       <c r="AZ25" s="12" t="n">
         <v>0.8544776119402986</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.831280409606686</v>
+        <v>2.828381582894828</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.148006923189673</v>
+        <v>2.145428494373691</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.249315068493151</v>
+        <v>3.246575342465754</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003531970894182528</v>
+        <v>0.003535590834163568</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3699,22 +3699,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>74.35420289855074</v>
+        <v>75.05960532322062</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.3966249999999998</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.2739726027397261</v>
+        <v>0.2712328767123288</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.003635797237595028</v>
+        <v>0.003566056851855931</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.2465753424657534</v>
+        <v>0.2438356164383562</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.0365</v>
+        <v>0.03686868686868687</v>
       </c>
     </row>
     <row r="27">
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1171</v>
+        <v>1153</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3808,22 +3808,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.04915307245813855</v>
+        <v>0.0493765780147074</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5795211750640479</v>
+        <v>0.6041797883781441</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.2684931506849315</v>
+        <v>0.2657534246575343</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.2559141823374343</v>
+        <v>0.2532488624439354</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.2465753424657534</v>
+        <v>0.2438356164383562</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.03724489795918368</v>
+        <v>0.03762886597938144</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12530</v>
+        <v>12470</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3938,15 +3938,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-2.905000878748662</v>
+        <v>-2.934364360215925</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.06740975067837196</v>
+        <v>0.0725456436246994</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.2465753424657534</v>
+        <v>0.2438356164383562</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>166.2</v>
+        <v>179.9</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15810</v>
+        <v>15350</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.131731449635735</v>
+        <v>-0.1571206183842583</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.2099696394686907</v>
+        <v>0.3489570032573288</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.667570805340278</v>
+        <v>2.669488870101082</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.072287720453714</v>
+        <v>3.167106620859387</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.745205479452055</v>
+        <v>2.742465753424657</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003748728985930099</v>
+        <v>0.00374603547218436</v>
       </c>
     </row>
     <row r="30">
@@ -4189,22 +4189,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05649332216360742</v>
+        <v>0.05649379049042826</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.6893078052173913</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.618590648752103</v>
+        <v>2.615850818628084</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.478568102436705</v>
+        <v>2.475973680274823</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.745205479452055</v>
+        <v>2.742465753424657</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003818848129151278</v>
+        <v>0.003822847973128921</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.08312426209928228</v>
+        <v>0.08314690119292749</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.522224877620397</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.162185562702315</v>
+        <v>2.159440169761754</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.996248850073421</v>
+        <v>1.993672480975061</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.317808219178082</v>
+        <v>2.315068493150685</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004624949945323809</v>
+        <v>0.004630829851193923</v>
       </c>
     </row>
     <row r="32">
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67780</v>
+        <v>67570</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4412,22 +4412,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2766204979059366</v>
+        <v>-0.2770449734188666</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1457362053703157</v>
+        <v>0.1492970253070889</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.616766453945738</v>
+        <v>1.614042182246498</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.23501833997987</v>
+        <v>2.232562362667746</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.619178082191781</v>
+        <v>1.616438356164384</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.006185185235378231</v>
+        <v>0.006195624940905534</v>
       </c>
     </row>
     <row r="33">
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>136.6</v>
+        <v>137.1</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.1023310648360507</v>
+        <v>-0.1024641967180709</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.001412884333821252</v>
+        <v>-0.002239241429613514</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.652456590335032</v>
+        <v>2.649743985294451</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.954827204586945</v>
+        <v>2.952243214817055</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.745205479452055</v>
+        <v>2.742465753424657</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003770089974870013</v>
+        <v>0.00377394950436646</v>
       </c>
     </row>
     <row r="34">
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.0313433891409984</v>
+        <v>0.03132179246280847</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.2280373831775702</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.647887587055733</v>
+        <v>1.645148713617739</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.597806903506941</v>
+        <v>1.595184670430656</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.665753424657534</v>
+        <v>1.663013698630137</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.006068375099461073</v>
+        <v>0.006078477840468084</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>845</v>
+        <v>840.2</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.1290362008837699</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.5712426035502955</v>
+        <v>0.580218995477267</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>2.986661597642756</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9614</v>
+        <v>9622</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.02171199907255639</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1453801639276056</v>
+        <v>0.1444278628143836</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.723830163616499</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>107</v>
+        <v>105.7</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.01794884892263297</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.1796635514018694</v>
+        <v>0.1941721854304637</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.375254091149866</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6413</v>
+        <v>6599</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.04519333319548185</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.549742710120068</v>
+        <v>1.477875435672071</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2712328767123288</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>22240</v>
+        <v>22670</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.1207236562143214</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.05035971223021574</v>
+        <v>0.03043670048522285</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.53005618451483</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22240</v>
+        <v>22670</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.05894631552153758</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2312949640287769</v>
+        <v>0.2079400088222321</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.932769398687092</v>
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>96.8</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1977</v>
+        <v>1994</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,16 +1617,16 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.0412406265738751</v>
+        <v>0.05005913407761536</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.127173025796661</v>
+        <v>3.062395684052156</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.8547945205479451</v>
+        <v>0.8547945205479452</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.8209385023331091</v>
+        <v>0.8140441740919735</v>
       </c>
       <c r="BC8" s="8" t="n">
         <v>0.8273972602739726</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12750</v>
+        <v>12650</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.009237794379734793</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4155294117647059</v>
+        <v>0.4267193675889327</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.094104689655294</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1165</v>
+        <v>1149</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03602932658469628</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4099802592274677</v>
+        <v>0.4296144490861618</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.62037673679665</v>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>223.2</v>
+        <v>220.6</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>221.8</v>
+        <v>217.7</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1284848073698582</v>
+        <v>-0.126088058465774</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.006311992786293796</v>
+        <v>0.01332108406063393</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.217440641181118</v>
+        <v>4.215306726674954</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.839204958037877</v>
+        <v>4.823491391220296</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.493150684931507</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002371106282410994</v>
+        <v>0.002372306607421669</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>248.2</v>
+        <v>247</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1928596893970326</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.01367979452054802</v>
+        <v>0.01860455465587041</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.139460127425606</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>163.7</v>
+        <v>165.2</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>77.09999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1676702829191477</v>
+        <v>-0.1715168388884515</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1571530479896239</v>
+        <v>0.1800000000000002</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.889986369995816</v>
+        <v>1.890895449323958</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.270718359815842</v>
+        <v>2.282358336392747</v>
       </c>
       <c r="BC15" s="8" t="n">
         <v>2.008219178082192</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005291043448118695</v>
+        <v>0.00528849969128396</v>
       </c>
     </row>
     <row r="16">
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18910</v>
+        <v>18700</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2538,7 +2538,7 @@
         <v>-0.05684158768249657</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1479348958223163</v>
+        <v>0.160826143315508</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.744636702301436</v>
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2668,7 +2668,7 @@
         <v>0.05642918568489265</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8543292682926831</v>
+        <v>0.8319879518072291</v>
       </c>
       <c r="BA17" s="8" t="n">
         <v>2.990938983838319</v>
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>159.2</v>
+        <v>146.9</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.02208886227830516</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4285804020100503</v>
+        <v>0.5481960517358748</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.18216755243813</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>29730</v>
+        <v>29650</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5921047315921046</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.01028618022199801</v>
+        <v>0.01301207885328837</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.421888800045325</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>449.6</v>
+        <v>445.2</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03835679493966514</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.4917303113879001</v>
+        <v>0.506473378256963</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7698630136986301</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103.9</v>
+        <v>101.7</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>222.8</v>
+        <v>214.9</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.04924509585505125</v>
+        <v>0.06078798012752074</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.07257630161579876</v>
+        <v>0.08845974872033491</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.835458814738462</v>
+        <v>1.832393243024379</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.749313694187638</v>
+        <v>1.727388768869818</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>2.008219178082192</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005448229031183639</v>
+        <v>0.005457343852400876</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10310</v>
+        <v>10250</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.02533663810346833</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5669499436469447</v>
+        <v>0.5761223335609758</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.309111024248148</v>
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>37.5</v>
+        <v>34.8</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3480,7 +3480,7 @@
         <v>0.1696979992903886</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.2549892991999998</v>
+        <v>0.3523591586206896</v>
       </c>
       <c r="BA24" s="8" t="n">
         <v>2.897854951018001</v>
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>49.7</v>
+        <v>49</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>26.8</v>
+        <v>26.5</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.3183294574077659</v>
+        <v>0.3245054160772011</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.8544776119402986</v>
+        <v>0.8490566037735849</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.828381582894828</v>
+        <v>2.82415520257259</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.145428494373691</v>
+        <v>2.132233789527954</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.246575342465754</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003535590834163568</v>
+        <v>0.003540881885985147</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15350</v>
+        <v>15500</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.1571206183842583</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.3489570032573288</v>
+        <v>0.3359025806451612</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.669488870101082</v>
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>95.90000000000001</v>
+        <v>96</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.08314690119292749</v>
+        <v>0.08264613488874688</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>1.522224877620397</v>
+        <v>1.524854934844193</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.159440169761754</v>
+        <v>2.15956550633508</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.993672480975061</v>
+        <v>1.994710401434165</v>
       </c>
       <c r="BC31" s="8" t="n">
         <v>2.315068493150685</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004630829851193923</v>
+        <v>0.004630561087711869</v>
       </c>
     </row>
     <row r="32">
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67570</v>
+        <v>67410</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2770449734188666</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1492970253070889</v>
+        <v>0.15202492211838</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.614042182246498</v>
@@ -4450,7 +4450,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>153.7</v>
+        <v>154</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>137.1</v>
+        <v>134.8</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.1024641967180709</v>
+        <v>-0.1031190498924929</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.002239241429613514</v>
+        <v>0.01676557863501471</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.649743985294451</v>
+        <v>2.649877356449939</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.952243214817055</v>
+        <v>2.95454748607639</v>
       </c>
       <c r="BC33" s="8" t="n">
         <v>2.742465753424657</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.00377394950436646</v>
+        <v>0.003773759557460077</v>
       </c>
     </row>
     <row r="34">
@@ -4616,7 +4616,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1498</v>
+        <v>1505</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4633,7 +4633,7 @@
         <v>0.03132179246280847</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2280373831775702</v>
+        <v>0.2223255813953489</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.645148713617739</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>840.2</v>
+        <v>815</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.1290362008837699</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.580218995477267</v>
+        <v>0.6290797546012268</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>2.986661597642756</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9622</v>
+        <v>9593</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.02171199907255639</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1444278628143836</v>
+        <v>0.1478875113103304</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.723830163616499</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112.7</v>
+        <v>113.6</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>105.7</v>
+        <v>105.3</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01794884892263297</v>
+        <v>0.01611764012146472</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.1941721854304637</v>
+        <v>0.208281101614435</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.375254091149866</v>
+        <v>4.377102461845022</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.298108000004623</v>
+        <v>4.307672939642886</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.742465753424658</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002285581543761699</v>
+        <v>0.002284616384279209</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6599</v>
+        <v>6635</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.04519333319548185</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.477875435672071</v>
+        <v>1.464431047475508</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2712328767123288</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>22670</v>
+        <v>22650</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.1207236562143214</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.03043670048522285</v>
+        <v>0.03134657836644594</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.53005618451483</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22670</v>
+        <v>22650</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.05894631552153758</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2079400088222321</v>
+        <v>0.2090066225165563</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.932769398687092</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1994</v>
+        <v>1989</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.05005913407761536</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.062395684052156</v>
+        <v>3.072607840120663</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8547945205479452</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>203.3</v>
+        <v>208.2</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1616049688741593</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.932941465814068</v>
+        <v>2.84037944284342</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.634235272574854</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12650</v>
+        <v>12760</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.009237794379734793</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4267193675889327</v>
+        <v>0.4144200626959247</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.094104689655294</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1149</v>
+        <v>1134</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03602932658469628</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4296144490861618</v>
+        <v>0.4485246931216931</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.62037673679665</v>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220.6</v>
+        <v>218</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>217.7</v>
+        <v>218.9</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.126088058465774</v>
+        <v>-0.1236552782005575</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.01332108406063393</v>
+        <v>-0.00411146642302429</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.215306726674954</v>
+        <v>4.21313071782131</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.823491391220296</v>
+        <v>4.807618067431591</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.493150684931507</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002372306607421669</v>
+        <v>0.002373531862588681</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1928596893970326</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.01860455465587041</v>
+        <v>0.02691969387755111</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.139460127425606</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>76.3</v>
+        <v>77.7</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2429,7 +2429,7 @@
         <v>-0.1715168388884515</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1800000000000002</v>
+        <v>0.1587387387387387</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.890895449323958</v>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>115.7</v>
+        <v>115.3</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18700</v>
+        <v>18690</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.05684158768249657</v>
+        <v>-0.05497688828316969</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.160826143315508</v>
+        <v>0.1574318630283573</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.744636702301436</v>
+        <v>1.744593246164286</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.849781202729838</v>
+        <v>1.846085269803477</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.742465753424657</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005731852360327231</v>
+        <v>0.005731995135247883</v>
       </c>
     </row>
     <row r="17">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>98.09999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05642918568489265</v>
+        <v>0.05852075964206207</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8319879518072291</v>
+        <v>0.8207831325301205</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.990938983838319</v>
+        <v>2.989781750739118</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.831177919321934</v>
+        <v>2.824490425440603</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.246575342465754</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003343431629342984</v>
+        <v>0.003344725747131158</v>
       </c>
     </row>
     <row r="18">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>146.9</v>
+        <v>150.6</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.02208886227830516</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5481960517358748</v>
+        <v>0.5101593625498009</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.18216755243813</v>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>374.1</v>
+        <v>372</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>29650</v>
+        <v>29840</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5921047315921046</v>
+        <v>-0.5904935125162195</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.01301207885328837</v>
+        <v>0.0009116273458444901</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.421888800045325</v>
+        <v>1.421845875682066</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.485916386319627</v>
+        <v>3.472096094053656</v>
       </c>
       <c r="BC20" s="8" t="n">
         <v>1.405479452054795</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.007032898774982427</v>
+        <v>0.007033111092440277</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>445.2</v>
+        <v>447.8</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03835679493966514</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.506473378256963</v>
+        <v>0.4977265475658774</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7698630136986301</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>214.9</v>
+        <v>213</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3262,7 +3262,7 @@
         <v>0.06078798012752074</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.08845974872033491</v>
+        <v>0.09816901408450707</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.832393243024379</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10250</v>
+        <v>10220</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.02533663810346833</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5761223335609758</v>
+        <v>0.5807489157534247</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.309111024248148</v>
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>34.8</v>
+        <v>33.6</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3480,7 +3480,7 @@
         <v>0.1696979992903886</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.3523591586206896</v>
+        <v>0.4006576999999998</v>
       </c>
       <c r="BA24" s="8" t="n">
         <v>2.897854951018001</v>
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>49</v>
+        <v>48.3</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>26.5</v>
+        <v>27.4</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.3245054160772011</v>
+        <v>0.3308031157452471</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.8490566037735849</v>
+        <v>0.7627737226277371</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.82415520257259</v>
+        <v>2.819828890663075</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.132233789527954</v>
+        <v>2.118892612513892</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.246575342465754</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003540881885985147</v>
+        <v>0.003546314470750929</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12470</v>
+        <v>12370</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-2.934364360215925</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.0725456436246994</v>
+        <v>0.0812161823767179</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15500</v>
+        <v>15970</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.1571206183842583</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.3359025806451612</v>
+        <v>0.2965867251095804</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.669488870101082</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67410</v>
+        <v>66960</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2770449734188666</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.15202492211838</v>
+        <v>0.1597670250896057</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.614042182246498</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>815</v>
+        <v>835.9</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.1290362008837699</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.6290797546012268</v>
+        <v>0.5883478885034092</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>2.986661597642756</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9593</v>
+        <v>9589</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.02171199907255639</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1478875113103304</v>
+        <v>0.1483663464386276</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.723830163616499</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>105.3</v>
+        <v>105.4</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.01611764012146472</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.208281101614435</v>
+        <v>0.2071347248576849</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.377102461845022</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6635</v>
+        <v>6650</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.04519333319548185</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.464431047475508</v>
+        <v>1.458872180451128</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2712328767123288</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>22650</v>
+        <v>22680</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.1207236562143214</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.03134657836644594</v>
+        <v>0.02998236331569659</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.53005618451483</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22650</v>
+        <v>22680</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.05894631552153758</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2090066225165563</v>
+        <v>0.2074074074074075</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.932769398687092</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.05005913407761536</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.072607840120663</v>
+        <v>3.074656435613682</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8547945205479452</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03602932658469628</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4485246931216931</v>
+        <v>0.44470272823219</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.62037673679665</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>29840</v>
+        <v>29880</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5904935125162195</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.0009116273458444901</v>
+        <v>-0.0004282811244979978</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.421845875682066</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>447.8</v>
+        <v>448</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03835679493966514</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.4977265475658774</v>
+        <v>0.4970579196428571</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7698630136986301</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10220</v>
+        <v>10210</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.02533663810346833</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5807489157534247</v>
+        <v>0.5822971517140059</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.309111024248148</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>66960</v>
+        <v>67260</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2770449734188666</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1597670250896057</v>
+        <v>0.1545941123996433</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.614042182246498</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>134.8</v>
+        <v>136</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4524,7 +4524,7 @@
         <v>-0.1031190498924929</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.01676557863501471</v>
+        <v>0.00779411764705884</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.649877356449939</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>78.09999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>835.9</v>
+        <v>816.6</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1290362008837699</v>
+        <v>0.1399569260379162</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.5883478885034092</v>
+        <v>0.5780063678667644</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.986661597642756</v>
+        <v>2.980811939997675</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.645319605611319</v>
+        <v>2.614846115596591</v>
       </c>
       <c r="BC2" s="8" t="n">
         <v>3.246575342465754</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003348219968372906</v>
+        <v>0.003354790641373974</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9589</v>
+        <v>9645</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.02171199907255639</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1483663464386276</v>
+        <v>0.14169879688958</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.723830163616499</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>113.6</v>
+        <v>112.7</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>105.4</v>
+        <v>106.1</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01611764012146472</v>
+        <v>0.01794884892263297</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2071347248576849</v>
+        <v>0.1896701225259192</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.377102461845022</v>
+        <v>4.375254091149866</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.307672939642886</v>
+        <v>4.298108000004623</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.742465753424658</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002284616384279209</v>
+        <v>0.002285581543761699</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6650</v>
+        <v>6745</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.04519333319548185</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.458872180451128</v>
+        <v>1.424240177909562</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2712328767123288</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>292</v>
+        <v>286.4</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>22680</v>
+        <v>22110</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1207236562143214</v>
+        <v>-0.1181136561834859</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02998236331569659</v>
+        <v>0.03627317955676168</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.53005618451483</v>
+        <v>6.52563125202738</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.426625577574409</v>
+        <v>7.399628418993987</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.917808219178082</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001531380392057527</v>
+        <v>0.001532418798088415</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22680</v>
+        <v>22110</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.05894631552153758</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2074074074074075</v>
+        <v>0.2385345997286297</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.932769398687092</v>
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>96.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1988</v>
+        <v>1974</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,16 +1617,16 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.05005913407761536</v>
+        <v>0.04374716377423899</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.074656435613682</v>
+        <v>3.12490514893617</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8547945205479452</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.8140441740919735</v>
+        <v>0.8189670355193761</v>
       </c>
       <c r="BC8" s="8" t="n">
         <v>0.8273972602739726</v>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>83.90000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>208.2</v>
+        <v>208.4</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1616049688741593</v>
+        <v>0.1632739367291341</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.84037944284342</v>
+        <v>2.827547984644913</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.634235272574854</v>
+        <v>1.634169678602777</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.406876964514687</v>
+        <v>1.404802108089602</v>
       </c>
       <c r="BC9" s="8" t="n">
         <v>1.663013698630137</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006119069982037708</v>
+        <v>0.006119315595520073</v>
       </c>
     </row>
     <row r="10">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>104.9</v>
+        <v>104.8</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1137</v>
+        <v>1131</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03602932658469628</v>
+        <v>0.03640198709613733</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.44470272823219</v>
+        <v>0.4509824084880636</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.62037673679665</v>
+        <v>2.620294729440699</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.52924957774584</v>
+        <v>2.528261004962391</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.742465753424657</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003816245145049169</v>
+        <v>0.003816364582061536</v>
       </c>
     </row>
     <row r="12">
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>218</v>
+        <v>220.2</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>218.9</v>
+        <v>218.6</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1236552782005575</v>
+        <v>-0.1257161541614853</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.00411146642302429</v>
+        <v>0.007319304666056681</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.21313071782131</v>
+        <v>4.214974729002787</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.807618067431591</v>
+        <v>4.821059829785894</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.493150684931507</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002373531862588681</v>
+        <v>0.002372493465071351</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>245</v>
+        <v>244.6</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1928596893970326</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.02691969387755111</v>
+        <v>0.02859903924775153</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.139460127425606</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>165.2</v>
+        <v>164.6</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>77.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1715168388884515</v>
+        <v>-0.1699846136787179</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1587387387387387</v>
+        <v>0.1590051679586564</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.890895449323958</v>
+        <v>1.89053359108873</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.282358336392747</v>
+        <v>2.277709090993818</v>
       </c>
       <c r="BC15" s="8" t="n">
         <v>2.008219178082192</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.00528849969128396</v>
+        <v>0.005289511938394677</v>
       </c>
     </row>
     <row r="16">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>115.3</v>
+        <v>115.1</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18690</v>
+        <v>18640</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.05497688828316969</v>
+        <v>-0.05404071914717222</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1574318630283573</v>
+        <v>0.1585234892703864</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.744593246164286</v>
+        <v>1.744571430541943</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.846085269803477</v>
+        <v>1.844235228570439</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.742465753424657</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005731995135247883</v>
+        <v>0.005732066813047345</v>
       </c>
     </row>
     <row r="17">
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2668,7 +2668,7 @@
         <v>0.05852075964206207</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8207831325301205</v>
+        <v>0.8429878048780488</v>
       </c>
       <c r="BA17" s="8" t="n">
         <v>2.989781750739118</v>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>89.2</v>
+        <v>89</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1211778189263902</v>
+        <v>0.1226260833860738</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>2.153535353535354</v>
+        <v>2.146464646464647</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.716439828223285</v>
+        <v>1.7163776809266</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.530925602744177</v>
+        <v>1.528895245111042</v>
       </c>
       <c r="BC18" s="8" t="n">
         <v>1.742465753424657</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005826012561332349</v>
+        <v>0.005826223511949551</v>
       </c>
     </row>
     <row r="19">
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>108.3</v>
+        <v>107.4</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>150.6</v>
+        <v>149.9</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.02208886227830516</v>
+        <v>0.0247077910268273</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5101593625498009</v>
+        <v>0.504603068712475</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.18216755243813</v>
+        <v>3.180820011442621</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.113396173151582</v>
+        <v>3.104123965189356</v>
       </c>
       <c r="BC19" s="8" t="n">
         <v>3.408219178082192</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003142512088132553</v>
+        <v>0.003143843400137761</v>
       </c>
     </row>
     <row r="20">
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>372</v>
+        <v>373.6</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>29880</v>
+        <v>29680</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5904935125162195</v>
+        <v>-0.5917225058824287</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.0004282811244979978</v>
+        <v>0.01063558113207552</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.421845875682066</v>
+        <v>1.421878616862526</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.472096094053656</v>
+        <v>3.482627961004065</v>
       </c>
       <c r="BC20" s="8" t="n">
         <v>1.405479452054795</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.007033111092440277</v>
+        <v>0.007032949143060955</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>213</v>
+        <v>213.2</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3262,7 +3262,7 @@
         <v>0.06078798012752074</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.09816901408450707</v>
+        <v>0.09713883677298307</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.832393243024379</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10210</v>
+        <v>10290</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.02533663810346833</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5822971517140059</v>
+        <v>0.5699955217687076</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.309111024248148</v>
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>33.6</v>
+        <v>35.9</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3480,7 +3480,7 @@
         <v>0.1696979992903886</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.4006576999999998</v>
+        <v>0.3109219699164345</v>
       </c>
       <c r="BA24" s="8" t="n">
         <v>2.897854951018001</v>
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>48.3</v>
+        <v>48.5</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>27.4</v>
+        <v>27.6</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.3308031157452471</v>
+        <v>0.3289911063932611</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.7627737226277371</v>
+        <v>0.757246376811594</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.819828890663075</v>
+        <v>2.821075392050281</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.118892612513892</v>
+        <v>2.122719541522273</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.246575342465754</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003546314470750929</v>
+        <v>0.003544747520105186</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1153</v>
+        <v>1136</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.0493765780147074</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.6041797883781441</v>
+        <v>0.6281860000000001</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2657534246575343</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12370</v>
+        <v>12420</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-2.934364360215925</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.0812161823767179</v>
+        <v>0.07686346022544299</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>179.9</v>
+        <v>172.5</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15970</v>
+        <v>15630</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1571206183842583</v>
+        <v>-0.1438345514558626</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.2965867251095804</v>
+        <v>0.2702975047984646</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.669488870101082</v>
+        <v>2.66706142844901</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.167106620859387</v>
+        <v>3.115123873527252</v>
       </c>
       <c r="BC29" s="8" t="n">
         <v>2.742465753424657</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.00374603547218436</v>
+        <v>0.003749444948411012</v>
       </c>
     </row>
     <row r="30">
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>575</v>
+        <v>572.5</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4192,7 +4192,7 @@
         <v>0.05649379049042826</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.6893078052173913</v>
+        <v>0.6966846951965067</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.615850818628084</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67260</v>
+        <v>66910</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2770449734188666</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1545941123996433</v>
+        <v>0.1606336870422955</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.614042182246498</v>
@@ -4450,7 +4450,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>154</v>
+        <v>152.9</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>136</v>
+        <v>135.5</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.1031190498924929</v>
+        <v>-0.1007091887035282</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.00779411764705884</v>
+        <v>0.00428782287822882</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.649877356449939</v>
+        <v>2.649386284989781</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.95454748607639</v>
+        <v>2.946084016104052</v>
       </c>
       <c r="BC33" s="8" t="n">
         <v>2.742465753424657</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003773759557460077</v>
+        <v>0.003774459034779284</v>
       </c>
     </row>
     <row r="34">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1399569260379162</v>
+        <v>0.1400371760145125</v>
       </c>
       <c r="AZ2" s="12" t="n">
         <v>0.5780063678667644</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.980811939997675</v>
+        <v>2.978029004980288</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.614846115596591</v>
+        <v>2.612220958785978</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.246575342465754</v>
+        <v>3.243835616438356</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003354790641373974</v>
+        <v>0.003357925655954513</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9645</v>
+        <v>9464</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.02171199907255639</v>
+        <v>-0.0218124685743514</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.14169879688958</v>
+        <v>0.1635339070160606</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.723830163616499</v>
+        <v>1.721094691293183</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.762088630323852</v>
+        <v>1.759473143953075</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.742465753424657</v>
+        <v>1.73972602739726</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005801035514438709</v>
+        <v>0.005810255560364476</v>
       </c>
     </row>
     <row r="4">
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>106.1</v>
+        <v>105.5</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01794884892263297</v>
+        <v>0.01793440861466473</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.1896701225259192</v>
+        <v>0.1964360189573462</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.375254091149866</v>
+        <v>4.372528961746084</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.298108000004623</v>
+        <v>4.295491855606669</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.742465753424658</v>
+        <v>4.739726027397261</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002285581543761699</v>
+        <v>0.002287006006703886</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6745</v>
+        <v>6697</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.04519333319548185</v>
+        <v>0.04553051219473913</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.424240177909562</v>
+        <v>1.441615648797969</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.2712328767123288</v>
+        <v>0.2684931506849316</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.2595049816124308</v>
+        <v>0.256800875300445</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.2438356164383562</v>
+        <v>0.2410958904109589</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.03686868686868687</v>
+        <v>0.03724489795918366</v>
       </c>
     </row>
     <row r="6">
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>22110</v>
+        <v>21390</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1181136561834859</v>
+        <v>-0.1181653804295655</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.03627317955676168</v>
+        <v>0.07115474520804121</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.52563125202738</v>
+        <v>6.52297958569731</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.399628418993987</v>
+        <v>7.397055457943837</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>6.917808219178082</v>
+        <v>6.915068493150685</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001532418798088415</v>
+        <v>0.001533041743979488</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22110</v>
+        <v>21390</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05894631552153758</v>
+        <v>-0.05903624809408117</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2385345997286297</v>
+        <v>0.2802244039270687</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.932769398687092</v>
+        <v>1.930030332851224</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.053835429971506</v>
+        <v>2.051120809852616</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>1.915068493150685</v>
+        <v>1.912328767123288</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005173922976425891</v>
+        <v>0.005181265718879688</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1974</v>
+        <v>1962</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04374716377423899</v>
+        <v>0.04387920050119664</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.12490514893617</v>
+        <v>3.150133926605505</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.8547945205479452</v>
+        <v>0.852054794520548</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.8189670355193761</v>
+        <v>0.816238884835958</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.8273972602739726</v>
+        <v>0.8246575342465754</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01169871794871795</v>
+        <v>0.01173633440514469</v>
       </c>
     </row>
     <row r="9">
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1632739367291341</v>
+        <v>0.1634654009791623</v>
       </c>
       <c r="AZ9" s="12" t="n">
         <v>2.827547984644913</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.634169678602777</v>
+        <v>1.631422428202702</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.404802108089602</v>
+        <v>1.402209663329663</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.663013698630137</v>
+        <v>1.66027397260274</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006119315595520073</v>
+        <v>0.006129620279290112</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12760</v>
+        <v>12490</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.009237794379734793</v>
+        <v>-0.009255564465641814</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4144200626959247</v>
+        <v>0.444995996797438</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.094104689655294</v>
+        <v>4.091373901970883</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.132277822499482</v>
+        <v>4.129595640639859</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.252054794520548</v>
+        <v>4.249315068493151</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002442536465974435</v>
+        <v>0.002444166737042252</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1131</v>
+        <v>1118</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03640198709613733</v>
+        <v>0.03638452687817048</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4509824084880636</v>
+        <v>0.4678542969588551</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.620294729440699</v>
+        <v>2.617558846036101</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.528261004962391</v>
+        <v>2.525663764896985</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.742465753424657</v>
+        <v>2.73972602739726</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003816364582061536</v>
+        <v>0.003820353462212892</v>
       </c>
     </row>
     <row r="12">
@@ -2111,7 +2111,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>-0.0821917808219178</v>
+        <v>-0.08493150684931507</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220.2</v>
+        <v>217.5</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>218.6</v>
+        <v>215.3</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1257161541614853</v>
+        <v>-0.1232724835778101</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.007319304666056681</v>
+        <v>0.01021830004644686</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.214974729002787</v>
+        <v>4.210047680727201</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.821059829785894</v>
+        <v>4.802002448728715</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.493150684931507</v>
+        <v>4.49041095890411</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002372493465071351</v>
+        <v>0.002375270010783512</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>244.6</v>
+        <v>244.3</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2317,22 +2317,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1928596893970326</v>
+        <v>-0.1930232186689829</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.02859903924775153</v>
+        <v>0.02986215718379048</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.139460127425606</v>
+        <v>3.13677584888771</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.889608889785592</v>
+        <v>3.88707075774095</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.246575342465754</v>
+        <v>3.243835616438356</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003185261030277877</v>
+        <v>0.003187986799740876</v>
       </c>
     </row>
     <row r="15">
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>77.40000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1699846136787179</v>
+        <v>-0.1702581714871968</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1590051679586564</v>
+        <v>0.1530462724935735</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.89053359108873</v>
+        <v>1.887858495314273</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.277709090993818</v>
+        <v>2.2752360197364</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.008219178082192</v>
+        <v>2.005479452054795</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005289511938394677</v>
+        <v>0.005297007177614386</v>
       </c>
     </row>
     <row r="16">
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18640</v>
+        <v>18300</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.05404071914717222</v>
+        <v>-0.05415552735808606</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1585234892703864</v>
+        <v>0.1800479693989072</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.744571430541943</v>
+        <v>1.741834379846844</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.844235228570439</v>
+        <v>1.841565320968243</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.742465753424657</v>
+        <v>1.73972602739726</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005732066813047345</v>
+        <v>0.005741073959557095</v>
       </c>
     </row>
     <row r="17">
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05852075964206207</v>
+        <v>0.05852798419805328</v>
       </c>
       <c r="AZ17" s="12" t="n">
         <v>0.8429878048780488</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.989781750739118</v>
+        <v>2.987038023274248</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.824490425440603</v>
+        <v>2.821879126357953</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.246575342465754</v>
+        <v>3.243835616438356</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003344725747131158</v>
+        <v>0.003347798026701542</v>
       </c>
     </row>
     <row r="18">
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1226260833860738</v>
+        <v>0.1227341744449786</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>2.146464646464647</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.7163776809266</v>
+        <v>1.713633316868852</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.528895245111042</v>
+        <v>1.526303693139102</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.742465753424657</v>
+        <v>1.73972602739726</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005826223511949551</v>
+        <v>0.005835554141928091</v>
       </c>
     </row>
     <row r="19">
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.0247077910268273</v>
+        <v>0.02469124128198948</v>
       </c>
       <c r="AZ19" s="12" t="n">
         <v>0.504603068712475</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.180820011442621</v>
+        <v>3.178088812873074</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.104123965189356</v>
+        <v>3.101508712904554</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.408219178082192</v>
+        <v>3.405479452054795</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003143843400137761</v>
+        <v>0.003146545168748681</v>
       </c>
     </row>
     <row r="20">
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>373.6</v>
+        <v>368.5</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>29680</v>
+        <v>29270</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5917225058824287</v>
+        <v>-0.5884841754585874</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.01063558113207552</v>
+        <v>0.01080267611889307</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.421878616862526</v>
+        <v>1.419052624281306</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.482627961004065</v>
+        <v>3.448354934740792</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.405479452054795</v>
+        <v>1.402739726027397</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.007032949143060955</v>
+        <v>0.00704695500990642</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3124,22 +3124,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03835679493966514</v>
+        <v>0.03836225503731567</v>
       </c>
       <c r="AZ21" s="12" t="n">
         <v>0.4970579196428571</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.7698630136986301</v>
+        <v>0.7671232876712328</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.7414243518706534</v>
+        <v>0.7387819462328825</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.7424657534246575</v>
+        <v>0.7397260273972602</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01298932384341637</v>
+        <v>0.01303571428571429</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101.7</v>
+        <v>103.9</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.06078798012752074</v>
+        <v>0.049221363068206</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.09713883677298307</v>
+        <v>0.1208724202626643</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.832393243024379</v>
+        <v>1.832725376141901</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.727388768869818</v>
+        <v>1.746748055894057</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.008219178082192</v>
+        <v>2.005479452054795</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005457343852400876</v>
+        <v>0.005456354852820971</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10290</v>
+        <v>10210</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02533663810346833</v>
+        <v>0.0253494154660002</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5699955217687076</v>
+        <v>0.5822971517140059</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.309111024248148</v>
+        <v>4.306369352395334</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.20263049628127</v>
+        <v>4.19990423502429</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.334246575342465</v>
+        <v>4.331506849315068</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002320664272451601</v>
+        <v>0.002322141735110969</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1696979992903886</v>
+        <v>0.1697922533035322</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.3109219699164345</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.897854951018001</v>
+        <v>2.895053735052019</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.47743858053619</v>
+        <v>2.474844338279973</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.246575342465754</v>
+        <v>3.243835616438356</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003450828343387943</v>
+        <v>0.00345416731956456</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.3289911063932611</v>
+        <v>0.3292347203001829</v>
       </c>
       <c r="AZ25" s="12" t="n">
         <v>0.757246376811594</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.821075392050281</v>
+        <v>2.818168161535952</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.122719541522273</v>
+        <v>2.120143356546932</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.246575342465754</v>
+        <v>3.243835616438356</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003544747520105186</v>
+        <v>0.003548404292009963</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3699,22 +3699,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>75.05960532322062</v>
+        <v>75.77945712158633</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.3966249999999998</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.2712328767123288</v>
+        <v>0.2684931506849315</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.003566056851855931</v>
+        <v>0.003496939946576484</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.2438356164383562</v>
+        <v>0.2410958904109589</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.03686868686868687</v>
+        <v>0.03724489795918368</v>
       </c>
     </row>
     <row r="27">
@@ -3808,22 +3808,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.0493765780147074</v>
+        <v>0.04960478245308372</v>
       </c>
       <c r="AZ27" s="12" t="n">
         <v>0.6281860000000001</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.2657534246575343</v>
+        <v>0.263013698630137</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.2532488624439354</v>
+        <v>0.2505835558555998</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.2438356164383562</v>
+        <v>0.2410958904109589</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.03762886597938144</v>
+        <v>0.03802083333333334</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12420</v>
+        <v>12260</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3938,15 +3938,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-2.934364360215925</v>
+        <v>-2.964327095328991</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.07686346022544299</v>
+        <v>0.09091714323001643</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.2438356164383562</v>
+        <v>0.2410958904109589</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15630</v>
+        <v>14810</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1438345514558626</v>
+        <v>-0.1439966020201371</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.2702975047984646</v>
+        <v>0.3406313301823092</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.66706142844901</v>
+        <v>2.664351442198815</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.115123873527252</v>
+        <v>3.112547740448914</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.742465753424657</v>
+        <v>2.73972602739726</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003749444948411012</v>
+        <v>0.003753258613566113</v>
       </c>
     </row>
     <row r="30">
@@ -4189,22 +4189,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05649379049042826</v>
+        <v>0.05649426882273228</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.6966846951965067</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.615850818628084</v>
+        <v>2.613110986280087</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.475973680274823</v>
+        <v>2.473379234883987</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.742465753424657</v>
+        <v>2.73972602739726</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003822847973128921</v>
+        <v>0.003826856207985093</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.08264613488874688</v>
+        <v>0.08266828635609079</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.524854934844193</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.15956550633508</v>
+        <v>2.156820236599555</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.994710401434165</v>
+        <v>1.992133937772123</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.315068493150685</v>
+        <v>2.312328767123287</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004630561087711869</v>
+        <v>0.004636455013870794</v>
       </c>
     </row>
     <row r="32">
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>66910</v>
+        <v>66540</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4412,22 +4412,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2770449734188666</v>
+        <v>-0.2774706363607922</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1606336870422955</v>
+        <v>0.1670874661857529</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.614042182246498</v>
+        <v>1.611317954272271</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.232562362667746</v>
+        <v>2.230107225201821</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.616438356164384</v>
+        <v>1.613698630136986</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.006195624940905534</v>
+        <v>0.006206099779057174</v>
       </c>
     </row>
     <row r="33">
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>135.5</v>
+        <v>134.5</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.1007091887035282</v>
+        <v>-0.1008412038593555</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.00428782287822882</v>
+        <v>0.01175464684014882</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.649386284989781</v>
+        <v>2.646673479314491</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.946084016104052</v>
+        <v>2.943499513850615</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.742465753424657</v>
+        <v>2.73972602739726</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003774459034779284</v>
+        <v>0.003778327805887894</v>
       </c>
     </row>
     <row r="34">
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03132179246280847</v>
+        <v>0.03130013309046374</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.2223255813953489</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.645148713617739</v>
+        <v>1.642409842656297</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.595184670430656</v>
+        <v>1.592562426744328</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.663013698630137</v>
+        <v>1.66027397260274</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.006078477840468084</v>
+        <v>0.006088614266842698</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>75.8</v>
+        <v>76.7</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>816.6</v>
+        <v>800</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1400371760145125</v>
+        <v>0.1357075970620614</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.5780063678667644</v>
+        <v>0.6298750000000002</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.978029004980288</v>
+        <v>2.980355532760723</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.612220958785978</v>
+        <v>2.62422787385639</v>
       </c>
       <c r="BC2" s="8" t="n">
         <v>3.243835616438356</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003357925655954513</v>
+        <v>0.003355304389049495</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9464</v>
+        <v>9320</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.0218124685743514</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1635339070160606</v>
+        <v>0.1815112549356221</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.721094691293183</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>105.5</v>
+        <v>104.3</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.01793440861466473</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.1964360189573462</v>
+        <v>0.2102013422818794</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.372528961746084</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6697</v>
+        <v>6717</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.04553051219473913</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.441615648797969</v>
+        <v>1.434345690040196</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2684931506849316</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21390</v>
+        <v>21020</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.1181653804295655</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.07115474520804121</v>
+        <v>0.09000951474785923</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.52297958569731</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21390</v>
+        <v>21020</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.05903624809408117</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2802244039270687</v>
+        <v>0.3027592768791627</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.930030332851224</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1962</v>
+        <v>1897</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04387920050119664</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.150133926605505</v>
+        <v>3.292336723247232</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.852054794520548</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>208.4</v>
+        <v>207</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1634654009791623</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.827547984644913</v>
+        <v>2.853434782608695</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.631422428202702</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12490</v>
+        <v>12540</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.009255564465641814</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.444995996797438</v>
+        <v>0.4392344497607656</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.091373901970883</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>104.8</v>
+        <v>104.5</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1118</v>
+        <v>1107</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03638452687817048</v>
+        <v>0.03750649140569062</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4678542969588551</v>
+        <v>0.4781963956639566</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.617558846036101</v>
+        <v>2.617311857182692</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.525663764896985</v>
+        <v>2.522694439855084</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.73972602739726</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003820353462212892</v>
+        <v>0.003820713978946371</v>
       </c>
     </row>
     <row r="12">
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>215.3</v>
+        <v>214.6</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2211,7 +2211,7 @@
         <v>-0.1232724835778101</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.01021830004644686</v>
+        <v>0.0135135135135136</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.210047680727201</v>
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>244.3</v>
+        <v>241.1</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1930232186689829</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.02986215718379048</v>
+        <v>0.04353100373289087</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.13677584888771</v>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>115.1</v>
+        <v>113</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18300</v>
+        <v>18430</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.05415552735808606</v>
+        <v>-0.04415491353501048</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1800479693989072</v>
+        <v>0.1503461313076506</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.741834379846844</v>
+        <v>1.741601394236764</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.841565320968243</v>
+        <v>1.822054032497823</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.73972602739726</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005741073959557095</v>
+        <v>0.00574184198123152</v>
       </c>
     </row>
     <row r="17">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>89</v>
+        <v>89.2</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2781,7 +2781,7 @@
         <v>4.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>118.8</v>
+        <v>110.9</v>
       </c>
       <c r="AK18" s="10" t="n">
         <v>46924</v>
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1227341744449786</v>
+        <v>0.1212836725077084</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>2.146464646464647</v>
+        <v>2.378178539224527</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.713633316868852</v>
+        <v>1.713695559577245</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.526303693139102</v>
+        <v>1.528333642587187</v>
       </c>
       <c r="BC18" s="8" t="n">
         <v>1.73972602739726</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005835554141928091</v>
+        <v>0.005835342190223636</v>
       </c>
     </row>
     <row r="19">
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>107.4</v>
+        <v>105.9</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>149.9</v>
+        <v>149</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.02469124128198948</v>
+        <v>0.02912501192626959</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.504603068712475</v>
+        <v>0.4925503355704699</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.178088812873074</v>
+        <v>3.175798821799795</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.101508712904554</v>
+        <v>3.08592132636586</v>
       </c>
       <c r="BC19" s="8" t="n">
         <v>3.405479452054795</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003146545168748681</v>
+        <v>0.003148814065726235</v>
       </c>
     </row>
     <row r="20">
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>29270</v>
+        <v>29160</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5884841754585874</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.01080267611889307</v>
+        <v>0.01461571776406023</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.419052624281306</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>448</v>
+        <v>444.3</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03836225503731567</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.4970579196428571</v>
+        <v>0.5095249786180507</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7671232876712328</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103.9</v>
+        <v>100.5</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>213.2</v>
+        <v>213.9</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.049221363068206</v>
+        <v>0.06724595119551441</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1208724202626643</v>
+        <v>0.08064516129032251</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.832725376141901</v>
+        <v>1.827931870540202</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.746748055894057</v>
+        <v>1.712755966412969</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>2.005479452054795</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005456354852820971</v>
+        <v>0.005470663409924976</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10210</v>
+        <v>10150</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.0253494154660002</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5822971517140059</v>
+        <v>0.5916506324137931</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.306369352395334</v>
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>35.9</v>
+        <v>36.3</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3480,7 +3480,7 @@
         <v>0.1697922533035322</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.3109219699164345</v>
+        <v>0.2964765487603305</v>
       </c>
       <c r="BA24" s="8" t="n">
         <v>2.895053735052019</v>
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>48.5</v>
+        <v>47.1</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>27.6</v>
+        <v>28.3</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.3292347203001829</v>
+        <v>0.3421507099908909</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.757246376811594</v>
+        <v>0.6643109540636043</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.818168161535952</v>
+        <v>2.809251874581975</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.120143356546932</v>
+        <v>2.093097186232566</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.243835616438356</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003548404292009963</v>
+        <v>0.003559666575460782</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1136</v>
+        <v>1171</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.04960478245308372</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.6281860000000001</v>
+        <v>0.5795211750640479</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.263013698630137</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12260</v>
+        <v>12120</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-2.964327095328991</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.09091714323001643</v>
+        <v>0.1035184963696372</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14810</v>
+        <v>14680</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.1439966020201371</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.3406313301823092</v>
+        <v>0.3525034059945504</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.664351442198815</v>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>99.59999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="F30" t="n">
         <v>0.1</v>
@@ -4189,22 +4189,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05649426882273228</v>
+        <v>0.05729694668427102</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.6966846951965067</v>
+        <v>0.693277697816594</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.613110986280087</v>
+        <v>2.61293253742495</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.473379234883987</v>
+        <v>2.471332718418623</v>
       </c>
       <c r="BC30" s="8" t="n">
         <v>2.73972602739726</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003826856207985093</v>
+        <v>0.003827117561119669</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>66540</v>
+        <v>66400</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2774706363607922</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1670874661857529</v>
+        <v>0.1695481927710842</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.611317954272271</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>800</v>
+        <v>815.6</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.1357075970620614</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.6298750000000002</v>
+        <v>0.598700343305542</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>2.980355532760723</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>112.8</v>
+        <v>112.7</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9320</v>
+        <v>9343</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.0218124685743514</v>
+        <v>-0.02131331429938522</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1815112549356221</v>
+        <v>0.1775578255378358</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.721094691293183</v>
+        <v>1.721073558341606</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.759473143953075</v>
+        <v>1.758554176211703</v>
       </c>
       <c r="BC3" s="8" t="n">
         <v>1.73972602739726</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005810255560364476</v>
+        <v>0.005810326904118968</v>
       </c>
     </row>
     <row r="4">
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>104.3</v>
+        <v>103.3</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.01793440861466473</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2102013422818794</v>
+        <v>0.2219167473378512</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.372528961746084</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6717</v>
+        <v>6605</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.04553051219473913</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.434345690040196</v>
+        <v>1.47562452687358</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2684931506849316</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>286.4</v>
+        <v>270</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21020</v>
+        <v>20790</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1181653804295655</v>
+        <v>-0.1101563064797458</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.09000951474785923</v>
+        <v>0.03896103896103886</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.52297958569731</v>
+        <v>6.509166152122161</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.397055457943837</v>
+        <v>7.314954524621803</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.915068493150685</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001533041743979488</v>
+        <v>0.001536295090076896</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21020</v>
+        <v>20790</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.05903624809408117</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.3027592768791627</v>
+        <v>0.3171717171717172</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.930030332851224</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1897</v>
+        <v>1905</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04387920050119664</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.292336723247232</v>
+        <v>3.274311162204724</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.852054794520548</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>207</v>
+        <v>210.9</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1634654009791623</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.853434782608695</v>
+        <v>2.782176386913229</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.631422428202702</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>112.8</v>
+        <v>112</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12540</v>
+        <v>12580</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.009255564465641814</v>
+        <v>-0.007552543206172349</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4392344497607656</v>
+        <v>0.4244833068362479</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.091373901970883</v>
+        <v>4.090515829951887</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.129595640639859</v>
+        <v>4.121644729854606</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.249315068493151</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002444166737042252</v>
+        <v>0.002444679452595499</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1107</v>
+        <v>1112</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03750649140569062</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4781963956639566</v>
+        <v>0.4715498291366906</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.617311857182692</v>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>217.5</v>
+        <v>215</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>214.6</v>
+        <v>213.5</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1232724835778101</v>
+        <v>-0.1208903164583938</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.0135135135135136</v>
+        <v>0.007025761124121788</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.210047680727201</v>
+        <v>4.207905604314668</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.802002448728715</v>
+        <v>4.786553581531011</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.49041095890411</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002375270010783512</v>
+        <v>0.002376479165727074</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>241.1</v>
+        <v>240.8</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1930232186689829</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.04353100373289087</v>
+        <v>0.04483108388704315</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.13677584888771</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>77.8</v>
+        <v>76.7</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2429,7 +2429,7 @@
         <v>-0.1702581714871968</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1530462724935735</v>
+        <v>0.1695827900912648</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.887858495314273</v>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>113</v>
+        <v>114.2</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18430</v>
+        <v>18440</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.04415491353501048</v>
+        <v>-0.04990498538145642</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1503461313076506</v>
+        <v>0.1619317396963125</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.741601394236764</v>
+        <v>1.741735340840344</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.822054032497823</v>
+        <v>1.833222271500538</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.73972602739726</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.00574184198123152</v>
+        <v>0.005741400409992973</v>
       </c>
     </row>
     <row r="17">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>97.5</v>
+        <v>97</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05852798419805328</v>
+        <v>0.06028566501993001</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8429878048780488</v>
+        <v>0.8335365853658536</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.987038023274248</v>
+        <v>2.986063642468323</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.821879126357953</v>
+        <v>2.816282197319149</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.243835616438356</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003347798026701542</v>
+        <v>0.003348890444857986</v>
       </c>
     </row>
     <row r="18">
@@ -2781,7 +2781,7 @@
         <v>4.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>110.9</v>
+        <v>110.8</v>
       </c>
       <c r="AK18" s="10" t="n">
         <v>46924</v>
@@ -2798,7 +2798,7 @@
         <v>0.1212836725077084</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>2.378178539224527</v>
+        <v>2.381227436823105</v>
       </c>
       <c r="BA18" s="8" t="n">
         <v>1.713695559577245</v>
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>149</v>
+        <v>145.8</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.02912501192626959</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4925503355704699</v>
+        <v>0.5253086419753086</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.175798821799795</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>29160</v>
+        <v>29090</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5884841754585874</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.01461571776406023</v>
+        <v>0.01705721313166042</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.419052624281306</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>444.3</v>
+        <v>445</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03836225503731567</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5095249786180507</v>
+        <v>0.50715044494382</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7671232876712328</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100.5</v>
+        <v>100.7</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>213.9</v>
+        <v>217.2</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.06724595119551441</v>
+        <v>0.06616000311822659</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.08064516129032251</v>
+        <v>0.06634438305709023</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.827931870540202</v>
+        <v>1.82822170139949</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.712755966412969</v>
+        <v>1.7147723569187</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>2.005479452054795</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005470663409924976</v>
+        <v>0.005469796137057706</v>
       </c>
     </row>
     <row r="23">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>91.7</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10150</v>
+        <v>9997</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.0253494154660002</v>
+        <v>0.02560833731394956</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5916506324137931</v>
+        <v>0.6142479155746723</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.306369352395334</v>
+        <v>4.306329910218397</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.19990423502429</v>
+        <v>4.198805483091723</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.331506849315068</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002322141735110969</v>
+        <v>0.002322163003877436</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>72.8</v>
+        <v>75</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1697922533035322</v>
+        <v>0.1584533969685273</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.2964765487603305</v>
+        <v>0.335655785123967</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.895053735052019</v>
+        <v>2.902418167623167</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.474844338279973</v>
+        <v>2.50542505656101</v>
       </c>
       <c r="BC24" s="8" t="n">
         <v>3.243835616438356</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.00345416731956456</v>
+        <v>0.003445402909736176</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>47.1</v>
+        <v>48</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>28.3</v>
+        <v>28</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.3421507099908909</v>
+        <v>0.3337883949781607</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.6643109540636043</v>
+        <v>0.7142857142857142</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.809251874581975</v>
+        <v>2.815032557517294</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.093097186232566</v>
+        <v>2.110554093974844</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.243835616438356</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003559666575460782</v>
+        <v>0.003552356782977835</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1171</v>
+        <v>1142</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.04960478245308372</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5795211750640479</v>
+        <v>0.6196316077057793</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.263013698630137</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12120</v>
+        <v>12090</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-2.964327095328991</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.1035184963696372</v>
+        <v>0.1062567556658396</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14680</v>
+        <v>14530</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.1439966020201371</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.3525034059945504</v>
+        <v>0.3664659325533379</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.664351442198815</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>66400</v>
+        <v>65200</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2774706363607922</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1695481927710842</v>
+        <v>0.1910736196319018</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.611317954272271</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>134.5</v>
+        <v>133</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4524,7 +4524,7 @@
         <v>-0.1008412038593555</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.01175464684014882</v>
+        <v>0.02316541353383461</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.646673479314491</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04387920050119664</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.274311162204724</v>
+        <v>3.285559349473684</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.852054794520548</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1112</v>
+        <v>1108</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03750649140569062</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4715498291366906</v>
+        <v>0.4768622833935017</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.617311857182692</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18440</v>
+        <v>18470</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2538,7 +2538,7 @@
         <v>-0.04990498538145642</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1619317396963125</v>
+        <v>0.1600444656199242</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.741735340840344</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>445</v>
+        <v>446.8</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03836225503731567</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.50715044494382</v>
+        <v>0.5010786660698296</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7671232876712328</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9997</v>
+        <v>10010</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.02560833731394956</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.6142479155746723</v>
+        <v>0.6121514897102898</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.306329910218397</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12090</v>
+        <v>12080</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-2.964327095328991</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.1062567556658396</v>
+        <v>0.107172531125828</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14530</v>
+        <v>14540</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.1439966020201371</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.3664659325533379</v>
+        <v>0.3655261348005503</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.664351442198815</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>65200</v>
+        <v>65110</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2774706363607922</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1910736196319018</v>
+        <v>0.1927200122868991</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.611317954272271</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>76.7</v>
+        <v>76.3</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>815.6</v>
+        <v>797.7</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1357075970620614</v>
+        <v>0.1376233484363588</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.598700343305542</v>
+        <v>0.6260498934436503</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.980355532760723</v>
+        <v>2.97932725976242</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.62422787385639</v>
+        <v>2.618904810504678</v>
       </c>
       <c r="BC2" s="8" t="n">
         <v>3.243835616438356</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003355304389049495</v>
+        <v>0.003356462425278326</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>112.7</v>
+        <v>110.7</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9343</v>
+        <v>9299</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.02131331429938522</v>
+        <v>-0.01118109766723456</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1775578255378358</v>
+        <v>0.1621335760834499</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.721073558341606</v>
+        <v>1.720644787197781</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.758554176211703</v>
+        <v>1.740101026728487</v>
       </c>
       <c r="BC3" s="8" t="n">
         <v>1.73972602739726</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005810326904118968</v>
+        <v>0.005811774791870825</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112.7</v>
+        <v>111.9</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>103.3</v>
+        <v>104.7</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01793440861466473</v>
+        <v>0.01957863211708709</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2219167473378512</v>
+        <v>0.1970200573065903</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.372528961746084</v>
+        <v>4.370864796816688</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.295491855606669</v>
+        <v>4.286932522056567</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.739726027397261</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002287006006703886</v>
+        <v>0.002287876762347585</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6605</v>
+        <v>6550</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.04553051219473913</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.47562452687358</v>
+        <v>1.496412213740458</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2684931506849316</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>270</v>
+        <v>269.2</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>20790</v>
+        <v>20990</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1101563064797458</v>
+        <v>-0.1097509141830052</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.03896103896103886</v>
+        <v>0.02601238685088147</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.509166152122161</v>
+        <v>6.508457385142227</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.314954524621803</v>
+        <v>7.310827372733912</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.915068493150685</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001536295090076896</v>
+        <v>0.001536462391661104</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>20790</v>
+        <v>20990</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.05903624809408117</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.3171717171717172</v>
+        <v>0.3046212482134349</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.930030332851224</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1900</v>
+        <v>1930</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04387920050119664</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.285559349473684</v>
+        <v>3.218944437305699</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.852054794520548</v>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>83.7</v>
+        <v>84</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>210.9</v>
+        <v>202.3</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1634654009791623</v>
+        <v>0.1609600815900223</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.782176386913229</v>
+        <v>2.957093425605536</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.631422428202702</v>
+        <v>1.631520894405022</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.402209663329663</v>
+        <v>1.40532040702944</v>
       </c>
       <c r="BC9" s="8" t="n">
         <v>1.66027397260274</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006129620279290112</v>
+        <v>0.006129250341992565</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12580</v>
+        <v>12360</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.007552543206172349</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4244833068362479</v>
+        <v>0.4498381877022655</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.090515829951887</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1108</v>
+        <v>1122</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03750649140569062</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4768622833935017</v>
+        <v>0.4584344117647059</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.617311857182692</v>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>215</v>
+        <v>215.2</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>213.5</v>
+        <v>213.1</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1208903164583938</v>
+        <v>-0.1210821782613975</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.007025761124121788</v>
+        <v>0.009854528390426998</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.207905604314668</v>
+        <v>4.208078487596199</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.786553581531011</v>
+        <v>4.787795153899743</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.49041095890411</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002376479165727074</v>
+        <v>0.002376381531256169</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>240.8</v>
+        <v>243.3</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1930232186689829</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.04483108388704315</v>
+        <v>0.03409504726674872</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.13677584888771</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>164.6</v>
+        <v>162.9</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>76.7</v>
+        <v>76.8</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1702581714871968</v>
+        <v>-0.1658660615107237</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1695827900912648</v>
+        <v>0.15599609375</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.887858495314273</v>
+        <v>1.886819490571545</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.2752360197364</v>
+        <v>2.262010216235558</v>
       </c>
       <c r="BC15" s="8" t="n">
         <v>2.005479452054795</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005297007177614386</v>
+        <v>0.005299924052072863</v>
       </c>
     </row>
     <row r="16">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>114.2</v>
+        <v>114</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18470</v>
+        <v>18410</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.04990498538145642</v>
+        <v>-0.04895325649035974</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1600444656199242</v>
+        <v>0.1617869418794136</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.741735340840344</v>
+        <v>1.74171316799849</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.833222271500538</v>
+        <v>1.831364420187235</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.73972602739726</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005741400409992973</v>
+        <v>0.005741473500766842</v>
       </c>
     </row>
     <row r="17">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>97</v>
+        <v>96.8</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>82</v>
+        <v>80.3</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.06028566501993001</v>
+        <v>0.0609921655884802</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8335365853658536</v>
+        <v>0.8684931506849314</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.986063642468323</v>
+        <v>2.985671506849072</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.816282197319149</v>
+        <v>2.814037279147171</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.243835616438356</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003348890444857986</v>
+        <v>0.003349330285351284</v>
       </c>
     </row>
     <row r="18">
@@ -2781,7 +2781,7 @@
         <v>4.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>110.8</v>
+        <v>111.5</v>
       </c>
       <c r="AK18" s="10" t="n">
         <v>46924</v>
@@ -2798,7 +2798,7 @@
         <v>0.1212836725077084</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>2.381227436823105</v>
+        <v>2.36</v>
       </c>
       <c r="BA18" s="8" t="n">
         <v>1.713695559577245</v>
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>145.8</v>
+        <v>146.7</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.02912501192626959</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5253086419753086</v>
+        <v>0.5159509202453989</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.175798821799795</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>29090</v>
+        <v>29190</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5884841754585874</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.01705721313166042</v>
+        <v>0.01357294724220615</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.419052624281306</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>446.8</v>
+        <v>446</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03836225503731567</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5010786660698296</v>
+        <v>0.503771183856502</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7671232876712328</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100.7</v>
+        <v>100.5</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>217.2</v>
+        <v>217.7</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.06616000311822659</v>
+        <v>0.06724595119551441</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.06634438305709023</v>
+        <v>0.06178226917776741</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.82822170139949</v>
+        <v>1.827931870540202</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.7147723569187</v>
+        <v>1.712755966412969</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>2.005479452054795</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005469796137057706</v>
+        <v>0.005470663409924976</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10010</v>
+        <v>10130</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.02560833731394956</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.6121514897102898</v>
+        <v>0.5930539399802566</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.306329910218397</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>75</v>
+        <v>73.8</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>36.3</v>
+        <v>35</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1584533969685273</v>
+        <v>0.1645812185632962</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.335655785123967</v>
+        <v>0.3631016034285715</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.902418167623167</v>
+        <v>2.898446479073364</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.50542505656101</v>
+        <v>2.488831549807302</v>
       </c>
       <c r="BC24" s="8" t="n">
         <v>3.243835616438356</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003445402909736176</v>
+        <v>0.003450124082745529</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.3337883949781607</v>
+        <v>0.3430933399075932</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.7142857142857142</v>
+        <v>0.6845878136200718</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.815032557517294</v>
+        <v>2.808598441344661</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.110554093974844</v>
+        <v>2.091141663719289</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.243835616438356</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003552356782977835</v>
+        <v>0.003560494748125097</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1142</v>
+        <v>1159</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.04960478245308372</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.6196316077057793</v>
+        <v>0.5958751475409836</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.263013698630137</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12080</v>
+        <v>12190</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-2.964327095328991</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.107172531125828</v>
+        <v>0.09718163872026264</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>172.5</v>
+        <v>169.6</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14540</v>
+        <v>14750</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1439966020201371</v>
+        <v>-0.1385681316057813</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.3655261348005503</v>
+        <v>0.3234549152542372</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.664351442198815</v>
+        <v>2.663353431885384</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.112547740448914</v>
+        <v>3.091774903626561</v>
       </c>
       <c r="BC29" s="8" t="n">
         <v>2.73972602739726</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003753258613566113</v>
+        <v>0.003754665032541706</v>
       </c>
     </row>
     <row r="30">
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>572.5</v>
+        <v>566</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4192,7 +4192,7 @@
         <v>0.05729694668427102</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.693277697816594</v>
+        <v>0.7127234664310955</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.61293253742495</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>65110</v>
+        <v>65430</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2774706363607922</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1927200122868991</v>
+        <v>0.1868867491976158</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.611317954272271</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>133</v>
+        <v>132.7</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4524,7 +4524,7 @@
         <v>-0.1008412038593555</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.02316541353383461</v>
+        <v>0.02547852298417497</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.646673479314491</v>
@@ -4616,7 +4616,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1505</v>
+        <v>1498</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4633,7 +4633,7 @@
         <v>0.03130013309046374</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2223255813953489</v>
+        <v>0.2280373831775702</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.642409842656297</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1376233484363588</v>
+        <v>0.1377016956509146</v>
       </c>
       <c r="AZ2" s="12" t="n">
         <v>0.6260498934436503</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.97932725976242</v>
+        <v>2.976545441634378</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.618904810504678</v>
+        <v>2.616279340193304</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.243835616438356</v>
+        <v>3.241095890410959</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003356462425278326</v>
+        <v>0.00335959930600258</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.01118109766723456</v>
+        <v>-0.01126720604610834</v>
       </c>
       <c r="AZ3" s="12" t="n">
         <v>0.1621335760834499</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.720644787197781</v>
+        <v>1.717908703451513</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.740101026728487</v>
+        <v>1.737485308423608</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.73972602739726</v>
+        <v>1.736986301369863</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005811774791870825</v>
+        <v>0.005821031105965432</v>
       </c>
     </row>
     <row r="4">
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01957863211708709</v>
+        <v>0.01956499700186828</v>
       </c>
       <c r="AZ4" s="12" t="n">
         <v>0.1970200573065903</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.370864796816688</v>
+        <v>4.368138889050017</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.286932522056567</v>
+        <v>4.284316254378054</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.739726027397261</v>
+        <v>4.736986301369863</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002287876762347585</v>
+        <v>0.002289304496491136</v>
       </c>
     </row>
     <row r="5">
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.04553051219473913</v>
+        <v>0.04587465157585103</v>
       </c>
       <c r="AZ5" s="12" t="n">
         <v>1.496412213740458</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.2684931506849316</v>
+        <v>0.2657534246575342</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.256800875300445</v>
+        <v>0.2540968215044848</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.2410958904109589</v>
+        <v>0.2383561643835616</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.03724489795918366</v>
+        <v>0.03762886597938145</v>
       </c>
     </row>
     <row r="6">
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1097509141830052</v>
+        <v>-0.1098000622830434</v>
       </c>
       <c r="AZ6" s="12" t="n">
         <v>0.02601238685088147</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.508457385142227</v>
+        <v>6.505803636502104</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.310827372733912</v>
+        <v>7.308249934489049</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>6.915068493150685</v>
+        <v>6.912328767123288</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001536462391661104</v>
+        <v>0.001537089122071409</v>
       </c>
     </row>
     <row r="7">
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05903624809408117</v>
+        <v>-0.05912642753237234</v>
       </c>
       <c r="AZ7" s="12" t="n">
         <v>0.3046212482134349</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.930030332851224</v>
+        <v>1.927291268828469</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.051120809852616</v>
+        <v>2.048406210171006</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>1.912328767123288</v>
+        <v>1.90958904109589</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005181265718879688</v>
+        <v>0.005188629327459487</v>
       </c>
     </row>
     <row r="8">
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04387920050119664</v>
+        <v>0.04401208920072403</v>
       </c>
       <c r="AZ8" s="12" t="n">
         <v>3.218944437305699</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.852054794520548</v>
+        <v>0.8493150684931506</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.816238884835958</v>
+        <v>0.8135107603431778</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.8246575342465754</v>
+        <v>0.821917808219178</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01173633440514469</v>
+        <v>0.0117741935483871</v>
       </c>
     </row>
     <row r="9">
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1609600815900223</v>
+        <v>0.1611479670535086</v>
       </c>
       <c r="AZ9" s="12" t="n">
         <v>2.957093425605536</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.631520894405022</v>
+        <v>1.628773783236158</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.40532040702944</v>
+        <v>1.402727154032989</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.66027397260274</v>
+        <v>1.657534246575342</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006129250341992565</v>
+        <v>0.00613958801579635</v>
       </c>
     </row>
     <row r="10">
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.007552543206172349</v>
+        <v>-0.007569310237581273</v>
       </c>
       <c r="AZ10" s="3" t="n">
         <v>0.4498381877022655</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.090515829951887</v>
+        <v>4.08778456636398</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.121644729854606</v>
+        <v>4.118962269639775</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.249315068493151</v>
+        <v>4.246575342465754</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002444679452595499</v>
+        <v>0.002446312871349491</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03750649140569062</v>
+        <v>0.03748999878289148</v>
       </c>
       <c r="AZ11" s="12" t="n">
         <v>0.4584344117647059</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.617311857182692</v>
+        <v>2.614575762839826</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.522694439855084</v>
+        <v>2.520097317474923</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.73972602739726</v>
+        <v>2.736986301369863</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003820713978946371</v>
+        <v>0.003824712269625908</v>
       </c>
     </row>
     <row r="12">
@@ -2111,7 +2111,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>-0.08493150684931507</v>
+        <v>-0.08767123287671233</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1210821782613975</v>
+        <v>-0.1211705312265202</v>
       </c>
       <c r="AZ13" s="12" t="n">
         <v>0.009854528390426998</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.208078487596199</v>
+        <v>4.20541835373513</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.787795153899743</v>
+        <v>4.785249588414843</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.49041095890411</v>
+        <v>4.487671232876712</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002376381531256169</v>
+        <v>0.002377884709405496</v>
       </c>
     </row>
     <row r="14">
@@ -2317,22 +2317,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1930232186689829</v>
+        <v>-0.1931869971280061</v>
       </c>
       <c r="AZ14" s="12" t="n">
         <v>0.03409504726674872</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.13677584888771</v>
+        <v>3.134091640926714</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.88707075774095</v>
+        <v>3.88453288403925</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.243835616438356</v>
+        <v>3.241095890410959</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003187986799740876</v>
+        <v>0.003190717166471596</v>
       </c>
     </row>
     <row r="15">
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1658660615107237</v>
+        <v>-0.1661360069706402</v>
       </c>
       <c r="AZ15" s="12" t="n">
         <v>0.15599609375</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.886819490571545</v>
+        <v>1.884143705181358</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.262010216235558</v>
+        <v>2.259533594125366</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.005479452054795</v>
+        <v>2.002739726027397</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005299924052072863</v>
+        <v>0.005307450791837267</v>
       </c>
     </row>
     <row r="16">
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.04895325649035974</v>
+        <v>-0.04906114493128649</v>
       </c>
       <c r="AZ16" s="12" t="n">
         <v>0.1617869418794136</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.74171316799849</v>
+        <v>1.738975955444459</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.831364420187235</v>
+        <v>1.82869376529872</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.73972602739726</v>
+        <v>1.736986301369863</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005741473500766842</v>
+        <v>0.005750510792683233</v>
       </c>
     </row>
     <row r="17">
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.0609921655884802</v>
+        <v>0.06100136049868643</v>
       </c>
       <c r="AZ17" s="12" t="n">
         <v>0.8684931506849314</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.985671506849072</v>
+        <v>2.982926675460489</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.814037279147171</v>
+        <v>2.811425872308466</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.243835616438356</v>
+        <v>3.241095890410959</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003349330285351284</v>
+        <v>0.0033524122742495</v>
       </c>
     </row>
     <row r="18">
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1212836725077084</v>
+        <v>0.121389890473591</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>2.36</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.713695559577245</v>
+        <v>1.710951275337642</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.528333642587187</v>
+        <v>1.525741662086024</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.73972602739726</v>
+        <v>1.736986301369863</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005835342190223636</v>
+        <v>0.005844701800772547</v>
       </c>
     </row>
     <row r="19">
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.02912501192626959</v>
+        <v>0.02911166182993484</v>
       </c>
       <c r="AZ19" s="12" t="n">
         <v>0.5159509202453989</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.175798821799795</v>
+        <v>3.173066007312716</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.08592132636586</v>
+        <v>3.083305850086732</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.405479452054795</v>
+        <v>3.402739726027397</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003148814065726235</v>
+        <v>0.003151525993141581</v>
       </c>
     </row>
     <row r="20">
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5884841754585874</v>
+        <v>-0.5891963855580248</v>
       </c>
       <c r="AZ20" s="12" t="n">
         <v>0.01357294724220615</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.419052624281306</v>
+        <v>1.416331869675058</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.448354934740792</v>
+        <v>3.447710341105362</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.402739726027397</v>
+        <v>1.4</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.00704695500990642</v>
+        <v>0.007060492116366944</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3124,22 +3124,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03836225503731567</v>
+        <v>0.03836778014608579</v>
       </c>
       <c r="AZ21" s="12" t="n">
         <v>0.503771183856502</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.7671232876712328</v>
+        <v>0.7643835616438355</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.7387819462328825</v>
+        <v>0.736139522295555</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.7397260273972602</v>
+        <v>0.736986301369863</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01303571428571429</v>
+        <v>0.01308243727598567</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.06724595119551441</v>
+        <v>0.06724577429750611</v>
       </c>
       <c r="AZ22" s="12" t="n">
         <v>0.06178226917776741</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.827931870540202</v>
+        <v>1.825192191736148</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.712755966412969</v>
+        <v>1.710189195115385</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.005479452054795</v>
+        <v>2.002739726027397</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005470663409924976</v>
+        <v>0.005478875071500204</v>
       </c>
     </row>
     <row r="23">
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02560833731394956</v>
+        <v>0.02562129550770047</v>
       </c>
       <c r="AZ23" s="12" t="n">
         <v>0.5930539399802566</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.306329910218397</v>
+        <v>4.30358820964963</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.198805483091723</v>
+        <v>4.196079223880856</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.331506849315068</v>
+        <v>4.328767123287672</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002322163003877436</v>
+        <v>0.002323642391615841</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1645812185632962</v>
+        <v>0.1646712390671095</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.3631016034285715</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.898446479073364</v>
+        <v>2.895648262275223</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.488831549807302</v>
+        <v>2.486236600634708</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.243835616438356</v>
+        <v>3.241095890410959</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003450124082745529</v>
+        <v>0.003453458118612311</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.3430933399075932</v>
+        <v>0.343350790544454</v>
       </c>
       <c r="AZ25" s="12" t="n">
         <v>0.6845878136200718</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.808598441344661</v>
+        <v>2.805680186352576</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.091141663719289</v>
+        <v>2.088568530350473</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.243835616438356</v>
+        <v>3.241095890410959</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003560494748125097</v>
+        <v>0.00356419810377609</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3699,22 +3699,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>75.77945712158633</v>
+        <v>76.51420508781978</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.3966249999999998</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.2684931506849315</v>
+        <v>0.2657534246575343</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.003496939946576484</v>
+        <v>0.003428448041961454</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.2410958904109589</v>
+        <v>0.2383561643835616</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.03724489795918368</v>
+        <v>0.03762886597938144</v>
       </c>
     </row>
     <row r="27">
@@ -3808,22 +3808,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.04960478245308372</v>
+        <v>0.04983783414943407</v>
       </c>
       <c r="AZ27" s="12" t="n">
         <v>0.5958751475409836</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.263013698630137</v>
+        <v>0.2602739726027397</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.2505835558555998</v>
+        <v>0.2479182633131245</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.2410958904109589</v>
+        <v>0.2383561643835616</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.03802083333333334</v>
+        <v>0.03842105263157895</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3938,7 +3938,7 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-2.964327095328991</v>
+        <v>-2.994907617705857</v>
       </c>
       <c r="AZ28" s="12" t="n">
         <v>0.09718163872026264</v>
@@ -3946,7 +3946,7 @@
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.2410958904109589</v>
+        <v>0.2383561643835616</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1385681316057813</v>
+        <v>-0.1387263991691636</v>
       </c>
       <c r="AZ29" s="12" t="n">
         <v>0.3234549152542372</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.663353431885384</v>
+        <v>2.660642854482149</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.091774903626561</v>
+        <v>3.089195874476511</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.73972602739726</v>
+        <v>2.736986301369863</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003754665032541706</v>
+        <v>0.003758490164568268</v>
       </c>
     </row>
     <row r="30">
@@ -4189,22 +4189,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05729694668427102</v>
+        <v>0.05729815811524917</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.7127234664310955</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.61293253742495</v>
+        <v>2.61019254202337</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.471332718418623</v>
+        <v>2.468738379981979</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.73972602739726</v>
+        <v>2.736986301369863</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003827117561119669</v>
+        <v>0.003831134998281849</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.08266828635609079</v>
+        <v>0.08269050979829519</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.524854934844193</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.156820236599555</v>
+        <v>2.154074948798058</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.992133937772123</v>
+        <v>1.989557430589616</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.312328767123287</v>
+        <v>2.309589041095891</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004636455013870794</v>
+        <v>0.004642364002041736</v>
       </c>
     </row>
     <row r="32">
@@ -4412,22 +4412,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2774706363607922</v>
+        <v>-0.2778974916370439</v>
       </c>
       <c r="AZ32" s="12" t="n">
         <v>0.1868867491976158</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.611317954272271</v>
+        <v>1.608593770205821</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.230107225201821</v>
+        <v>2.227652932341402</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.613698630136986</v>
+        <v>1.610958904109589</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.006206099779057174</v>
+        <v>0.006216609926768827</v>
       </c>
     </row>
     <row r="33">
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.1008412038593555</v>
+        <v>-0.1009734685772185</v>
       </c>
       <c r="AZ33" s="12" t="n">
         <v>0.02547852298417497</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.646673479314491</v>
+        <v>2.643960722339263</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.943499513850615</v>
+        <v>2.940915123110976</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.73972602739726</v>
+        <v>2.736986301369863</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003778327805887894</v>
+        <v>0.00378220444634761</v>
       </c>
     </row>
     <row r="34">
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03130013309046374</v>
+        <v>0.03127841070938566</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.2280373831775702</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.642409842656297</v>
+        <v>1.63967097418384</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.592562426744328</v>
+        <v>1.589940172466094</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.66027397260274</v>
+        <v>1.657534246575342</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.006088614266842698</v>
+        <v>0.00609878454729467</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1377016956509146</v>
+        <v>0.1378588684213147</v>
       </c>
       <c r="AZ2" s="12" t="n">
         <v>0.6260498934436503</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.976545441634378</v>
+        <v>2.970981539033887</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.616279340193304</v>
+        <v>2.61102815251234</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.241095890410959</v>
+        <v>3.235616438356165</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.00335959930600258</v>
+        <v>0.003365890992123711</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.01126720604610834</v>
+        <v>-0.01144020173049566</v>
       </c>
       <c r="AZ3" s="12" t="n">
         <v>0.1621335760834499</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.717908703451513</v>
+        <v>1.712436568990507</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.737485308423608</v>
+        <v>1.732253903090298</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.736986301369863</v>
+        <v>1.731506849315068</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005821031105965432</v>
+        <v>0.005839632358409088</v>
       </c>
     </row>
     <row r="4">
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01956499700186828</v>
+        <v>0.0195376847938483</v>
       </c>
       <c r="AZ4" s="12" t="n">
         <v>0.1970200573065903</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.368138889050017</v>
+        <v>4.362687115164009</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.284316254378054</v>
+        <v>4.279083726116657</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.736986301369863</v>
+        <v>4.731506849315068</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002289304496491136</v>
+        <v>0.002292165295384486</v>
       </c>
     </row>
     <row r="5">
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.04587465157585103</v>
+        <v>0.04658469068645121</v>
       </c>
       <c r="AZ5" s="12" t="n">
         <v>1.496412213740458</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.2657534246575342</v>
+        <v>0.2602739726027397</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.2540968215044848</v>
+        <v>0.2486888781375418</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.2383561643835616</v>
+        <v>0.2328767123287671</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.03762886597938145</v>
+        <v>0.03842105263157895</v>
       </c>
     </row>
     <row r="6">
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1098000622830434</v>
+        <v>-0.1098984719821578</v>
       </c>
       <c r="AZ6" s="12" t="n">
         <v>0.02601238685088147</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.505803636502104</v>
+        <v>6.500496296808379</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.308249934489049</v>
+        <v>7.303095312378877</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>6.912328767123288</v>
+        <v>6.906849315068493</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001537089122071409</v>
+        <v>0.001538344080729623</v>
       </c>
     </row>
     <row r="7">
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05912642753237234</v>
+        <v>-0.05930753108382617</v>
       </c>
       <c r="AZ7" s="12" t="n">
         <v>0.3046212482134349</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.927291268828469</v>
+        <v>1.921813146252262</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.048406210171006</v>
+        <v>2.042977072482034</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>1.90958904109589</v>
+        <v>1.904109589041096</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005188629327459487</v>
+        <v>0.005203419499705814</v>
       </c>
     </row>
     <row r="8">
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04401208920072403</v>
+        <v>0.04428045571121422</v>
       </c>
       <c r="AZ8" s="12" t="n">
         <v>3.218944437305699</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.8493150684931506</v>
+        <v>0.8438356164383563</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.8135107603431778</v>
+        <v>0.8080545909131818</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.821917808219178</v>
+        <v>0.8164383561643835</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.0117741935483871</v>
+        <v>0.01185064935064935</v>
       </c>
     </row>
     <row r="9">
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1611479670535086</v>
+        <v>0.1615257805128324</v>
       </c>
       <c r="AZ9" s="12" t="n">
         <v>2.957093425605536</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.628773783236158</v>
+        <v>1.62327948096023</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.402727154032989</v>
+        <v>1.397540638524206</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.657534246575342</v>
+        <v>1.652054794520548</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.00613958801579635</v>
+        <v>0.006160368634786553</v>
       </c>
     </row>
     <row r="10">
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.007569310237581273</v>
+        <v>-0.007602909158934027</v>
       </c>
       <c r="AZ10" s="3" t="n">
         <v>0.4498381877022655</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.08778456636398</v>
+        <v>4.082322071064996</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.118962269639775</v>
+        <v>4.113597378248246</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.246575342465754</v>
+        <v>4.241095890410959</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002446312871349491</v>
+        <v>0.00244958624672923</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03748999878289148</v>
+        <v>0.03745693468390322</v>
       </c>
       <c r="AZ11" s="12" t="n">
         <v>0.4584344117647059</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.614575762839826</v>
+        <v>2.609103591427394</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.520097317474923</v>
+        <v>2.514903032791763</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.736986301369863</v>
+        <v>2.731506849315068</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003824712269625908</v>
+        <v>0.003832733982988073</v>
       </c>
     </row>
     <row r="12">
@@ -2111,7 +2111,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>-0.08767123287671233</v>
+        <v>-0.09315068493150686</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1211705312265202</v>
+        <v>-0.1213475481992788</v>
       </c>
       <c r="AZ13" s="12" t="n">
         <v>0.009854528390426998</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.20541835373513</v>
+        <v>4.200098326123705</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.785249588414843</v>
+        <v>4.780158887073008</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.487671232876712</v>
+        <v>4.482191780821918</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002377884709405496</v>
+        <v>0.002380896641824349</v>
       </c>
     </row>
     <row r="14">
@@ -2317,22 +2317,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1931869971280061</v>
+        <v>-0.1935153038571337</v>
       </c>
       <c r="AZ14" s="12" t="n">
         <v>0.03409504726674872</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.134091640926714</v>
+        <v>3.128723437245256</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.88453288403925</v>
+        <v>3.879457914339657</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.241095890410959</v>
+        <v>3.235616438356165</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003190717166471596</v>
+        <v>0.003196191737804953</v>
       </c>
     </row>
     <row r="15">
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1661360069706402</v>
+        <v>-0.1666779512874945</v>
       </c>
       <c r="AZ15" s="12" t="n">
         <v>0.15599609375</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.884143705181358</v>
+        <v>1.878792588436656</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.259533594125366</v>
+        <v>2.254581636642661</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.002739726027397</v>
+        <v>1.997260273972603</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005307450791837267</v>
+        <v>0.00532256730282346</v>
       </c>
     </row>
     <row r="16">
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.04906114493128649</v>
+        <v>-0.04927790153886943</v>
       </c>
       <c r="AZ16" s="12" t="n">
         <v>0.1617869418794136</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.738975955444459</v>
+        <v>1.733501553200114</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.82869376529872</v>
+        <v>1.823352540143976</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.736986301369863</v>
+        <v>1.731506849315068</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005750510792683233</v>
+        <v>0.005768670920161333</v>
       </c>
     </row>
     <row r="17">
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.06100136049868643</v>
+        <v>0.06101982124306364</v>
       </c>
       <c r="AZ17" s="12" t="n">
         <v>0.8684931506849314</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.982926675460489</v>
+        <v>2.977436973162164</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.811425872308466</v>
+        <v>2.806202969586256</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.241095890410959</v>
+        <v>3.235616438356165</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.0033524122742495</v>
+        <v>0.003358593343918739</v>
       </c>
     </row>
     <row r="18">
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.121389890473591</v>
+        <v>0.1216034267921888</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>2.36</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.710951275337642</v>
+        <v>1.705462659769155</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.525741662086024</v>
+        <v>1.520557640098174</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.736986301369863</v>
+        <v>1.731506849315068</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005844701800772547</v>
+        <v>0.005863511547859724</v>
       </c>
     </row>
     <row r="19">
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.02911166182993484</v>
+        <v>0.02908490695483685</v>
       </c>
       <c r="AZ19" s="12" t="n">
         <v>0.5159509202453989</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.173066007312716</v>
+        <v>3.167600406351001</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.083305850086732</v>
+        <v>3.078074884728648</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.402739726027397</v>
+        <v>3.397260273972603</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003151525993141581</v>
+        <v>0.003156963858177983</v>
       </c>
     </row>
     <row r="20">
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5891963855580248</v>
+        <v>-0.5906253431422434</v>
       </c>
       <c r="AZ20" s="12" t="n">
         <v>0.01357294724220615</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.416331869675058</v>
+        <v>1.41089048352207</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.447710341105362</v>
+        <v>3.44645292493596</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.4</v>
+        <v>1.394520547945205</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.007060492116366944</v>
+        <v>0.007087722340458733</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3124,22 +3124,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03836778014608579</v>
+        <v>0.03837902818271566</v>
       </c>
       <c r="AZ21" s="12" t="n">
         <v>0.503771183856502</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.7643835616438355</v>
+        <v>0.7589041095890411</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.736139522295555</v>
+        <v>0.7308546195479426</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.736986301369863</v>
+        <v>0.7315068493150685</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01308243727598567</v>
+        <v>0.01317689530685921</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.06724577429750611</v>
+        <v>0.06724547501544796</v>
       </c>
       <c r="AZ22" s="12" t="n">
         <v>0.06178226917776741</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.825192191736148</v>
+        <v>1.819712819575399</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.710189195115385</v>
+        <v>1.705055549239091</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.002739726027397</v>
+        <v>1.997260273972603</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005478875071500204</v>
+        <v>0.005495372617275588</v>
       </c>
     </row>
     <row r="23">
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02562129550770047</v>
+        <v>0.02564726212416082</v>
       </c>
       <c r="AZ23" s="12" t="n">
         <v>0.5930539399802566</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.30358820964963</v>
+        <v>4.298104800689286</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.196079223880856</v>
+        <v>4.190626699268637</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.328767123287672</v>
+        <v>4.323287671232877</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002323642391615841</v>
+        <v>0.002326606833410926</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1646712390671095</v>
+        <v>0.1648518638545546</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.3631016034285715</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.895648262275223</v>
+        <v>2.890051436747248</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.486236600634708</v>
+        <v>2.481046325653735</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.241095890410959</v>
+        <v>3.235616438356165</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003453458118612311</v>
+        <v>0.003460146028146474</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.343350790544454</v>
+        <v>0.343867506643477</v>
       </c>
       <c r="AZ25" s="12" t="n">
         <v>0.6845878136200718</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.805680186352576</v>
+        <v>2.799842335621992</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.088568530350473</v>
+        <v>2.083421410057785</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.241095890410959</v>
+        <v>3.235616438356165</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.00356419810377609</v>
+        <v>0.003571629685276001</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3699,22 +3699,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>76.51420508781978</v>
+        <v>78.03027076361423</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.3966249999999998</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.2657534246575343</v>
+        <v>0.2602739726027398</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.003428448041961454</v>
+        <v>0.003293345323100812</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.2383561643835616</v>
+        <v>0.2328767123287671</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.03762886597938144</v>
+        <v>0.03842105263157894</v>
       </c>
     </row>
     <row r="27">
@@ -3808,22 +3808,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.04983783414943407</v>
+        <v>0.05031910472959734</v>
       </c>
       <c r="AZ27" s="12" t="n">
         <v>0.5958751475409836</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.2602739726027397</v>
+        <v>0.2547945205479452</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.2479182633131245</v>
+        <v>0.2425877234838469</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.2383561643835616</v>
+        <v>0.2328767123287671</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.03842105263157895</v>
+        <v>0.03924731182795699</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3938,7 +3938,7 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-2.994907617705857</v>
+        <v>-3.058000060537302</v>
       </c>
       <c r="AZ28" s="12" t="n">
         <v>0.09718163872026264</v>
@@ -3946,7 +3946,7 @@
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.2383561643835616</v>
+        <v>0.2328767123287671</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1387263991691636</v>
+        <v>-0.1390438149771524</v>
       </c>
       <c r="AZ29" s="12" t="n">
         <v>0.3234549152542372</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.660642854482149</v>
+        <v>2.655221852555313</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.089195874476511</v>
+        <v>3.084038303859621</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.736986301369863</v>
+        <v>2.731506849315068</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003758490164568268</v>
+        <v>0.00376616364104426</v>
       </c>
     </row>
     <row r="30">
@@ -4189,22 +4189,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05729815811524917</v>
+        <v>0.05730061589382765</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.7127234664310955</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.61019254202337</v>
+        <v>2.604712543455652</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.468738379981979</v>
+        <v>2.463549632243109</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.736986301369863</v>
+        <v>2.731506849315068</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003831134998281849</v>
+        <v>0.003839195240613031</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.08269050979829519</v>
+        <v>0.08273517370060836</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.524854934844193</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.154074948798058</v>
+        <v>2.148584318721442</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.989557430589616</v>
+        <v>1.984404285470785</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.309589041095891</v>
+        <v>2.304109589041096</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004642364002041736</v>
+        <v>0.004654227396554164</v>
       </c>
     </row>
     <row r="32">
@@ -4412,22 +4412,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2778974916370439</v>
+        <v>-0.2787547989461667</v>
       </c>
       <c r="AZ32" s="12" t="n">
         <v>0.1868867491976158</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.608593770205821</v>
+        <v>1.603145534532296</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.227652932341402</v>
+        <v>2.222746899653393</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.610958904109589</v>
+        <v>1.605479452054795</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.006216609926768827</v>
+        <v>0.006237736864555728</v>
       </c>
     </row>
     <row r="33">
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.1009734685772185</v>
+        <v>-0.1012387495563641</v>
       </c>
       <c r="AZ33" s="12" t="n">
         <v>0.02547852298417497</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.643960722339263</v>
+        <v>2.638535355020807</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.940915123110976</v>
+        <v>2.935746677683761</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.736986301369863</v>
+        <v>2.731506849315068</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.00378220444634761</v>
+        <v>0.003789981430785544</v>
       </c>
     </row>
     <row r="34">
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03127841070938566</v>
+        <v>0.0312347756522329</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.2280373831775702</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.63967097418384</v>
+        <v>1.634193244756023</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.589940172466094</v>
+        <v>1.584695632206965</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.657534246575342</v>
+        <v>1.652054794520548</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.00609878454729467</v>
+        <v>0.006119227350920148</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>797.7</v>
+        <v>799</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1378588684213147</v>
+        <v>0.1379376949034397</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.6260498934436503</v>
+        <v>0.6234042553191488</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.970981539033887</v>
+        <v>2.968199454025969</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.61102815251234</v>
+        <v>2.608402434790454</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.235616438356165</v>
+        <v>3.232876712328767</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003365890992123711</v>
+        <v>0.003369045832292815</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9299</v>
+        <v>9287</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.01144020173049566</v>
+        <v>-0.01152709146582617</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1621335760834499</v>
+        <v>0.1636352023258318</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.712436568990507</v>
+        <v>1.709700518379055</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.732253903090298</v>
+        <v>1.729638216301146</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.731506849315068</v>
+        <v>1.728767123287671</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005839632358409088</v>
+        <v>0.005848977579699674</v>
       </c>
     </row>
     <row r="4">
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>104.7</v>
+        <v>105.7</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.0195376847938483</v>
+        <v>0.01952400764770816</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.1970200573065903</v>
+        <v>0.1856953642384107</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.362687115164009</v>
+        <v>4.359961249096889</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.279083726116657</v>
+        <v>4.276467465593467</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.731506849315068</v>
+        <v>4.728767123287671</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002292165295384486</v>
+        <v>0.002293598366744974</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6550</v>
+        <v>6402</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.04658469068645121</v>
+        <v>0.04695105340039786</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.496412213740458</v>
+        <v>1.554123711340206</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.2602739726027397</v>
+        <v>0.2575342465753425</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.2486888781375418</v>
+        <v>0.245984992076655</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.2328767123287671</v>
+        <v>0.2301369863013699</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.03842105263157895</v>
+        <v>0.03882978723404255</v>
       </c>
     </row>
     <row r="6">
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>20990</v>
+        <v>20970</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1098984719821578</v>
+        <v>-0.1099477336677492</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02601238685088147</v>
+        <v>0.02699093943729136</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.500496296808379</v>
+        <v>6.4978427058452</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.303095312378877</v>
+        <v>7.300518128695599</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>6.906849315068493</v>
+        <v>6.904109589041096</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001538344080729623</v>
+        <v>0.00153897231014909</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>20990</v>
+        <v>20970</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05930753108382617</v>
+        <v>-0.05939845724984626</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.3046212482134349</v>
+        <v>0.305865522174535</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.921813146252262</v>
+        <v>1.919074087713895</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.042977072482034</v>
+        <v>2.040262534657193</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>1.904109589041096</v>
+        <v>1.901369863013699</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005203419499705814</v>
+        <v>0.005210846242998645</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1930</v>
+        <v>1913</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04428045571121422</v>
+        <v>0.04441595038934703</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.218944437305699</v>
+        <v>3.256436363826451</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.8438356164383563</v>
+        <v>0.8410958904109589</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.8080545909131818</v>
+        <v>0.8053265464754797</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.8164383561643835</v>
+        <v>0.8136986301369863</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01185064935064935</v>
+        <v>0.01188925081433225</v>
       </c>
     </row>
     <row r="9">
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>202.3</v>
+        <v>205.7</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1615257805128324</v>
+        <v>0.1617157157616957</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.957093425605536</v>
+        <v>2.891686922702966</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.62327948096023</v>
+        <v>1.620532289570589</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.397540638524206</v>
+        <v>1.394947376181499</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.652054794520548</v>
+        <v>1.649315068493151</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006160368634786553</v>
+        <v>0.006170811938989388</v>
       </c>
     </row>
     <row r="10">
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.007602909158934027</v>
+        <v>-0.007619741134756854</v>
       </c>
       <c r="AZ10" s="3" t="n">
         <v>0.4498381877022655</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.082322071064996</v>
+        <v>4.079590839395059</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.113597378248246</v>
+        <v>4.110914947119109</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.241095890410959</v>
+        <v>4.238356164383561</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.00244958624672923</v>
+        <v>0.002451226212058768</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1122</v>
+        <v>1115</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03745693468390322</v>
+        <v>0.03744036303844014</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4584344117647059</v>
+        <v>0.4675905022421525</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.609103591427394</v>
+        <v>2.606367514394811</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.514903032791763</v>
+        <v>2.512305870538255</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.731506849315068</v>
+        <v>2.728767123287671</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003832733982988073</v>
+        <v>0.003836757458328728</v>
       </c>
     </row>
     <row r="12">
@@ -2111,7 +2111,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>-0.09315068493150686</v>
+        <v>-0.0958904109589041</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>213.1</v>
+        <v>211</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1213475481992788</v>
+        <v>-0.1214362125698142</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.009854528390426998</v>
+        <v>0.01990521327014205</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.200098326123705</v>
+        <v>4.197438432606687</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.780158887073008</v>
+        <v>4.777613751739378</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.482191780821918</v>
+        <v>4.47945205479452</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002380896641824349</v>
+        <v>0.002382405402856574</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>243.3</v>
+        <v>243.1</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2317,22 +2317,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1935153038571337</v>
+        <v>-0.19367983325633</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.03409504726674872</v>
+        <v>0.03494580419580418</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.128723437245256</v>
+        <v>3.126039441780408</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.879457914339657</v>
+        <v>3.876920819684991</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.235616438356165</v>
+        <v>3.232876712328767</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003196191737804953</v>
+        <v>0.003198935965537463</v>
       </c>
     </row>
     <row r="15">
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>162.9</v>
+        <v>169.9</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>76.8</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1666779512874945</v>
+        <v>-0.184672126824877</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.15599609375</v>
+        <v>0.1963242894056849</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.878792588436656</v>
+        <v>1.880289300755154</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.254581636642661</v>
+        <v>2.306175665788001</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>1.997260273972603</v>
+        <v>1.994520547945206</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.00532256730282346</v>
+        <v>0.005318330533489628</v>
       </c>
     </row>
     <row r="16">
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18410</v>
+        <v>18390</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.04927790153886943</v>
+        <v>-0.04938677269173673</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1617869418794136</v>
+        <v>0.1630504404567701</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.733501553200114</v>
+        <v>1.730764363579605</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.823352540143976</v>
+        <v>1.820681970185079</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.731506849315068</v>
+        <v>1.728767123287671</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005768670920161333</v>
+        <v>0.005777794025824392</v>
       </c>
     </row>
     <row r="17">
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>80.3</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.06101982124306364</v>
+        <v>0.06102908720529984</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8684931506849314</v>
+        <v>0.8546353522867736</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.977436973162164</v>
+        <v>2.974692102180586</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.806202969586256</v>
+        <v>2.803591473647328</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.235616438356165</v>
+        <v>3.232876712328767</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003358593343918739</v>
+        <v>0.003361692456395584</v>
       </c>
     </row>
     <row r="18">
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1216034267921888</v>
+        <v>0.121710748791532</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>2.36</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.705462659769155</v>
+        <v>1.702718328284696</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.520557640098174</v>
+        <v>1.51796559863504</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.731506849315068</v>
+        <v>1.728767123287671</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005863511547859724</v>
+        <v>0.005872961977260157</v>
       </c>
     </row>
     <row r="19">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>146.7</v>
+        <v>149.7</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.02908490695483685</v>
+        <v>0.02907150207993674</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5159509202453989</v>
+        <v>0.4855711422845694</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.167600406351001</v>
+        <v>3.16486761992532</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.078074884728648</v>
+        <v>3.075459395706283</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.397260273972603</v>
+        <v>3.394520547945206</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003156963858177983</v>
+        <v>0.003159689819897101</v>
       </c>
     </row>
     <row r="20">
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>29190</v>
+        <v>29120</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5906253431422434</v>
+        <v>-0.5913420980173589</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.01357294724220615</v>
+        <v>0.01600942067307698</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.41089048352207</v>
+        <v>1.408169852181606</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.44645292493596</v>
+        <v>3.445840262355729</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.394520547945205</v>
+        <v>1.391780821917808</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.007087722340458733</v>
+        <v>0.007101416057521406</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>446</v>
+        <v>445.8</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3124,22 +3124,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03837902818271566</v>
+        <v>0.03838475252868134</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.503771183856502</v>
+        <v>0.5044458232391205</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.7589041095890411</v>
+        <v>0.7561643835616438</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.7308546195479426</v>
+        <v>0.7282121407505526</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.7315068493150685</v>
+        <v>0.7287671232876712</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01317689530685921</v>
+        <v>0.01322463768115942</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100.5</v>
+        <v>101</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>217.7</v>
+        <v>217.9</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.06724547501544796</v>
+        <v>0.06452227704971938</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.06178226917776741</v>
+        <v>0.06608536025699863</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.819712819575399</v>
+        <v>1.817699644986432</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.705055549239091</v>
+        <v>1.707526168474476</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>1.997260273972603</v>
+        <v>1.994520547945206</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005495372617275588</v>
+        <v>0.005501458960825536</v>
       </c>
     </row>
     <row r="23">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>91.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10130</v>
+        <v>9989</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02564726212416082</v>
+        <v>0.0330741433741987</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5930539399802566</v>
+        <v>0.5661573947342076</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.298104800689286</v>
+        <v>4.294224045889197</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.190626699268637</v>
+        <v>4.156743321310433</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.323287671232877</v>
+        <v>4.32054794520548</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002326606833410926</v>
+        <v>0.002328709422968479</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1648518638545546</v>
+        <v>0.1649424693066562</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.3631016034285715</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.890051436747248</v>
+        <v>2.887252827204402</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.481046325653735</v>
+        <v>2.478450999320868</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.235616438356165</v>
+        <v>3.232876712328767</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003460146028146474</v>
+        <v>0.003463499942151777</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.343867506643477</v>
+        <v>0.3441267762187247</v>
       </c>
       <c r="AZ25" s="12" t="n">
         <v>0.6845878136200718</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.799842335621992</v>
+        <v>2.79692273666616</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.083421410057785</v>
+        <v>2.080847421650521</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.235616438356165</v>
+        <v>3.232876712328767</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003571629685276001</v>
+        <v>0.003575357970710222</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3699,22 +3699,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>78.03027076361423</v>
+        <v>78.81257912656564</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.3966249999999998</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.2602739726027398</v>
+        <v>0.2575342465753425</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.003293345323100812</v>
+        <v>0.003226737556832343</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.2328767123287671</v>
+        <v>0.2301369863013699</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.03842105263157894</v>
+        <v>0.03882978723404255</v>
       </c>
     </row>
     <row r="27">
@@ -3808,22 +3808,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05031910472959734</v>
+        <v>0.05056765331511932</v>
       </c>
       <c r="AZ27" s="12" t="n">
         <v>0.5958751475409836</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.2547945205479452</v>
+        <v>0.252054794520548</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.2425877234838469</v>
+        <v>0.2399224778386964</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.2328767123287671</v>
+        <v>0.2301369863013699</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.03924731182795699</v>
+        <v>0.03967391304347826</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3938,7 +3938,7 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-3.058000060537302</v>
+        <v>-3.090553074568182</v>
       </c>
       <c r="AZ28" s="12" t="n">
         <v>0.09718163872026264</v>
@@ -3946,7 +3946,7 @@
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.2328767123287671</v>
+        <v>0.2301369863013699</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14750</v>
+        <v>14930</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1390438149771524</v>
+        <v>-0.1392029648551538</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.3234549152542372</v>
+        <v>0.3074989953114533</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.655221852555313</v>
+        <v>2.652511428297174</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.084038303859621</v>
+        <v>3.081459763451481</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.731506849315068</v>
+        <v>2.728767123287671</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.00376616364104426</v>
+        <v>0.003770012032113911</v>
       </c>
     </row>
     <row r="30">
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>566</v>
+        <v>564.9</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4189,22 +4189,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05730061589382765</v>
+        <v>0.05730186230959407</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.7127234664310955</v>
+        <v>0.7160585625774476</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.604712543455652</v>
+        <v>2.601972540274347</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.463549632243109</v>
+        <v>2.460955222939397</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.731506849315068</v>
+        <v>2.728767123287671</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003839195240613031</v>
+        <v>0.00384323809925589</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.08273517370060836</v>
+        <v>0.08275761471092204</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.524854934844193</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.148584318721442</v>
+        <v>2.145838976307578</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.984404285470785</v>
+        <v>1.981827647437493</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.304109589041096</v>
+        <v>2.301369863013699</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004654227396554164</v>
+        <v>0.004660181919711123</v>
       </c>
     </row>
     <row r="32">
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>65430</v>
+        <v>65080</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4412,22 +4412,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2787547989461667</v>
+        <v>-0.2791852609225388</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1868867491976158</v>
+        <v>0.1932698217578366</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.603145534532296</v>
+        <v>1.600421483295761</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.222746899653393</v>
+        <v>2.220295169524515</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.605479452054795</v>
+        <v>1.602739726027397</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.006237736864555728</v>
+        <v>0.00624835401447306</v>
       </c>
     </row>
     <row r="33">
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>132.7</v>
+        <v>127</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.1012387495563641</v>
+        <v>-0.101371767253067</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.02547852298417497</v>
+        <v>0.07150393700787405</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.638535355020807</v>
+        <v>2.635822744944681</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.935746677683761</v>
+        <v>2.93316262375541</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.731506849315068</v>
+        <v>2.728767123287671</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003789981430785544</v>
+        <v>0.003793881822736101</v>
       </c>
     </row>
     <row r="34">
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.0312347756522329</v>
+        <v>0.03121286233646841</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.2280373831775702</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.634193244756023</v>
+        <v>1.631454383825944</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.584695632206965</v>
+        <v>1.582073346262846</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.652054794520548</v>
+        <v>1.649315068493151</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.006119227350920148</v>
+        <v>0.006129500217192022</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>76.3</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1379376949034397</v>
+        <v>0.1341065388398261</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.6234042553191488</v>
+        <v>0.6424812030075187</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.968199454025969</v>
+        <v>2.970254566499487</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.608402434790454</v>
+        <v>2.61902604806248</v>
       </c>
       <c r="BC2" s="8" t="n">
         <v>3.232876712328767</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003369045832292815</v>
+        <v>0.003366714797036817</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>110.7</v>
+        <v>108.2</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9287</v>
+        <v>9196</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.01152709146582617</v>
+        <v>0.001625516521331287</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1636352023258318</v>
+        <v>0.1486110073945195</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.709700518379055</v>
+        <v>1.709144487423852</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.729638216301146</v>
+        <v>1.706370753572404</v>
       </c>
       <c r="BC3" s="8" t="n">
         <v>1.728767123287671</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005848977579699674</v>
+        <v>0.005850880410393351</v>
       </c>
     </row>
     <row r="4">
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>105.7</v>
+        <v>104.8</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.01952400764770816</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.1856953642384107</v>
+        <v>0.1958778625954201</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.359961249096889</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6402</v>
+        <v>6516</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.04695105340039786</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.554123711340206</v>
+        <v>1.509438305709024</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2575342465753425</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>269.2</v>
+        <v>274.5</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>20970</v>
+        <v>20940</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1099477336677492</v>
+        <v>-0.1126104720948105</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02699093943729136</v>
+        <v>0.04871060171919761</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.4978427058452</v>
+        <v>6.502478220467233</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.300518128695599</v>
+        <v>7.32764813645848</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.904109589041096</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.00153897231014909</v>
+        <v>0.001537875200953992</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>20970</v>
+        <v>20940</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.05939845724984626</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.305865522174535</v>
+        <v>0.3077363896848138</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.919074087713895</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1913</v>
+        <v>1938</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04441595038934703</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.256436363826451</v>
+        <v>3.201528773993807</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8410958904109589</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>205.7</v>
+        <v>205.3</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1617157157616957</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.891686922702966</v>
+        <v>2.899269361909401</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.620532289570589</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>112</v>
+        <v>112.1</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12360</v>
+        <v>12070</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.007619741134756854</v>
+        <v>-0.00783397069666731</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4498381877022655</v>
+        <v>0.4859983429991714</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.079590839395059</v>
+        <v>4.079698926539897</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.110914947119109</v>
+        <v>4.111911520901931</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.238356164383561</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002451226212058768</v>
+        <v>0.002451161269510952</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1115</v>
+        <v>1137</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03744036303844014</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4675905022421525</v>
+        <v>0.4391938522427441</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.606367514394811</v>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>215.2</v>
+        <v>218</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>211</v>
+        <v>210.9</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1214362125698142</v>
+        <v>-0.1241037199457679</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.01990521327014205</v>
+        <v>0.03366524419155992</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.197438432606687</v>
+        <v>4.199833956742061</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.777613751739378</v>
+        <v>4.794898725317139</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.47945205479452</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002382405402856574</v>
+        <v>0.002381046513504859</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>243.1</v>
+        <v>244.8</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.19367983325633</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.03494580419580418</v>
+        <v>0.02775868055555542</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.126039441780408</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>77.40000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2429,7 +2429,7 @@
         <v>-0.184672126824877</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1963242894056849</v>
+        <v>0.2041027308192458</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.880289300755154</v>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>114</v>
+        <v>112.6</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18390</v>
+        <v>18400</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.04938677269173673</v>
+        <v>-0.04261229686679587</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1630504404567701</v>
+        <v>0.1481430347826087</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.730764363579605</v>
+        <v>1.730606561471948</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.820681970185079</v>
+        <v>1.807633998022182</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.728767123287671</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005777794025824392</v>
+        <v>0.005778320863116694</v>
       </c>
     </row>
     <row r="17">
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>80.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2668,7 +2668,7 @@
         <v>0.06102908720529984</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8546353522867736</v>
+        <v>0.8297560975609755</v>
       </c>
       <c r="BA17" s="8" t="n">
         <v>2.974692102180586</v>
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>149.7</v>
+        <v>146.1</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.02907150207993674</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4855711422845694</v>
+        <v>0.5221765913757701</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.16486761992532</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>29120</v>
+        <v>29060</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5913420980173589</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.01600942067307698</v>
+        <v>0.0181071689607708</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.408169852181606</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>445.8</v>
+        <v>440.9</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03838475252868134</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5044458232391205</v>
+        <v>0.5211656792923565</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7561643835616438</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101</v>
+        <v>101.3</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>217.9</v>
+        <v>224.1</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.06452227704971938</v>
+        <v>0.06289831626738977</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.06608536025699863</v>
+        <v>0.03966979027219986</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.817699644986432</v>
+        <v>1.818132525499761</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.707526168474476</v>
+        <v>1.710542295225896</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>1.994520547945206</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005501458960825536</v>
+        <v>0.005500149114405859</v>
       </c>
     </row>
     <row r="23">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>88.8</v>
+        <v>91</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9989</v>
+        <v>10030</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.0330741433741987</v>
+        <v>0.02722514960649494</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5661573947342076</v>
+        <v>0.5983979431704887</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.294224045889197</v>
+        <v>4.29512420579644</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.156743321310433</v>
+        <v>4.181288014065657</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.32054794520548</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002328709422968479</v>
+        <v>0.002328221378675058</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3685,7 +3685,7 @@
         <v>0.55865</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AK26" s="10" t="n">
         <v>46377</v>
@@ -3702,7 +3702,7 @@
         <v>78.81257912656564</v>
       </c>
       <c r="AZ26" s="12" t="n">
-        <v>0.3966249999999998</v>
+        <v>0.3144705882352941</v>
       </c>
       <c r="BA26" s="8" t="n">
         <v>0.2575342465753425</v>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1159</v>
+        <v>1135</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.05056765331511932</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5958751475409836</v>
+        <v>0.6296205251101323</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.252054794520548</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12190</v>
+        <v>12090</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-3.090553074568182</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.09718163872026264</v>
+        <v>0.1062567556658396</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14930</v>
+        <v>14990</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.1392029648551538</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.3074989953114533</v>
+        <v>0.3022655103402268</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.652511428297174</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>65080</v>
+        <v>66290</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2791852609225388</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1932698217578366</v>
+        <v>0.1714889123548047</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.600421483295761</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>127</v>
+        <v>127.7</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4524,7 +4524,7 @@
         <v>-0.101371767253067</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.07150393700787405</v>
+        <v>0.06563038371182461</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.635822744944681</v>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102.2</v>
+        <v>102.7</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03121286233646841</v>
+        <v>0.02817616918009656</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2280373831775702</v>
+        <v>0.2340453938584781</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.631454383825944</v>
+        <v>1.631574281995246</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.582073346262846</v>
+        <v>1.586862573654397</v>
       </c>
       <c r="BC34" s="8" t="n">
         <v>1.649315068493151</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.006129500217192022</v>
+        <v>0.006129049783605951</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>77.09999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>798</v>
+        <v>797.7</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1341065388398261</v>
+        <v>0.1369748390559151</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.6424812030075187</v>
+        <v>0.6303121474238436</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.970254566499487</v>
+        <v>2.968716648661693</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.61902604806248</v>
+        <v>2.611066266978046</v>
       </c>
       <c r="BC2" s="8" t="n">
         <v>3.232876712328767</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003366714797036817</v>
+        <v>0.003368458894353569</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>108.2</v>
+        <v>110</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9196</v>
+        <v>9206</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>0.001625516521331287</v>
+        <v>-0.007892066035953911</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1486110073945195</v>
+        <v>0.1664507060612643</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.709144487423852</v>
+        <v>1.709546781762804</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.706370753572404</v>
+        <v>1.723145963496305</v>
       </c>
       <c r="BC3" s="8" t="n">
         <v>1.728767123287671</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005850880410393351</v>
+        <v>0.005849503568243082</v>
       </c>
     </row>
     <row r="4">
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>104.8</v>
+        <v>105.7</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.01952400764770816</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.1958778625954201</v>
+        <v>0.1856953642384107</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.359961249096889</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6516</v>
+        <v>6479</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.04695105340039786</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.509438305709024</v>
+        <v>1.523769100169779</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2575342465753425</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>274.5</v>
+        <v>267.5</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1126104720948105</v>
+        <v>-0.1090804149515572</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.04871060171919761</v>
+        <v>0.02196752626552056</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.502478220467233</v>
+        <v>6.496324179265773</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.32764813645848</v>
+        <v>7.291706556111394</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.904109589041096</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001537875200953992</v>
+        <v>0.001539332047485694</v>
       </c>
     </row>
     <row r="7">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1938</v>
+        <v>1930</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04441595038934703</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.201528773993807</v>
+        <v>3.218944437305699</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8410958904109589</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>205.3</v>
+        <v>201.4</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1617157157616957</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.899269361909401</v>
+        <v>2.974776564051638</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.620532289570589</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>112.1</v>
+        <v>112.4</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12070</v>
+        <v>12140</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.00783397069666731</v>
+        <v>-0.008475219077492517</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4859983429991714</v>
+        <v>0.4813838550247116</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.079698926539897</v>
+        <v>4.080022183330774</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.111911520901931</v>
+        <v>4.114896835492857</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.238356164383561</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002451161269510952</v>
+        <v>0.002450967066026191</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03744036303844014</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4391938522427441</v>
+        <v>0.4481092123893804</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.606367514394811</v>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>218</v>
+        <v>212.2</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>210.9</v>
+        <v>211.6</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1241037199457679</v>
+        <v>-0.1185289225157764</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.03366524419155992</v>
+        <v>0.002835538752362865</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.199833956742061</v>
+        <v>4.194813743000903</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.794898725317139</v>
+        <v>4.758878481836497</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.47945205479452</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002381046513504859</v>
+        <v>0.002383896070876834</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>244.8</v>
+        <v>245.4</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.19367983325633</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.02775868055555542</v>
+        <v>0.02524582314588431</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.126039441780408</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>169.9</v>
+        <v>169.7</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>76.90000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.184672126824877</v>
+        <v>-0.1841812859624</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.2041027308192458</v>
+        <v>0.1964618369987066</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.880289300755154</v>
+        <v>1.880174379850606</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.306175665788001</v>
+        <v>2.304647279473846</v>
       </c>
       <c r="BC15" s="8" t="n">
         <v>1.994520547945206</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005318330533489628</v>
+        <v>0.00531865560299496</v>
       </c>
     </row>
     <row r="16">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>112.6</v>
+        <v>113</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18400</v>
+        <v>18430</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.04261229686679587</v>
+        <v>-0.04456135948084364</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1481430347826087</v>
+        <v>0.1503461313076506</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.730606561471948</v>
+        <v>1.730651956986279</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.807633998022182</v>
+        <v>1.811369023180699</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.728767123287671</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005778320863116694</v>
+        <v>0.005778169296045976</v>
       </c>
     </row>
     <row r="17">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>96.8</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>82</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.06102908720529984</v>
+        <v>0.06424309857008612</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8297560975609755</v>
+        <v>0.8328606658446365</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.974692102180586</v>
+        <v>2.972904643178114</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.803591473647328</v>
+        <v>2.793445075821962</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.232876712328767</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003361692456395584</v>
+        <v>0.003363713674081969</v>
       </c>
     </row>
     <row r="18">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>89.2</v>
+        <v>88.8</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.121710748791532</v>
+        <v>0.1246350051679028</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>2.36</v>
+        <v>2.344932735426009</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.702718328284696</v>
+        <v>1.702592858279469</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.51796559863504</v>
+        <v>1.513907045802189</v>
       </c>
       <c r="BC18" s="8" t="n">
         <v>1.728767123287671</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005872961977260157</v>
+        <v>0.005873394776309208</v>
       </c>
     </row>
     <row r="19">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>146.1</v>
+        <v>145.7</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.02907150207993674</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5221765913757701</v>
+        <v>0.5263555250514758</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.16486761992532</v>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>368.5</v>
+        <v>362.5</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5913420980173589</v>
+        <v>-0.5865712822616119</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.0181071689607708</v>
+        <v>0.001530118719889728</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.408169852181606</v>
+        <v>1.408042769284349</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.445840262355729</v>
+        <v>3.405769141986258</v>
       </c>
       <c r="BC20" s="8" t="n">
         <v>1.391780821917808</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.007101416057521406</v>
+        <v>0.007102056995813129</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>440.9</v>
+        <v>450.2</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03838475252868134</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5211656792923565</v>
+        <v>0.4897422212350064</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7561643835616438</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101.3</v>
+        <v>101</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>224.1</v>
+        <v>219.9</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.06289831626738977</v>
+        <v>0.06452227704971938</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.03966979027219986</v>
+        <v>0.0563892678490221</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.818132525499761</v>
+        <v>1.817699644986432</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.710542295225896</v>
+        <v>1.707526168474476</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>1.994520547945206</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005500149114405859</v>
+        <v>0.005501458960825536</v>
       </c>
     </row>
     <row r="23">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>91</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10030</v>
+        <v>10020</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02722514960649494</v>
+        <v>0.02696345164651724</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5983979431704887</v>
+        <v>0.6017513849301397</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.29512420579644</v>
+        <v>4.295164212391057</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.181288014065657</v>
+        <v>4.182392475121365</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.32054794520548</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002328221378675058</v>
+        <v>0.002328199692843209</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>47</v>
+        <v>46.9</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>27.9</v>
+        <v>27.7</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.3441267762187247</v>
+        <v>0.3450758045030267</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.6845878136200718</v>
+        <v>0.6931407942238268</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.79692273666616</v>
+        <v>2.79626409577228</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.080847421650521</v>
+        <v>2.07888959596997</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.232876712328767</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003575357970710222</v>
+        <v>0.003576200121840842</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1135</v>
+        <v>1152</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.05056765331511932</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.6296205251101323</v>
+        <v>0.6055723055555555</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.252054794520548</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12090</v>
+        <v>12070</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-3.090553074568182</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.1062567556658396</v>
+        <v>0.1080898240265122</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14990</v>
+        <v>14940</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.1392029648551538</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.3022655103402268</v>
+        <v>0.306623828647925</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.652511428297174</v>
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>564.9</v>
+        <v>564.6</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4192,7 +4192,7 @@
         <v>0.05730186230959407</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.7160585625774476</v>
+        <v>0.7169703896563939</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.601972540274347</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>66290</v>
+        <v>64500</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2791852609225388</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1714889123548047</v>
+        <v>0.204</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.600421483295761</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>127.7</v>
+        <v>130.4</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4524,7 +4524,7 @@
         <v>-0.101371767253067</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.06563038371182461</v>
+        <v>0.04356595092024551</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.635822744944681</v>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102.7</v>
+        <v>102.3</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -4616,7 +4616,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1498</v>
+        <v>1486</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.02817616918009656</v>
+        <v>0.03060361809562129</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2340453938584781</v>
+        <v>0.239165545087483</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.631574281995246</v>
+        <v>1.631478436291611</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.586862573654397</v>
+        <v>1.583031931623045</v>
       </c>
       <c r="BC34" s="8" t="n">
         <v>1.649315068493151</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.006129049783605951</v>
+        <v>0.006129409851551725</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1369748390559151</v>
+        <v>0.1370529990865618</v>
       </c>
       <c r="AZ2" s="12" t="n">
         <v>0.6303121474238436</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.968716648661693</v>
+        <v>2.96593495672818</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.611066266978046</v>
+        <v>2.608440379745561</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.232876712328767</v>
+        <v>3.23013698630137</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003368458894353569</v>
+        <v>0.003371618105553915</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9206</v>
+        <v>9294</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.007892066035953911</v>
+        <v>-0.007974136419600196</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1664507060612643</v>
+        <v>0.1554061975468044</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.709546781762804</v>
+        <v>1.706810526203686</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.723145963496305</v>
+        <v>1.720530269285016</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.728767123287671</v>
+        <v>1.726027397260274</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005849503568243082</v>
+        <v>0.005858881139104617</v>
       </c>
     </row>
     <row r="4">
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>105.7</v>
+        <v>106</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01952400764770816</v>
+        <v>0.01951031643781244</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.1856953642384107</v>
+        <v>0.1823396226415095</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.359961249096889</v>
+        <v>4.357235396981941</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.276467465593467</v>
+        <v>4.273851207515192</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.728767123287671</v>
+        <v>4.726027397260274</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002293598366744974</v>
+        <v>0.00229503322380208</v>
       </c>
     </row>
     <row r="5">
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.04695105340039786</v>
+        <v>0.04732530347084083</v>
       </c>
       <c r="AZ5" s="12" t="n">
         <v>1.523769100169779</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.2575342465753425</v>
+        <v>0.2547945205479452</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.245984992076655</v>
+        <v>0.24328116555912</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.2301369863013699</v>
+        <v>0.2273972602739726</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.03882978723404255</v>
+        <v>0.03924731182795699</v>
       </c>
     </row>
     <row r="6">
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>20940</v>
+        <v>20880</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1090804149515572</v>
+        <v>-0.109129443491648</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02196752626552056</v>
+        <v>0.02490421455938696</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.496324179265773</v>
+        <v>6.493670407072114</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.291706556111394</v>
+        <v>7.289128998182616</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>6.904109589041096</v>
+        <v>6.901369863013699</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001539332047485694</v>
+        <v>0.001539961127240031</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>20940</v>
+        <v>20880</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05939845724984626</v>
+        <v>-0.05948963438740604</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.3077363896848138</v>
+        <v>0.3114942528735631</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.919074087713895</v>
+        <v>1.916335031018811</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.040262534657193</v>
+        <v>2.037548017634682</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>1.901369863013699</v>
+        <v>1.898630136986301</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005210846242998645</v>
+        <v>0.005218294211677353</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1930</v>
+        <v>1914</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04441595038934703</v>
+        <v>0.0445523307779236</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.218944437305699</v>
+        <v>3.254212520376175</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.8410958904109589</v>
+        <v>0.8383561643835618</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.8053265464754797</v>
+        <v>0.8025985292275413</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.8136986301369863</v>
+        <v>0.810958904109589</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01188925081433225</v>
+        <v>0.0119281045751634</v>
       </c>
     </row>
     <row r="9">
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>201.4</v>
+        <v>191</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1617157157616957</v>
+        <v>0.1619063415684573</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.974776564051638</v>
+        <v>3.191204188481676</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.620532289570589</v>
+        <v>1.617785071156441</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.394947376181499</v>
+        <v>1.392354110893821</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.649315068493151</v>
+        <v>1.646575342465753</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006170811938989388</v>
+        <v>0.006181290814392112</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12140</v>
+        <v>12200</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.008475219077492517</v>
+        <v>-0.008492589818210548</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4813838550247116</v>
+        <v>0.4740983606557376</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.080022183330774</v>
+        <v>4.077291208192734</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.114896835492857</v>
+        <v>4.112214559692677</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.238356164383561</v>
+        <v>4.235616438356164</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002450967066026191</v>
+        <v>0.002452608727065271</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1130</v>
+        <v>1137</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03744036303844014</v>
+        <v>0.03742376488222731</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4481092123893804</v>
+        <v>0.4391938522427441</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.606367514394811</v>
+        <v>2.603631443169437</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.512305870538255</v>
+        <v>2.509708695043257</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.728767123287671</v>
+        <v>2.726027397260274</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003836757458328728</v>
+        <v>0.003840789381398336</v>
       </c>
     </row>
     <row r="12">
@@ -2111,7 +2111,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>-0.0958904109589041</v>
+        <v>-0.09863013698630137</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>211.6</v>
+        <v>212.4</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1185289225157764</v>
+        <v>-0.1186163405096527</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.002835538752362865</v>
+        <v>-0.0009416195856875031</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.194813743000903</v>
+        <v>4.192153148044506</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.758878481836497</v>
+        <v>4.756331823156994</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.47945205479452</v>
+        <v>4.476712328767123</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002383896070876834</v>
+        <v>0.002385409036085586</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>245.4</v>
+        <v>248.1</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2317,22 +2317,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.19367983325633</v>
+        <v>-0.1938446141007949</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.02524582314588431</v>
+        <v>0.01408837162434495</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.126039441780408</v>
+        <v>3.123355517403693</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.876920819684991</v>
+        <v>3.874383986059744</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.232876712328767</v>
+        <v>3.23013698630137</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003198935965537463</v>
+        <v>0.003201684836797752</v>
       </c>
     </row>
     <row r="15">
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>77.3</v>
+        <v>79</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1841812859624</v>
+        <v>-0.1844707502926064</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1964618369987066</v>
+        <v>0.1707151898734178</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.880174379850606</v>
+        <v>1.877502430670157</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.304647279473846</v>
+        <v>2.302188954404507</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>1.994520547945206</v>
+        <v>1.991780821917808</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.00531865560299496</v>
+        <v>0.00532622479558154</v>
       </c>
     </row>
     <row r="16">
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.04456135948084364</v>
+        <v>-0.04466374389046267</v>
       </c>
       <c r="AZ16" s="12" t="n">
         <v>0.1503461313076506</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.730651956986279</v>
+        <v>1.727914615705354</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.811369023180699</v>
+        <v>1.808697832470031</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.728767123287671</v>
+        <v>1.726027397260274</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005778169296045976</v>
+        <v>0.005787323001442342</v>
       </c>
     </row>
     <row r="17">
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.06424309857008612</v>
+        <v>0.06425495011031726</v>
       </c>
       <c r="AZ17" s="12" t="n">
         <v>0.8328606658446365</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.972904643178114</v>
+        <v>2.970158315384524</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.793445075821962</v>
+        <v>2.790833451210772</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.232876712328767</v>
+        <v>3.23013698630137</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003363713674081969</v>
+        <v>0.0033668238989831</v>
       </c>
     </row>
     <row r="18">
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1246350051679028</v>
+        <v>0.1247472620982728</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>2.344932735426009</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.702592858279469</v>
+        <v>1.699848316345822</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.513907045802189</v>
+        <v>1.511315807228256</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.728767123287671</v>
+        <v>1.726027397260274</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005873394776309208</v>
+        <v>0.005882877844946237</v>
       </c>
     </row>
     <row r="19">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>145.7</v>
+        <v>148.2</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.02907150207993674</v>
+        <v>0.02905807884910312</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5263555250514758</v>
+        <v>0.500607287449393</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.16486761992532</v>
+        <v>3.162134842902535</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.075459395706283</v>
+        <v>3.07284390249291</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.394520547945206</v>
+        <v>3.391780821917808</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003159689819897101</v>
+        <v>0.00316242048388454</v>
       </c>
     </row>
     <row r="20">
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>29060</v>
+        <v>28910</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5865712822616119</v>
+        <v>-0.5872887721497637</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.001530118719889728</v>
+        <v>0.006726573849878736</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.408042769284349</v>
+        <v>1.405322153351281</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.405769141986258</v>
+        <v>3.405097943836994</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.391780821917808</v>
+        <v>1.389041095890411</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.007102056995813129</v>
+        <v>0.007115806134666657</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>450.2</v>
+        <v>449</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3124,22 +3124,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03838475252868134</v>
+        <v>0.03839054472234518</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.4897422212350064</v>
+        <v>0.4937237149220488</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.7561643835616438</v>
+        <v>0.7534246575342467</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.7282121407505526</v>
+        <v>0.7255696436793968</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.7287671232876712</v>
+        <v>0.726027397260274</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01322463768115942</v>
+        <v>0.01327272727272727</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>219.9</v>
+        <v>222</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.06452227704971938</v>
+        <v>0.01872717049672369</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.0563892678490221</v>
+        <v>0.1396396396396395</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.817699644986432</v>
+        <v>1.827051745726306</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.707526168474476</v>
+        <v>1.793465216830773</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>1.994520547945206</v>
+        <v>1.991780821917808</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005501458960825536</v>
+        <v>0.005473298730258299</v>
       </c>
     </row>
     <row r="23">
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02696345164651724</v>
+        <v>0.02697730694031901</v>
       </c>
       <c r="AZ23" s="12" t="n">
         <v>0.6017513849301397</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.295164212391057</v>
+        <v>4.29242236883649</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.182392475121365</v>
+        <v>4.179666230040598</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.32054794520548</v>
+        <v>4.317808219178082</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002328199692843209</v>
+        <v>0.002329686862271807</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>35</v>
+        <v>36.3</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1649424693066562</v>
+        <v>0.1650332709139776</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.3631016034285715</v>
+        <v>0.3142852925619835</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.887252827204402</v>
+        <v>2.884454085930782</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.478450999320868</v>
+        <v>2.475855546741515</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.232876712328767</v>
+        <v>3.23013698630137</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003463499942151777</v>
+        <v>0.00346686052268123</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>27.7</v>
+        <v>32</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.3450758045030267</v>
+        <v>0.3453366036893714</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.6931407942238268</v>
+        <v>0.465625</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.79626409577228</v>
+        <v>2.793343306175603</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.07888959596997</v>
+        <v>2.076315546990473</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.232876712328767</v>
+        <v>3.23013698630137</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003576200121840842</v>
+        <v>0.003579939486096004</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3699,22 +3699,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>78.81257912656564</v>
+        <v>79.61176711614394</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.3144705882352941</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.2575342465753425</v>
+        <v>0.2547945205479452</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.003226737556832343</v>
+        <v>0.003160760887189609</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.2301369863013699</v>
+        <v>0.2273972602739726</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.03882978723404255</v>
+        <v>0.03924731182795699</v>
       </c>
     </row>
     <row r="27">
@@ -3808,22 +3808,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05056765331511932</v>
+        <v>0.05082170930906543</v>
       </c>
       <c r="AZ27" s="12" t="n">
         <v>0.6055723055555555</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.252054794520548</v>
+        <v>0.2493150684931507</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.2399224778386964</v>
+        <v>0.2372572495262588</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.2301369863013699</v>
+        <v>0.2273972602739726</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.03967391304347826</v>
+        <v>0.04010989010989011</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12070</v>
+        <v>11870</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3938,15 +3938,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-3.090553074568182</v>
+        <v>-3.123806152281406</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.1080898240265122</v>
+        <v>0.1267602507160912</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.2301369863013699</v>
+        <v>0.2273972602739726</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>169.6</v>
+        <v>134.3</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14940</v>
+        <v>14700</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1392029648551538</v>
+        <v>-0.06057490513956099</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.306623828647925</v>
+        <v>0.05155986394557832</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.652511428297174</v>
+        <v>2.634921867367654</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.081459763451481</v>
+        <v>2.804823803178366</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.728767123287671</v>
+        <v>2.726027397260274</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003770012032113911</v>
+        <v>0.003795178947750062</v>
       </c>
     </row>
     <row r="30">
@@ -4189,22 +4189,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05730186230959407</v>
+        <v>0.05730312045536456</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.7169703896563939</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.601972540274347</v>
+        <v>2.599232534484579</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.460955222939397</v>
+        <v>2.458360790011789</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.728767123287671</v>
+        <v>2.726027397260274</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.00384323809925589</v>
+        <v>0.003847289485387644</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.08275761471092204</v>
+        <v>0.08278012879652392</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.524854934844193</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.145838976307578</v>
+        <v>2.143093615550243</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.981827647437493</v>
+        <v>1.979250965689797</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.301369863013699</v>
+        <v>2.298630136986302</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004660181919711123</v>
+        <v>0.004666151738514923</v>
       </c>
     </row>
     <row r="32">
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>64500</v>
+        <v>65240</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4412,22 +4412,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2791852609225388</v>
+        <v>-0.2796169351205883</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.204</v>
+        <v>0.1903433476394849</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.600421483295761</v>
+        <v>1.597697476708094</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.220295169524515</v>
+        <v>2.217844303399248</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.602739726027397</v>
+        <v>1.6</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.00624835401447306</v>
+        <v>0.006259007193654748</v>
       </c>
     </row>
     <row r="33">
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.101371767253067</v>
+        <v>-0.1015050373826717</v>
       </c>
       <c r="AZ33" s="12" t="n">
         <v>0.04356595092024551</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.635822744944681</v>
+        <v>2.633110184102825</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.93316262375541</v>
+        <v>2.930578682859321</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.728767123287671</v>
+        <v>2.726027397260274</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003793881822736101</v>
+        <v>0.003797790179983404</v>
       </c>
     </row>
     <row r="34">
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03060361809562129</v>
+        <v>0.03058070181718849</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.239165545087483</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.631478436291611</v>
+        <v>1.628739615003775</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.583031931623045</v>
+        <v>1.580409580862394</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.649315068493151</v>
+        <v>1.646575342465753</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.006129409851551725</v>
+        <v>0.006139716814081927</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>76.5</v>
+        <v>74</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>797.7</v>
+        <v>803.9</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1370529990865618</v>
+        <v>0.1493500568084806</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.6303121474238436</v>
+        <v>0.5648712526433637</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.96593495672818</v>
+        <v>2.959294007975387</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.608440379745561</v>
+        <v>2.57475430609258</v>
       </c>
       <c r="BC2" s="8" t="n">
         <v>3.23013698630137</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003371618105553915</v>
+        <v>0.003379184350405772</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>110</v>
+        <v>109.9</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9294</v>
+        <v>9231</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.007974136419600196</v>
+        <v>-0.007451126824951393</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1554061975468044</v>
+        <v>0.1622341098472537</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.706810526203686</v>
+        <v>1.706788410396121</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.720530269285016</v>
+        <v>1.719601378354602</v>
       </c>
       <c r="BC3" s="8" t="n">
         <v>1.726027397260274</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005858881139104617</v>
+        <v>0.005858957055889047</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>111.9</v>
+        <v>110.7</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01951031643781244</v>
+        <v>0.02201110633407521</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.1823396226415095</v>
+        <v>0.1696603773584906</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.357235396981941</v>
+        <v>4.354696263642233</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.273851207515192</v>
+        <v>4.26090894380043</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.726027397260274</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.00229503322380208</v>
+        <v>0.002296371410215435</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6479</v>
+        <v>6525</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.04732530347084083</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.523769100169779</v>
+        <v>1.505977011494253</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2547945205479452</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>267.5</v>
+        <v>279.9</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>20880</v>
+        <v>21350</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.109129443491648</v>
+        <v>-0.1153122696775186</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02490421455938696</v>
+        <v>0.04880562060889937</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.493670407072114</v>
+        <v>6.504401306799538</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.289128998182616</v>
+        <v>7.352200198852753</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.901369863013699</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001539961127240031</v>
+        <v>0.001537420513944343</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>114.1</v>
+        <v>113.6</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>20880</v>
+        <v>21350</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05948963438740604</v>
+        <v>-0.05733283533690949</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.3114942528735631</v>
+        <v>0.2770023419203747</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.916335031018811</v>
+        <v>1.916319198176364</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.037548017634682</v>
+        <v>2.032869362603987</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>1.898630136986301</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005218294211677353</v>
+        <v>0.005218337325804775</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1914</v>
+        <v>1968</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.0445523307779236</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.254212520376175</v>
+        <v>3.137481079268293</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8383561643835618</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>191</v>
+        <v>196.1</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1619063415684573</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>3.191204188481676</v>
+        <v>3.082202957674656</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.617785071156441</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>112.4</v>
+        <v>113.9</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12200</v>
+        <v>12430</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.008492589818210548</v>
+        <v>-0.01166874967617452</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4740983606557376</v>
+        <v>0.466130329847144</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.077291208192734</v>
+        <v>4.078886135575507</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.112214559692677</v>
+        <v>4.127043573942506</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.235616438356164</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002452608727065271</v>
+        <v>0.002451649707203473</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>104.5</v>
+        <v>104</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1137</v>
+        <v>1149</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03742376488222731</v>
+        <v>0.03931213828554555</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4391938522427441</v>
+        <v>0.4173489295039163</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.603631443169437</v>
+        <v>2.60321544149022</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.509708695043257</v>
+        <v>2.504748425034752</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.726027397260274</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003840789381398336</v>
+        <v>0.003841403151125849</v>
       </c>
     </row>
     <row r="12">
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>212.4</v>
+        <v>211</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2211,7 +2211,7 @@
         <v>-0.1186163405096527</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.0009416195856875031</v>
+        <v>0.005687203791469031</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.192153148044506</v>
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>248.1</v>
+        <v>248.8</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1938446141007949</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.01408837162434495</v>
+        <v>0.01123522909967845</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.123355517403693</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>79</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2429,7 +2429,7 @@
         <v>-0.1844707502926064</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1707151898734178</v>
+        <v>0.2073955613577025</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.877502430670157</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18430</v>
+        <v>18600</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2538,7 +2538,7 @@
         <v>-0.04466374389046267</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1503461313076506</v>
+        <v>0.1398322150537634</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.727914615705354</v>
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>81.09999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2668,7 +2668,7 @@
         <v>0.06425495011031726</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8328606658446365</v>
+        <v>0.8373918417799753</v>
       </c>
       <c r="BA17" s="8" t="n">
         <v>2.970158315384524</v>
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>148.2</v>
+        <v>145.5</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.02905807884910312</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.500607287449393</v>
+        <v>0.5284536082474227</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.162134842902535</v>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>362.5</v>
+        <v>362</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>28910</v>
+        <v>29060</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5872887721497637</v>
+        <v>-0.586885041673852</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.006726573849878736</v>
+        <v>0.0001486978664830829</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.405322153351281</v>
+        <v>1.405311400039203</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.405097943836994</v>
+        <v>3.40174416761189</v>
       </c>
       <c r="BC20" s="8" t="n">
         <v>1.389041095890411</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.007115806134666657</v>
+        <v>0.007115860584153118</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>449</v>
+        <v>448.4</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03839054472234518</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.4937237149220488</v>
+        <v>0.4957224531668152</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7534246575342467</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>110</v>
+        <v>102.3</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.01872717049672369</v>
+        <v>0.05752489343604983</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1396396396396395</v>
+        <v>0.0694999999999999</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.827051745726306</v>
+        <v>1.816823025596404</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.793465216830773</v>
+        <v>1.717995516581444</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>1.991780821917808</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005473298730258299</v>
+        <v>0.005504113421678662</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10020</v>
+        <v>10040</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.02697730694031901</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.6017513849301397</v>
+        <v>0.5985606451195218</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.29242236883649</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>73.8</v>
+        <v>72.3</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1650332709139776</v>
+        <v>0.1729201238719515</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.3142852925619835</v>
+        <v>0.2875721768595041</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.884454085930782</v>
+        <v>2.87931194346769</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.475855546741515</v>
+        <v>2.454823550953097</v>
       </c>
       <c r="BC24" s="8" t="n">
         <v>3.23013698630137</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.00346686052268123</v>
+        <v>0.003473051963920426</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3589,7 +3589,7 @@
         <v>0.3453366036893714</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.465625</v>
+        <v>0.6172413793103448</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>2.793343306175603</v>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1152</v>
+        <v>1168</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.05082170930906543</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.6055723055555555</v>
+        <v>0.5835781643835618</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2493150684931507</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>11870</v>
+        <v>11880</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-3.123806152281406</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.1267602507160912</v>
+        <v>0.1258117993265995</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>134.3</v>
+        <v>169.6</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14700</v>
+        <v>14620</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.06057490513956099</v>
+        <v>-0.1393624104764262</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.05155986394557832</v>
+        <v>0.3352229822161421</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.634921867367654</v>
+        <v>2.649801055353615</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>2.804823803178366</v>
+        <v>3.07888138701968</v>
       </c>
       <c r="BC29" s="8" t="n">
         <v>2.726027397260274</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003795178947750062</v>
+        <v>0.003773868222973254</v>
       </c>
     </row>
     <row r="30">
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>65240</v>
+        <v>65730</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2796169351205883</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1903433476394849</v>
+        <v>0.1814696485623004</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.597697476708094</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>130.4</v>
+        <v>130</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4524,7 +4524,7 @@
         <v>-0.1015050373826717</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.04356595092024551</v>
+        <v>0.04677692307692327</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.633110184102825</v>
@@ -4616,7 +4616,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1486</v>
+        <v>1503</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4633,7 +4633,7 @@
         <v>0.03058070181718849</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.239165545087483</v>
+        <v>0.2251497005988023</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.628739615003775</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>803.9</v>
+        <v>799</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.1493500568084806</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.5648712526433637</v>
+        <v>0.574468085106383</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>2.959294007975387</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>109.9</v>
+        <v>109.6</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9231</v>
+        <v>9177</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.007451126824951393</v>
+        <v>-0.005877567944558518</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1622341098472537</v>
+        <v>0.1658817338999672</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.706788410396121</v>
+        <v>1.706721877584554</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.719601378354602</v>
+        <v>1.716812560054344</v>
       </c>
       <c r="BC3" s="8" t="n">
         <v>1.726027397260274</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005858957055889047</v>
+        <v>0.005859185454488079</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>110.7</v>
+        <v>111.6</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>106</v>
+        <v>106.1</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02201110633407521</v>
+        <v>0.02013230751476978</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.1696603773584906</v>
+        <v>0.1780584354382659</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.354696263642233</v>
+        <v>4.356604803264308</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.26090894380043</v>
+        <v>4.270627222735255</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.726027397260274</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002296371410215435</v>
+        <v>0.002295365416782174</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6525</v>
+        <v>6503</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.04732530347084083</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.505977011494253</v>
+        <v>1.514454866984468</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2547945205479452</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>279.9</v>
+        <v>271.4</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21350</v>
+        <v>21250</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1153122696775186</v>
+        <v>-0.1111101718485865</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.04880562060889937</v>
+        <v>0.02174117647058815</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.504401306799538</v>
+        <v>6.497131556586003</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.352200198852753</v>
+        <v>7.309265277675426</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.901369863013699</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001537420513944343</v>
+        <v>0.001539140759719297</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>113.6</v>
+        <v>113.2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21350</v>
+        <v>21250</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05733283533690949</v>
+        <v>-0.05559695960061107</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2770023419203747</v>
+        <v>0.2784941176470588</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.916319198176364</v>
+        <v>1.916306455655834</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.032869362603987</v>
+        <v>2.029119320544993</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>1.898630136986301</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005218337325804775</v>
+        <v>0.0052183720252498</v>
       </c>
     </row>
     <row r="8">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>96.59999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1617,16 +1617,16 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.0445523307779236</v>
+        <v>0.04583403527452132</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.137481079268293</v>
+        <v>3.133197972560976</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8383561643835618</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.8025985292275413</v>
+        <v>0.8016149179573233</v>
       </c>
       <c r="BC8" s="8" t="n">
         <v>0.810958904109589</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>196.1</v>
+        <v>194</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1619063415684573</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>3.082202957674656</v>
+        <v>3.126391752577319</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.617785071156441</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>113.9</v>
+        <v>111.2</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12430</v>
+        <v>12200</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.01166874967617452</v>
+        <v>-0.005913003718690617</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.466130329847144</v>
+        <v>0.4583606557377049</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.078886135575507</v>
+        <v>4.075988335536971</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.127043573942506</v>
+        <v>4.100233028683072</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.235616438356164</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002451649707203473</v>
+        <v>0.002453392693206174</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1149</v>
+        <v>1152</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03931213828554555</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4173489295039163</v>
+        <v>0.4136579166666665</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.60321544149022</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2211,7 +2211,7 @@
         <v>-0.1186163405096527</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.005687203791469031</v>
+        <v>0.01047619047619053</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.192153148044506</v>
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>248.8</v>
+        <v>247.5</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1938446141007949</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.01123522909967845</v>
+        <v>0.01654676767676766</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.123355517403693</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>76.59999999999999</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2429,7 +2429,7 @@
         <v>-0.1844707502926064</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.2073955613577025</v>
+        <v>0.2153285151116953</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.877502430670157</v>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>113</v>
+        <v>113.2</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18600</v>
+        <v>18410</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.04466374389046267</v>
+        <v>-0.04563557511279162</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1398322150537634</v>
+        <v>0.1536340510592071</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.727914615705354</v>
+        <v>1.727937252261324</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.808697832470031</v>
+        <v>1.810563352113151</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.726027397260274</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005787323001442342</v>
+        <v>0.005787247185575263</v>
       </c>
     </row>
     <row r="17">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>95.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>80.90000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.06425495011031726</v>
+        <v>0.0617496695092544</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8373918417799753</v>
+        <v>0.8669576059850372</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.970158315384524</v>
+        <v>2.971552124865073</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.790833451210772</v>
+        <v>2.798731386691685</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.23013698630137</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.0033668238989831</v>
+        <v>0.003365244686883647</v>
       </c>
     </row>
     <row r="18">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>88.8</v>
+        <v>89</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2781,7 +2781,7 @@
         <v>4.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>111.5</v>
+        <v>105</v>
       </c>
       <c r="AK18" s="10" t="n">
         <v>46924</v>
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1247472620982728</v>
+        <v>0.1232802479770389</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>2.344932735426009</v>
+        <v>2.56</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.699848316345822</v>
+        <v>1.69991125620254</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.511315807228256</v>
+        <v>1.513345631478857</v>
       </c>
       <c r="BC18" s="8" t="n">
         <v>1.726027397260274</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005882877844946237</v>
+        <v>0.005882660029170681</v>
       </c>
     </row>
     <row r="19">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>145.5</v>
+        <v>144.3</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.02905807884910312</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5284536082474227</v>
+        <v>0.5411642411642412</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.162134842902535</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>29060</v>
+        <v>28980</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.586885041673852</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.0001486978664830829</v>
+        <v>0.002909632850241595</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.405311400039203</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>448.4</v>
+        <v>453</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03839054472234518</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.4957224531668152</v>
+        <v>0.4805341015452538</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7534246575342467</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102.3</v>
+        <v>101.7</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>220</v>
+        <v>219.8</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.05752489343604983</v>
+        <v>0.06073572241461278</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.0694999999999999</v>
+        <v>0.06419472247497726</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.816823025596404</v>
+        <v>1.815968799356659</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.717995516581444</v>
+        <v>1.711989858532214</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>1.991780821917808</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005504113421678662</v>
+        <v>0.005506702540012081</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10040</v>
+        <v>10020</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.02697730694031901</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5985606451195218</v>
+        <v>0.6017513849301397</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.29242236883649</v>
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>36.3</v>
+        <v>33.4</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3480,7 +3480,7 @@
         <v>0.1729201238719515</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.2875721768595041</v>
+        <v>0.3993673658682633</v>
       </c>
       <c r="BA24" s="8" t="n">
         <v>2.87931194346769</v>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1168</v>
+        <v>1129</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.05082170930906543</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5835781643835618</v>
+        <v>0.6382810416297608</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2493150684931507</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>11880</v>
+        <v>11820</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-3.123806152281406</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.1258117993265995</v>
+        <v>0.131526580033841</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14620</v>
+        <v>14280</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.1393624104764262</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.3352229822161421</v>
+        <v>0.3670140056022408</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.649801055353615</v>
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>564.6</v>
+        <v>560.1</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4192,7 +4192,7 @@
         <v>0.05730312045536456</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.7169703896563939</v>
+        <v>0.7307650098196752</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.599232534484579</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>65730</v>
+        <v>65540</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2796169351205883</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1814696485623004</v>
+        <v>0.1848947207812024</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.597697476708094</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>130</v>
+        <v>131.5</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4524,7 +4524,7 @@
         <v>-0.1015050373826717</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.04677692307692327</v>
+        <v>0.03483650190114074</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.633110184102825</v>
@@ -4616,7 +4616,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4633,7 +4633,7 @@
         <v>0.03058070181718849</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2251497005988023</v>
+        <v>0.2275999999999998</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.628739615003775</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1493500568084806</v>
+        <v>0.1494389982290459</v>
       </c>
       <c r="AZ2" s="12" t="n">
         <v>0.574468085106383</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.959294007975387</v>
+        <v>2.956505972606375</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.57475430609258</v>
+        <v>2.572129514625394</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.23013698630137</v>
+        <v>3.227397260273972</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003379184350405772</v>
+        <v>0.003382370978667184</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.005877567944558518</v>
+        <v>-0.005956942554963774</v>
       </c>
       <c r="AZ3" s="12" t="n">
         <v>0.1658817338999672</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.706721877584554</v>
+        <v>1.703985507432241</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.716812560054344</v>
+        <v>1.714196879772947</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.726027397260274</v>
+        <v>1.723287671232877</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005859185454488079</v>
+        <v>0.005868594513499786</v>
       </c>
     </row>
     <row r="4">
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02013230751476978</v>
+        <v>0.02011891388123976</v>
       </c>
       <c r="AZ4" s="12" t="n">
         <v>0.1780584354382659</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.356604803264308</v>
+        <v>4.353878662631438</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.270627222735255</v>
+        <v>4.268010918517592</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.726027397260274</v>
+        <v>4.723287671232876</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002295365416782174</v>
+        <v>0.002296802638490643</v>
       </c>
     </row>
     <row r="5">
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.04732530347084083</v>
+        <v>0.04770769809333015</v>
       </c>
       <c r="AZ5" s="12" t="n">
         <v>1.514454866984468</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.2547945205479452</v>
+        <v>0.252054794520548</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.24328116555912</v>
+        <v>0.2405774005280763</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.2273972602739726</v>
+        <v>0.2246575342465753</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.03924731182795699</v>
+        <v>0.03967391304347826</v>
       </c>
     </row>
     <row r="6">
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21250</v>
+        <v>21420</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1111101718485865</v>
+        <v>-0.1111598572355574</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02174117647058815</v>
+        <v>0.01363211951447241</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.497131556586003</v>
+        <v>6.49447836714229</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.309265277675426</v>
+        <v>7.306688857394951</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>6.901369863013699</v>
+        <v>6.898630136986301</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001539140759719297</v>
+        <v>0.001539769544940407</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21250</v>
+        <v>21420</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05559695960061107</v>
+        <v>-0.05568325484130165</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2784941176470588</v>
+        <v>0.2683473389355742</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.916306455655834</v>
+        <v>1.913567363087068</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.029119320544993</v>
+        <v>2.026404141298459</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>1.898630136986301</v>
+        <v>1.895890410958904</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.0052183720252498</v>
+        <v>0.005225841636359994</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1968</v>
+        <v>1975</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04583403527452132</v>
+        <v>0.04597549415849128</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.133197972560976</v>
+        <v>3.118548663291139</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.8383561643835618</v>
+        <v>0.8356164383561644</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.8016149179573233</v>
+        <v>0.7988872043588697</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.810958904109589</v>
+        <v>0.8082191780821918</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.0119281045751634</v>
+        <v>0.0119672131147541</v>
       </c>
     </row>
     <row r="9">
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1619063415684573</v>
+        <v>0.1620976616245981</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>3.126391752577319</v>
+        <v>3.191204188481676</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.617785071156441</v>
+        <v>1.615037825573978</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.392354110893821</v>
+        <v>1.389760842747222</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.646575342465753</v>
+        <v>1.643835616438356</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006181290814392112</v>
+        <v>0.006191805443594513</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12200</v>
+        <v>12220</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.005913003718690617</v>
+        <v>-0.005928835479311641</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4583606557377049</v>
+        <v>0.4559738134206219</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.075988335536971</v>
+        <v>4.073256626250636</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.100233028683072</v>
+        <v>4.097550328013629</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.235616438356164</v>
+        <v>4.232876712328767</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002453392693206174</v>
+        <v>0.002455038048806866</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03931213828554555</v>
+        <v>0.0392972019234907</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4136579166666665</v>
+        <v>0.4185835540069685</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.60321544149022</v>
+        <v>2.600479007427757</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.504748425034752</v>
+        <v>2.502151456402357</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.726027397260274</v>
+        <v>2.723287671232877</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003841403151125849</v>
+        <v>0.003845445385806603</v>
       </c>
     </row>
     <row r="12">
@@ -2111,7 +2111,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>-0.09863013698630137</v>
+        <v>-0.1013698630136986</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>210</v>
+        <v>210.6</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1186163405096527</v>
+        <v>-0.1187038614666475</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.01047619047619053</v>
+        <v>0.007597340930674212</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.192153148044506</v>
+        <v>4.189492633215793</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.756331823156994</v>
+        <v>4.753785305570407</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.476712328767123</v>
+        <v>4.473972602739726</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002385409036085586</v>
+        <v>0.002386923877301139</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>247.5</v>
+        <v>248</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2317,22 +2317,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1938446141007949</v>
+        <v>-0.1940096469592627</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.01654676767676766</v>
+        <v>0.01449727822580638</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.123355517403693</v>
+        <v>3.120671664243623</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.874383986059744</v>
+        <v>3.871847414141314</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.23013698630137</v>
+        <v>3.227397260273972</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003201684836797752</v>
+        <v>0.003204438363246959</v>
       </c>
     </row>
     <row r="15">
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>169.7</v>
+        <v>167.5</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>76.09999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1844707502926064</v>
+        <v>-0.1792923555127194</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.2153285151116953</v>
+        <v>0.1886393229166667</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.877502430670157</v>
+        <v>1.873548312420406</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.302188954404507</v>
+        <v>2.282844963130403</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>1.991780821917808</v>
+        <v>1.989041095890411</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.00532622479558154</v>
+        <v>0.005337465777480361</v>
       </c>
     </row>
     <row r="16">
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18410</v>
+        <v>18510</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.04563557511279162</v>
+        <v>-0.0457396495122239</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1536340510592071</v>
+        <v>0.1474015602377095</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.727937252261324</v>
+        <v>1.725199950468022</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.810563352113151</v>
+        <v>1.80789231113519</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.726027397260274</v>
+        <v>1.723287671232877</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005787247185575263</v>
+        <v>0.0057964295659104</v>
       </c>
     </row>
     <row r="17">
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.0617496695092544</v>
+        <v>0.06175955013784563</v>
       </c>
       <c r="AZ17" s="12" t="n">
         <v>0.8669576059850372</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.971552124865073</v>
+        <v>2.968806908590064</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.798731386691685</v>
+        <v>2.796119807167857</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.23013698630137</v>
+        <v>3.227397260273972</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003365244686883647</v>
+        <v>0.003368356483901194</v>
       </c>
     </row>
     <row r="18">
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1232802479770389</v>
+        <v>0.1233905994162098</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>2.56</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.69991125620254</v>
+        <v>1.697166795435657</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.513345631478857</v>
+        <v>1.510753958879147</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.726027397260274</v>
+        <v>1.723287671232877</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005882660029170681</v>
+        <v>0.005892172782836607</v>
       </c>
     </row>
     <row r="19">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>144.3</v>
+        <v>145.7</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.02905807884910312</v>
+        <v>0.02904463721385509</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5411642411642412</v>
+        <v>0.5263555250514758</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.162134842902535</v>
+        <v>3.159402075307331</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.07284390249291</v>
+        <v>3.070228405117033</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.391780821917808</v>
+        <v>3.389041095890411</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.00316242048388454</v>
+        <v>0.003165155862293105</v>
       </c>
     </row>
     <row r="20">
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>362</v>
+        <v>362.5</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>28980</v>
+        <v>29310</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.586885041673852</v>
+        <v>-0.5880078026568221</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.002909632850241595</v>
+        <v>-0.007012444558171405</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.405311400039203</v>
+        <v>1.402601579193074</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.40174416761189</v>
+        <v>3.404437239923615</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.389041095890411</v>
+        <v>1.386301369863014</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.007115860584153118</v>
+        <v>0.007129608399381003</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3124,22 +3124,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03839054472234518</v>
+        <v>0.03839640549883393</v>
       </c>
       <c r="AZ21" s="12" t="n">
         <v>0.4805341015452538</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.7534246575342467</v>
+        <v>0.7506849315068491</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.7255696436793968</v>
+        <v>0.722927128340962</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.726027397260274</v>
+        <v>0.7232876712328767</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01327272727272727</v>
+        <v>0.01332116788321168</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101.7</v>
+        <v>108.9</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>219.8</v>
+        <v>223.6</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.06073572241461278</v>
+        <v>0.02395510290556944</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.06419472247497726</v>
+        <v>0.120169946332737</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.815968799356659</v>
+        <v>1.822943918888303</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.711989858532214</v>
+        <v>1.780296727576754</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>1.991780821917808</v>
+        <v>1.989041095890411</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005506702540012081</v>
+        <v>0.005485632276662883</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10020</v>
+        <v>10110</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02697730694031901</v>
+        <v>0.02699118018014566</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.6017513849301397</v>
+        <v>0.5874924705242333</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.29242236883649</v>
+        <v>4.289680522474748</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.179666230040598</v>
+        <v>4.176939982797408</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.317808219178082</v>
+        <v>4.315068493150685</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002329686862271807</v>
+        <v>0.00233117593433996</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1729201238719515</v>
+        <v>0.1730178913816333</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.3993673658682633</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.87931194346769</v>
+        <v>2.876508273795126</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.454823550953097</v>
+        <v>2.452228815032859</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.23013698630137</v>
+        <v>3.227397260273972</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003473051963920426</v>
+        <v>0.00347643707167457</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>29</v>
+        <v>29.8</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.3453366036893714</v>
+        <v>0.345598017950363</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.6172413793103448</v>
+        <v>0.5738255033557047</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.793343306175603</v>
+        <v>2.7904220615658</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.076315546990473</v>
+        <v>2.073741209738267</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.23013698630137</v>
+        <v>3.227397260273972</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003579939486096004</v>
+        <v>0.003583687262846775</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3699,22 +3699,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>79.61176711614394</v>
+        <v>80.42838505732709</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.3144705882352941</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.2547945205479452</v>
+        <v>0.252054794520548</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.003160760887189609</v>
+        <v>0.003095416841966063</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.2273972602739726</v>
+        <v>0.2246575342465753</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.03924731182795699</v>
+        <v>0.03967391304347826</v>
       </c>
     </row>
     <row r="27">
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1129</v>
+        <v>1113</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3808,22 +3808,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05082170930906543</v>
+        <v>0.05108145628162595</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.6382810416297608</v>
+        <v>0.6618322515723272</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.2493150684931507</v>
+        <v>0.2465753424657534</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.2372572495262588</v>
+        <v>0.2345920394581542</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.2273972602739726</v>
+        <v>0.2246575342465753</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.04010989010989011</v>
+        <v>0.04055555555555556</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>11820</v>
+        <v>11660</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3938,15 +3938,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-3.123806152281406</v>
+        <v>-3.157782121840622</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.131526580033841</v>
+        <v>0.1470535313893655</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.2273972602739726</v>
+        <v>0.2246575342465753</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14280</v>
+        <v>14140</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1393624104764262</v>
+        <v>-0.1395221526651917</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.3670140056022408</v>
+        <v>0.3805487977369164</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.649801055353615</v>
+        <v>2.647090733858501</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.07888138701968</v>
+        <v>3.076303175099091</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.726027397260274</v>
+        <v>2.723287671232877</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003773868222973254</v>
+        <v>0.003777732237165749</v>
       </c>
     </row>
     <row r="30">
@@ -4189,22 +4189,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05730312045536456</v>
+        <v>0.05730439036558674</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.7307650098196752</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.599232534484579</v>
+        <v>2.596492526078686</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.458360790011789</v>
+        <v>2.455766333459459</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.726027397260274</v>
+        <v>2.723287671232877</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003847289485387644</v>
+        <v>0.003851349426028332</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.08278012879652392</v>
+        <v>0.08280271623610196</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.524854934844193</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.143093615550243</v>
+        <v>2.140348236379154</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.979250965689797</v>
+        <v>1.976674240178446</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.298630136986302</v>
+        <v>2.295890410958904</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004666151738514923</v>
+        <v>0.004672136912130284</v>
       </c>
     </row>
     <row r="32">
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>65540</v>
+        <v>65840</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4412,22 +4412,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2796169351205883</v>
+        <v>-0.2800498265795348</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1848947207812024</v>
+        <v>0.1794957472660996</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.597697476708094</v>
+        <v>1.594973514957111</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.217844303399248</v>
+        <v>2.215394306219043</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.6</v>
+        <v>1.597260273972603</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.006259007193654748</v>
+        <v>0.006269696585067684</v>
       </c>
     </row>
     <row r="33">
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>131.5</v>
+        <v>132.1</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.1015050373826717</v>
+        <v>-0.10163856066971</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.03483650190114074</v>
+        <v>0.03013626040878137</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.633110184102825</v>
+        <v>2.630397672629992</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.930578682859321</v>
+        <v>2.927994855379033</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.726027397260274</v>
+        <v>2.723287671232877</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003797790179983404</v>
+        <v>0.003801706526755531</v>
       </c>
     </row>
     <row r="34">
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03058070181718849</v>
+        <v>0.03055771778294077</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.2275999999999998</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.628739615003775</v>
+        <v>1.626000796392671</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.580409580862394</v>
+        <v>1.57778721980824</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.646575342465753</v>
+        <v>1.643835616438356</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.006139716814081927</v>
+        <v>0.006150058488400059</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.1494389982290459</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.574468085106383</v>
+        <v>0.5764411027568923</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>2.956505972606375</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9177</v>
+        <v>9063</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.005956942554963774</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1658817338999672</v>
+        <v>0.180546912942734</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.703985507432241</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>111.6</v>
+        <v>112.1</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>106.1</v>
+        <v>105.7</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02011891388123976</v>
+        <v>0.019082919462173</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.1780584354382659</v>
+        <v>0.1878145695364239</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.353878662631438</v>
+        <v>4.354928620615905</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.268010918517592</v>
+        <v>4.27338005322888</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.723287671232876</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002296802638490643</v>
+        <v>0.002296248887446915</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6503</v>
+        <v>6610</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.04770769809333015</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.514454866984468</v>
+        <v>1.47375189107413</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.252054794520548</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>271.4</v>
+        <v>279.7</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21420</v>
+        <v>21820</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1111598572355574</v>
+        <v>-0.1152661124481381</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.01363211951447241</v>
+        <v>0.02548120989917502</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.49447836714229</v>
+        <v>6.501582264967062</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.306688857394951</v>
+        <v>7.348630312960571</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.898630136986301</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001539769544940407</v>
+        <v>0.001538087129018379</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21420</v>
+        <v>21820</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.05568325484130165</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2683473389355742</v>
+        <v>0.245096241979835</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.913567363087068</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1975</v>
+        <v>1966</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04597549415849128</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.118548663291139</v>
+        <v>3.137402650050864</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8356164383561644</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>191</v>
+        <v>191.7</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1620976616245981</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>3.191204188481676</v>
+        <v>3.175899843505477</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.615037825573978</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>111.2</v>
+        <v>113.9</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12220</v>
+        <v>12340</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.005928835479311641</v>
+        <v>-0.01168806008300443</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4559738134206219</v>
+        <v>0.4768233387358185</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.073256626250636</v>
+        <v>4.076156075188901</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.097550328013629</v>
+        <v>4.124361864464817</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.232876712328767</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002455038048806866</v>
+        <v>0.002453291732588177</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1148</v>
+        <v>1152</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.0392972019234907</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4185835540069685</v>
+        <v>0.4136579166666665</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.600479007427757</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>210.6</v>
+        <v>207</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2211,7 +2211,7 @@
         <v>-0.1187038614666475</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.007597340930674212</v>
+        <v>0.02512077294685988</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.189492633215793</v>
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>248</v>
+        <v>247.5</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1940096469592627</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.01449727822580638</v>
+        <v>0.01654676767676766</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.120671664243623</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>167.5</v>
+        <v>169.7</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>76.8</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1792923555127194</v>
+        <v>-0.1847609418851515</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1886393229166667</v>
+        <v>0.2315113182423438</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.873548312420406</v>
+        <v>1.874830639173762</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.282844963130403</v>
+        <v>2.299731128571175</v>
       </c>
       <c r="BC15" s="8" t="n">
         <v>1.989041095890411</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005337465777480361</v>
+        <v>0.005333815114311873</v>
       </c>
     </row>
     <row r="16">
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18510</v>
+        <v>18610</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2538,7 +2538,7 @@
         <v>-0.0457396495122239</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1474015602377095</v>
+        <v>0.1412360494357874</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.725199950468022</v>
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>80.2</v>
+        <v>78.5</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2668,7 +2668,7 @@
         <v>0.06175955013784563</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8669576059850372</v>
+        <v>0.9073885350318469</v>
       </c>
       <c r="BA17" s="8" t="n">
         <v>2.968806908590064</v>
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105.9</v>
+        <v>107.3</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>145.7</v>
+        <v>151.5</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.02904463721385509</v>
+        <v>0.02488573350604409</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5263555250514758</v>
+        <v>0.4873267326732673</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.159402075307331</v>
+        <v>3.161550232605037</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.070228405117033</v>
+        <v>3.08478314142363</v>
       </c>
       <c r="BC19" s="8" t="n">
         <v>3.389041095890411</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003165155862293105</v>
+        <v>0.003163005255102417</v>
       </c>
     </row>
     <row r="20">
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>362.5</v>
+        <v>378.2</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>29310</v>
+        <v>30420</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5880078026568221</v>
+        <v>-0.6002206536451652</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.007012444558171405</v>
+        <v>-0.001808360420775923</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.402601579193074</v>
+        <v>1.402926990175111</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.404437239923615</v>
+        <v>3.509253299268507</v>
       </c>
       <c r="BC20" s="8" t="n">
         <v>1.386301369863014</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.007129608399381003</v>
+        <v>0.007127954676210069</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>453</v>
+        <v>447.3</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03839640549883393</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.4805341015452538</v>
+        <v>0.4994007332886203</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7506849315068491</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>108.9</v>
+        <v>102</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>223.6</v>
+        <v>218.4</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.02395510290556944</v>
+        <v>0.05911582503842886</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.120169946332737</v>
+        <v>0.07417582417582413</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.822943918888303</v>
+        <v>1.813660184345875</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.780296727576754</v>
+        <v>1.712428557358274</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>1.989041095890411</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005485632276662883</v>
+        <v>0.005513712042813939</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10110</v>
+        <v>10190</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.02699118018014566</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5874924705242333</v>
+        <v>0.5750293304219822</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.289680522474748</v>
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>46.9</v>
+        <v>48.9</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.345598017950363</v>
+        <v>0.3270906654498866</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.5738255033557047</v>
+        <v>0.6409395973154361</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.7904220615658</v>
+        <v>2.803203161281068</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.073741209738267</v>
+        <v>2.112292124615899</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.227397260273972</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003583687262846775</v>
+        <v>0.003567347575132581</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1113</v>
+        <v>1143</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.05108145628162595</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.6618322515723272</v>
+        <v>0.6182146071741033</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2465753424657534</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>11660</v>
+        <v>11470</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-3.157782121840622</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.1470535313893655</v>
+        <v>0.1660544181342634</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14140</v>
+        <v>14240</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.1395221526651917</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.3805487977369164</v>
+        <v>0.3708539325842697</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.647090733858501</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>65840</v>
+        <v>66740</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2800498265795348</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1794957472660996</v>
+        <v>0.1635900509439616</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.594973514957111</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>132.1</v>
+        <v>132.4</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4524,7 +4524,7 @@
         <v>-0.10163856066971</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.03013626040878137</v>
+        <v>0.02780211480362538</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.630397672629992</v>
@@ -4616,7 +4616,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1500</v>
+        <v>1509</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4633,7 +4633,7 @@
         <v>0.03055771778294077</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2275999999999998</v>
+        <v>0.2202783300198807</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.626000796392671</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>798</v>
+        <v>790.3</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.1494389982290459</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.5764411027568923</v>
+        <v>0.5918005820574466</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>2.956505972606375</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9063</v>
+        <v>9219</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.005956942554963774</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.180546912942734</v>
+        <v>0.1605701998047508</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.703985507432241</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112.1</v>
+        <v>112</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>105.7</v>
+        <v>105.6</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.019082919462173</v>
+        <v>0.01928964793997449</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.1878145695364239</v>
+        <v>0.187878787878788</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.354928620615905</v>
+        <v>4.354719242820756</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.27338005322888</v>
+        <v>4.272307927017428</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.723287671232876</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002296248887446915</v>
+        <v>0.002296359292619409</v>
       </c>
     </row>
     <row r="5">
@@ -1201,7 +1201,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>99.09999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6610</v>
+        <v>6590</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,16 +1272,16 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.04770769809333015</v>
+        <v>0.05978953853035893</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.47375189107413</v>
+        <v>1.473748103186646</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.252054794520548</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.2405774005280763</v>
+        <v>0.2378347637494891</v>
       </c>
       <c r="BC5" s="8" t="n">
         <v>0.2246575342465753</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21820</v>
+        <v>21250</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.1152661124481381</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02548120989917502</v>
+        <v>0.05298823529411756</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.501582264967062</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21820</v>
+        <v>21250</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.05568325484130165</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.245096241979835</v>
+        <v>0.2784941176470588</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.913567363087068</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1966</v>
+        <v>1917</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04597549415849128</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.137402650050864</v>
+        <v>3.243157856025039</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8356164383561644</v>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>84</v>
+        <v>84.2</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>191.7</v>
+        <v>192</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1620976616245981</v>
+        <v>0.160418263423683</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>3.175899843505477</v>
+        <v>3.179302083333333</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.615037825573978</v>
+        <v>1.615103835920002</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.389760842747222</v>
+        <v>1.391829038569955</v>
       </c>
       <c r="BC9" s="8" t="n">
         <v>1.643835616438356</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006191805443594513</v>
+        <v>0.006191552380472033</v>
       </c>
     </row>
     <row r="10">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>113.9</v>
+        <v>112.4</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12340</v>
+        <v>12210</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.01168806008300443</v>
+        <v>-0.008509983013531095</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4768233387358185</v>
+        <v>0.4728910728910729</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.076156075188901</v>
+        <v>4.074560244060455</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.124361864464817</v>
+        <v>4.109532294076605</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.232876712328767</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002453291732588177</v>
+        <v>0.002454252582122732</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>104</v>
+        <v>105.1</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1152</v>
+        <v>1181</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.0392972019234907</v>
+        <v>0.03515570821260949</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4136579166666665</v>
+        <v>0.3935298882303131</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.600479007427757</v>
+        <v>2.601390842249824</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.502151456402357</v>
+        <v>2.513043034599705</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.723287671232877</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003845445385806603</v>
+        <v>0.003844097487231661</v>
       </c>
     </row>
     <row r="12">
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>212.2</v>
+        <v>210.5</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>207</v>
+        <v>206.8</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1187038614666475</v>
+        <v>-0.1170316143044057</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.02512077294685988</v>
+        <v>0.01789168278529973</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.189492633215793</v>
+        <v>4.187976895795471</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.753785305570407</v>
+        <v>4.743065509073943</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.473972602739726</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002386923877301139</v>
+        <v>0.002387787766938142</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>247.5</v>
+        <v>243.7</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1940096469592627</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.01654676767676766</v>
+        <v>0.03239772260976626</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.120671664243623</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>169.7</v>
+        <v>167.1</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>75.09999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1847609418851515</v>
+        <v>-0.178286286874268</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.2315113182423438</v>
+        <v>0.1998616600790513</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.874830639173762</v>
+        <v>1.873311913636397</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.299731128571175</v>
+        <v>2.279762262346178</v>
       </c>
       <c r="BC15" s="8" t="n">
         <v>1.989041095890411</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005333815114311873</v>
+        <v>0.005338139328110292</v>
       </c>
     </row>
     <row r="16">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>113.2</v>
+        <v>112.7</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18610</v>
+        <v>18250</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.0457396495122239</v>
+        <v>-0.04330151801210644</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1412360494357874</v>
+        <v>0.1586078728767124</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.725199950468022</v>
+        <v>1.725143161548407</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.80789231113519</v>
+        <v>1.803225565868764</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.723287671232877</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.0057964295659104</v>
+        <v>0.005796620374986428</v>
       </c>
     </row>
     <row r="17">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>96.59999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>78.5</v>
+        <v>78</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.06175955013784563</v>
+        <v>0.06283108234275304</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9073885350318469</v>
+        <v>0.9136538461538459</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.968806908590064</v>
+        <v>2.968211182507234</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.796119807167857</v>
+        <v>2.792740287538951</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.227397260273972</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003368356483901194</v>
+        <v>0.003369032519968153</v>
       </c>
     </row>
     <row r="18">
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>107.3</v>
+        <v>106.2</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>151.5</v>
+        <v>157</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.02488573350604409</v>
+        <v>0.02814728861430701</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4873267326732673</v>
+        <v>0.4205095541401274</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.161550232605037</v>
+        <v>3.159866385886339</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.08478314142363</v>
+        <v>3.073359644944521</v>
       </c>
       <c r="BC19" s="8" t="n">
         <v>3.389041095890411</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003163005255102417</v>
+        <v>0.003164690774478748</v>
       </c>
     </row>
     <row r="20">
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>378.2</v>
+        <v>365</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>30420</v>
+        <v>29750</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.6002206536451652</v>
+        <v>-0.5900126009065347</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.001808360420775923</v>
+        <v>-0.01495174117647069</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.402926990175111</v>
+        <v>1.402654982283159</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.509253299268507</v>
+        <v>3.42121486022402</v>
       </c>
       <c r="BC20" s="8" t="n">
         <v>1.386301369863014</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.007127954676210069</v>
+        <v>0.007129336954781702</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>447.3</v>
+        <v>453</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03839640549883393</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.4994007332886203</v>
+        <v>0.4805341015452538</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7506849315068491</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102</v>
+        <v>101.8</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>218.4</v>
+        <v>217.1</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.05911582503842886</v>
+        <v>0.06018912327592031</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.07417582417582413</v>
+        <v>0.07848917549516354</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.813660184345875</v>
+        <v>1.813374575286635</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.712428557358274</v>
+        <v>1.710425560378716</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>1.989041095890411</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005513712042813939</v>
+        <v>0.005514580460255613</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10190</v>
+        <v>10200</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.02699118018014566</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5750293304219822</v>
+        <v>0.5734851840196078</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.289680522474748</v>
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>48.9</v>
+        <v>47</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.3270906654498866</v>
+        <v>0.3446471487761645</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.6409395973154361</v>
+        <v>0.5824915824915826</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.803203161281068</v>
+        <v>2.791082183470787</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.112292124615899</v>
+        <v>2.075698584577449</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.227397260273972</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003567347575132581</v>
+        <v>0.003582839681046126</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1143</v>
+        <v>1135</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.05108145628162595</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.6182146071741033</v>
+        <v>0.6296205251101323</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2465753424657534</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>11470</v>
+        <v>11530</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-3.157782121840622</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.1660544181342634</v>
+        <v>0.1599864853425847</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>169.6</v>
+        <v>134</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14240</v>
+        <v>14270</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1395221526651917</v>
+        <v>-0.05988101481176222</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.3708539325842697</v>
+        <v>0.08082690960056049</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.647090733858501</v>
+        <v>2.632047830353444</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.076303175099091</v>
+        <v>2.799696497807068</v>
       </c>
       <c r="BC29" s="8" t="n">
         <v>2.723287671232877</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003777732237165749</v>
+        <v>0.003799323053584916</v>
       </c>
     </row>
     <row r="30">
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>560.1</v>
+        <v>560</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4192,7 +4192,7 @@
         <v>0.05730439036558674</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.7307650098196752</v>
+        <v>0.7310740750000002</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.596492526078686</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>66740</v>
+        <v>67170</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2800498265795348</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1635900509439616</v>
+        <v>0.1561411344350156</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.594973514957111</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>132.4</v>
+        <v>133.8</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4524,7 +4524,7 @@
         <v>-0.10163856066971</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.02780211480362538</v>
+        <v>0.01704783258594933</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.630397672629992</v>
@@ -4616,7 +4616,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1509</v>
+        <v>1495</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4633,7 +4633,7 @@
         <v>0.03055771778294077</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2202783300198807</v>
+        <v>0.231705685618729</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.626000796392671</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1494389982290459</v>
+        <v>0.1495281220610244</v>
       </c>
       <c r="AZ2" s="12" t="n">
         <v>0.5918005820574466</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.956505972606375</v>
+        <v>2.95371783417793</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.572129514625394</v>
+        <v>2.569504631937249</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.227397260273972</v>
+        <v>3.224657534246576</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003382370978667184</v>
+        <v>0.003385563740817907</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.005956942554963774</v>
+        <v>-0.006036557894216882</v>
       </c>
       <c r="AZ3" s="12" t="n">
         <v>0.1605701998047508</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.703985507432241</v>
+        <v>1.701249147481358</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.714196879772947</v>
+        <v>1.711581206525201</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.723287671232877</v>
+        <v>1.720547945205479</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005868594513499786</v>
+        <v>0.005878033805221687</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>114.9</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01928964793997449</v>
+        <v>0.01337112560980665</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.187878787878788</v>
+        <v>0.218636363636364</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.354719242820756</v>
+        <v>4.357946849619954</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.272307927017428</v>
+        <v>4.300445058563825</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.723287671232876</v>
+        <v>4.720547945205479</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002296359292619409</v>
+        <v>0.002294658550246448</v>
       </c>
     </row>
     <row r="5">
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.05978953853035893</v>
+        <v>0.06031230934228432</v>
       </c>
       <c r="AZ5" s="12" t="n">
         <v>1.473748103186646</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.252054794520548</v>
+        <v>0.2493150684931507</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.2378347637494891</v>
+        <v>0.2351336170451532</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.2246575342465753</v>
+        <v>0.2219178082191781</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.03967391304347826</v>
+        <v>0.0401098901098901</v>
       </c>
     </row>
     <row r="6">
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21250</v>
+        <v>21220</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1152661124481381</v>
+        <v>-0.1153171165227908</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.05298823529411756</v>
+        <v>0.05447690857681442</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.501582264967062</v>
+        <v>6.498930182790867</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.348630312960571</v>
+        <v>7.34605620179639</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>6.898630136986301</v>
+        <v>6.895890410958904</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001538087129018379</v>
+        <v>0.001538714791317492</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21250</v>
+        <v>21220</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05568325484130165</v>
+        <v>-0.05576978942999603</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2784941176470588</v>
+        <v>0.2803016022620171</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.913567363087068</v>
+        <v>1.91082827227607</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.026404141298459</v>
+        <v>2.023688980595696</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>1.895890410958904</v>
+        <v>1.893150684931507</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005225841636359994</v>
+        <v>0.005233332657407548</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1917</v>
+        <v>1939</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04597549415849128</v>
+        <v>0.04611788381852741</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.243157856025039</v>
+        <v>3.195014755028365</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.8356164383561644</v>
+        <v>0.8328767123287673</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.7988872043588697</v>
+        <v>0.7961595200806723</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.8082191780821918</v>
+        <v>0.8054794520547945</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.0119672131147541</v>
+        <v>0.01200657894736842</v>
       </c>
     </row>
     <row r="9">
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.160418263423683</v>
+        <v>0.160607387867483</v>
       </c>
       <c r="AZ9" s="12" t="n">
         <v>3.179302083333333</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.615103835920002</v>
+        <v>1.612356675718806</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.391829038569955</v>
+        <v>1.389235233700669</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.643835616438356</v>
+        <v>1.641095890410959</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006191552380472033</v>
+        <v>0.006202101650704485</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12210</v>
+        <v>12160</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.008509983013531095</v>
+        <v>-0.008527398708109875</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4728910728910729</v>
+        <v>0.4789473684210526</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.074560244060455</v>
+        <v>4.071829290955252</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.109532294076605</v>
+        <v>4.106850038669402</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.232876712328767</v>
+        <v>4.23013698630137</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002454252582122732</v>
+        <v>0.002455898635586955</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1181</v>
+        <v>1176</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03515570821260949</v>
+        <v>0.03513704449503973</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.3935298882303131</v>
+        <v>0.3994547602040814</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.601390842249824</v>
+        <v>2.598655221141676</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.513043034599705</v>
+        <v>2.510445582989788</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.723287671232877</v>
+        <v>2.720547945205479</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003844097487231661</v>
+        <v>0.00384814419344428</v>
       </c>
     </row>
     <row r="12">
@@ -2111,7 +2111,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>-0.1013698630136986</v>
+        <v>-0.1041095890410959</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>206.8</v>
+        <v>205.8</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1170316143044057</v>
+        <v>-0.1171184587564298</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.01789168278529973</v>
+        <v>0.02283770651117578</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.187976895795471</v>
+        <v>4.185316003837315</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.743065509073943</v>
+        <v>4.740518187685913</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.473972602739726</v>
+        <v>4.471232876712329</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002387787766938142</v>
+        <v>0.002389305847116796</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>243.7</v>
+        <v>244.1</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2317,22 +2317,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1940096469592627</v>
+        <v>-0.1941749324021536</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.03239772260976626</v>
+        <v>0.03070596067185583</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.120671664243623</v>
+        <v>3.11798788242899</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.871847414141314</v>
+        <v>3.869311104609428</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.227397260273972</v>
+        <v>3.224657534246576</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003204438363246959</v>
+        <v>0.003207196556584996</v>
       </c>
     </row>
     <row r="15">
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.178286286874268</v>
+        <v>-0.1785709517835199</v>
       </c>
       <c r="AZ15" s="12" t="n">
         <v>0.1998616600790513</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.873311913636397</v>
+        <v>1.949002189203464</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.279762262346178</v>
+        <v>2.372696940089003</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>1.989041095890411</v>
+        <v>1.986301369863014</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005338139328110292</v>
+        <v>0.005130830563144154</v>
       </c>
     </row>
     <row r="16">
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18250</v>
+        <v>18340</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.04330151801210644</v>
+        <v>-0.04340244481403007</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1586078728767124</v>
+        <v>0.1529222290076337</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.725143161548407</v>
+        <v>1.722405786175503</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.803225565868764</v>
+        <v>1.800554242312123</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.723287671232877</v>
+        <v>1.720547945205479</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005796620374986428</v>
+        <v>0.005805832795188403</v>
       </c>
     </row>
     <row r="17">
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.06283108234275304</v>
+        <v>0.06284184375592114</v>
       </c>
       <c r="AZ17" s="12" t="n">
         <v>0.9136538461538459</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.968211182507234</v>
+        <v>2.96546547036928</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.792740287538951</v>
+        <v>2.790128642178574</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.227397260273972</v>
+        <v>3.224657534246576</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003369032519968153</v>
+        <v>0.00337215189315785</v>
       </c>
     </row>
     <row r="18">
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1233905994162098</v>
+        <v>0.1235013341863834</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>2.56</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.697166795435657</v>
+        <v>1.694422318269051</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.510753958879147</v>
+        <v>1.508162266221176</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.723287671232877</v>
+        <v>1.720547945205479</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005892172782836607</v>
+        <v>0.005901716409292561</v>
       </c>
     </row>
     <row r="19">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.02814728861430701</v>
+        <v>0.02813317120455302</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4205095541401274</v>
+        <v>0.385217391304348</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.159866385886339</v>
+        <v>3.157133960991176</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.073359644944521</v>
+        <v>3.070744188996745</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.389041095890411</v>
+        <v>3.386301369863014</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003164690774478748</v>
+        <v>0.003167429739617548</v>
       </c>
     </row>
     <row r="20">
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>29750</v>
+        <v>29950</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5900126009065347</v>
+        <v>-0.590733507210915</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.01495174117647069</v>
+        <v>-0.02152969282136896</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.402654982283159</v>
+        <v>1.399934460906896</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.42121486022402</v>
+        <v>3.420593880937013</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.386301369863014</v>
+        <v>1.383561643835616</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.007129336954781702</v>
+        <v>0.007143191541639646</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>453</v>
+        <v>452.7</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3124,22 +3124,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03839640549883393</v>
+        <v>0.03840233560404845</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.4805341015452538</v>
+        <v>0.4815152374641041</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.7506849315068491</v>
+        <v>0.7479452054794522</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.722927128340962</v>
+        <v>0.7202845947417534</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.7232876712328767</v>
+        <v>0.7205479452054795</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01332116788321168</v>
+        <v>0.01336996336996337</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101.8</v>
+        <v>102.9</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>217.1</v>
+        <v>226.5</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.06018912327592031</v>
+        <v>0.05430838372315997</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.07848917549516354</v>
+        <v>0.04490066225165568</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.813374575286635</v>
+        <v>1.935476932618022</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.710425560378716</v>
+        <v>1.835778755531777</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>1.989041095890411</v>
+        <v>1.986301369863014</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005514580460255613</v>
+        <v>0.005166685188272176</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10200</v>
+        <v>10260</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02699118018014566</v>
+        <v>0.02700507140079333</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5734851840196078</v>
+        <v>0.564283516276803</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.289680522474748</v>
+        <v>4.286938673300265</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.176939982797408</v>
+        <v>4.174213733387951</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.315068493150685</v>
+        <v>4.312328767123287</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.00233117593433996</v>
+        <v>0.002332666912704301</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1730178913816333</v>
+        <v>0.1731158715329388</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.3993673658682633</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.876508273795126</v>
+        <v>2.873704460140817</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.452228815032859</v>
+        <v>2.449633944842702</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.227397260273972</v>
+        <v>3.224657534246576</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.00347643707167457</v>
+        <v>0.003479828958998094</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>29.7</v>
+        <v>30.4</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.3446471487761645</v>
+        <v>0.3089672501445484</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.5824915824915826</v>
+        <v>0.6776315789473686</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.791082183470787</v>
+        <v>2.812839486039933</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.075698584577449</v>
+        <v>2.148899818333356</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.227397260273972</v>
+        <v>3.224657534246576</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003582839681046126</v>
+        <v>0.00355512642994021</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3685,7 +3685,7 @@
         <v>0.55865</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AK26" s="10" t="n">
         <v>46377</v>
@@ -3699,22 +3699,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>80.42838505732709</v>
+        <v>81.26300746542961</v>
       </c>
       <c r="AZ26" s="12" t="n">
-        <v>0.3144705882352941</v>
+        <v>0.1761052631578948</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.252054794520548</v>
+        <v>0.2493150684931507</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.003095416841966063</v>
+        <v>0.003030706950483465</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.2246575342465753</v>
+        <v>0.2219178082191781</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.03967391304347826</v>
+        <v>0.04010989010989011</v>
       </c>
     </row>
     <row r="27">
@@ -3808,22 +3808,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05108145628162595</v>
+        <v>0.05134708605334042</v>
       </c>
       <c r="AZ27" s="12" t="n">
         <v>0.6296205251101323</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.2465753424657534</v>
+        <v>0.2438356164383561</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.2345920394581542</v>
+        <v>0.2319268485859341</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.2246575342465753</v>
+        <v>0.2219178082191781</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.04055555555555556</v>
+        <v>0.04101123595505619</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>11530</v>
+        <v>11400</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3938,15 +3938,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-3.157782121840622</v>
+        <v>-3.19250481484524</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.1599864853425847</v>
+        <v>0.1732144014035089</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.2246575342465753</v>
+        <v>0.2219178082191781</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14270</v>
+        <v>14330</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.05988101481176222</v>
+        <v>-0.05997771208426097</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.08082690960056049</v>
+        <v>0.07630146545708305</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.632047830353444</v>
+        <v>2.629326824619516</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>2.799696497807068</v>
+        <v>2.797089875868136</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.723287671232877</v>
+        <v>2.720547945205479</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003799323053584916</v>
+        <v>0.003803254850772337</v>
       </c>
     </row>
     <row r="30">
@@ -4189,22 +4189,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05730439036558674</v>
+        <v>0.0573056720748554</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.7310740750000002</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.596492526078686</v>
+        <v>2.593752515048967</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.455766333459459</v>
+        <v>2.453171853281549</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.723287671232877</v>
+        <v>2.720547945205479</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003851349426028332</v>
+        <v>0.003855417948312317</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.08280271623610196</v>
+        <v>0.08282537730979386</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.524854934844193</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.140348236379154</v>
+        <v>2.137602838723664</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.976674240178446</v>
+        <v>1.974097470853881</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.295890410958904</v>
+        <v>2.293150684931507</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004672136912130284</v>
+        <v>0.004678137500028245</v>
       </c>
     </row>
     <row r="32">
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67170</v>
+        <v>67340</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4412,22 +4412,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2800498265795348</v>
+        <v>-0.2804839403659049</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1561411344350156</v>
+        <v>0.1532224532224533</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.594973514957111</v>
+        <v>1.592249598231658</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.215394306219043</v>
+        <v>2.212945182962818</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.597260273972603</v>
+        <v>1.594520547945205</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.006269696585067684</v>
+        <v>0.006280422372915611</v>
       </c>
     </row>
     <row r="33">
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>133.8</v>
+        <v>133.6</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.10163856066971</v>
+        <v>-0.1017723378414652</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.01704783258594933</v>
+        <v>0.01857035928143724</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.630397672629992</v>
+        <v>2.627685210661425</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.927994855379033</v>
+        <v>2.925411141699671</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.723287671232877</v>
+        <v>2.720547945205479</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003801706526755531</v>
+        <v>0.003805630887378196</v>
       </c>
     </row>
     <row r="34">
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03055771778294077</v>
+        <v>0.03053466564977493</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.231705685618729</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.626000796392671</v>
+        <v>1.623261980471859</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.57778721980824</v>
+        <v>1.575164848480236</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.643835616438356</v>
+        <v>1.641095890410959</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.006150058488400059</v>
+        <v>0.006160435050103955</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>790.3</v>
+        <v>785.9</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.1495281220610244</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.5918005820574466</v>
+        <v>0.6007125588497264</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>2.95371783417793</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9219</v>
+        <v>8836</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.006036557894216882</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1605701998047508</v>
+        <v>0.2108755853327295</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.701249147481358</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>114.9</v>
+        <v>112.5</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>105.6</v>
+        <v>104.4</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01337112560980665</v>
+        <v>0.01824400310351207</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.218636363636364</v>
+        <v>0.2068965517241379</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.357946849619954</v>
+        <v>4.353037860645039</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.300445058563825</v>
+        <v>4.275043945633255</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.720547945205479</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002294658550246448</v>
+        <v>0.002297246272633656</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6590</v>
+        <v>6528</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.06031230934228432</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.473748103186646</v>
+        <v>1.497242647058823</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2493150684931507</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>279.7</v>
+        <v>261.5</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21220</v>
+        <v>20050</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1153171165227908</v>
+        <v>-0.1061103150524991</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.05447690857681442</v>
+        <v>0.04339152119700751</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.498930182790867</v>
+        <v>6.482872638481394</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.34605620179639</v>
+        <v>7.252430302808718</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.895890410958904</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001538714791317492</v>
+        <v>0.00154252606177105</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21220</v>
+        <v>20050</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.05576978942999603</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2803016022620171</v>
+        <v>0.3550124688279301</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.91082827227607</v>
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>96.5</v>
+        <v>96.8</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1939</v>
+        <v>1811</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,16 +1617,16 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04611788381852741</v>
+        <v>0.04225557634759794</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.195014755028365</v>
+        <v>3.505478228602981</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8328767123287673</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.7961595200806723</v>
+        <v>0.7991098644417309</v>
       </c>
       <c r="BC8" s="8" t="n">
         <v>0.8054794520547945</v>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>84.2</v>
+        <v>85</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>192</v>
+        <v>194.5</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.160607387867483</v>
+        <v>0.1539419734324165</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>3.179302083333333</v>
+        <v>3.164781491002571</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.612356675718806</v>
+        <v>1.612618752377486</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.389235233700669</v>
+        <v>1.397486866328927</v>
       </c>
       <c r="BC9" s="8" t="n">
         <v>1.641095890410959</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006202101650704485</v>
+        <v>0.006201093708762217</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12160</v>
+        <v>11950</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.008527398708109875</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4789473684210526</v>
+        <v>0.5049372384937239</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.071829290955252</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105.1</v>
+        <v>105.4</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1176</v>
+        <v>1103</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03513704449503973</v>
+        <v>0.0340170651282383</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.3994547602040814</v>
+        <v>0.4963340815956483</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.598655221141676</v>
+        <v>2.598901480237724</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.510445582989788</v>
+        <v>2.513402890420778</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.720547945205479</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.00384814419344428</v>
+        <v>0.003847779562265397</v>
       </c>
     </row>
     <row r="12">
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>210.5</v>
+        <v>209.6</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>205.8</v>
+        <v>203.2</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1171184587564298</v>
+        <v>-0.1162257868639513</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.02283770651117578</v>
+        <v>0.03149606299212593</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.185316003837315</v>
+        <v>4.184505055915161</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.740518187685913</v>
+        <v>4.734812346545572</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.471232876712329</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002389305847116796</v>
+        <v>0.002389768889361033</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>244.1</v>
+        <v>234.9</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1941749324021536</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.03070596067185583</v>
+        <v>0.07107418050234138</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.11798788242899</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>75.90000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2429,7 +2429,7 @@
         <v>-0.1785709517835199</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1998616600790513</v>
+        <v>0.2030317040951124</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.949002189203464</v>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>112.7</v>
+        <v>112.2</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18340</v>
+        <v>18110</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.04340244481403007</v>
+        <v>-0.04094368203689964</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1529222290076337</v>
+        <v>0.1623845654334624</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.722405786175503</v>
+        <v>1.722348523120735</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.800554242312123</v>
+        <v>1.795878397192314</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.720547945205479</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005805832795188403</v>
+        <v>0.005806025822161089</v>
       </c>
     </row>
     <row r="17">
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>78</v>
+        <v>77.3</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2668,7 +2668,7 @@
         <v>0.06284184375592114</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9136538461538459</v>
+        <v>0.9309831824062094</v>
       </c>
       <c r="BA17" s="8" t="n">
         <v>2.96546547036928</v>
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106.2</v>
+        <v>110.8</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>161</v>
+        <v>163.6</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.02813317120455302</v>
+        <v>0.0147740382430584</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.385217391304348</v>
+        <v>0.4222493887530563</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.157133960991176</v>
+        <v>3.16399328343293</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.070744188996745</v>
+        <v>3.117928882878152</v>
       </c>
       <c r="BC19" s="8" t="n">
         <v>3.386301369863014</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003167429739617548</v>
+        <v>0.003160562967172298</v>
       </c>
     </row>
     <row r="20">
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>29950</v>
+        <v>29090</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.590733507210915</v>
+        <v>-0.5842326201722955</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.02152969282136896</v>
+        <v>-0.01468269989687188</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.399934460906896</v>
+        <v>1.399761306875514</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.420593880937013</v>
+        <v>3.366693431927199</v>
       </c>
       <c r="BC20" s="8" t="n">
         <v>1.383561643835616</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.007143191541639646</v>
+        <v>0.007144075172588935</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>452.7</v>
+        <v>440</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03840233560404845</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.4815152374641041</v>
+        <v>0.5242771545454543</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7479452054794522</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102.9</v>
+        <v>102.7</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>226.5</v>
+        <v>217.8</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.05430838372315997</v>
+        <v>0.05536871551723985</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.04490066225165568</v>
+        <v>0.08452708907254336</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.935476932618022</v>
+        <v>1.935416231871676</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.835778755531777</v>
+        <v>1.833876827515322</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>1.986301369863014</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005166685188272176</v>
+        <v>0.005166847231786073</v>
       </c>
     </row>
     <row r="23">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>91.09999999999999</v>
+        <v>91</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10260</v>
+        <v>10210</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02700507140079333</v>
+        <v>0.02726727039354749</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.564283516276803</v>
+        <v>0.5702185475024486</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.286938673300265</v>
+        <v>4.286898586431736</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.174213733387951</v>
+        <v>4.173109287118064</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.312328767123287</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002332666912704301</v>
+        <v>0.002332688725516049</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>30.4</v>
+        <v>35.1</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.3089672501445484</v>
+        <v>0.344908255929895</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.6776315789473686</v>
+        <v>0.3390313390313391</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.812839486039933</v>
+        <v>2.788161225966279</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.148899818333356</v>
+        <v>2.073123734405579</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.224657534246576</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.00355512642994021</v>
+        <v>0.003586593166445872</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1135</v>
+        <v>1143</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.05134708605334042</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.6296205251101323</v>
+        <v>0.6182146071741033</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2438356164383561</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>11400</v>
+        <v>11700</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-3.19250481484524</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.1732144014035089</v>
+        <v>0.1431319808547009</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>134</v>
+        <v>135.5</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14330</v>
+        <v>13990</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.05997771208426097</v>
+        <v>-0.06391180183706356</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.07630146545708305</v>
+        <v>0.1147998570407434</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.629326824619516</v>
+        <v>2.630087531516776</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>2.797089875868136</v>
+        <v>2.809657825703065</v>
       </c>
       <c r="BC29" s="8" t="n">
         <v>2.720547945205479</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003803254850772337</v>
+        <v>0.003802154825711441</v>
       </c>
     </row>
     <row r="30">
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>560</v>
+        <v>558.7</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4192,7 +4192,7 @@
         <v>0.0573056720748554</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.7310740750000002</v>
+        <v>0.7351019903347056</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.593752515048967</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67340</v>
+        <v>63720</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2804839403659049</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1532224532224533</v>
+        <v>0.218738229755179</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.592249598231658</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>133.6</v>
+        <v>132.8</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4524,7 +4524,7 @@
         <v>-0.1017723378414652</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.01857035928143724</v>
+        <v>0.02470632530120476</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.627685210661425</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1495281220610244</v>
+        <v>0.1496174288408212</v>
       </c>
       <c r="AZ2" s="12" t="n">
         <v>0.6007125588497264</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.95371783417793</v>
+        <v>2.950929592374399</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.569504631937249</v>
+        <v>2.56687965782658</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.224657534246576</v>
+        <v>3.221917808219178</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003385563740817907</v>
+        <v>0.003388762654941464</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.006036557894216882</v>
+        <v>-0.006116415099487949</v>
       </c>
       <c r="AZ3" s="12" t="n">
         <v>0.2108755853327295</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.701249147481358</v>
+        <v>1.698512797780199</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.711581206525201</v>
+        <v>1.708965540416105</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.720547945205479</v>
+        <v>1.717808219178082</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005878033805221687</v>
+        <v>0.005887503475433971</v>
       </c>
     </row>
     <row r="4">
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01824400310351207</v>
+        <v>0.01822964813045744</v>
       </c>
       <c r="AZ4" s="12" t="n">
         <v>0.2068965517241379</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.353037860645039</v>
+        <v>4.350312651760037</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.275043945633255</v>
+        <v>4.272427796369437</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.720547945205479</v>
+        <v>4.717808219178083</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002297246272633656</v>
+        <v>0.002298685359075107</v>
       </c>
     </row>
     <row r="5">
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.06031230934228432</v>
+        <v>0.06084670623580286</v>
       </c>
       <c r="AZ5" s="12" t="n">
         <v>1.497242647058823</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.2493150684931507</v>
+        <v>0.2465753424657534</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.2351336170451532</v>
+        <v>0.2324325852324842</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.2219178082191781</v>
+        <v>0.2191780821917808</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.0401098901098901</v>
+        <v>0.04055555555555556</v>
       </c>
     </row>
     <row r="6">
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1061103150524991</v>
+        <v>-0.1061584800527618</v>
       </c>
       <c r="AZ6" s="12" t="n">
         <v>0.04339152119700751</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.482872638481394</v>
+        <v>6.480218162454872</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.252430302808718</v>
+        <v>7.249851363849587</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>6.895890410958904</v>
+        <v>6.893150684931507</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.00154252606177105</v>
+        <v>0.001543157922975196</v>
       </c>
     </row>
     <row r="7">
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05576978942999603</v>
+        <v>-0.05585656436407902</v>
       </c>
       <c r="AZ7" s="12" t="n">
         <v>0.3550124688279301</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.91082827227607</v>
+        <v>1.90808918323017</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.023688980595696</v>
+        <v>2.020973838519557</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>1.893150684931507</v>
+        <v>1.89041095890411</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005233332657407548</v>
+        <v>0.005240845180554496</v>
       </c>
     </row>
     <row r="8">
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04225557634759794</v>
+        <v>0.04238621400862781</v>
       </c>
       <c r="AZ8" s="12" t="n">
         <v>3.505478228602981</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.8328767123287673</v>
+        <v>0.8301369863013699</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.7991098644417309</v>
+        <v>0.7963813940986166</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.8054794520547945</v>
+        <v>0.8027397260273973</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01200657894736842</v>
+        <v>0.01204620462046205</v>
       </c>
     </row>
     <row r="9">
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1539419734324165</v>
+        <v>0.1541203150820777</v>
       </c>
       <c r="AZ9" s="12" t="n">
         <v>3.164781491002571</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.612618752377486</v>
+        <v>1.609872012276844</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.397486866328927</v>
+        <v>1.394890975610592</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.641095890410959</v>
+        <v>1.638356164383562</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006201093708762217</v>
+        <v>0.006211673924225188</v>
       </c>
     </row>
     <row r="10">
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.008527398708109875</v>
+        <v>-0.0085448369467213</v>
       </c>
       <c r="AZ10" s="3" t="n">
         <v>0.5049372384937239</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.071829290955252</v>
+        <v>4.069098348898489</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.106850038669402</v>
+        <v>4.104167793495896</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.23013698630137</v>
+        <v>4.227397260273973</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002455898635586955</v>
+        <v>0.002457546891857999</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.0340170651282383</v>
+        <v>0.0339973694258684</v>
       </c>
       <c r="AZ11" s="12" t="n">
         <v>0.4963340815956483</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.598901480237724</v>
+        <v>2.596166083626457</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.513402890420778</v>
+        <v>2.510805308013491</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.720547945205479</v>
+        <v>2.717808219178082</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003847779562265397</v>
+        <v>0.003851833695489732</v>
       </c>
     </row>
     <row r="12">
@@ -2111,7 +2111,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>-0.1041095890410959</v>
+        <v>-0.1068493150684932</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1162257868639513</v>
+        <v>-0.1163123168293717</v>
       </c>
       <c r="AZ13" s="12" t="n">
         <v>0.03149606299212593</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.184505055915161</v>
+        <v>4.18184399764549</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.734812346545572</v>
+        <v>4.732264664639477</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.471232876712329</v>
+        <v>4.468493150684932</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002389768889361033</v>
+        <v>0.002391289585558504</v>
       </c>
     </row>
     <row r="14">
@@ -2317,22 +2317,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1941749324021536</v>
+        <v>-0.1943404710015798</v>
       </c>
       <c r="AZ14" s="12" t="n">
         <v>0.07107418050234138</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.11798788242899</v>
+        <v>3.115304172088871</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.869311104609428</v>
+        <v>3.866775058146156</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.224657534246576</v>
+        <v>3.221917808219178</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003207196556584996</v>
+        <v>0.003209959428550699</v>
       </c>
     </row>
     <row r="15">
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1785709517835199</v>
+        <v>-0.1788467989681234</v>
       </c>
       <c r="AZ15" s="12" t="n">
         <v>0.2030317040951124</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.949002189203464</v>
+        <v>1.94627871584483</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.372696940089003</v>
+        <v>2.370177347417144</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>1.986301369863014</v>
+        <v>1.983561643835617</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005130830563144154</v>
+        <v>0.00513801025443535</v>
       </c>
     </row>
     <row r="16">
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.04094368203689964</v>
+        <v>-0.04104140848918544</v>
       </c>
       <c r="AZ16" s="12" t="n">
         <v>0.1623845654334624</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.722348523120735</v>
+        <v>1.719611072953516</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.795878397192314</v>
+        <v>1.793206805983472</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.720547945205479</v>
+        <v>1.717808219178082</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005806025822161089</v>
+        <v>0.005815268439057274</v>
       </c>
     </row>
     <row r="17">
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.06284184375592114</v>
+        <v>0.06285263192767336</v>
       </c>
       <c r="AZ17" s="12" t="n">
         <v>0.9309831824062094</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.96546547036928</v>
+        <v>2.962719743282316</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.790128642178574</v>
+        <v>2.787516965460107</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.224657534246576</v>
+        <v>3.221917808219178</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.00337215189315785</v>
+        <v>0.003375277065160835</v>
       </c>
     </row>
     <row r="18">
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1235013341863834</v>
+        <v>0.1236124542072565</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>2.56</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.694422318269051</v>
+        <v>1.691677824620852</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.508162266221176</v>
+        <v>1.50557055351828</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.720547945205479</v>
+        <v>1.717808219178082</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005901716409292561</v>
+        <v>0.005911291059360699</v>
       </c>
     </row>
     <row r="19">
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.0147740382430584</v>
+        <v>0.01475016488699721</v>
       </c>
       <c r="AZ19" s="12" t="n">
         <v>0.4222493887530563</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.16399328343293</v>
+        <v>3.161265726344481</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.117928882878152</v>
+        <v>3.115314326355906</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.386301369863014</v>
+        <v>3.383561643835617</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003160562967172298</v>
+        <v>0.003163289917916349</v>
       </c>
     </row>
     <row r="20">
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5842326201722955</v>
+        <v>-0.5849539464989054</v>
       </c>
       <c r="AZ20" s="12" t="n">
         <v>-0.01468269989687188</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.399761306875514</v>
+        <v>1.397040790706495</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.366693431927199</v>
+        <v>3.365989819495562</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.383561643835616</v>
+        <v>1.380821917808219</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.007144075172588935</v>
+        <v>0.007157987130027119</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3124,22 +3124,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03840233560404845</v>
+        <v>0.0384083357948612</v>
       </c>
       <c r="AZ21" s="12" t="n">
         <v>0.5242771545454543</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.7479452054794522</v>
+        <v>0.7452054794520547</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.7202845947417534</v>
+        <v>0.717642042888291</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.7205479452054795</v>
+        <v>0.7178082191780822</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01336996336996337</v>
+        <v>0.01341911764705882</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.05536871551723985</v>
+        <v>0.05534737709163567</v>
       </c>
       <c r="AZ22" s="12" t="n">
         <v>0.08452708907254336</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.935416231871676</v>
+        <v>1.932677727326094</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.833876827515322</v>
+        <v>1.831319022796301</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>1.986301369863014</v>
+        <v>1.983561643835617</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005166847231786073</v>
+        <v>0.005174168387522756</v>
       </c>
     </row>
     <row r="23">
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02726727039354749</v>
+        <v>0.027281347077991</v>
       </c>
       <c r="AZ23" s="12" t="n">
         <v>0.5702185475024486</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.286898586431736</v>
+        <v>4.284156707607761</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.173109287118064</v>
+        <v>4.170383040433527</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.312328767123287</v>
+        <v>4.30958904109589</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002332688725516049</v>
+        <v>0.002334181656390417</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1731158715329388</v>
+        <v>0.1732140649710665</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.3993673658682633</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.873704460140817</v>
+        <v>2.870900502051266</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.449633944842702</v>
+        <v>2.447038940094933</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.224657534246576</v>
+        <v>3.221917808219178</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003479828958998094</v>
+        <v>0.003483227646814988</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.344908255929895</v>
+        <v>0.3451699797977679</v>
       </c>
       <c r="AZ25" s="12" t="n">
         <v>0.3390313390313391</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.788161225966279</v>
+        <v>2.785239812333834</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.073123734405579</v>
+        <v>2.0705485954664</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.224657534246576</v>
+        <v>3.221917808219178</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003586593166445872</v>
+        <v>0.003590355112589285</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3699,22 +3699,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>81.26300746542961</v>
+        <v>82.11623439000959</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.1761052631578948</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.2493150684931507</v>
+        <v>0.2465753424657535</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.003030706950483465</v>
+        <v>0.002966632743595412</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.2219178082191781</v>
+        <v>0.2191780821917808</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.04010989010989011</v>
+        <v>0.04055555555555555</v>
       </c>
     </row>
     <row r="27">
@@ -3808,22 +3808,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05134708605334042</v>
+        <v>0.05161879916386514</v>
       </c>
       <c r="AZ27" s="12" t="n">
         <v>0.6182146071741033</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.2438356164383561</v>
+        <v>0.2410958904109589</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.2319268485859341</v>
+        <v>0.2292616779032978</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.2219178082191781</v>
+        <v>0.2191780821917808</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.04101123595505619</v>
+        <v>0.04147727272727272</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3938,7 +3938,7 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-3.19250481484524</v>
+        <v>-3.227999122076868</v>
       </c>
       <c r="AZ28" s="12" t="n">
         <v>0.1431319808547009</v>
@@ -3946,7 +3946,7 @@
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.2219178082191781</v>
+        <v>0.2191780821917808</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.06391180183706356</v>
+        <v>-0.06401195071817971</v>
       </c>
       <c r="AZ29" s="12" t="n">
         <v>0.1147998570407434</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.630087531516776</v>
+        <v>2.627367147079461</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>2.809657825703065</v>
+        <v>2.8070520228281</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.720547945205479</v>
+        <v>2.717808219178082</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003802154825711441</v>
+        <v>0.003806091589108831</v>
       </c>
     </row>
     <row r="30">
@@ -4189,22 +4189,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.0573056720748554</v>
+        <v>0.05730696561791335</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.7351019903347056</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.593752515048967</v>
+        <v>2.591012501387694</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.453171853281549</v>
+        <v>2.450577349477169</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.720547945205479</v>
+        <v>2.717808219178082</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003855417948312317</v>
+        <v>0.003859495079488888</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.08282537730979386</v>
+        <v>0.08284811229919795</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.524854934844193</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.137602838723664</v>
+        <v>2.134857422512752</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.974097470853881</v>
+        <v>1.971520657666231</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.293150684931507</v>
+        <v>2.29041095890411</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004678137500028245</v>
+        <v>0.004684153561988175</v>
       </c>
     </row>
     <row r="32">
@@ -4412,22 +4412,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2804839403659049</v>
+        <v>-0.2809192815737115</v>
       </c>
       <c r="AZ32" s="12" t="n">
         <v>0.218738229755179</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.592249598231658</v>
+        <v>1.58952572672162</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.212945182962818</v>
+        <v>2.210496938647312</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.594520547945205</v>
+        <v>1.591780821917808</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.006280422372915611</v>
+        <v>0.006291184742649554</v>
       </c>
     </row>
     <row r="33">
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.1017723378414652</v>
+        <v>-0.1019063696279857</v>
       </c>
       <c r="AZ33" s="12" t="n">
         <v>0.02470632530120476</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.627685210661425</v>
+        <v>2.624972798332849</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.925411141699671</v>
+        <v>2.922827542207949</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.720547945205479</v>
+        <v>2.717808219178082</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003805630887378196</v>
+        <v>0.003809563286275239</v>
       </c>
     </row>
     <row r="34">
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03053466564977493</v>
+        <v>0.03051154507228296</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.231705685618729</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.623261980471859</v>
+        <v>1.620523167254992</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.575164848480236</v>
+        <v>1.57254246689815</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.641095890410959</v>
+        <v>1.638356164383562</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.006160435050103955</v>
+        <v>0.006170846675977503</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1496174288408212</v>
+        <v>0.1497965934001751</v>
       </c>
       <c r="AZ2" s="12" t="n">
         <v>0.6007125588497264</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.950929592374399</v>
+        <v>2.945352797372956</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.56687965782658</v>
+        <v>2.561629434527169</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.221917808219178</v>
+        <v>3.216438356164383</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003388762654941464</v>
+        <v>0.003395179011804387</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.006116415099487949</v>
+        <v>-0.006276859692590602</v>
       </c>
       <c r="AZ3" s="12" t="n">
         <v>0.2108755853327295</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.698512797780199</v>
+        <v>1.693040129321755</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.708965540416105</v>
+        <v>1.703734230037163</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.717808219178082</v>
+        <v>1.712328767123288</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005887503475433971</v>
+        <v>0.005906534539146497</v>
       </c>
     </row>
     <row r="4">
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01822964813045744</v>
+        <v>0.0182008932658273</v>
       </c>
       <c r="AZ4" s="12" t="n">
         <v>0.2068965517241379</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.350312651760037</v>
+        <v>4.344862278424718</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.272427796369437</v>
+        <v>4.267195508431342</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.717808219178083</v>
+        <v>4.712328767123288</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002298685359075107</v>
+        <v>0.002301568924211246</v>
       </c>
     </row>
     <row r="5">
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.06084670623580286</v>
+        <v>0.06195196363876181</v>
       </c>
       <c r="AZ5" s="12" t="n">
         <v>1.497242647058823</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.2465753424657534</v>
+        <v>0.2410958904109589</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.2324325852324842</v>
+        <v>0.2270308814956635</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.2191780821917808</v>
+        <v>0.2136986301369863</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.04055555555555556</v>
+        <v>0.04147727272727273</v>
       </c>
     </row>
     <row r="6">
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1061584800527618</v>
+        <v>-0.1062549219042102</v>
       </c>
       <c r="AZ6" s="12" t="n">
         <v>0.04339152119700751</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.480218162454872</v>
+        <v>6.474909368801821</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.249851363849587</v>
+        <v>7.244693735933339</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>6.893150684931507</v>
+        <v>6.887671232876713</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001543157922975196</v>
+        <v>0.001544423161841182</v>
       </c>
     </row>
     <row r="7">
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05585656436407902</v>
+        <v>-0.05603083928572188</v>
       </c>
       <c r="AZ7" s="12" t="n">
         <v>0.3550124688279301</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.90808918323017</v>
+        <v>1.902611010463177</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.020973838519557</v>
+        <v>2.015543610581005</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>1.89041095890411</v>
+        <v>1.884931506849315</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005240845180554496</v>
+        <v>0.005255935104446584</v>
       </c>
     </row>
     <row r="8">
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04238621400862781</v>
+        <v>0.04265009378041662</v>
       </c>
       <c r="AZ8" s="12" t="n">
         <v>3.505478228602981</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.8301369863013699</v>
+        <v>0.8246575342465754</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.7963813940986166</v>
+        <v>0.790924528915114</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.8027397260273973</v>
+        <v>0.7972602739726027</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01204620462046205</v>
+        <v>0.01212624584717608</v>
       </c>
     </row>
     <row r="9">
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1541203150820777</v>
+        <v>0.1544789558395269</v>
       </c>
       <c r="AZ9" s="12" t="n">
         <v>3.164781491002571</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.609872012276844</v>
+        <v>1.604378455402661</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.394890975610592</v>
+        <v>1.389699177527209</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.638356164383562</v>
+        <v>1.632876712328767</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006211673924225188</v>
+        <v>0.00623294333473846</v>
       </c>
     </row>
     <row r="10">
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.0085448369467213</v>
+        <v>-0.008579781235731576</v>
       </c>
       <c r="AZ10" s="3" t="n">
         <v>0.5049372384937239</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.069098348898489</v>
+        <v>4.063636498016038</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.104167793495896</v>
+        <v>4.098803333949613</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.227397260273973</v>
+        <v>4.221917808219178</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002457546891857999</v>
+        <v>0.002460850030479408</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.0339973694258684</v>
+        <v>0.03395787811064695</v>
       </c>
       <c r="AZ11" s="12" t="n">
         <v>0.4963340815956483</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.596166083626457</v>
+        <v>2.590695312236569</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.510805308013491</v>
+        <v>2.505610109543873</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.717808219178082</v>
+        <v>2.712328767123288</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003851833695489732</v>
+        <v>0.003859967612851747</v>
       </c>
     </row>
     <row r="12">
@@ -2111,7 +2111,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>-0.1068493150684932</v>
+        <v>-0.1123287671232877</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1163123168293717</v>
+        <v>-0.1164856837521366</v>
       </c>
       <c r="AZ13" s="12" t="n">
         <v>0.03149606299212593</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.18184399764549</v>
+        <v>4.176522121706837</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.732264664639477</v>
+        <v>4.727169718589081</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.468493150684932</v>
+        <v>4.463013698630137</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002391289585558504</v>
+        <v>0.002394336653462584</v>
       </c>
     </row>
     <row r="14">
@@ -2317,22 +2317,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1943404710015798</v>
+        <v>-0.1946723099669876</v>
       </c>
       <c r="AZ14" s="12" t="n">
         <v>0.07107418050234138</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.115304172088871</v>
+        <v>3.109936966349903</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.866775058146156</v>
+        <v>3.861703757165507</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.221917808219178</v>
+        <v>3.216438356164383</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003209959428550699</v>
+        <v>0.003215499255516064</v>
       </c>
     </row>
     <row r="15">
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1788467989681234</v>
+        <v>-0.1794005262352887</v>
       </c>
       <c r="AZ15" s="12" t="n">
         <v>0.2030317040951124</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.94627871584483</v>
+        <v>1.940831890584482</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.370177347417144</v>
+        <v>2.365139087501989</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>1.983561643835617</v>
+        <v>1.978082191780822</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.00513801025443535</v>
+        <v>0.005152429764016551</v>
       </c>
     </row>
     <row r="16">
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.04104140848918544</v>
+        <v>-0.04123776189492634</v>
       </c>
       <c r="AZ16" s="12" t="n">
         <v>0.1623845654334624</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.719611072953516</v>
+        <v>1.714136193622062</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.793206805983472</v>
+        <v>1.787863690804022</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.717808219178082</v>
+        <v>1.712328767123288</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005815268439057274</v>
+        <v>0.005833842163305276</v>
       </c>
     </row>
     <row r="17">
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.06285263192767336</v>
+        <v>0.06287428883973793</v>
       </c>
       <c r="AZ17" s="12" t="n">
         <v>0.9309831824062094</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.962719743282316</v>
+        <v>2.957228244096572</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.787516965460107</v>
+        <v>2.782293517820213</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.221917808219178</v>
+        <v>3.216438356164383</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003375277065160835</v>
+        <v>0.003381544870593843</v>
       </c>
     </row>
     <row r="18">
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1236124542072565</v>
+        <v>0.1238358577443991</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>2.56</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.691677824620852</v>
+        <v>1.686188787549446</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.50557055351828</v>
+        <v>1.500387068031199</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.717808219178082</v>
+        <v>1.712328767123288</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005911291059360699</v>
+        <v>0.005930534038559877</v>
       </c>
     </row>
     <row r="19">
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.01475016488699721</v>
+        <v>0.01470230844433782</v>
       </c>
       <c r="AZ19" s="12" t="n">
         <v>0.4222493887530563</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.161265726344481</v>
+        <v>3.15581066714259</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.115314326355906</v>
+        <v>3.11008523473336</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.383561643835617</v>
+        <v>3.378082191780822</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003163289917916349</v>
+        <v>0.003168757905573099</v>
       </c>
     </row>
     <row r="20">
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5849539464989054</v>
+        <v>-0.5864013005822087</v>
       </c>
       <c r="AZ20" s="12" t="n">
         <v>-0.01468269989687188</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.397040790706495</v>
+        <v>1.391599885825106</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.365989819495562</v>
+        <v>3.364613785739689</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.380821917808219</v>
+        <v>1.375342465753425</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.007157987130027119</v>
+        <v>0.007185973570320329</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3124,22 +3124,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.0384083357948612</v>
+        <v>0.03842054951685352</v>
       </c>
       <c r="AZ21" s="12" t="n">
         <v>0.5242771545454543</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.7452054794520547</v>
+        <v>0.7397260273972603</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.717642042888291</v>
+        <v>0.7123568844447783</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.7178082191780822</v>
+        <v>0.7123287671232876</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01341911764705882</v>
+        <v>0.01351851851851852</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.05534737709163567</v>
+        <v>0.05530457683170272</v>
       </c>
       <c r="AZ22" s="12" t="n">
         <v>0.08452708907254336</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.932677727326094</v>
+        <v>1.92720072530887</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.831319022796301</v>
+        <v>1.826203323304846</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>1.983561643835617</v>
+        <v>1.978082191780822</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005174168387522756</v>
+        <v>0.005188873099037108</v>
       </c>
     </row>
     <row r="23">
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.027281347077991</v>
+        <v>0.02730955529232128</v>
       </c>
       <c r="AZ23" s="12" t="n">
         <v>0.5702185475024486</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.284156707607761</v>
+        <v>4.278672941372176</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.170383040433527</v>
+        <v>4.16493054048804</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.30958904109589</v>
+        <v>4.304109589041096</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002334181656390417</v>
+        <v>0.002337173263070906</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1732140649710665</v>
+        <v>0.1734110943019541</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.3993673658682633</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.870900502051266</v>
+        <v>2.865292150742733</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.447038940094933</v>
+        <v>2.441848525769441</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.221917808219178</v>
+        <v>3.216438356164383</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003483227646814988</v>
+        <v>0.003490045508067241</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.3451699797977679</v>
+        <v>0.3456952861280487</v>
       </c>
       <c r="AZ25" s="12" t="n">
         <v>0.3390313390313391</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.785239812333834</v>
+        <v>2.779395610066296</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.0705485954664</v>
+        <v>2.065397448231697</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.221917808219178</v>
+        <v>3.216438356164383</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003590355112589285</v>
+        <v>0.00359790450980869</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3699,22 +3699,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>82.11623439000959</v>
+        <v>83.88103836290364</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.1761052631578948</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.2465753424657535</v>
+        <v>0.2410958904109589</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.002966632743595412</v>
+        <v>0.002840397514697785</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.2191780821917808</v>
+        <v>0.2136986301369863</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.04055555555555555</v>
+        <v>0.04147727272727274</v>
       </c>
     </row>
     <row r="27">
@@ -3808,22 +3808,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05161879916386514</v>
+        <v>0.05218132419712265</v>
       </c>
       <c r="AZ27" s="12" t="n">
         <v>0.6182146071741033</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.2410958904109589</v>
+        <v>0.2356164383561644</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.2292616779032978</v>
+        <v>0.2239314013066653</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.2191780821917808</v>
+        <v>0.2136986301369863</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.04147727272727272</v>
+        <v>0.04244186046511628</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3938,7 +3938,7 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-3.227999122076868</v>
+        <v>-3.301407799343399</v>
       </c>
       <c r="AZ28" s="12" t="n">
         <v>0.1431319808547009</v>
@@ -3946,7 +3946,7 @@
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.2191780821917808</v>
+        <v>0.2136986301369863</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.06401195071817971</v>
+        <v>-0.06421283110501705</v>
       </c>
       <c r="AZ29" s="12" t="n">
         <v>0.1147998570407434</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.627367147079461</v>
+        <v>2.621926487207051</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>2.8070520228281</v>
+        <v>2.801840604742564</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.717808219178082</v>
+        <v>2.712328767123288</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003806091589108831</v>
+        <v>0.003813989464919086</v>
       </c>
     </row>
     <row r="30">
@@ -4189,22 +4189,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05730696561791335</v>
+        <v>0.05730958834511155</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.7351019903347056</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.591012501387694</v>
+        <v>2.585532466139397</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.450577349477169</v>
+        <v>2.445388270985267</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.717808219178082</v>
+        <v>2.712328767123288</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003859495079488888</v>
+        <v>0.003867675278095254</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.08284811229919795</v>
+        <v>0.08289380515889547</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.524854934844193</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.134857422512752</v>
+        <v>2.129366534138726</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.971520657666231</v>
+        <v>1.96636689950062</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.29041095890411</v>
+        <v>2.284931506849315</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004684153561988175</v>
+        <v>0.004696232348765048</v>
       </c>
     </row>
     <row r="32">
@@ -4412,22 +4412,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2809192815737115</v>
+        <v>-0.2817936667682043</v>
       </c>
       <c r="AZ32" s="12" t="n">
         <v>0.218738229755179</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.58952572672162</v>
+        <v>1.584078120112555</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.210496938647312</v>
+        <v>2.20560310709667</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.591780821917808</v>
+        <v>1.586301369863014</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.006291184742649554</v>
+        <v>0.006312819975879386</v>
       </c>
     </row>
     <row r="33">
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.1019063696279857</v>
+        <v>-0.1021751999794164</v>
       </c>
       <c r="AZ33" s="12" t="n">
         <v>0.02470632530120476</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.624972798332849</v>
+        <v>2.619548123141032</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.922827542207949</v>
+        <v>2.917660687342315</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.717808219178082</v>
+        <v>2.712328767123288</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003809563286275239</v>
+        <v>0.003817452297081398</v>
       </c>
     </row>
     <row r="34">
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03051154507228296</v>
+        <v>0.03046509719104977</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.231705685618729</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.620523167254992</v>
+        <v>1.61504554898816</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.57254246689815</v>
+        <v>1.567297673051345</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.638356164383562</v>
+        <v>1.632876712328767</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.006170846675977503</v>
+        <v>0.006191775833359676</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1497965934001751</v>
+        <v>0.1498864522632603</v>
       </c>
       <c r="AZ2" s="12" t="n">
         <v>0.6007125588497264</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.945352797372956</v>
+        <v>2.942564243537196</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.561629434527169</v>
+        <v>2.559004184931045</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.216438356164383</v>
+        <v>3.213698630136986</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003395179011804387</v>
+        <v>0.003398396491075146</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8836</v>
+        <v>8737</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.006276859692590602</v>
+        <v>-0.006357449390757199</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2108755853327295</v>
+        <v>0.2245961625271831</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.693040129321755</v>
+        <v>1.690303810662592</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.703734230037163</v>
+        <v>1.70111858598064</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.712328767123288</v>
+        <v>1.70958904109589</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005906534539146497</v>
+        <v>0.005916096228925877</v>
       </c>
     </row>
     <row r="4">
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>104.4</v>
+        <v>85</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.0182008932658273</v>
+        <v>0.01818649331710654</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2068965517241379</v>
+        <v>0.4823529411764707</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.344862278424718</v>
+        <v>4.34213711403012</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.267195508431342</v>
+        <v>4.264579369820606</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.712328767123288</v>
+        <v>4.70958904109589</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002301568924211246</v>
+        <v>0.002303013409615382</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6528</v>
+        <v>6561</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.06195196363876181</v>
+        <v>0.06252366239041456</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.497242647058823</v>
+        <v>1.484682213077275</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.2410958904109589</v>
+        <v>0.2383561643835616</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.2270308814956635</v>
+        <v>0.2243302175947022</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.2136986301369863</v>
+        <v>0.210958904109589</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.04147727272727273</v>
+        <v>0.04195402298850575</v>
       </c>
     </row>
     <row r="6">
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>20050</v>
+        <v>20370</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1062549219042102</v>
+        <v>-0.1063031988411979</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.04339152119700751</v>
+        <v>0.0270004909180166</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.474909368801821</v>
+        <v>6.472255051267872</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.244693735933339</v>
+        <v>7.242115047156591</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>6.887671232876713</v>
+        <v>6.884931506849315</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001544423161841182</v>
+        <v>0.001545056540693814</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>20050</v>
+        <v>20370</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05603083928572188</v>
+        <v>-0.05611834129593881</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.3550124688279301</v>
+        <v>0.3337260677466862</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.902611010463177</v>
+        <v>1.899871926756946</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.015543610581005</v>
+        <v>2.012828524886741</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>1.884931506849315</v>
+        <v>1.882191780821918</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005255935104446584</v>
+        <v>0.005263512692179128</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04265009378041662</v>
+        <v>0.04278335325416859</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.505478228602981</v>
+        <v>3.507967443093922</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.8246575342465754</v>
+        <v>0.821917808219178</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.790924528915114</v>
+        <v>0.7881961345606975</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.7972602739726027</v>
+        <v>0.7945205479452054</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01212624584717608</v>
+        <v>0.01216666666666667</v>
       </c>
     </row>
     <row r="9">
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>194.5</v>
+        <v>198</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1544789558395269</v>
+        <v>0.1546592619614867</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>3.164781491002571</v>
+        <v>3.091161616161616</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.604378455402661</v>
+        <v>1.601631638355548</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.389699177527209</v>
+        <v>1.387103270305703</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.632876712328767</v>
+        <v>1.63013698630137</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.00623294333473846</v>
+        <v>0.006243632905670717</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11950</v>
+        <v>11910</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.008579781235731576</v>
+        <v>-0.008597287376273015</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.5049372384937239</v>
+        <v>0.5099916036943746</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.063636498016038</v>
+        <v>4.060905589233355</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.098803333949613</v>
+        <v>4.096121119626808</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.221917808219178</v>
+        <v>4.219178082191781</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002460850030479408</v>
+        <v>0.002462504921688629</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105.4</v>
+        <v>106</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1103</v>
+        <v>1098</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03395787811064695</v>
+        <v>0.03170348056136373</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4963340815956483</v>
+        <v>0.5117048087431693</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.590695312236569</v>
+        <v>2.588450843761543</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.505610109543873</v>
+        <v>2.50890967466072</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.712328767123288</v>
+        <v>2.70958904109589</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003859967612851747</v>
+        <v>0.003863314624691878</v>
       </c>
     </row>
     <row r="12">
@@ -2111,7 +2111,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>-0.1123287671232877</v>
+        <v>-0.1150684931506849</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>203.2</v>
+        <v>205.4</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1164856837521366</v>
+        <v>-0.1165725210708736</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.03149606299212593</v>
+        <v>0.02044790652385586</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.176522121706837</v>
+        <v>4.173861304275777</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.727169718589081</v>
+        <v>4.724622454958329</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.463013698630137</v>
+        <v>4.46027397260274</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002394336653462584</v>
+        <v>0.002395863032093526</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>234.9</v>
+        <v>236.3</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2317,22 +2317,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1946723099669876</v>
+        <v>-0.1948386114857114</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.07107418050234138</v>
+        <v>0.06472841726618705</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.109936966349903</v>
+        <v>3.10725347121063</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.861703757165507</v>
+        <v>3.859168504024069</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.216438356164383</v>
+        <v>3.213698630136986</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003215499255516064</v>
+        <v>0.003218276234189501</v>
       </c>
     </row>
     <row r="15">
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1794005262352887</v>
+        <v>-0.1796784113174733</v>
       </c>
       <c r="AZ15" s="12" t="n">
         <v>0.2030317040951124</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.940831890584482</v>
+        <v>1.938108538985669</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.365139087501989</v>
+        <v>2.36262042316643</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>1.978082191780822</v>
+        <v>1.975342465753425</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005152429764016551</v>
+        <v>0.005159669749576363</v>
       </c>
     </row>
     <row r="16">
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18110</v>
+        <v>18060</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.04123776189492634</v>
+        <v>-0.04133639163645049</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1623845654334624</v>
+        <v>0.1656026843853822</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.714136193622062</v>
+        <v>1.711398764522951</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.787863690804022</v>
+        <v>1.785192167088026</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.712328767123288</v>
+        <v>1.70958904109589</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005833842163305276</v>
+        <v>0.005843173553293688</v>
       </c>
     </row>
     <row r="17">
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.06287428883973793</v>
+        <v>0.06288515772714177</v>
       </c>
       <c r="AZ17" s="12" t="n">
         <v>0.9309831824062094</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.957228244096572</v>
+        <v>2.954482471915</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.782293517820213</v>
+        <v>2.779681746834082</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.216438356164383</v>
+        <v>3.213698630136986</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003381544870593843</v>
+        <v>0.003384687536669771</v>
       </c>
     </row>
     <row r="18">
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1238358577443991</v>
+        <v>0.1239481451648965</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>2.56</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.686188787549446</v>
+        <v>1.683444243959741</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.500387068031199</v>
+        <v>1.49779529527384</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.712328767123288</v>
+        <v>1.70958904109589</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005930534038559877</v>
+        <v>0.005940202674297271</v>
       </c>
     </row>
     <row r="19">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>163.6</v>
+        <v>174.8</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.01470230844433782</v>
+        <v>0.01467832516827256</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4222493887530563</v>
+        <v>0.3311212814645308</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.15581066714259</v>
+        <v>3.153083165122781</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.11008523473336</v>
+        <v>3.107470699741102</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.378082191780822</v>
+        <v>3.375342465753425</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003168757905573099</v>
+        <v>0.003171498966666362</v>
       </c>
     </row>
     <row r="20">
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>29090</v>
+        <v>29180</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5864013005822087</v>
+        <v>-0.5871273362647478</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.01468269989687188</v>
+        <v>-0.01772171830020564</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.391599885825106</v>
+        <v>1.388879497333691</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.364613785739689</v>
+        <v>3.363941523201175</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.375342465753425</v>
+        <v>1.372602739726027</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.007185973570320329</v>
+        <v>0.007200048686151358</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>440</v>
+        <v>437.7</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3124,22 +3124,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03842054951685352</v>
+        <v>0.03842676461848402</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5242771545454543</v>
+        <v>0.5322868357322366</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.7397260273972603</v>
+        <v>0.7369863013698631</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.7123568844447783</v>
+        <v>0.7097142778678577</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.7123287671232876</v>
+        <v>0.7095890410958904</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01351851851851852</v>
+        <v>0.01356877323420074</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>217.8</v>
+        <v>215</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.05530457683170272</v>
+        <v>0.05528311463325005</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.08452708907254336</v>
+        <v>0.09865116279069763</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.92720072530887</v>
+        <v>1.924462227858108</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.826203323304846</v>
+        <v>1.823645428579543</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>1.978082191780822</v>
+        <v>1.975342465753425</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005188873099037108</v>
+        <v>0.005196256832294298</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10210</v>
+        <v>10410</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02730955529232128</v>
+        <v>0.02732368689329746</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5702185475024486</v>
+        <v>0.5400510441882804</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.278672941372176</v>
+        <v>4.275931053949171</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.16493054048804</v>
+        <v>4.162204287219252</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.304109589041096</v>
+        <v>4.301369863013699</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002337173263070906</v>
+        <v>0.002338671946256987</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1734110943019541</v>
+        <v>0.1735099314985253</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.3993673658682633</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.865292150742733</v>
+        <v>2.862487756607015</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.441848525769441</v>
+        <v>2.439253115609965</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.216438356164383</v>
+        <v>3.213698630136986</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003490045508067241</v>
+        <v>0.003493464723794408</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>35.1</v>
+        <v>38</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.3456952861280487</v>
+        <v>0.309878802464829</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.3390313390313391</v>
+        <v>0.3421052631578947</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.779395610066296</v>
+        <v>2.801261468930981</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.065397448231697</v>
+        <v>2.138565387621956</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.216438356164383</v>
+        <v>3.213698630136986</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.00359790450980869</v>
+        <v>0.003569820279510076</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3699,22 +3699,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>83.88103836290364</v>
+        <v>84.79395658902425</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.1761052631578948</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.2410958904109589</v>
+        <v>0.2383561643835616</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.002840397514697785</v>
+        <v>0.002778239562086532</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.2136986301369863</v>
+        <v>0.210958904109589</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.04147727272727274</v>
+        <v>0.04195402298850575</v>
       </c>
     </row>
     <row r="27">
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1143</v>
+        <v>1401</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3808,22 +3808,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05218132419712265</v>
+        <v>0.05247258548233187</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.6182146071741033</v>
+        <v>0.3202136302640972</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.2356164383561644</v>
+        <v>0.2328767123287671</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.2239314013066653</v>
+        <v>0.2212662976129144</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.2136986301369863</v>
+        <v>0.210958904109589</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.04244186046511628</v>
+        <v>0.04294117647058824</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>11700</v>
+        <v>11770</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3938,15 +3938,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-3.301407799343399</v>
+        <v>-3.339377803006159</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.1431319808547009</v>
+        <v>0.1363334049277827</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.2136986301369863</v>
+        <v>0.210958904109589</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>13990</v>
+        <v>14290</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.06421283110501705</v>
+        <v>-0.06431356375963532</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1147998570407434</v>
+        <v>0.09139608117564735</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.621926487207051</v>
+        <v>2.61920621197998</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>2.801840604742564</v>
+        <v>2.799234989986691</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.712328767123288</v>
+        <v>2.70958904109589</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003813989464919086</v>
+        <v>0.00381795062727823</v>
       </c>
     </row>
     <row r="30">
@@ -4189,22 +4189,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05730958834511155</v>
+        <v>0.05731091759948424</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.7351019903347056</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.585532466139397</v>
+        <v>2.582792444536746</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.445388270985267</v>
+        <v>2.442793696295798</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.712328767123288</v>
+        <v>2.70958904109589</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003867675278095254</v>
+        <v>0.003871778400603777</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4286,7 +4286,7 @@
         <v>0.9284102</v>
       </c>
       <c r="AJ31" t="n">
-        <v>35.3</v>
+        <v>176.5</v>
       </c>
       <c r="AK31" s="10" t="n">
         <v>47133</v>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.08289380515889547</v>
+        <v>0.08291676359977262</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>1.524854934844193</v>
+        <v>-0.4950290130311615</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.129366534138726</v>
+        <v>2.126621061831702</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.96636689950062</v>
+        <v>1.963789954421339</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.284931506849315</v>
+        <v>2.282191780821918</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004696232348765048</v>
+        <v>0.004702295194700459</v>
       </c>
     </row>
     <row r="32">
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>63720</v>
+        <v>62770</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4412,22 +4412,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2817936667682043</v>
+        <v>-0.2822327210819827</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.218738229755179</v>
+        <v>0.2371833678508841</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.584078120112555</v>
+        <v>1.581354385398546</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.20560310709667</v>
+        <v>2.203157530087363</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.586301369863014</v>
+        <v>1.583561643835616</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.006312819975879386</v>
+        <v>0.006323693216609201</v>
       </c>
     </row>
     <row r="33">
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>132.8</v>
+        <v>129.6</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.1021751999794164</v>
+        <v>-0.1023100000183647</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.02470632530120476</v>
+        <v>0.05000771604938281</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.619548123141032</v>
+        <v>2.616835860551703</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.917660687342315</v>
+        <v>2.915077432749877</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.712328767123288</v>
+        <v>2.70958904109589</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003817452297081398</v>
+        <v>0.003821408958333259</v>
       </c>
     </row>
     <row r="34">
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03046509719104977</v>
+        <v>0.03044176918479434</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.231705685618729</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.61504554898816</v>
+        <v>1.612306743965963</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.567297673051345</v>
+        <v>1.564675260826718</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.632876712328767</v>
+        <v>1.63013698630137</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.006191775833359676</v>
+        <v>0.006202293724457131</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>785.9</v>
+        <v>775</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.1498864522632603</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.6007125588497264</v>
+        <v>0.623225806451613</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>2.942564243537196</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8737</v>
+        <v>8728</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.006357449390757199</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2245961625271831</v>
+        <v>0.2258589220898257</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.690303810662592</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112.5</v>
+        <v>111.9</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>85</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01818649331710654</v>
+        <v>0.01942787233220943</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.4823529411764707</v>
+        <v>0.4641121495327105</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.34213711403012</v>
+        <v>4.340880578763315</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.264579369820606</v>
+        <v>4.258153712074213</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.70958904109589</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002303013409615382</v>
+        <v>0.002303680052596362</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6561</v>
+        <v>6649</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.06252366239041456</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.484682213077275</v>
+        <v>1.451797262746278</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2383561643835616</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>261.5</v>
+        <v>270.6</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>20370</v>
+        <v>21020</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1063031988411979</v>
+        <v>-0.1110045697425465</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.0270004909180166</v>
+        <v>0.02987630827783061</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.472255051267872</v>
+        <v>6.480509228035925</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.242115047156591</v>
+        <v>7.289699145201642</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.884931506849315</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001545056540693814</v>
+        <v>0.001543088613582723</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>113.2</v>
+        <v>115.3</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>20370</v>
+        <v>21020</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05611834129593881</v>
+        <v>-0.06520067623859201</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.3337260677466862</v>
+        <v>0.3164605137963843</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.899871926756946</v>
+        <v>1.899938601470257</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.012828524886741</v>
+        <v>2.032456114565167</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>1.882191780821918</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005263512692179128</v>
+        <v>0.005263327979262885</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1810</v>
+        <v>1873</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04278335325416859</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.507967443093922</v>
+        <v>3.356337998932194</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.821917808219178</v>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>85</v>
+        <v>84.2</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>198</v>
+        <v>191.9</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1546592619614867</v>
+        <v>0.1613708309282219</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>3.091161616161616</v>
+        <v>3.18147993746743</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.601631638355548</v>
+        <v>1.601367763086347</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.387103270305703</v>
+        <v>1.378859982049367</v>
       </c>
       <c r="BC9" s="8" t="n">
         <v>1.63013698630137</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006243632905670717</v>
+        <v>0.006244661738866785</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11910</v>
+        <v>11730</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.008597287376273015</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.5099916036943746</v>
+        <v>0.533162830349531</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.060905589233355</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1098</v>
+        <v>1119</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03170348056136373</v>
+        <v>0.03543774293709638</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5117048087431693</v>
+        <v>0.4693412868632707</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.588450843761543</v>
+        <v>2.587630176392962</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.50890967466072</v>
+        <v>2.499068818037245</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.70958904109589</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003863314624691878</v>
+        <v>0.003864539875609095</v>
       </c>
     </row>
     <row r="12">
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>209.6</v>
+        <v>202.2</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>205.4</v>
+        <v>199.3</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1165725210708736</v>
+        <v>-0.1090293132728682</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.02044790652385586</v>
+        <v>0.01455092824887094</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.173861304275777</v>
+        <v>4.16695875251725</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.724622454958329</v>
+        <v>4.67687524920045</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.46027397260274</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002395863032093526</v>
+        <v>0.002399831770343064</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>236.3</v>
+        <v>240</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1948386114857114</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.06472841726618705</v>
+        <v>0.04831385416666678</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.10725347121063</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>75.7</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2429,7 +2429,7 @@
         <v>-0.1796784113174733</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.2030317040951124</v>
+        <v>0.1397934918648309</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.938108538985669</v>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>112.2</v>
+        <v>110.5</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18060</v>
+        <v>17880</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.04133639163645049</v>
+        <v>-0.03279652847111132</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1656026843853822</v>
+        <v>0.1594985011185683</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.711398764522951</v>
+        <v>1.711199924826783</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.785192167088026</v>
+        <v>1.769224341308283</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.70958904109589</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005843173553293688</v>
+        <v>0.005843852524135809</v>
       </c>
     </row>
     <row r="17">
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>77.3</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2668,7 +2668,7 @@
         <v>0.06288515772714177</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9309831824062094</v>
+        <v>0.9161103979460845</v>
       </c>
       <c r="BA17" s="8" t="n">
         <v>2.954482471915</v>
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>110.8</v>
+        <v>113.3</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>174.8</v>
+        <v>170</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.01467832516827256</v>
+        <v>0.007704213569764262</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.3311212814645308</v>
+        <v>0.3995882352941176</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.153083165122781</v>
+        <v>3.156624159965127</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.107470699741102</v>
+        <v>3.13249078197547</v>
       </c>
       <c r="BC19" s="8" t="n">
         <v>3.375342465753425</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003171498966666362</v>
+        <v>0.003167941285766018</v>
       </c>
     </row>
     <row r="20">
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>29180</v>
+        <v>28760</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5871273362647478</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.01772171830020564</v>
+        <v>-0.003376903337969472</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.388879497333691</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>437.7</v>
+        <v>445.7</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03842676461848402</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5322868357322366</v>
+        <v>0.504783369979807</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7369863013698631</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>215</v>
+        <v>216.1</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3262,7 +3262,7 @@
         <v>0.05528311463325005</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.09865116279069763</v>
+        <v>0.09305876908838484</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.924462227858108</v>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>91</v>
+        <v>90.7</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10410</v>
+        <v>10200</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02732368689329746</v>
+        <v>0.02811444772899778</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5400510441882804</v>
+        <v>0.5665763577450982</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.275931053949171</v>
+        <v>4.275810002184662</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.162204287219252</v>
+        <v>4.158885240480279</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.301369863013699</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002338671946256987</v>
+        <v>0.002338738156019713</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>51</v>
+        <v>47.4</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.309878802464829</v>
+        <v>0.3421644866946098</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.3421052631578947</v>
+        <v>0.3542857142857143</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.801261468930981</v>
+        <v>2.779105340873034</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.138565387621956</v>
+        <v>2.07061456954298</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.213698630136986</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003569820279510076</v>
+        <v>0.003598280300112186</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1401</v>
+        <v>1168</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.05247258548233187</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.3202136302640972</v>
+        <v>0.5835781643835618</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2328767123287671</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>11770</v>
+        <v>11100</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-3.339377803006159</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.1363334049277827</v>
+        <v>0.2049228987387388</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14290</v>
+        <v>14380</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.06431356375963532</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.09139608117564735</v>
+        <v>0.08456536856745478</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.61920621197998</v>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>99.40000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="F30" t="n">
         <v>0.1</v>
@@ -4189,22 +4189,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05731091759948424</v>
+        <v>0.05690527279998519</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.7351019903347056</v>
+        <v>0.7368475657776983</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.582792444536746</v>
+        <v>2.582882635544143</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.442793696295798</v>
+        <v>2.443816586042279</v>
       </c>
       <c r="BC30" s="8" t="n">
         <v>2.70958904109589</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003871778400603777</v>
+        <v>0.003871643202980174</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>62770</v>
+        <v>62830</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2822327210819827</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.2371833678508841</v>
+        <v>0.2360019099156454</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.581354385398546</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>129.6</v>
+        <v>129.9</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4524,7 +4524,7 @@
         <v>-0.1023100000183647</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.05000771604938281</v>
+        <v>0.04758275596612793</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.616835860551703</v>
@@ -4616,7 +4616,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1495</v>
+        <v>1468</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4633,7 +4633,7 @@
         <v>0.03044176918479434</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.231705685618729</v>
+        <v>0.254359673024523</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.612306743965963</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>775</v>
+        <v>759.7</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.1498864522632603</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.623225806451613</v>
+        <v>0.6559168092668157</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>2.942564243537196</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>109.6</v>
+        <v>109.5</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8728</v>
+        <v>8632</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.006357449390757199</v>
+        <v>-0.005826941305026977</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2258589220898257</v>
+        <v>0.2383612766450418</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.690303810662592</v>
+        <v>1.690281380991378</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.70111858598064</v>
+        <v>1.700188278296507</v>
       </c>
       <c r="BC3" s="8" t="n">
         <v>1.70958904109589</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005916096228925877</v>
+        <v>0.005916174734253319</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>111.9</v>
+        <v>112.6</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>85.59999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01942787233220943</v>
+        <v>0.01798041500834919</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.4641121495327105</v>
+        <v>0.4801877934272301</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.340880578763315</v>
+        <v>4.342345469872633</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.258153712074213</v>
+        <v>4.265647360059495</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.70958904109589</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002303680052596362</v>
+        <v>0.002302902905671693</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6649</v>
+        <v>6528</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.06252366239041456</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.451797262746278</v>
+        <v>1.497242647058823</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2383561643835616</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>270.6</v>
+        <v>270</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21020</v>
+        <v>20690</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1110045697425465</v>
+        <v>-0.1107004185181548</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02987630827783061</v>
+        <v>0.04398260028999523</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.480509228035925</v>
+        <v>6.479979006744726</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.289699145201642</v>
+        <v>7.286609756351283</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.884931506849315</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001543088613582723</v>
+        <v>0.001543214876096271</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21020</v>
+        <v>20690</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.06520067623859201</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.3164605137963843</v>
+        <v>0.3374577090381827</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.899938601470257</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1873</v>
+        <v>1812</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04278335325416859</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.356337998932194</v>
+        <v>3.502991761589404</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.821917808219178</v>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>84.2</v>
+        <v>85.8</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>191.9</v>
+        <v>192.1</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1613708309282219</v>
+        <v>0.1480487484287922</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>3.18147993746743</v>
+        <v>3.256501821967724</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.601367763086347</v>
+        <v>1.601891683506494</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.378859982049367</v>
+        <v>1.395316780492838</v>
       </c>
       <c r="BC9" s="8" t="n">
         <v>1.63013698630137</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006244661738866785</v>
+        <v>0.006242619337476233</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11730</v>
+        <v>11590</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.008597287376273015</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.533162830349531</v>
+        <v>0.5516824849007764</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.060905589233355</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105</v>
+        <v>105.4</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1119</v>
+        <v>1078</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03543774293709638</v>
+        <v>0.03393808228357245</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4693412868632707</v>
+        <v>0.5310357068645641</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.587630176392962</v>
+        <v>2.587959937504598</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.499068818037245</v>
+        <v>2.503012493541961</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.70958904109589</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003864539875609095</v>
+        <v>0.003864047451075442</v>
       </c>
     </row>
     <row r="12">
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>202.2</v>
+        <v>209.5</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>199.3</v>
+        <v>194.8</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1090293132728682</v>
+        <v>-0.1164728490133076</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.01455092824887094</v>
+        <v>0.07546201232032845</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.16695875251725</v>
+        <v>4.173770731729526</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.67687524920045</v>
+        <v>4.723986950563324</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.46027397260274</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002399831770343064</v>
+        <v>0.002395915023309439</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>240</v>
+        <v>234.9</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1948386114857114</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.04831385416666678</v>
+        <v>0.07107418050234138</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.10725347121063</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>79.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2429,7 +2429,7 @@
         <v>-0.1796784113174733</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1397934918648309</v>
+        <v>0.1888968668407311</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.938108538985669</v>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>110.5</v>
+        <v>109.8</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17880</v>
+        <v>17680</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.03279652847111132</v>
+        <v>-0.02921941375447046</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1594985011185683</v>
+        <v>0.1651866696832578</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.711199924826783</v>
+        <v>1.711116660371009</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.769224341308283</v>
+        <v>1.762619364885233</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.70958904109589</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005843852524135809</v>
+        <v>0.005844136891187636</v>
       </c>
     </row>
     <row r="17">
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>77.90000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2668,7 +2668,7 @@
         <v>0.06288515772714177</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9161103979460845</v>
+        <v>0.9691952506596304</v>
       </c>
       <c r="BA17" s="8" t="n">
         <v>2.954482471915</v>
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.007704213569764262</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.3995882352941176</v>
+        <v>0.4596932515337424</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.156624159965127</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>28760</v>
+        <v>28260</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5871273362647478</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.003376903337969472</v>
+        <v>0.01425620169851372</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.388879497333691</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>445.7</v>
+        <v>444.7</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03842676461848402</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.504783369979807</v>
+        <v>0.508167186867551</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7369863013698631</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102.7</v>
+        <v>102.6</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>216.1</v>
+        <v>218</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.05528311463325005</v>
+        <v>0.05581705104310562</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.09305876908838484</v>
+        <v>0.0824770642201833</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.924462227858108</v>
+        <v>1.924431664296431</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.823645428579543</v>
+        <v>1.822694246503378</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>1.975342465753425</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005196256832294298</v>
+        <v>0.005196339358537827</v>
       </c>
     </row>
     <row r="23">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>90.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10200</v>
+        <v>10020</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02811444772899778</v>
+        <v>0.02758691482812082</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5665763577450982</v>
+        <v>0.5982349164670659</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.275810002184662</v>
+        <v>4.275890781607252</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.158885240480279</v>
+        <v>4.161098900643804</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.301369863013699</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002338738156019713</v>
+        <v>0.002338693972964653</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>33.4</v>
+        <v>31.3</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3480,7 +3480,7 @@
         <v>0.1735099314985253</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.3993673658682633</v>
+        <v>0.4932546332268368</v>
       </c>
       <c r="BA24" s="8" t="n">
         <v>2.862487756607015</v>
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>47.4</v>
+        <v>48</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>35</v>
+        <v>35.8</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.3421644866946098</v>
+        <v>0.3365544256905079</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.3542857142857143</v>
+        <v>0.3407821229050281</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.779105340873034</v>
+        <v>2.782986687742444</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.07061456954298</v>
+        <v>2.082209773316684</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.213698630136986</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003598280300112186</v>
+        <v>0.003593261888044456</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>99.40000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1168</v>
+        <v>1147</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3808,22 +3808,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05247258548233187</v>
+        <v>0.04819484922381504</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5835781643835618</v>
+        <v>0.6141936181342633</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2328767123287671</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.2212662976129144</v>
+        <v>0.222169296578028</v>
       </c>
       <c r="BC27" s="8" t="n">
         <v>0.210958904109589</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.04294117647058824</v>
+        <v>0.04294117647058823</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>11100</v>
+        <v>11120</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-3.339377803006159</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.2049228987387388</v>
+        <v>0.2027557712230217</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14380</v>
+        <v>14200</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.06431356375963532</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.08456536856745478</v>
+        <v>0.09831338028169001</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.61920621197998</v>
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>558.7</v>
+        <v>561.5</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4192,7 +4192,7 @@
         <v>0.05690527279998519</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.7368475657776983</v>
+        <v>0.7281865271593946</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.582882635544143</v>
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>180.6</v>
+        <v>171.6</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>62830</v>
+        <v>63030</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4412,22 +4412,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2822327210819827</v>
+        <v>-0.2588563562972265</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.2360019099156454</v>
+        <v>0.1706806282722513</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.581354385398546</v>
+        <v>1.580503697638359</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.203157530087363</v>
+        <v>2.132520073628534</v>
       </c>
       <c r="BC32" s="8" t="n">
         <v>1.583561643835616</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.006323693216609201</v>
+        <v>0.006327096871043284</v>
       </c>
     </row>
     <row r="33">
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>129.9</v>
+        <v>130.9</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4524,7 +4524,7 @@
         <v>-0.1023100000183647</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.04758275596612793</v>
+        <v>0.03957983193277315</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.616835860551703</v>
@@ -4616,7 +4616,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1468</v>
+        <v>1494</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4633,7 +4633,7 @@
         <v>0.03044176918479434</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.254359673024523</v>
+        <v>0.2325301204819277</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.612306743965963</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>759.7</v>
+        <v>761.9</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.1498864522632603</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.6559168092668157</v>
+        <v>0.6511353195957474</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>2.942564243537196</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>109.5</v>
+        <v>108.7</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8632</v>
+        <v>8726</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.005826941305026977</v>
+        <v>-0.001555012163512163</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2383612766450418</v>
+        <v>0.2160712220948888</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.690281380991378</v>
+        <v>1.69010080387498</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.700188278296507</v>
+        <v>1.692733024317372</v>
       </c>
       <c r="BC3" s="8" t="n">
         <v>1.70958904109589</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005916174734253319</v>
+        <v>0.005916806841978</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112.6</v>
+        <v>111.9</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>85.2</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01798041500834919</v>
+        <v>0.01942787233220943</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.4801877934272301</v>
+        <v>0.4727144535840191</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.342345469872633</v>
+        <v>4.340880578763315</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.265647360059495</v>
+        <v>4.258153712074213</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.70958904109589</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002302902905671693</v>
+        <v>0.002303680052596362</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6528</v>
+        <v>6499</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.06252366239041456</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.497242647058823</v>
+        <v>1.508385905523927</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2383561643835616</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>270</v>
+        <v>264.9</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>20690</v>
+        <v>20230</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1107004185181548</v>
+        <v>-0.1080822204673974</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.04398260028999523</v>
+        <v>0.04755313890261981</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.479979006744726</v>
+        <v>6.475393169797554</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.286609756351283</v>
+        <v>7.260078583914871</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.884931506849315</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001543214876096271</v>
+        <v>0.001544307772173877</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>115.3</v>
+        <v>113.7</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>20690</v>
+        <v>20230</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.06520067623859201</v>
+        <v>-0.05830402299743202</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.3374577090381827</v>
+        <v>0.3488877904102818</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.899938601470257</v>
+        <v>1.899887971339325</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.032456114565167</v>
+        <v>2.017517349268812</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>1.882191780821918</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005263327979262885</v>
+        <v>0.005263468241735593</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1812</v>
+        <v>1787</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04278335325416859</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.502991761589404</v>
+        <v>3.565988288752098</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.821917808219178</v>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>85.8</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>192.1</v>
+        <v>186.8</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1480487484287922</v>
+        <v>0.151341527556207</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>3.256501821967724</v>
+        <v>3.35686295503212</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.601891683506494</v>
+        <v>1.601762134028138</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.395316780492838</v>
+        <v>1.391213723896485</v>
       </c>
       <c r="BC9" s="8" t="n">
         <v>1.63013698630137</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006242619337476233</v>
+        <v>0.006243124236463148</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11590</v>
+        <v>11430</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.008597287376273015</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.5516824849007764</v>
+        <v>0.573403324584427</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.060905589233355</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105.4</v>
+        <v>104.7</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03393808228357245</v>
+        <v>0.03656775163759845</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5310357068645641</v>
+        <v>0.5265318491620112</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.587959937504598</v>
+        <v>2.587381534185445</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.503012493541961</v>
+        <v>2.496104601071979</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.70958904109589</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003864047451075442</v>
+        <v>0.003864911250187221</v>
       </c>
     </row>
     <row r="12">
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>209.5</v>
+        <v>203</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>194.8</v>
+        <v>193.7</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1164728490133076</v>
+        <v>-0.1098615632545373</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.07546201232032845</v>
+        <v>0.04801239029426951</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.173770731729526</v>
+        <v>4.167725094844624</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.723986950563324</v>
+        <v>4.682108897670706</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.46027397260274</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002395915023309439</v>
+        <v>0.002399390500196321</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>234.9</v>
+        <v>234.5</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1948386114857114</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.07107418050234138</v>
+        <v>0.07290117270788921</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.10725347121063</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>167.1</v>
+        <v>163</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>76.59999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1796784113174733</v>
+        <v>-0.1690992796764703</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1888968668407311</v>
+        <v>0.1627617801047121</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.938108538985669</v>
+        <v>1.937485560189381</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.36262042316643</v>
+        <v>2.331789481943135</v>
       </c>
       <c r="BC15" s="8" t="n">
         <v>1.975342465753425</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005159669749576363</v>
+        <v>0.005161328788960131</v>
       </c>
     </row>
     <row r="16">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>109.8</v>
+        <v>110.3</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17680</v>
+        <v>18010</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.02921941375447046</v>
+        <v>-0.03177816236138964</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1651866696832578</v>
+        <v>0.1490455036091061</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.711116660371009</v>
+        <v>1.711176218885994</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.762619364885233</v>
+        <v>1.767339004725787</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.70958904109589</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005844136891187636</v>
+        <v>0.005843933482496722</v>
       </c>
     </row>
     <row r="17">
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>75.8</v>
+        <v>75.5</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2668,7 +2668,7 @@
         <v>0.06288515772714177</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9691952506596304</v>
+        <v>0.9770198675496686</v>
       </c>
       <c r="BA17" s="8" t="n">
         <v>2.954482471915</v>
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>113.3</v>
+        <v>112</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>163</v>
+        <v>161.3</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.007704213569764262</v>
+        <v>0.01130482512794983</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4596932515337424</v>
+        <v>0.4581525108493489</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.156624159965127</v>
+        <v>3.154799400726013</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.13249078197547</v>
+        <v>3.119533618686007</v>
       </c>
       <c r="BC19" s="8" t="n">
         <v>3.375342465753425</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003167941285766018</v>
+        <v>0.003169773646368357</v>
       </c>
     </row>
     <row r="20">
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>357</v>
+        <v>356.6</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>28260</v>
+        <v>28820</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5871273362647478</v>
+        <v>-0.5867955010153783</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.01425620169851372</v>
+        <v>-0.006566100346981352</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.388879497333691</v>
+        <v>1.388870659001967</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.363941523201175</v>
+        <v>3.36121862761629</v>
       </c>
       <c r="BC20" s="8" t="n">
         <v>1.372602739726027</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.007200048686151358</v>
+        <v>0.007200094504974231</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>444.7</v>
+        <v>437.9</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03842676461848402</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.508167186867551</v>
+        <v>0.5315870015985384</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7369863013698631</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102.6</v>
+        <v>101.9</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>218</v>
+        <v>218.4</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.05581705104310562</v>
+        <v>0.05957709855402057</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.0824770642201833</v>
+        <v>0.07312271062271058</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.924431664296431</v>
+        <v>1.924216488384556</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.822694246503378</v>
+        <v>1.81602310111316</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>1.975342465753425</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005196339358537827</v>
+        <v>0.005196920440275061</v>
       </c>
     </row>
     <row r="23">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>90.90000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10020</v>
+        <v>10100</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02758691482812082</v>
+        <v>0.02811444772899778</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5982349164670659</v>
+        <v>0.5820870147524755</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.275890781607252</v>
+        <v>4.275810002184662</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.161098900643804</v>
+        <v>4.158885240480279</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.301369863013699</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002338693972964653</v>
+        <v>0.002338738156019713</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>31.3</v>
+        <v>33</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3480,7 +3480,7 @@
         <v>0.1735099314985253</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.4932546332268368</v>
+        <v>0.4163293945454543</v>
       </c>
       <c r="BA24" s="8" t="n">
         <v>2.862487756607015</v>
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>48</v>
+        <v>47.5</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>35.8</v>
+        <v>35.2</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.3365544256905079</v>
+        <v>0.3412227403099111</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.3407821229050281</v>
+        <v>0.3494318181818181</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.782986687742444</v>
+        <v>2.779757801355723</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.082209773316684</v>
+        <v>2.072554929029473</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.213698630136986</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003593261888044456</v>
+        <v>0.003597435717285468</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.04819484922381504</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.6141936181342633</v>
+        <v>0.6085839096437879</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2328767123287671</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>11120</v>
+        <v>11300</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-3.339377803006159</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.2027557712230217</v>
+        <v>0.1835968297345134</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14200</v>
+        <v>13500</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.06431356375963532</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.09831338028169001</v>
+        <v>0.1552629629629629</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.61920621197998</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>63030</v>
+        <v>63410</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2588563562972265</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1706806282722513</v>
+        <v>0.1636650370604005</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.580503697638359</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>130.9</v>
+        <v>128.8</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4524,7 +4524,7 @@
         <v>-0.1023100000183647</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.03957983193277315</v>
+        <v>0.05652950310559013</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.616835860551703</v>
@@ -4616,7 +4616,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1494</v>
+        <v>1469</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4633,7 +4633,7 @@
         <v>0.03044176918479434</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2325301204819277</v>
+        <v>0.253505786249149</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.612306743965963</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1498864522632603</v>
+        <v>0.1499764962412413</v>
       </c>
       <c r="AZ2" s="12" t="n">
         <v>0.6511353195957474</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.942564243537196</v>
+        <v>2.939775585050645</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.559004184931045</v>
+        <v>2.556378843097625</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.213698630136986</v>
+        <v>3.210958904109589</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003398396491075146</v>
+        <v>0.00340162019538227</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8726</v>
+        <v>8721</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.001555012163512163</v>
+        <v>-0.001629013101258186</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2160712220948888</v>
+        <v>0.2167684306845545</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.69010080387498</v>
+        <v>1.687364205332899</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.692733024317372</v>
+        <v>1.690117428767026</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.70958904109589</v>
+        <v>1.706849315068493</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005916806841978</v>
+        <v>0.005926402828977343</v>
       </c>
     </row>
     <row r="4">
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>85.09999999999999</v>
+        <v>85</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01942787233220943</v>
+        <v>0.01941408192094371</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.4727144535840191</v>
+        <v>0.4744470588235297</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.340880578763315</v>
+        <v>4.33815482505264</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.258153712074213</v>
+        <v>4.255537471954471</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.70958904109589</v>
+        <v>4.706849315068493</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002303680052596362</v>
+        <v>0.002305127503115027</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6499</v>
+        <v>6841</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.06252366239041456</v>
+        <v>0.06310866582699863</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.508385905523927</v>
+        <v>1.382984943721678</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.2383561643835616</v>
+        <v>0.2356164383561644</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.2243302175947022</v>
+        <v>0.22162968465023</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.210958904109589</v>
+        <v>0.2082191780821918</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.04195402298850575</v>
+        <v>0.04244186046511628</v>
       </c>
     </row>
     <row r="6">
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>20230</v>
+        <v>19960</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1080822204673974</v>
+        <v>-0.1081310935682398</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.04755313890261981</v>
+        <v>0.0617234468937875</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.475393169797554</v>
+        <v>6.472739400895915</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.260078583914871</v>
+        <v>7.257500910971792</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>6.884931506849315</v>
+        <v>6.882191780821918</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001544307772173877</v>
+        <v>0.001544940925416503</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>20230</v>
+        <v>19960</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05830402299743202</v>
+        <v>-0.05839467834934314</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.3488877904102818</v>
+        <v>0.3671342685370742</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.899887971339325</v>
+        <v>1.897148910803036</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.017517349268812</v>
+        <v>2.014802664323613</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>1.882191780821918</v>
+        <v>1.879452054794521</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005263468241735593</v>
+        <v>0.005271067517713801</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1787</v>
+        <v>1770</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04278335325416859</v>
+        <v>0.04291750422205509</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.565988288752098</v>
+        <v>3.609842413559321</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.821917808219178</v>
+        <v>0.8191780821917809</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.7881961345606975</v>
+        <v>0.7854677660270277</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.7945205479452054</v>
+        <v>0.7917808219178082</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01216666666666667</v>
+        <v>0.01220735785953177</v>
       </c>
     </row>
     <row r="9">
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>186.8</v>
+        <v>185.9</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.151341527556207</v>
+        <v>0.1515167584652182</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>3.35686295503212</v>
+        <v>3.377955890263582</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.601762134028138</v>
+        <v>1.599015514789754</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.391213723896485</v>
+        <v>1.388616798700332</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.63013698630137</v>
+        <v>1.627397260273973</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006243124236463148</v>
+        <v>0.006253848013047483</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11430</v>
+        <v>11380</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.008597287376273015</v>
+        <v>-0.008614816241133015</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.573403324584427</v>
+        <v>0.5803163444639718</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.060905589233355</v>
+        <v>4.058174691585139</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.096121119626808</v>
+        <v>4.09343891563766</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.219178082191781</v>
+        <v>4.216438356164383</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002462504921688629</v>
+        <v>0.00246416203342246</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03656775163759845</v>
+        <v>0.03655028534996823</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5265318491620112</v>
+        <v>0.5293798563432837</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.587381534185445</v>
+        <v>2.584645652435944</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.496104601071979</v>
+        <v>2.493507250893569</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.70958904109589</v>
+        <v>2.706849315068493</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003864911250187221</v>
+        <v>0.003869002310075011</v>
       </c>
     </row>
     <row r="12">
@@ -2111,7 +2111,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>-0.1150684931506849</v>
+        <v>-0.1178082191780822</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>193.7</v>
+        <v>193</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1098615632545373</v>
+        <v>-0.1099453482563602</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.04801239029426951</v>
+        <v>0.05181347150259064</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.167725094844624</v>
+        <v>4.16506245303853</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.682108897670706</v>
+        <v>4.679558097785419</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.46027397260274</v>
+        <v>4.457534246575342</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002399390500196321</v>
+        <v>0.00240092438294766</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>234.5</v>
+        <v>233.6</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2317,22 +2317,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1948386114857114</v>
+        <v>-0.1950051684664675</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.07290117270788921</v>
+        <v>0.07703478167808231</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.10725347121063</v>
+        <v>3.104570048065022</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.859168504024069</v>
+        <v>3.856633516703143</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.213698630136986</v>
+        <v>3.210958904109589</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003218276234189501</v>
+        <v>0.00322105793883848</v>
       </c>
     </row>
     <row r="15">
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1690992796764703</v>
+        <v>-0.1693676987003622</v>
       </c>
       <c r="AZ15" s="12" t="n">
         <v>0.1627617801047121</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.937485560189381</v>
+        <v>1.934761630579364</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.331789481943135</v>
+        <v>2.329263655593654</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>1.975342465753425</v>
+        <v>1.972602739726027</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005161328788960131</v>
+        <v>0.005168595366968024</v>
       </c>
     </row>
     <row r="16">
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.03177816236138964</v>
+        <v>-0.03186328154340003</v>
       </c>
       <c r="AZ16" s="12" t="n">
         <v>0.1490455036091061</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.711176218885994</v>
+        <v>1.708438474253499</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.767339004725787</v>
+        <v>1.764666541082219</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.70958904109589</v>
+        <v>1.706849315068493</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005843933482496722</v>
+        <v>0.005853298290047873</v>
       </c>
     </row>
     <row r="17">
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.06288515772714177</v>
+        <v>0.06289605366731629</v>
       </c>
       <c r="AZ17" s="12" t="n">
         <v>0.9770198675496686</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.954482471915</v>
+        <v>2.951736684618842</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.779681746834082</v>
+        <v>2.777069944360456</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.213698630136986</v>
+        <v>3.210958904109589</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003384687536669771</v>
+        <v>0.00338783606685137</v>
       </c>
     </row>
     <row r="18">
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1239481451648965</v>
+        <v>0.1240608256447696</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>2.56</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.683444243959741</v>
+        <v>1.680699683555434</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.49779529527384</v>
+        <v>1.495203502525205</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.70958904109589</v>
+        <v>1.706849315068493</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005940202674297271</v>
+        <v>0.00594990294687598</v>
       </c>
     </row>
     <row r="19">
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.01130482512794983</v>
+        <v>0.01127835448358626</v>
       </c>
       <c r="AZ19" s="12" t="n">
         <v>0.4581525108493489</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.154799400726013</v>
+        <v>3.15207311624646</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.119533618686007</v>
+        <v>3.116919394419433</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.375342465753425</v>
+        <v>3.372602739726027</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003169773646368357</v>
+        <v>0.003172515240353359</v>
       </c>
     </row>
     <row r="20">
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>356.6</v>
+        <v>357</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>28820</v>
+        <v>29030</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5867955010153783</v>
+        <v>-0.5878549496639066</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.006566100346981352</v>
+        <v>-0.01264621908370656</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.388870659001967</v>
+        <v>1.386159151622624</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.36121862761629</v>
+        <v>3.363279870745136</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.372602739726027</v>
+        <v>1.36986301369863</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.007200094504974231</v>
+        <v>0.007214178825204957</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>437.9</v>
+        <v>438</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3124,22 +3124,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03842676461848402</v>
+        <v>0.03843305294704299</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5315870015985384</v>
+        <v>0.531237324200913</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.7369863013698631</v>
+        <v>0.7342465753424658</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.7097142778678577</v>
+        <v>0.7070716530629445</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.7095890410958904</v>
+        <v>0.7068493150684931</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01356877323420074</v>
+        <v>0.01361940298507463</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>218.4</v>
+        <v>220</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.05957709855402057</v>
+        <v>0.05956083228542976</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.07312271062271058</v>
+        <v>0.06531818181818183</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.924216488384556</v>
+        <v>1.921477693012287</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.81602310111316</v>
+        <v>1.813466140370381</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>1.975342465753425</v>
+        <v>1.972602739726027</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005196920440275061</v>
+        <v>0.005204327917189124</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10100</v>
+        <v>10140</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02811444772899778</v>
+        <v>0.02812910431519744</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5820870147524755</v>
+        <v>0.5758460403353058</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.275810002184662</v>
+        <v>4.27306803050799</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.158885240480279</v>
+        <v>4.156159000434229</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.301369863013699</v>
+        <v>4.298630136986302</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002338738156019713</v>
+        <v>0.002340238893601509</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>33</v>
+        <v>32.9</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1735099314985253</v>
+        <v>0.1736089845895693</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.4163293945454543</v>
+        <v>0.4206343471124618</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.862487756607015</v>
+        <v>2.859683216202558</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.439253115609965</v>
+        <v>2.436657569729356</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.213698630136986</v>
+        <v>3.210958904109589</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003493464723794408</v>
+        <v>0.003496890824599531</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>35.2</v>
+        <v>39.9</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.3412227403099111</v>
+        <v>0.3414823144262281</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.3494318181818181</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.779757801355723</v>
+        <v>2.776838273771276</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.072554929029473</v>
+        <v>2.069977549393911</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.213698630136986</v>
+        <v>3.210958904109589</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003597435717285468</v>
+        <v>0.003601218009149238</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3699,22 +3699,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>84.79395658902425</v>
+        <v>85.7281650774971</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.1761052631578948</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.2383561643835616</v>
+        <v>0.2356164383561643</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.002778239562086532</v>
+        <v>0.002716723432873579</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.210958904109589</v>
+        <v>0.2082191780821918</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.04195402298850575</v>
+        <v>0.04244186046511629</v>
       </c>
     </row>
     <row r="27">
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1151</v>
+        <v>1138</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3808,22 +3808,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.04819484922381504</v>
+        <v>0.04844281050629076</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.6085839096437879</v>
+        <v>0.6269596485061513</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.2328767123287671</v>
+        <v>0.2301369863013698</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.222169296578028</v>
+        <v>0.2195036143080014</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.210958904109589</v>
+        <v>0.2082191780821918</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.04294117647058823</v>
+        <v>0.04345238095238096</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>11300</v>
+        <v>11190</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3938,15 +3938,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-3.339377803006159</v>
+        <v>-3.37823082878265</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.1835968297345134</v>
+        <v>0.1952318298480789</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.210958904109589</v>
+        <v>0.2082191780821918</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>13500</v>
+        <v>13200</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.06431356375963532</v>
+        <v>-0.06441449215807431</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1552629629629629</v>
+        <v>0.1815189393939394</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.61920621197998</v>
+        <v>2.616485973365</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>2.799234989986691</v>
+        <v>2.796629438393433</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.70958904109589</v>
+        <v>2.706849315068493</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.00381795062727823</v>
+        <v>0.003821919972740859</v>
       </c>
     </row>
     <row r="30">
@@ -4189,22 +4189,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05690527279998519</v>
+        <v>0.05690624343923208</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.7281865271593946</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.582882635544143</v>
+        <v>2.580142693726169</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.443816586042279</v>
+        <v>2.441221924595923</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.70958904109589</v>
+        <v>2.706849315068493</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003871643202980174</v>
+        <v>0.003875754633383584</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.08291676359977262</v>
+        <v>0.08293979709754964</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>-0.4950290130311615</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.126621061831702</v>
+        <v>2.123875570681433</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.963789954421339</v>
+        <v>1.961212965276331</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.282191780821918</v>
+        <v>2.279452054794521</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004702295194700459</v>
+        <v>0.004708373756938858</v>
       </c>
     </row>
     <row r="32">
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>63410</v>
+        <v>62960</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4412,22 +4412,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2588563562972265</v>
+        <v>-0.2592714897740506</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1636650370604005</v>
+        <v>0.171982210927573</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.580503697638359</v>
+        <v>1.577779065734254</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.132520073628534</v>
+        <v>2.130036908195923</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.583561643835616</v>
+        <v>1.580821917808219</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.006327096871043284</v>
+        <v>0.006338022995219728</v>
       </c>
     </row>
     <row r="33">
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>128.8</v>
+        <v>128</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.1023100000183647</v>
+        <v>-0.1024450576201802</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.05652950310559013</v>
+        <v>0.06313281250000014</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.616835860551703</v>
+        <v>2.614123648150192</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.915077432749877</v>
+        <v>2.912494293908048</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.70958904109589</v>
+        <v>2.706849315068493</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003821408958333259</v>
+        <v>0.003825373756545986</v>
       </c>
     </row>
     <row r="34">
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03044176918479434</v>
+        <v>0.03041837132914476</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.253505786249149</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.612306743965963</v>
+        <v>1.609567941703246</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.564675260826718</v>
+        <v>1.562052838428192</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.63013698630137</v>
+        <v>1.627397260273973</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.006202293724457131</v>
+        <v>0.006212847398922468</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>761.9</v>
+        <v>754.9</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1499764962412413</v>
+        <v>0.1550846283533959</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.6511353195957474</v>
+        <v>0.6439263478606438</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.939775585050645</v>
+        <v>2.936993029436521</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.556378843097625</v>
+        <v>2.542664803377466</v>
       </c>
       <c r="BC2" s="8" t="n">
         <v>3.210958904109589</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.00340162019538227</v>
+        <v>0.003404842946433059</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8721</v>
+        <v>8694</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.001629013101258186</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2167684306845545</v>
+        <v>0.2205472146307799</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.687364205332899</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>85</v>
+        <v>84.3</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.01941408192094371</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.4744470588235297</v>
+        <v>0.486690391459075</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.33815482505264</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6841</v>
+        <v>6670</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.06310866582699863</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.382984943721678</v>
+        <v>1.44407796101949</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2356164383561644</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>264.9</v>
+        <v>277.7</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>19960</v>
+        <v>20950</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1081310935682398</v>
+        <v>-0.1145948105239406</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.0617234468937875</v>
+        <v>0.06042959427207628</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.472739400895915</v>
+        <v>6.483989007875072</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.257500910971792</v>
+        <v>7.323188394357603</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.882191780821918</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001544940925416503</v>
+        <v>0.00154226048006167</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>19960</v>
+        <v>20950</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.05839467834934314</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.3671342685370742</v>
+        <v>0.3025298329355608</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.897148910803036</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1770</v>
+        <v>1800</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04291750422205509</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.609842413559321</v>
+        <v>3.533011706666667</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8191780821917809</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>185.9</v>
+        <v>183.6</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1515167584652182</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>3.377955890263582</v>
+        <v>3.432799564270153</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.599015514789754</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>112.4</v>
+        <v>112</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11380</v>
+        <v>11140</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.008614816241133015</v>
+        <v>-0.007755183017990473</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.5803163444639718</v>
+        <v>0.6086175942549372</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.058174691585139</v>
+        <v>4.057741372280997</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.09343891563766</v>
+        <v>4.089455850848318</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.216438356164383</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.00246416203342246</v>
+        <v>0.002464425177097636</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1072</v>
+        <v>1079</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03655028534996823</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5293798563432837</v>
+        <v>0.5194580222428176</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.584645652435944</v>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>203</v>
+        <v>197.5</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1099453482563602</v>
+        <v>-0.1041349717494501</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.05181347150259064</v>
+        <v>0.02331606217616589</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.16506245303853</v>
+        <v>4.159688289238046</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.679558097785419</v>
+        <v>4.643208695578963</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.457534246575342</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.00240092438294766</v>
+        <v>0.002404026288669759</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>233.6</v>
+        <v>234.4</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1950051684664675</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.07703478167808231</v>
+        <v>0.07335889505119453</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.104570048065022</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>76.40000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2429,7 +2429,7 @@
         <v>-0.1693676987003622</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1627617801047121</v>
+        <v>0.1766225165562916</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.934761630579364</v>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>110.3</v>
+        <v>110.5</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18010</v>
+        <v>17820</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.03186328154340003</v>
+        <v>-0.03288312615522147</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1490455036091061</v>
+        <v>0.1634025364758698</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.708438474253499</v>
+        <v>1.708462214708598</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.764666541082219</v>
+        <v>1.766551965861786</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.706849315068493</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005853298290047873</v>
+        <v>0.005853216953765429</v>
       </c>
     </row>
     <row r="17">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>161.3</v>
+        <v>157.6</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.01127835448358626</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4581525108493489</v>
+        <v>0.4923857868020307</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.15207311624646</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>29030</v>
+        <v>28440</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5878549496639066</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.01264621908370656</v>
+        <v>0.007836858649789002</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.386159151622624</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>438</v>
+        <v>443.1</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03843305294704299</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.531237324200913</v>
+        <v>0.5136130625141049</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7342465753424658</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101.9</v>
+        <v>101.8</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>220</v>
+        <v>219.9</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.05956083228542976</v>
+        <v>0.06010187956439402</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.06531818181818183</v>
+        <v>0.06475670759436092</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.921477693012287</v>
+        <v>1.921446738632287</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.813466140370381</v>
+        <v>1.812511396944064</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>1.972602739726027</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005204327917189124</v>
+        <v>0.005204411758567995</v>
       </c>
     </row>
     <row r="23">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>90.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10140</v>
+        <v>9970</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02812910431519744</v>
+        <v>0.02839358046998515</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5758460403353058</v>
+        <v>0.6009489811434301</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.27306803050799</v>
+        <v>4.273027495674614</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.156159000434229</v>
+        <v>4.155050728459237</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.298630136986302</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002340238893601509</v>
+        <v>0.00234026109359758</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3480,7 +3480,7 @@
         <v>0.1736089845895693</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.4206343471124618</v>
+        <v>0.4163293945454543</v>
       </c>
       <c r="BA24" s="8" t="n">
         <v>2.859683216202558</v>
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>47.5</v>
+        <v>49.8</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>39.9</v>
+        <v>34.9</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.3414823144262281</v>
+        <v>0.3205239255300329</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.4269340974212035</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.776838273771276</v>
+        <v>2.791265266914232</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.069977549393911</v>
+        <v>2.11375592138088</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.210958904109589</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003601218009149238</v>
+        <v>0.003582604677001942</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>99.5</v>
+        <v>99.3</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1138</v>
+        <v>1154</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3808,22 +3808,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.04844281050629076</v>
+        <v>0.05710738462023344</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.6269596485061513</v>
+        <v>0.601177220103986</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.2301369863013698</v>
+        <v>0.2301369863013699</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.2195036143080014</v>
+        <v>0.2177044542963312</v>
       </c>
       <c r="BC27" s="8" t="n">
         <v>0.2082191780821918</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.04345238095238096</v>
+        <v>0.04345238095238095</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>11190</v>
+        <v>11310</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-3.37823082878265</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.1952318298480789</v>
+        <v>0.1825503250221046</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>135.5</v>
+        <v>135.4</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>13200</v>
+        <v>13570</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.06441449215807431</v>
+        <v>-0.06415302853351419</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1815189393939394</v>
+        <v>0.1484554163596168</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.616485973365</v>
+        <v>2.616435487117816</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>2.796629438393433</v>
+        <v>2.795794148927814</v>
       </c>
       <c r="BC29" s="8" t="n">
         <v>2.706849315068493</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003821919972740859</v>
+        <v>0.003821993719790006</v>
       </c>
     </row>
     <row r="30">
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>561.5</v>
+        <v>561</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4192,7 +4192,7 @@
         <v>0.05690624343923208</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.7281865271593946</v>
+        <v>0.7297268003565063</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.580142693726169</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>62960</v>
+        <v>63250</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2592714897740506</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.171982210927573</v>
+        <v>0.166608695652174</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.577779065734254</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>128</v>
+        <v>127.6</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4524,7 +4524,7 @@
         <v>-0.1024450576201802</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.06313281250000014</v>
+        <v>0.0664655172413795</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.614123648150192</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>754.9</v>
+        <v>750</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1550846283533959</v>
+        <v>0.1709951195438013</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.6439263478606438</v>
+        <v>0.5866666666666667</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.936993029436521</v>
+        <v>2.928242722219982</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.542664803377466</v>
+        <v>2.500644685317538</v>
       </c>
       <c r="BC2" s="8" t="n">
         <v>3.210958904109589</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003404842946433059</v>
+        <v>0.003415017451974993</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8694</v>
+        <v>8567</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.001629013101258186</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2205472146307799</v>
+        <v>0.238641004318898</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.687364205332899</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>111.9</v>
+        <v>110.7</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>84.3</v>
+        <v>83</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.01941408192094371</v>
+        <v>0.02192368187738385</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.486690391459075</v>
+        <v>0.4937831325301205</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.33815482505264</v>
+        <v>4.33560711496662</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.255537471954471</v>
+        <v>4.242593837341789</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.706849315068493</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002305127503115027</v>
+        <v>0.002306482053108493</v>
       </c>
     </row>
     <row r="5">
@@ -1201,7 +1201,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>98.8</v>
+        <v>99.5</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6670</v>
+        <v>6672</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,16 +1272,16 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.06310866582699863</v>
+        <v>0.03308288848144259</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.44407796101949</v>
+        <v>1.460656474820144</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2356164383561644</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.22162968465023</v>
+        <v>0.2280711847841208</v>
       </c>
       <c r="BC5" s="8" t="n">
         <v>0.2082191780821918</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>277.7</v>
+        <v>270.4</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>20950</v>
+        <v>20920</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1145948105239406</v>
+        <v>-0.1109530326305887</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.06042959427207628</v>
+        <v>0.03403441682600383</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.483989007875072</v>
+        <v>6.477679694961992</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.323188394357603</v>
+        <v>7.286093910346164</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.882191780821918</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.00154226048006167</v>
+        <v>0.001543762654361791</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>20950</v>
+        <v>20920</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.05839467834934314</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.3025298329355608</v>
+        <v>0.3043977055449332</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.897148910803036</v>
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>96.8</v>
+        <v>97</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1800</v>
+        <v>1781</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,16 +1617,16 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04291750422205509</v>
+        <v>0.04031324719785246</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.533011706666667</v>
+        <v>3.590836260527793</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.8191780821917809</v>
+        <v>0.8191780821917808</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.7854677660270277</v>
+        <v>0.7874340583456831</v>
       </c>
       <c r="BC8" s="8" t="n">
         <v>0.7917808219178082</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>183.6</v>
+        <v>182</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1515167584652182</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>3.432799564270153</v>
+        <v>3.47176923076923</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.599015514789754</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>112</v>
+        <v>111.1</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11140</v>
+        <v>10850</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.007755183017990473</v>
+        <v>-0.005806788412494948</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.6086175942549372</v>
+        <v>0.6383410138248848</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.057741372280997</v>
+        <v>4.056756462437005</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.089455850848318</v>
+        <v>4.080450776725048</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.216438356164383</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002464425177097636</v>
+        <v>0.002465023496626841</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1079</v>
+        <v>1088</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03655028534996823</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5194580222428176</v>
+        <v>0.5068889761029411</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.584645652435944</v>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>197.5</v>
+        <v>201</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>193</v>
+        <v>193.3</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1041349717494501</v>
+        <v>-0.1078558667550956</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.02331606217616589</v>
+        <v>0.0398344542162441</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.159688289238046</v>
+        <v>4.163136493728737</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.643208695578963</v>
+        <v>4.666439355025053</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.457534246575342</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002404026288669759</v>
+        <v>0.002402035103836685</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>234.4</v>
+        <v>233.1</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1950051684664675</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.07335889505119453</v>
+        <v>0.07934502359502371</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.104570048065022</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>163</v>
+        <v>161.9</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>75.5</v>
+        <v>76.3</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1693676987003622</v>
+        <v>-0.1664571243653934</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1766225165562916</v>
+        <v>0.1564285714285716</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.934761630579364</v>
+        <v>1.934590371813222</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.329263655593654</v>
+        <v>2.320924847855423</v>
       </c>
       <c r="BC15" s="8" t="n">
         <v>1.972602739726027</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005168595366968024</v>
+        <v>0.005169052914611253</v>
       </c>
     </row>
     <row r="16">
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17820</v>
+        <v>17750</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2538,7 +2538,7 @@
         <v>-0.03288312615522147</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1634025364758698</v>
+        <v>0.1679906028169014</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.708462214708598</v>
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>75.5</v>
+        <v>76</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2668,7 +2668,7 @@
         <v>0.06289605366731629</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9770198675496686</v>
+        <v>0.9640131578947366</v>
       </c>
       <c r="BA17" s="8" t="n">
         <v>2.951736684618842</v>
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>157.6</v>
+        <v>157</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.01127835448358626</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4923857868020307</v>
+        <v>0.4980891719745224</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.15207311624646</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>28440</v>
+        <v>28370</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5878549496639066</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.007836858649789002</v>
+        <v>0.01032359041240749</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.386159151622624</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>443.1</v>
+        <v>445</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03843305294704299</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5136130625141049</v>
+        <v>0.50715044494382</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7342465753424658</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>219.9</v>
+        <v>220.4</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3262,7 +3262,7 @@
         <v>0.06010187956439402</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.06475670759436092</v>
+        <v>0.06234119782214154</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.921446738632287</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9970</v>
+        <v>9927</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.02839358046998515</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.6009489811434301</v>
+        <v>0.607883685101239</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.273027495674614</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>34.9</v>
+        <v>35</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3589,7 +3589,7 @@
         <v>0.3205239255300329</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.4269340974212035</v>
+        <v>0.4228571428571428</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>2.791265266914232</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>99.3</v>
+        <v>99.5</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1154</v>
+        <v>1160</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3808,22 +3808,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05710738462023344</v>
+        <v>0.04844281050629076</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.601177220103986</v>
+        <v>0.5961035172413793</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.2301369863013699</v>
+        <v>0.2301369863013698</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.2177044542963312</v>
+        <v>0.2195036143080014</v>
       </c>
       <c r="BC27" s="8" t="n">
         <v>0.2082191780821918</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.04345238095238095</v>
+        <v>0.04345238095238096</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>11310</v>
+        <v>11100</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-3.37823082878265</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.1825503250221046</v>
+        <v>0.2049228987387388</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>13570</v>
+        <v>13620</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.06415302853351419</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1484554163596168</v>
+        <v>0.1442393538913362</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.616435487117816</v>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>99.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="F30" t="n">
         <v>0.1</v>
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>561</v>
+        <v>558.5</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4189,22 +4189,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05690624343923208</v>
+        <v>0.06058113454327251</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.7297268003565063</v>
+        <v>0.7217537296329453</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.580142693726169</v>
+        <v>2.579324970465352</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.441221924595923</v>
+        <v>2.43199212814219</v>
       </c>
       <c r="BC30" s="8" t="n">
         <v>2.706849315068493</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003875754633383584</v>
+        <v>0.003876983363672798</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>63250</v>
+        <v>62610</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2592714897740506</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.166608695652174</v>
+        <v>0.1785337805462386</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.577779065734254</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>127.6</v>
+        <v>125.4</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4524,7 +4524,7 @@
         <v>-0.1024450576201802</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.0664655172413795</v>
+        <v>0.08517543859649135</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.614123648150192</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>70</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>750</v>
+        <v>700</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1709951195438013</v>
+        <v>0.162397228892249</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.5866666666666667</v>
+        <v>0.7388571428571427</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.928242722219982</v>
+        <v>2.932986943549029</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.500644685317538</v>
+        <v>2.52322258746619</v>
       </c>
       <c r="BC2" s="8" t="n">
         <v>3.210958904109589</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003415017451974993</v>
+        <v>0.003409493527407118</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8567</v>
+        <v>8634</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.001629013101258186</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.238641004318898</v>
+        <v>0.2290291271716469</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.687364205332899</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>110.7</v>
+        <v>111.4</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>83</v>
+        <v>81.5</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02192368187738385</v>
+        <v>0.02045557021158273</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.4937831325301205</v>
+        <v>0.5308957055214725</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.33560711496662</v>
+        <v>4.33709874312665</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.242593837341789</v>
+        <v>4.250159310931479</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.706849315068493</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002306482053108493</v>
+        <v>0.002305688800802104</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6672</v>
+        <v>6520</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.03308288848144259</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.460656474820144</v>
+        <v>1.518021472392638</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2356164383561644</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>270.4</v>
+        <v>262</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>20920</v>
+        <v>20610</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1109530326305887</v>
+        <v>-0.1066149382420804</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.03403441682600383</v>
+        <v>0.01698204754973309</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.477679694961992</v>
+        <v>6.470066516466213</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.286093910346164</v>
+        <v>7.242192413353118</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.882191780821918</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001543762654361791</v>
+        <v>0.001545579164379557</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>20920</v>
+        <v>20610</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.05839467834934314</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.3043977055449332</v>
+        <v>0.3240174672489082</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.897148910803036</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1781</v>
+        <v>1777</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04031324719785246</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.590836260527793</v>
+        <v>3.601170163196398</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8191780821917808</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>182</v>
+        <v>182.1</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1515167584652182</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>3.47176923076923</v>
+        <v>3.469313563975837</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.599015514789754</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>111.1</v>
+        <v>111.2</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>10850</v>
+        <v>10740</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.005806788412494948</v>
+        <v>-0.006024256933494241</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.6383410138248848</v>
+        <v>0.656610800744879</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.056756462437005</v>
+        <v>4.056866583334664</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.080450776725048</v>
+        <v>4.081454312777153</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.216438356164383</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002465023496626841</v>
+        <v>0.002464956585232388</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1088</v>
+        <v>1072</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03655028534996823</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5068889761029411</v>
+        <v>0.5293798563432837</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.584645652435944</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>193.3</v>
+        <v>190.7</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2211,7 +2211,7 @@
         <v>-0.1078558667550956</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.0398344542162441</v>
+        <v>0.0540115364446776</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.163136493728737</v>
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>233.1</v>
+        <v>233.2</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1950051684664675</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.07934502359502371</v>
+        <v>0.07888218267581482</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.104570048065022</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>76.3</v>
+        <v>75</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2429,7 +2429,7 @@
         <v>-0.1664571243653934</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1564285714285716</v>
+        <v>0.1764733333333335</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.934590371813222</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17750</v>
+        <v>17570</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2538,7 +2538,7 @@
         <v>-0.03288312615522147</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1679906028169014</v>
+        <v>0.1799563574274332</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.708462214708598</v>
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2668,7 +2668,7 @@
         <v>0.06289605366731629</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9640131578947366</v>
+        <v>0.9901999999999997</v>
       </c>
       <c r="BA17" s="8" t="n">
         <v>2.951736684618842</v>
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>157</v>
+        <v>158.9</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.01127835448358626</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4980891719745224</v>
+        <v>0.4801762114537445</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.15207311624646</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>28370</v>
+        <v>28170</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5878549496639066</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.01032359041240749</v>
+        <v>0.0174966368477103</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.386159151622624</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>445</v>
+        <v>444.5</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03843305294704299</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.50715044494382</v>
+        <v>0.5088457772778401</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7342465753424658</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101.8</v>
+        <v>102.9</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>220.4</v>
+        <v>227.8</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.06010187956439402</v>
+        <v>0.05419483102791098</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.06234119782214154</v>
+        <v>0.0389376646180859</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.921446738632287</v>
+        <v>1.921784803491922</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.812511396944064</v>
+        <v>1.822988262632679</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>1.972602739726027</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005204411758567995</v>
+        <v>0.005203496240489465</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9927</v>
+        <v>9999</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.02839358046998515</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.607883685101239</v>
+        <v>0.5963057647764776</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.273027495674614</v>
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>49.8</v>
+        <v>47.5</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>35</v>
+        <v>35.5</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.3205239255300329</v>
+        <v>0.3414823144262281</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.4228571428571428</v>
+        <v>0.3380281690140845</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.791265266914232</v>
+        <v>2.776838273771276</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.11375592138088</v>
+        <v>2.069977549393911</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.210958904109589</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003582604677001942</v>
+        <v>0.003601218009149238</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.04844281050629076</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5961035172413793</v>
+        <v>0.597480655737705</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2301369863013698</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>11100</v>
+        <v>10780</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-3.37823082878265</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.2049228987387388</v>
+        <v>0.240690554359926</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>13620</v>
+        <v>13530</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.06415302853351419</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1442393538913362</v>
+        <v>0.151850702143385</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.616435487117816</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>62610</v>
+        <v>62280</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2592714897740506</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1785337805462386</v>
+        <v>0.1847784200385356</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.577779065734254</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>700</v>
+        <v>696.2</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.162397228892249</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7388571428571427</v>
+        <v>0.748348175811548</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>2.932986943549029</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8634</v>
+        <v>8595</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.001629013101258186</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2290291271716469</v>
+        <v>0.2346058736474694</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.687364205332899</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>111.4</v>
+        <v>111.2</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>81.5</v>
+        <v>81.8</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02045557021158273</v>
+        <v>0.02087383110940005</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.5308957055214725</v>
+        <v>0.5225427872860637</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.33709874312665</v>
+        <v>4.33667413338872</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.250159310931479</v>
+        <v>4.24800205592104</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.706849315068493</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002305688800802104</v>
+        <v>0.00230591455396855</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6520</v>
+        <v>6601</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.03308288848144259</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.518021472392638</v>
+        <v>1.487123163157098</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2356164383561644</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1066149382420804</v>
+        <v>-0.1081830219767087</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.01698204754973309</v>
+        <v>0.02862688015526449</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.470066516466213</v>
+        <v>6.472830716835205</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.242192413353118</v>
+        <v>7.258025891346235</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.882191780821918</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001545579164379557</v>
+        <v>0.001544919130047843</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>113.7</v>
+        <v>113.4</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05839467834934314</v>
+        <v>-0.05708329330948547</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.3240174672489082</v>
+        <v>0.320524017467249</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.897148910803036</v>
+        <v>1.897139284154529</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.014802664323613</v>
+        <v>2.011990317589325</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>1.879452054794521</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005271067517713801</v>
+        <v>0.005271094264676807</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1777</v>
+        <v>1774</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04031324719785246</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.601170163196398</v>
+        <v>3.608951172491545</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8191780821917808</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>182.1</v>
+        <v>182.7</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1515167584652182</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>3.469313563975837</v>
+        <v>3.45463601532567</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.599015514789754</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>111.2</v>
+        <v>110.3</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>10740</v>
+        <v>10630</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.006024256933494241</v>
+        <v>-0.004058115428290113</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.656610800744879</v>
+        <v>0.6602069614299153</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.056866583334664</v>
+        <v>4.055869229867206</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.081454312777153</v>
+        <v>4.072395480797931</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.216438356164383</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002464956585232388</v>
+        <v>0.00246556272730899</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03655028534996823</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5293798563432837</v>
+        <v>0.5322385102803739</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.584645652435944</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>190.7</v>
+        <v>191</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2211,7 +2211,7 @@
         <v>-0.1078558667550956</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.0540115364446776</v>
+        <v>0.05235602094240832</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.163136493728737</v>
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>233.2</v>
+        <v>231.8</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1950051684664675</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.07888218267581482</v>
+        <v>0.08539829594477988</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.104570048065022</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>161.9</v>
+        <v>162.2</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>75</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1664571243653934</v>
+        <v>-0.1672539098942746</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1764733333333335</v>
+        <v>0.1849731903485257</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.934590371813222</v>
+        <v>1.934637248682125</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.320924847855423</v>
+        <v>2.323201839874749</v>
       </c>
       <c r="BC15" s="8" t="n">
         <v>1.972602739726027</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005169052914611253</v>
+        <v>0.005168927666833668</v>
       </c>
     </row>
     <row r="16">
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17570</v>
+        <v>17600</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2538,7 +2538,7 @@
         <v>-0.03288312615522147</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1799563574274332</v>
+        <v>0.1779450681818182</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.708462214708598</v>
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>75</v>
+        <v>75.5</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2668,7 +2668,7 @@
         <v>0.06289605366731629</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9901999999999997</v>
+        <v>0.9770198675496686</v>
       </c>
       <c r="BA17" s="8" t="n">
         <v>2.951736684618842</v>
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>158.9</v>
+        <v>157.9</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.01127835448358626</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4801762114537445</v>
+        <v>0.4895503483217227</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.15207311624646</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>28170</v>
+        <v>28240</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5878549496639066</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.0174966368477103</v>
+        <v>0.01497451345609058</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.386159151622624</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>444.5</v>
+        <v>448</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03843305294704299</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5088457772778401</v>
+        <v>0.4970579196428571</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7342465753424658</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102.9</v>
+        <v>102.5</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>227.8</v>
+        <v>227.9</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.05419483102791098</v>
+        <v>0.05633158488664117</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.0389376646180859</v>
+        <v>0.03444493198771381</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.921784803491922</v>
+        <v>1.921662487237738</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.822988262632679</v>
+        <v>1.819184917625992</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>1.972602739726027</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005203496240489465</v>
+        <v>0.005203827449623755</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9999</v>
+        <v>9900</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.02839358046998515</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5963057647764776</v>
+        <v>0.6122688224242423</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.273027495674614</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>72.3</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>33</v>
+        <v>32.8</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1736089845895693</v>
+        <v>0.1924557712585674</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.4163293945454543</v>
+        <v>0.3579547213414636</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.859683216202558</v>
+        <v>2.847260386690346</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.436657569729356</v>
+        <v>2.38772829593942</v>
       </c>
       <c r="BC24" s="8" t="n">
         <v>3.210958904109589</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003496890824599531</v>
+        <v>0.00351214804474697</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>35.5</v>
+        <v>35.1</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3589,7 +3589,7 @@
         <v>0.3414823144262281</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.3380281690140845</v>
+        <v>0.3532763532763532</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>2.776838273771276</v>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1159</v>
+        <v>1156</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.04844281050629076</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.597480655737705</v>
+        <v>0.601626366782007</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2301369863013698</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>10780</v>
+        <v>10960</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-3.37823082878265</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.240690554359926</v>
+        <v>0.2203142496350365</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>13530</v>
+        <v>13520</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.06415302853351419</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.151850702143385</v>
+        <v>0.1527026627218935</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.616435487117816</v>
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>558.5</v>
+        <v>555.7</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4192,7 +4192,7 @@
         <v>0.06058113454327251</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.7217537296329453</v>
+        <v>0.7304291128306637</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.579324970465352</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>62280</v>
+        <v>62600</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2592714897740506</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1847784200385356</v>
+        <v>0.1787220447284346</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.577779065734254</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>125.4</v>
+        <v>126.1</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4524,7 +4524,7 @@
         <v>-0.1024450576201802</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.08517543859649135</v>
+        <v>0.07915146708961163</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.614123648150192</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.162397228892249</v>
+        <v>0.1624983834653163</v>
       </c>
       <c r="AZ2" s="12" t="n">
         <v>0.748348175811548</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.932986943549029</v>
+        <v>2.930191614868854</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.52322258746619</v>
+        <v>2.520598442583794</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.210958904109589</v>
+        <v>3.208219178082192</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003409493527407118</v>
+        <v>0.003412746097987714</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.001629013101258186</v>
+        <v>-0.001703240440347008</v>
       </c>
       <c r="AZ3" s="12" t="n">
         <v>0.2346058736474694</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.687364205332899</v>
+        <v>1.684627616379729</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.690117428767026</v>
+        <v>1.68750183775295</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.706849315068493</v>
+        <v>1.704109589041096</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005926402828977343</v>
+        <v>0.005936029958650468</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>111.2</v>
+        <v>111</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02087383110940005</v>
+        <v>0.02128019196158979</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.5225427872860637</v>
+        <v>0.5198044009779952</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.33667413338872</v>
+        <v>4.333521610478425</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.24800205592104</v>
+        <v>4.24322496861019</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.706849315068493</v>
+        <v>4.704109589041096</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.00230591455396855</v>
+        <v>0.002307592046113274</v>
       </c>
     </row>
     <row r="5">
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.03308288848144259</v>
+        <v>0.03333041784790625</v>
       </c>
       <c r="AZ5" s="12" t="n">
         <v>1.487123163157098</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.2356164383561644</v>
+        <v>0.2328767123287671</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.2280711847841208</v>
+        <v>0.2253651961719796</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.2082191780821918</v>
+        <v>0.2054794520547945</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.04244186046511628</v>
+        <v>0.04294117647058824</v>
       </c>
     </row>
     <row r="6">
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>20610</v>
+        <v>20810</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1081830219767087</v>
+        <v>-0.1082319492052185</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02862688015526449</v>
+        <v>0.01874098990869766</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.472830716835205</v>
+        <v>6.470177015224881</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.258025891346235</v>
+        <v>7.255448330379616</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>6.882191780821918</v>
+        <v>6.879452054794521</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001544919130047843</v>
+        <v>0.001545552768721651</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>20610</v>
+        <v>20810</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05708329330948547</v>
+        <v>-0.05717245505826921</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.320524017467249</v>
+        <v>0.3078327727054302</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.897139284154529</v>
+        <v>1.894400212642041</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.011990317589325</v>
+        <v>2.009275421370002</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>1.879452054794521</v>
+        <v>1.876712328767123</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005271094264676807</v>
+        <v>0.005278715623692535</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1774</v>
+        <v>1778</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04031324719785246</v>
+        <v>0.04043959643913091</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.608951172491545</v>
+        <v>3.598582328458942</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.8191780821917808</v>
+        <v>0.8164383561643835</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.7874340583456831</v>
+        <v>0.7847051947644208</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.7917808219178082</v>
+        <v>0.7890410958904109</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01220735785953177</v>
+        <v>0.01224832214765101</v>
       </c>
     </row>
     <row r="9">
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1515167584652182</v>
+        <v>0.1516926331481733</v>
       </c>
       <c r="AZ9" s="12" t="n">
         <v>3.45463601532567</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.599015514789754</v>
+        <v>1.596268870327</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.388616798700332</v>
+        <v>1.386019867092116</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.627397260273973</v>
+        <v>1.624657534246575</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006253848013047483</v>
+        <v>0.006264608792346787</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>10630</v>
+        <v>10580</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.004058115428290113</v>
+        <v>-0.004072892550144437</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.6602069614299153</v>
+        <v>0.6680529300567108</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.055869229867206</v>
+        <v>4.053137014398234</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.072395480797931</v>
+        <v>4.06971251618664</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.216438356164383</v>
+        <v>4.213698630136986</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.00246556272730899</v>
+        <v>0.00246722476059317</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03655028534996823</v>
+        <v>0.0365327904038982</v>
       </c>
       <c r="AZ11" s="12" t="n">
         <v>0.5322385102803739</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.584645652435944</v>
+        <v>2.581909776960356</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.493507250893569</v>
+        <v>2.490909888103281</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.706849315068493</v>
+        <v>2.704109589041096</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003869002310075011</v>
+        <v>0.003873102030611175</v>
       </c>
     </row>
     <row r="12">
@@ -2111,7 +2111,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>-0.1178082191780822</v>
+        <v>-0.1205479452054795</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>191</v>
+        <v>195.6</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1078558667550956</v>
+        <v>-0.1079387638646849</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.05235602094240832</v>
+        <v>0.02760736196319025</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.163136493728737</v>
+        <v>4.160473319655832</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.666439355025053</v>
+        <v>4.66388757982612</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.457534246575342</v>
+        <v>4.454794520547945</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002402035103836685</v>
+        <v>0.002403572678319022</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>231.8</v>
+        <v>232.5</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2317,22 +2317,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1950051684664675</v>
+        <v>-0.1951719814899235</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.08539829594477988</v>
+        <v>0.08213043010752696</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.104570048065022</v>
+        <v>3.101886697043582</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.856633516703143</v>
+        <v>3.854098795896662</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.210958904109589</v>
+        <v>3.208219178082192</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.00322105793883848</v>
+        <v>0.003223844381398918</v>
       </c>
     </row>
     <row r="15">
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1672539098942746</v>
+        <v>-0.1675209463338584</v>
       </c>
       <c r="AZ15" s="12" t="n">
         <v>0.1849731903485257</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.934637248682125</v>
+        <v>1.931913234107697</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.323201839874749</v>
+        <v>2.320674887373772</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>1.972602739726027</v>
+        <v>1.96986301369863</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005168927666833668</v>
+        <v>0.005176215900099029</v>
       </c>
     </row>
     <row r="16">
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17600</v>
+        <v>17450</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.03288312615522147</v>
+        <v>-0.03296999197968759</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1779450681818182</v>
+        <v>0.188070670487106</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.708462214708598</v>
+        <v>1.705724510840817</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.766551965861786</v>
+        <v>1.763879607348222</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.706849315068493</v>
+        <v>1.704109589041096</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005853216953765429</v>
+        <v>0.005862611421976119</v>
       </c>
     </row>
     <row r="17">
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.06289605366731629</v>
+        <v>0.06290697673450069</v>
       </c>
       <c r="AZ17" s="12" t="n">
         <v>0.9770198675496686</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.951736684618842</v>
+        <v>2.948990882166305</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.777069944360456</v>
+        <v>2.774458110366625</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.210958904109589</v>
+        <v>3.208219178082192</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.00338783606685137</v>
+        <v>0.003390990477615204</v>
       </c>
     </row>
     <row r="18">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>89</v>
+        <v>89.2</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1240608256447696</v>
+        <v>0.1226935973834777</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>2.56</v>
+        <v>2.568000000000001</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.680699683555434</v>
+        <v>1.678018619610151</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.495203502525205</v>
+        <v>1.494636313523921</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.706849315068493</v>
+        <v>1.704109589041096</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.00594990294687598</v>
+        <v>0.005959409438688632</v>
       </c>
     </row>
     <row r="19">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>157.9</v>
+        <v>154.8</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.01127835448358626</v>
+        <v>0.01125184271313513</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4895503483217227</v>
+        <v>0.5193798449612403</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.15207311624646</v>
+        <v>3.149346852257836</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.116919394419433</v>
+        <v>3.114305180209417</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.372602739726027</v>
+        <v>3.36986301369863</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003172515240353359</v>
+        <v>0.00317526156029171</v>
       </c>
     </row>
     <row r="20">
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>28240</v>
+        <v>27990</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5878549496639066</v>
+        <v>-0.5885841447505966</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.01497451345609058</v>
+        <v>0.02404002357984991</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.386159151622624</v>
+        <v>1.383438848802663</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.363279870745136</v>
+        <v>3.362628909777947</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.36986301369863</v>
+        <v>1.367123287671233</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.007214178825204957</v>
+        <v>0.007228364310178791</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3124,22 +3124,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03843305294704299</v>
+        <v>0.03843941531739248</v>
       </c>
       <c r="AZ21" s="12" t="n">
         <v>0.4970579196428571</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.7342465753424658</v>
+        <v>0.7315068493150685</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.7070716530629445</v>
+        <v>0.70442901003665</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.7068493150684931</v>
+        <v>0.7041095890410959</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01361940298507463</v>
+        <v>0.01367041198501873</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102.5</v>
+        <v>109.9</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>227.9</v>
+        <v>229.8</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.05633158488664117</v>
+        <v>0.01868867434734623</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.03444493198771381</v>
+        <v>0.09995648389904255</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.921662487237738</v>
+        <v>1.921082283086089</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.819184917625992</v>
+        <v>1.885838462194437</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>1.972602739726027</v>
+        <v>1.96986301369863</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005203827449623755</v>
+        <v>0.005205399106557619</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9900</v>
+        <v>9836</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02839358046998515</v>
+        <v>0.0284084257705148</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.6122688224242423</v>
+        <v>0.622759388165921</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.273027495674614</v>
+        <v>4.270285493692074</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.155050728459237</v>
+        <v>4.152324491597438</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.298630136986302</v>
+        <v>4.295890410958904</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.00234026109359758</v>
+        <v>0.002341763803561067</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1924557712585674</v>
+        <v>0.1925715352992118</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.3579547213414636</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.847260386690346</v>
+        <v>2.844443801918676</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.38772829593942</v>
+        <v>2.385134742634131</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.210958904109589</v>
+        <v>3.208219178082192</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.00351214804474697</v>
+        <v>0.003515625794137557</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>35.1</v>
+        <v>34.9</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.3414823144262281</v>
+        <v>0.3417425029710373</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.3532763532763532</v>
+        <v>0.3610315186246418</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.776838273771276</v>
+        <v>2.773918292692336</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.069977549393911</v>
+        <v>2.067399882279956</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.210958904109589</v>
+        <v>3.208219178082192</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003601218009149238</v>
+        <v>0.003605008852043044</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3699,22 +3699,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>85.7281650774971</v>
+        <v>86.68441514536849</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.1761052631578948</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.2356164383561643</v>
+        <v>0.2328767123287671</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.002716723432873579</v>
+        <v>0.002655850665625016</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.2082191780821918</v>
+        <v>0.2054794520547945</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.04244186046511629</v>
+        <v>0.04294117647058825</v>
       </c>
     </row>
     <row r="27">
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1156</v>
+        <v>1210</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3808,22 +3808,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.04844281050629076</v>
+        <v>0.04869679564780004</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.601626366782007</v>
+        <v>0.530148826446281</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.2301369863013698</v>
+        <v>0.2273972602739726</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.2195036143080014</v>
+        <v>0.2168379470764998</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.2082191780821918</v>
+        <v>0.2054794520547945</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.04345238095238096</v>
+        <v>0.04397590361445783</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>10960</v>
+        <v>10900</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3938,15 +3938,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-3.37823082878265</v>
+        <v>-3.417998042159337</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.2203142496350365</v>
+        <v>0.2270315757798167</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.2082191780821918</v>
+        <v>0.2054794520547945</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>13520</v>
+        <v>13430</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.06415302853351419</v>
+        <v>-0.06425393560421563</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1527026627218935</v>
+        <v>0.1604274013402829</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.616435487117816</v>
+        <v>2.613715246270763</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>2.795794148927814</v>
+        <v>2.793188607166039</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.706849315068493</v>
+        <v>2.704109589041096</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003821993719790006</v>
+        <v>0.003825971484180595</v>
       </c>
     </row>
     <row r="30">
@@ -4189,22 +4189,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.06058113454327251</v>
+        <v>0.06058548198807408</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.7304291128306637</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.579324970465352</v>
+        <v>2.576584276198603</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.43199212814219</v>
+        <v>2.429398025860942</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.706849315068493</v>
+        <v>2.704109589041096</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003876983363672798</v>
+        <v>0.003881107283148382</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.08293979709754964</v>
+        <v>0.08296290594127034</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>-0.4950290130311615</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.123875570681433</v>
+        <v>2.121130060615015</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.961212965276331</v>
+        <v>1.958635932014134</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.279452054794521</v>
+        <v>2.276712328767123</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004708373756938858</v>
+        <v>0.004714468096831617</v>
       </c>
     </row>
     <row r="32">
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>62600</v>
+        <v>62240</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4412,22 +4412,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2592714897740506</v>
+        <v>-0.2596878278597914</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1787220447284346</v>
+        <v>0.1855398457583548</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.577779065734254</v>
+        <v>1.575054478100056</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.130036908195923</v>
+        <v>2.12755447954698</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.580821917808219</v>
+        <v>1.578082191780822</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.006338022995219728</v>
+        <v>0.006348986742390474</v>
       </c>
     </row>
     <row r="33">
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>126.1</v>
+        <v>125.8</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.1024450576201802</v>
+        <v>-0.102580373528932</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.07915146708961163</v>
+        <v>0.08172496025437215</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.614123648150192</v>
+        <v>2.611411486074697</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.912494293908048</v>
+        <v>2.909911271211636</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.706849315068493</v>
+        <v>2.704109589041096</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003825373756545986</v>
+        <v>0.003829346716641484</v>
       </c>
     </row>
     <row r="34">
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03041837132914476</v>
+        <v>0.03039490326687519</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.253505786249149</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.609567941703246</v>
+        <v>1.606829142214129</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.562052838428192</v>
+        <v>1.559430405876101</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.627397260273973</v>
+        <v>1.624657534246575</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.006212847398922468</v>
+        <v>0.00622343703962234</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>696.2</v>
+        <v>695.8</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.1624983834653163</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.748348175811548</v>
+        <v>0.7493532624317332</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>2.930191614868854</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8595</v>
+        <v>8557</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.001703240440347008</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2346058736474694</v>
+        <v>0.2400885221456117</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.684627616379729</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>111</v>
+        <v>109.8</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>81.8</v>
+        <v>81.3</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02128019196158979</v>
+        <v>0.02381711834395683</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.5198044009779952</v>
+        <v>0.5126199261992621</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.333521610478425</v>
+        <v>4.330938537209782</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.24322496861019</v>
+        <v>4.230187657162009</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.704109589041096</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002307592046113274</v>
+        <v>0.002308968348103717</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6601</v>
+        <v>6602</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.03333041784790625</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.487123163157098</v>
+        <v>1.486746440472584</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2328767123287671</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>20810</v>
+        <v>20940</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1082319492052185</v>
+        <v>-0.109265970864719</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.01874098990869766</v>
+        <v>0.02005730659025784</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.470177015224881</v>
+        <v>6.471991878741362</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.255448330379616</v>
+        <v>7.265908416033382</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.879452054794521</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001545552768721651</v>
+        <v>0.001545119367786467</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>20810</v>
+        <v>20940</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.05717245505826921</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.3078327727054302</v>
+        <v>0.2997134670487105</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.894400212642041</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1778</v>
+        <v>1796</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04043959643913091</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.598582328458942</v>
+        <v>3.552494086859689</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8164383561643835</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>182.7</v>
+        <v>184.1</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1516926331481733</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>3.45463601532567</v>
+        <v>3.420760456273764</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.596268870327</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>110.3</v>
+        <v>110.8</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>10580</v>
+        <v>10460</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.004072892550144437</v>
+        <v>-0.005168345294599788</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.6680529300567108</v>
+        <v>0.6948374760994265</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.053137014398234</v>
+        <v>4.05369316653799</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.06971251618664</v>
+        <v>4.074752896497258</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.213698630136986</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.00246722476059317</v>
+        <v>0.0024668862662194</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>104.7</v>
+        <v>104</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1070</v>
+        <v>1076</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.0365327904038982</v>
+        <v>0.03919199665203198</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5322385102803739</v>
+        <v>0.5135073605947953</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.581909776960356</v>
+        <v>2.581324111717545</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.490909888103281</v>
+        <v>2.483972278495027</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.704109589041096</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003873102030611175</v>
+        <v>0.003873980781648635</v>
       </c>
     </row>
     <row r="12">
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>195.6</v>
+        <v>199</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2211,7 +2211,7 @@
         <v>-0.1079387638646849</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.02760736196319025</v>
+        <v>0.01005025125628145</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.160473319655832</v>
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>232.5</v>
+        <v>232</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1951719814899235</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.08213043010752696</v>
+        <v>0.0844626077586208</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.101886697043582</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>74.59999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2429,7 +2429,7 @@
         <v>-0.1675209463338584</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1849731903485257</v>
+        <v>0.1770838881491346</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.931913234107697</v>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>110.5</v>
+        <v>109.7</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17450</v>
+        <v>17280</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.03296999197968759</v>
+        <v>-0.0288669973485524</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.188070670487106</v>
+        <v>0.1910728287037038</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.705724510840817</v>
+        <v>1.705629005891838</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.763879607348222</v>
+        <v>1.75632894900598</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.704109589041096</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005862611421976119</v>
+        <v>0.005862939692897169</v>
       </c>
     </row>
     <row r="17">
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>75.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2668,7 +2668,7 @@
         <v>0.06290697673450069</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9770198675496686</v>
+        <v>1.000871313672922</v>
       </c>
       <c r="BA17" s="8" t="n">
         <v>2.948990882166305</v>
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>154.8</v>
+        <v>153</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.01125184271313513</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5193798449612403</v>
+        <v>0.5372549019607844</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.149346852257836</v>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>357</v>
+        <v>357.2</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27990</v>
+        <v>27810</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5885841447505966</v>
+        <v>-0.5887498804570687</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.02404002357984991</v>
+        <v>0.03124551945343401</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.383438848802663</v>
+        <v>1.383443263528795</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.362628909777947</v>
+        <v>3.363994799725218</v>
       </c>
       <c r="BC20" s="8" t="n">
         <v>1.367123287671233</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.007228364310178791</v>
+        <v>0.007228341243639196</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>448</v>
+        <v>442.6</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03843941531739248</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.4970579196428571</v>
+        <v>0.5153229733393581</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7315068493150685</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>109.9</v>
+        <v>103</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>229.8</v>
+        <v>223.3</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.01868867434734623</v>
+        <v>0.05363913914885517</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.09995648389904255</v>
+        <v>0.06090461262875047</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.921082283086089</v>
+        <v>1.919076892710424</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.885838462194437</v>
+        <v>1.821379655904471</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>1.96986301369863</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005205399106557619</v>
+        <v>0.005210838626625542</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9836</v>
+        <v>9957</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.0284084257705148</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.622759388165921</v>
+        <v>0.6030392027719191</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.270285493692074</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>68.90000000000001</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>32.8</v>
+        <v>31.4</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1925715352992118</v>
+        <v>0.1942968603732242</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.3579547213414636</v>
+        <v>0.4123241286624202</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.844443801918676</v>
+        <v>2.843297520131462</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.385134742634131</v>
+        <v>2.38072929308624</v>
       </c>
       <c r="BC24" s="8" t="n">
         <v>3.208219178082192</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003515625794137557</v>
+        <v>0.003517043126579888</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>34.9</v>
+        <v>35.6</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3589,7 +3589,7 @@
         <v>0.3417425029710373</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.3610315186246418</v>
+        <v>0.3342696629213482</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>2.773918292692336</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>10900</v>
+        <v>10910</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-3.417998042159337</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.2270315757798167</v>
+        <v>0.2259068905591202</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>13430</v>
+        <v>13290</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.06425393560421563</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1604274013402829</v>
+        <v>0.1726516177577124</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.613715246270763</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>62240</v>
+        <v>60780</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2596878278597914</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1855398457583548</v>
+        <v>0.2140177690029614</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.575054478100056</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>125.8</v>
+        <v>119.9</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4524,7 +4524,7 @@
         <v>-0.102580373528932</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.08172496025437215</v>
+        <v>0.134954128440367</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.611411486074697</v>
@@ -4616,7 +4616,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1469</v>
+        <v>1466</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4633,7 +4633,7 @@
         <v>0.03039490326687519</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.253505786249149</v>
+        <v>0.2560709413369713</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.606829142214129</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>71.59999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>695.8</v>
+        <v>639.3</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1624983834653163</v>
+        <v>0.1760624187742313</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7493532624317332</v>
+        <v>0.837478492100735</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.930191614868854</v>
+        <v>2.922689783449672</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.520598442583794</v>
+        <v>2.485148523405662</v>
       </c>
       <c r="BC2" s="8" t="n">
         <v>3.208219178082192</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003412746097987714</v>
+        <v>0.003421505784372684</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8557</v>
+        <v>8533</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.001703240440347008</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2400885221456117</v>
+        <v>0.2435764073596625</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.684627616379729</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>81.3</v>
+        <v>81.5</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.02381711834395683</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.5126199261992621</v>
+        <v>0.5089079754601229</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.330938537209782</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6602</v>
+        <v>6601</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.03333041784790625</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.486746440472584</v>
+        <v>1.487123163157098</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2328767123287671</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>267</v>
+        <v>258.6</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>20940</v>
+        <v>20440</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.109265970864719</v>
+        <v>-0.1048595950437166</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02005730659025784</v>
+        <v>0.01213307240704498</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.471991878741362</v>
+        <v>6.464215948193968</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.265908416033382</v>
+        <v>7.221454771120142</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.879452054794521</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001545119367786467</v>
+        <v>0.001546978021796115</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>113.4</v>
+        <v>108.4</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>20940</v>
+        <v>20440</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05717245505826921</v>
+        <v>-0.03447496766791744</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2997134670487105</v>
+        <v>0.27279843444227</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.894400212642041</v>
+        <v>1.894233623698784</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.009275421370002</v>
+        <v>1.961868993829755</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>1.876712328767123</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005278715623692535</v>
+        <v>0.005279179861918749</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1796</v>
+        <v>1768</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04043959643913091</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.552494086859689</v>
+        <v>3.624592409502262</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8164383561643835</v>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>85.40000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>184.1</v>
+        <v>183.3</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1516926331481733</v>
+        <v>0.1459266200145003</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>3.420760456273764</v>
+        <v>3.476448445171848</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.596268870327</v>
+        <v>1.596495742102589</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.386019867092116</v>
+        <v>1.393191949832169</v>
       </c>
       <c r="BC9" s="8" t="n">
         <v>1.624657534246575</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006264608792346787</v>
+        <v>0.006263718553254627</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>10460</v>
+        <v>10680</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.005168345294599788</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.6948374760994265</v>
+        <v>0.6599250936329588</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.05369316653799</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1076</v>
+        <v>1060</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03919199665203198</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5135073605947953</v>
+        <v>0.5363527547169811</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.581324111717545</v>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>201</v>
+        <v>202.9</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>199</v>
+        <v>198.3</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1079387638646849</v>
+        <v>-0.1099253315907801</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.01005025125628145</v>
+        <v>0.02319717599596571</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.160473319655832</v>
+        <v>4.16230431228835</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.66388757982612</v>
+        <v>4.676354085806532</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.454794520547945</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002403572678319022</v>
+        <v>0.002402515349605038</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>232</v>
+        <v>228.6</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1951719814899235</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.0844626077586208</v>
+        <v>0.1005919728783902</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.101886697043582</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>75.09999999999999</v>
+        <v>74.3</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2429,7 +2429,7 @@
         <v>-0.1675209463338584</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1770838881491346</v>
+        <v>0.189757738896366</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.931913234107697</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17280</v>
+        <v>16910</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2538,7 +2538,7 @@
         <v>-0.0288669973485524</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1910728287037038</v>
+        <v>0.2171341502069781</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.705629005891838</v>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>96.3</v>
+        <v>96.2</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>74.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.06290697673450069</v>
+        <v>0.06326717243736693</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>1.000871313672922</v>
+        <v>1.015</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.948990882166305</v>
+        <v>2.948790470838616</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.774458110366625</v>
+        <v>2.773329739955193</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.208219178082192</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003390990477615204</v>
+        <v>0.003391220942583983</v>
       </c>
     </row>
     <row r="18">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>153</v>
+        <v>157.9</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.01125184271313513</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5372549019607844</v>
+        <v>0.4895503483217227</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.149346852257836</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27810</v>
+        <v>27330</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5887498804570687</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.03124551945343401</v>
+        <v>0.0493574056348336</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.383443263528795</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>442.6</v>
+        <v>448</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03843941531739248</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5153229733393581</v>
+        <v>0.4970579196428571</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7315068493150685</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>223.3</v>
+        <v>229.3</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3262,7 +3262,7 @@
         <v>0.05363913914885517</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.06090461262875047</v>
+        <v>0.03314435237679891</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.919076892710424</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9957</v>
+        <v>9853</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.0284084257705148</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.6030392027719191</v>
+        <v>0.6199595394296151</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.270285493692074</v>
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>47.5</v>
+        <v>46.5</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>35.6</v>
+        <v>35.1</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.3417425029710373</v>
+        <v>0.351303063075594</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.3342696629213482</v>
+        <v>0.3247863247863247</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.773918292692336</v>
+        <v>2.767275603051404</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.067399882279956</v>
+        <v>2.047857123000245</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.208219178082192</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003605008852043044</v>
+        <v>0.00361366247329079</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1210</v>
+        <v>1139</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.04869679564780004</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.530148826446281</v>
+        <v>0.6255312379280071</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2273972602739726</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>10910</v>
+        <v>10770</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-3.417998042159337</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.2259068905591202</v>
+        <v>0.2418425418755805</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>13290</v>
+        <v>13080</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.06425393560421563</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1726516177577124</v>
+        <v>0.1914785932721712</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.613715246270763</v>
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>555.7</v>
+        <v>552.1</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4192,7 +4192,7 @@
         <v>0.06058548198807408</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.7304291128306637</v>
+        <v>0.7417124760007243</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.576584276198603</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>60780</v>
+        <v>61050</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2596878278597914</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.2140177690029614</v>
+        <v>0.2086486486486487</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.575054478100056</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>119.9</v>
+        <v>122.3</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4524,7 +4524,7 @@
         <v>-0.102580373528932</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.134954128440367</v>
+        <v>0.1126819296811121</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.611411486074697</v>
@@ -4616,7 +4616,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1466</v>
+        <v>1440</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4633,7 +4633,7 @@
         <v>0.03039490326687519</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2560709413369713</v>
+        <v>0.2787499999999998</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.606829142214129</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>69.09999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>639.3</v>
+        <v>659.5</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1760624187742313</v>
+        <v>0.1673065563936408</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.837478492100735</v>
+        <v>0.8224412433661867</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.922689783449672</v>
+        <v>2.92754279426137</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.485148523405662</v>
+        <v>2.507946844148573</v>
       </c>
       <c r="BC2" s="8" t="n">
         <v>3.208219178082192</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003421505784372684</v>
+        <v>0.003415833927210973</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8533</v>
+        <v>8369</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.001703240440347008</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2435764073596625</v>
+        <v>0.267945690524555</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.684627616379729</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>109.8</v>
+        <v>110.9</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>81.5</v>
+        <v>80.2</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02381711834395683</v>
+        <v>0.02149026750163547</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.5089079754601229</v>
+        <v>0.5487281795511223</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.330938537209782</v>
+        <v>4.333308104222993</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.230187657162009</v>
+        <v>4.242143309716903</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.704109589041096</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002308968348103717</v>
+        <v>0.002307705743391423</v>
       </c>
     </row>
     <row r="5">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>258.6</v>
+        <v>260.9</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>20440</v>
+        <v>20080</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1048595950437166</v>
+        <v>-0.1060828625154999</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.01213307240704498</v>
+        <v>0.03944223107569722</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.464215948193968</v>
+        <v>6.46638568660396</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.221454771120142</v>
+        <v>7.233764087799562</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.879452054794521</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001546978021796115</v>
+        <v>0.001546458947030708</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>108.4</v>
+        <v>111.8</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>20440</v>
+        <v>20080</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.03447496766791744</v>
+        <v>-0.05007832824393775</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.27279843444227</v>
+        <v>0.3362549800796812</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.894233623698784</v>
+        <v>1.894348139063308</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>1.961868993829755</v>
+        <v>1.994215097294645</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>1.876712328767123</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005279179861918749</v>
+        <v>0.005278860729868095</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1768</v>
+        <v>1741</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04043959643913091</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.624592409502262</v>
+        <v>3.696312107983918</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8164383561643835</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>183.3</v>
+        <v>182</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1459266200145003</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>3.476448445171848</v>
+        <v>3.508423076923076</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.596495742102589</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>110.8</v>
+        <v>109</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>10680</v>
+        <v>10700</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.005168345294599788</v>
+        <v>-0.001195186192163681</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.6599250936329588</v>
+        <v>0.6299065420560748</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.05369316653799</v>
+        <v>4.051670211485144</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.074752896497258</v>
+        <v>4.05651850639224</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.213698630136986</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.0024668862662194</v>
+        <v>0.002468117955813213</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>104</v>
+        <v>104.4</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1060</v>
+        <v>1053</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03919199665203198</v>
+        <v>0.03766938941644479</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5363527547169811</v>
+        <v>0.5525142564102565</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.581324111717545</v>
+        <v>2.581659546986132</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.483972278495027</v>
+        <v>2.487940352984666</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.704109589041096</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003873980781648635</v>
+        <v>0.003873477434960062</v>
       </c>
     </row>
     <row r="12">
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>202.9</v>
+        <v>202.1</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1099253315907801</v>
+        <v>-0.1090917730793429</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.02319717599596571</v>
+        <v>0.01916288451840642</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.16230431228835</v>
+        <v>4.161536855083607</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.676354085806532</v>
+        <v>4.671117326492292</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.454794520547945</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002402515349605038</v>
+        <v>0.002402958413737056</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>228.6</v>
+        <v>224.8</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1951719814899235</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.1005919728783902</v>
+        <v>0.1191962855871886</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.101886697043582</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>74.3</v>
+        <v>76</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2429,7 +2429,7 @@
         <v>-0.1675209463338584</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.189757738896366</v>
+        <v>0.1631447368421053</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.931913234107697</v>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>109.7</v>
+        <v>109</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16910</v>
+        <v>16750</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.0288669973485524</v>
+        <v>-0.02523779582600495</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2171341502069781</v>
+        <v>0.2209197373134328</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.705629005891838</v>
+        <v>1.705544544933741</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.75632894900598</v>
+        <v>1.749703196975107</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.704109589041096</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005862939692897169</v>
+        <v>0.005863230033894242</v>
       </c>
     </row>
     <row r="17">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>96.2</v>
+        <v>95.3</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>74</v>
+        <v>74.3</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.06326717243736693</v>
+        <v>0.0665319012978688</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>1.015</v>
+        <v>0.9880888290713326</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.948790470838616</v>
+        <v>2.9469707165613</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.773329739955193</v>
+        <v>2.7631341481442</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.208219178082192</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003391220942583983</v>
+        <v>0.003393315021354739</v>
       </c>
     </row>
     <row r="18">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>89.2</v>
+        <v>89</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1226935973834777</v>
+        <v>0.1241739011692074</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>2.568000000000001</v>
+        <v>2.56</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.678018619610151</v>
+        <v>1.677955106251871</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.494636313523921</v>
+        <v>1.492611689798792</v>
       </c>
       <c r="BC18" s="8" t="n">
         <v>1.704109589041096</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005959409438688632</v>
+        <v>0.005959635012129426</v>
       </c>
     </row>
     <row r="19">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>157.9</v>
+        <v>155.3</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.01125184271313513</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4895503483217227</v>
+        <v>0.5144880875724405</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.149346852257836</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27330</v>
+        <v>27000</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5887498804570687</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.0493574056348336</v>
+        <v>0.06218288503703695</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.383443263528795</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>448</v>
+        <v>446.3</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03843941531739248</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.4970579196428571</v>
+        <v>0.5027603585032487</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7315068493150685</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103</v>
+        <v>101.4</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>229.3</v>
+        <v>217.3</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.05363913914885517</v>
+        <v>0.06226128671407001</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.03314435237679891</v>
+        <v>0.07326277036355267</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.919076892710424</v>
+        <v>1.9185834890783</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.821379655904471</v>
+        <v>1.806131422724744</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>1.96986301369863</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005210838626625542</v>
+        <v>0.005212178702113227</v>
       </c>
     </row>
     <row r="23">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>90.59999999999999</v>
+        <v>90</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9853</v>
+        <v>9860</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.0284084257705148</v>
+        <v>0.03000393254644408</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.6199595394296151</v>
+        <v>0.6080888742393511</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.270285493692074</v>
+        <v>4.270040452529486</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.152324491597438</v>
+        <v>4.145654514126765</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.295890410958904</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002341763803561067</v>
+        <v>0.002341898188359364</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>31.4</v>
+        <v>33.4</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3480,7 +3480,7 @@
         <v>0.1942968603732242</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.4123241286624202</v>
+        <v>0.327753821556886</v>
       </c>
       <c r="BA24" s="8" t="n">
         <v>2.843297520131462</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>35.1</v>
+        <v>31.9</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3589,7 +3589,7 @@
         <v>0.351303063075594</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.3247863247863247</v>
+        <v>0.4576802507836992</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>2.767275603051404</v>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1139</v>
+        <v>1127</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.04869679564780004</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.6255312379280071</v>
+        <v>0.6428394676131322</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2273972602739726</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>10770</v>
+        <v>10740</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-3.417998042159337</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.2418425418755805</v>
+        <v>0.245311375791434</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>13080</v>
+        <v>13000</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.06425393560421563</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1914785932721712</v>
+        <v>0.1988107692307692</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.613715246270763</v>
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>552.1</v>
+        <v>551.1</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4192,7 +4192,7 @@
         <v>0.06058548198807408</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.7417124760007243</v>
+        <v>0.7448729050988929</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.576584276198603</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>61050</v>
+        <v>61330</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2596878278597914</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.2086486486486487</v>
+        <v>0.2031306049241806</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.575054478100056</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>122.3</v>
+        <v>120.8</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4524,7 +4524,7 @@
         <v>-0.102580373528932</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.1126819296811121</v>
+        <v>0.1264983443708612</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.611411486074697</v>
@@ -4616,7 +4616,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4633,7 +4633,7 @@
         <v>0.03039490326687519</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2787499999999998</v>
+        <v>0.2796386379430158</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.606829142214129</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1673065563936408</v>
+        <v>0.1674121825732627</v>
       </c>
       <c r="AZ2" s="12" t="n">
         <v>0.8224412433661867</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.92754279426137</v>
+        <v>2.924744750027849</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.507946844148573</v>
+        <v>2.505323135810519</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.208219178082192</v>
+        <v>3.205479452054794</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003415833927210973</v>
+        <v>0.003419101786542153</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8369</v>
+        <v>8474</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.001703240440347008</v>
+        <v>-0.001777695263379242</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.267945690524555</v>
+        <v>0.2522347750767053</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.684627616379729</v>
+        <v>1.681891037061412</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.68750183775295</v>
+        <v>1.684886251369805</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.704109589041096</v>
+        <v>1.701369863013699</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005936029958650468</v>
+        <v>0.005945688382686151</v>
       </c>
     </row>
     <row r="4">
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>80.2</v>
+        <v>80.3</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02149026750163547</v>
+        <v>0.02147750270929551</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.5487281795511223</v>
+        <v>0.5467995018679952</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.333308104222993</v>
+        <v>4.330581353460824</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.242143309716903</v>
+        <v>4.239526902917286</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.704109589041096</v>
+        <v>4.701369863013698</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002307705743391423</v>
+        <v>0.002309158790426234</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6601</v>
+        <v>6612</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.03333041784790625</v>
+        <v>0.03358385015785047</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.487123163157098</v>
+        <v>1.482985480943739</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.2328767123287671</v>
+        <v>0.2301369863013699</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.2253651961719796</v>
+        <v>0.2226592320170473</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.2054794520547945</v>
+        <v>0.2027397260273973</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.04294117647058824</v>
+        <v>0.04345238095238095</v>
       </c>
     </row>
     <row r="6">
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>20080</v>
+        <v>20000</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1060828625154999</v>
+        <v>-0.1061311520476367</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.03944223107569722</v>
+        <v>0.04360000000000008</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.46638568660396</v>
+        <v>6.463731438500159</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.233764087799562</v>
+        <v>7.23118548465695</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>6.879452054794521</v>
+        <v>6.876712328767123</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001546458947030708</v>
+        <v>0.00154709398048883</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>20080</v>
+        <v>20000</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05007832824393775</v>
+        <v>-0.0501582324094231</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.3362549800796812</v>
+        <v>0.3415999999999999</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.894348139063308</v>
+        <v>1.89160899953235</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>1.994215097294645</v>
+        <v>1.991499072872646</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>1.876712328767123</v>
+        <v>1.873972602739726</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005278860729868095</v>
+        <v>0.005286504770527227</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1741</v>
+        <v>1743</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04043959643913091</v>
+        <v>0.04056679664352857</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.696312107983918</v>
+        <v>3.690923339070568</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.8164383561643835</v>
+        <v>0.8136986301369864</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.7847051947644208</v>
+        <v>0.7819763543884618</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.7890410958904109</v>
+        <v>0.7863013698630137</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01224832214765101</v>
+        <v>0.01228956228956229</v>
       </c>
     </row>
     <row r="9">
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>182</v>
+        <v>174.7</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1459266200145003</v>
+        <v>0.1460931634870607</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>3.508423076923076</v>
+        <v>3.696811677160847</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.596495742102589</v>
+        <v>1.593749461675701</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.393191949832169</v>
+        <v>1.390593288966682</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.624657534246575</v>
+        <v>1.621917808219178</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006263718553254627</v>
+        <v>0.006274511923276696</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>10700</v>
+        <v>10560</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.001195186192163681</v>
+        <v>-0.001208222745799985</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.6299065420560748</v>
+        <v>0.6515151515151516</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.051670211485144</v>
+        <v>4.048937149368941</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.05651850639224</v>
+        <v>4.053835085126512</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.213698630136986</v>
+        <v>4.210958904109589</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002468117955813213</v>
+        <v>0.002469783953440369</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03766938941644479</v>
+        <v>0.03765289113661231</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5525142564102565</v>
+        <v>0.5466390842005677</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.581659546986132</v>
+        <v>2.578923454185004</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.487940352984666</v>
+        <v>2.485343100967158</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.704109589041096</v>
+        <v>2.701369863013698</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003873477434960062</v>
+        <v>0.003877586976756631</v>
       </c>
     </row>
     <row r="12">
@@ -2111,7 +2111,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>-0.1205479452054795</v>
+        <v>-0.1232876712328767</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1090917730793429</v>
+        <v>-0.1091753145785747</v>
       </c>
       <c r="AZ13" s="12" t="n">
         <v>0.01916288451840642</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.161536855083607</v>
+        <v>4.158874099314747</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.671117326492292</v>
+        <v>4.668566292981986</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.454794520547945</v>
+        <v>4.452054794520548</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002402958413737056</v>
+        <v>0.002404496929024057</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>224.8</v>
+        <v>225.5</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2317,22 +2317,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1951719814899235</v>
+        <v>-0.1953390511384759</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.1191962855871886</v>
+        <v>0.1157220620842572</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.101886697043582</v>
+        <v>3.099203418277102</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.854098795896662</v>
+        <v>3.851564342300958</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.208219178082192</v>
+        <v>3.205479452054794</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003223844381398918</v>
+        <v>0.003226635573846639</v>
       </c>
     </row>
     <row r="15">
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1675209463338584</v>
+        <v>-0.1677886470425115</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1631447368421053</v>
+        <v>0.1189746835443037</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.931913234107697</v>
+        <v>1.929189259138994</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.320674887373772</v>
+        <v>2.318148211128216</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>1.96986301369863</v>
+        <v>1.967123287671233</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005176215900099029</v>
+        <v>0.005183524608914236</v>
       </c>
     </row>
     <row r="16">
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16750</v>
+        <v>16770</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.02523779582600495</v>
+        <v>-0.02531363004292031</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2209197373134328</v>
+        <v>0.2194636612999405</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.705544544933741</v>
+        <v>1.702806583616394</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.749703196975107</v>
+        <v>1.747030261325371</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.704109589041096</v>
+        <v>1.701369863013699</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005863230033894242</v>
+        <v>0.005872657585550413</v>
       </c>
     </row>
     <row r="17">
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.0665319012978688</v>
+        <v>0.06654577556947415</v>
       </c>
       <c r="AZ17" s="12" t="n">
         <v>0.9880888290713326</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.9469707165613</v>
+        <v>2.944223244466702</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.7631341481442</v>
+        <v>2.760522156580346</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.208219178082192</v>
+        <v>3.205479452054794</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003393315021354739</v>
+        <v>0.003396481574144809</v>
       </c>
     </row>
     <row r="18">
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1241739011692074</v>
+        <v>0.1242873737368327</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>2.56</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.677955106251871</v>
+        <v>1.675210511963826</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.492611689798792</v>
+        <v>1.490019857108127</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.704109589041096</v>
+        <v>1.701369863013699</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005959635012129426</v>
+        <v>0.005969399026918197</v>
       </c>
     </row>
     <row r="19">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>155.3</v>
+        <v>155.1</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.01125184271313513</v>
+        <v>0.01122528971023235</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5144880875724405</v>
+        <v>0.516441005802708</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.149346852257836</v>
+        <v>3.146620608812316</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.114305180209417</v>
+        <v>3.11169097611669</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.36986301369863</v>
+        <v>3.367123287671233</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.00317526156029171</v>
+        <v>0.003178012618360901</v>
       </c>
     </row>
     <row r="20">
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27000</v>
+        <v>26920</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5887498804570687</v>
+        <v>-0.5894806891546405</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.06218288503703695</v>
+        <v>0.065339446359584</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.383443263528795</v>
+        <v>1.380723004629139</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.363994799725218</v>
+        <v>3.363357016715958</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.367123287671233</v>
+        <v>1.364383561643836</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.007228341243639196</v>
+        <v>0.007242582303961821</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>446.3</v>
+        <v>445.6</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3124,22 +3124,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03843941531739248</v>
+        <v>0.03844585255665141</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5027603585032487</v>
+        <v>0.505121068222621</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.7315068493150685</v>
+        <v>0.7287671232876712</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.70442901003665</v>
+        <v>0.7017863487956048</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.7041095890410959</v>
+        <v>0.7013698630136986</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01367041198501873</v>
+        <v>0.0137218045112782</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101.4</v>
+        <v>102</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>217.3</v>
+        <v>223</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.06226128671407001</v>
+        <v>0.05898666310529611</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.07326277036355267</v>
+        <v>0.05201793721973091</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.9185834890783</v>
+        <v>1.916031092548013</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.806131422724744</v>
+        <v>1.809306159654156</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>1.96986301369863</v>
+        <v>1.967123287671233</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005212178702113227</v>
+        <v>0.005219121985490125</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9860</v>
+        <v>9796</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.03000393254644408</v>
+        <v>0.03001982212296182</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.6080888742393511</v>
+        <v>0.6185949673336057</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.270040452529486</v>
+        <v>4.267298281844049</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.145654514126765</v>
+        <v>4.142928310883154</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.295890410958904</v>
+        <v>4.293150684931507</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002341898188359364</v>
+        <v>0.002343403094774675</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1942968603732242</v>
+        <v>0.1944144031692417</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.327753821556886</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.843297520131462</v>
+        <v>2.840479646229135</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.38072929308624</v>
+        <v>2.378135794990623</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.208219178082192</v>
+        <v>3.205479452054794</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003517043126579888</v>
+        <v>0.003520532179582927</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>31.9</v>
+        <v>34.3</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.351303063075594</v>
+        <v>0.3515732775576871</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.4576802507836992</v>
+        <v>0.3556851311953353</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.767275603051404</v>
+        <v>2.764347589456071</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.047857123000245</v>
+        <v>2.045281329068068</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.208219178082192</v>
+        <v>3.205479452054794</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.00361366247329079</v>
+        <v>0.003617490086320026</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3699,22 +3699,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>86.68441514536849</v>
+        <v>87.66349388692869</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.1761052631578948</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.2328767123287671</v>
+        <v>0.2301369863013698</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.002655850665625016</v>
+        <v>0.002595622800460134</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.2054794520547945</v>
+        <v>0.2027397260273973</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.04294117647058825</v>
+        <v>0.04345238095238096</v>
       </c>
     </row>
     <row r="27">
@@ -3808,22 +3808,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.04869679564780004</v>
+        <v>0.0489570250224249</v>
       </c>
       <c r="AZ27" s="12" t="n">
         <v>0.6428394676131322</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.2273972602739726</v>
+        <v>0.2246575342465753</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.2168379470764998</v>
+        <v>0.2141722958018919</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.2054794520547945</v>
+        <v>0.2027397260273973</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.04397590361445783</v>
+        <v>0.04451219512195122</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>10740</v>
+        <v>10660</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3938,15 +3938,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-3.417998042159337</v>
+        <v>-3.458712092693471</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.245311375791434</v>
+        <v>0.2546570521575986</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.2054794520547945</v>
+        <v>0.2027397260273973</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>13000</v>
+        <v>13060</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.06425393560421563</v>
+        <v>-0.0643550391755475</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1988107692307692</v>
+        <v>0.1933032159264931</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.613715246270763</v>
+        <v>2.610995042179248</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>2.793188607166039</v>
+        <v>2.790583128752753</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.704109589041096</v>
+        <v>2.701369863013698</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003825971484180595</v>
+        <v>0.003829957483049671</v>
       </c>
     </row>
     <row r="30">
@@ -4189,22 +4189,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.06058548198807408</v>
+        <v>0.0605898480496373</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.7448729050988929</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.576584276198603</v>
+        <v>2.573843577783582</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.429398025860942</v>
+        <v>2.426803898337071</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.704109589041096</v>
+        <v>2.701369863013698</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003881107283148382</v>
+        <v>0.003885239991395016</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.08296290594127034</v>
+        <v>0.08298609042149702</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>-0.4950290130311615</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.121130060615015</v>
+        <v>2.118384531559156</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.958635932014134</v>
+        <v>1.956058854582964</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.276712328767123</v>
+        <v>2.273972602739726</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004714468096831617</v>
+        <v>0.004720578276050704</v>
       </c>
     </row>
     <row r="32">
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>61330</v>
+        <v>60340</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4412,22 +4412,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2596878278597914</v>
+        <v>-0.2601053757304991</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.2031306049241806</v>
+        <v>0.2228704010606564</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.575054478100056</v>
+        <v>1.572329934928092</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.12755447954698</v>
+        <v>2.125072791926899</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.578082191780822</v>
+        <v>1.575342465753425</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.006348986742390474</v>
+        <v>0.006359988306434764</v>
       </c>
     </row>
     <row r="33">
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.102580373528932</v>
+        <v>-0.1027159484915333</v>
       </c>
       <c r="AZ33" s="12" t="n">
         <v>0.1264983443708612</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.611411486074697</v>
+        <v>2.608699374463915</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.909911271211636</v>
+        <v>2.907328365057093</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.704109589041096</v>
+        <v>2.701369863013698</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003829346716641484</v>
+        <v>0.003833327863642774</v>
       </c>
     </row>
     <row r="34">
@@ -4616,7 +4616,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1439</v>
+        <v>1400</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03039490326687519</v>
+        <v>0.03037136463833637</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2796386379430158</v>
+        <v>0.3152857142857142</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.606829142214129</v>
+        <v>1.604090345512827</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.559430405876101</v>
+        <v>1.556807963190891</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.624657534246575</v>
+        <v>1.621917808219178</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.00622343703962234</v>
+        <v>0.006234062830671175</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>659.5</v>
+        <v>673.8</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.1674121825732627</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.8224412433661867</v>
+        <v>0.7837637281092316</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>2.924744750027849</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8474</v>
+        <v>8498</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.001777695263379242</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2522347750767053</v>
+        <v>0.2486982212285245</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.681891037061412</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6612</v>
+        <v>6601</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.03358385015785047</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.482985480943739</v>
+        <v>1.487123163157098</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2301369863013699</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>20000</v>
+        <v>19980</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.1061311520476367</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.04360000000000008</v>
+        <v>0.04464464464464468</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.463731438500159</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>20000</v>
+        <v>19980</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.0501582324094231</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.3415999999999999</v>
+        <v>0.3429429429429429</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.89160899953235</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1743</v>
+        <v>1729</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04056679664352857</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.690923339070568</v>
+        <v>3.728906524002314</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8136986301369864</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>174.7</v>
+        <v>182</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1460931634870607</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>3.696811677160847</v>
+        <v>3.508423076923076</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.593749461675701</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>10560</v>
+        <v>10540</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.001208222745799985</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.6515151515151516</v>
+        <v>0.6546489563567361</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.048937149368941</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>104.4</v>
+        <v>104</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1057</v>
+        <v>1045</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03765289113661231</v>
+        <v>0.03917687345296694</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5466390842005677</v>
+        <v>0.5584056650717701</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.578923454185004</v>
+        <v>2.578587718633865</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.485343100967158</v>
+        <v>2.481375196568567</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.701369863013698</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003877586976756631</v>
+        <v>0.003878091843739176</v>
       </c>
     </row>
     <row r="12">
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>202.1</v>
+        <v>197.7</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1091753145785747</v>
+        <v>-0.1045124112115089</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.01916288451840642</v>
+        <v>-0.003025718608169581</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.158874099314747</v>
+        <v>4.154559696030474</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.668566292981986</v>
+        <v>4.639438612042849</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.452054794520548</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002404496929024057</v>
+        <v>0.002406993937180545</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>225.5</v>
+        <v>223.3</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1953390511384759</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.1157220620842572</v>
+        <v>0.1267143976712941</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.099203418277102</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>162.2</v>
+        <v>159.2</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1677886470425115</v>
+        <v>-0.1597019882856402</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1189746835443037</v>
+        <v>0.09827848101265824</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.929189259138994</v>
+        <v>1.928713684463491</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.318148211128216</v>
+        <v>2.295273412022679</v>
       </c>
       <c r="BC15" s="8" t="n">
         <v>1.967123287671233</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005183524608914236</v>
+        <v>0.005184802742135203</v>
       </c>
     </row>
     <row r="16">
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16770</v>
+        <v>17000</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2538,7 +2538,7 @@
         <v>-0.02531363004292031</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2194636612999405</v>
+        <v>0.2029650352941177</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.702806583616394</v>
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>155.1</v>
+        <v>154.6</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.01122528971023235</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.516441005802708</v>
+        <v>0.5213454075032342</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.146620608812316</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>26920</v>
+        <v>26950</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5894806891546405</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.065339446359584</v>
+        <v>0.06415353974025972</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.380723004629139</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>445.6</v>
+        <v>439.5</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03844585255665141</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.505121068222621</v>
+        <v>0.526011258248009</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7287671232876712</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>223</v>
+        <v>221.7</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3262,7 +3262,7 @@
         <v>0.05898666310529611</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.05201793721973091</v>
+        <v>0.05818673883626535</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.916031092548013</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9796</v>
+        <v>9788</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.03001982212296182</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.6185949673336057</v>
+        <v>0.6199178892521455</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.267298281844049</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>68.59999999999999</v>
+        <v>65.8</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>33.4</v>
+        <v>35.2</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1944144031692417</v>
+        <v>0.2110456352147238</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.327753821556886</v>
+        <v>0.2084345715909088</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.840479646229135</v>
+        <v>2.829353398365493</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.378135794990623</v>
+        <v>2.336289662498008</v>
       </c>
       <c r="BC24" s="8" t="n">
         <v>3.205479452054794</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003520532179582927</v>
+        <v>0.003534376442962892</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>46.5</v>
+        <v>46.1</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>34.3</v>
+        <v>30.9</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.3515732775576871</v>
+        <v>0.3554806539836442</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.3556851311953353</v>
+        <v>0.4919093851132688</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.764347589456071</v>
+        <v>2.761621591199398</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.045281329068068</v>
+        <v>2.037374405221663</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.205479452054794</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003617490086320026</v>
+        <v>0.003621060912859139</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1127</v>
+        <v>1138</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.0489570250224249</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.6428394676131322</v>
+        <v>0.6269596485061513</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2246575342465753</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>10660</v>
+        <v>11010</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-3.458712092693471</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.2546570521575986</v>
+        <v>0.2147724047229793</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>135.4</v>
+        <v>118.7</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>13060</v>
+        <v>12840</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.0643550391755475</v>
+        <v>-0.01641301951012546</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1933032159264931</v>
+        <v>0.06404750778816193</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.610995042179248</v>
+        <v>2.601606223098305</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>2.790583128752753</v>
+        <v>2.645018971075215</v>
       </c>
       <c r="BC29" s="8" t="n">
         <v>2.701369863013698</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003829957483049671</v>
+        <v>0.003843779243459373</v>
       </c>
     </row>
     <row r="30">
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>60340</v>
+        <v>60510</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2601053757304991</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.2228704010606564</v>
+        <v>0.2194348041646008</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.572329934928092</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>120.8</v>
+        <v>119.1</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4524,7 +4524,7 @@
         <v>-0.1027159484915333</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.1264983443708612</v>
+        <v>0.1425776658270363</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.608699374463915</v>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102.3</v>
+        <v>101.5</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -4616,7 +4616,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1400</v>
+        <v>1436</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03037136463833637</v>
+        <v>0.03534908511692694</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.3152857142857142</v>
+        <v>0.2722841225626742</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.604090345512827</v>
+        <v>1.603893860795588</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.556807963190891</v>
+        <v>1.549133411958782</v>
       </c>
       <c r="BC34" s="8" t="n">
         <v>1.621917808219178</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.006234062830671175</v>
+        <v>0.006234826533371507</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>673.8</v>
+        <v>660</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.1674121825732627</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7837637281092316</v>
+        <v>0.8210606060606063</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>2.924744750027849</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8498</v>
+        <v>8650</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.001777695263379242</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2486982212285245</v>
+        <v>0.2267557784971099</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.681891037061412</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>110.9</v>
+        <v>110.6</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>80.3</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02147750270929551</v>
+        <v>0.02210949647691195</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.5467995018679952</v>
+        <v>0.5180392156862745</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.330581353460824</v>
+        <v>4.329938626302781</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.239526902917286</v>
+        <v>4.236276681928459</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.701369863013698</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002309158790426234</v>
+        <v>0.002309501557193833</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6601</v>
+        <v>6555</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.03358385015785047</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.487123163157098</v>
+        <v>1.504576659038902</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2301369863013699</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>19980</v>
+        <v>20300</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.1061311520476367</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.04464464464464468</v>
+        <v>0.02817733990147775</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.463731438500159</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>19980</v>
+        <v>20300</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.0501582324094231</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.3429429429429429</v>
+        <v>0.3217733990147784</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.89160899953235</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1729</v>
+        <v>1758</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04056679664352857</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.728906524002314</v>
+        <v>3.650898395904437</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8136986301369864</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>182</v>
+        <v>179.6</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1460931634870607</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>3.508423076923076</v>
+        <v>3.568669265033408</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.593749461675701</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>10540</v>
+        <v>10430</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.001208222745799985</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.6546489563567361</v>
+        <v>0.6720997123681687</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.048937149368941</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>104</v>
+        <v>103.5</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1045</v>
+        <v>1033</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03917687345296694</v>
+        <v>0.04109344902977755</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5584056650717701</v>
+        <v>0.568929748305905</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.578587718633865</v>
+        <v>2.578165131628138</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.481375196568567</v>
+        <v>2.476401262567542</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.701369863013698</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003878091843739176</v>
+        <v>0.003878727501711613</v>
       </c>
     </row>
     <row r="12">
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>197.7</v>
+        <v>204</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>198.3</v>
+        <v>202.6</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1045124112115089</v>
+        <v>-0.1111491589775429</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.003025718608169581</v>
+        <v>0.006910167818361401</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.154559696030474</v>
+        <v>4.160689209847411</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.639438612042849</v>
+        <v>4.680975724859882</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.452054794520548</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002406993937180545</v>
+        <v>0.002403447961537781</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>223.3</v>
+        <v>228.2</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1953390511384759</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.1267143976712941</v>
+        <v>0.1025211437335671</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.099203418277102</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>159.2</v>
+        <v>161.9</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1597019882856402</v>
+        <v>-0.1669903123127899</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.09827848101265824</v>
+        <v>0.1169050632911395</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.928713684463491</v>
+        <v>1.92914228801483</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.295273412022679</v>
+        <v>2.315870171175261</v>
       </c>
       <c r="BC15" s="8" t="n">
         <v>1.967123287671233</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005184802742135203</v>
+        <v>0.005183650818359503</v>
       </c>
     </row>
     <row r="16">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>109</v>
+        <v>109.8</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17000</v>
+        <v>17260</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.02531363004292031</v>
+        <v>-0.02946436395647331</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2029650352941177</v>
+        <v>0.1935399953650057</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.702806583616394</v>
+        <v>1.702903183539017</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.747030261325371</v>
+        <v>1.754601397719975</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.701369863013699</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005872657585550413</v>
+        <v>0.005872324449601266</v>
       </c>
     </row>
     <row r="17">
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>357.2</v>
+        <v>343.8</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>26950</v>
+        <v>27470</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5894806891546405</v>
+        <v>-0.5780087278237902</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.06415353974025972</v>
+        <v>0.004844422424463035</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.380723004629139</v>
+        <v>1.380417505333056</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.363357016715958</v>
+        <v>3.271199184320188</v>
       </c>
       <c r="BC20" s="8" t="n">
         <v>1.364383561643836</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.007242582303961821</v>
+        <v>0.007244185155118908</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>439.5</v>
+        <v>442.5</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03844585255665141</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.526011258248009</v>
+        <v>0.5156654192090393</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7287671232876712</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>221.7</v>
+        <v>217.5</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3262,7 +3262,7 @@
         <v>0.05898666310529611</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.05818673883626535</v>
+        <v>0.07862068965517244</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.916031092548013</v>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>90</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9788</v>
+        <v>10020</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.03001982212296182</v>
+        <v>0.03028719216534387</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.6199178892521455</v>
+        <v>0.5806525741516968</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.267298281844049</v>
+        <v>4.267257133433564</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.142928310883154</v>
+        <v>4.141813239923049</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.293150684931507</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002343403094774675</v>
+        <v>0.002343425691798821</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>65.8</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.2110456352147238</v>
+        <v>0.198484146083595</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.2084345715909088</v>
+        <v>0.2470016323863635</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.829353398365493</v>
+        <v>2.837769648205393</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.336289662498008</v>
+        <v>2.367799071417551</v>
       </c>
       <c r="BC24" s="8" t="n">
         <v>3.205479452054794</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003534376442962892</v>
+        <v>0.003523894198503394</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>46.1</v>
+        <v>45.2</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>30.9</v>
+        <v>31.3</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.3554806539836442</v>
+        <v>0.3644448106098595</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.4919093851132688</v>
+        <v>0.4440894568690097</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.761621591199398</v>
+        <v>2.755344490208284</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.037374405221663</v>
+        <v>2.019388742426849</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.205479452054794</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003621060912859139</v>
+        <v>0.003629310249784437</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1138</v>
+        <v>1110</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.0489570250224249</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.6269596485061513</v>
+        <v>0.668000072072072</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2246575342465753</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>11010</v>
+        <v>10990</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-3.458712092693471</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.2147724047229793</v>
+        <v>0.2169830915377617</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>12840</v>
+        <v>13180</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.01641301951012546</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.06404750778816193</v>
+        <v>0.03659863429438537</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.601606223098305</v>
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>551.1</v>
+        <v>547</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4192,7 +4192,7 @@
         <v>0.0605898480496373</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.7448729050988929</v>
+        <v>0.7579514771480802</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.573843577783582</v>
@@ -4286,7 +4286,7 @@
         <v>0.9284102</v>
       </c>
       <c r="AJ31" t="n">
-        <v>176.5</v>
+        <v>151.9</v>
       </c>
       <c r="AK31" s="10" t="n">
         <v>47133</v>
@@ -4306,7 +4306,7 @@
         <v>0.08298609042149702</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>-0.4950290130311615</v>
+        <v>-0.4132496431863069</v>
       </c>
       <c r="BA31" s="8" t="n">
         <v>2.118384531559156</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>60510</v>
+        <v>60020</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2601053757304991</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.2194348041646008</v>
+        <v>0.2293902032655781</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.572329934928092</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>119.1</v>
+        <v>117.6</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4524,7 +4524,7 @@
         <v>-0.1027159484915333</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.1425776658270363</v>
+        <v>0.1571513605442179</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.608699374463915</v>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>101.5</v>
+        <v>102.3</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03534908511692694</v>
+        <v>0.03037136463833637</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2722841225626742</v>
+        <v>0.2823119777158773</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.603893860795588</v>
+        <v>1.604090345512827</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.549133411958782</v>
+        <v>1.556807963190891</v>
       </c>
       <c r="BC34" s="8" t="n">
         <v>1.621917808219178</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.006234826533371507</v>
+        <v>0.006234062830671175</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>660</v>
+        <v>652.9</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.1674121825732627</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.8210606060606063</v>
+        <v>0.8408638382600706</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>2.924744750027849</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8650</v>
+        <v>8457</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.001777695263379242</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2267557784971099</v>
+        <v>0.2547519787158568</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.681891037061412</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>110.6</v>
+        <v>110.5</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>81.59999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02210949647691195</v>
+        <v>0.02232064576924134</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.5180392156862745</v>
+        <v>0.512958435207824</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.329938626302781</v>
+        <v>4.329723748725152</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.236276681928459</v>
+        <v>4.235191538626579</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.701369863013698</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002309501557193833</v>
+        <v>0.002309616174229224</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6555</v>
+        <v>6620</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.03358385015785047</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.504576659038902</v>
+        <v>1.479984894259819</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2301369863013699</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>260.9</v>
+        <v>264.2</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>20300</v>
+        <v>20600</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1061311520476367</v>
+        <v>-0.1078645711218598</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02817733990147775</v>
+        <v>0.02601941747572822</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.463731438500159</v>
+        <v>6.466791029872023</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.23118548465695</v>
+        <v>7.248665192014634</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.876712328767123</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.00154709398048883</v>
+        <v>0.001546362013834534</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>20300</v>
+        <v>20600</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.0501582324094231</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.3217733990147784</v>
+        <v>0.3025242718446601</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.89160899953235</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1758</v>
+        <v>1766</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04056679664352857</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.650898395904437</v>
+        <v>3.629829773499433</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8136986301369864</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>179.6</v>
+        <v>179.3</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1460931634870607</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>3.568669265033408</v>
+        <v>3.576313441160066</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.593749461675701</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>109</v>
+        <v>107.6</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>10430</v>
+        <v>10540</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.001208222745799985</v>
+        <v>0.001941546820251594</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.6720997123681687</v>
+        <v>0.6333965844402276</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.048937149368941</v>
+        <v>4.047322038229348</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.053835085126512</v>
+        <v>4.039479200232664</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.210958904109589</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002469783953440369</v>
+        <v>0.002470769537374119</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103.5</v>
+        <v>104.4</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1033</v>
+        <v>1053</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.04109344902977755</v>
+        <v>0.03765289113661231</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.568929748305905</v>
+        <v>0.5525142564102565</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.578165131628138</v>
+        <v>2.578923454185004</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.476401262567542</v>
+        <v>2.485343100967158</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.701369863013698</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003878727501711613</v>
+        <v>0.003877586976756631</v>
       </c>
     </row>
     <row r="12">
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>204</v>
+        <v>203.4</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>202.6</v>
+        <v>201.7</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1111491589775429</v>
+        <v>-0.1105283700404943</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.006910167818361401</v>
+        <v>0.008428358948934234</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.160689209847411</v>
+        <v>4.160119062485363</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.680975724859882</v>
+        <v>4.677067735903795</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.452054794520548</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002403447961537781</v>
+        <v>0.002403777355839845</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>228.2</v>
+        <v>226</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1953390511384759</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.1025211437335671</v>
+        <v>0.1132536504424779</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.099203418277102</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>161.9</v>
+        <v>160.2</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>79</v>
+        <v>77.3</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1669903123127899</v>
+        <v>-0.1624232790865132</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1169050632911395</v>
+        <v>0.1294825355756792</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.92914228801483</v>
+        <v>1.928873669738443</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.315870171175261</v>
+        <v>2.302921776090857</v>
       </c>
       <c r="BC15" s="8" t="n">
         <v>1.967123287671233</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005183650818359503</v>
+        <v>0.00518437270251919</v>
       </c>
     </row>
     <row r="16">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>109.8</v>
+        <v>111.2</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17260</v>
+        <v>17300</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.02946436395647331</v>
+        <v>-0.03661399342715765</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1935399953650057</v>
+        <v>0.2059633572254336</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.702903183539017</v>
+        <v>1.703069621488273</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.754601397719975</v>
+        <v>1.767795680930417</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.701369863013699</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005872324449601266</v>
+        <v>0.005871750557831708</v>
       </c>
     </row>
     <row r="17">
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>74.3</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2668,7 +2668,7 @@
         <v>0.06654577556947415</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9880888290713326</v>
+        <v>0.9988497970230039</v>
       </c>
       <c r="BA17" s="8" t="n">
         <v>2.944223244466702</v>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>89</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1242873737368327</v>
+        <v>0.1235453861017199</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>2.56</v>
+        <v>2.564</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.675210511963826</v>
+        <v>1.675242346017649</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.490019857108127</v>
+        <v>1.491032197488799</v>
       </c>
       <c r="BC18" s="8" t="n">
         <v>1.701369863013699</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005969399026918197</v>
+        <v>0.00596928559248266</v>
       </c>
     </row>
     <row r="19">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>154.6</v>
+        <v>154.4</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.01122528971023235</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5213454075032342</v>
+        <v>0.5233160621761659</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.146620608812316</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27470</v>
+        <v>27420</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5780087278237902</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.004844422424463035</v>
+        <v>0.006676742669584179</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.380417505333056</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>442.5</v>
+        <v>443.9</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03844585255665141</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5156654192090393</v>
+        <v>0.5108852173913043</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7287671232876712</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102</v>
+        <v>101.7</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>217.5</v>
+        <v>214.6</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.05898666310529611</v>
+        <v>0.06061378614117361</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.07862068965517244</v>
+        <v>0.08998136067101581</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.916031092548013</v>
+        <v>1.915938001280978</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.809306159654156</v>
+        <v>1.806442671513564</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>1.967123287671233</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005219121985490125</v>
+        <v>0.005219375571294111</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10020</v>
+        <v>9968</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.03028719216534387</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5806525741516968</v>
+        <v>0.5888983540329056</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.267257133433564</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>67.90000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>35.2</v>
+        <v>33.9</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.198484146083595</v>
+        <v>0.2061965159162643</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.2470016323863635</v>
+        <v>0.2700313522123892</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.837769648205393</v>
+        <v>2.832611536814342</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.367799071417551</v>
+        <v>2.34838311953057</v>
       </c>
       <c r="BC24" s="8" t="n">
         <v>3.205479452054794</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003523894198503394</v>
+        <v>0.003530311117509026</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>45.2</v>
+        <v>45.3</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>31.3</v>
+        <v>29.7</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.3644448106098595</v>
+        <v>0.3634367456021155</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.4440894568690097</v>
+        <v>0.5252525252525253</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.755344490208284</v>
+        <v>2.756051985763499</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.019388742426849</v>
+        <v>2.021400695450952</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.205479452054794</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003629310249784437</v>
+        <v>0.003628378583443061</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>99.5</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3808,16 +3808,16 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.0489570250224249</v>
+        <v>0.05338929074848333</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.668000072072072</v>
+        <v>0.670839472448058</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2246575342465753</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.2141722958018919</v>
+        <v>0.2132711393780597</v>
       </c>
       <c r="BC27" s="8" t="n">
         <v>0.2027397260273973</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>10990</v>
+        <v>10760</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-3.458712092693471</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.2169830915377617</v>
+        <v>0.2429966706319704</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>13180</v>
+        <v>13290</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.01641301951012546</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.03659863429438537</v>
+        <v>0.02801881113619253</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.601606223098305</v>
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4192,7 +4192,7 @@
         <v>0.0605898480496373</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.7579514771480802</v>
+        <v>0.7611711684981683</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.573843577783582</v>
@@ -4286,7 +4286,7 @@
         <v>0.9284102</v>
       </c>
       <c r="AJ31" t="n">
-        <v>151.9</v>
+        <v>155.5</v>
       </c>
       <c r="AK31" s="10" t="n">
         <v>47133</v>
@@ -4306,7 +4306,7 @@
         <v>0.08298609042149702</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>-0.4132496431863069</v>
+        <v>-0.4268335742765273</v>
       </c>
       <c r="BA31" s="8" t="n">
         <v>2.118384531559156</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>60020</v>
+        <v>61070</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2601053757304991</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.2293902032655781</v>
+        <v>0.2082528246274766</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.572329934928092</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>117.6</v>
+        <v>120</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4524,7 +4524,7 @@
         <v>-0.1027159484915333</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.1571513605442179</v>
+        <v>0.1340083333333335</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.608699374463915</v>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102.3</v>
+        <v>101.5</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -4616,7 +4616,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1436</v>
+        <v>1421</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03037136463833637</v>
+        <v>0.03534908511692694</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2823119777158773</v>
+        <v>0.2857142857142858</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.604090345512827</v>
+        <v>1.603893860795588</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.556807963190891</v>
+        <v>1.549133411958782</v>
       </c>
       <c r="BC34" s="8" t="n">
         <v>1.621917808219178</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.006234062830671175</v>
+        <v>0.006234826533371507</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1674121825732627</v>
+        <v>0.1675180286484271</v>
       </c>
       <c r="AZ2" s="12" t="n">
         <v>0.8408638382600706</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.924744750027849</v>
+        <v>2.921946578838321</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.505323135810519</v>
+        <v>2.50269932210032</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.205479452054794</v>
+        <v>3.202739726027397</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003419101786542153</v>
+        <v>0.003422376053150056</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.001777695263379242</v>
+        <v>-0.001852378659848942</v>
       </c>
       <c r="AZ3" s="12" t="n">
         <v>0.2547519787158568</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.681891037061412</v>
+        <v>1.679154467424184</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.684886251369805</v>
+        <v>1.68227066971285</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.701369863013699</v>
+        <v>1.698630136986301</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005945688382686151</v>
+        <v>0.005955378253758846</v>
       </c>
     </row>
     <row r="4">
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>81.8</v>
+        <v>82.5</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02232064576924134</v>
+        <v>0.02230829397421952</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.512958435207824</v>
+        <v>0.5001212121212122</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.329723748725152</v>
+        <v>4.326996594551714</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.235191538626579</v>
+        <v>4.232575065717731</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.701369863013698</v>
+        <v>4.698630136986301</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002309616174229224</v>
+        <v>0.002311071844288341</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6620</v>
+        <v>6670</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.03358385015785047</v>
+        <v>0.03384339876974388</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.479984894259819</v>
+        <v>1.461394302848576</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.2301369863013699</v>
+        <v>0.2273972602739726</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.2226592320170473</v>
+        <v>0.2199532932594738</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.2027397260273973</v>
+        <v>0.2</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.04345238095238095</v>
+        <v>0.04397590361445782</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>264.2</v>
+        <v>264.5</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>20600</v>
+        <v>20690</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1078645711218598</v>
+        <v>-0.1080697967764073</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02601941747572822</v>
+        <v>0.02271628806186565</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.466791029872023</v>
+        <v>6.464412412970759</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.248665192014634</v>
+        <v>7.247666229495576</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>6.876712328767123</v>
+        <v>6.873972602739726</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001546362013834534</v>
+        <v>0.001546931006433799</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>20600</v>
+        <v>20690</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.0501582324094231</v>
+        <v>-0.05023836142518368</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.3025242718446601</v>
+        <v>0.2968583856935718</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.89160899953235</v>
+        <v>1.888869861652488</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>1.991499072872646</v>
+        <v>1.988783064018957</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>1.873972602739726</v>
+        <v>1.871232876712329</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005286504770527227</v>
+        <v>0.005294170976528496</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1766</v>
+        <v>1763</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04056679664352857</v>
+        <v>0.04069485643566913</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.629829773499433</v>
+        <v>3.637708099829836</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.8136986301369864</v>
+        <v>0.810958904109589</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.7819763543884618</v>
+        <v>0.7792475374453999</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.7863013698630137</v>
+        <v>0.7835616438356164</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01228956228956229</v>
+        <v>0.01233108108108108</v>
       </c>
     </row>
     <row r="9">
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1460931634870607</v>
+        <v>0.146260319994183</v>
       </c>
       <c r="AZ9" s="12" t="n">
         <v>3.576313441160066</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.593749461675701</v>
+        <v>1.591003157213226</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.390593288966682</v>
+        <v>1.387994619949245</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.621917808219178</v>
+        <v>1.619178082191781</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006274511923276696</v>
+        <v>0.006285342649800791</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>10540</v>
+        <v>10790</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>0.001941546820251594</v>
+        <v>0.001930426435869851</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.6333965844402276</v>
+        <v>0.5955514365152919</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.047322038229348</v>
+        <v>4.044588032233638</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.039479200232664</v>
+        <v>4.036795295878279</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.210958904109589</v>
+        <v>4.208219178082191</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002470769537374119</v>
+        <v>0.002472439694798153</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1053</v>
+        <v>1066</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03765289113661231</v>
+        <v>0.0376363662080922</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5525142564102565</v>
+        <v>0.5335811557223265</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.578923454185004</v>
+        <v>2.576187367222356</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.485343100967158</v>
+        <v>2.482745835746581</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.701369863013698</v>
+        <v>2.698630136986301</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003877586976756631</v>
+        <v>0.003881705239002859</v>
       </c>
     </row>
     <row r="12">
@@ -2111,7 +2111,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>-0.1232876712328767</v>
+        <v>-0.126027397260274</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>203.4</v>
+        <v>200.9</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>201.7</v>
+        <v>202.1</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1105283700404943</v>
+        <v>-0.1079995388177655</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.008428358948934234</v>
+        <v>-0.005937654626422484</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.160119062485363</v>
+        <v>4.155049983211889</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.677067735903795</v>
+        <v>4.658125375523788</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.452054794520548</v>
+        <v>4.449315068493151</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002403777355839845</v>
+        <v>0.002406709916945431</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>226</v>
+        <v>224.9</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2317,22 +2317,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1953390511384759</v>
+        <v>-0.1955063779962575</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.1132536504424779</v>
+        <v>0.1186986438417075</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.099203418277102</v>
+        <v>3.096520211896656</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.851564342300958</v>
+        <v>3.849030156614779</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.205479452054794</v>
+        <v>3.202739726027397</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003226635573846639</v>
+        <v>0.003229431528197544</v>
       </c>
     </row>
     <row r="15">
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1624232790865132</v>
+        <v>-0.1626864077952896</v>
       </c>
       <c r="AZ15" s="12" t="n">
         <v>0.1294825355756792</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.928873669738443</v>
+        <v>1.926149415968194</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.302921776090857</v>
+        <v>2.300391912779651</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>1.967123287671233</v>
+        <v>1.964383561643836</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.00518437270251919</v>
+        <v>0.005191705231742587</v>
       </c>
     </row>
     <row r="16">
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17300</v>
+        <v>17500</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.03661399342715765</v>
+        <v>-0.03670657526600996</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2059633572254336</v>
+        <v>0.1921809188571431</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.703069621488273</v>
+        <v>1.700332051067797</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.767795680930417</v>
+        <v>1.765123696901946</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.701369863013699</v>
+        <v>1.698630136986301</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005871750557831708</v>
+        <v>0.005881204199920873</v>
       </c>
     </row>
     <row r="17">
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.06654577556947415</v>
+        <v>0.0665596828253497</v>
       </c>
       <c r="AZ17" s="12" t="n">
         <v>0.9988497970230039</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.944223244466702</v>
+        <v>2.941475753850131</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.760522156580346</v>
+        <v>2.757910130315512</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.205479452054794</v>
+        <v>3.202739726027397</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003396481574144809</v>
+        <v>0.003399654063750445</v>
       </c>
     </row>
     <row r="18">
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1235453861017199</v>
+        <v>0.1236580777847952</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>2.564</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.675242346017649</v>
+        <v>1.672497784956651</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.491032197488799</v>
+        <v>1.488440138528485</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.701369863013699</v>
+        <v>1.698630136986301</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.00596928559248266</v>
+        <v>0.005979081162286373</v>
       </c>
     </row>
     <row r="19">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>154.4</v>
+        <v>154</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.01122528971023235</v>
+        <v>0.01119869536815086</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5233160621761659</v>
+        <v>0.5272727272727273</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.146620608812316</v>
+        <v>3.143894385962247</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.11169097611669</v>
+        <v>3.109076782202175</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.367123287671233</v>
+        <v>3.364383561643836</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003178012618360901</v>
+        <v>0.003180768426780123</v>
       </c>
     </row>
     <row r="20">
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27420</v>
+        <v>27660</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5780087278237902</v>
+        <v>-0.5787389239718821</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.006676742669584179</v>
+        <v>-0.002057979609544458</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.380417505333056</v>
+        <v>1.377697218865878</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.271199184320188</v>
+        <v>3.270411859209895</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.364383561643836</v>
+        <v>1.361643835616438</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.007244185155118908</v>
+        <v>0.00725848892126821</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>443.9</v>
+        <v>448.9</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3124,22 +3124,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03844585255665141</v>
+        <v>0.038452365504426</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5108852173913043</v>
+        <v>0.4940564669191356</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.7287671232876712</v>
+        <v>0.7260273972602741</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.7017863487956048</v>
+        <v>0.6991436693464586</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.7013698630136986</v>
+        <v>0.6986301369863014</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.0137218045112782</v>
+        <v>0.01377358490566037</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>214.6</v>
+        <v>224.8</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.06061378614117361</v>
+        <v>0.06059877293448147</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.08998136067101581</v>
+        <v>0.04052491103202849</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.915938001280978</v>
+        <v>1.913199134107255</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.806442671513564</v>
+        <v>1.803885864221572</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>1.967123287671233</v>
+        <v>1.964383561643836</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005219375571294111</v>
+        <v>0.005226847441924146</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9968</v>
+        <v>9977</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.03028719216534387</v>
+        <v>0.03030327448831704</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5888983540329056</v>
+        <v>0.5874650489124988</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.267257133433564</v>
+        <v>4.264514931559813</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.141813239923049</v>
+        <v>4.139087040830492</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.293150684931507</v>
+        <v>4.29041095890411</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002343425691798821</v>
+        <v>0.002344932579786359</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.2061965159162643</v>
+        <v>0.2063247861417476</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.2700313522123892</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.832611536814342</v>
+        <v>2.829785774237246</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.34838311953057</v>
+        <v>2.345790956752119</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.205479452054794</v>
+        <v>3.202739726027397</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003530311117509026</v>
+        <v>0.003533836409470059</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>45.3</v>
+        <v>49</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.3634367456021155</v>
+        <v>0.328402582644894</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.5252525252525253</v>
+        <v>0.6498316498316499</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.756051985763499</v>
+        <v>2.777644330869872</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.021400695450952</v>
+        <v>2.090965771339806</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.205479452054794</v>
+        <v>3.202739726027397</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003628378583443061</v>
+        <v>0.003600172955501582</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3699,22 +3699,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>87.66349388692869</v>
+        <v>88.66622632896684</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.1761052631578948</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.2301369863013698</v>
+        <v>0.2273972602739727</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.002595622800460134</v>
+        <v>0.002536041379055021</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.2027397260273973</v>
+        <v>0.2</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.04345238095238096</v>
+        <v>0.04397590361445782</v>
       </c>
     </row>
     <row r="27">
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1107</v>
+        <v>1210</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3808,22 +3808,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05338929074848333</v>
+        <v>0.0537100494266862</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.670839472448058</v>
+        <v>0.5286109884297521</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.2246575342465753</v>
+        <v>0.2219178082191781</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.2132711393780597</v>
+        <v>0.2106061419267297</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.2027397260273973</v>
+        <v>0.2</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.04451219512195122</v>
+        <v>0.04506172839506173</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>10760</v>
+        <v>10780</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3938,15 +3938,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-3.458712092693471</v>
+        <v>-3.500407203414941</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.2429966706319704</v>
+        <v>0.240690554359926</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.2027397260273973</v>
+        <v>0.2</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>118.7</v>
+        <v>121</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>13290</v>
+        <v>13280</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.01641301951012546</v>
+        <v>-0.02362596990146945</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.02801881113619253</v>
+        <v>0.04872740963855415</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.601606223098305</v>
+        <v>2.600295747773492</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>2.645018971075215</v>
+        <v>2.663216828402414</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.701369863013698</v>
+        <v>2.698630136986301</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003843779243459373</v>
+        <v>0.003845716399206713</v>
       </c>
     </row>
     <row r="30">
@@ -4189,22 +4189,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.0605898480496373</v>
+        <v>0.06059423278485436</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.7611711684981683</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.573843577783582</v>
+        <v>2.571102875207592</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.426803898337071</v>
+        <v>2.424209745565484</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.701369863013698</v>
+        <v>2.698630136986301</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003885239991395016</v>
+        <v>0.003889381516557403</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.08298609042149702</v>
+        <v>0.08300935083032031</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>-0.4268335742765273</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.118384531559156</v>
+        <v>2.11563898344018</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.956058854582964</v>
+        <v>1.953481732930712</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.273972602739726</v>
+        <v>2.271232876712329</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004720578276050704</v>
+        <v>0.004726704356590786</v>
       </c>
     </row>
     <row r="32">
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>61070</v>
+        <v>61260</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4412,22 +4412,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2601053757304991</v>
+        <v>-0.2605241385913359</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.2082528246274766</v>
+        <v>0.2045053868756121</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.572329934928092</v>
+        <v>1.569605436411785</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.125072791926899</v>
+        <v>2.122591849613274</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.575342465753425</v>
+        <v>1.572602739726027</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.006359988306434764</v>
+        <v>0.006371027882561759</v>
       </c>
     </row>
     <row r="33">
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.1027159484915333</v>
+        <v>-0.1028517832577547</v>
       </c>
       <c r="AZ33" s="12" t="n">
         <v>0.1340083333333335</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.608699374463915</v>
+        <v>2.605987313457048</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.907328365057093</v>
+        <v>2.904745575842525</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.701369863013698</v>
+        <v>2.698630136986301</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003833327863642774</v>
+        <v>0.003837317222674508</v>
       </c>
     </row>
     <row r="34">
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03534908511692694</v>
+        <v>0.03533330091412761</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.2857142857142858</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.603893860795588</v>
+        <v>1.601154757687908</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.549133411958782</v>
+        <v>1.546511404853103</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.621917808219178</v>
+        <v>1.619178082191781</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.006234826533371507</v>
+        <v>0.006245492480964271</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>652.9</v>
+        <v>675</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.1675180286484271</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.8408638382600706</v>
+        <v>0.7805925925925927</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>2.921946578838321</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8457</v>
+        <v>8594</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.001852378659848942</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2547519787158568</v>
+        <v>0.2347495326972306</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.679154467424184</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>82.5</v>
+        <v>81.7</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.02230829397421952</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.5001212121212122</v>
+        <v>0.5148102815177478</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.326996594551714</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6670</v>
+        <v>6657</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.03384339876974388</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.461394302848576</v>
+        <v>1.466200991437585</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2273972602739726</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>264.5</v>
+        <v>270.5</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>20690</v>
+        <v>20810</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1080697967764073</v>
+        <v>-0.1111532575271851</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02271628806186565</v>
+        <v>0.03988467083133118</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.464412412970759</v>
+        <v>6.469809339044477</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.247666229495576</v>
+        <v>7.278880632498187</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.873972602739726</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001546931006433799</v>
+        <v>0.00154564060174869</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>20690</v>
+        <v>20810</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.05023836142518368</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2968583856935718</v>
+        <v>0.2893801057184047</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.888869861652488</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1763</v>
+        <v>1784</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04069485643566913</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.637708099829836</v>
+        <v>3.583116244394619</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.810958904109589</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>179.3</v>
+        <v>175</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.146260319994183</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>3.576313441160066</v>
+        <v>3.688759999999999</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.591003157213226</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>107.6</v>
+        <v>109</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>10790</v>
+        <v>10860</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>0.001930426435869851</v>
+        <v>-0.001221276155293012</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.5955514365152919</v>
+        <v>0.6058931860036831</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.044588032233638</v>
+        <v>4.046204095695407</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.036795295878279</v>
+        <v>4.051151670632225</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.208219178082191</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002472439694798153</v>
+        <v>0.002471452196550984</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>200.9</v>
+        <v>203.3</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1079995388177655</v>
+        <v>-0.1105089109783906</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.005937654626422484</v>
+        <v>0.005937654626422706</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.155049983211889</v>
+        <v>4.157361454134043</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.658125375523788</v>
+        <v>4.673865208370899</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.449315068493151</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002406709916945431</v>
+        <v>0.002405371798994309</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>224.9</v>
+        <v>231.8</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1955063779962575</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.1186986438417075</v>
+        <v>0.08539829594477988</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.096520211896656</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>160.2</v>
+        <v>161.9</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>77.3</v>
+        <v>79.8</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1626864077952896</v>
+        <v>-0.1672579027482989</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1294825355756792</v>
+        <v>0.1057080200501255</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.926149415968194</v>
+        <v>1.926418305521109</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.300391912779651</v>
+        <v>2.313343245020118</v>
       </c>
       <c r="BC15" s="8" t="n">
         <v>1.964383561643836</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005191705231742587</v>
+        <v>0.005190980573295027</v>
       </c>
     </row>
     <row r="16">
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17500</v>
+        <v>17320</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2538,7 +2538,7 @@
         <v>-0.03670657526600996</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1921809188571431</v>
+        <v>0.2045707898383373</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.700332051067797</v>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>95.3</v>
+        <v>94</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>73.90000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.0665596828253497</v>
+        <v>0.07135755752227305</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9988497970230039</v>
+        <v>0.9557046979865773</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.941475753850131</v>
+        <v>2.938790672868647</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.757910130315512</v>
+        <v>2.743053103265713</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.202739726027397</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003399654063750445</v>
+        <v>0.003402760221175836</v>
       </c>
     </row>
     <row r="18">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>89.09999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2781,7 +2781,7 @@
         <v>4.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>105</v>
+        <v>100.6</v>
       </c>
       <c r="AK18" s="10" t="n">
         <v>46924</v>
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1236580777847952</v>
+        <v>0.1229162355905209</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>2.564</v>
+        <v>2.724055666003977</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.672497784956651</v>
+        <v>1.672529614581014</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.488440138528485</v>
+        <v>1.48945180554938</v>
       </c>
       <c r="BC18" s="8" t="n">
         <v>1.698630136986301</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005979081162286373</v>
+        <v>0.005978967375417805</v>
       </c>
     </row>
     <row r="19">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.01119869536815086</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5272727272727273</v>
+        <v>0.488607594936709</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.143894385962247</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27660</v>
+        <v>27570</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5787389239718821</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.002057979609544458</v>
+        <v>0.001199720130576676</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.377697218865878</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>99.8</v>
+        <v>100.5</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>448.9</v>
+        <v>458.3</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3124,22 +3124,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.038452365504426</v>
+        <v>0.02868683472961315</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.4940564669191356</v>
+        <v>0.4736769146847042</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.7260273972602741</v>
+        <v>0.726027397260274</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.6991436693464586</v>
+        <v>0.705780780650418</v>
       </c>
       <c r="BC21" s="8" t="n">
         <v>0.6986301369863014</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01377358490566037</v>
+        <v>0.01377358490566038</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>224.8</v>
+        <v>212.7</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3262,7 +3262,7 @@
         <v>0.06059877293448147</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.04052491103202849</v>
+        <v>0.09971791255289153</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.913199134107255</v>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>89.90000000000001</v>
+        <v>90</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9977</v>
+        <v>10080</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.03030327448831704</v>
+        <v>0.03003573242595473</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5874650489124988</v>
+        <v>0.5729916964285715</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.264514931559813</v>
+        <v>4.264556107884658</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.139087040830492</v>
+        <v>4.140202105261645</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.29041095890411</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002344932579786359</v>
+        <v>0.002344909938342981</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>49</v>
+        <v>43.8</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.328402582644894</v>
+        <v>0.3791852176590282</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.6498316498316499</v>
+        <v>0.4747474747474747</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.777644330869872</v>
+        <v>2.742213609050467</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.090965771339806</v>
+        <v>1.988285238225644</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.202739726027397</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003600172955501582</v>
+        <v>0.003646688925689728</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1210</v>
+        <v>1108</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.0537100494266862</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5286109884297521</v>
+        <v>0.6693314945848376</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2219178082191781</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>10780</v>
+        <v>10980</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-3.500407203414941</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.240690554359926</v>
+        <v>0.2180914550091075</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>121</v>
+        <v>124.5</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>13280</v>
+        <v>13370</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.02362596990146945</v>
+        <v>-0.03415342323134281</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.04872740963855415</v>
+        <v>0.07179880329094979</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.600295747773492</v>
+        <v>2.602371249467343</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>2.663216828402414</v>
+        <v>2.694394029095029</v>
       </c>
       <c r="BC29" s="8" t="n">
         <v>2.698630136986301</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003845716399206713</v>
+        <v>0.003842649276903445</v>
       </c>
     </row>
     <row r="30">
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>546</v>
+        <v>534.9</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4192,7 +4192,7 @@
         <v>0.06059423278485436</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.7611711684981683</v>
+        <v>0.7977181865769303</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.571102875207592</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>61260</v>
+        <v>62560</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2605241385913359</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.2045053868756121</v>
+        <v>0.1794757033248082</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.569605436411785</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>120</v>
+        <v>120.4</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4524,7 +4524,7 @@
         <v>-0.1028517832577547</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.1340083333333335</v>
+        <v>0.1302408637873755</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.605987313457048</v>
@@ -4616,7 +4616,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1421</v>
+        <v>1385</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4633,7 +4633,7 @@
         <v>0.03533330091412761</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2857142857142858</v>
+        <v>0.3191335740072203</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.601154757687908</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>675</v>
+        <v>668.7</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.1675180286484271</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7805925925925927</v>
+        <v>0.7973680275160759</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>2.921946578838321</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8594</v>
+        <v>8450</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.001852378659848942</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2347495326972306</v>
+        <v>0.2557914182248522</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.679154467424184</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>110.5</v>
+        <v>109.6</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>81.7</v>
+        <v>81.3</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02230829397421952</v>
+        <v>0.02422060890885348</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.5148102815177478</v>
+        <v>0.5098646986469866</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.326996594551714</v>
+        <v>4.325047307264282</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.232575065717731</v>
+        <v>4.222769264398949</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.698630136986301</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002311071844288341</v>
+        <v>0.00231211343820544</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6657</v>
+        <v>6641</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.03384339876974388</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.466200991437585</v>
+        <v>1.472142749585906</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2273972602739726</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>270.5</v>
+        <v>269.1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>20810</v>
+        <v>20610</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1111532575271851</v>
+        <v>-0.1104411128699389</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.03988467083133118</v>
+        <v>0.04454148471615715</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.469809339044477</v>
+        <v>6.468567648258291</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.278880632498187</v>
+        <v>7.271657606757777</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.873972602739726</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.00154564060174869</v>
+        <v>0.001545937299224593</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>20810</v>
+        <v>20610</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.05023836142518368</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2893801057184047</v>
+        <v>0.3018922852983987</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.888869861652488</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1784</v>
+        <v>1762</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04069485643566913</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.583116244394619</v>
+        <v>3.640340170261067</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.810958904109589</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>175</v>
+        <v>178.8</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.146260319994183</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>3.688759999999999</v>
+        <v>3.589110738255033</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.591003157213226</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>109</v>
+        <v>106.4</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>10860</v>
+        <v>10940</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.001221276155293012</v>
+        <v>0.004673313580744728</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.6058931860036831</v>
+        <v>0.5561243144424131</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.046204095695407</v>
+        <v>4.043173332029554</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.051151670632225</v>
+        <v>4.024366206781512</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.208219178082191</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002471452196550984</v>
+        <v>0.002473304797689763</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1066</v>
+        <v>1043</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.0376363662080922</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5335811557223265</v>
+        <v>0.5673993403643338</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.576187367222356</v>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>203.3</v>
+        <v>207.3</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>202.1</v>
+        <v>207.2</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1105089109783906</v>
+        <v>-0.1146087138449885</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.005937654626422706</v>
+        <v>0.0004826254826255649</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.157361454134043</v>
+        <v>4.161114749608427</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.673865208370899</v>
+        <v>4.699746670964991</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.449315068493151</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002405371798994309</v>
+        <v>0.002403202170990605</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>231.8</v>
+        <v>228.8</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1955063779962575</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.08539829594477988</v>
+        <v>0.09962991695804191</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.096520211896656</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>161.9</v>
+        <v>160.9</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>79.8</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1672579027482989</v>
+        <v>-0.164577741936131</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1057080200501255</v>
+        <v>0.1329521963824289</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.926418305521109</v>
+        <v>1.926260643356167</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.313343245020118</v>
+        <v>2.305732968882548</v>
       </c>
       <c r="BC15" s="8" t="n">
         <v>1.964383561643836</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005190980573295027</v>
+        <v>0.005191405448941103</v>
       </c>
     </row>
     <row r="16">
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17320</v>
+        <v>17110</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2538,7 +2538,7 @@
         <v>-0.03670657526600996</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2045707898383373</v>
+        <v>0.2193551186440679</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.700332051067797</v>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>94</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>74.5</v>
+        <v>75.7</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.07135755752227305</v>
+        <v>0.07098530768547689</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9557046979865773</v>
+        <v>0.9267503302509905</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.938790672868647</v>
+        <v>2.9389994527348</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.743053103265713</v>
+        <v>2.744201467232373</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.202739726027397</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003402760221175836</v>
+        <v>0.003402518496794816</v>
       </c>
     </row>
     <row r="18">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>158</v>
+        <v>154.7</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.01119869536815086</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.488607594936709</v>
+        <v>0.5203619909502264</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.143894385962247</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27570</v>
+        <v>27410</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5787389239718821</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.001199720130576676</v>
+        <v>0.007044008901860632</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.377697218865878</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>458.3</v>
+        <v>455</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.02868683472961315</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.4736769146847042</v>
+        <v>0.4843651208791209</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.726027397260274</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101.7</v>
+        <v>101.4</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>212.7</v>
+        <v>210.4</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.06059877293448147</v>
+        <v>0.06223529704016895</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.09971791255289153</v>
+        <v>0.1084600760456274</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.913199134107255</v>
+        <v>1.913105523504286</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.803885864221572</v>
+        <v>1.801018596195209</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>1.964383561643836</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005226847441924146</v>
+        <v>0.005227103197989171</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10080</v>
+        <v>9957</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.03003573242595473</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5729916964285715</v>
+        <v>0.5924230491111782</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.264556107884658</v>
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>43.8</v>
+        <v>44</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>29.7</v>
+        <v>29.5</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.3791852176590282</v>
+        <v>0.3770813865135745</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.4747474747474747</v>
+        <v>0.4915254237288136</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.742213609050467</v>
+        <v>2.743701898894741</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>1.988285238225644</v>
+        <v>1.992403590495917</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.202739726027397</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003646688925689728</v>
+        <v>0.003644710820817796</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1108</v>
+        <v>1099</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.0537100494266862</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.6693314945848376</v>
+        <v>0.6830020891719746</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2219178082191781</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>10980</v>
+        <v>11020</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-3.500407203414941</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.2180914550091075</v>
+        <v>0.213670070417423</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>124.5</v>
+        <v>121</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>13370</v>
+        <v>13300</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.03415342323134281</v>
+        <v>-0.02362596990146945</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.07179880329094979</v>
+        <v>0.0471503759398495</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.602371249467343</v>
+        <v>2.600295747773492</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>2.694394029095029</v>
+        <v>2.663216828402414</v>
       </c>
       <c r="BC29" s="8" t="n">
         <v>2.698630136986301</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003842649276903445</v>
+        <v>0.003845716399206713</v>
       </c>
     </row>
     <row r="30">
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>62560</v>
+        <v>63240</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2605241385913359</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1794757033248082</v>
+        <v>0.1667931688804554</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.569605436411785</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>120.4</v>
+        <v>120.8</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4524,7 +4524,7 @@
         <v>-0.1028517832577547</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.1302408637873755</v>
+        <v>0.1264983443708612</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.605987313457048</v>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>101.5</v>
+        <v>101.6</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -4616,7 +4616,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1385</v>
+        <v>1368</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03533330091412761</v>
+        <v>0.03470664186006318</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.3191335740072203</v>
+        <v>0.3368421052631578</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.601154757687908</v>
+        <v>1.601179489289788</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.546511404853103</v>
+        <v>1.547471935051458</v>
       </c>
       <c r="BC34" s="8" t="n">
         <v>1.619178082191781</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.006245492480964271</v>
+        <v>0.006245396013931927</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1675180286484271</v>
+        <v>0.1677303831287204</v>
       </c>
       <c r="AZ2" s="12" t="n">
         <v>0.7973680275160759</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.921946578838321</v>
+        <v>2.91634985399445</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.50269932210032</v>
+        <v>2.497451377586513</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.202739726027397</v>
+        <v>3.197260273972603</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003422376053150056</v>
+        <v>0.003428943885557233</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.001852378659848942</v>
+        <v>-0.002002435565874774</v>
       </c>
       <c r="AZ3" s="12" t="n">
         <v>0.2557914182248522</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.679154467424184</v>
+        <v>1.67368135737942</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.68227066971285</v>
+        <v>1.677039520961571</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.698630136986301</v>
+        <v>1.693150684931507</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005955378253758846</v>
+        <v>0.00597485295268962</v>
       </c>
     </row>
     <row r="4">
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02422060890885348</v>
+        <v>0.02419780452388148</v>
       </c>
       <c r="AZ4" s="12" t="n">
         <v>0.5098646986469866</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.325047307264282</v>
+        <v>4.31959113490934</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.222769264398949</v>
+        <v>4.21753602266057</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.698630136986301</v>
+        <v>4.693150684931507</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.00231211343820544</v>
+        <v>0.002315033920498562</v>
       </c>
     </row>
     <row r="5">
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.03384339876974388</v>
+        <v>0.03438175101436453</v>
       </c>
       <c r="AZ5" s="12" t="n">
         <v>1.472142749585906</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.2273972602739726</v>
+        <v>0.2219178082191781</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.2199532932594738</v>
+        <v>0.2145414959240675</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.2</v>
+        <v>0.1945205479452055</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.04397590361445782</v>
+        <v>0.04506172839506173</v>
       </c>
     </row>
     <row r="6">
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1104411128699389</v>
+        <v>-0.1105405592195836</v>
       </c>
       <c r="AZ6" s="12" t="n">
         <v>0.04454148471615715</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.468567648258291</v>
+        <v>6.463261761844028</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.271657606757777</v>
+        <v>7.266505323922503</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>6.873972602739726</v>
+        <v>6.868493150684931</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001545937299224593</v>
+        <v>0.001547206405755553</v>
       </c>
     </row>
     <row r="7">
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05023836142518368</v>
+        <v>-0.05039929781602731</v>
       </c>
       <c r="AZ7" s="12" t="n">
         <v>0.3018922852983987</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.888869861652488</v>
+        <v>1.883391590874032</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>1.988783064018957</v>
+        <v>1.983351093298949</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>1.871232876712329</v>
+        <v>1.865753424657534</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005294170976528496</v>
+        <v>0.005309570271235662</v>
       </c>
     </row>
     <row r="8">
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04069485643566913</v>
+        <v>0.04095358986838127</v>
       </c>
       <c r="AZ8" s="12" t="n">
         <v>3.640340170261067</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.810958904109589</v>
+        <v>0.8054794520547944</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.7792475374453999</v>
+        <v>0.7737899747832558</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.7835616438356164</v>
+        <v>0.7780821917808219</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01233108108108108</v>
+        <v>0.01241496598639456</v>
       </c>
     </row>
     <row r="9">
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.146260319994183</v>
+        <v>0.1465964853844417</v>
       </c>
       <c r="AZ9" s="12" t="n">
         <v>3.589110738255033</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.591003157213226</v>
+        <v>1.585510475663199</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.387994619949245</v>
+        <v>1.382797257687036</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.619178082191781</v>
+        <v>1.613698630136986</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006285342649800791</v>
+        <v>0.006307116952864738</v>
       </c>
     </row>
     <row r="10">
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>0.004673313580744728</v>
+        <v>0.004654410621422434</v>
       </c>
       <c r="AZ10" s="3" t="n">
         <v>0.5561243144424131</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.043173332029554</v>
+        <v>4.037703655913472</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.024366206781512</v>
+        <v>4.018997590839199</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.208219178082191</v>
+        <v>4.202739726027398</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002473304797689763</v>
+        <v>0.00247665526055989</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.0376363662080922</v>
+        <v>0.03760323605711868</v>
       </c>
       <c r="AZ11" s="12" t="n">
         <v>0.5673993403643338</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.576187367222356</v>
+        <v>2.570715210888513</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.482745835746581</v>
+        <v>2.47755126579713</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.698630136986301</v>
+        <v>2.693150684931507</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003881705239002859</v>
+        <v>0.003889968035994043</v>
       </c>
     </row>
     <row r="12">
@@ -2111,7 +2111,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>-0.126027397260274</v>
+        <v>-0.1315068493150685</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1146087138449885</v>
+        <v>-0.114781348940567</v>
       </c>
       <c r="AZ13" s="12" t="n">
         <v>0.0004826254826255649</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.161114749608427</v>
+        <v>4.155792711262943</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.699746670964991</v>
+        <v>4.694651096979571</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.449315068493151</v>
+        <v>4.443835616438356</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002403202170990605</v>
+        <v>0.002406279786982207</v>
       </c>
     </row>
     <row r="14">
@@ -2317,22 +2317,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1955063779962575</v>
+        <v>-0.1958418056847585</v>
       </c>
       <c r="AZ14" s="12" t="n">
         <v>0.09962991695804191</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.096520211896656</v>
+        <v>3.091154016819625</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.849030156614779</v>
+        <v>3.843962591778116</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.202739726027397</v>
+        <v>3.197260273972603</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003229431528197544</v>
+        <v>0.00323503777087388</v>
       </c>
     </row>
     <row r="15">
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.164577741936131</v>
+        <v>-0.165109686947769</v>
       </c>
       <c r="AZ15" s="12" t="n">
         <v>0.1329521963824289</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.926260643356167</v>
+        <v>1.920812479135173</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.305732968882548</v>
+        <v>2.300676447080787</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>1.964383561643836</v>
+        <v>1.958904109589041</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005191405448941103</v>
+        <v>0.005206130274883679</v>
       </c>
     </row>
     <row r="16">
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.03670657526600996</v>
+        <v>-0.03689260324406018</v>
       </c>
       <c r="AZ16" s="12" t="n">
         <v>0.2193551186440679</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.700332051067797</v>
+        <v>1.694856930379332</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.765123696901946</v>
+        <v>1.759779787890907</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.698630136986301</v>
+        <v>1.693150684931507</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005881204199920873</v>
+        <v>0.005900203032336107</v>
       </c>
     </row>
     <row r="17">
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.07098530768547689</v>
+        <v>0.07102040966426254</v>
       </c>
       <c r="AZ17" s="12" t="n">
         <v>0.9267503302509905</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.9389994527348</v>
+        <v>2.933500316659781</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.744201467232373</v>
+        <v>2.738977044871963</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.202739726027397</v>
+        <v>3.197260273972603</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003402518496794816</v>
+        <v>0.003408896853771764</v>
       </c>
     </row>
     <row r="18">
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1229162355905209</v>
+        <v>0.123140444886678</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>2.724055666003977</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.672529614581014</v>
+        <v>1.6670405423338</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.48945180554938</v>
+        <v>1.484267216912485</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.698630136986301</v>
+        <v>1.693150684931507</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005978967375417805</v>
+        <v>0.005998654349461916</v>
       </c>
     </row>
     <row r="19">
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.01119869536815086</v>
+        <v>0.01114538223772246</v>
       </c>
       <c r="AZ19" s="12" t="n">
         <v>0.5203619909502264</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.143894385962247</v>
+        <v>3.138442002258745</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.109076782202175</v>
+        <v>3.103848425152468</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.364383561643836</v>
+        <v>3.358904109589041</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003180768426780123</v>
+        <v>0.00318629434375495</v>
       </c>
     </row>
     <row r="20">
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5787389239718821</v>
+        <v>-0.5802042058331384</v>
       </c>
       <c r="AZ20" s="12" t="n">
         <v>0.007044008901860632</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.377697218865878</v>
+        <v>1.372256778409732</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.270411859209895</v>
+        <v>3.268867381420891</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.361643835616438</v>
+        <v>1.356164383561644</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.00725848892126821</v>
+        <v>0.007287265880069985</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3124,22 +3124,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.02868683472961315</v>
+        <v>0.02862966588985583</v>
       </c>
       <c r="AZ21" s="12" t="n">
         <v>0.4843651208791209</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.726027397260274</v>
+        <v>0.7205479452054795</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.705780780650418</v>
+        <v>0.7004930628577016</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.6986301369863014</v>
+        <v>0.6931506849315069</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01377358490566038</v>
+        <v>0.01387832699619772</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.06223529704016895</v>
+        <v>0.0622092381552777</v>
       </c>
       <c r="AZ22" s="12" t="n">
         <v>0.1084600760456274</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.913105523504286</v>
+        <v>1.907627561893543</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.801018596195209</v>
+        <v>1.795905640216884</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>1.964383561643836</v>
+        <v>1.958904109589041</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005227103197989171</v>
+        <v>0.005242113397687457</v>
       </c>
     </row>
     <row r="23">
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.03003573242595473</v>
+        <v>0.03006761537342038</v>
       </c>
       <c r="AZ23" s="12" t="n">
         <v>0.5924230491111782</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.264556107884658</v>
+        <v>4.25907175011774</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.140202105261645</v>
+        <v>4.134749686867634</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.29041095890411</v>
+        <v>4.284931506849315</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002344909938342981</v>
+        <v>0.002347929451933641</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.2063247861417476</v>
+        <v>0.2065821840313405</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.2700313522123892</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.829785774237246</v>
+        <v>2.824133649551954</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.345790956752119</v>
+        <v>2.340606124413485</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.202739726027397</v>
+        <v>3.197260273972603</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003533836409470059</v>
+        <v>0.003540908909033568</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.3770813865135745</v>
+        <v>0.3776754947408499</v>
       </c>
       <c r="AZ25" s="12" t="n">
         <v>0.4915254237288136</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.743701898894741</v>
+        <v>2.737802337867539</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>1.992403590495917</v>
+        <v>1.987262129811301</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.202739726027397</v>
+        <v>3.197260273972603</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003644710820817796</v>
+        <v>0.003652564636126709</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3699,22 +3699,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>88.66622632896684</v>
+        <v>90.7461561331974</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.1761052631578948</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.2273972602739727</v>
+        <v>0.2219178082191781</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.002536041379055021</v>
+        <v>0.002418824042033947</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.2</v>
+        <v>0.1945205479452055</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.04397590361445782</v>
+        <v>0.04506172839506173</v>
       </c>
     </row>
     <row r="27">
@@ -3808,22 +3808,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.0537100494266862</v>
+        <v>0.05437608263405887</v>
       </c>
       <c r="AZ27" s="12" t="n">
         <v>0.6830020891719746</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.2219178082191781</v>
+        <v>0.2164383561643836</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.2106061419267297</v>
+        <v>0.2052762384591216</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.2</v>
+        <v>0.1945205479452055</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.04506172839506173</v>
+        <v>0.04620253164556962</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3938,7 +3938,7 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-3.500407203414941</v>
+        <v>-3.586885947670282</v>
       </c>
       <c r="AZ28" s="12" t="n">
         <v>0.213670070417423</v>
@@ -3946,7 +3946,7 @@
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.2</v>
+        <v>0.1945205479452055</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.02362596990146945</v>
+        <v>-0.02375949200825453</v>
       </c>
       <c r="AZ29" s="12" t="n">
         <v>0.0471503759398495</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.600295747773492</v>
+        <v>2.59484269811781</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>2.663216828402414</v>
+        <v>2.657995316600559</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.698630136986301</v>
+        <v>2.693150684931507</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003845716399206713</v>
+        <v>0.003853798154028211</v>
       </c>
     </row>
     <row r="30">
@@ -4189,22 +4189,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.06059423278485436</v>
+        <v>0.06060305850504278</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.7977181865769303</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.571102875207592</v>
+        <v>2.565621457521643</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.424209745565484</v>
+        <v>2.419021364258535</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.698630136986301</v>
+        <v>2.693150684931507</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003889381516557403</v>
+        <v>0.003897691130810805</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.08300935083032031</v>
+        <v>0.08305610060982326</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>-0.4268335742765273</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.11563898344018</v>
+        <v>2.110147829716211</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.953481732930712</v>
+        <v>1.948327356752874</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.271232876712329</v>
+        <v>2.265753424657534</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004726704356590786</v>
+        <v>0.004739004471238812</v>
       </c>
     </row>
     <row r="32">
@@ -4412,22 +4412,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2605241385913359</v>
+        <v>-0.2613653302508022</v>
       </c>
       <c r="AZ32" s="12" t="n">
         <v>0.1667931688804554</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.569605436411785</v>
+        <v>1.564156574125349</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.122591849613274</v>
+        <v>2.117632218179598</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.572602739726027</v>
+        <v>1.567123287671233</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.006371027882561759</v>
+        <v>0.006393221858618494</v>
       </c>
     </row>
     <row r="33">
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.1028517832577547</v>
+        <v>-0.1031242352145111</v>
       </c>
       <c r="AZ33" s="12" t="n">
         <v>0.1264983443708612</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.605987313457048</v>
+        <v>2.600563343814386</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.904745575842525</v>
+        <v>2.899580349834047</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.698630136986301</v>
+        <v>2.693150684931507</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003837317222674508</v>
+        <v>0.003845320677839156</v>
       </c>
     </row>
     <row r="34">
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03470664186006318</v>
+        <v>0.03467295817275835</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.3368421052631578</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.601179489289788</v>
+        <v>1.595701366624902</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.547471935051458</v>
+        <v>1.542227767741146</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.619178082191781</v>
+        <v>1.613698630136986</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.006245396013931927</v>
+        <v>0.00626683677106274</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1677303831287204</v>
+        <v>0.1678368928622456</v>
       </c>
       <c r="AZ2" s="12" t="n">
         <v>0.7973680275160759</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.91634985399445</v>
+        <v>2.91355129953748</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.497451377586513</v>
+        <v>2.494827246291793</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.197260273972603</v>
+        <v>3.194520547945205</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003428943885557233</v>
+        <v>0.003432237490236564</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.002002435565874774</v>
+        <v>-0.002077811289383328</v>
       </c>
       <c r="AZ3" s="12" t="n">
         <v>0.2557914182248522</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.67368135737942</v>
+        <v>1.670944817065843</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.677039520961571</v>
+        <v>1.674423954060805</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.693150684931507</v>
+        <v>1.69041095890411</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.00597485295268962</v>
+        <v>0.005984638090897499</v>
       </c>
     </row>
     <row r="4">
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02419780452388148</v>
+        <v>0.02418638545535353</v>
       </c>
       <c r="AZ4" s="12" t="n">
         <v>0.5098646986469866</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.31959113490934</v>
+        <v>4.316863065647536</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.21753602266057</v>
+        <v>4.214919400367013</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.693150684931507</v>
+        <v>4.69041095890411</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002315033920498562</v>
+        <v>0.002316496921011319</v>
       </c>
     </row>
     <row r="5">
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.03438175101436453</v>
+        <v>0.0346610360206772</v>
       </c>
       <c r="AZ5" s="12" t="n">
         <v>1.472142749585906</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.2219178082191781</v>
+        <v>0.2191780821917808</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.2145414959240675</v>
+        <v>0.2118356394619277</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.1945205479452055</v>
+        <v>0.1917808219178082</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.04506172839506173</v>
+        <v>0.04562500000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>20610</v>
+        <v>20760</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1105405592195836</v>
+        <v>-0.1105903401330087</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.04454148471615715</v>
+        <v>0.03699421965317917</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.463261761844028</v>
+        <v>6.460608898477294</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.266505323922503</v>
+        <v>7.26392931176783</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>6.868493150684931</v>
+        <v>6.865753424657535</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001547206405755553</v>
+        <v>0.001547841721599478</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>20610</v>
+        <v>20760</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05039929781602731</v>
+        <v>-0.05048010710881115</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.3018922852983987</v>
+        <v>0.2924855491329479</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.883391590874032</v>
+        <v>1.880652457989525</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>1.983351093298949</v>
+        <v>1.9806351315749</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>1.865753424657534</v>
+        <v>1.863013698630137</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005309570271235662</v>
+        <v>0.005317303554687773</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1762</v>
+        <v>1776</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04095358986838127</v>
+        <v>0.0410842813509166</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.640340170261067</v>
+        <v>3.603760912162162</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.8054794520547944</v>
+        <v>0.8027397260273974</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.7737899747832558</v>
+        <v>0.7710612295344215</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.7780821917808219</v>
+        <v>0.7753424657534247</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01241496598639456</v>
+        <v>0.01245733788395904</v>
       </c>
     </row>
     <row r="9">
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>178.8</v>
+        <v>173.6</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1465964853844417</v>
+        <v>0.1467655009638282</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>3.589110738255033</v>
+        <v>3.726572580645161</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.585510475663199</v>
+        <v>1.58276409831415</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.382797257687036</v>
+        <v>1.380198564557336</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.613698630136986</v>
+        <v>1.610958904109589</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006307116952864738</v>
+        <v>0.006318060923072049</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>10940</v>
+        <v>10850</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>0.004654410621422434</v>
+        <v>0.004644941002314483</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.5561243144424131</v>
+        <v>0.5690322580645162</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.037703655913472</v>
+        <v>4.034968827098913</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.018997590839199</v>
+        <v>4.016313288825507</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.202739726027398</v>
+        <v>4.2</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.00247665526055989</v>
+        <v>0.002478333892653605</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03760323605711868</v>
+        <v>0.03758663065981212</v>
       </c>
       <c r="AZ11" s="12" t="n">
         <v>0.5673993403643338</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.570715210888513</v>
+        <v>2.567979141555529</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.47755126579713</v>
+        <v>2.474953961118914</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.693150684931507</v>
+        <v>2.690410958904109</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003889968035994043</v>
+        <v>0.003894112626609028</v>
       </c>
     </row>
     <row r="12">
@@ -2111,7 +2111,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>-0.1315068493150685</v>
+        <v>-0.1342465753424658</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.114781348940567</v>
+        <v>-0.1148678205613724</v>
       </c>
       <c r="AZ13" s="12" t="n">
         <v>0.0004826254826255649</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.155792711262943</v>
+        <v>4.153131813428391</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.694651096979571</v>
+        <v>4.692103518439934</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.443835616438356</v>
+        <v>4.441095890410959</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002406279786982207</v>
+        <v>0.002407821482493484</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>228.8</v>
+        <v>227</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2317,22 +2317,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1958418056847585</v>
+        <v>-0.196009907692481</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.09962991695804191</v>
+        <v>0.108349449339207</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.091154016819625</v>
+        <v>3.088471028386639</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.843962591778116</v>
+        <v>3.841429214037287</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.197260273972603</v>
+        <v>3.194520547945205</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.00323503777087388</v>
+        <v>0.003237848083432992</v>
       </c>
     </row>
     <row r="15">
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.165109686947769</v>
+        <v>-0.1653766589104863</v>
       </c>
       <c r="AZ15" s="12" t="n">
         <v>0.1329521963824289</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.920812479135173</v>
+        <v>1.918088456588749</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.300676447080787</v>
+        <v>2.29814859249549</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>1.958904109589041</v>
+        <v>1.956164383561644</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005206130274883679</v>
+        <v>0.005213523894400907</v>
       </c>
     </row>
     <row r="16">
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17110</v>
+        <v>17030</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.03689260324406018</v>
+        <v>-0.03698605209610008</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2193551186440679</v>
+        <v>0.2250831520845569</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.694856930379332</v>
+        <v>1.692119380174685</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.759779787890907</v>
+        <v>1.757107863139219</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.693150684931507</v>
+        <v>1.69041095890411</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005900203032336107</v>
+        <v>0.005909748518433525</v>
       </c>
     </row>
     <row r="17">
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>75.7</v>
+        <v>75.5</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.07102040966426254</v>
+        <v>0.07103802111002223</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9267503302509905</v>
+        <v>0.9318543046357615</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.933500316659781</v>
+        <v>2.930750714464695</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.738977044871963</v>
+        <v>2.736364775759565</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.197260273972603</v>
+        <v>3.194520547945205</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003408896853771764</v>
+        <v>0.003412095048086173</v>
       </c>
     </row>
     <row r="18">
@@ -2781,7 +2781,7 @@
         <v>4.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>100.6</v>
+        <v>100</v>
       </c>
       <c r="AK18" s="10" t="n">
         <v>46924</v>
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.123140444886678</v>
+        <v>0.1232531436916476</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>2.724055666003977</v>
+        <v>2.7464</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.6670405423338</v>
+        <v>1.664295980790226</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.484267216912485</v>
+        <v>1.481674892375911</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.693150684931507</v>
+        <v>1.69041095890411</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005998654349461916</v>
+        <v>0.00600854662597448</v>
       </c>
     </row>
     <row r="19">
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.01114538223772246</v>
+        <v>0.01111866323409471</v>
       </c>
       <c r="AZ19" s="12" t="n">
         <v>0.5203619909502264</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.138442002258745</v>
+        <v>3.13571584151089</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.103848425152468</v>
+        <v>3.101234262140118</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.358904109589041</v>
+        <v>3.356164383561644</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.00318629434375495</v>
+        <v>0.003189064476959007</v>
       </c>
     </row>
     <row r="20">
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27410</v>
+        <v>27200</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5802042058331384</v>
+        <v>-0.5809393001516904</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.007044008901860632</v>
+        <v>0.0148189810294117</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.372256778409732</v>
+        <v>1.369536624660258</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.268867381420891</v>
+        <v>3.268110383903808</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.356164383561644</v>
+        <v>1.353424657534247</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.007287265880069985</v>
+        <v>0.007301739741703301</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3124,22 +3124,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.02862966588985583</v>
+        <v>0.02860079444459443</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.4843651208791209</v>
+        <v>0.4524432903225806</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.7205479452054795</v>
+        <v>0.7178082191780822</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.7004930628577016</v>
+        <v>0.6978491782768567</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.6931506849315069</v>
+        <v>0.6904109589041096</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01387832699619772</v>
+        <v>0.01393129770992366</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.0622092381552777</v>
+        <v>0.06219618255323699</v>
       </c>
       <c r="AZ22" s="12" t="n">
         <v>0.1084600760456274</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.907627561893543</v>
+        <v>1.904888582586162</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.795905640216884</v>
+        <v>1.793349113727106</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>1.958904109589041</v>
+        <v>1.956164383561644</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005242113397687457</v>
+        <v>0.005249650867466249</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9957</v>
+        <v>10040</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.03006761537342038</v>
+        <v>0.03008358809918421</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5924230491111782</v>
+        <v>0.57925859561753</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.25907175011774</v>
+        <v>4.256329566297032</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.134749686867634</v>
+        <v>4.132023474086454</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.284931506849315</v>
+        <v>4.282191780821917</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002347929451933641</v>
+        <v>0.002349442129477749</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>33.9</v>
+        <v>34.9</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.2065821840313405</v>
+        <v>0.2067113134936583</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.2700313522123892</v>
+        <v>0.2336407690544411</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.824133649551954</v>
+        <v>2.82130728613131</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.340606124413485</v>
+        <v>2.338013454073858</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.197260273972603</v>
+        <v>3.194520547945205</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003540908909033568</v>
+        <v>0.003544456163692968</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.3776754947408499</v>
+        <v>0.3779736341979096</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.4915254237288136</v>
+        <v>0.4864864864864864</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.737802337867539</v>
+        <v>2.734851738122234</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>1.987262129811301</v>
+        <v>1.984690904274185</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.197260273972603</v>
+        <v>3.194520547945205</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003652564636126709</v>
+        <v>0.003656505345648486</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3699,22 +3699,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>90.7461561331974</v>
+        <v>91.82521489971346</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.1761052631578948</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.2219178082191781</v>
+        <v>0.2191780821917808</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.002418824042033947</v>
+        <v>0.002361191217586477</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.1945205479452055</v>
+        <v>0.1917808219178082</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.04506172839506173</v>
+        <v>0.04562500000000001</v>
       </c>
     </row>
     <row r="27">
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1099</v>
+        <v>1195</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3808,22 +3808,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05437608263405887</v>
+        <v>0.05472198575158485</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.6830020891719746</v>
+        <v>0.5477985740585776</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.2164383561643836</v>
+        <v>0.2136986301369863</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.2052762384591216</v>
+        <v>0.2026113355214708</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.1945205479452055</v>
+        <v>0.1917808219178082</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.04620253164556962</v>
+        <v>0.0467948717948718</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>11020</v>
+        <v>10850</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3938,15 +3938,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-3.586885947670282</v>
+        <v>-3.631746794274673</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.213670070417423</v>
+        <v>0.2326860991705071</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.1945205479452055</v>
+        <v>0.1917808219178082</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>13300</v>
+        <v>13450</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.02375949200825453</v>
+        <v>-0.02382645028739662</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.0471503759398495</v>
+        <v>0.03547211895910762</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.59484269811781</v>
+        <v>2.592116211533499</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>2.657995316600559</v>
+        <v>2.655384600716387</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.693150684931507</v>
+        <v>2.690410958904109</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003853798154028211</v>
+        <v>0.003857851725746504</v>
       </c>
     </row>
     <row r="30">
@@ -4189,22 +4189,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.06060305850504278</v>
+        <v>0.06060749960502867</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.7977181865769303</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.565621457521643</v>
+        <v>2.562880742386016</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.419021364258535</v>
+        <v>2.416427135712726</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.693150684931507</v>
+        <v>2.690410958904109</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003897691130810805</v>
+        <v>0.003901859276795728</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4286,7 +4286,7 @@
         <v>0.9284102</v>
       </c>
       <c r="AJ31" t="n">
-        <v>155.5</v>
+        <v>155.6</v>
       </c>
       <c r="AK31" s="10" t="n">
         <v>47133</v>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.08305610060982326</v>
+        <v>0.08307959057241759</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>-0.4268335742765273</v>
+        <v>-0.4272019331619538</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.110147829716211</v>
+        <v>2.107402223961906</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.948327356752874</v>
+        <v>1.945750102121419</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.265753424657534</v>
+        <v>2.263013698630137</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004739004471238812</v>
+        <v>0.004745178630968724</v>
       </c>
     </row>
     <row r="32">
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>63240</v>
+        <v>62840</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4412,22 +4412,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2613653302508022</v>
+        <v>-0.2617877696071202</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1667931688804554</v>
+        <v>0.1742202418841503</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.564156574125349</v>
+        <v>1.561432210747606</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.117632218179598</v>
+        <v>2.115153537779515</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.567123287671233</v>
+        <v>1.564383561643836</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.006393221858618494</v>
+        <v>0.006404376655719209</v>
       </c>
     </row>
     <row r="33">
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.1031242352145111</v>
+        <v>-0.1032608539189982</v>
       </c>
       <c r="AZ33" s="12" t="n">
         <v>0.1264983443708612</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.600563343814386</v>
+        <v>2.597851435459527</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.899580349834047</v>
+        <v>2.896997913844686</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.693150684931507</v>
+        <v>2.690410958904109</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003845320677839156</v>
+        <v>0.003849334824734166</v>
       </c>
     </row>
     <row r="34">
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03467295817275835</v>
+        <v>0.03465604375356141</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.3368421052631578</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.595701366624902</v>
+        <v>1.592962308158181</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.542227767741146</v>
+        <v>1.539605666806117</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.613698630136986</v>
+        <v>1.610958904109589</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.00626683677106274</v>
+        <v>0.006277612438653507</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>70.7</v>
+        <v>70</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>668.7</v>
+        <v>638.9</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1678368928622456</v>
+        <v>0.1716511885251849</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7973680275160759</v>
+        <v>0.8625763030208171</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.91355129953748</v>
+        <v>2.911440850712569</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.494827246291793</v>
+        <v>2.484904107319981</v>
       </c>
       <c r="BC2" s="8" t="n">
         <v>3.194520547945205</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003432237490236564</v>
+        <v>0.003434725454770108</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8450</v>
+        <v>8389</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.002077811289383328</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2557914182248522</v>
+        <v>0.2649228136845869</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.670944817065843</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>81.3</v>
+        <v>80.5</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.02418638545535353</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.5098646986469866</v>
+        <v>0.5248695652173914</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.316863065647536</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6641</v>
+        <v>6520</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.0346610360206772</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.472142749585906</v>
+        <v>1.518021472392638</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2191780821917808</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>269.1</v>
+        <v>268.8</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>20760</v>
+        <v>20910</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1105903401330087</v>
+        <v>-0.1104370198452403</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.03699421965317917</v>
+        <v>0.02840746054519361</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.460608898477294</v>
+        <v>6.460341325346586</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.26392931176783</v>
+        <v>7.26237654833912</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.865753424657535</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001547841721599478</v>
+        <v>0.001547905829799716</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>20760</v>
+        <v>20910</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.05048010710881115</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2924855491329479</v>
+        <v>0.2832137733142037</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.880652457989525</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1776</v>
+        <v>1791</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.0410842813509166</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.603760912162162</v>
+        <v>3.565203450586265</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8027397260273974</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>173.6</v>
+        <v>167.1</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1467655009638282</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>3.726572580645161</v>
+        <v>3.910430879712746</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.58276409831415</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106.4</v>
+        <v>105.8</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>10850</v>
+        <v>10910</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>0.004644941002314483</v>
+        <v>0.006033621842025268</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.5690322580645162</v>
+        <v>0.5516040329972502</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.034968827098913</v>
+        <v>4.034249689664065</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.016313288825507</v>
+        <v>4.010054537021778</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.2</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002478333892653605</v>
+        <v>0.002478775675591043</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03758663065981212</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5673993403643338</v>
+        <v>0.5643995330143541</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.567979141555529</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>207.2</v>
+        <v>205</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2211,7 +2211,7 @@
         <v>-0.1148678205613724</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.0004826254826255649</v>
+        <v>0.01121951219512196</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.153131813428391</v>
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>227</v>
+        <v>220.6</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.196009907692481</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.108349449339207</v>
+        <v>0.1405046464188577</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.088471028386639</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>160.9</v>
+        <v>161.9</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>77.40000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1653766589104863</v>
+        <v>-0.1680646898648217</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1329521963824289</v>
+        <v>0.1564285714285716</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.918088456588749</v>
+        <v>1.918246597471948</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.29814859249549</v>
+        <v>2.305764131059973</v>
       </c>
       <c r="BC15" s="8" t="n">
         <v>1.956164383561644</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005213523894400907</v>
+        <v>0.005213094089768736</v>
       </c>
     </row>
     <row r="16">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>111.2</v>
+        <v>110.8</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17030</v>
+        <v>16960</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.03698605209610008</v>
+        <v>-0.03494606882799409</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2250831520845569</v>
+        <v>0.2257145471698112</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.692119380174685</v>
+        <v>1.692071884287634</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.757107863139219</v>
+        <v>1.753344377585928</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.69041095890411</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005909748518433525</v>
+        <v>0.005909914403081063</v>
       </c>
     </row>
     <row r="17">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>94.09999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.07103802111002223</v>
+        <v>0.07441594955313147</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9318543046357615</v>
+        <v>0.9133774834437087</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.930750714464695</v>
+        <v>2.928853279383908</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.736364775759565</v>
+        <v>2.725995719443731</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.194520547945205</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003412095048086173</v>
+        <v>0.003414305547631777</v>
       </c>
     </row>
     <row r="18">
@@ -2781,7 +2781,7 @@
         <v>4.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>100</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="AK18" s="10" t="n">
         <v>46924</v>
@@ -2798,7 +2798,7 @@
         <v>0.1232531436916476</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>2.7464</v>
+        <v>2.898439125910511</v>
       </c>
       <c r="BA18" s="8" t="n">
         <v>1.664295980790226</v>
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>154.7</v>
+        <v>151.8</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.01111866323409471</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5203619909502264</v>
+        <v>0.5494071146245059</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.13571584151089</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27200</v>
+        <v>26960</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5809393001516904</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.0148189810294117</v>
+        <v>0.02385297789317509</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.369536624660258</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>465</v>
+        <v>477.3</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.02860079444459443</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.4524432903225806</v>
+        <v>0.4150138906348209</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7178082191780822</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101.4</v>
+        <v>102.9</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>210.4</v>
+        <v>207.5</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.06219618255323699</v>
+        <v>0.05405706244647791</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1084600760456274</v>
+        <v>0.1405783132530121</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.904888582586162</v>
+        <v>1.905354334844619</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.793349113727106</v>
+        <v>1.807638696924311</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>1.956164383561644</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005249650867466249</v>
+        <v>0.00524836762229609</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10040</v>
+        <v>9921</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.03008358809918421</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.57925859561753</v>
+        <v>0.5982014212276989</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.256329566297032</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>66.59999999999999</v>
+        <v>63.4</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.2067113134936583</v>
+        <v>0.2266769896859807</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.2336407690544411</v>
+        <v>0.1743667381088825</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.82130728613131</v>
+        <v>2.807813839841474</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.338013454073858</v>
+        <v>2.288959411034727</v>
       </c>
       <c r="BC24" s="8" t="n">
         <v>3.194520547945205</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003544456163692968</v>
+        <v>0.003561489675029378</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>44</v>
+        <v>43.4</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>29.6</v>
+        <v>29.9</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.3779736341979096</v>
+        <v>0.3843442254262373</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.4864864864864864</v>
+        <v>0.4515050167224079</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.734851738122234</v>
+        <v>2.73033759372998</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>1.984690904274185</v>
+        <v>1.972296733414924</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.194520547945205</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003656505345648486</v>
+        <v>0.003662550749388744</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1195</v>
+        <v>1125</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.05472198575158485</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5477985740585776</v>
+        <v>0.644106040888889</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2136986301369863</v>
@@ -3846,7 +3846,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>510.8</v>
+        <v>485.2</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>10850</v>
+        <v>10900</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3938,10 +3938,10 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-3.631746794274673</v>
+        <v>-3.583030617903576</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.2326860991705071</v>
+        <v>0.1655358664220183</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>121</v>
+        <v>123.5</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>13450</v>
+        <v>13660</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.02382645028739662</v>
+        <v>-0.03140833466514546</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.03547211895910762</v>
+        <v>0.04061859443631022</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.592116211533499</v>
+        <v>2.593612081884983</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>2.655384600716387</v>
+        <v>2.677714639417569</v>
       </c>
       <c r="BC29" s="8" t="n">
         <v>2.690410958904109</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003857851725746504</v>
+        <v>0.003855626702946345</v>
       </c>
     </row>
     <row r="30">
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>534.9</v>
+        <v>529</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4192,7 +4192,7 @@
         <v>0.06060749960502867</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.7977181865769303</v>
+        <v>0.8177683516068051</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.562880742386016</v>
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.08307959057241759</v>
+        <v>0.07300732782397515</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>-0.4272019331619538</v>
+        <v>-0.4152686401028277</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.107402223961906</v>
+        <v>2.109917904370568</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.945750102121419</v>
+        <v>1.966359268626259</v>
       </c>
       <c r="BC31" s="8" t="n">
         <v>2.263013698630137</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004745178630968724</v>
+        <v>0.004739520897607249</v>
       </c>
     </row>
     <row r="32">
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>62840</v>
+        <v>62510</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2617877696071202</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1742202418841503</v>
+        <v>0.1804191329387299</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.561432210747606</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>120.8</v>
+        <v>117</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4524,7 +4524,7 @@
         <v>-0.1032608539189982</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.1264983443708612</v>
+        <v>0.1630854700854703</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.597851435459527</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>70</v>
+        <v>69.8</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>638.9</v>
+        <v>668</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1716511885251849</v>
+        <v>0.1727504916097196</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.8625763030208171</v>
+        <v>0.7763473053892214</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.911440850712569</v>
+        <v>2.910831270999969</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.484904107319981</v>
+        <v>2.48205504224906</v>
       </c>
       <c r="BC2" s="8" t="n">
         <v>3.194520547945205</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003434725454770108</v>
+        <v>0.003435444747219808</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8389</v>
+        <v>8553</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.002077811289383328</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2649228136845869</v>
+        <v>0.2406684770256051</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.670944817065843</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>80.5</v>
+        <v>81.7</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.02418638545535353</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.5248695652173914</v>
+        <v>0.5024724602203183</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.316863065647536</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6520</v>
+        <v>6615</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.0346610360206772</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.518021472392638</v>
+        <v>1.481859410430839</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2191780821917808</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>268.8</v>
+        <v>274.7</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>20910</v>
+        <v>21120</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1104370198452403</v>
+        <v>-0.1134155422320592</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02840746054519361</v>
+        <v>0.04053030303030303</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.460341325346586</v>
+        <v>6.465515740794723</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.26237654833912</v>
+        <v>7.292611193605022</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.865753424657535</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001547905829799716</v>
+        <v>0.00154666702563326</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>20910</v>
+        <v>21120</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.05048010710881115</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2832137733142037</v>
+        <v>0.2704545454545455</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.880652457989525</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1791</v>
+        <v>1779</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.0410842813509166</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.565203450586265</v>
+        <v>3.595997403035413</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8027397260273974</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>167.1</v>
+        <v>168</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1467655009638282</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>3.910430879712746</v>
+        <v>3.884124999999999</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.58276409831415</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>10910</v>
+        <v>10880</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>0.006033621842025268</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.5516040329972502</v>
+        <v>0.5558823529411765</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.034249689664065</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1045</v>
+        <v>1064</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03758663065981212</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5643995330143541</v>
+        <v>0.5364638270676694</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.567979141555529</v>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>207.3</v>
+        <v>204.8</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>205</v>
+        <v>202.4</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1148678205613724</v>
+        <v>-0.1123137402947446</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.01121951219512196</v>
+        <v>0.01185770750988135</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.153131813428391</v>
+        <v>4.150798106611677</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.692103518439934</v>
+        <v>4.675974265941544</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.441095890410959</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002407821482493484</v>
+        <v>0.002409175234052293</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>220.6</v>
+        <v>227.2</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.196009907692481</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.1405046464188577</v>
+        <v>0.1073737896126761</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.088471028386639</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>76.3</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2429,7 +2429,7 @@
         <v>-0.1680646898648217</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1564285714285716</v>
+        <v>0.1043241551939926</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.918246597471948</v>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>110.8</v>
+        <v>112</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16960</v>
+        <v>17080</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.03494606882799409</v>
+        <v>-0.04103125333374257</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2257145471698112</v>
+        <v>0.2302845901639343</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.692071884287634</v>
+        <v>1.692213576185109</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.753344377585928</v>
+        <v>1.764618067135025</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.69041095890411</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005909914403081063</v>
+        <v>0.005909419555978148</v>
       </c>
     </row>
     <row r="17">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>93.2</v>
+        <v>93.8</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.07441594955313147</v>
+        <v>0.07215911587383773</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9133774834437087</v>
+        <v>0.9256953642384105</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.928853279383908</v>
+        <v>2.930121674126908</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.725995719443731</v>
+        <v>2.732916813134385</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.194520547945205</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003414305547631777</v>
+        <v>0.003412827558766724</v>
       </c>
     </row>
     <row r="18">
@@ -2781,7 +2781,7 @@
         <v>4.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>96.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AK18" s="10" t="n">
         <v>46924</v>
@@ -2798,7 +2798,7 @@
         <v>0.1232531436916476</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>2.898439125910511</v>
+        <v>2.947734457323499</v>
       </c>
       <c r="BA18" s="8" t="n">
         <v>1.664295980790226</v>
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>151.8</v>
+        <v>157.8</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.01111866323409471</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5494071146245059</v>
+        <v>0.4904942965779469</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.13571584151089</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>26960</v>
+        <v>27200</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5809393001516904</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.02385297789317509</v>
+        <v>0.0148189810294117</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.369536624660258</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100.5</v>
+        <v>100.1</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>477.3</v>
+        <v>487.2</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3124,16 +3124,16 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.02860079444459443</v>
+        <v>0.03422495721330954</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.4150138906348209</v>
+        <v>0.3807430747126435</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.7178082191780822</v>
+        <v>0.7178082191780824</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.6978491782768567</v>
+        <v>0.6940542424272923</v>
       </c>
       <c r="BC21" s="8" t="n">
         <v>0.6904109589041096</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102.9</v>
+        <v>101.9</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>207.5</v>
+        <v>211.7</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.05405706244647791</v>
+        <v>0.05946267030941987</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1405783132530121</v>
+        <v>0.1070854983467171</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.905354334844619</v>
+        <v>1.905044953107431</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.807638696924311</v>
+        <v>1.798123715440635</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>1.956164383561644</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.00524836762229609</v>
+        <v>0.005249219963911304</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9921</v>
+        <v>10110</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.03008358809918421</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5982014212276989</v>
+        <v>0.5683240652818993</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.256329566297032</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>63.4</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>34.9</v>
+        <v>31</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.2266769896859807</v>
+        <v>0.2171503606197188</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.1743667381088825</v>
+        <v>0.3533898470967742</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.807813839841474</v>
+        <v>2.814276372763663</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.288959411034727</v>
+        <v>2.312184643588947</v>
       </c>
       <c r="BC24" s="8" t="n">
         <v>3.194520547945205</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003561489675029378</v>
+        <v>0.003553311286972091</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>43.4</v>
+        <v>43.3</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>29.9</v>
+        <v>29.6</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.3843442254262373</v>
+        <v>0.3854177630634166</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.4515050167224079</v>
+        <v>0.4628378378378377</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.73033759372998</v>
+        <v>2.729575352787289</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>1.972296733414924</v>
+        <v>1.970218244316205</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.194520547945205</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003662550749388744</v>
+        <v>0.003663573526112244</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.05472198575158485</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.644106040888889</v>
+        <v>0.6426459111900533</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2136986301369863</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>10900</v>
+        <v>10920</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-3.583030617903576</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.1655358664220183</v>
+        <v>0.1634011853479853</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>13660</v>
+        <v>13720</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.03140833466514546</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.04061859443631022</v>
+        <v>0.03606778425655977</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.593612081884983</v>
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4192,7 +4192,7 @@
         <v>0.06060749960502867</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.8177683516068051</v>
+        <v>0.8456803416506715</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.562880742386016</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>62510</v>
+        <v>63230</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2617877696071202</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1804191329387299</v>
+        <v>0.166977700458643</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.561432210747606</v>
@@ -4450,7 +4450,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>152.9</v>
+        <v>142</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>117</v>
+        <v>120.8</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.1032608539189982</v>
+        <v>-0.07761278023076963</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.1630854700854703</v>
+        <v>0.04619205298013251</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.597851435459527</v>
+        <v>2.5925883128421</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.896997913844686</v>
+        <v>2.810737461747066</v>
       </c>
       <c r="BC33" s="8" t="n">
         <v>2.690410958904109</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003849334824734166</v>
+        <v>0.003857149224373999</v>
       </c>
     </row>
     <row r="34">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>668</v>
+        <v>642.8</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.1727504916097196</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7763473053892214</v>
+        <v>0.8459863098942129</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>2.910831270999969</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>108.7</v>
+        <v>106.8</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8553</v>
+        <v>8450</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.002077811289383328</v>
+        <v>0.008375876084176743</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2406684770256051</v>
+        <v>0.2338410622485207</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.670944817065843</v>
+        <v>1.67050320032332</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.674423954060805</v>
+        <v>1.656627493718295</v>
       </c>
       <c r="BC3" s="8" t="n">
         <v>1.69041095890411</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005984638090897499</v>
+        <v>0.005986220198838612</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>109.6</v>
+        <v>108.8</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>81.7</v>
+        <v>81</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02418638545535353</v>
+        <v>0.02590568265280916</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.5024724602203183</v>
+        <v>0.5043950617283952</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.316863065647536</v>
+        <v>4.31510563500583</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.214919400367013</v>
+        <v>4.206142638617359</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.69041095890411</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002316496921011319</v>
+        <v>0.002317440370144377</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6615</v>
+        <v>6587</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.0346610360206772</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.481859410430839</v>
+        <v>1.492409291027782</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2191780821917808</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>274.7</v>
+        <v>275</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21120</v>
+        <v>21180</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1134155422320592</v>
+        <v>-0.1135649550425713</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.04053030303030303</v>
+        <v>0.03871576959395662</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.465515740794723</v>
+        <v>6.465773994383762</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.292611193605022</v>
+        <v>7.294131737192637</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.865753424657535</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.00154666702563326</v>
+        <v>0.00154660524922246</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>111.8</v>
+        <v>113.2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21120</v>
+        <v>21180</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05048010710881115</v>
+        <v>-0.05673775614193567</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2704545454545455</v>
+        <v>0.2827195467422097</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.880652457989525</v>
+        <v>1.880698391493224</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>1.9806351315749</v>
+        <v>1.993823460802294</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>1.863013698630137</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005317303554687773</v>
+        <v>0.005317173686770833</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1779</v>
+        <v>1800</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.0410842813509166</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.595997403035413</v>
+        <v>3.542377433333333</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.8027397260273974</v>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>86.09999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1467655009638282</v>
+        <v>0.1451177395798497</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>3.884124999999999</v>
+        <v>3.924784431137724</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.58276409831415</v>
+        <v>1.582828947131967</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.380198564557336</v>
+        <v>1.382241225005139</v>
       </c>
       <c r="BC9" s="8" t="n">
         <v>1.610958904109589</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006318060923072049</v>
+        <v>0.006317802070855266</v>
       </c>
     </row>
     <row r="10">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105.8</v>
+        <v>107.9</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>10880</v>
+        <v>10790</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>0.006033621842025268</v>
+        <v>0.001216023366745436</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.5558823529411765</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.034249689664065</v>
+        <v>4.03673605940882</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.010054537021778</v>
+        <v>4.031833255958753</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.2</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002478775675591043</v>
+        <v>0.002477248909225068</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03758663065981212</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5364638270676694</v>
+        <v>0.5350211380281691</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.567979141555529</v>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>204.8</v>
+        <v>206.2</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>202.4</v>
+        <v>200.3</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1123137402947446</v>
+        <v>-0.1137488704751088</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.01185770750988135</v>
+        <v>0.02945581627558647</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.150798106611677</v>
+        <v>4.152110782447501</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.675974265941544</v>
+        <v>4.685027351867409</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.441095890410959</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002409175234052293</v>
+        <v>0.002408413581418318</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>227.2</v>
+        <v>231.4</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.196009907692481</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.1073737896126761</v>
+        <v>0.08727452463267071</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.088471028386639</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>161.9</v>
+        <v>161.5</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>79.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1680646898648217</v>
+        <v>-0.1669925389389275</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1043241551939926</v>
+        <v>0.1460611979166668</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.918246597471948</v>
+        <v>1.918183514905389</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.305764131059973</v>
+        <v>2.302720689274541</v>
       </c>
       <c r="BC15" s="8" t="n">
         <v>1.956164383561644</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005213094089768736</v>
+        <v>0.005213265530797368</v>
       </c>
     </row>
     <row r="16">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17080</v>
+        <v>17010</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.04103125333374257</v>
+        <v>-0.05094638153717832</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2302845901639343</v>
+        <v>0.2574072663139331</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.692213576185109</v>
+        <v>1.692444535359058</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.764618067135025</v>
+        <v>1.783297068189154</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.69041095890411</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005909419555978148</v>
+        <v>0.005908613127979682</v>
       </c>
     </row>
     <row r="17">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>93.8</v>
+        <v>93.5</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>75.5</v>
+        <v>74.3</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.07215911587383773</v>
+        <v>0.07328507964511669</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9256953642384105</v>
+        <v>0.9505383580080755</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.930121674126908</v>
+        <v>2.92948920557431</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.732916813134385</v>
+        <v>2.729460477120347</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.194520547945205</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003412827558766724</v>
+        <v>0.003413564378722316</v>
       </c>
     </row>
     <row r="18">
@@ -2781,7 +2781,7 @@
         <v>4.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>94.90000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="AK18" s="10" t="n">
         <v>46924</v>
@@ -2798,7 +2798,7 @@
         <v>0.1232531436916476</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>2.947734457323499</v>
+        <v>2.91473354231975</v>
       </c>
       <c r="BA18" s="8" t="n">
         <v>1.664295980790226</v>
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>112</v>
+        <v>111.3</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>157.8</v>
+        <v>155.5</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.01111866323409471</v>
+        <v>0.01309066123191961</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4904942965779469</v>
+        <v>0.5030868167202571</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.13571584151089</v>
+        <v>3.134713583348776</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.101234262140118</v>
+        <v>3.0942083500572</v>
       </c>
       <c r="BC19" s="8" t="n">
         <v>3.356164383561644</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003189064476959007</v>
+        <v>0.003190084112666243</v>
       </c>
     </row>
     <row r="20">
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27200</v>
+        <v>27180</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5809393001516904</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.0148189810294117</v>
+        <v>0.01556572052980121</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.369536624660258</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>487.2</v>
+        <v>487.7</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03422495721330954</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.3807430747126435</v>
+        <v>0.3793275087143735</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7178082191780824</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101.9</v>
+        <v>101.7</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>211.7</v>
+        <v>211</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.05946267030941987</v>
+        <v>0.06055359393852228</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1070854983467171</v>
+        <v>0.1085781990521326</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.905044953107431</v>
+        <v>1.904982540568818</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.798123715440635</v>
+        <v>1.796215251597408</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>1.956164383561644</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005249219963911304</v>
+        <v>0.005249391942990748</v>
       </c>
     </row>
     <row r="23">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>90</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.03008358809918421</v>
+        <v>0.02981589737046682</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5683240652818993</v>
+        <v>0.5700666475766567</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.256329566297032</v>
+        <v>4.256370745706033</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.132023474086454</v>
+        <v>4.133137540966551</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.282191780821917</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002349442129477749</v>
+        <v>0.002349419399164964</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>64.90000000000001</v>
+        <v>63.1</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>31</v>
+        <v>30.8</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.2171503606197188</v>
+        <v>0.2286193940823452</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.3533898470967742</v>
+        <v>0.3243981149350648</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.814276372763663</v>
+        <v>2.806490825893092</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.312184643588947</v>
+        <v>2.284263816288898</v>
       </c>
       <c r="BC24" s="8" t="n">
         <v>3.194520547945205</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003553311286972091</v>
+        <v>0.003563168604628438</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>43.3</v>
+        <v>42.3</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>29.6</v>
+        <v>30</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.3854177630634166</v>
+        <v>0.3963440426513406</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.4628378378378377</v>
+        <v>0.4099999999999999</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.729575352787289</v>
+        <v>2.721792369367749</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>1.970218244316205</v>
+        <v>1.949227615996186</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.194520547945205</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003663573526112244</v>
+        <v>0.003674049539025977</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1126</v>
+        <v>1119</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.05472198575158485</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.6426459111900533</v>
+        <v>0.6529216228775694</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2136986301369863</v>
@@ -3846,7 +3846,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>485.2</v>
+        <v>485.1</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>10920</v>
+        <v>11090</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3938,10 +3938,10 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-3.583030617903576</v>
+        <v>-3.582830319099763</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.1634011853479853</v>
+        <v>0.1453311606853021</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>123.5</v>
+        <v>122.8</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>13720</v>
+        <v>13780</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.03140833466514546</v>
+        <v>-0.02930717907923597</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.03606778425655977</v>
+        <v>0.02570972423802598</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.593612081884983</v>
+        <v>2.593198184264088</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>2.677714639417569</v>
+        <v>2.671492081093455</v>
       </c>
       <c r="BC29" s="8" t="n">
         <v>2.690410958904109</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003855626702946345</v>
+        <v>0.00385624209544858</v>
       </c>
     </row>
     <row r="30">
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>521</v>
+        <v>524.8</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4192,7 +4192,7 @@
         <v>0.06060749960502867</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.8456803416506715</v>
+        <v>0.8323160403963414</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.562880742386016</v>
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>98</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.07300732782397515</v>
+        <v>0.07251163533137636</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>-0.4152686401028277</v>
+        <v>-0.4146719754498716</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.109917904370568</v>
+        <v>2.110041424836782</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.966359268626259</v>
+        <v>1.967383248187175</v>
       </c>
       <c r="BC31" s="8" t="n">
         <v>2.263013698630137</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004739520897607249</v>
+        <v>0.004739243449105995</v>
       </c>
     </row>
     <row r="32">
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>63230</v>
+        <v>62860</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2617877696071202</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.166977700458643</v>
+        <v>0.1738466433343939</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.561432210747606</v>
@@ -4450,7 +4450,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>142</v>
+        <v>143.2</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>120.8</v>
+        <v>121.3</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.07761278023076963</v>
+        <v>-0.08056939306307402</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.04619205298013251</v>
+        <v>0.05068425391591092</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.5925883128421</v>
+        <v>2.593199179490269</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.810737461747066</v>
+        <v>2.820440346367722</v>
       </c>
       <c r="BC33" s="8" t="n">
         <v>2.690410958904109</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003857149224373999</v>
+        <v>0.003856240615487796</v>
       </c>
     </row>
     <row r="34">
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>101.6</v>
+        <v>101.8</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -4616,7 +4616,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1368</v>
+        <v>1341</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03465604375356141</v>
+        <v>0.03339977437903058</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.3368421052631578</v>
+        <v>0.3664429530201341</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.592962308158181</v>
+        <v>1.593011891891686</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.539605666806117</v>
+        <v>1.541525294844317</v>
       </c>
       <c r="BC34" s="8" t="n">
         <v>1.610958904109589</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.006277612438653507</v>
+        <v>0.006277417043086288</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>642.8</v>
+        <v>668.7</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1727504916097196</v>
+        <v>0.1728616234434923</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.8459863098942129</v>
+        <v>0.7744878121728724</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.910831270999969</v>
+        <v>2.908029887516021</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.48205504224906</v>
+        <v>2.479431357791483</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.194520547945205</v>
+        <v>3.191780821917808</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003435444747219808</v>
+        <v>0.003438754203637774</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>0.008375876084176743</v>
+        <v>0.008315434816349783</v>
       </c>
       <c r="AZ3" s="12" t="n">
         <v>0.2338410622485207</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.67050320032332</v>
+        <v>1.667766026468609</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.656627493718295</v>
+        <v>1.654012195868417</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.69041095890411</v>
+        <v>1.687671232876712</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005986220198838612</v>
+        <v>0.005996044913550842</v>
       </c>
     </row>
     <row r="4">
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>81</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02590568265280916</v>
+        <v>0.02589512527737425</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.5043950617283952</v>
+        <v>0.5025400739827375</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.31510563500583</v>
+        <v>4.312376714917245</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.206142638617359</v>
+        <v>4.203525885505397</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.69041095890411</v>
+        <v>4.687671232876713</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002317440370144377</v>
+        <v>0.00231890687226102</v>
       </c>
     </row>
     <row r="5">
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.0346610360206772</v>
+        <v>0.03494740150983618</v>
       </c>
       <c r="AZ5" s="12" t="n">
         <v>1.492409291027782</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.2191780821917808</v>
+        <v>0.2164383561643835</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.2118356394619277</v>
+        <v>0.2091298126345665</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.1917808219178082</v>
+        <v>0.189041095890411</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.04562500000000001</v>
+        <v>0.04620253164556963</v>
       </c>
     </row>
     <row r="6">
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21180</v>
+        <v>21220</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1135649550425713</v>
+        <v>-0.1136157075461084</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.03871576959395662</v>
+        <v>0.03675777568331773</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.465773994383762</v>
+        <v>6.463121963382302</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.294131737192637</v>
+        <v>7.291557418610849</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>6.865753424657535</v>
+        <v>6.863013698630137</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.00154660524922246</v>
+        <v>0.001547239872101496</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21180</v>
+        <v>21220</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05673775614193567</v>
+        <v>-0.05682724231700709</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2827195467422097</v>
+        <v>0.2803016022620171</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.880698391493224</v>
+        <v>1.877959322358917</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>1.993823460802294</v>
+        <v>1.991108529228866</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>1.863013698630137</v>
+        <v>1.86027397260274</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005317173686770833</v>
+        <v>0.005324928969941124</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1800</v>
+        <v>1808</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.0410842813509166</v>
+        <v>0.04121586810922209</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.542377433333333</v>
+        <v>3.522278418141592</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.8027397260273974</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.7710612295344215</v>
+        <v>0.7683325086590798</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.7753424657534247</v>
+        <v>0.7726027397260274</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01245733788395904</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="9">
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1451177395798497</v>
+        <v>0.1452845085420704</v>
       </c>
       <c r="AZ9" s="12" t="n">
         <v>3.924784431137724</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.582828947131967</v>
+        <v>1.580082657392226</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.382241225005139</v>
+        <v>1.379642041437937</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.610958904109589</v>
+        <v>1.608219178082192</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006317802070855266</v>
+        <v>0.006328782835009424</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>10790</v>
+        <v>10610</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>0.001216023366745436</v>
+        <v>0.001204425956847222</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.6271442035815269</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.03673605940882</v>
+        <v>4.034002290183384</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.031833255958753</v>
+        <v>4.029149477968102</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.2</v>
+        <v>4.197260273972603</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002477248909225068</v>
+        <v>0.002478927695290278</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>104.4</v>
+        <v>103.4</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1065</v>
+        <v>1083</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03758663065981212</v>
+        <v>0.0414128150373357</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5350211380281691</v>
+        <v>0.4950494293628811</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.567979141555529</v>
+        <v>2.564396045055456</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.474953961118914</v>
+        <v>2.462420289079619</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.690410958904109</v>
+        <v>2.687671232876713</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003894112626609028</v>
+        <v>0.003899553666556893</v>
       </c>
     </row>
     <row r="12">
@@ -2111,7 +2111,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>-0.1342465753424658</v>
+        <v>-0.136986301369863</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1137488704751088</v>
+        <v>-0.1138349171435974</v>
       </c>
       <c r="AZ13" s="12" t="n">
         <v>0.02945581627558647</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.152110782447501</v>
+        <v>4.149449649135804</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.685027351867409</v>
+        <v>4.682479291285952</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.441095890410959</v>
+        <v>4.438356164383562</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002408413581418318</v>
+        <v>0.002409958150012177</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>231.4</v>
+        <v>229.6</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2317,22 +2317,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.196009907692481</v>
+        <v>-0.1961782692634519</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.08727452463267071</v>
+        <v>0.09579845383275276</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.088471028386639</v>
+        <v>3.08578811286689</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.841429214037287</v>
+        <v>3.83889610702532</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.194520547945205</v>
+        <v>3.191780821917808</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003237848083432992</v>
+        <v>0.003240663206362985</v>
       </c>
     </row>
     <row r="15">
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1669925389389275</v>
+        <v>-0.167261765392901</v>
       </c>
       <c r="AZ15" s="12" t="n">
         <v>0.1460611979166668</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.918183514905389</v>
+        <v>1.915459628671883</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.302720689274541</v>
+        <v>2.30019416554787</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>1.956164383561644</v>
+        <v>1.953424657534247</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005213265530797368</v>
+        <v>0.005220679073739432</v>
       </c>
     </row>
     <row r="16">
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17010</v>
+        <v>17050</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.05094638153717832</v>
+        <v>-0.05106037476576621</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2574072663139331</v>
+        <v>0.2544573372434018</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.692444535359058</v>
+        <v>1.689707465280812</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.783297068189154</v>
+        <v>1.780626944378815</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.69041095890411</v>
+        <v>1.687671232876712</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005908613127979682</v>
+        <v>0.005918184186005301</v>
       </c>
     </row>
     <row r="17">
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.07328507964511669</v>
+        <v>0.07330456621413474</v>
       </c>
       <c r="AZ17" s="12" t="n">
         <v>0.9505383580080755</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.92948920557431</v>
+        <v>2.926738527547379</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.729460477120347</v>
+        <v>2.726848109731666</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.194520547945205</v>
+        <v>3.191780821917808</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003413564378722316</v>
+        <v>0.0034167725971681</v>
       </c>
     </row>
     <row r="18">
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1232531436916476</v>
+        <v>0.1233662412943334</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>2.91473354231975</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.664295980790226</v>
+        <v>1.661551402185147</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.481674892375911</v>
+        <v>1.479082547710105</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.69041095890411</v>
+        <v>1.687671232876712</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.00600854662597448</v>
+        <v>0.006018471644541813</v>
       </c>
     </row>
     <row r="19">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>155.5</v>
+        <v>153.2</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.01309066123191961</v>
+        <v>0.01306534196919224</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5030868167202571</v>
+        <v>0.5256527415143604</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.134713583348776</v>
+        <v>3.131986739476984</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.0942083500572</v>
+        <v>3.091594006551484</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.356164383561644</v>
+        <v>3.353424657534247</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003190084112666243</v>
+        <v>0.003192861538637906</v>
       </c>
     </row>
     <row r="20">
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27180</v>
+        <v>27130</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5809393001516904</v>
+        <v>-0.5816760358072484</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.01556572052980121</v>
+        <v>0.01743738606708445</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.369536624660258</v>
+        <v>1.366816515389776</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.268110383903808</v>
+        <v>3.267363652061747</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.353424657534247</v>
+        <v>1.350684931506849</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.007301739741703301</v>
+        <v>0.007316270975221784</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>487.7</v>
+        <v>484.8</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3124,22 +3124,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03422495721330954</v>
+        <v>0.03421634093715722</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.3793275087143735</v>
+        <v>0.3875784364686468</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.7178082191780824</v>
+        <v>0.7150684931506849</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.6940542424272923</v>
+        <v>0.6914109406768066</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.6904109589041096</v>
+        <v>0.6876712328767123</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01393129770992366</v>
+        <v>0.01398467432950192</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.06055359393852228</v>
+        <v>0.06053848745559016</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1085781990521326</v>
+        <v>0.08795348837209294</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.904982540568818</v>
+        <v>1.902243678737477</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.796215251597408</v>
+        <v>1.793658317201932</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>1.956164383561644</v>
+        <v>1.953424657534247</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005249391942990748</v>
+        <v>0.005256950048921715</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10110</v>
+        <v>10030</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02981589737046682</v>
+        <v>0.02983171833529976</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5700666475766567</v>
+        <v>0.5825896118644067</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.256370745706033</v>
+        <v>4.253628586577793</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.133137540966551</v>
+        <v>4.130411319485954</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.282191780821917</v>
+        <v>4.279452054794521</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002349419399164964</v>
+        <v>0.002350933984117636</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.2286193940823452</v>
+        <v>0.2287686253086942</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.3243981149350648</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.806490825893092</v>
+        <v>2.803649380583854</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.284263816288898</v>
+        <v>2.281673964355588</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.194520547945205</v>
+        <v>3.191780821917808</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003563168604628438</v>
+        <v>0.003566779808221783</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>42.3</v>
+        <v>42</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>30</v>
+        <v>30.5</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.3963440426513406</v>
+        <v>0.4000123706541471</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.4099999999999999</v>
+        <v>0.3770491803278688</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.721792369367749</v>
+        <v>2.716429501697643</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>1.949227615996186</v>
+        <v>1.940289642175381</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.194520547945205</v>
+        <v>3.191780821917808</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003674049539025977</v>
+        <v>0.003681302972799575</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3699,22 +3699,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>91.82521489971346</v>
+        <v>92.93165571940203</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.1761052631578948</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.2191780821917808</v>
+        <v>0.2164383561643836</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.002361191217586477</v>
+        <v>0.002304211019242975</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.1917808219178082</v>
+        <v>0.189041095890411</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.04562500000000001</v>
+        <v>0.04620253164556962</v>
       </c>
     </row>
     <row r="27">
@@ -3808,22 +3808,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05472198575158485</v>
+        <v>0.05507692614886499</v>
       </c>
       <c r="AZ27" s="12" t="n">
         <v>0.6529216228775694</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.2136986301369863</v>
+        <v>0.2109589041095891</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.2026113355214708</v>
+        <v>0.1999464672965695</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.1917808219178082</v>
+        <v>0.189041095890411</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.0467948717948718</v>
+        <v>0.0474025974025974</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>11090</v>
+        <v>11030</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3938,15 +3938,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-3.582830319099763</v>
+        <v>-3.628210392034766</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.1453311606853021</v>
+        <v>0.1515614299184045</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.1917808219178082</v>
+        <v>0.189041095890411</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>122.8</v>
+        <v>126.6</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>13780</v>
+        <v>13850</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.02930717907923597</v>
+        <v>-0.04059869433718793</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.02570972423802598</v>
+        <v>0.0521054151624547</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.593198184264088</v>
+        <v>2.592676835400779</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>2.671492081093455</v>
+        <v>2.70239035542025</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.690410958904109</v>
+        <v>2.687671232876713</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.00385624209544858</v>
+        <v>0.003857017528547552</v>
       </c>
     </row>
     <row r="30">
@@ -4189,22 +4189,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.06060749960502867</v>
+        <v>0.06061195960869967</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.8323160403963414</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.562880742386016</v>
+        <v>2.560140023038081</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.416427135712726</v>
+        <v>2.41383288189831</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.690410958904109</v>
+        <v>2.687671232876713</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003901859276795728</v>
+        <v>0.003906036353485519</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.07251163533137636</v>
+        <v>0.07252307095614709</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>-0.4146719754498716</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.110041424836782</v>
+        <v>2.107298849495352</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.967383248187175</v>
+        <v>1.964805146444737</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.263013698630137</v>
+        <v>2.26027397260274</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004739243449105995</v>
+        <v>0.004745411407781465</v>
       </c>
     </row>
     <row r="32">
@@ -4412,22 +4412,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2617877696071202</v>
+        <v>-0.2622114450693513</v>
       </c>
       <c r="AZ32" s="12" t="n">
         <v>0.1738466433343939</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.561432210747606</v>
+        <v>1.558707892810305</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.115153537779515</v>
+        <v>2.11267562012645</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.564383561643836</v>
+        <v>1.561643835616438</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.006404376655719209</v>
+        <v>0.006415570259267944</v>
       </c>
     </row>
     <row r="33">
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.08056939306307402</v>
+        <v>-0.08068801371640044</v>
       </c>
       <c r="AZ33" s="12" t="n">
         <v>0.05068425391591092</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.593199179490269</v>
+        <v>2.5904839392754</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.820440346367722</v>
+        <v>2.817850716542555</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.690410958904109</v>
+        <v>2.687671232876713</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003856240615487796</v>
+        <v>0.003860282570521228</v>
       </c>
     </row>
     <row r="34">
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03339977437903058</v>
+        <v>0.03338081943516876</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.3664429530201341</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.593011891891686</v>
+        <v>1.590272914036867</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.541525294844317</v>
+        <v>1.538903068576488</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.610958904109589</v>
+        <v>1.608219178082192</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.006277417043086288</v>
+        <v>0.006288228839045782</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>69.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1728616234434923</v>
+        <v>0.1795543002616211</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7744878121728724</v>
+        <v>0.7439808583819347</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.908029887516021</v>
+        <v>2.904305474339486</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.479431357791483</v>
+        <v>2.462205829519947</v>
       </c>
       <c r="BC2" s="8" t="n">
         <v>3.191780821917808</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003438754203637774</v>
+        <v>0.003443163981321303</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106.8</v>
+        <v>106.7</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8450</v>
+        <v>8594</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>0.008315434816349783</v>
+        <v>0.008874648165272126</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2338410622485207</v>
+        <v>0.2120310500349081</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.667766026468609</v>
+        <v>1.66774241383396</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.654012195868417</v>
+        <v>1.653071981605343</v>
       </c>
       <c r="BC3" s="8" t="n">
         <v>1.687671232876712</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005996044913550842</v>
+        <v>0.005996129808206459</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>108.8</v>
+        <v>109.2</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>81.09999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02589512527737425</v>
+        <v>0.02503303531093581</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.5025400739827375</v>
+        <v>0.4951589242053793</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.312376714917245</v>
+        <v>4.313258501321299</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.203525885505397</v>
+        <v>4.207921454953795</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.687671232876713</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.00231890687226102</v>
+        <v>0.002318432803630169</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6587</v>
+        <v>6573</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.03494740150983618</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.492409291027782</v>
+        <v>1.497717937015062</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2164383561643835</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>275</v>
+        <v>279.8</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21220</v>
+        <v>21720</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1136157075461084</v>
+        <v>-0.1159810181842663</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.03675777568331773</v>
+        <v>0.03057090239410676</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.463121963382302</v>
+        <v>6.467192972495396</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.291557418610849</v>
+        <v>7.315672067597558</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.863013698630137</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001547239872101496</v>
+        <v>0.001546265905862007</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21220</v>
+        <v>21720</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.05682724231700709</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2803016022620171</v>
+        <v>0.2508287292817679</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.877959322358917</v>
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>97</v>
+        <v>96.7</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1808</v>
+        <v>1869</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,16 +1617,16 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04121586810922209</v>
+        <v>0.04521963824289405</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.522278418141592</v>
+        <v>3.36115137399679</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.8000000000000002</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.7683325086590798</v>
+        <v>0.765389369592089</v>
       </c>
       <c r="BC8" s="8" t="n">
         <v>0.7726027397260274</v>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>86.3</v>
+        <v>87.2</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>167</v>
+        <v>165.1</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1452845085420704</v>
+        <v>0.1379326271525005</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>3.924784431137724</v>
+        <v>4.033410054512417</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.580082657392226</v>
+        <v>1.580372099518032</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.379642041437937</v>
+        <v>1.388809901226461</v>
       </c>
       <c r="BC9" s="8" t="n">
         <v>1.608219178082192</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006328782835009424</v>
+        <v>0.006327623730544035</v>
       </c>
     </row>
     <row r="10">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>107.9</v>
+        <v>107.7</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>10610</v>
+        <v>10860</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>0.001204425956847222</v>
+        <v>0.001658410375181289</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.6271442035815269</v>
+        <v>0.5867403314917128</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.034002290183384</v>
+        <v>4.0337690066424</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.029149477968102</v>
+        <v>4.027090438078098</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.197260273972603</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002478927695290278</v>
+        <v>0.002479071058241813</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103.4</v>
+        <v>104.4</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1083</v>
+        <v>1107</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.0414128150373357</v>
+        <v>0.03756999826410752</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4950494293628811</v>
+        <v>0.4767818536585366</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.564396045055456</v>
+        <v>2.565243078137446</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.462420289079619</v>
+        <v>2.472356643338947</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.687671232876713</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003899553666556893</v>
+        <v>0.003898266049414986</v>
       </c>
     </row>
     <row r="12">
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>200.3</v>
+        <v>201.2</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2211,7 +2211,7 @@
         <v>-0.1138349171435974</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.02945581627558647</v>
+        <v>0.0248508946322068</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.149449649135804</v>
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>229.6</v>
+        <v>235.8</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1961782692634519</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.09579845383275276</v>
+        <v>0.06698611111111097</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.08578811286689</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>76.8</v>
+        <v>77</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2429,7 +2429,7 @@
         <v>-0.167261765392901</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1460611979166668</v>
+        <v>0.1430844155844158</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.915459628671883</v>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>114</v>
+        <v>113.6</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17050</v>
+        <v>17490</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.05106037476576621</v>
+        <v>-0.04909672466100134</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2544573372434018</v>
+        <v>0.2186077895940537</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.689707465280812</v>
+        <v>1.689661715853906</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.780626944378815</v>
+        <v>1.776901772950081</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.687671232876712</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005918184186005301</v>
+        <v>0.005918344427272705</v>
       </c>
     </row>
     <row r="17">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>93.5</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.07330456621413474</v>
+        <v>0.07557310398568072</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9505383580080755</v>
+        <v>0.9380215343203231</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.926738527547379</v>
+        <v>2.925462119007555</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.726848109731666</v>
+        <v>2.719910072283197</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.191780821917808</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.0034167725971681</v>
+        <v>0.003418263369409971</v>
       </c>
     </row>
     <row r="18">
@@ -2781,7 +2781,7 @@
         <v>4.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>95.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AK18" s="10" t="n">
         <v>46924</v>
@@ -2798,7 +2798,7 @@
         <v>0.1233662412943334</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>2.91473354231975</v>
+        <v>2.947734457323499</v>
       </c>
       <c r="BA18" s="8" t="n">
         <v>1.661551402185147</v>
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>153.2</v>
+        <v>160.5</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.01306534196919224</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5256527415143604</v>
+        <v>0.4562616822429906</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.131986739476984</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27130</v>
+        <v>27810</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5816760358072484</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.01743738606708445</v>
+        <v>-0.007440622653721696</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.366816515389776</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>484.8</v>
+        <v>479.6</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03421634093715722</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.3875784364686468</v>
+        <v>0.4026230733944951</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7150684931506849</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101.7</v>
+        <v>102.9</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>215</v>
+        <v>223.5</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.06053848745559016</v>
+        <v>0.05403393851308523</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.08795348837209294</v>
+        <v>0.05892617449664428</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.902243678737477</v>
+        <v>1.902615932720056</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.793658317201932</v>
+        <v>1.805080332995783</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>1.953424657534247</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005256950048921715</v>
+        <v>0.005255921506819086</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10030</v>
+        <v>10230</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.02983171833529976</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5825896118644067</v>
+        <v>0.5516494434995112</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.253628586577793</v>
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>30.8</v>
+        <v>30.6</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3480,7 +3480,7 @@
         <v>0.2287686253086942</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.3243981149350648</v>
+        <v>0.3330543117647058</v>
       </c>
       <c r="BA24" s="8" t="n">
         <v>2.803649380583854</v>
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>42</v>
+        <v>38.1</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>30.5</v>
+        <v>29.7</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.4000123706541471</v>
+        <v>0.4468073797994214</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.3770491803278688</v>
+        <v>0.2828282828282829</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.716429501697643</v>
+        <v>2.682537068902471</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>1.940289642175381</v>
+        <v>1.854107952693997</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.191780821917808</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003681302972799575</v>
+        <v>0.003727814282950947</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>11030</v>
+        <v>11210</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-3.628210392034766</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.1515614299184045</v>
+        <v>0.1330707022301516</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>126.6</v>
+        <v>128</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>13850</v>
+        <v>14350</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.04059869433718793</v>
+        <v>-0.04461425494675601</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.0521054151624547</v>
+        <v>0.02667595818815327</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.592676835400779</v>
+        <v>2.593462247237738</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>2.70239035542025</v>
+        <v>2.71457080102572</v>
       </c>
       <c r="BC29" s="8" t="n">
         <v>2.687671232876713</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003857017528547552</v>
+        <v>0.003855849457863081</v>
       </c>
     </row>
     <row r="30">
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>62860</v>
+        <v>63960</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2622114450693513</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1738466433343939</v>
+        <v>0.1536585365853658</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.558707892810305</v>
@@ -4616,7 +4616,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1341</v>
+        <v>1595</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4633,7 +4633,7 @@
         <v>0.03338081943516876</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.3664429530201341</v>
+        <v>0.1488401253918494</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.590272914036867</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>668.7</v>
+        <v>648.9</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.1795543002616211</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7439808583819347</v>
+        <v>0.797195253505933</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>2.904305474339486</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106.7</v>
+        <v>108.4</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8594</v>
+        <v>8857</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>0.008874648165272126</v>
+        <v>-0.0005199056856515907</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2120310500349081</v>
+        <v>0.1947782644236198</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.66774241383396</v>
+        <v>1.668139251324108</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.653071981605343</v>
+        <v>1.669006977541123</v>
       </c>
       <c r="BC3" s="8" t="n">
         <v>1.687671232876712</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005996129808206459</v>
+        <v>0.005994703375070377</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>109.2</v>
+        <v>109</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>81.8</v>
+        <v>81.5</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02503303531093581</v>
+        <v>0.02546357695769961</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.4951589242053793</v>
+        <v>0.497914110429448</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.313258501321299</v>
+        <v>4.312818271306725</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.207921454953795</v>
+        <v>4.205725457457792</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.687671232876713</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002318432803630169</v>
+        <v>0.00231866945716916</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6573</v>
+        <v>6555</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.03494740150983618</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.497717937015062</v>
+        <v>1.504576659038902</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2164383561643835</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>279.8</v>
+        <v>289.5</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21720</v>
+        <v>21770</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1159810181842663</v>
+        <v>-0.1206169771659352</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.03057090239410676</v>
+        <v>0.06384933394579706</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.467192972495396</v>
+        <v>6.475081543724746</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.315672067597558</v>
+        <v>7.363209631744916</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.863013698630137</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001546265905862007</v>
+        <v>0.001544382095031898</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21720</v>
+        <v>21770</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.05682724231700709</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2508287292817679</v>
+        <v>0.247955902618282</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.877959322358917</v>
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>96.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1869</v>
+        <v>1858</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,16 +1617,16 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04521963824289405</v>
+        <v>0.04254770500257861</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.36115137399679</v>
+        <v>3.396044255113025</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.765389369592089</v>
+        <v>0.7673509769972792</v>
       </c>
       <c r="BC8" s="8" t="n">
         <v>0.7726027397260274</v>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>87.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>165.1</v>
+        <v>165</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1379326271525005</v>
+        <v>0.1444615121234821</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>4.033410054512417</v>
+        <v>3.990254545454546</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.580372099518032</v>
+        <v>1.580115049859818</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.388809901226461</v>
+        <v>1.380662462757709</v>
       </c>
       <c r="BC9" s="8" t="n">
         <v>1.608219178082192</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006327623730544035</v>
+        <v>0.006328653094524453</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>10860</v>
+        <v>10900</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>0.001658410375181289</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.5867403314917128</v>
+        <v>0.5809174311926606</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.0337690066424</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1107</v>
+        <v>1112</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03756999826410752</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4767818536585366</v>
+        <v>0.4701416474820144</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.565243078137446</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>201.2</v>
+        <v>202.3</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2211,7 +2211,7 @@
         <v>-0.1138349171435974</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.0248508946322068</v>
+        <v>0.01927829955511595</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.149449649135804</v>
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>235.8</v>
+        <v>234.2</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1961782692634519</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.06698611111111097</v>
+        <v>0.07427551238257912</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.08578811286689</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>77</v>
+        <v>77.2</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2429,7 +2429,7 @@
         <v>-0.167261765392901</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1430844155844158</v>
+        <v>0.1401230569948189</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.915459628671883</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17490</v>
+        <v>17570</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2538,7 +2538,7 @@
         <v>-0.04909672466100134</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2186077895940537</v>
+        <v>0.2130592054638587</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.689661715853906</v>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>92.90000000000001</v>
+        <v>93</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.07557310398568072</v>
+        <v>0.07519363740498779</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9380215343203231</v>
+        <v>0.9401076716016152</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.925462119007555</v>
+        <v>2.925675825448741</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.719910072283197</v>
+        <v>2.721068767212897</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.191780821917808</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003418263369409971</v>
+        <v>0.003418013681835785</v>
       </c>
     </row>
     <row r="18">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>160.5</v>
+        <v>159.1</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.01306534196919224</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4562616822429906</v>
+        <v>0.4690760527969831</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.131986739476984</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27810</v>
+        <v>27870</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5816760358072484</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.007440622653721696</v>
+        <v>-0.009577456620021518</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.366816515389776</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>479.6</v>
+        <v>479</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03421634093715722</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.4026230733944951</v>
+        <v>0.4043800125260959</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7150684931506849</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>223.5</v>
+        <v>222.1</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3262,7 +3262,7 @@
         <v>0.05403393851308523</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.05892617449664428</v>
+        <v>0.06560108059432679</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.902615932720056</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10230</v>
+        <v>10250</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.02983171833529976</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5516494434995112</v>
+        <v>0.5486218348292682</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.253628586577793</v>
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>38.1</v>
+        <v>37</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.4468073797994214</v>
+        <v>0.4612146308359823</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.2828282828282829</v>
+        <v>0.2457912457912459</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.682537068902471</v>
+        <v>2.671948099802084</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>1.854107952693997</v>
+        <v>1.828580171191841</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.191780821917808</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003727814282950947</v>
+        <v>0.003742587665060081</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1119</v>
+        <v>1110</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.05507692614886499</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.6529216228775694</v>
+        <v>0.6663236900900902</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2109589041095891</v>
@@ -3846,7 +3846,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>485.1</v>
+        <v>470</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>11210</v>
+        <v>11900</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3938,10 +3938,10 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-3.628210392034766</v>
+        <v>-3.596601860755103</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.1330707022301516</v>
+        <v>0.03414692436974787</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14350</v>
+        <v>14230</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.04461425494675601</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.02667595818815327</v>
+        <v>0.03533380182712564</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.593462247237738</v>
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>524.8</v>
+        <v>518.3</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4192,7 +4192,7 @@
         <v>0.06061195960869967</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.8323160403963414</v>
+        <v>0.8552951147983794</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.560140023038081</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>63960</v>
+        <v>65010</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2622114450693513</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1536585365853658</v>
+        <v>0.1350253807106598</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.558707892810305</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>121.3</v>
+        <v>123.7</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4524,7 +4524,7 @@
         <v>-0.08068801371640044</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.05068425391591092</v>
+        <v>0.0302991107518189</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.5904839392754</v>
@@ -4616,7 +4616,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1595</v>
+        <v>1430</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4633,7 +4633,7 @@
         <v>0.03338081943516876</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.1488401253918494</v>
+        <v>0.2813986013986014</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.590272914036867</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>648.9</v>
+        <v>662.2</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.1795543002616211</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.797195253505933</v>
+        <v>0.7610993657505281</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>2.904305474339486</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>108.4</v>
+        <v>107</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8857</v>
+        <v>8830</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.0005199056856515907</v>
+        <v>0.007199508260911728</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1947782644236198</v>
+        <v>0.1829537078142693</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.668139251324108</v>
+        <v>1.667813149658653</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.669006977541123</v>
+        <v>1.655891544802673</v>
       </c>
       <c r="BC3" s="8" t="n">
         <v>1.687671232876712</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005994703375070377</v>
+        <v>0.005995875498431388</v>
       </c>
     </row>
     <row r="4">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6555</v>
+        <v>6569</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.03494740150983618</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.504576659038902</v>
+        <v>1.499238849139899</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2164383561643835</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>289.5</v>
+        <v>277.7</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21770</v>
+        <v>21530</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1206169771659352</v>
+        <v>-0.1149521787486078</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.06384933394579706</v>
+        <v>0.03186251741755686</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.475081543724746</v>
+        <v>6.465426052134834</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.363209631744916</v>
+        <v>7.305171423385009</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.863013698630137</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001544382095031898</v>
+        <v>0.001546688481062756</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>113.2</v>
+        <v>113</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21770</v>
+        <v>21530</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05682724231700709</v>
+        <v>-0.05593937842520476</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.247955902618282</v>
+        <v>0.259637714816535</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.877959322358917</v>
+        <v>1.87795280483581</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>1.991108529228866</v>
+        <v>1.989229040930848</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>1.86027397260274</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005324928969941124</v>
+        <v>0.005324947450356348</v>
       </c>
     </row>
     <row r="8">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>96.90000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1858</v>
+        <v>1851</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,16 +1617,16 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04254770500257861</v>
+        <v>0.04388229220443993</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.396044255113025</v>
+        <v>3.408115111831442</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.7673509769972792</v>
+        <v>0.7663699307616221</v>
       </c>
       <c r="BC8" s="8" t="n">
         <v>0.7726027397260274</v>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>86.40000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>165</v>
+        <v>162.5</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1444615121234821</v>
+        <v>0.1411848896615913</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>3.990254545454546</v>
+        <v>4.090486153846154</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.580115049859818</v>
+        <v>1.580244036892647</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.380662462757709</v>
+        <v>1.384739713265267</v>
       </c>
       <c r="BC9" s="8" t="n">
         <v>1.608219178082192</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006328653094524453</v>
+        <v>0.006328136519764221</v>
       </c>
     </row>
     <row r="10">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>107.7</v>
+        <v>107.2</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>10900</v>
+        <v>10950</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>0.001658410375181289</v>
+        <v>0.002798038511800585</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.5809174311926606</v>
+        <v>0.566392694063927</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.0337690066424</v>
+        <v>4.033182471618067</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.027090438078098</v>
+        <v>4.021928959497667</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.197260273972603</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002479071058241813</v>
+        <v>0.002479431582967312</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>104.4</v>
+        <v>104.6</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1112</v>
+        <v>1103</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03756999826410752</v>
+        <v>0.03680763071136577</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4701416474820144</v>
+        <v>0.4849767071622844</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.565243078137446</v>
+        <v>2.565410925893056</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.472356643338947</v>
+        <v>2.474336463103476</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.687671232876713</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003898266049414986</v>
+        <v>0.003898010996627708</v>
       </c>
     </row>
     <row r="12">
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>206.2</v>
+        <v>206.1</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>202.3</v>
+        <v>202.5</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1138349171435974</v>
+        <v>-0.1137327704752841</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.01927829955511595</v>
+        <v>0.01777777777777767</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.149449649135804</v>
+        <v>4.14935634970681</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.682479291285952</v>
+        <v>4.681834340114337</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.438356164383562</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002409958150012177</v>
+        <v>0.002410012338589958</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>234.2</v>
+        <v>235.1</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1961782692634519</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.07427551238257912</v>
+        <v>0.07016301573798378</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.08578811286689</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>77.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2429,7 +2429,7 @@
         <v>-0.167261765392901</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1401230569948189</v>
+        <v>0.1342461340206187</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.915459628671883</v>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>113.6</v>
+        <v>115.5</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17570</v>
+        <v>17590</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.04909672466100134</v>
+        <v>-0.05832759400560176</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2130592054638587</v>
+        <v>0.231945719158613</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.689661715853906</v>
+        <v>1.68987681535372</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.776901772950081</v>
+        <v>1.79454851240886</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.687671232876712</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005918344427272705</v>
+        <v>0.005917591098441593</v>
       </c>
     </row>
     <row r="17">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>93</v>
+        <v>93.7</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>74.3</v>
+        <v>75.7</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.07519363740498779</v>
+        <v>0.07255276715439667</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9401076716016152</v>
+        <v>0.9185601056803172</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.925675825448741</v>
+        <v>2.927160908337233</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.721068767212897</v>
+        <v>2.729153285486663</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.191780821917808</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003418013681835785</v>
+        <v>0.003416279566838188</v>
       </c>
     </row>
     <row r="18">
@@ -2781,7 +2781,7 @@
         <v>4.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>94.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="AK18" s="10" t="n">
         <v>46924</v>
@@ -2798,7 +2798,7 @@
         <v>0.1233662412943334</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>2.947734457323499</v>
+        <v>2.922931937172775</v>
       </c>
       <c r="BA18" s="8" t="n">
         <v>1.661551402185147</v>
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>111.3</v>
+        <v>111</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>159.1</v>
+        <v>161.1</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.01306534196919224</v>
+        <v>0.0139161862685272</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4690760527969831</v>
+        <v>0.4469273743016762</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.131986739476984</v>
+        <v>3.131553643381977</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.091594006551484</v>
+        <v>3.088572493261895</v>
       </c>
       <c r="BC19" s="8" t="n">
         <v>3.353424657534247</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003192861538637906</v>
+        <v>0.003193303113658408</v>
       </c>
     </row>
     <row r="20">
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>343.8</v>
+        <v>348.3</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27870</v>
+        <v>27900</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5816760358072484</v>
+        <v>-0.5856172648477618</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.009577456620021518</v>
+        <v>0.002307279354838654</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.366816515389776</v>
+        <v>1.366921470094383</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.267363652061747</v>
+        <v>3.298693102144316</v>
       </c>
       <c r="BC20" s="8" t="n">
         <v>1.350684931506849</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.007316270975221784</v>
+        <v>0.007315709218693829</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>479</v>
+        <v>479.2</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03421634093715722</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.4043800125260959</v>
+        <v>0.4037938772954923</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7150684931506849</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102.9</v>
+        <v>103.3</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>222.1</v>
+        <v>221.6</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.05403393851308523</v>
+        <v>0.05189163367857701</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.06560108059432679</v>
+        <v>0.07215703971119125</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.902615932720056</v>
+        <v>1.902738601269293</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.805080332995783</v>
+        <v>1.808873215024264</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>1.953424657534247</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005255921506819086</v>
+        <v>0.005255582660345002</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10250</v>
+        <v>10200</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.02983171833529976</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5486218348292682</v>
+        <v>0.5562131183333334</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.253628586577793</v>
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>30.6</v>
+        <v>33.7</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3480,7 +3480,7 @@
         <v>0.2287686253086942</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.3330543117647058</v>
+        <v>0.2104291376854597</v>
       </c>
       <c r="BA24" s="8" t="n">
         <v>2.803649380583854</v>
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>29.7</v>
+        <v>29.3</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.4612146308359823</v>
+        <v>0.448093312066198</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.2457912457912459</v>
+        <v>0.2969283276450512</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.671948099802084</v>
+        <v>2.681594797594295</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>1.828580171191841</v>
+        <v>1.851810774381719</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.191780821917808</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003742587665060081</v>
+        <v>0.003729124179749742</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1110</v>
+        <v>1151</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.05507692614886499</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.6663236900900902</v>
+        <v>0.6069672423979149</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2109589041095891</v>
@@ -3846,7 +3846,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>11900</v>
+        <v>11830</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3938,10 +3938,10 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-3.596601860755103</v>
+        <v>-3.603041028801422</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.03414692436974787</v>
+        <v>0.04690613355874884</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>128</v>
+        <v>126.3</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14230</v>
+        <v>14250</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.04461425494675601</v>
+        <v>-0.03973013469482473</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.03533380182712564</v>
+        <v>0.02014947368421049</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.593462247237738</v>
+        <v>2.592506709652139</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>2.71457080102572</v>
+        <v>2.699768891350388</v>
       </c>
       <c r="BC29" s="8" t="n">
         <v>2.687671232876713</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003855849457863081</v>
+        <v>0.003857270634158471</v>
       </c>
     </row>
     <row r="30">
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>518.3</v>
+        <v>516.3</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4192,7 +4192,7 @@
         <v>0.06061195960869967</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.8552951147983794</v>
+        <v>0.8624820027116018</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.560140023038081</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>65010</v>
+        <v>64240</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2622114450693513</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1350253807106598</v>
+        <v>0.1486301369863015</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.558707892810305</v>
@@ -4450,7 +4450,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>143.2</v>
+        <v>140.1</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>123.7</v>
+        <v>122.4</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.08068801371640044</v>
+        <v>-0.07297159830771868</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.0302991107518189</v>
+        <v>0.01870098039215673</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.5904839392754</v>
+        <v>2.588887507024243</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.817850716542555</v>
+        <v>2.792673344525641</v>
       </c>
       <c r="BC33" s="8" t="n">
         <v>2.687671232876713</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003860282570521228</v>
+        <v>0.00386266300596983</v>
       </c>
     </row>
     <row r="34">
@@ -4616,7 +4616,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1430</v>
+        <v>1404</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4633,7 +4633,7 @@
         <v>0.03338081943516876</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2813986013986014</v>
+        <v>0.3051282051282049</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.590272914036867</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>662.2</v>
+        <v>665.9</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1795543002616211</v>
+        <v>0.1796716911745976</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7610993657505281</v>
+        <v>0.7513140111127794</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.904305474339486</v>
+        <v>2.901500224606841</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.462205829519947</v>
+        <v>2.459582819791005</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.191780821917808</v>
+        <v>3.189041095890411</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003443163981321303</v>
+        <v>0.003446492926380876</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8830</v>
+        <v>8846</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>0.007199508260911728</v>
+        <v>-0.003857956061794257</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1829537078142693</v>
+        <v>0.2028853583540582</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.667813149658653</v>
+        <v>1.665540608031541</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.655891544802673</v>
+        <v>1.671991076138997</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.687671232876712</v>
+        <v>1.684931506849315</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005995875498431388</v>
+        <v>0.006004056551835587</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>109</v>
+        <v>107.9</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>81.5</v>
+        <v>81.2</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02546357695769961</v>
+        <v>0.02784009195802691</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.497914110429448</v>
+        <v>0.4882758620689656</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.312818271306725</v>
+        <v>4.307643226527645</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.205725457457792</v>
+        <v>4.190966338277018</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.687671232876713</v>
+        <v>4.684931506849315</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.00231866945716916</v>
+        <v>0.002321455021719827</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6569</v>
+        <v>6613</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.03494740150983618</v>
+        <v>0.03524111980711326</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.499238849139899</v>
+        <v>1.482610010585211</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.2164383561643835</v>
+        <v>0.2136986301369863</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.2091298126345665</v>
+        <v>0.2064240166356633</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.189041095890411</v>
+        <v>0.1863013698630137</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.04620253164556963</v>
+        <v>0.0467948717948718</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>277.7</v>
+        <v>289.7</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21530</v>
+        <v>22000</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1149521787486078</v>
+        <v>-0.1207636218826573</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.03186251741755686</v>
+        <v>0.05345454545454542</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.465426052134834</v>
+        <v>6.472589400988722</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.305171423385009</v>
+        <v>7.361603275387784</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>6.863013698630137</v>
+        <v>6.86027397260274</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001546688481062756</v>
+        <v>0.00154497672886101</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21530</v>
+        <v>22000</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05593937842520476</v>
+        <v>-0.05602792061932163</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.259637714816535</v>
+        <v>0.2327272727272727</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.87795280483581</v>
+        <v>1.875213728764326</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>1.989229040930848</v>
+        <v>1.986513976127998</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>1.86027397260274</v>
+        <v>1.857534246575342</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005324947450356348</v>
+        <v>0.005332725463027359</v>
       </c>
     </row>
     <row r="8">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>96.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1851</v>
+        <v>1876</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04388229220443993</v>
+        <v>0.04268475415234409</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.408115111831442</v>
+        <v>3.353864726012794</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.8</v>
+        <v>0.7972602739726028</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.7663699307616221</v>
+        <v>0.7646225484717475</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.7726027397260274</v>
+        <v>0.7698630136986301</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.0125</v>
+        <v>0.01254295532646048</v>
       </c>
     </row>
     <row r="9">
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>162.5</v>
+        <v>167.4</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1411848896615913</v>
+        <v>0.1413451299449764</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>4.090486153846154</v>
+        <v>3.941481481481481</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.580244036892647</v>
+        <v>1.577498002057812</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.384739713265267</v>
+        <v>1.382139337760054</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.608219178082192</v>
+        <v>1.605479452054795</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006328136519764221</v>
+        <v>0.006339152244221683</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>10950</v>
+        <v>11090</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>0.002798038511800585</v>
+        <v>0.002787409235237855</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.566392694063927</v>
+        <v>0.5466185752930568</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.033182471618067</v>
+        <v>4.030448222319122</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.021928959497667</v>
+        <v>4.019244941849528</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.197260273972603</v>
+        <v>4.194520547945205</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002479431582967312</v>
+        <v>0.002481113625185338</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1103</v>
+        <v>1114</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03680763071136577</v>
+        <v>0.03679027819592591</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4849767071622844</v>
+        <v>0.4703135619389585</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.565410925893056</v>
+        <v>2.562675019561701</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.474336463103476</v>
+        <v>2.471739052203404</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.687671232876713</v>
+        <v>2.684931506849315</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003898010996627708</v>
+        <v>0.00390217250477211</v>
       </c>
     </row>
     <row r="12">
@@ -2111,7 +2111,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>-0.136986301369863</v>
+        <v>-0.1397260273972603</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>206.1</v>
+        <v>209.2</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>202.5</v>
+        <v>207</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1137327704752841</v>
+        <v>-0.1169579649452623</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.01777777777777767</v>
+        <v>0.01062801932367141</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.14935634970681</v>
+        <v>4.149553865245122</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.681834340114337</v>
+        <v>4.69915779828975</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.438356164383562</v>
+        <v>4.435616438356164</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002410012338589958</v>
+        <v>0.002409897623876075</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>235.1</v>
+        <v>241.7</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2317,22 +2317,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1961782692634519</v>
+        <v>-0.1963468909905799</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.07016301573798378</v>
+        <v>0.04094052544476634</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.08578811286689</v>
+        <v>3.083105270392902</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.83889610702532</v>
+        <v>3.836363271453184</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.191780821917808</v>
+        <v>3.189041095890411</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003240663206362985</v>
+        <v>0.003243483151882657</v>
       </c>
     </row>
     <row r="15">
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>161.5</v>
+        <v>161.6</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>77.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.167261765392901</v>
+        <v>-0.1678006127657781</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1342461340206187</v>
+        <v>0.1233673469387755</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.915459628671883</v>
+        <v>1.912751607029824</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.30019416554787</v>
+        <v>2.298429482610857</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>1.953424657534247</v>
+        <v>1.950684931506849</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005220679073739432</v>
+        <v>0.005228070369015811</v>
       </c>
     </row>
     <row r="16">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>115.5</v>
+        <v>116</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17590</v>
+        <v>17740</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.05832759400560176</v>
+        <v>-0.06084495472754142</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.231945719158613</v>
+        <v>0.2268170462232244</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.68987681535372</v>
+        <v>1.687195765784105</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.79454851240886</v>
+        <v>1.79650396840985</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.687671232876712</v>
+        <v>1.684931506849315</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005917591098441593</v>
+        <v>0.005926994485641456</v>
       </c>
     </row>
     <row r="17">
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>75.7</v>
+        <v>77</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.07255276715439667</v>
+        <v>0.07257168298979411</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9185601056803172</v>
+        <v>0.8861688311688314</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.927160908337233</v>
+        <v>2.924410558701584</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.729153285486663</v>
+        <v>2.726540897061339</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.191780821917808</v>
+        <v>3.189041095890411</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003416279566838188</v>
+        <v>0.0034194925094375</v>
       </c>
     </row>
     <row r="18">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>89.2</v>
+        <v>90.3</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2781,7 +2781,7 @@
         <v>4.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>95.5</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="AK18" s="10" t="n">
         <v>46924</v>
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1233662412943334</v>
+        <v>0.1153413361603937</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>2.922931937172775</v>
+        <v>3.149452954048139</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.661551402185147</v>
+        <v>1.65915611676491</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.479082547710105</v>
+        <v>1.487576998156116</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.687671232876712</v>
+        <v>1.684931506849315</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.006018471644541813</v>
+        <v>0.00602716037324951</v>
       </c>
     </row>
     <row r="19">
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>111</v>
+        <v>108.9</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>161.1</v>
+        <v>160.5</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.0139161862685272</v>
+        <v>0.01993912078422138</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4469273743016762</v>
+        <v>0.4248598130841124</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.131553643381977</v>
+        <v>3.125736580842355</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.088572493261895</v>
+        <v>3.064630542300413</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.353424657534247</v>
+        <v>3.350684931506849</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003193303113658408</v>
+        <v>0.003199245918958756</v>
       </c>
     </row>
     <row r="20">
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27900</v>
+        <v>27800</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5856172648477618</v>
+        <v>-0.5863564105927969</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.002307279354838654</v>
+        <v>0.005912701223021566</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.366921470094383</v>
+        <v>1.364201429957333</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.298693102144316</v>
+        <v>3.29801177847911</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.350684931506849</v>
+        <v>1.347945205479452</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.007315709218693829</v>
+        <v>0.007330295790932255</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>479.2</v>
+        <v>480.5</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3124,22 +3124,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03421634093715722</v>
+        <v>0.03420768574366763</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.4037938772954923</v>
+        <v>0.3999958917793962</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.7150684931506849</v>
+        <v>0.7123287671232877</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.6914109406768066</v>
+        <v>0.6887676208005296</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.6876712328767123</v>
+        <v>0.684931506849315</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01398467432950192</v>
+        <v>0.01403846153846154</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>221.6</v>
+        <v>233.5</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.05189163367857701</v>
+        <v>0.05186582312976027</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.07215703971119125</v>
+        <v>0.01751605995717331</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.902738601269293</v>
+        <v>1.900000353352153</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.808873215024264</v>
+        <v>1.806314371636129</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>1.953424657534247</v>
+        <v>1.950684931506849</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005255582660345002</v>
+        <v>0.005263156915922196</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10200</v>
+        <v>10240</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02983171833529976</v>
+        <v>0.02984756000173268</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5562131183333334</v>
+        <v>0.5501341608398438</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.253628586577793</v>
+        <v>4.25088642418149</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.130411319485954</v>
+        <v>4.127685095621665</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.279452054794521</v>
+        <v>4.276712328767124</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002350933984117636</v>
+        <v>0.002352450524933868</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>63.1</v>
+        <v>62.5</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>33.7</v>
+        <v>30.6</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.2287686253086942</v>
+        <v>0.2328483802649334</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.2104291376854597</v>
+        <v>0.3203786764705883</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.803649380583854</v>
+        <v>2.79812468940215</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.281673964355588</v>
+        <v>2.269642183251152</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.191780821917808</v>
+        <v>3.189041095890411</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003566779808221783</v>
+        <v>0.003573822152341828</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>38</v>
+        <v>40.9</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>29.3</v>
+        <v>29</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.448093312066198</v>
+        <v>0.4129207788096025</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.2969283276450512</v>
+        <v>0.4103448275862069</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.681594797594295</v>
+        <v>2.704419438622446</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>1.851810774381719</v>
+        <v>1.914063038198746</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.191780821917808</v>
+        <v>3.189041095890411</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003729124179749742</v>
+        <v>0.003697651280414445</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3699,22 +3699,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>92.93165571940203</v>
+        <v>94.06653163665185</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.1761052631578948</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.2164383561643836</v>
+        <v>0.2136986301369863</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.002304211019242975</v>
+        <v>0.002247884996517503</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.189041095890411</v>
+        <v>0.1863013698630137</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.04620253164556962</v>
+        <v>0.04679487179487181</v>
       </c>
     </row>
     <row r="27">
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1151</v>
+        <v>1160</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3808,22 +3808,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05507692614886499</v>
+        <v>0.05544126054872672</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.6069672423979149</v>
+        <v>0.5944993931034483</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.2109589041095891</v>
+        <v>0.2082191780821918</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.1999464672965695</v>
+        <v>0.1972816355255413</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.189041095890411</v>
+        <v>0.1863013698630137</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.0474025974025974</v>
+        <v>0.04802631578947368</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>11830</v>
+        <v>11930</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3938,15 +3938,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-3.603041028801422</v>
+        <v>-3.649263453879148</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.04690613355874884</v>
+        <v>0.03813072590108968</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.189041095890411</v>
+        <v>0.1863013698630137</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>126.3</v>
+        <v>132.2</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14250</v>
+        <v>14370</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.03973013469482473</v>
+        <v>-0.0563967063708844</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.02014947368421049</v>
+        <v>0.05888796102992333</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.592506709652139</v>
+        <v>2.593016391619835</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>2.699768891350388</v>
+        <v>2.747994214440526</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.687671232876713</v>
+        <v>2.684931506849315</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003857270634158471</v>
+        <v>0.003856512451027386</v>
       </c>
     </row>
     <row r="30">
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>516.3</v>
+        <v>509.8</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4189,22 +4189,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.06061195960869967</v>
+        <v>0.06061643857418632</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.8624820027116018</v>
+        <v>0.8862288309140838</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.560140023038081</v>
+        <v>2.557399299464866</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.41383288189831</v>
+        <v>2.411238602809931</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.687671232876713</v>
+        <v>2.684931506849315</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003906036353485519</v>
+        <v>0.003910222389633286</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>98.09999999999999</v>
+        <v>96</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.07252307095614709</v>
+        <v>0.08312680213483183</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>-0.4146719754498716</v>
+        <v>-0.4272019331619538</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.107298849495352</v>
+        <v>2.101910954292387</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.964805146444737</v>
+        <v>1.940595459506257</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.26027397260274</v>
+        <v>2.257534246575343</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004745411407781465</v>
+        <v>0.004757575471776598</v>
       </c>
     </row>
     <row r="32">
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>64240</v>
+        <v>64360</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4412,22 +4412,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2622114450693513</v>
+        <v>-0.2626363619912454</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1486301369863015</v>
+        <v>0.1464885021752642</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.558707892810305</v>
+        <v>1.555983620512458</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.11267562012645</v>
+        <v>2.110198469664684</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.561643835616438</v>
+        <v>1.558904109589041</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.006415570259267944</v>
+        <v>0.006426802871296634</v>
       </c>
     </row>
     <row r="33">
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>122.4</v>
+        <v>121.2</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.07297159830771868</v>
+        <v>-0.07308412988093427</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.01870098039215673</v>
+        <v>0.02878712871287115</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.588887507024243</v>
+        <v>2.586171114845258</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.792673344525641</v>
+        <v>2.790081816716607</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.687671232876713</v>
+        <v>2.684931506849315</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.00386266300596983</v>
+        <v>0.003866720165033761</v>
       </c>
     </row>
     <row r="34">
@@ -4616,7 +4616,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1404</v>
+        <v>1448</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03338081943516876</v>
+        <v>0.03336180867044046</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.3051282051282049</v>
+        <v>0.2654696132596683</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.590272914036867</v>
+        <v>1.587533938386534</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.538903068576488</v>
+        <v>1.536280831230942</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.608219178082192</v>
+        <v>1.605479452054795</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.006288228839045782</v>
+        <v>0.006299077933517029</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>665.9</v>
+        <v>642.4</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.1796716911745976</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7513140111127794</v>
+        <v>0.8153798256537981</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>2.901500224606841</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8846</v>
+        <v>8868</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.003857956061794257</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2028853583540582</v>
+        <v>0.1999012043301758</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.665540608031541</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>107.9</v>
+        <v>108.4</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>81.2</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02784009195802691</v>
+        <v>0.02675113192817394</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.4882758620689656</v>
+        <v>0.4914987714987715</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.307643226527645</v>
+        <v>4.308760250627574</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.190966338277018</v>
+        <v>4.196499148275585</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.684931506849315</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002321455021719827</v>
+        <v>0.002320853196355841</v>
       </c>
     </row>
     <row r="5">
@@ -1201,7 +1201,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>99.5</v>
+        <v>99.7</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6613</v>
+        <v>6610</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,16 +1272,16 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.03524111980711326</v>
+        <v>0.02587195953041485</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.482610010585211</v>
+        <v>1.488729198184569</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2136986301369863</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.2064240166356633</v>
+        <v>0.2083092613573386</v>
       </c>
       <c r="BC5" s="8" t="n">
         <v>0.1863013698630137</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>289.7</v>
+        <v>287</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>22000</v>
+        <v>21990</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1207636218826573</v>
+        <v>-0.1194926054054293</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.05345454545454542</v>
+        <v>0.04411095952705768</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.472589400988722</v>
+        <v>6.470439556102501</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.361603275387784</v>
+        <v>7.348535169408557</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.86027397260274</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.00154497672886101</v>
+        <v>0.001545490057251002</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>113</v>
+        <v>112.8</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22000</v>
+        <v>21990</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05602792061932163</v>
+        <v>-0.0551364427988317</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2327272727272727</v>
+        <v>0.2311050477489769</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.875213728764326</v>
+        <v>1.87520718479004</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>1.986513976127998</v>
+        <v>1.984632776339362</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>1.857534246575342</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005332725463027359</v>
+        <v>0.005332744072820765</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04268475415234409</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.353864726012794</v>
+        <v>3.360838348104645</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.7972602739726028</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>167.4</v>
+        <v>152.3</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1413451299449764</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>3.941481481481481</v>
+        <v>4.431411687458962</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.577498002057812</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>107.2</v>
+        <v>109.1</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11090</v>
+        <v>11280</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>0.002787409235237855</v>
+        <v>-0.001510650551418449</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.5466185752930568</v>
+        <v>0.5475177304964538</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.030448222319122</v>
+        <v>4.032653336982015</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.019244941849528</v>
+        <v>4.038754483669815</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.194520547945205</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002481113625185338</v>
+        <v>0.002479756915451569</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1114</v>
+        <v>1122</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03679027819592591</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4703135619389585</v>
+        <v>0.4598300427807485</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.562675019561701</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>207</v>
+        <v>206.8</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2211,7 +2211,7 @@
         <v>-0.1169579649452623</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.01062801932367141</v>
+        <v>0.01160541586073482</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.149553865245122</v>
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>241.7</v>
+        <v>240.9</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1963468909905799</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.04094052544476634</v>
+        <v>0.04439736405147365</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.083105270392902</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>78.40000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2429,7 +2429,7 @@
         <v>-0.1678006127657781</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1233673469387755</v>
+        <v>0.121936305732484</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.912751607029824</v>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>116</v>
+        <v>116.1</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17740</v>
+        <v>17770</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.06084495472754142</v>
+        <v>-0.06132150257298787</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2268170462232244</v>
+        <v>0.2258017017445133</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.687195765784105</v>
+        <v>1.687206874297654</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.79650396840985</v>
+        <v>1.797427850880162</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.684931506849315</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005926994485641456</v>
+        <v>0.005926955462508278</v>
       </c>
     </row>
     <row r="17">
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>77</v>
+        <v>75.3</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2668,7 +2668,7 @@
         <v>0.07257168298979411</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8861688311688314</v>
+        <v>0.9287516600265606</v>
       </c>
       <c r="BA17" s="8" t="n">
         <v>2.924410558701584</v>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>90.3</v>
+        <v>91</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2781,7 +2781,7 @@
         <v>4.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>91.40000000000001</v>
+        <v>85</v>
       </c>
       <c r="AK18" s="10" t="n">
         <v>46924</v>
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1153413361603937</v>
+        <v>0.1102441743568059</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>3.149452954048139</v>
+        <v>3.496470588235294</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.65915611676491</v>
+        <v>1.65937502420844</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.487576998156116</v>
+        <v>1.494603675961426</v>
       </c>
       <c r="BC18" s="8" t="n">
         <v>1.684931506849315</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.00602716037324951</v>
+        <v>0.006026365260481265</v>
       </c>
     </row>
     <row r="19">
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>108.9</v>
+        <v>111</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>160.5</v>
+        <v>161</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.01993912078422138</v>
+        <v>0.01389145096772747</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4248598130841124</v>
+        <v>0.4478260869565218</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.125736580842355</v>
+        <v>3.128826513802257</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.064630542300413</v>
+        <v>3.085958078466773</v>
       </c>
       <c r="BC19" s="8" t="n">
         <v>3.350684931506849</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003199245918958756</v>
+        <v>0.003196086441957326</v>
       </c>
     </row>
     <row r="20">
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>348.3</v>
+        <v>348.4</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27800</v>
+        <v>27900</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5863564105927969</v>
+        <v>-0.5864430092279312</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.005912701223021566</v>
+        <v>0.002595050609318861</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.364201429957333</v>
+        <v>1.364203736416055</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.29801177847911</v>
+        <v>3.298707957684926</v>
       </c>
       <c r="BC20" s="8" t="n">
         <v>1.347945205479452</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.007330295790932255</v>
+        <v>0.007330283397604036</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>480.5</v>
+        <v>480.4</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03420768574366763</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.3999958917793962</v>
+        <v>0.4002873147377184</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7123287671232877</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103.3</v>
+        <v>103</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>233.5</v>
+        <v>237.9</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.05186582312976027</v>
+        <v>0.05347332956662582</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.01751605995717331</v>
+        <v>-0.004203446826397728</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.900000353352153</v>
+        <v>1.899908304099122</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.806314371636129</v>
+        <v>1.803470719928619</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>1.950684931506849</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005263156915922196</v>
+        <v>0.005263411912261571</v>
       </c>
     </row>
     <row r="23">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>90.09999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10240</v>
+        <v>10280</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02984756000173268</v>
+        <v>0.02931259177412775</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5501341608398438</v>
+        <v>0.5475300409533075</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.25088642418149</v>
+        <v>4.250968652911403</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.127685095621665</v>
+        <v>4.129910278843878</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.276712328767124</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002352450524933868</v>
+        <v>0.002352405020241964</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>29</v>
+        <v>29.5</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3589,7 +3589,7 @@
         <v>0.4129207788096025</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.4103448275862069</v>
+        <v>0.3864406779661016</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>2.704419438622446</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>11930</v>
+        <v>12020</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-3.649263453879148</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.03813072590108968</v>
+        <v>0.03035770049916797</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14370</v>
+        <v>14460</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.0563967063708844</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.05888796102992333</v>
+        <v>0.05229737206085727</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.593016391619835</v>
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>509.8</v>
+        <v>516.3</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4192,7 +4192,7 @@
         <v>0.06061643857418632</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.8862288309140838</v>
+        <v>0.8624820027116018</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.557399299464866</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>64360</v>
+        <v>64580</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2626363619912454</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1464885021752642</v>
+        <v>0.1425828429854443</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.555983620512458</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>121.2</v>
+        <v>122.1</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4524,7 +4524,7 @@
         <v>-0.07308412988093427</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.02878712871287115</v>
+        <v>0.02120393120393116</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.586171114845258</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>642.4</v>
+        <v>656.2</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1796716911745976</v>
+        <v>0.1797893292661508</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.8153798256537981</v>
+        <v>0.7772020725388598</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.901500224606841</v>
+        <v>2.898694830114494</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.459582819791005</v>
+        <v>2.456959694590163</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.189041095890411</v>
+        <v>3.186301369863014</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003446492926380876</v>
+        <v>0.003449828486983231</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8868</v>
+        <v>8830</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.003857956061794257</v>
+        <v>-0.003936391566222364</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1999012043301758</v>
+        <v>0.2050649920724801</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.665540608031541</v>
+        <v>1.662804197582399</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.671991076138997</v>
+        <v>1.669375513273708</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.684931506849315</v>
+        <v>1.682191780821918</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.006004056551835587</v>
+        <v>0.006013937187877742</v>
       </c>
     </row>
     <row r="4">
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>81.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02675113192817394</v>
+        <v>0.02674099521868663</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.4914987714987715</v>
+        <v>0.4933333333333336</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.308760250627574</v>
+        <v>4.306030913655036</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.196499148275585</v>
+        <v>4.193882326416595</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.684931506849315</v>
+        <v>4.682191780821918</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002320853196355841</v>
+        <v>0.002322324247206071</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6610</v>
+        <v>6510</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.02587195953041485</v>
+        <v>0.02605226035312529</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.488729198184569</v>
+        <v>1.526958525345622</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.2136986301369863</v>
+        <v>0.210958904109589</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.2083092613573386</v>
+        <v>0.205602494396324</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.1863013698630137</v>
+        <v>0.1835616438356164</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.0467948717948718</v>
+        <v>0.0474025974025974</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>287</v>
+        <v>283.2</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21990</v>
+        <v>21410</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1194926054054293</v>
+        <v>-0.1177315792778932</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.04411095952705768</v>
+        <v>0.05819710415693602</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.470439556102501</v>
+        <v>6.464706338373369</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.348535169408557</v>
+        <v>7.327369071061418</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>6.86027397260274</v>
+        <v>6.857534246575343</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001545490057251002</v>
+        <v>0.001546860673414002</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21990</v>
+        <v>21410</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.0551364427988317</v>
+        <v>-0.05522403109376531</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2311050477489769</v>
+        <v>0.2644558617468473</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.87520718479004</v>
+        <v>1.872468101708693</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>1.984632776339362</v>
+        <v>1.98191757975856</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>1.857534246575342</v>
+        <v>1.854794520547945</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005332744072820765</v>
+        <v>0.005340544915491296</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1873</v>
+        <v>1849</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04268475415234409</v>
+        <v>0.04282274859857214</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.360838348104645</v>
+        <v>3.417441982693348</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.7972602739726028</v>
+        <v>0.7945205479452054</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.7646225484717475</v>
+        <v>0.761894146452928</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.7698630136986301</v>
+        <v>0.7671232876712328</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01254295532646048</v>
+        <v>0.01258620689655172</v>
       </c>
     </row>
     <row r="9">
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>152.3</v>
+        <v>158.4</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1413451299449764</v>
+        <v>0.1415059653290149</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>4.431411687458962</v>
+        <v>4.222247474747475</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.577498002057812</v>
+        <v>1.574751943877323</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.382139337760054</v>
+        <v>1.37953895267068</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.605479452054795</v>
+        <v>1.602739726027397</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006339152244221683</v>
+        <v>0.006350206481014527</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11280</v>
+        <v>11410</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.001510650551418449</v>
+        <v>-0.001523943562856673</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.5475177304964538</v>
+        <v>0.52988606485539</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.032653336982015</v>
+        <v>4.029920401684287</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.038754483669815</v>
+        <v>4.036071146326964</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.194520547945205</v>
+        <v>4.191780821917808</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002479756915451569</v>
+        <v>0.002481438590156904</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1122</v>
+        <v>1111</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03679027819592591</v>
+        <v>0.03677289701157765</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4598300427807485</v>
+        <v>0.4742838055805578</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.562675019561701</v>
+        <v>2.559939119507766</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.471739052203404</v>
+        <v>2.469141628688987</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.684931506849315</v>
+        <v>2.682191780821918</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.00390217250477211</v>
+        <v>0.003906342898468162</v>
       </c>
     </row>
     <row r="12">
@@ -2111,7 +2111,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>-0.1397260273972603</v>
+        <v>-0.1424657534246575</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>209.2</v>
+        <v>208.9</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>206.8</v>
+        <v>204.5</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1169579649452623</v>
+        <v>-0.1167443136679522</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.01160541586073482</v>
+        <v>0.02151589242053786</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.149553865245122</v>
+        <v>4.146620113034834</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.69915779828975</v>
+        <v>4.694699595147548</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.435616438356164</v>
+        <v>4.432876712328767</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002409897623876075</v>
+        <v>0.002411602637185201</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>240.9</v>
+        <v>240</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2317,22 +2317,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1963468909905799</v>
+        <v>-0.1965157734685486</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.04439736405147365</v>
+        <v>0.04831385416666678</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.083105270392902</v>
+        <v>3.080422501097496</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.836363271453184</v>
+        <v>3.833830708034337</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.189041095890411</v>
+        <v>3.186301369863014</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003243483151882657</v>
+        <v>0.003246307932251887</v>
       </c>
     </row>
     <row r="15">
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>161.6</v>
+        <v>159.7</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>78.5</v>
+        <v>77.7</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1678006127657781</v>
+        <v>-0.1629123247686792</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.121936305732484</v>
+        <v>0.1201608751608751</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.912751607029824</v>
+        <v>1.909724344372981</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.298429482610857</v>
+        <v>2.28139106676639</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>1.950684931506849</v>
+        <v>1.947945205479452</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005228070369015811</v>
+        <v>0.005236357817537954</v>
       </c>
     </row>
     <row r="16">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>116.1</v>
+        <v>116</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17770</v>
+        <v>17480</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.06132150257298787</v>
+        <v>-0.06097354973921788</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2258017017445133</v>
+        <v>0.2450648970251716</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.687206874297654</v>
+        <v>1.684459037331015</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.797427850880162</v>
+        <v>1.793835559012438</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.684931506849315</v>
+        <v>1.682191780821918</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005926955462508278</v>
+        <v>0.005936624030848955</v>
       </c>
     </row>
     <row r="17">
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>75.3</v>
+        <v>76.5</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.07257168298979411</v>
+        <v>0.07259064193172297</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9287516600265606</v>
+        <v>0.8984967320261439</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.924410558701584</v>
+        <v>2.92166018465868</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.726540897061339</v>
+        <v>2.723928468550504</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.189041095890411</v>
+        <v>3.186301369863014</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.0034194925094375</v>
+        <v>0.003422711529735358</v>
       </c>
     </row>
     <row r="18">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>91</v>
+        <v>90.5</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2781,7 +2781,7 @@
         <v>4.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>85</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="AK18" s="10" t="n">
         <v>46924</v>
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1102441743568059</v>
+        <v>0.1139771140623296</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>3.496470588235294</v>
+        <v>3.204646017699115</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.65937502420844</v>
+        <v>1.656474969996302</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.494603675961426</v>
+        <v>1.486991922083256</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.684931506849315</v>
+        <v>1.682191780821918</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.006026365260481265</v>
+        <v>0.006036915849095098</v>
       </c>
     </row>
     <row r="19">
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>111</v>
+        <v>109.8</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.01389145096772747</v>
+        <v>0.01730608569508603</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4478260869565218</v>
+        <v>0.4501886792452832</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.128826513802257</v>
+        <v>3.124344656268637</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.085958078466773</v>
+        <v>3.071194304449573</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.350684931506849</v>
+        <v>3.347945205479452</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003196086441957326</v>
+        <v>0.003200671212740935</v>
       </c>
     </row>
     <row r="20">
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>348.4</v>
+        <v>348.3</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27900</v>
+        <v>27470</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5864430092279312</v>
+        <v>-0.5870971939259892</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.002595050609318861</v>
+        <v>0.01799683633054228</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.364203736416055</v>
+        <v>1.361481434221098</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.298707957684926</v>
+        <v>3.297341200381815</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.347945205479452</v>
+        <v>1.345205479452055</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.007330283397604036</v>
+        <v>0.007344940407300512</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>480.4</v>
+        <v>486.8</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3124,22 +3124,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03420768574366763</v>
+        <v>0.03419899117402514</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.4002873147377184</v>
+        <v>0.3818776211996711</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.7123287671232877</v>
+        <v>0.7095890410958905</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.6887676208005296</v>
+        <v>0.6861242828039925</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.684931506849315</v>
+        <v>0.6821917808219178</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01403846153846154</v>
+        <v>0.01409266409266409</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103</v>
+        <v>104.4</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>237.9</v>
+        <v>238.6</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.05347332956662582</v>
+        <v>0.04599953430881787</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>-0.004203446826397728</v>
+        <v>0.006370494551550809</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.899908304099122</v>
+        <v>1.897596697279591</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.803470719928619</v>
+        <v>1.814146789781792</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>1.950684931506849</v>
+        <v>1.947945205479452</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005263411912261571</v>
+        <v>0.005269823674512121</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10280</v>
+        <v>10160</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02931259177412775</v>
+        <v>0.02932810880998959</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5475300409533075</v>
+        <v>0.5658079548228345</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.250968652911403</v>
+        <v>4.248226543151447</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.129910278843878</v>
+        <v>4.127184040531876</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.276712328767124</v>
+        <v>4.273972602739726</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002352405020241964</v>
+        <v>0.002353923430971677</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>62.5</v>
+        <v>62.3</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>30.6</v>
+        <v>30.2</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.2328483802649334</v>
+        <v>0.234324664562183</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.3203786764705883</v>
+        <v>0.3335859609271521</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.79812468940215</v>
+        <v>2.794375255570815</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.269642183251152</v>
+        <v>2.263889992477777</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.189041095890411</v>
+        <v>3.186301369863014</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003573822152341828</v>
+        <v>0.003578617431593765</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>40.9</v>
+        <v>41.7</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>29.5</v>
+        <v>29.1</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.4129207788096025</v>
+        <v>0.4040475246746727</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.3864406779661016</v>
+        <v>0.4329896907216495</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.704419438622446</v>
+        <v>2.708058783837429</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>1.914063038198746</v>
+        <v>1.928751510362803</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.189041095890411</v>
+        <v>3.186301369863014</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003697651280414445</v>
+        <v>0.003692682027319065</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3699,22 +3699,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>94.06653163665185</v>
+        <v>95.2309503997147</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.1761052631578948</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.2136986301369863</v>
+        <v>0.210958904109589</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.002247884996517503</v>
+        <v>0.002192214700502578</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.1863013698630137</v>
+        <v>0.1835616438356164</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.04679487179487181</v>
+        <v>0.0474025974025974</v>
       </c>
     </row>
     <row r="27">
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3808,22 +3808,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05544126054872672</v>
+        <v>0.0558153646992192</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5944993931034483</v>
+        <v>0.5917549879518074</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.2082191780821918</v>
+        <v>0.2054794520547945</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.1972816355255413</v>
+        <v>0.1946168420397363</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.1863013698630137</v>
+        <v>0.1835616438356164</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.04802631578947368</v>
+        <v>0.04866666666666667</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12020</v>
+        <v>11990</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3938,15 +3938,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-3.649263453879148</v>
+        <v>-3.696686459704526</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.03035770049916797</v>
+        <v>0.03293574311926606</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.1863013698630137</v>
+        <v>0.1835616438356164</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>132.2</v>
+        <v>133.5</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14460</v>
+        <v>14280</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.0563967063708844</v>
+        <v>-0.06001075655483196</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.05229737206085727</v>
+        <v>0.07603991596638648</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.593016391619835</v>
+        <v>2.590977057294787</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>2.747994214440526</v>
+        <v>2.756390113357638</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.684931506849315</v>
+        <v>2.682191780821918</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003856512451027386</v>
+        <v>0.003859547876676646</v>
       </c>
     </row>
     <row r="30">
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>516.3</v>
+        <v>506.4</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4189,22 +4189,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.06061643857418632</v>
+        <v>0.06062093655987117</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.8624820027116018</v>
+        <v>0.8988930845181673</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.557399299464866</v>
+        <v>2.554658571653338</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.411238602809931</v>
+        <v>2.408644298442179</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.684931506849315</v>
+        <v>2.682191780821918</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003910222389633286</v>
+        <v>0.003914417414115792</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>96</v>
+        <v>96.5</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.08312680213483183</v>
+        <v>0.08059495938947277</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>-0.4272019331619538</v>
+        <v>-0.4242186098971723</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.101910954292387</v>
+        <v>2.099804638537972</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.940595459506257</v>
+        <v>1.943193071828083</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.257534246575343</v>
+        <v>2.254794520547945</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004757575471776598</v>
+        <v>0.004762347799632772</v>
       </c>
     </row>
     <row r="32">
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>64580</v>
+        <v>64500</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4412,22 +4412,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2626363619912454</v>
+        <v>-0.2630625257568865</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1425828429854443</v>
+        <v>0.1439999999999999</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.555983620512458</v>
+        <v>1.553259394054216</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.110198469664684</v>
+        <v>2.107722090872802</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.558904109589041</v>
+        <v>1.556164383561644</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.006426802871296634</v>
+        <v>0.006438074695237253</v>
       </c>
     </row>
     <row r="33">
@@ -4450,7 +4450,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>140.1</v>
+        <v>135.3</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>122.1</v>
+        <v>122.3</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.07308412988093427</v>
+        <v>-0.06074466419735771</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.02120393120393116</v>
+        <v>-0.01539656582174964</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.586171114845258</v>
+        <v>2.580863562670343</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.790081816716607</v>
+        <v>2.747776312034322</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.684931506849315</v>
+        <v>2.682191780821918</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003866720165033761</v>
+        <v>0.003874672084429483</v>
       </c>
     </row>
     <row r="34">
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>101.8</v>
+        <v>100.9</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -4616,7 +4616,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1448</v>
+        <v>1499</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03336180867044046</v>
+        <v>0.03905483371928593</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2654696132596683</v>
+        <v>0.2116077384923283</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.587533938386534</v>
+        <v>1.584569554571448</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.536280831230942</v>
+        <v>1.525010522206511</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.605479452054795</v>
+        <v>1.602739726027397</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.006299077933517029</v>
+        <v>0.006310862133599769</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>656.2</v>
+        <v>650</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.1797893292661508</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7772020725388598</v>
+        <v>0.7941538461538458</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>2.898694830114494</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8830</v>
+        <v>8894</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.003936391566222364</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2050649920724801</v>
+        <v>0.1963935102316168</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.662804197582399</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>108.4</v>
+        <v>108.5</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>81.3</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02674099521868663</v>
+        <v>0.02652386000439076</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.4933333333333336</v>
+        <v>0.4983970406905058</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.306030913655036</v>
+        <v>4.306253414887631</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.193882326416595</v>
+        <v>4.194986188503414</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.682191780821918</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002322324247206071</v>
+        <v>0.002322204254266105</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6510</v>
+        <v>6549</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.02605226035312529</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.526958525345622</v>
+        <v>1.511910215300046</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.210958904109589</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>283.2</v>
+        <v>288.5</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21410</v>
+        <v>21890</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1177315792778932</v>
+        <v>-0.1202533440191309</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.05819710415693602</v>
+        <v>0.05436272270443121</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.464706338373369</v>
+        <v>6.46898764819477</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.327369071061418</v>
+        <v>7.353239258388775</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.857534246575343</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001546860673414002</v>
+        <v>0.001545836929027155</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21410</v>
+        <v>21890</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.05522403109376531</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2644558617468473</v>
+        <v>0.236729100045683</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>1.872468101708693</v>
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>96.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1849</v>
+        <v>1864</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,16 +1617,16 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04282274859857214</v>
+        <v>0.04148176449902709</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.417441982693348</v>
+        <v>3.38641597639485</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.7945205479452054</v>
+        <v>0.7945205479452057</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.761894146452928</v>
+        <v>0.7628751410039191</v>
       </c>
       <c r="BC8" s="8" t="n">
         <v>0.7671232876712328</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>158.4</v>
+        <v>153.2</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1415059653290149</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>4.222247474747475</v>
+        <v>4.399503916449087</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.574751943877323</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>109.1</v>
+        <v>108</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11410</v>
+        <v>11620</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.001523943562856673</v>
+        <v>0.0009543121953127331</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.52988606485539</v>
+        <v>0.4870912220309811</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.029920401684287</v>
+        <v>4.028651271160065</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.036071146326964</v>
+        <v>4.024810345563473</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.191780821917808</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002481438590156904</v>
+        <v>0.00248222030821756</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1111</v>
+        <v>1124</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03677289701157765</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4742838055805578</v>
+        <v>0.457232480427046</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.559939119507766</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>204.5</v>
+        <v>205.5</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2211,7 +2211,7 @@
         <v>-0.1167443136679522</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.02151589242053786</v>
+        <v>0.01654501216545023</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.146620113034834</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>159.7</v>
+        <v>161.4</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>77.7</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1629123247686792</v>
+        <v>-0.1675327820981264</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1201608751608751</v>
+        <v>0.1219770408163265</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.909724344372981</v>
+        <v>1.909996122273894</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.28139106676639</v>
+        <v>2.294379984220632</v>
       </c>
       <c r="BC15" s="8" t="n">
         <v>1.947945205479452</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005236357817537954</v>
+        <v>0.005235612723702692</v>
       </c>
     </row>
     <row r="16">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>116</v>
+        <v>116.1</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17480</v>
+        <v>17600</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.06097354973921788</v>
+        <v>-0.06145077828502106</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2450648970251716</v>
+        <v>0.2376418318181819</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.684459037331015</v>
+        <v>1.684470161780353</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.793835559012438</v>
+        <v>1.794759531846799</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.682191780821918</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005936624030848955</v>
+        <v>0.005936584824649422</v>
       </c>
     </row>
     <row r="17">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>93.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.07259064193172297</v>
+        <v>0.07183978777175219</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8984967320261439</v>
+        <v>0.9025490196078434</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.92166018465868</v>
+        <v>2.922081739828763</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.723928468550504</v>
+        <v>2.726229958213698</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.186301369863014</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003422711529735358</v>
+        <v>0.003422217751029104</v>
       </c>
     </row>
     <row r="18">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>90.5</v>
+        <v>91</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2781,7 +2781,7 @@
         <v>4.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>90.40000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="AK18" s="10" t="n">
         <v>46924</v>
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1139771140623296</v>
+        <v>0.1103369053691986</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>3.204646017699115</v>
+        <v>3.270391061452514</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.656474969996302</v>
+        <v>1.656631314767486</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.486991922083256</v>
+        <v>1.49200779219046</v>
       </c>
       <c r="BC18" s="8" t="n">
         <v>1.682191780821918</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.006036915849095098</v>
+        <v>0.006036346114466353</v>
       </c>
     </row>
     <row r="19">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>159</v>
+        <v>160.7</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.01730608569508603</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4501886792452832</v>
+        <v>0.4348475420037339</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.124344656268637</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27470</v>
+        <v>27590</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5870971939259892</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.01799683633054228</v>
+        <v>0.01356915889815147</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.361481434221098</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>486.8</v>
+        <v>489</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03419899117402514</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.3818776211996711</v>
+        <v>0.3756605848670755</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7095890410958905</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>104.4</v>
+        <v>105.2</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>238.6</v>
+        <v>243.2</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.04599953430881787</v>
+        <v>0.04181112892876739</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.006370494551550809</v>
+        <v>-0.005098684210526394</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.897596697279591</v>
+        <v>1.897836791837811</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.814146789781792</v>
+        <v>1.821670684003198</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>1.947945205479452</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005269823674512121</v>
+        <v>0.00526915699126914</v>
       </c>
     </row>
     <row r="23">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>90.3</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10160</v>
+        <v>10250</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02932810880998959</v>
+        <v>0.02906100274512852</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5658079548228345</v>
+        <v>0.5537781783414635</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.248226543151447</v>
+        <v>4.248267564785691</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.127184040531876</v>
+        <v>4.128295167587724</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.273972602739726</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002353923430971677</v>
+        <v>0.002353900701286093</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>62.3</v>
+        <v>62.8</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>30.2</v>
+        <v>29.8</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.234324664562183</v>
+        <v>0.2310285553332363</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.3335859609271521</v>
+        <v>0.3623330442953019</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.794375255570815</v>
+        <v>2.796628211116113</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.263889992477777</v>
+        <v>2.271781754371305</v>
       </c>
       <c r="BC24" s="8" t="n">
         <v>3.186301369863014</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003578617431593765</v>
+        <v>0.003575734507808986</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>29.1</v>
+        <v>29</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3589,7 +3589,7 @@
         <v>0.4040475246746727</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.4329896907216495</v>
+        <v>0.4379310344827587</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>2.708058783837429</v>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1162</v>
+        <v>1173</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.0558153646992192</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5917549879518074</v>
+        <v>0.5768280443307758</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2054794520547945</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>11990</v>
+        <v>11850</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-3.696686459704526</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.03293574311926606</v>
+        <v>0.04513920337552735</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>133.5</v>
+        <v>131.7</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14280</v>
+        <v>14450</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.06001075655483196</v>
+        <v>-0.05512569310630946</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.07603991596638648</v>
+        <v>0.04904290657439425</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.590977057294787</v>
+        <v>2.590029987856634</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>2.756390113357638</v>
+        <v>2.741137068666259</v>
       </c>
       <c r="BC29" s="8" t="n">
         <v>2.682191780821918</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003859547876676646</v>
+        <v>0.003860959157571549</v>
       </c>
     </row>
     <row r="30">
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>64500</v>
+        <v>64340</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2630625257568865</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1439999999999999</v>
+        <v>0.146844886540255</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.553259394054216</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>122.3</v>
+        <v>122</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4524,7 +4524,7 @@
         <v>-0.06074466419735771</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.01539656582174964</v>
+        <v>-0.01297540983606549</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.580863562670343</v>
@@ -4616,7 +4616,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1499</v>
+        <v>1457</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4633,7 +4633,7 @@
         <v>0.03905483371928593</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2116077384923283</v>
+        <v>0.2465339739190118</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.584569554571448</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>650</v>
+        <v>665.6</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.1797893292661508</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7941538461538458</v>
+        <v>0.752103365384615</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>2.898694830114494</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8894</v>
+        <v>8878</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.003936391566222364</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1963935102316168</v>
+        <v>0.1985496598332956</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.662804197582399</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>108.5</v>
+        <v>108.6</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>81.09999999999999</v>
+        <v>81</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02652386000439076</v>
+        <v>0.02630697942191858</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.4983970406905058</v>
+        <v>0.5016296296296296</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.306253414887631</v>
+        <v>4.30647558005676</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.194986188503414</v>
+        <v>4.196089149157341</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.682191780821918</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002322204254266105</v>
+        <v>0.002322084454933377</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6549</v>
+        <v>6416</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.02605226035312529</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.511910215300046</v>
+        <v>1.563980673316708</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.210958904109589</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>288.5</v>
+        <v>284</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21890</v>
+        <v>21480</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1202533440191309</v>
+        <v>-0.1181158007402503</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.05436272270443121</v>
+        <v>0.05772811918063314</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.46898764819477</v>
+        <v>6.46536093079389</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.353239258388775</v>
+        <v>7.331303742850694</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.857534246575343</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001545836929027155</v>
+        <v>0.001546704059841573</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>112.8</v>
+        <v>113</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21890</v>
+        <v>21480</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05522403109376531</v>
+        <v>-0.05611671337796642</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.236729100045683</v>
+        <v>0.2625698324022345</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.872468101708693</v>
+        <v>1.872474654532998</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>1.98191757975856</v>
+        <v>1.983798930516298</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>1.854794520547945</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005340544915491296</v>
+        <v>0.005340526225971285</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04148176449902709</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.38641597639485</v>
+        <v>3.367670608974359</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.7945205479452057</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>153.2</v>
+        <v>147</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1415059653290149</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>4.399503916449087</v>
+        <v>4.627238095238095</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.574751943877323</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11620</v>
+        <v>11510</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>0.0009543121953127331</v>
+        <v>0.003235061922746731</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4870912220309811</v>
+        <v>0.4874022589052998</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.028651271160065</v>
+        <v>4.027477743462235</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.024810345563473</v>
+        <v>4.014490617725607</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.191780821917808</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.00248222030821756</v>
+        <v>0.002482943578330855</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>104.6</v>
+        <v>104.1</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1124</v>
+        <v>1099</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03677289701157765</v>
+        <v>0.03868614478617853</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.457232480427046</v>
+        <v>0.4832573412192902</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.559939119507766</v>
+        <v>2.559517772593538</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.469141628688987</v>
+        <v>2.464187844847429</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.682191780821918</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003906342898468162</v>
+        <v>0.003906985959260242</v>
       </c>
     </row>
     <row r="12">
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>205.5</v>
+        <v>204.6</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2211,7 +2211,7 @@
         <v>-0.1167443136679522</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.01654501216545023</v>
+        <v>0.02101661779081132</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.146620113034834</v>
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>240</v>
+        <v>234.8</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1965157734685486</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.04831385416666678</v>
+        <v>0.07153034497444621</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.080422501097496</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>78.40000000000001</v>
+        <v>78</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2429,7 +2429,7 @@
         <v>-0.1675327820981264</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1219770408163265</v>
+        <v>0.1277307692307694</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.909996122273894</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17600</v>
+        <v>17690</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2538,7 +2538,7 @@
         <v>-0.06145077828502106</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2376418318181819</v>
+        <v>0.2313451803278688</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.684470161780353</v>
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>76.5</v>
+        <v>75.3</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2668,7 +2668,7 @@
         <v>0.07183978777175219</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9025490196078434</v>
+        <v>0.9328685258964147</v>
       </c>
       <c r="BA17" s="8" t="n">
         <v>2.922081739828763</v>
@@ -2781,7 +2781,7 @@
         <v>4.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>89.5</v>
+        <v>85.5</v>
       </c>
       <c r="AK18" s="10" t="n">
         <v>46924</v>
@@ -2798,7 +2798,7 @@
         <v>0.1103369053691986</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>3.270391061452514</v>
+        <v>3.470175438596491</v>
       </c>
       <c r="BA18" s="8" t="n">
         <v>1.656631314767486</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27590</v>
+        <v>27820</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5870971939259892</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.01356915889815147</v>
+        <v>0.005189543278216968</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.361481434221098</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03419899117402514</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.3756605848670755</v>
+        <v>0.3507992489959837</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7095890410958905</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>105.2</v>
+        <v>105.1</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>243.2</v>
+        <v>243</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.04181112892876739</v>
+        <v>0.04233199410019216</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>-0.005098684210526394</v>
+        <v>-0.005226337448559826</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.897836791837811</v>
+        <v>1.897806927254121</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.821670684003198</v>
+        <v>1.820731722710315</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>1.947945205479452</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.00526915699126914</v>
+        <v>0.005269239908650083</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10250</v>
+        <v>10310</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.02906100274512852</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5537781783414635</v>
+        <v>0.5447358223084384</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.248267564785691</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>62.8</v>
+        <v>65</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>29.8</v>
+        <v>29.1</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.2310285553332363</v>
+        <v>0.2169416842912569</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.3623330442953019</v>
+        <v>0.4439770103092784</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.796628211116113</v>
+        <v>2.806198262648878</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.271781754371305</v>
+        <v>2.30594308574712</v>
       </c>
       <c r="BC24" s="8" t="n">
         <v>3.186301369863014</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003575734507808986</v>
+        <v>0.003563540086636864</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>41.7</v>
+        <v>38.7</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.4040475246746727</v>
+        <v>0.4399140370523463</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.4379310344827587</v>
+        <v>0.3391003460207613</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.708058783837429</v>
+        <v>2.682099052577353</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>1.928751510362803</v>
+        <v>1.862679981971624</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.186301369863014</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003692682027319065</v>
+        <v>0.003728423076094277</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3685,7 +3685,7 @@
         <v>0.55865</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AK26" s="10" t="n">
         <v>46377</v>
@@ -3702,7 +3702,7 @@
         <v>95.2309503997147</v>
       </c>
       <c r="AZ26" s="12" t="n">
-        <v>0.1761052631578948</v>
+        <v>0.1173</v>
       </c>
       <c r="BA26" s="8" t="n">
         <v>0.210958904109589</v>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1173</v>
+        <v>1180</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.0558153646992192</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5768280443307758</v>
+        <v>0.5674739796610171</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2054794520547945</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>11850</v>
+        <v>11820</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-3.696686459704526</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.04513920337552735</v>
+        <v>0.04779184094754663</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14450</v>
+        <v>14240</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.05512569310630946</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.04904290657439425</v>
+        <v>0.06451334269662912</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.590029987856634</v>
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>506.4</v>
+        <v>516</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4192,7 +4192,7 @@
         <v>0.06062093655987117</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.8988930845181673</v>
+        <v>0.8635648410852712</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.554658571653338</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>64340</v>
+        <v>64210</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2630625257568865</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.146844886540255</v>
+        <v>0.1491667964491512</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.553259394054216</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>122</v>
+        <v>121.5</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4524,7 +4524,7 @@
         <v>-0.06074466419735771</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.01297540983606549</v>
+        <v>-0.008913580246913466</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.580863562670343</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>68.59999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>665.6</v>
+        <v>620.7</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1797893292661508</v>
+        <v>0.1820596867976914</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.752103365384615</v>
+        <v>0.8678910907040438</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.898694830114494</v>
+        <v>2.897426129708613</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.456959694590163</v>
+        <v>2.451167366647963</v>
       </c>
       <c r="BC2" s="8" t="n">
         <v>3.186301369863014</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003449828486983231</v>
+        <v>0.00345133906865321</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8878</v>
+        <v>8830</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.003936391566222364</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1985496598332956</v>
+        <v>0.2050649920724801</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.662804197582399</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>108.6</v>
+        <v>108.3</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>81</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02630697942191858</v>
+        <v>0.02695838560590007</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.5016296296296296</v>
+        <v>0.5086567164179103</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.30647558005676</v>
+        <v>4.305808075543283</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.196089149157341</v>
+        <v>4.19277756128636</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.682191780821918</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002322084454933377</v>
+        <v>0.002322444434251347</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6416</v>
+        <v>6524</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.02605226035312529</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.563980673316708</v>
+        <v>1.52153586756591</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.210958904109589</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>284</v>
+        <v>281.9</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21480</v>
+        <v>21300</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1181158007402503</v>
+        <v>-0.1171044595692895</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.05772811918063314</v>
+        <v>0.05877934272300478</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.46536093079389</v>
+        <v>6.463636157708626</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.331303742850694</v>
+        <v>7.320952323029534</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.857534246575343</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001546704059841573</v>
+        <v>0.001547116786280406</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>113</v>
+        <v>112.2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21480</v>
+        <v>21300</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05611671337796642</v>
+        <v>-0.05253134499587245</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2625698324022345</v>
+        <v>0.2642253521126761</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.872474654532998</v>
+        <v>1.872448336298782</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>1.983798930516298</v>
+        <v>1.976264150174577</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>1.854794520547945</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005340526225971285</v>
+        <v>0.005340601289842118</v>
       </c>
     </row>
     <row r="8">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>97</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1872</v>
+        <v>1843</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,16 +1617,16 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04148176449902709</v>
+        <v>0.04282274859857214</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.367670608974359</v>
+        <v>3.431823237113402</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.7945205479452057</v>
+        <v>0.7945205479452054</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.7628751410039191</v>
+        <v>0.761894146452928</v>
       </c>
       <c r="BC8" s="8" t="n">
         <v>0.7671232876712328</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>147</v>
+        <v>147.2</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1415059653290149</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>4.627238095238095</v>
+        <v>4.619592391304348</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.574751943877323</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>107</v>
+        <v>106.3</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11510</v>
+        <v>11530</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>0.003235061922746731</v>
+        <v>0.004847647701778578</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4874022589052998</v>
+        <v>0.4751084128360799</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.027477743462235</v>
+        <v>4.026644799200488</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.014490617725607</v>
+        <v>4.007219212195964</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.191780821917808</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002482943578330855</v>
+        <v>0.002483457195426215</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>104.1</v>
+        <v>103.8</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1099</v>
+        <v>1080</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03868614478617853</v>
+        <v>0.03984029814960437</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4832573412192902</v>
+        <v>0.5050019666666665</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.559517772593538</v>
+        <v>2.559263403175928</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.464187844847429</v>
+        <v>2.461208137182351</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.682191780821918</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003906985959260242</v>
+        <v>0.003907374281049172</v>
       </c>
     </row>
     <row r="12">
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>204.6</v>
+        <v>203.3</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2211,7 +2211,7 @@
         <v>-0.1167443136679522</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.02101661779081132</v>
+        <v>0.0275454992621742</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.146620113034834</v>
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>234.8</v>
+        <v>233.3</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.1965157734685486</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.07153034497444621</v>
+        <v>0.07841973853407636</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.080422501097496</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>161.4</v>
+        <v>160.4</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>78</v>
+        <v>77.8</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1675327820981264</v>
+        <v>-0.1648239652391604</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1277307692307694</v>
+        <v>0.1236246786632391</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.909996122273894</v>
+        <v>1.9098367692474</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.294379984220632</v>
+        <v>2.286747571479705</v>
       </c>
       <c r="BC15" s="8" t="n">
         <v>1.947945205479452</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005235612723702692</v>
+        <v>0.005236049572938451</v>
       </c>
     </row>
     <row r="16">
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17690</v>
+        <v>17750</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2538,7 +2538,7 @@
         <v>-0.06145077828502106</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2313451803278688</v>
+        <v>0.2271828867605634</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.684470161780353</v>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>93.90000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>75.3</v>
+        <v>76.5</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.07183978777175219</v>
+        <v>0.07259064193172297</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9328685258964147</v>
+        <v>0.8984967320261439</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.922081739828763</v>
+        <v>2.92166018465868</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.726229958213698</v>
+        <v>2.723928468550504</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.186301369863014</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003422217751029104</v>
+        <v>0.003422711529735358</v>
       </c>
     </row>
     <row r="18">
@@ -2781,7 +2781,7 @@
         <v>4.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>85.5</v>
+        <v>87.5</v>
       </c>
       <c r="AK18" s="10" t="n">
         <v>46924</v>
@@ -2798,7 +2798,7 @@
         <v>0.1103369053691986</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>3.470175438596491</v>
+        <v>3.367999999999999</v>
       </c>
       <c r="BA18" s="8" t="n">
         <v>1.656631314767486</v>
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>160.7</v>
+        <v>158.6</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.01730608569508603</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4348475420037339</v>
+        <v>0.453846153846154</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.124344656268637</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27820</v>
+        <v>27770</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3016,7 +3016,7 @@
         <v>-0.5870971939259892</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.005189543278216968</v>
+        <v>0.006999391213539763</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.361481434221098</v>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.03419899117402514</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.3507992489959837</v>
+        <v>0.3644990385395537</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.7095890410958905</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>105.1</v>
+        <v>107</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.04233199410019216</v>
+        <v>0.0325640479636857</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>-0.005226337448559826</v>
+        <v>0.004489795918367401</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.897806927254121</v>
+        <v>1.898367304425482</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.820731722710315</v>
+        <v>1.838498355786493</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>1.947945205479452</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005269239908650083</v>
+        <v>0.005267684486920923</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10310</v>
+        <v>10210</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3371,7 +3371,7 @@
         <v>0.02906100274512852</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5447358223084384</v>
+        <v>0.5598654581782567</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.248267564785691</v>
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>29.1</v>
+        <v>32.4</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3480,7 +3480,7 @@
         <v>0.2169416842912569</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.4439770103092784</v>
+        <v>0.2969052777777779</v>
       </c>
       <c r="BA24" s="8" t="n">
         <v>2.806198262648878</v>
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>38.7</v>
+        <v>38.9</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.4399140370523463</v>
+        <v>0.4374051666127835</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.3391003460207613</v>
+        <v>0.3506944444444444</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.682099052577353</v>
+        <v>2.68392983014807</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>1.862679981971624</v>
+        <v>1.867204802437643</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.186301369863014</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003728423076094277</v>
+        <v>0.003725879822815005</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3685,7 +3685,7 @@
         <v>0.55865</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AK26" s="10" t="n">
         <v>46377</v>
@@ -3702,7 +3702,7 @@
         <v>95.2309503997147</v>
       </c>
       <c r="AZ26" s="12" t="n">
-        <v>0.1173</v>
+        <v>0.1761052631578948</v>
       </c>
       <c r="BA26" s="8" t="n">
         <v>0.210958904109589</v>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1180</v>
+        <v>1172</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.0558153646992192</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5674739796610171</v>
+        <v>0.5781734607508533</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2054794520547945</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>11820</v>
+        <v>11900</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-3.696686459704526</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.04779184094754663</v>
+        <v>0.04074786218487403</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>131.7</v>
+        <v>133</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14240</v>
+        <v>14330</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.05512569310630946</v>
+        <v>-0.05866307088989309</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.06451334269662912</v>
+        <v>0.06826936496859726</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.590029987856634</v>
+        <v>2.590716056923219</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>2.741137068666259</v>
+        <v>2.752166601359572</v>
       </c>
       <c r="BC29" s="8" t="n">
         <v>2.682191780821918</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003860959157571549</v>
+        <v>0.003859936704864592</v>
       </c>
     </row>
     <row r="30">
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>516</v>
+        <v>527.6</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4192,7 +4192,7 @@
         <v>0.06062093655987117</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.8635648410852712</v>
+        <v>0.8225918460955266</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.554658571653338</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>64210</v>
+        <v>64970</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2630625257568865</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1491667964491512</v>
+        <v>0.1357241803909497</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.553259394054216</v>
@@ -4450,7 +4450,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>135.3</v>
+        <v>140.1</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>121.5</v>
+        <v>121</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.06074466419735771</v>
+        <v>-0.07319688135359792</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.008913580246913466</v>
+        <v>0.03048760330578504</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.580863562670343</v>
+        <v>2.58345476671008</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.747776312034322</v>
+        <v>2.787490368486482</v>
       </c>
       <c r="BC33" s="8" t="n">
         <v>2.682191780821918</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003874672084429483</v>
+        <v>0.003870785789965495</v>
       </c>
     </row>
     <row r="34">
@@ -4616,7 +4616,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1457</v>
+        <v>1407</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4633,7 +4633,7 @@
         <v>0.03905483371928593</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2465339739190118</v>
+        <v>0.2908315565031983</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.584569554571448</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.1820596867976914</v>
+        <v>0.1821796292724435</v>
       </c>
       <c r="AZ2" s="12" t="n">
         <v>0.8678910907040438</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>2.897426129708613</v>
+        <v>2.894619308173645</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.451167366647963</v>
+        <v>2.448544397567652</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.186301369863014</v>
+        <v>3.183561643835616</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.00345133906865321</v>
+        <v>0.003454685723874854</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8830</v>
+        <v>8905</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.003936391566222364</v>
+        <v>-0.004015070914747227</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2050649920724801</v>
+        <v>0.1949156518809656</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.662804197582399</v>
+        <v>1.660067797463994</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.669375513273708</v>
+        <v>1.666759956888764</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.682191780821918</v>
+        <v>1.679452054794521</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.006013937187877742</v>
+        <v>0.00602385036037475</v>
       </c>
     </row>
     <row r="4">
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02695838560590007</v>
+        <v>0.02694835001889034</v>
       </c>
       <c r="AZ4" s="12" t="n">
         <v>0.5086567164179103</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.305808075543283</v>
+        <v>4.30307863825204</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.19277756128636</v>
+        <v>4.19016072052006</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.682191780821918</v>
+        <v>4.67945205479452</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002322444434251347</v>
+        <v>0.002323917557793486</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6524</v>
+        <v>6628</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.02605226035312529</v>
+        <v>0.02623731623975442</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.52153586756591</v>
+        <v>1.481970428485214</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.210958904109589</v>
+        <v>0.2082191780821918</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.205602494396324</v>
+        <v>0.2028957384293231</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.1835616438356164</v>
+        <v>0.1808219178082192</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.0474025974025974</v>
+        <v>0.04802631578947368</v>
       </c>
     </row>
     <row r="6">
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21300</v>
+        <v>22170</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1171044595692895</v>
+        <v>-0.1171563904947118</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.05877934272300478</v>
+        <v>0.01723049165539026</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.463636157708626</v>
+        <v>6.460985135100352</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.320952323029534</v>
+        <v>7.318380136115887</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>6.857534246575343</v>
+        <v>6.854794520547945</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001547116786280406</v>
+        <v>0.001547751587551777</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21300</v>
+        <v>22170</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05253134499587245</v>
+        <v>-0.05261553126693773</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2642253521126761</v>
+        <v>0.214614343707713</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.872448336298782</v>
+        <v>1.869709228220901</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>1.976264150174577</v>
+        <v>1.973548532752773</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>1.854794520547945</v>
+        <v>1.852054794520548</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.005340601289842118</v>
+        <v>0.00534842522519685</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1843</v>
+        <v>1908</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04282274859857214</v>
+        <v>0.04296169815402628</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.431823237113402</v>
+        <v>3.280843933962265</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.7945205479452054</v>
+        <v>0.7917808219178082</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.761894146452928</v>
+        <v>0.7591657712063715</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.7671232876712328</v>
+        <v>0.7643835616438356</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01258620689655172</v>
+        <v>0.01262975778546713</v>
       </c>
     </row>
     <row r="9">
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>147.2</v>
+        <v>148.5</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1415059653290149</v>
+        <v>0.1416673990561705</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>4.619592391304348</v>
+        <v>4.570397306397306</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.574751943877323</v>
+        <v>1.572005862224458</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.37953895267068</v>
+        <v>1.376938558045936</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.602739726027397</v>
+        <v>1.6</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.006350206481014527</v>
+        <v>0.006361299432973842</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11530</v>
+        <v>11810</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>0.004847647701778578</v>
+        <v>0.004838272636815301</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4751084128360799</v>
+        <v>0.4401354784081286</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.026644799200488</v>
+        <v>4.023909923343403</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.007219212195964</v>
+        <v>4.004534891753461</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.191780821917808</v>
+        <v>4.189041095890411</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002483457195426215</v>
+        <v>0.00248514509283328</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1080</v>
+        <v>1111</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03984029814960437</v>
+        <v>0.03982568610358052</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5050019666666665</v>
+        <v>0.463008212421242</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.559263403175928</v>
+        <v>2.556526898483157</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.461208137182351</v>
+        <v>2.458611027453011</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.682191780821918</v>
+        <v>2.67945205479452</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003907374281049172</v>
+        <v>0.003911556731882313</v>
       </c>
     </row>
     <row r="12">
@@ -2111,7 +2111,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>-0.1424657534246575</v>
+        <v>-0.1452054794520548</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>203.3</v>
+        <v>206.9</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2208,22 +2208,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1167443136679522</v>
+        <v>-0.1168319610248402</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.0275454992621742</v>
+        <v>0.009666505558240779</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.146620113034834</v>
+        <v>4.143959992887181</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.694699595147548</v>
+        <v>4.692153486097491</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.432876712328767</v>
+        <v>4.43013698630137</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002411602637185201</v>
+        <v>0.002413150710229902</v>
       </c>
     </row>
     <row r="14">
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>233.3</v>
+        <v>239.6</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2317,22 +2317,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1965157734685486</v>
+        <v>-0.196684917293822</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.07841973853407636</v>
+        <v>0.0500639607679465</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.080422501097496</v>
+        <v>3.077739805113782</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.833830708034337</v>
+        <v>3.831298417484714</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.186301369863014</v>
+        <v>3.183561643835616</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003246307932251887</v>
+        <v>0.003249137559771824</v>
       </c>
     </row>
     <row r="15">
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>77.8</v>
+        <v>78.7</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2426,22 +2426,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1648239652391604</v>
+        <v>-0.1650922921986447</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1236246786632391</v>
+        <v>0.1107750952986024</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.9098367692474</v>
+        <v>1.907112825844704</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.286747571479705</v>
+        <v>2.284219929969137</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>1.947945205479452</v>
+        <v>1.945205479452055</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005236049572938451</v>
+        <v>0.005243528261402557</v>
       </c>
     </row>
     <row r="16">
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17750</v>
+        <v>18110</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.06145077828502106</v>
+        <v>-0.06158045516486838</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2271828867605634</v>
+        <v>0.2027883070127001</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.684470161780353</v>
+        <v>1.681733458633227</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.794759531846799</v>
+        <v>1.792091253735222</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.682191780821918</v>
+        <v>1.679452054794521</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005936584824649422</v>
+        <v>0.005946245493698607</v>
       </c>
     </row>
     <row r="17">
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.07259064193172297</v>
+        <v>0.07260964410134219</v>
       </c>
       <c r="AZ17" s="12" t="n">
         <v>0.8984967320261439</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.92166018465868</v>
+        <v>2.918909786139122</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.723928468550504</v>
+        <v>2.721315999899157</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.186301369863014</v>
+        <v>3.183561643835616</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003422711529735358</v>
+        <v>0.003425936645074297</v>
       </c>
     </row>
     <row r="18">
@@ -2795,22 +2795,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1103369053691986</v>
+        <v>0.1104299663493276</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>3.367999999999999</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.656631314767486</v>
+        <v>1.653887591185815</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.49200779219046</v>
+        <v>1.489411886661497</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.682191780821918</v>
+        <v>1.679452054794521</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.006036346114466353</v>
+        <v>0.006046360135533839</v>
       </c>
     </row>
     <row r="19">
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>158.6</v>
+        <v>162.6</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2904,22 +2904,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.01730608569508603</v>
+        <v>0.01728380311422285</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.453846153846154</v>
+        <v>0.4180811808118083</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.124344656268637</v>
+        <v>3.121616319793711</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.071194304449573</v>
+        <v>3.068579594246434</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.347945205479452</v>
+        <v>3.345205479452055</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003200671212740935</v>
+        <v>0.003203468644301821</v>
       </c>
     </row>
     <row r="20">
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27770</v>
+        <v>28530</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5870971939259892</v>
+        <v>-0.5878396190565787</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.006999391213539763</v>
+        <v>-0.01982568895899062</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.361481434221098</v>
+        <v>1.358761483003065</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.297341200381815</v>
+        <v>3.296681451751636</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.345205479452055</v>
+        <v>1.342465753424658</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.007344940407300512</v>
+        <v>0.007359643414308823</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>493</v>
+        <v>495.8</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3124,22 +3124,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03419899117402514</v>
+        <v>0.0341902567623044</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.3644990385395537</v>
+        <v>0.3567931141589349</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.7095890410958905</v>
+        <v>0.706849315068493</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.6861242828039925</v>
+        <v>0.6834809266927308</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.6821917808219178</v>
+        <v>0.6794520547945205</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01409266409266409</v>
+        <v>0.01414728682170543</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.0325640479636857</v>
+        <v>0.01760514610515645</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.004489795918367401</v>
+        <v>0.01199999999999979</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.898367304425482</v>
+        <v>1.896487057015129</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.838498355786493</v>
+        <v>1.863676755442775</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>1.947945205479452</v>
+        <v>1.945205479452055</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005267684486920923</v>
+        <v>0.00527290706414783</v>
       </c>
     </row>
     <row r="23">
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10210</v>
+        <v>10450</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02906100274512852</v>
+        <v>0.0290763676115322</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5598654581782567</v>
+        <v>0.5240407969377991</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.248267564785691</v>
+        <v>4.245525479701754</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.128295167587724</v>
+        <v>4.125568921143862</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.273972602739726</v>
+        <v>4.271232876712329</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002353900701286093</v>
+        <v>0.002355421030402695</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3477,22 +3477,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.2169416842912569</v>
+        <v>0.2170808754769724</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.2969052777777779</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.806198262648878</v>
+        <v>2.803364443878886</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.30594308574712</v>
+        <v>2.303350993647198</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.186301369863014</v>
+        <v>3.183561643835616</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003563540086636864</v>
+        <v>0.00356714233921133</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3586,22 +3586,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.4374051666127835</v>
+        <v>0.4377667849391939</v>
       </c>
       <c r="AZ25" s="12" t="n">
         <v>0.3506944444444444</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>2.68392983014807</v>
+        <v>2.680926358472093</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>1.867204802437643</v>
+        <v>1.864646190574972</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.186301369863014</v>
+        <v>3.183561643835616</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003725879822815005</v>
+        <v>0.003730053967502179</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3685,7 +3685,7 @@
         <v>0.55865</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AK26" s="10" t="n">
         <v>46377</v>
@@ -3699,22 +3699,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>95.2309503997147</v>
+        <v>96.4260780596431</v>
       </c>
       <c r="AZ26" s="12" t="n">
-        <v>0.1761052631578948</v>
+        <v>0.1173</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.210958904109589</v>
+        <v>0.2082191780821918</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.002192214700502578</v>
+        <v>0.002137201683872797</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.1835616438356164</v>
+        <v>0.1808219178082192</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.0474025974025974</v>
+        <v>0.04802631578947369</v>
       </c>
     </row>
     <row r="27">
@@ -3808,22 +3808,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.0558153646992192</v>
+        <v>0.05619963465909845</v>
       </c>
       <c r="AZ27" s="12" t="n">
         <v>0.5781734607508533</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.2054794520547945</v>
+        <v>0.2027397260273973</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.1946168420397363</v>
+        <v>0.1919520887666601</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.1835616438356164</v>
+        <v>0.1808219178082192</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.04866666666666667</v>
+        <v>0.04932432432432433</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>11900</v>
+        <v>11950</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3938,15 +3938,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-3.696686459704526</v>
+        <v>-3.745357437623008</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.04074786218487403</v>
+        <v>0.03639326861924674</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.1835616438356164</v>
+        <v>0.1808219178082192</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>133</v>
+        <v>137.8</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14330</v>
+        <v>15070</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4059,22 +4059,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.05866307088989309</v>
+        <v>-0.07142474116015102</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.06826936496859726</v>
+        <v>0.05247378898473798</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.590716056923219</v>
+        <v>2.590439355480434</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>2.752166601359572</v>
+        <v>2.789692414071961</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.682191780821918</v>
+        <v>2.67945205479452</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003859936704864592</v>
+        <v>0.003860349009461893</v>
       </c>
     </row>
     <row r="30">
@@ -4189,22 +4189,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.06062093655987117</v>
+        <v>0.06062545362438981</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.8225918460955266</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.554658571653338</v>
+        <v>2.551917839590411</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.408644298442179</v>
+        <v>2.406049968789593</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.682191780821918</v>
+        <v>2.67945205479452</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003914417414115792</v>
+        <v>0.003918621455934108</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4303,22 +4303,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.08059495938947277</v>
+        <v>0.08061580172941352</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>-0.4242186098971723</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.099804638537972</v>
+        <v>2.097059701056295</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>1.943193071828083</v>
+        <v>1.94061543214542</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.254794520547945</v>
+        <v>2.252054794520548</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004762347799632772</v>
+        <v>0.004768581454768774</v>
       </c>
     </row>
     <row r="32">
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>64970</v>
+        <v>66000</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4412,22 +4412,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2630625257568865</v>
+        <v>-0.2634899417809036</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1357241803909497</v>
+        <v>0.1180000000000001</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.553259394054216</v>
+        <v>1.550535213636878</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.107722090872802</v>
+        <v>2.105246488264015</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.556164383561644</v>
+        <v>1.553424657534247</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.006438074695237253</v>
+        <v>0.006449385935933934</v>
       </c>
     </row>
     <row r="33">
@@ -4521,22 +4521,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.07319688135359792</v>
+        <v>-0.07330985338059916</v>
       </c>
       <c r="AZ33" s="12" t="n">
         <v>0.03048760330578504</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.58345476671008</v>
+        <v>2.580738462745228</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.787490368486482</v>
+        <v>2.784899000124103</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.682191780821918</v>
+        <v>2.67945205479452</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003870785789965495</v>
+        <v>0.003874859907099081</v>
       </c>
     </row>
     <row r="34">
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03905483371928593</v>
+        <v>0.03904483589253448</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.2908315565031983</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.584569554571448</v>
+        <v>1.581830222985229</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.525010522206511</v>
+        <v>1.522388802044759</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.602739726027397</v>
+        <v>1.6</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.006310862133599769</v>
+        <v>0.006321790957520085</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>620.7</v>
+        <v>633.5</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.1821796292724435</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.8678910907040438</v>
+        <v>0.8301499605367011</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>2.894619308173645</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8905</v>
+        <v>8890</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.004015070914747227</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1949156518809656</v>
+        <v>0.1969318200224972</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.660067797463994</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>80.40000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.02694835001889034</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.5086567164179103</v>
+        <v>0.5124189526184539</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.30307863825204</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6628</v>
+        <v>6588</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.02623731623975442</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.481970428485214</v>
+        <v>1.497040072859745</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2082191780821918</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>281.9</v>
+        <v>292.8</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>22170</v>
+        <v>22600</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1171563904947118</v>
+        <v>-0.1223127317531069</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.01723049165539026</v>
+        <v>0.03646017699115034</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.460985135100352</v>
+        <v>6.469718072643116</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.318380136115887</v>
+        <v>7.371324965856958</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.854794520547945</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001547751587551777</v>
+        <v>0.001545662405643997</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>112.2</v>
+        <v>113.8</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22170</v>
+        <v>22600</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05261553126693773</v>
+        <v>-0.05975716492910126</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.214614343707713</v>
+        <v>0.208495575221239</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.869709228220901</v>
+        <v>1.869761652502748</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>1.973548532752773</v>
+        <v>1.988594417060098</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>1.852054794520548</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.00534842522519685</v>
+        <v>0.005348275266323178</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1908</v>
+        <v>1912</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04296169815402628</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.280843933962265</v>
+        <v>3.271888193514645</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.7917808219178082</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>148.5</v>
+        <v>148.9</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1416673990561705</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>4.570397306397306</v>
+        <v>4.555433176628609</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.572005862224458</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106.3</v>
+        <v>106.1</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11810</v>
+        <v>11970</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>0.004838272636815301</v>
+        <v>0.005301760740768336</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4401354784081286</v>
+        <v>0.4182121971595656</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.023909923343403</v>
+        <v>4.023670030918289</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.004534891753461</v>
+        <v>4.002449998648566</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.189041095890411</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.00248514509283328</v>
+        <v>0.00248529325793591</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103.8</v>
+        <v>103.4</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03982568610358052</v>
+        <v>0.04137327647775295</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.463008212421242</v>
+        <v>0.4534457199281869</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.556526898483157</v>
+        <v>2.556185590318328</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.458611027453011</v>
+        <v>2.454629524356664</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.67945205479452</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003911556731882313</v>
+        <v>0.003912079012523765</v>
       </c>
     </row>
     <row r="12">
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>206.9</v>
+        <v>205</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2211,7 +2211,7 @@
         <v>-0.1168319610248402</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.009666505558240779</v>
+        <v>0.01902439024390246</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.143959992887181</v>
@@ -2303,7 +2303,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>239.6</v>
+        <v>243.3</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2320,7 +2320,7 @@
         <v>-0.196684917293822</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.0500639607679465</v>
+        <v>0.03409504726674872</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.077739805113782</v>
@@ -2412,7 +2412,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>78.7</v>
+        <v>78.8</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2429,7 +2429,7 @@
         <v>-0.1650922921986447</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1107750952986024</v>
+        <v>0.1093654822335026</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.907112825844704</v>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>116.1</v>
+        <v>116.5</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18110</v>
+        <v>18090</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2535,22 +2535,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.06158045516486838</v>
+        <v>-0.06348556514145465</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2027883070127001</v>
+        <v>0.2082666445550028</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.681733458633227</v>
+        <v>1.681777870549964</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.792091253735222</v>
+        <v>1.795784248433913</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.679452054794521</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005946245493698607</v>
+        <v>0.005946088466920941</v>
       </c>
     </row>
     <row r="17">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>93.7</v>
+        <v>96.5</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2651,7 +2651,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>76.5</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2665,22 +2665,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.07260964410134219</v>
+        <v>0.06228239229774665</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8984967320261439</v>
+        <v>0.9200898587933248</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>2.918909786139122</v>
+        <v>2.924680693715155</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.721315999899157</v>
+        <v>2.753204529154426</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.183561643835616</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003425936645074297</v>
+        <v>0.003419176671658208</v>
       </c>
     </row>
     <row r="18">
@@ -2781,7 +2781,7 @@
         <v>4.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>87.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="AK18" s="10" t="n">
         <v>46924</v>
@@ -2798,7 +2798,7 @@
         <v>0.1104299663493276</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>3.367999999999999</v>
+        <v>3.464953271028038</v>
       </c>
       <c r="BA18" s="8" t="n">
         <v>1.653887591185815</v>
@@ -2890,7 +2890,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>162.6</v>
+        <v>160.6</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2907,7 +2907,7 @@
         <v>0.01728380311422285</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4180811808118083</v>
+        <v>0.4357409713574099</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.121616319793711</v>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>348.3</v>
+        <v>359.6</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2999,7 +2999,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>28530</v>
+        <v>28790</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3013,22 +3013,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5878396190565787</v>
+        <v>-0.5973638302181619</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.01982568895899062</v>
+        <v>0.002835343105245025</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.358761483003065</v>
+        <v>1.359015234590237</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.296681451751636</v>
+        <v>3.375293469850455</v>
       </c>
       <c r="BC20" s="8" t="n">
         <v>1.342465753424658</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.007359643414308823</v>
+        <v>0.007358269241930275</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3110,7 +3110,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>495.8</v>
+        <v>499.5</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3127,7 +3127,7 @@
         <v>0.0341902567623044</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.3567931141589349</v>
+        <v>0.3467427947947945</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.706849315068493</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>110</v>
+        <v>108.8</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3242,7 +3242,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>250</v>
+        <v>248.4</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3259,22 +3259,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.01760514610515645</v>
+        <v>0.02349289484934595</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.01199999999999979</v>
+        <v>0.007407407407407307</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.896487057015129</v>
+        <v>1.896148582387873</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.863676755442775</v>
+        <v>1.85262505673474</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>1.945205479452055</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.00527290706414783</v>
+        <v>0.005273848311721817</v>
       </c>
     </row>
     <row r="23">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>90.40000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3354,7 +3354,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10450</v>
+        <v>10410</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3368,22 +3368,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.0290763676115322</v>
+        <v>0.02880945527375952</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.5240407969377991</v>
+        <v>0.531589225264169</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.245525479701754</v>
+        <v>4.24556644901181</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.125568921143862</v>
+        <v>4.126679072833844</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.271232876712329</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002355421030402695</v>
+        <v>0.002355398300815096</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3463,7 +3463,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>32.4</v>
+        <v>30.1</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3480,7 +3480,7 @@
         <v>0.2170808754769724</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.2969052777777779</v>
+        <v>0.3960043521594683</v>
       </c>
       <c r="BA24" s="8" t="n">
         <v>2.803364443878886</v>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>28.8</v>
+        <v>29.2</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3589,7 +3589,7 @@
         <v>0.4377667849391939</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.3506944444444444</v>
+        <v>0.3321917808219177</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>2.680926358472093</v>
@@ -3685,7 +3685,7 @@
         <v>0.55865</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AK26" s="10" t="n">
         <v>46377</v>
@@ -3702,7 +3702,7 @@
         <v>96.4260780596431</v>
       </c>
       <c r="AZ26" s="12" t="n">
-        <v>0.1173</v>
+        <v>0.1761052631578948</v>
       </c>
       <c r="BA26" s="8" t="n">
         <v>0.2082191780821918</v>
@@ -3794,7 +3794,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1172</v>
+        <v>1193</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3811,7 +3811,7 @@
         <v>0.05619963465909845</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5781734607508533</v>
+        <v>0.5503933746856664</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.2027397260273973</v>
@@ -3921,7 +3921,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>11950</v>
+        <v>12090</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3941,7 +3941,7 @@
         <v>-3.745357437623008</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.03639326861924674</v>
+        <v>0.02439202315963596</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4045,7 +4045,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15070</v>
+        <v>15140</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4062,7 +4062,7 @@
         <v>-0.07142474116015102</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.05247378898473798</v>
+        <v>0.04760766182298548</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.590439355480434</v>
@@ -4175,7 +4175,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>527.6</v>
+        <v>532.9</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4192,7 +4192,7 @@
         <v>0.06062545362438981</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.8225918460955266</v>
+        <v>0.8044651116532182</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.551917839590411</v>
@@ -4398,7 +4398,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>66000</v>
+        <v>65120</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4415,7 +4415,7 @@
         <v>-0.2634899417809036</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1180000000000001</v>
+        <v>0.133108108108108</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.550535213636878</v>
@@ -4507,7 +4507,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4524,7 +4524,7 @@
         <v>-0.07330985338059916</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.03048760330578504</v>
+        <v>0.01373170731707307</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.580738462745228</v>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100.9</v>
+        <v>102</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -4630,22 +4630,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03904483589253448</v>
+        <v>0.03206336179055898</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2908315565031983</v>
+        <v>0.3049040511727079</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.581830222985229</v>
+        <v>1.582105740328933</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.522388802044759</v>
+        <v>1.532954079082982</v>
       </c>
       <c r="BC34" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.006321790957520085</v>
+        <v>0.006320690043082024</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>620.7</v>
+        <v>635.4</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.1821796292724435</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.8678910907040438</v>
+        <v>0.8246773685867173</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>2.894619308173645</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>109</v>
+        <v>110.1</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8905</v>
+        <v>8920</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.004015070914747227</v>
+        <v>-0.009943369788166142</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1949156518809656</v>
+        <v>0.2049447681614349</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.660067797463994</v>
+        <v>1.660318463256142</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.666759956888764</v>
+        <v>1.676993429053546</v>
       </c>
       <c r="BC3" s="8" t="n">
         <v>1.679452054794521</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.00602385036037475</v>
+        <v>0.006022940912424987</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>108.3</v>
+        <v>108.2</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>80.40000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02694835001889034</v>
+        <v>0.02716610702465719</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.5086567164179103</v>
+        <v>0.5091407222914075</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.30307863825204</v>
+        <v>4.302855352191287</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.19016072052006</v>
+        <v>4.189055034784161</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.67945205479452</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002323917557793486</v>
+        <v>0.002324038151760636</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6628</v>
+        <v>6579</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.02623731623975442</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.481970428485214</v>
+        <v>1.500455996352029</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.2082191780821918</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>281.9</v>
+        <v>291.3</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>22170</v>
+        <v>22250</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1171563904947118</v>
+        <v>-0.1216167976891737</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.01723049165539026</v>
+        <v>0.047370786516854</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.460985135100352</v>
+        <v>6.468548021389617</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.318380136115887</v>
+        <v>7.364152689136517</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>6.854794520547945</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001547751587551777</v>
+        <v>0.00154594198990761</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>112.2</v>
+        <v>113.8</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22170</v>
+        <v>22250</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.05261553126693773</v>
+        <v>-0.05975716492910126</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.214614343707713</v>
+        <v>0.2275056179775281</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>1.869709228220901</v>
+        <v>1.869761652502748</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>1.973548532752773</v>
+        <v>1.988594417060098</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>1.852054794520548</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.00534842522519685</v>
+        <v>0.005348275266323178</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1908</v>
+        <v>1899</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04296169815402628</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.280843933962265</v>
+        <v>3.301132293838863</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.7917808219178082</v>
@@ -1712,7 +1712,7 @@
         <v